--- a/data.xlsx
+++ b/data.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="territory-wise-MPE-sales-achiev" sheetId="1" r:id="rId1"/>
     <sheet name="territory-wise-ASE-sales-achiev" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'territory-wise-ASE-sales-achiev'!$A$1:$L$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'territory-wise-ASE-sales-achiev'!$A$1:$L$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'territory-wise-ASE-sales-achiev'!$A$1:$L$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'territory-wise-MPE-sales-achiev'!$A$1:$M$52</definedName>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="741" count="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1028" count="1028">
   <si>
     <t>Region</t>
   </si>
@@ -6804,6 +6805,2589 @@
         <rFont val="Helvetica"/>
       </rPr>
       <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
     </r>
   </si>
 </sst>
@@ -6815,7 +9399,7 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -6823,11 +9407,6 @@
     <font>
       <name val="Helvetica"/>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <name val="Helvetica"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
     </font>
@@ -6892,10 +9471,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7196,7 +9775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -7257,40 +9836,40 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>454</v>
+        <v>773</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>455</v>
+        <v>774</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>456</v>
+        <v>775</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>457</v>
+        <v>776</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>458</v>
+        <v>777</v>
       </c>
       <c r="F2" s="3">
         <v>747825.09</v>
       </c>
       <c r="G2" s="3">
-        <v>404509.45</v>
+        <v>420744.84</v>
       </c>
       <c r="H2" s="3">
-        <v>205428.84</v>
+        <v>197496.99</v>
       </c>
       <c r="I2" s="3">
-        <v>609938.29</v>
+        <v>618241.83</v>
       </c>
       <c r="J2" s="3">
-        <v>81.56</v>
+        <v>82.67</v>
       </c>
       <c r="K2" s="3">
-        <v>-137886.8</v>
+        <v>-129583.26</v>
       </c>
       <c r="L2" s="3">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="M2" s="3">
         <v>11070.38</v>
@@ -7298,40 +9877,40 @@
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>459</v>
+        <v>778</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>460</v>
+        <v>779</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>461</v>
+        <v>780</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>462</v>
+        <v>781</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>463</v>
+        <v>782</v>
       </c>
       <c r="F3" s="3">
         <v>755003.49</v>
       </c>
       <c r="G3" s="3">
-        <v>289313.83</v>
+        <v>312089.38</v>
       </c>
       <c r="H3" s="3">
-        <v>272360.41</v>
+        <v>295793.85</v>
       </c>
       <c r="I3" s="3">
-        <v>561674.24</v>
+        <v>607883.23</v>
       </c>
       <c r="J3" s="3">
-        <v>74.39</v>
+        <v>80.51</v>
       </c>
       <c r="K3" s="3">
-        <v>-193329.25</v>
+        <v>-147120.26</v>
       </c>
       <c r="L3" s="3">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="M3" s="3">
         <v>7607.09</v>
@@ -7339,204 +9918,204 @@
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>464</v>
+        <v>783</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>465</v>
+        <v>784</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>466</v>
+        <v>785</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>467</v>
+        <v>786</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>468</v>
+        <v>787</v>
       </c>
       <c r="F4" s="3">
         <v>664724.91</v>
       </c>
       <c r="G4" s="3">
-        <v>351788.5</v>
+        <v>386158.7</v>
       </c>
       <c r="H4" s="3">
-        <v>229164.56</v>
+        <v>209776.75</v>
       </c>
       <c r="I4" s="3">
-        <v>580953.06</v>
+        <v>595935.45</v>
       </c>
       <c r="J4" s="3">
-        <v>87.4</v>
+        <v>89.65</v>
       </c>
       <c r="K4" s="3">
-        <v>-83771.85</v>
+        <v>-68789.46</v>
       </c>
       <c r="L4" s="3">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="M4" s="3">
-        <v>11324.33</v>
+        <v>13467.47</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>469</v>
+        <v>788</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>470</v>
+        <v>789</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>471</v>
+        <v>790</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>472</v>
+        <v>791</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>473</v>
+        <v>792</v>
       </c>
       <c r="F5" s="3">
         <v>745422.79</v>
       </c>
       <c r="G5" s="3">
-        <v>283498.8</v>
+        <v>307011.19</v>
       </c>
       <c r="H5" s="3">
-        <v>212004.63</v>
+        <v>201600.89</v>
       </c>
       <c r="I5" s="3">
-        <v>495503.43</v>
+        <v>508612.08</v>
       </c>
       <c r="J5" s="3">
-        <v>66.47</v>
+        <v>68.23</v>
       </c>
       <c r="K5" s="3">
-        <v>-249919.36</v>
+        <v>-236810.71</v>
       </c>
       <c r="L5" s="3">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="M5" s="3">
-        <v>15886.83</v>
+        <v>16830.93</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>474</v>
+        <v>793</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>475</v>
+        <v>794</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>476</v>
+        <v>795</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>477</v>
+        <v>796</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>478</v>
+        <v>797</v>
       </c>
       <c r="F6" s="3">
         <v>750633.4</v>
       </c>
       <c r="G6" s="3">
-        <v>446598.75</v>
+        <v>480931.58</v>
       </c>
       <c r="H6" s="3">
-        <v>240267.68</v>
+        <v>231933.53</v>
       </c>
       <c r="I6" s="3">
-        <v>686866.43</v>
+        <v>712865.11</v>
       </c>
       <c r="J6" s="3">
-        <v>91.5</v>
+        <v>94.97</v>
       </c>
       <c r="K6" s="3">
-        <v>-63766.97</v>
+        <v>-37768.29</v>
       </c>
       <c r="L6" s="3">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="M6" s="3">
-        <v>18240.25</v>
+        <v>18699.25</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>479</v>
+        <v>798</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>480</v>
+        <v>799</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>481</v>
+        <v>800</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>482</v>
+        <v>801</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>483</v>
+        <v>802</v>
       </c>
       <c r="F7" s="3">
         <v>804591.82</v>
       </c>
       <c r="G7" s="3">
-        <v>277521.02</v>
+        <v>301246.41</v>
       </c>
       <c r="H7" s="3">
-        <v>208388.55</v>
+        <v>207832.56</v>
       </c>
       <c r="I7" s="3">
-        <v>485909.57</v>
+        <v>509078.97</v>
       </c>
       <c r="J7" s="3">
-        <v>60.39</v>
+        <v>63.27</v>
       </c>
       <c r="K7" s="3">
-        <v>-318682.25</v>
+        <v>-295512.85</v>
       </c>
       <c r="L7" s="3">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M7" s="3">
-        <v>8655.93</v>
+        <v>9218.43</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>484</v>
+        <v>803</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>485</v>
+        <v>804</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>486</v>
+        <v>805</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>487</v>
+        <v>806</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>488</v>
+        <v>807</v>
       </c>
       <c r="F8" s="3">
         <v>726832.71</v>
       </c>
       <c r="G8" s="3">
-        <v>250283.51</v>
+        <v>271531.42</v>
       </c>
       <c r="H8" s="3">
-        <v>174750.6</v>
+        <v>162611.43</v>
       </c>
       <c r="I8" s="3">
-        <v>425034.11</v>
+        <v>434142.85</v>
       </c>
       <c r="J8" s="3">
-        <v>58.48</v>
+        <v>59.73</v>
       </c>
       <c r="K8" s="3">
-        <v>-301798.6</v>
+        <v>-292689.86</v>
       </c>
       <c r="L8" s="3">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="M8" s="3">
         <v>2474.76</v>
@@ -7544,122 +10123,122 @@
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>489</v>
+        <v>808</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>490</v>
+        <v>809</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>491</v>
+        <v>810</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>492</v>
+        <v>811</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>493</v>
+        <v>812</v>
       </c>
       <c r="F9" s="3">
         <v>741741.03</v>
       </c>
       <c r="G9" s="3">
-        <v>342920.84</v>
+        <v>375630.68</v>
       </c>
       <c r="H9" s="3">
-        <v>215503.46</v>
+        <v>202357.22</v>
       </c>
       <c r="I9" s="3">
-        <v>558424.3</v>
+        <v>577987.9</v>
       </c>
       <c r="J9" s="3">
-        <v>75.29</v>
+        <v>77.92</v>
       </c>
       <c r="K9" s="3">
-        <v>-183316.73</v>
+        <v>-163753.13</v>
       </c>
       <c r="L9" s="3">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="M9" s="3">
-        <v>10546.35</v>
+        <v>11040.03</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>494</v>
+        <v>813</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>495</v>
+        <v>814</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>496</v>
+        <v>815</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>497</v>
+        <v>816</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>498</v>
+        <v>817</v>
       </c>
       <c r="F10" s="3">
         <v>859984.15</v>
       </c>
       <c r="G10" s="3">
-        <v>369562.7</v>
+        <v>406200.33</v>
       </c>
       <c r="H10" s="3">
-        <v>259460.28</v>
+        <v>233886.44</v>
       </c>
       <c r="I10" s="3">
-        <v>629022.98</v>
+        <v>640086.77</v>
       </c>
       <c r="J10" s="3">
-        <v>73.14</v>
+        <v>74.43</v>
       </c>
       <c r="K10" s="3">
-        <v>-230961.17</v>
+        <v>-219897.38</v>
       </c>
       <c r="L10" s="3">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="M10" s="3">
-        <v>11957.56</v>
+        <v>14805.16</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>499</v>
+        <v>818</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>500</v>
+        <v>819</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>501</v>
+        <v>820</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>502</v>
+        <v>821</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>503</v>
+        <v>822</v>
       </c>
       <c r="F11" s="3">
         <v>903047.31</v>
       </c>
       <c r="G11" s="3">
-        <v>325558.4</v>
+        <v>349592.06</v>
       </c>
       <c r="H11" s="3">
-        <v>194612.0</v>
+        <v>185884.86</v>
       </c>
       <c r="I11" s="3">
-        <v>520170.4</v>
+        <v>535476.92</v>
       </c>
       <c r="J11" s="3">
-        <v>57.6</v>
+        <v>59.3</v>
       </c>
       <c r="K11" s="3">
-        <v>-382876.91</v>
+        <v>-367570.39</v>
       </c>
       <c r="L11" s="3">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="M11" s="3">
         <v>11612.29</v>
@@ -7667,81 +10246,81 @@
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>504</v>
+        <v>823</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>505</v>
+        <v>824</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>506</v>
+        <v>825</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>507</v>
+        <v>826</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>508</v>
+        <v>827</v>
       </c>
       <c r="F12" s="3">
         <v>775221.33</v>
       </c>
       <c r="G12" s="3">
-        <v>357478.27</v>
+        <v>392186.34</v>
       </c>
       <c r="H12" s="3">
-        <v>222624.27</v>
+        <v>201757.37</v>
       </c>
       <c r="I12" s="3">
-        <v>580102.54</v>
+        <v>593943.71</v>
       </c>
       <c r="J12" s="3">
-        <v>74.83</v>
+        <v>76.62</v>
       </c>
       <c r="K12" s="3">
-        <v>-195118.79</v>
+        <v>-181277.62</v>
       </c>
       <c r="L12" s="3">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="M12" s="3">
-        <v>6606.72</v>
+        <v>7251.66</v>
       </c>
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>509</v>
+        <v>828</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>510</v>
+        <v>829</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>511</v>
+        <v>830</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>512</v>
+        <v>831</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>513</v>
+        <v>832</v>
       </c>
       <c r="F13" s="3">
         <v>808635.23</v>
       </c>
       <c r="G13" s="3">
-        <v>388358.73</v>
+        <v>415158.68</v>
       </c>
       <c r="H13" s="3">
-        <v>233595.67</v>
+        <v>221821.15</v>
       </c>
       <c r="I13" s="3">
-        <v>621954.4</v>
+        <v>636979.83</v>
       </c>
       <c r="J13" s="3">
-        <v>76.91</v>
+        <v>78.77</v>
       </c>
       <c r="K13" s="3">
-        <v>-186680.83</v>
+        <v>-171655.4</v>
       </c>
       <c r="L13" s="3">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M13" s="3">
         <v>8334.11</v>
@@ -7749,40 +10328,40 @@
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>514</v>
+        <v>833</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>515</v>
+        <v>834</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>516</v>
+        <v>835</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>517</v>
+        <v>836</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>518</v>
+        <v>837</v>
       </c>
       <c r="F14" s="3">
         <v>773239.07</v>
       </c>
       <c r="G14" s="3">
-        <v>293420.36</v>
+        <v>322969.62</v>
       </c>
       <c r="H14" s="3">
-        <v>288293.87</v>
+        <v>268899.01</v>
       </c>
       <c r="I14" s="3">
-        <v>581714.23</v>
+        <v>591868.63</v>
       </c>
       <c r="J14" s="3">
-        <v>75.23</v>
+        <v>76.54</v>
       </c>
       <c r="K14" s="3">
-        <v>-191524.84</v>
+        <v>-181370.44</v>
       </c>
       <c r="L14" s="3">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M14" s="3">
         <v>8112.85</v>
@@ -7790,40 +10369,40 @@
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>519</v>
+        <v>838</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>520</v>
+        <v>839</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>521</v>
+        <v>840</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>522</v>
+        <v>841</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>523</v>
+        <v>842</v>
       </c>
       <c r="F15" s="3">
         <v>788718.67</v>
       </c>
       <c r="G15" s="3">
-        <v>213296.79</v>
+        <v>232096.88</v>
       </c>
       <c r="H15" s="3">
-        <v>251298.19</v>
+        <v>241863.83</v>
       </c>
       <c r="I15" s="3">
-        <v>464594.98</v>
+        <v>473960.71</v>
       </c>
       <c r="J15" s="3">
-        <v>58.91</v>
+        <v>60.09</v>
       </c>
       <c r="K15" s="3">
-        <v>-324123.69</v>
+        <v>-314757.96</v>
       </c>
       <c r="L15" s="3">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="M15" s="3">
         <v>11703.66</v>
@@ -7831,81 +10410,81 @@
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>524</v>
+        <v>843</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>525</v>
+        <v>844</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>526</v>
+        <v>845</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>527</v>
+        <v>846</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>528</v>
+        <v>847</v>
       </c>
       <c r="F16" s="3">
         <v>757031.95</v>
       </c>
       <c r="G16" s="3">
-        <v>178752.56</v>
+        <v>200093.93</v>
       </c>
       <c r="H16" s="3">
-        <v>164169.21</v>
+        <v>150712.4</v>
       </c>
       <c r="I16" s="3">
-        <v>342921.77</v>
+        <v>350806.33</v>
       </c>
       <c r="J16" s="3">
-        <v>45.3</v>
+        <v>46.34</v>
       </c>
       <c r="K16" s="3">
-        <v>-414110.18</v>
+        <v>-406225.62</v>
       </c>
       <c r="L16" s="3">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M16" s="3">
-        <v>4999.74</v>
+        <v>5337.74</v>
       </c>
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>529</v>
+        <v>848</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>530</v>
+        <v>849</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>531</v>
+        <v>850</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>532</v>
+        <v>851</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>533</v>
+        <v>852</v>
       </c>
       <c r="F17" s="3">
         <v>792097.85</v>
       </c>
       <c r="G17" s="3">
-        <v>230802.54</v>
+        <v>249065.85</v>
       </c>
       <c r="H17" s="3">
-        <v>222398.75</v>
+        <v>212124.65</v>
       </c>
       <c r="I17" s="3">
-        <v>453201.29</v>
+        <v>461190.5</v>
       </c>
       <c r="J17" s="3">
-        <v>57.22</v>
+        <v>58.22</v>
       </c>
       <c r="K17" s="3">
-        <v>-338896.56</v>
+        <v>-330907.35</v>
       </c>
       <c r="L17" s="3">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="M17" s="3">
         <v>12960.73</v>
@@ -7913,634 +10492,634 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>534</v>
+        <v>853</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>535</v>
+        <v>854</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>536</v>
+        <v>855</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>537</v>
+        <v>856</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>538</v>
+        <v>857</v>
       </c>
       <c r="F18" s="3">
         <v>1027095.81</v>
       </c>
       <c r="G18" s="3">
-        <v>514456.32</v>
+        <v>595477.93</v>
       </c>
       <c r="H18" s="3">
-        <v>171443.11</v>
+        <v>85029.9</v>
       </c>
       <c r="I18" s="3">
-        <v>685899.43</v>
+        <v>680507.83</v>
       </c>
       <c r="J18" s="3">
-        <v>66.78</v>
+        <v>66.26</v>
       </c>
       <c r="K18" s="3">
-        <v>-341196.38</v>
+        <v>-346587.98</v>
       </c>
       <c r="L18" s="3">
-        <v>5.39</v>
+        <v>6.22</v>
       </c>
       <c r="M18" s="3">
-        <v>36938.03</v>
+        <v>42329.63</v>
       </c>
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>539</v>
+        <v>858</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>540</v>
+        <v>859</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>541</v>
+        <v>860</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>542</v>
+        <v>861</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>543</v>
+        <v>862</v>
       </c>
       <c r="F19" s="3">
         <v>863850.75</v>
       </c>
       <c r="G19" s="3">
-        <v>508523.71</v>
+        <v>586071.53</v>
       </c>
       <c r="H19" s="3">
-        <v>166053.25</v>
+        <v>81681.74</v>
       </c>
       <c r="I19" s="3">
-        <v>674576.96</v>
+        <v>667753.27</v>
       </c>
       <c r="J19" s="3">
-        <v>78.09</v>
+        <v>77.3</v>
       </c>
       <c r="K19" s="3">
-        <v>-189273.79</v>
+        <v>-196097.48</v>
       </c>
       <c r="L19" s="3">
-        <v>4.32</v>
+        <v>5.39</v>
       </c>
       <c r="M19" s="3">
-        <v>29145.97</v>
+        <v>35969.66</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>544</v>
+        <v>863</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>545</v>
+        <v>864</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>546</v>
+        <v>865</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>547</v>
+        <v>866</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>548</v>
+        <v>867</v>
       </c>
       <c r="F20" s="3">
         <v>1246040.32</v>
       </c>
       <c r="G20" s="3">
-        <v>545106.56</v>
+        <v>624262.57</v>
       </c>
       <c r="H20" s="3">
-        <v>230952.84</v>
+        <v>148685.31</v>
       </c>
       <c r="I20" s="3">
-        <v>776059.4</v>
+        <v>772947.88</v>
       </c>
       <c r="J20" s="3">
-        <v>62.28</v>
+        <v>62.03</v>
       </c>
       <c r="K20" s="3">
-        <v>-469980.92</v>
+        <v>-473092.44</v>
       </c>
       <c r="L20" s="3">
-        <v>5.03</v>
+        <v>5.45</v>
       </c>
       <c r="M20" s="3">
-        <v>39028.23</v>
+        <v>42139.75</v>
       </c>
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>549</v>
+        <v>868</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>550</v>
+        <v>869</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>551</v>
+        <v>870</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>552</v>
+        <v>871</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>553</v>
+        <v>872</v>
       </c>
       <c r="F21" s="3">
         <v>875303.02</v>
       </c>
       <c r="G21" s="3">
-        <v>582489.14</v>
+        <v>620068.84</v>
       </c>
       <c r="H21" s="3">
-        <v>131178.39</v>
+        <v>120786.92</v>
       </c>
       <c r="I21" s="3">
-        <v>713667.53</v>
+        <v>740855.76</v>
       </c>
       <c r="J21" s="3">
-        <v>81.53</v>
+        <v>84.64</v>
       </c>
       <c r="K21" s="3">
-        <v>-161635.49</v>
+        <v>-134447.26</v>
       </c>
       <c r="L21" s="3">
         <v>1.77</v>
       </c>
       <c r="M21" s="3">
-        <v>12601.47</v>
+        <v>13141.47</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>554</v>
+        <v>873</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>555</v>
+        <v>874</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>556</v>
+        <v>875</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>557</v>
+        <v>876</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>558</v>
+        <v>877</v>
       </c>
       <c r="F22" s="3">
         <v>859661.34</v>
       </c>
       <c r="G22" s="3">
-        <v>571669.64</v>
+        <v>602858.92</v>
       </c>
       <c r="H22" s="3">
-        <v>160113.35</v>
+        <v>169774.51</v>
       </c>
       <c r="I22" s="3">
-        <v>731782.99</v>
+        <v>772633.43</v>
       </c>
       <c r="J22" s="3">
-        <v>85.12</v>
+        <v>89.88</v>
       </c>
       <c r="K22" s="3">
-        <v>-127878.35</v>
+        <v>-87027.91</v>
       </c>
       <c r="L22" s="3">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="M22" s="3">
-        <v>20474.54</v>
+        <v>22313.83</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>559</v>
+        <v>878</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>560</v>
+        <v>879</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>561</v>
+        <v>880</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>562</v>
+        <v>881</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>563</v>
+        <v>882</v>
       </c>
       <c r="F23" s="3">
         <v>867257.37</v>
       </c>
       <c r="G23" s="3">
-        <v>623050.02</v>
+        <v>664923.6</v>
       </c>
       <c r="H23" s="3">
-        <v>156073.28</v>
+        <v>154577.86</v>
       </c>
       <c r="I23" s="3">
-        <v>779123.3</v>
+        <v>819501.46</v>
       </c>
       <c r="J23" s="3">
-        <v>89.84</v>
+        <v>94.49</v>
       </c>
       <c r="K23" s="3">
-        <v>-88134.07</v>
+        <v>-47755.91</v>
       </c>
       <c r="L23" s="3">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="M23" s="3">
-        <v>14735.91</v>
+        <v>14893.41</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>564</v>
+        <v>883</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>565</v>
+        <v>884</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>566</v>
+        <v>885</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>567</v>
+        <v>886</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>568</v>
+        <v>887</v>
       </c>
       <c r="F24" s="3">
         <v>778641.12</v>
       </c>
       <c r="G24" s="3">
-        <v>504749.33</v>
+        <v>539129.27</v>
       </c>
       <c r="H24" s="3">
-        <v>131043.07</v>
+        <v>158079.19</v>
       </c>
       <c r="I24" s="3">
-        <v>635792.4</v>
+        <v>697208.46</v>
       </c>
       <c r="J24" s="3">
-        <v>81.65</v>
+        <v>89.54</v>
       </c>
       <c r="K24" s="3">
-        <v>-142848.72</v>
+        <v>-81432.66</v>
       </c>
       <c r="L24" s="3">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="M24" s="3">
-        <v>18226.31</v>
+        <v>20716.24</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>569</v>
+        <v>888</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>570</v>
+        <v>889</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>571</v>
+        <v>890</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>572</v>
+        <v>891</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>573</v>
+        <v>892</v>
       </c>
       <c r="F25" s="3">
         <v>979868.9</v>
       </c>
       <c r="G25" s="3">
-        <v>544548.15</v>
+        <v>567222.97</v>
       </c>
       <c r="H25" s="3">
-        <v>204723.19</v>
+        <v>205535.85</v>
       </c>
       <c r="I25" s="3">
-        <v>749271.34</v>
+        <v>772758.82</v>
       </c>
       <c r="J25" s="3">
-        <v>76.47</v>
+        <v>78.86</v>
       </c>
       <c r="K25" s="3">
-        <v>-230597.56</v>
+        <v>-207110.08</v>
       </c>
       <c r="L25" s="3">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M25" s="3">
-        <v>10766.99</v>
+        <v>11328.99</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>574</v>
+        <v>893</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>575</v>
+        <v>894</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>576</v>
+        <v>895</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>577</v>
+        <v>896</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>578</v>
+        <v>897</v>
       </c>
       <c r="F26" s="3">
         <v>1011213.65</v>
       </c>
       <c r="G26" s="3">
-        <v>381881.55</v>
+        <v>405416.82</v>
       </c>
       <c r="H26" s="3">
-        <v>164114.34</v>
+        <v>168378.98</v>
       </c>
       <c r="I26" s="3">
-        <v>545995.89</v>
+        <v>573795.8</v>
       </c>
       <c r="J26" s="3">
-        <v>53.99</v>
+        <v>56.74</v>
       </c>
       <c r="K26" s="3">
-        <v>-465217.76</v>
+        <v>-437417.85</v>
       </c>
       <c r="L26" s="3">
-        <v>4.32</v>
+        <v>4.15</v>
       </c>
       <c r="M26" s="3">
-        <v>23594.82</v>
+        <v>23830.93</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>579</v>
+        <v>898</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>580</v>
+        <v>899</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>581</v>
+        <v>900</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>582</v>
+        <v>901</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>583</v>
+        <v>902</v>
       </c>
       <c r="F27" s="3">
         <v>905279.17</v>
       </c>
       <c r="G27" s="3">
-        <v>499350.03</v>
+        <v>531754.36</v>
       </c>
       <c r="H27" s="3">
-        <v>167548.42</v>
+        <v>168695.36</v>
       </c>
       <c r="I27" s="3">
-        <v>666898.45</v>
+        <v>700449.72</v>
       </c>
       <c r="J27" s="3">
-        <v>73.67</v>
+        <v>77.37</v>
       </c>
       <c r="K27" s="3">
-        <v>-238380.72</v>
+        <v>-204829.45</v>
       </c>
       <c r="L27" s="3">
-        <v>2.09</v>
+        <v>2.0</v>
       </c>
       <c r="M27" s="3">
-        <v>13921.98</v>
+        <v>14041.92</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>584</v>
+        <v>903</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>585</v>
+        <v>904</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>586</v>
+        <v>905</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>587</v>
+        <v>906</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>588</v>
+        <v>907</v>
       </c>
       <c r="F28" s="3">
         <v>948604.6</v>
       </c>
       <c r="G28" s="3">
-        <v>437976.06</v>
+        <v>459956.71</v>
       </c>
       <c r="H28" s="3">
-        <v>113885.48</v>
+        <v>195239.42</v>
       </c>
       <c r="I28" s="3">
-        <v>551861.54</v>
+        <v>655196.13</v>
       </c>
       <c r="J28" s="3">
-        <v>58.18</v>
+        <v>69.07</v>
       </c>
       <c r="K28" s="3">
-        <v>-396743.06</v>
+        <v>-293408.47</v>
       </c>
       <c r="L28" s="3">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="M28" s="3">
-        <v>10652.34</v>
+        <v>12076.54</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>589</v>
+        <v>908</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>590</v>
+        <v>909</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>591</v>
+        <v>910</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>592</v>
+        <v>911</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>593</v>
+        <v>912</v>
       </c>
       <c r="F29" s="3">
         <v>824118.89</v>
       </c>
       <c r="G29" s="3">
-        <v>448278.8</v>
+        <v>468067.08</v>
       </c>
       <c r="H29" s="3">
-        <v>122212.88</v>
+        <v>130210.33</v>
       </c>
       <c r="I29" s="3">
-        <v>570491.68</v>
+        <v>598277.41</v>
       </c>
       <c r="J29" s="3">
-        <v>69.22</v>
+        <v>72.6</v>
       </c>
       <c r="K29" s="3">
-        <v>-253627.21</v>
+        <v>-225841.48</v>
       </c>
       <c r="L29" s="3">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="M29" s="3">
-        <v>17279.03</v>
+        <v>17901.53</v>
       </c>
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>594</v>
+        <v>913</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>595</v>
+        <v>914</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>596</v>
+        <v>915</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>597</v>
+        <v>916</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>598</v>
+        <v>917</v>
       </c>
       <c r="F30" s="3">
         <v>877850.52</v>
       </c>
       <c r="G30" s="3">
-        <v>586381.18</v>
+        <v>620041.23</v>
       </c>
       <c r="H30" s="3">
-        <v>193555.54</v>
+        <v>192645.05</v>
       </c>
       <c r="I30" s="3">
-        <v>779936.72</v>
+        <v>812686.28</v>
       </c>
       <c r="J30" s="3">
-        <v>88.85</v>
+        <v>92.58</v>
       </c>
       <c r="K30" s="3">
-        <v>-97913.8</v>
+        <v>-65164.24</v>
       </c>
       <c r="L30" s="3">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="M30" s="3">
-        <v>16703.66</v>
+        <v>17341.06</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>599</v>
+        <v>918</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>600</v>
+        <v>919</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>601</v>
+        <v>920</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>602</v>
+        <v>921</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>603</v>
+        <v>922</v>
       </c>
       <c r="F31" s="3">
         <v>990466.72</v>
       </c>
       <c r="G31" s="3">
-        <v>573155.22</v>
+        <v>603373.43</v>
       </c>
       <c r="H31" s="3">
-        <v>156048.41</v>
+        <v>160654.28</v>
       </c>
       <c r="I31" s="3">
-        <v>729203.63</v>
+        <v>764027.71</v>
       </c>
       <c r="J31" s="3">
-        <v>73.62</v>
+        <v>77.14</v>
       </c>
       <c r="K31" s="3">
-        <v>-261263.09</v>
+        <v>-226439.01</v>
       </c>
       <c r="L31" s="3">
-        <v>3.97</v>
+        <v>3.88</v>
       </c>
       <c r="M31" s="3">
-        <v>28968.08</v>
+        <v>29643.08</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>604</v>
+        <v>923</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>605</v>
+        <v>924</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>606</v>
+        <v>925</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>607</v>
+        <v>926</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>608</v>
+        <v>927</v>
       </c>
       <c r="F32" s="3">
         <v>892245.98</v>
       </c>
       <c r="G32" s="3">
-        <v>490441.98</v>
+        <v>520388.03</v>
       </c>
       <c r="H32" s="3">
-        <v>157223.21</v>
+        <v>152131.78</v>
       </c>
       <c r="I32" s="3">
-        <v>647665.19</v>
+        <v>672519.81</v>
       </c>
       <c r="J32" s="3">
-        <v>72.59</v>
+        <v>75.37</v>
       </c>
       <c r="K32" s="3">
-        <v>-244580.79</v>
+        <v>-219726.17</v>
       </c>
       <c r="L32" s="3">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="M32" s="3">
-        <v>22970.3</v>
+        <v>23660.3</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>609</v>
+        <v>928</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>610</v>
+        <v>929</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>611</v>
+        <v>930</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>612</v>
+        <v>931</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>613</v>
+        <v>932</v>
       </c>
       <c r="F33" s="3">
         <v>1265248.83</v>
@@ -8569,19 +11148,19 @@
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>614</v>
+        <v>933</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>615</v>
+        <v>934</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>616</v>
+        <v>935</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>617</v>
+        <v>936</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>618</v>
+        <v>937</v>
       </c>
       <c r="F34" s="3">
         <v>1062018.28</v>
@@ -8610,19 +11189,19 @@
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>619</v>
+        <v>938</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>620</v>
+        <v>939</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>621</v>
+        <v>940</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>622</v>
+        <v>941</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>623</v>
+        <v>942</v>
       </c>
       <c r="F35" s="3">
         <v>1027050.57</v>
@@ -8651,40 +11230,40 @@
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>624</v>
+        <v>943</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>625</v>
+        <v>944</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>626</v>
+        <v>945</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>627</v>
+        <v>946</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>628</v>
+        <v>947</v>
       </c>
       <c r="F36" s="3">
         <v>1150571.33</v>
       </c>
       <c r="G36" s="3">
-        <v>662993.12</v>
+        <v>694085.83</v>
       </c>
       <c r="H36" s="3">
-        <v>318623.03</v>
+        <v>291529.76</v>
       </c>
       <c r="I36" s="3">
-        <v>981616.15</v>
+        <v>985615.59</v>
       </c>
       <c r="J36" s="3">
-        <v>85.32</v>
+        <v>85.66</v>
       </c>
       <c r="K36" s="3">
-        <v>-168955.18</v>
+        <v>-164955.74</v>
       </c>
       <c r="L36" s="3">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="M36" s="3">
         <v>21450.86</v>
@@ -8692,40 +11271,40 @@
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>629</v>
+        <v>948</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>630</v>
+        <v>949</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>631</v>
+        <v>950</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>632</v>
+        <v>951</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>633</v>
+        <v>952</v>
       </c>
       <c r="F37" s="3">
         <v>1374896.6</v>
       </c>
       <c r="G37" s="3">
-        <v>623485.86</v>
+        <v>655101.62</v>
       </c>
       <c r="H37" s="3">
-        <v>305132.96</v>
+        <v>279050.14</v>
       </c>
       <c r="I37" s="3">
-        <v>928618.82</v>
+        <v>934151.76</v>
       </c>
       <c r="J37" s="3">
-        <v>67.54</v>
+        <v>67.94</v>
       </c>
       <c r="K37" s="3">
-        <v>-446277.78</v>
+        <v>-440744.84</v>
       </c>
       <c r="L37" s="3">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="M37" s="3">
         <v>29630.76</v>
@@ -8733,40 +11312,40 @@
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>634</v>
+        <v>953</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>635</v>
+        <v>954</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>636</v>
+        <v>955</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>637</v>
+        <v>956</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>638</v>
+        <v>957</v>
       </c>
       <c r="F38" s="3">
         <v>904558.95</v>
       </c>
       <c r="G38" s="3">
-        <v>462483.56</v>
+        <v>493494.33</v>
       </c>
       <c r="H38" s="3">
-        <v>247247.57</v>
+        <v>219768.3</v>
       </c>
       <c r="I38" s="3">
-        <v>709731.13</v>
+        <v>713262.63</v>
       </c>
       <c r="J38" s="3">
-        <v>78.46</v>
+        <v>78.85</v>
       </c>
       <c r="K38" s="3">
-        <v>-194827.82</v>
+        <v>-191296.32</v>
       </c>
       <c r="L38" s="3">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="M38" s="3">
         <v>17498.94</v>
@@ -8774,40 +11353,40 @@
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>639</v>
+        <v>958</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>640</v>
+        <v>959</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>641</v>
+        <v>960</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>642</v>
+        <v>961</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>643</v>
+        <v>962</v>
       </c>
       <c r="F39" s="3">
         <v>1106940.64</v>
       </c>
       <c r="G39" s="3">
-        <v>444237.95</v>
+        <v>466035.7</v>
       </c>
       <c r="H39" s="3">
-        <v>243173.42</v>
+        <v>223677.21</v>
       </c>
       <c r="I39" s="3">
-        <v>687411.37</v>
+        <v>689712.91</v>
       </c>
       <c r="J39" s="3">
-        <v>62.1</v>
+        <v>62.31</v>
       </c>
       <c r="K39" s="3">
-        <v>-419529.27</v>
+        <v>-417227.73</v>
       </c>
       <c r="L39" s="3">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="M39" s="3">
         <v>20733.63</v>
@@ -8815,19 +11394,19 @@
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>644</v>
+        <v>963</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>645</v>
+        <v>964</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>646</v>
+        <v>965</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>647</v>
+        <v>966</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>648</v>
+        <v>967</v>
       </c>
       <c r="F40" s="3">
         <v>887573.45</v>
@@ -8836,19 +11415,19 @@
         <v>422036.87</v>
       </c>
       <c r="H40" s="3">
-        <v>123187.11</v>
+        <v>145344.43</v>
       </c>
       <c r="I40" s="3">
-        <v>545223.98</v>
+        <v>567381.3</v>
       </c>
       <c r="J40" s="3">
-        <v>61.43</v>
+        <v>63.92</v>
       </c>
       <c r="K40" s="3">
-        <v>-342349.47</v>
+        <v>-320192.15</v>
       </c>
       <c r="L40" s="3">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="M40" s="3">
         <v>5998.03</v>
@@ -8856,19 +11435,19 @@
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>649</v>
+        <v>968</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>650</v>
+        <v>969</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>651</v>
+        <v>970</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>652</v>
+        <v>971</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>653</v>
+        <v>972</v>
       </c>
       <c r="F41" s="3">
         <v>1236217.2</v>
@@ -8877,19 +11456,19 @@
         <v>579919.9</v>
       </c>
       <c r="H41" s="3">
-        <v>183761.71</v>
+        <v>230819.64</v>
       </c>
       <c r="I41" s="3">
-        <v>763681.61</v>
+        <v>810739.54</v>
       </c>
       <c r="J41" s="3">
-        <v>61.78</v>
+        <v>65.58</v>
       </c>
       <c r="K41" s="3">
-        <v>-472535.59</v>
+        <v>-425477.66</v>
       </c>
       <c r="L41" s="3">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="M41" s="3">
         <v>17477.0</v>
@@ -8897,19 +11476,19 @@
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>654</v>
+        <v>973</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>655</v>
+        <v>974</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>656</v>
+        <v>975</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>657</v>
+        <v>976</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>658</v>
+        <v>977</v>
       </c>
       <c r="F42" s="3">
         <v>912015.93</v>
@@ -8918,19 +11497,19 @@
         <v>502437.15</v>
       </c>
       <c r="H42" s="3">
-        <v>158718.25</v>
+        <v>191522.73</v>
       </c>
       <c r="I42" s="3">
-        <v>661155.4</v>
+        <v>693959.88</v>
       </c>
       <c r="J42" s="3">
-        <v>72.49</v>
+        <v>76.09</v>
       </c>
       <c r="K42" s="3">
-        <v>-250860.53</v>
+        <v>-218056.05</v>
       </c>
       <c r="L42" s="3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M42" s="3">
         <v>14540.24</v>
@@ -8938,19 +11517,19 @@
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>659</v>
+        <v>978</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>660</v>
+        <v>979</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>661</v>
+        <v>980</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>662</v>
+        <v>981</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>663</v>
+        <v>982</v>
       </c>
       <c r="F43" s="3">
         <v>1043081.21</v>
@@ -8959,19 +11538,19 @@
         <v>679446.22</v>
       </c>
       <c r="H43" s="3">
-        <v>179217.85</v>
+        <v>247615.35</v>
       </c>
       <c r="I43" s="3">
-        <v>858664.07</v>
+        <v>927061.57</v>
       </c>
       <c r="J43" s="3">
-        <v>82.32</v>
+        <v>88.88</v>
       </c>
       <c r="K43" s="3">
-        <v>-184417.14</v>
+        <v>-116019.64</v>
       </c>
       <c r="L43" s="3">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="M43" s="3">
         <v>19197.77</v>
@@ -8979,19 +11558,19 @@
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>664</v>
+        <v>983</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>665</v>
+        <v>984</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>666</v>
+        <v>985</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>667</v>
+        <v>986</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>668</v>
+        <v>987</v>
       </c>
       <c r="F44" s="3">
         <v>1113507.9</v>
@@ -9000,19 +11579,19 @@
         <v>610519.31</v>
       </c>
       <c r="H44" s="3">
-        <v>53419.93</v>
+        <v>174890.04</v>
       </c>
       <c r="I44" s="3">
-        <v>663939.24</v>
+        <v>785409.35</v>
       </c>
       <c r="J44" s="3">
-        <v>59.63</v>
+        <v>70.53</v>
       </c>
       <c r="K44" s="3">
-        <v>-449568.66</v>
+        <v>-328098.55</v>
       </c>
       <c r="L44" s="3">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="M44" s="3">
         <v>16611.34</v>
@@ -9020,19 +11599,19 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>669</v>
+        <v>988</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>670</v>
+        <v>989</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>671</v>
+        <v>990</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>672</v>
+        <v>991</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>673</v>
+        <v>992</v>
       </c>
       <c r="F45" s="3">
         <v>918319.81</v>
@@ -9041,19 +11620,19 @@
         <v>632676.37</v>
       </c>
       <c r="H45" s="3">
-        <v>58420.56</v>
+        <v>155347.39</v>
       </c>
       <c r="I45" s="3">
-        <v>691096.93</v>
+        <v>788023.76</v>
       </c>
       <c r="J45" s="3">
-        <v>75.26</v>
+        <v>85.81</v>
       </c>
       <c r="K45" s="3">
-        <v>-227222.88</v>
+        <v>-130296.05</v>
       </c>
       <c r="L45" s="3">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="M45" s="3">
         <v>12200.15</v>
@@ -9061,19 +11640,19 @@
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>674</v>
+        <v>993</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>675</v>
+        <v>994</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>676</v>
+        <v>995</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>677</v>
+        <v>996</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>678</v>
+        <v>997</v>
       </c>
       <c r="F46" s="3">
         <v>1066780.42</v>
@@ -9082,19 +11661,19 @@
         <v>700229.0</v>
       </c>
       <c r="H46" s="3">
-        <v>41957.94</v>
+        <v>127968.35</v>
       </c>
       <c r="I46" s="3">
-        <v>742186.94</v>
+        <v>828197.35</v>
       </c>
       <c r="J46" s="3">
-        <v>69.57</v>
+        <v>77.64</v>
       </c>
       <c r="K46" s="3">
-        <v>-324593.48</v>
+        <v>-238583.07</v>
       </c>
       <c r="L46" s="3">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M46" s="3">
         <v>14068.12</v>
@@ -9102,19 +11681,19 @@
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>679</v>
+        <v>998</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>680</v>
+        <v>999</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>681</v>
+        <v>1000</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>682</v>
+        <v>1001</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>683</v>
+        <v>1002</v>
       </c>
       <c r="F47" s="3">
         <v>1336954.46</v>
@@ -9123,19 +11702,19 @@
         <v>426103.49</v>
       </c>
       <c r="H47" s="3">
-        <v>279175.64</v>
+        <v>334968.86</v>
       </c>
       <c r="I47" s="3">
-        <v>705279.13</v>
+        <v>761072.35</v>
       </c>
       <c r="J47" s="3">
-        <v>52.75</v>
+        <v>56.93</v>
       </c>
       <c r="K47" s="3">
-        <v>-631675.33</v>
+        <v>-575882.11</v>
       </c>
       <c r="L47" s="3">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="M47" s="3">
         <v>22942.59</v>
@@ -9143,19 +11722,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>684</v>
+        <v>1003</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>685</v>
+        <v>1004</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>686</v>
+        <v>1005</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>687</v>
+        <v>1006</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>688</v>
+        <v>1007</v>
       </c>
       <c r="F48" s="3">
         <v>1022376.56</v>
@@ -9164,19 +11743,19 @@
         <v>364309.9</v>
       </c>
       <c r="H48" s="3">
-        <v>148582.01</v>
+        <v>196619.56</v>
       </c>
       <c r="I48" s="3">
-        <v>512891.91</v>
+        <v>560929.46</v>
       </c>
       <c r="J48" s="3">
-        <v>50.17</v>
+        <v>54.87</v>
       </c>
       <c r="K48" s="3">
-        <v>-509484.65</v>
+        <v>-461447.1</v>
       </c>
       <c r="L48" s="3">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="M48" s="3">
         <v>18249.36</v>
@@ -9184,19 +11763,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>689</v>
+        <v>1008</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>690</v>
+        <v>1009</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>691</v>
+        <v>1010</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>692</v>
+        <v>1011</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>693</v>
+        <v>1012</v>
       </c>
       <c r="F49" s="3">
         <v>972020.19</v>
@@ -9205,19 +11784,19 @@
         <v>437419.04</v>
       </c>
       <c r="H49" s="3">
-        <v>158549.86</v>
+        <v>228871.67</v>
       </c>
       <c r="I49" s="3">
-        <v>595968.9</v>
+        <v>666290.71</v>
       </c>
       <c r="J49" s="3">
-        <v>61.31</v>
+        <v>68.55</v>
       </c>
       <c r="K49" s="3">
-        <v>-376051.29</v>
+        <v>-305729.48</v>
       </c>
       <c r="L49" s="3">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="M49" s="3">
         <v>17023.85</v>
@@ -9225,19 +11804,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>694</v>
+        <v>1013</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>695</v>
+        <v>1014</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>696</v>
+        <v>1015</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>697</v>
+        <v>1016</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>698</v>
+        <v>1017</v>
       </c>
       <c r="F50" s="3">
         <v>963790.11</v>
@@ -9246,19 +11825,19 @@
         <v>428712.74</v>
       </c>
       <c r="H50" s="3">
-        <v>167782.69</v>
+        <v>219677.56</v>
       </c>
       <c r="I50" s="3">
-        <v>596495.43</v>
+        <v>648390.3</v>
       </c>
       <c r="J50" s="3">
-        <v>61.89</v>
+        <v>67.28</v>
       </c>
       <c r="K50" s="3">
-        <v>-367294.68</v>
+        <v>-315399.81</v>
       </c>
       <c r="L50" s="3">
-        <v>4.53</v>
+        <v>4.17</v>
       </c>
       <c r="M50" s="3">
         <v>27010.91</v>
@@ -9266,19 +11845,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>699</v>
+        <v>1018</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>700</v>
+        <v>1019</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>701</v>
+        <v>1020</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>702</v>
+        <v>1021</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>703</v>
+        <v>1022</v>
       </c>
       <c r="F51" s="3">
         <v>954958.72</v>
@@ -9287,19 +11866,19 @@
         <v>548398.72</v>
       </c>
       <c r="H51" s="3">
-        <v>101322.72</v>
+        <v>177454.38</v>
       </c>
       <c r="I51" s="3">
-        <v>649721.44</v>
+        <v>725853.1</v>
       </c>
       <c r="J51" s="3">
-        <v>68.04</v>
+        <v>76.01</v>
       </c>
       <c r="K51" s="3">
-        <v>-305237.28</v>
+        <v>-229105.62</v>
       </c>
       <c r="L51" s="3">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="M51" s="3">
         <v>23047.94</v>
@@ -9307,19 +11886,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>704</v>
+        <v>1023</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>705</v>
+        <v>1024</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>706</v>
+        <v>1025</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>707</v>
+        <v>1026</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>708</v>
+        <v>1027</v>
       </c>
       <c r="F52" s="3">
         <v>1154949.94</v>
@@ -9328,19 +11907,19 @@
         <v>556971.85</v>
       </c>
       <c r="H52" s="3">
-        <v>139183.52</v>
+        <v>213580.22</v>
       </c>
       <c r="I52" s="3">
-        <v>696155.37</v>
+        <v>770552.07</v>
       </c>
       <c r="J52" s="3">
-        <v>60.28</v>
+        <v>66.72</v>
       </c>
       <c r="K52" s="3">
-        <v>-458794.57</v>
+        <v>-384397.87</v>
       </c>
       <c r="L52" s="3">
-        <v>7.02</v>
+        <v>6.35</v>
       </c>
       <c r="M52" s="3">
         <v>48900.67</v>
@@ -9353,7 +11932,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -9401,246 +11980,246 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="8:8" ht="35.2">
+    <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>709</v>
+        <v>741</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>712</v>
+        <v>744</v>
       </c>
       <c r="E2" s="3">
         <v>5936775.24</v>
       </c>
       <c r="F2" s="3">
-        <v>2646434.7</v>
+        <v>2855344.19</v>
       </c>
       <c r="G2" s="3">
-        <v>1757868.72</v>
+        <v>1707375.46</v>
       </c>
       <c r="H2" s="3">
-        <v>4404303.42</v>
+        <v>4562719.65</v>
       </c>
       <c r="I2" s="3">
-        <v>74.19</v>
+        <v>76.86</v>
       </c>
       <c r="J2" s="3">
-        <v>-1532471.82</v>
+        <v>-1374055.59</v>
       </c>
       <c r="K2" s="3">
-        <v>85805.92</v>
+        <v>90408.34</v>
       </c>
       <c r="L2" s="3">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
     </row>
-    <row r="3" spans="8:8" ht="23.2">
+    <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>714</v>
+        <v>746</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>715</v>
+        <v>747</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="E3" s="3">
         <v>3346888.02</v>
       </c>
       <c r="F3" s="3">
-        <v>1440958.1</v>
+        <v>1563137.41</v>
       </c>
       <c r="G3" s="3">
-        <v>910292.22</v>
+        <v>842408.36</v>
       </c>
       <c r="H3" s="3">
-        <v>2351250.32</v>
+        <v>2405545.77</v>
       </c>
       <c r="I3" s="3">
-        <v>70.25</v>
+        <v>71.87</v>
       </c>
       <c r="J3" s="3">
-        <v>-995637.7</v>
+        <v>-941342.25</v>
       </c>
       <c r="K3" s="3">
-        <v>38510.68</v>
+        <v>42003.22</v>
       </c>
       <c r="L3" s="3">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
     </row>
-    <row r="4" spans="8:8" ht="23.2">
+    <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>718</v>
+        <v>750</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>719</v>
+        <v>751</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>720</v>
+        <v>752</v>
       </c>
       <c r="E4" s="3">
         <v>6248074.42</v>
       </c>
       <c r="F4" s="3">
-        <v>2484358.85</v>
+        <v>2810038.31</v>
       </c>
       <c r="G4" s="3">
-        <v>1494609.22</v>
+        <v>1187910.54</v>
       </c>
       <c r="H4" s="3">
-        <v>3978968.07</v>
+        <v>3997948.85</v>
       </c>
       <c r="I4" s="3">
-        <v>63.68</v>
+        <v>63.99</v>
       </c>
       <c r="J4" s="3">
-        <v>-2269106.35</v>
+        <v>-2250125.57</v>
       </c>
       <c r="K4" s="3">
-        <v>142889.21</v>
+        <v>158554.02</v>
       </c>
       <c r="L4" s="3">
-        <v>3.59</v>
+        <v>3.97</v>
       </c>
     </row>
-    <row r="5" spans="8:8" ht="23.2">
+    <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>721</v>
+        <v>753</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>723</v>
+        <v>755</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="E5" s="3">
         <v>7225829.17</v>
       </c>
       <c r="F5" s="3">
-        <v>4145713.93</v>
+        <v>4391331.5</v>
       </c>
       <c r="G5" s="3">
-        <v>1228679.53</v>
+        <v>1278931.94</v>
       </c>
       <c r="H5" s="3">
-        <v>5374393.46</v>
+        <v>5670263.44</v>
       </c>
       <c r="I5" s="3">
-        <v>74.38</v>
+        <v>78.47</v>
       </c>
       <c r="J5" s="3">
-        <v>-1851435.71</v>
+        <v>-1555565.73</v>
       </c>
       <c r="K5" s="3">
-        <v>124974.36</v>
+        <v>132343.33</v>
       </c>
       <c r="L5" s="3">
         <v>2.33</v>
       </c>
     </row>
-    <row r="6" spans="8:8" ht="23.2">
+    <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>725</v>
+        <v>757</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>726</v>
+        <v>758</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>727</v>
+        <v>759</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>728</v>
+        <v>760</v>
       </c>
       <c r="E6" s="3">
         <v>6938999.79</v>
       </c>
       <c r="F6" s="3">
-        <v>3844122.94</v>
+        <v>3957735.53</v>
       </c>
       <c r="G6" s="3">
-        <v>1226577.5</v>
+        <v>1232382.28</v>
       </c>
       <c r="H6" s="3">
-        <v>5070700.44</v>
+        <v>5190117.81</v>
       </c>
       <c r="I6" s="3">
-        <v>73.08</v>
+        <v>74.8</v>
       </c>
       <c r="J6" s="3">
-        <v>-1868299.35</v>
+        <v>-1748881.98</v>
       </c>
       <c r="K6" s="3">
-        <v>167356.15</v>
+        <v>169981.05</v>
       </c>
       <c r="L6" s="3">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
     </row>
-    <row r="7" spans="8:8" ht="34.85">
+    <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>730</v>
+        <v>762</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="E7" s="3">
         <v>4536967.52</v>
       </c>
       <c r="F7" s="3">
-        <v>2193200.49</v>
+        <v>2308717.48</v>
       </c>
       <c r="G7" s="3">
-        <v>1114176.98</v>
+        <v>1014025.41</v>
       </c>
       <c r="H7" s="3">
-        <v>3307377.47</v>
+        <v>3322742.89</v>
       </c>
       <c r="I7" s="3">
-        <v>72.9</v>
+        <v>73.24</v>
       </c>
       <c r="J7" s="3">
-        <v>-1229590.05</v>
+        <v>-1214224.63</v>
       </c>
       <c r="K7" s="3">
         <v>89314.19</v>
       </c>
       <c r="L7" s="3">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
     </row>
-    <row r="8" spans="8:8" ht="23.2">
+    <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>734</v>
+        <v>766</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>735</v>
+        <v>767</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>736</v>
+        <v>768</v>
       </c>
       <c r="E8" s="3">
         <v>7177495.92</v>
@@ -9649,36 +12228,36 @@
         <v>4127264.82</v>
       </c>
       <c r="G8" s="3">
-        <v>798683.35</v>
+        <v>1273507.93</v>
       </c>
       <c r="H8" s="3">
-        <v>4925948.17</v>
+        <v>5400772.75</v>
       </c>
       <c r="I8" s="3">
-        <v>68.63</v>
+        <v>75.25</v>
       </c>
       <c r="J8" s="3">
-        <v>-2251547.75</v>
+        <v>-1776723.17</v>
       </c>
       <c r="K8" s="3">
         <v>100092.65</v>
       </c>
       <c r="L8" s="3">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
     </row>
-    <row r="9" spans="8:8" ht="23.2">
+    <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>737</v>
+        <v>769</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>738</v>
+        <v>770</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>739</v>
+        <v>771</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>740</v>
+        <v>772</v>
       </c>
       <c r="E9" s="3">
         <v>6405049.98</v>
@@ -9687,28 +12266,25 @@
         <v>2761915.74</v>
       </c>
       <c r="G9" s="3">
-        <v>994596.44</v>
+        <v>1371172.25</v>
       </c>
       <c r="H9" s="3">
-        <v>3756512.18</v>
+        <v>4133087.99</v>
       </c>
       <c r="I9" s="3">
-        <v>58.65</v>
+        <v>64.53</v>
       </c>
       <c r="J9" s="3">
-        <v>-2648537.8</v>
+        <v>-2271961.99</v>
       </c>
       <c r="K9" s="3">
         <v>157175.32</v>
       </c>
       <c r="L9" s="3">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L9">
-    <filterColumn colId="0" showButton="1"/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="territory-wise-MPE-sales-achiev" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1028" count="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1315" count="1315">
   <si>
     <t>Region</t>
   </si>
@@ -9388,6 +9388,2589 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
     </r>
   </si>
 </sst>
@@ -9775,7 +12358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:T52"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -9836,286 +12419,286 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>773</v>
+        <v>1028</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>774</v>
+        <v>1029</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>775</v>
+        <v>1030</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>776</v>
+        <v>1031</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>777</v>
+        <v>1032</v>
       </c>
       <c r="F2" s="3">
         <v>747825.09</v>
       </c>
       <c r="G2" s="3">
-        <v>420744.84</v>
+        <v>433335.2</v>
       </c>
       <c r="H2" s="3">
-        <v>197496.99</v>
+        <v>196201.49</v>
       </c>
       <c r="I2" s="3">
-        <v>618241.83</v>
+        <v>629536.69</v>
       </c>
       <c r="J2" s="3">
-        <v>82.67</v>
+        <v>84.18</v>
       </c>
       <c r="K2" s="3">
-        <v>-129583.26</v>
+        <v>-118288.4</v>
       </c>
       <c r="L2" s="3">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="M2" s="3">
-        <v>11070.38</v>
+        <v>13001.24</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>778</v>
+        <v>1033</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>779</v>
+        <v>1034</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>780</v>
+        <v>1035</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>781</v>
+        <v>1036</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>782</v>
+        <v>1037</v>
       </c>
       <c r="F3" s="3">
         <v>755003.49</v>
       </c>
       <c r="G3" s="3">
-        <v>312089.38</v>
+        <v>356000.98</v>
       </c>
       <c r="H3" s="3">
-        <v>295793.85</v>
+        <v>274374.86</v>
       </c>
       <c r="I3" s="3">
-        <v>607883.23</v>
+        <v>630375.84</v>
       </c>
       <c r="J3" s="3">
-        <v>80.51</v>
+        <v>83.49</v>
       </c>
       <c r="K3" s="3">
-        <v>-147120.26</v>
+        <v>-124627.65</v>
       </c>
       <c r="L3" s="3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M3" s="3">
-        <v>7607.09</v>
+        <v>8112.89</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>783</v>
+        <v>1038</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>784</v>
+        <v>1039</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>785</v>
+        <v>1040</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>786</v>
+        <v>1041</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>787</v>
+        <v>1042</v>
       </c>
       <c r="F4" s="3">
         <v>664724.91</v>
       </c>
       <c r="G4" s="3">
-        <v>386158.7</v>
+        <v>401266.61</v>
       </c>
       <c r="H4" s="3">
-        <v>209776.75</v>
+        <v>226635.15</v>
       </c>
       <c r="I4" s="3">
-        <v>595935.45</v>
+        <v>627901.76</v>
       </c>
       <c r="J4" s="3">
-        <v>89.65</v>
+        <v>94.46</v>
       </c>
       <c r="K4" s="3">
-        <v>-68789.46</v>
+        <v>-36823.15</v>
       </c>
       <c r="L4" s="3">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="M4" s="3">
-        <v>13467.47</v>
+        <v>15630.2</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>788</v>
+        <v>1043</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>789</v>
+        <v>1044</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>790</v>
+        <v>1045</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>791</v>
+        <v>1046</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>792</v>
+        <v>1047</v>
       </c>
       <c r="F5" s="3">
         <v>745422.79</v>
       </c>
       <c r="G5" s="3">
-        <v>307011.19</v>
+        <v>317514.42</v>
       </c>
       <c r="H5" s="3">
-        <v>201600.89</v>
+        <v>221782.22</v>
       </c>
       <c r="I5" s="3">
-        <v>508612.08</v>
+        <v>539296.64</v>
       </c>
       <c r="J5" s="3">
-        <v>68.23</v>
+        <v>72.35</v>
       </c>
       <c r="K5" s="3">
-        <v>-236810.71</v>
+        <v>-206126.15</v>
       </c>
       <c r="L5" s="3">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="M5" s="3">
-        <v>16830.93</v>
+        <v>18120.3</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>793</v>
+        <v>1048</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>794</v>
+        <v>1049</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>795</v>
+        <v>1050</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>796</v>
+        <v>1051</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>797</v>
+        <v>1052</v>
       </c>
       <c r="F6" s="3">
         <v>750633.4</v>
       </c>
       <c r="G6" s="3">
-        <v>480931.58</v>
+        <v>503665.43</v>
       </c>
       <c r="H6" s="3">
-        <v>231933.53</v>
+        <v>233464.17</v>
       </c>
       <c r="I6" s="3">
-        <v>712865.11</v>
+        <v>737129.6</v>
       </c>
       <c r="J6" s="3">
-        <v>94.97</v>
+        <v>98.2</v>
       </c>
       <c r="K6" s="3">
-        <v>-37768.29</v>
+        <v>-13503.8</v>
       </c>
       <c r="L6" s="3">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="M6" s="3">
-        <v>18699.25</v>
+        <v>18828.78</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>798</v>
+        <v>1053</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>799</v>
+        <v>1054</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>800</v>
+        <v>1055</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>801</v>
+        <v>1056</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>802</v>
+        <v>1057</v>
       </c>
       <c r="F7" s="3">
         <v>804591.82</v>
       </c>
       <c r="G7" s="3">
-        <v>301246.41</v>
+        <v>310652.86</v>
       </c>
       <c r="H7" s="3">
-        <v>207832.56</v>
+        <v>216466.54</v>
       </c>
       <c r="I7" s="3">
-        <v>509078.97</v>
+        <v>527119.4</v>
       </c>
       <c r="J7" s="3">
-        <v>63.27</v>
+        <v>65.51</v>
       </c>
       <c r="K7" s="3">
-        <v>-295512.85</v>
+        <v>-277472.42</v>
       </c>
       <c r="L7" s="3">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="M7" s="3">
-        <v>9218.43</v>
+        <v>11278.51</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>803</v>
+        <v>1058</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>804</v>
+        <v>1059</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>805</v>
+        <v>1060</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>806</v>
+        <v>1061</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>807</v>
+        <v>1062</v>
       </c>
       <c r="F8" s="3">
         <v>726832.71</v>
       </c>
       <c r="G8" s="3">
-        <v>271531.42</v>
+        <v>281204.5</v>
       </c>
       <c r="H8" s="3">
-        <v>162611.43</v>
+        <v>174721.77</v>
       </c>
       <c r="I8" s="3">
-        <v>434142.85</v>
+        <v>455926.27</v>
       </c>
       <c r="J8" s="3">
-        <v>59.73</v>
+        <v>62.73</v>
       </c>
       <c r="K8" s="3">
-        <v>-292689.86</v>
+        <v>-270906.44</v>
       </c>
       <c r="L8" s="3">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="M8" s="3">
         <v>2474.76</v>
@@ -10123,204 +12706,204 @@
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>808</v>
+        <v>1063</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>809</v>
+        <v>1064</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>810</v>
+        <v>1065</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>811</v>
+        <v>1066</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>812</v>
+        <v>1067</v>
       </c>
       <c r="F9" s="3">
         <v>741741.03</v>
       </c>
       <c r="G9" s="3">
-        <v>375630.68</v>
+        <v>393574.77</v>
       </c>
       <c r="H9" s="3">
-        <v>202357.22</v>
+        <v>199162.37</v>
       </c>
       <c r="I9" s="3">
-        <v>577987.9</v>
+        <v>592737.14</v>
       </c>
       <c r="J9" s="3">
-        <v>77.92</v>
+        <v>79.91</v>
       </c>
       <c r="K9" s="3">
-        <v>-163753.13</v>
+        <v>-149003.89</v>
       </c>
       <c r="L9" s="3">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="M9" s="3">
-        <v>11040.03</v>
+        <v>13247.78</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>813</v>
+        <v>1068</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>814</v>
+        <v>1069</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>815</v>
+        <v>1070</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>816</v>
+        <v>1071</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>817</v>
+        <v>1072</v>
       </c>
       <c r="F10" s="3">
         <v>859984.15</v>
       </c>
       <c r="G10" s="3">
-        <v>406200.33</v>
+        <v>420196.37</v>
       </c>
       <c r="H10" s="3">
-        <v>233886.44</v>
+        <v>241191.95</v>
       </c>
       <c r="I10" s="3">
-        <v>640086.77</v>
+        <v>661388.32</v>
       </c>
       <c r="J10" s="3">
-        <v>74.43</v>
+        <v>76.91</v>
       </c>
       <c r="K10" s="3">
-        <v>-219897.38</v>
+        <v>-198595.83</v>
       </c>
       <c r="L10" s="3">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="M10" s="3">
-        <v>14805.16</v>
+        <v>15467.44</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>818</v>
+        <v>1073</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>819</v>
+        <v>1074</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>820</v>
+        <v>1075</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>821</v>
+        <v>1076</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>822</v>
+        <v>1077</v>
       </c>
       <c r="F11" s="3">
         <v>903047.31</v>
       </c>
       <c r="G11" s="3">
-        <v>349592.06</v>
+        <v>363634.16</v>
       </c>
       <c r="H11" s="3">
-        <v>185884.86</v>
+        <v>184170.36</v>
       </c>
       <c r="I11" s="3">
-        <v>535476.92</v>
+        <v>547804.52</v>
       </c>
       <c r="J11" s="3">
-        <v>59.3</v>
+        <v>60.66</v>
       </c>
       <c r="K11" s="3">
-        <v>-367570.39</v>
+        <v>-355242.79</v>
       </c>
       <c r="L11" s="3">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="M11" s="3">
-        <v>11612.29</v>
+        <v>13495.5</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>823</v>
+        <v>1078</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>824</v>
+        <v>1079</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>825</v>
+        <v>1080</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>826</v>
+        <v>1081</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>827</v>
+        <v>1082</v>
       </c>
       <c r="F12" s="3">
         <v>775221.33</v>
       </c>
       <c r="G12" s="3">
-        <v>392186.34</v>
+        <v>413873.87</v>
       </c>
       <c r="H12" s="3">
-        <v>201757.37</v>
+        <v>201452.32</v>
       </c>
       <c r="I12" s="3">
-        <v>593943.71</v>
+        <v>615326.19</v>
       </c>
       <c r="J12" s="3">
-        <v>76.62</v>
+        <v>79.37</v>
       </c>
       <c r="K12" s="3">
-        <v>-181277.62</v>
+        <v>-159895.14</v>
       </c>
       <c r="L12" s="3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M12" s="3">
-        <v>7251.66</v>
+        <v>7660.09</v>
       </c>
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>828</v>
+        <v>1083</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>829</v>
+        <v>1084</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>830</v>
+        <v>1085</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>831</v>
+        <v>1086</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>832</v>
+        <v>1087</v>
       </c>
       <c r="F13" s="3">
         <v>808635.23</v>
       </c>
       <c r="G13" s="3">
-        <v>415158.68</v>
+        <v>430439.35</v>
       </c>
       <c r="H13" s="3">
-        <v>221821.15</v>
+        <v>222332.37</v>
       </c>
       <c r="I13" s="3">
-        <v>636979.83</v>
+        <v>652771.72</v>
       </c>
       <c r="J13" s="3">
-        <v>78.77</v>
+        <v>80.73</v>
       </c>
       <c r="K13" s="3">
-        <v>-171655.4</v>
+        <v>-155863.51</v>
       </c>
       <c r="L13" s="3">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M13" s="3">
         <v>8334.11</v>
@@ -10328,81 +12911,81 @@
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>833</v>
+        <v>1088</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>834</v>
+        <v>1089</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>835</v>
+        <v>1090</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>836</v>
+        <v>1091</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>837</v>
+        <v>1092</v>
       </c>
       <c r="F14" s="3">
         <v>773239.07</v>
       </c>
       <c r="G14" s="3">
-        <v>322969.62</v>
+        <v>339605.28</v>
       </c>
       <c r="H14" s="3">
-        <v>268899.01</v>
+        <v>271917.34</v>
       </c>
       <c r="I14" s="3">
-        <v>591868.63</v>
+        <v>611522.62</v>
       </c>
       <c r="J14" s="3">
-        <v>76.54</v>
+        <v>79.09</v>
       </c>
       <c r="K14" s="3">
-        <v>-181370.44</v>
+        <v>-161716.45</v>
       </c>
       <c r="L14" s="3">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M14" s="3">
-        <v>8112.85</v>
+        <v>8220.8</v>
       </c>
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>838</v>
+        <v>1093</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>839</v>
+        <v>1094</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>840</v>
+        <v>1095</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>841</v>
+        <v>1096</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>842</v>
+        <v>1097</v>
       </c>
       <c r="F15" s="3">
         <v>788718.67</v>
       </c>
       <c r="G15" s="3">
-        <v>232096.88</v>
+        <v>245089.78</v>
       </c>
       <c r="H15" s="3">
-        <v>241863.83</v>
+        <v>252408.27</v>
       </c>
       <c r="I15" s="3">
-        <v>473960.71</v>
+        <v>497498.05</v>
       </c>
       <c r="J15" s="3">
-        <v>60.09</v>
+        <v>63.08</v>
       </c>
       <c r="K15" s="3">
-        <v>-314757.96</v>
+        <v>-291220.62</v>
       </c>
       <c r="L15" s="3">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="M15" s="3">
         <v>11703.66</v>
@@ -10410,40 +12993,40 @@
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>843</v>
+        <v>1098</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>844</v>
+        <v>1099</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>845</v>
+        <v>1100</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>846</v>
+        <v>1101</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>847</v>
+        <v>1102</v>
       </c>
       <c r="F16" s="3">
         <v>757031.95</v>
       </c>
       <c r="G16" s="3">
-        <v>200093.93</v>
+        <v>204003.16</v>
       </c>
       <c r="H16" s="3">
-        <v>150712.4</v>
+        <v>158761.67</v>
       </c>
       <c r="I16" s="3">
-        <v>350806.33</v>
+        <v>362764.83</v>
       </c>
       <c r="J16" s="3">
-        <v>46.34</v>
+        <v>47.92</v>
       </c>
       <c r="K16" s="3">
-        <v>-406225.62</v>
+        <v>-394267.12</v>
       </c>
       <c r="L16" s="3">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="M16" s="3">
         <v>5337.74</v>
@@ -10451,60 +13034,60 @@
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>848</v>
+        <v>1103</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>849</v>
+        <v>1104</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>850</v>
+        <v>1105</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>851</v>
+        <v>1106</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>852</v>
+        <v>1107</v>
       </c>
       <c r="F17" s="3">
         <v>792097.85</v>
       </c>
       <c r="G17" s="3">
-        <v>249065.85</v>
+        <v>253932.12</v>
       </c>
       <c r="H17" s="3">
-        <v>212124.65</v>
+        <v>218726.29</v>
       </c>
       <c r="I17" s="3">
-        <v>461190.5</v>
+        <v>472658.41</v>
       </c>
       <c r="J17" s="3">
-        <v>58.22</v>
+        <v>59.67</v>
       </c>
       <c r="K17" s="3">
-        <v>-330907.35</v>
+        <v>-319439.44</v>
       </c>
       <c r="L17" s="3">
-        <v>2.81</v>
+        <v>3.07</v>
       </c>
       <c r="M17" s="3">
-        <v>12960.73</v>
+        <v>14489.96</v>
       </c>
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>853</v>
+        <v>1108</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>854</v>
+        <v>1109</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>855</v>
+        <v>1110</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>856</v>
+        <v>1111</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>857</v>
+        <v>1112</v>
       </c>
       <c r="F18" s="3">
         <v>1027095.81</v>
@@ -10513,19 +13096,19 @@
         <v>595477.93</v>
       </c>
       <c r="H18" s="3">
-        <v>85029.9</v>
+        <v>152981.57</v>
       </c>
       <c r="I18" s="3">
-        <v>680507.83</v>
+        <v>748459.5</v>
       </c>
       <c r="J18" s="3">
-        <v>66.26</v>
+        <v>72.87</v>
       </c>
       <c r="K18" s="3">
-        <v>-346587.98</v>
+        <v>-278636.31</v>
       </c>
       <c r="L18" s="3">
-        <v>6.22</v>
+        <v>5.66</v>
       </c>
       <c r="M18" s="3">
         <v>42329.63</v>
@@ -10533,19 +13116,19 @@
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>858</v>
+        <v>1113</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>859</v>
+        <v>1114</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>860</v>
+        <v>1115</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>861</v>
+        <v>1116</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>862</v>
+        <v>1117</v>
       </c>
       <c r="F19" s="3">
         <v>863850.75</v>
@@ -10554,19 +13137,19 @@
         <v>586071.53</v>
       </c>
       <c r="H19" s="3">
-        <v>81681.74</v>
+        <v>177201.17</v>
       </c>
       <c r="I19" s="3">
-        <v>667753.27</v>
+        <v>763272.7</v>
       </c>
       <c r="J19" s="3">
-        <v>77.3</v>
+        <v>88.36</v>
       </c>
       <c r="K19" s="3">
-        <v>-196097.48</v>
+        <v>-100578.05</v>
       </c>
       <c r="L19" s="3">
-        <v>5.39</v>
+        <v>4.71</v>
       </c>
       <c r="M19" s="3">
         <v>35969.66</v>
@@ -10574,19 +13157,19 @@
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>863</v>
+        <v>1118</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>864</v>
+        <v>1119</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>865</v>
+        <v>1120</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>866</v>
+        <v>1121</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>867</v>
+        <v>1122</v>
       </c>
       <c r="F20" s="3">
         <v>1246040.32</v>
@@ -10595,19 +13178,19 @@
         <v>624262.57</v>
       </c>
       <c r="H20" s="3">
-        <v>148685.31</v>
+        <v>222892.1</v>
       </c>
       <c r="I20" s="3">
-        <v>772947.88</v>
+        <v>847154.67</v>
       </c>
       <c r="J20" s="3">
-        <v>62.03</v>
+        <v>67.99</v>
       </c>
       <c r="K20" s="3">
-        <v>-473092.44</v>
+        <v>-398885.65</v>
       </c>
       <c r="L20" s="3">
-        <v>5.45</v>
+        <v>4.97</v>
       </c>
       <c r="M20" s="3">
         <v>42139.75</v>
@@ -10615,368 +13198,368 @@
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>868</v>
+        <v>1123</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>869</v>
+        <v>1124</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>870</v>
+        <v>1125</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>871</v>
+        <v>1126</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>872</v>
+        <v>1127</v>
       </c>
       <c r="F21" s="3">
         <v>875303.02</v>
       </c>
       <c r="G21" s="3">
-        <v>620068.84</v>
+        <v>648246.35</v>
       </c>
       <c r="H21" s="3">
-        <v>120786.92</v>
+        <v>105734.14</v>
       </c>
       <c r="I21" s="3">
-        <v>740855.76</v>
+        <v>753980.49</v>
       </c>
       <c r="J21" s="3">
-        <v>84.64</v>
+        <v>86.14</v>
       </c>
       <c r="K21" s="3">
-        <v>-134447.26</v>
+        <v>-121322.53</v>
       </c>
       <c r="L21" s="3">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="M21" s="3">
-        <v>13141.47</v>
+        <v>16187.85</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>873</v>
+        <v>1128</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>874</v>
+        <v>1129</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>875</v>
+        <v>1130</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>876</v>
+        <v>1131</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>877</v>
+        <v>1132</v>
       </c>
       <c r="F22" s="3">
         <v>859661.34</v>
       </c>
       <c r="G22" s="3">
-        <v>602858.92</v>
+        <v>645099.24</v>
       </c>
       <c r="H22" s="3">
-        <v>169774.51</v>
+        <v>145871.87</v>
       </c>
       <c r="I22" s="3">
-        <v>772633.43</v>
+        <v>790971.11</v>
       </c>
       <c r="J22" s="3">
-        <v>89.88</v>
+        <v>92.01</v>
       </c>
       <c r="K22" s="3">
-        <v>-87027.91</v>
+        <v>-68690.23</v>
       </c>
       <c r="L22" s="3">
-        <v>2.89</v>
+        <v>3.07</v>
       </c>
       <c r="M22" s="3">
-        <v>22313.83</v>
+        <v>24300.43</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>878</v>
+        <v>1133</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>879</v>
+        <v>1134</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>880</v>
+        <v>1135</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>881</v>
+        <v>1136</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>882</v>
+        <v>1137</v>
       </c>
       <c r="F23" s="3">
         <v>867257.37</v>
       </c>
       <c r="G23" s="3">
-        <v>664923.6</v>
+        <v>699295.26</v>
       </c>
       <c r="H23" s="3">
-        <v>154577.86</v>
+        <v>139289.13</v>
       </c>
       <c r="I23" s="3">
-        <v>819501.46</v>
+        <v>838584.39</v>
       </c>
       <c r="J23" s="3">
-        <v>94.49</v>
+        <v>96.69</v>
       </c>
       <c r="K23" s="3">
-        <v>-47755.91</v>
+        <v>-28672.98</v>
       </c>
       <c r="L23" s="3">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="M23" s="3">
-        <v>14893.41</v>
+        <v>14994.16</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>883</v>
+        <v>1138</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>884</v>
+        <v>1139</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>885</v>
+        <v>1140</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>886</v>
+        <v>1141</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>887</v>
+        <v>1142</v>
       </c>
       <c r="F24" s="3">
         <v>778641.12</v>
       </c>
       <c r="G24" s="3">
-        <v>539129.27</v>
+        <v>603872.26</v>
       </c>
       <c r="H24" s="3">
-        <v>158079.19</v>
+        <v>102576.19</v>
       </c>
       <c r="I24" s="3">
-        <v>697208.46</v>
+        <v>706448.45</v>
       </c>
       <c r="J24" s="3">
-        <v>89.54</v>
+        <v>90.73</v>
       </c>
       <c r="K24" s="3">
-        <v>-81432.66</v>
+        <v>-72192.67</v>
       </c>
       <c r="L24" s="3">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="M24" s="3">
-        <v>20716.24</v>
+        <v>22140.44</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>888</v>
+        <v>1143</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>889</v>
+        <v>1144</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>890</v>
+        <v>1145</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>891</v>
+        <v>1146</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>892</v>
+        <v>1147</v>
       </c>
       <c r="F25" s="3">
         <v>979868.9</v>
       </c>
       <c r="G25" s="3">
-        <v>567222.97</v>
+        <v>587644.12</v>
       </c>
       <c r="H25" s="3">
-        <v>205535.85</v>
+        <v>194303.87</v>
       </c>
       <c r="I25" s="3">
-        <v>772758.82</v>
+        <v>781947.99</v>
       </c>
       <c r="J25" s="3">
-        <v>78.86</v>
+        <v>79.8</v>
       </c>
       <c r="K25" s="3">
-        <v>-207110.08</v>
+        <v>-197920.91</v>
       </c>
       <c r="L25" s="3">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="M25" s="3">
-        <v>11328.99</v>
+        <v>14086.82</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>893</v>
+        <v>1148</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>894</v>
+        <v>1149</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>895</v>
+        <v>1150</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>896</v>
+        <v>1151</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>897</v>
+        <v>1152</v>
       </c>
       <c r="F26" s="3">
         <v>1011213.65</v>
       </c>
       <c r="G26" s="3">
-        <v>405416.82</v>
+        <v>428934.18</v>
       </c>
       <c r="H26" s="3">
-        <v>168378.98</v>
+        <v>159920.62</v>
       </c>
       <c r="I26" s="3">
-        <v>573795.8</v>
+        <v>588854.8</v>
       </c>
       <c r="J26" s="3">
-        <v>56.74</v>
+        <v>58.23</v>
       </c>
       <c r="K26" s="3">
-        <v>-437417.85</v>
+        <v>-422358.85</v>
       </c>
       <c r="L26" s="3">
-        <v>4.15</v>
+        <v>4.34</v>
       </c>
       <c r="M26" s="3">
-        <v>23830.93</v>
+        <v>25561.99</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>898</v>
+        <v>1153</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>899</v>
+        <v>1154</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>900</v>
+        <v>1155</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>901</v>
+        <v>1156</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>902</v>
+        <v>1157</v>
       </c>
       <c r="F27" s="3">
         <v>905279.17</v>
       </c>
       <c r="G27" s="3">
-        <v>531754.36</v>
+        <v>561447.94</v>
       </c>
       <c r="H27" s="3">
-        <v>168695.36</v>
+        <v>167639.85</v>
       </c>
       <c r="I27" s="3">
-        <v>700449.72</v>
+        <v>729087.79</v>
       </c>
       <c r="J27" s="3">
-        <v>77.37</v>
+        <v>80.54</v>
       </c>
       <c r="K27" s="3">
-        <v>-204829.45</v>
+        <v>-176191.38</v>
       </c>
       <c r="L27" s="3">
-        <v>2.0</v>
+        <v>2.01</v>
       </c>
       <c r="M27" s="3">
-        <v>14041.92</v>
+        <v>14637.65</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>903</v>
+        <v>1158</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>904</v>
+        <v>1159</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>905</v>
+        <v>1160</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>906</v>
+        <v>1161</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>907</v>
+        <v>1162</v>
       </c>
       <c r="F28" s="3">
         <v>948604.6</v>
       </c>
       <c r="G28" s="3">
-        <v>459956.71</v>
+        <v>509852.33</v>
       </c>
       <c r="H28" s="3">
-        <v>195239.42</v>
+        <v>168250.34</v>
       </c>
       <c r="I28" s="3">
-        <v>655196.13</v>
+        <v>678102.67</v>
       </c>
       <c r="J28" s="3">
-        <v>69.07</v>
+        <v>71.48</v>
       </c>
       <c r="K28" s="3">
-        <v>-293408.47</v>
+        <v>-270501.93</v>
       </c>
       <c r="L28" s="3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="M28" s="3">
-        <v>12076.54</v>
+        <v>12526.98</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>908</v>
+        <v>1163</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>909</v>
+        <v>1164</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>910</v>
+        <v>1165</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>911</v>
+        <v>1166</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>912</v>
+        <v>1167</v>
       </c>
       <c r="F29" s="3">
         <v>824118.89</v>
       </c>
       <c r="G29" s="3">
-        <v>468067.08</v>
+        <v>492157.73</v>
       </c>
       <c r="H29" s="3">
-        <v>130210.33</v>
+        <v>135763.44</v>
       </c>
       <c r="I29" s="3">
-        <v>598277.41</v>
+        <v>627921.17</v>
       </c>
       <c r="J29" s="3">
-        <v>72.6</v>
+        <v>76.19</v>
       </c>
       <c r="K29" s="3">
-        <v>-225841.48</v>
+        <v>-196197.72</v>
       </c>
       <c r="L29" s="3">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="M29" s="3">
         <v>17901.53</v>
@@ -10984,593 +13567,593 @@
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>913</v>
+        <v>1168</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>914</v>
+        <v>1169</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>915</v>
+        <v>1170</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>916</v>
+        <v>1171</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>917</v>
+        <v>1172</v>
       </c>
       <c r="F30" s="3">
         <v>877850.52</v>
       </c>
       <c r="G30" s="3">
-        <v>620041.23</v>
+        <v>682732.01</v>
       </c>
       <c r="H30" s="3">
-        <v>192645.05</v>
+        <v>157754.94</v>
       </c>
       <c r="I30" s="3">
-        <v>812686.28</v>
+        <v>840486.95</v>
       </c>
       <c r="J30" s="3">
-        <v>92.58</v>
+        <v>95.74</v>
       </c>
       <c r="K30" s="3">
-        <v>-65164.24</v>
+        <v>-37363.57</v>
       </c>
       <c r="L30" s="3">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="M30" s="3">
-        <v>17341.06</v>
+        <v>18740.24</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>918</v>
+        <v>1173</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>919</v>
+        <v>1174</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>920</v>
+        <v>1175</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>921</v>
+        <v>1176</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>922</v>
+        <v>1177</v>
       </c>
       <c r="F31" s="3">
         <v>990466.72</v>
       </c>
       <c r="G31" s="3">
-        <v>603373.43</v>
+        <v>634450.62</v>
       </c>
       <c r="H31" s="3">
-        <v>160654.28</v>
+        <v>163426.52</v>
       </c>
       <c r="I31" s="3">
-        <v>764027.71</v>
+        <v>797877.14</v>
       </c>
       <c r="J31" s="3">
-        <v>77.14</v>
+        <v>80.56</v>
       </c>
       <c r="K31" s="3">
-        <v>-226439.01</v>
+        <v>-192589.58</v>
       </c>
       <c r="L31" s="3">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="M31" s="3">
-        <v>29643.08</v>
+        <v>32803.64</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>923</v>
+        <v>1178</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>924</v>
+        <v>1179</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>925</v>
+        <v>1180</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>926</v>
+        <v>1181</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>927</v>
+        <v>1182</v>
       </c>
       <c r="F32" s="3">
         <v>892245.98</v>
       </c>
       <c r="G32" s="3">
-        <v>520388.03</v>
+        <v>544226.1</v>
       </c>
       <c r="H32" s="3">
-        <v>152131.78</v>
+        <v>153077.58</v>
       </c>
       <c r="I32" s="3">
-        <v>672519.81</v>
+        <v>697303.68</v>
       </c>
       <c r="J32" s="3">
-        <v>75.37</v>
+        <v>78.15</v>
       </c>
       <c r="K32" s="3">
-        <v>-219726.17</v>
+        <v>-194942.3</v>
       </c>
       <c r="L32" s="3">
-        <v>3.52</v>
+        <v>3.78</v>
       </c>
       <c r="M32" s="3">
-        <v>23660.3</v>
+        <v>26384.82</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>928</v>
+        <v>1183</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>929</v>
+        <v>1184</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>930</v>
+        <v>1185</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>931</v>
+        <v>1186</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>932</v>
+        <v>1187</v>
       </c>
       <c r="F33" s="3">
         <v>1265248.83</v>
       </c>
       <c r="G33" s="3">
-        <v>599111.82</v>
+        <v>664527.91</v>
       </c>
       <c r="H33" s="3">
-        <v>376866.48</v>
+        <v>308019.73</v>
       </c>
       <c r="I33" s="3">
-        <v>975978.3</v>
+        <v>972547.64</v>
       </c>
       <c r="J33" s="3">
-        <v>77.14</v>
+        <v>76.87</v>
       </c>
       <c r="K33" s="3">
-        <v>-289270.53</v>
+        <v>-292701.19</v>
       </c>
       <c r="L33" s="3">
-        <v>3.97</v>
+        <v>4.33</v>
       </c>
       <c r="M33" s="3">
-        <v>38705.04</v>
+        <v>42135.7</v>
       </c>
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>933</v>
+        <v>1188</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>934</v>
+        <v>1189</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>935</v>
+        <v>1190</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>936</v>
+        <v>1191</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>937</v>
+        <v>1192</v>
       </c>
       <c r="F34" s="3">
         <v>1062018.28</v>
       </c>
       <c r="G34" s="3">
-        <v>549534.6</v>
+        <v>593694.76</v>
       </c>
       <c r="H34" s="3">
-        <v>91326.66</v>
+        <v>46572.5</v>
       </c>
       <c r="I34" s="3">
-        <v>640861.26</v>
+        <v>640267.26</v>
       </c>
       <c r="J34" s="3">
-        <v>60.34</v>
+        <v>60.29</v>
       </c>
       <c r="K34" s="3">
-        <v>-421157.02</v>
+        <v>-421751.02</v>
       </c>
       <c r="L34" s="3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="M34" s="3">
-        <v>20853.8</v>
+        <v>21447.8</v>
       </c>
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>938</v>
+        <v>1193</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>939</v>
+        <v>1194</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>940</v>
+        <v>1195</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>941</v>
+        <v>1196</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>942</v>
+        <v>1197</v>
       </c>
       <c r="F35" s="3">
         <v>1027050.57</v>
       </c>
       <c r="G35" s="3">
-        <v>597219.34</v>
+        <v>646905.99</v>
       </c>
       <c r="H35" s="3">
-        <v>129344.32</v>
+        <v>78544.2</v>
       </c>
       <c r="I35" s="3">
-        <v>726563.66</v>
+        <v>725450.19</v>
       </c>
       <c r="J35" s="3">
-        <v>70.74</v>
+        <v>70.63</v>
       </c>
       <c r="K35" s="3">
-        <v>-300486.91</v>
+        <v>-301600.38</v>
       </c>
       <c r="L35" s="3">
-        <v>3.01</v>
+        <v>3.17</v>
       </c>
       <c r="M35" s="3">
-        <v>21876.24</v>
+        <v>22989.71</v>
       </c>
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>943</v>
+        <v>1198</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>944</v>
+        <v>1199</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>945</v>
+        <v>1200</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>946</v>
+        <v>1201</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>947</v>
+        <v>1202</v>
       </c>
       <c r="F36" s="3">
         <v>1150571.33</v>
       </c>
       <c r="G36" s="3">
-        <v>694085.83</v>
+        <v>756420.19</v>
       </c>
       <c r="H36" s="3">
-        <v>291529.76</v>
+        <v>303154.11</v>
       </c>
       <c r="I36" s="3">
-        <v>985615.59</v>
+        <v>1059574.3</v>
       </c>
       <c r="J36" s="3">
-        <v>85.66</v>
+        <v>92.09</v>
       </c>
       <c r="K36" s="3">
-        <v>-164955.74</v>
+        <v>-90997.03</v>
       </c>
       <c r="L36" s="3">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="M36" s="3">
-        <v>21450.86</v>
+        <v>26971.06</v>
       </c>
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>948</v>
+        <v>1203</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>949</v>
+        <v>1204</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>950</v>
+        <v>1205</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>951</v>
+        <v>1206</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>952</v>
+        <v>1207</v>
       </c>
       <c r="F37" s="3">
         <v>1374896.6</v>
       </c>
       <c r="G37" s="3">
-        <v>655101.62</v>
+        <v>708178.88</v>
       </c>
       <c r="H37" s="3">
-        <v>279050.14</v>
+        <v>291642.97</v>
       </c>
       <c r="I37" s="3">
-        <v>934151.76</v>
+        <v>999821.85</v>
       </c>
       <c r="J37" s="3">
-        <v>67.94</v>
+        <v>72.72</v>
       </c>
       <c r="K37" s="3">
-        <v>-440744.84</v>
+        <v>-375074.75</v>
       </c>
       <c r="L37" s="3">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="M37" s="3">
-        <v>29630.76</v>
+        <v>32842.86</v>
       </c>
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>953</v>
+        <v>1208</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>954</v>
+        <v>1209</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>955</v>
+        <v>1210</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>956</v>
+        <v>1211</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>957</v>
+        <v>1212</v>
       </c>
       <c r="F38" s="3">
         <v>904558.95</v>
       </c>
       <c r="G38" s="3">
-        <v>493494.33</v>
+        <v>536752.81</v>
       </c>
       <c r="H38" s="3">
-        <v>219768.3</v>
+        <v>245612.05</v>
       </c>
       <c r="I38" s="3">
-        <v>713262.63</v>
+        <v>782364.86</v>
       </c>
       <c r="J38" s="3">
-        <v>78.85</v>
+        <v>86.49</v>
       </c>
       <c r="K38" s="3">
-        <v>-191296.32</v>
+        <v>-122194.09</v>
       </c>
       <c r="L38" s="3">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="M38" s="3">
-        <v>17498.94</v>
+        <v>19098.98</v>
       </c>
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>958</v>
+        <v>1213</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>959</v>
+        <v>1214</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>960</v>
+        <v>1215</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>961</v>
+        <v>1216</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>962</v>
+        <v>1217</v>
       </c>
       <c r="F39" s="3">
         <v>1106940.64</v>
       </c>
       <c r="G39" s="3">
-        <v>466035.7</v>
+        <v>508788.01</v>
       </c>
       <c r="H39" s="3">
-        <v>223677.21</v>
+        <v>237111.85</v>
       </c>
       <c r="I39" s="3">
-        <v>689712.91</v>
+        <v>745899.86</v>
       </c>
       <c r="J39" s="3">
-        <v>62.31</v>
+        <v>67.38</v>
       </c>
       <c r="K39" s="3">
-        <v>-417227.73</v>
+        <v>-361040.78</v>
       </c>
       <c r="L39" s="3">
-        <v>3.01</v>
+        <v>3.18</v>
       </c>
       <c r="M39" s="3">
-        <v>20733.63</v>
+        <v>23734.72</v>
       </c>
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>963</v>
+        <v>1218</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>964</v>
+        <v>1219</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>965</v>
+        <v>1220</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>966</v>
+        <v>1221</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>967</v>
+        <v>1222</v>
       </c>
       <c r="F40" s="3">
         <v>887573.45</v>
       </c>
       <c r="G40" s="3">
-        <v>422036.87</v>
+        <v>457043.02</v>
       </c>
       <c r="H40" s="3">
-        <v>145344.43</v>
+        <v>110925.96</v>
       </c>
       <c r="I40" s="3">
-        <v>567381.3</v>
+        <v>567968.98</v>
       </c>
       <c r="J40" s="3">
-        <v>63.92</v>
+        <v>63.99</v>
       </c>
       <c r="K40" s="3">
-        <v>-320192.15</v>
+        <v>-319604.47</v>
       </c>
       <c r="L40" s="3">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="M40" s="3">
-        <v>5998.03</v>
+        <v>7048.51</v>
       </c>
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>968</v>
+        <v>1223</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>969</v>
+        <v>1224</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>970</v>
+        <v>1225</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>971</v>
+        <v>1226</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>972</v>
+        <v>1227</v>
       </c>
       <c r="F41" s="3">
         <v>1236217.2</v>
       </c>
       <c r="G41" s="3">
-        <v>579919.9</v>
+        <v>628068.11</v>
       </c>
       <c r="H41" s="3">
-        <v>230819.64</v>
+        <v>181378.27</v>
       </c>
       <c r="I41" s="3">
-        <v>810739.54</v>
+        <v>809446.38</v>
       </c>
       <c r="J41" s="3">
-        <v>65.58</v>
+        <v>65.48</v>
       </c>
       <c r="K41" s="3">
-        <v>-425477.66</v>
+        <v>-426770.82</v>
       </c>
       <c r="L41" s="3">
-        <v>2.16</v>
+        <v>3.32</v>
       </c>
       <c r="M41" s="3">
-        <v>17477.0</v>
+        <v>26896.64</v>
       </c>
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>973</v>
+        <v>1228</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>974</v>
+        <v>1229</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>975</v>
+        <v>1230</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>976</v>
+        <v>1231</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>977</v>
+        <v>1232</v>
       </c>
       <c r="F42" s="3">
         <v>912015.93</v>
       </c>
       <c r="G42" s="3">
-        <v>502437.15</v>
+        <v>538954.43</v>
       </c>
       <c r="H42" s="3">
-        <v>191522.73</v>
+        <v>159630.38</v>
       </c>
       <c r="I42" s="3">
-        <v>693959.88</v>
+        <v>698584.81</v>
       </c>
       <c r="J42" s="3">
-        <v>76.09</v>
+        <v>76.6</v>
       </c>
       <c r="K42" s="3">
-        <v>-218056.05</v>
+        <v>-213431.12</v>
       </c>
       <c r="L42" s="3">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="M42" s="3">
-        <v>14540.24</v>
+        <v>14747.12</v>
       </c>
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>978</v>
+        <v>1233</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>979</v>
+        <v>1234</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>980</v>
+        <v>1235</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>981</v>
+        <v>1236</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>982</v>
+        <v>1237</v>
       </c>
       <c r="F43" s="3">
         <v>1043081.21</v>
       </c>
       <c r="G43" s="3">
-        <v>679446.22</v>
+        <v>759332.15</v>
       </c>
       <c r="H43" s="3">
-        <v>247615.35</v>
+        <v>181868.85</v>
       </c>
       <c r="I43" s="3">
-        <v>927061.57</v>
+        <v>941201.0</v>
       </c>
       <c r="J43" s="3">
-        <v>88.88</v>
+        <v>90.23</v>
       </c>
       <c r="K43" s="3">
-        <v>-116019.64</v>
+        <v>-101880.21</v>
       </c>
       <c r="L43" s="3">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="M43" s="3">
-        <v>19197.77</v>
+        <v>20597.93</v>
       </c>
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>983</v>
+        <v>1238</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>984</v>
+        <v>1239</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>985</v>
+        <v>1240</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>986</v>
+        <v>1241</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>987</v>
+        <v>1242</v>
       </c>
       <c r="F44" s="3">
         <v>1113507.9</v>
@@ -11599,19 +14182,19 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>988</v>
+        <v>1243</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>989</v>
+        <v>1244</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>990</v>
+        <v>1245</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>991</v>
+        <v>1246</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>992</v>
+        <v>1247</v>
       </c>
       <c r="F45" s="3">
         <v>918319.81</v>
@@ -11640,19 +14223,19 @@
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>993</v>
+        <v>1248</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>994</v>
+        <v>1249</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>995</v>
+        <v>1250</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>996</v>
+        <v>1251</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>997</v>
+        <v>1252</v>
       </c>
       <c r="F46" s="3">
         <v>1066780.42</v>
@@ -11681,19 +14264,19 @@
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>998</v>
+        <v>1253</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>999</v>
+        <v>1254</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1000</v>
+        <v>1255</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1001</v>
+        <v>1256</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1002</v>
+        <v>1257</v>
       </c>
       <c r="F47" s="3">
         <v>1336954.46</v>
@@ -11722,19 +14305,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>1003</v>
+        <v>1258</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1004</v>
+        <v>1259</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1005</v>
+        <v>1260</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1006</v>
+        <v>1261</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1007</v>
+        <v>1262</v>
       </c>
       <c r="F48" s="3">
         <v>1022376.56</v>
@@ -11763,19 +14346,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>1008</v>
+        <v>1263</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1009</v>
+        <v>1264</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1010</v>
+        <v>1265</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1011</v>
+        <v>1266</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1012</v>
+        <v>1267</v>
       </c>
       <c r="F49" s="3">
         <v>972020.19</v>
@@ -11804,19 +14387,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>1013</v>
+        <v>1268</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1014</v>
+        <v>1269</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1015</v>
+        <v>1270</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1016</v>
+        <v>1271</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1017</v>
+        <v>1272</v>
       </c>
       <c r="F50" s="3">
         <v>963790.11</v>
@@ -11845,19 +14428,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>1018</v>
+        <v>1273</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1019</v>
+        <v>1274</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1020</v>
+        <v>1275</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1021</v>
+        <v>1276</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1022</v>
+        <v>1277</v>
       </c>
       <c r="F51" s="3">
         <v>954958.72</v>
@@ -11886,19 +14469,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>1023</v>
+        <v>1278</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1024</v>
+        <v>1279</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1025</v>
+        <v>1280</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1026</v>
+        <v>1281</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1027</v>
+        <v>1282</v>
       </c>
       <c r="F52" s="3">
         <v>1154949.94</v>
@@ -11932,7 +14515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -11982,282 +14565,282 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>741</v>
+        <v>1283</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>742</v>
+        <v>1284</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>743</v>
+        <v>1285</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>744</v>
+        <v>1286</v>
       </c>
       <c r="E2" s="3">
         <v>5936775.24</v>
       </c>
       <c r="F2" s="3">
-        <v>2855344.19</v>
+        <v>2997214.77</v>
       </c>
       <c r="G2" s="3">
-        <v>1707375.46</v>
+        <v>1742808.57</v>
       </c>
       <c r="H2" s="3">
-        <v>4562719.65</v>
+        <v>4740023.34</v>
       </c>
       <c r="I2" s="3">
-        <v>76.86</v>
+        <v>79.84</v>
       </c>
       <c r="J2" s="3">
-        <v>-1374055.59</v>
+        <v>-1196751.9</v>
       </c>
       <c r="K2" s="3">
-        <v>90408.34</v>
+        <v>100694.46</v>
       </c>
       <c r="L2" s="3">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>745</v>
+        <v>1287</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>746</v>
+        <v>1288</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>747</v>
+        <v>1289</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>748</v>
+        <v>1290</v>
       </c>
       <c r="E3" s="3">
         <v>3346888.02</v>
       </c>
       <c r="F3" s="3">
-        <v>1563137.41</v>
+        <v>1628143.75</v>
       </c>
       <c r="G3" s="3">
-        <v>842408.36</v>
+        <v>849147.0</v>
       </c>
       <c r="H3" s="3">
-        <v>2405545.77</v>
+        <v>2477290.75</v>
       </c>
       <c r="I3" s="3">
-        <v>71.87</v>
+        <v>74.02</v>
       </c>
       <c r="J3" s="3">
-        <v>-941342.25</v>
+        <v>-869597.27</v>
       </c>
       <c r="K3" s="3">
-        <v>42003.22</v>
+        <v>44957.14</v>
       </c>
       <c r="L3" s="3">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>749</v>
+        <v>1291</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>750</v>
+        <v>1292</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>751</v>
+        <v>1293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>752</v>
+        <v>1294</v>
       </c>
       <c r="E4" s="3">
         <v>6248074.42</v>
       </c>
       <c r="F4" s="3">
-        <v>2810038.31</v>
+        <v>2848442.36</v>
       </c>
       <c r="G4" s="3">
-        <v>1187910.54</v>
+        <v>1454888.41</v>
       </c>
       <c r="H4" s="3">
-        <v>3997948.85</v>
+        <v>4303330.77</v>
       </c>
       <c r="I4" s="3">
-        <v>63.99</v>
+        <v>68.87</v>
       </c>
       <c r="J4" s="3">
-        <v>-2250125.57</v>
+        <v>-1944743.65</v>
       </c>
       <c r="K4" s="3">
-        <v>158554.02</v>
+        <v>160191.2</v>
       </c>
       <c r="L4" s="3">
-        <v>3.97</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>753</v>
+        <v>1295</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>754</v>
+        <v>1296</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>755</v>
+        <v>1297</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>756</v>
+        <v>1298</v>
       </c>
       <c r="E5" s="3">
         <v>7225829.17</v>
       </c>
       <c r="F5" s="3">
-        <v>4391331.5</v>
+        <v>4684391.67</v>
       </c>
       <c r="G5" s="3">
-        <v>1278931.94</v>
+        <v>1183585.99</v>
       </c>
       <c r="H5" s="3">
-        <v>5670263.44</v>
+        <v>5867977.66</v>
       </c>
       <c r="I5" s="3">
-        <v>78.47</v>
+        <v>81.21</v>
       </c>
       <c r="J5" s="3">
-        <v>-1555565.73</v>
+        <v>-1357851.51</v>
       </c>
       <c r="K5" s="3">
-        <v>132343.33</v>
+        <v>144436.32</v>
       </c>
       <c r="L5" s="3">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>757</v>
+        <v>1299</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>758</v>
+        <v>1300</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>759</v>
+        <v>1301</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>760</v>
+        <v>1302</v>
       </c>
       <c r="E6" s="3">
         <v>6938999.79</v>
       </c>
       <c r="F6" s="3">
-        <v>3957735.53</v>
+        <v>4258695.12</v>
       </c>
       <c r="G6" s="3">
-        <v>1232382.28</v>
+        <v>1043158.91</v>
       </c>
       <c r="H6" s="3">
-        <v>5190117.81</v>
+        <v>5301854.03</v>
       </c>
       <c r="I6" s="3">
-        <v>74.8</v>
+        <v>76.41</v>
       </c>
       <c r="J6" s="3">
-        <v>-1748881.98</v>
+        <v>-1637145.76</v>
       </c>
       <c r="K6" s="3">
-        <v>169981.05</v>
+        <v>182403.43</v>
       </c>
       <c r="L6" s="3">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>761</v>
+        <v>1303</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>762</v>
+        <v>1304</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>763</v>
+        <v>1305</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>764</v>
+        <v>1306</v>
       </c>
       <c r="E7" s="3">
         <v>4536967.52</v>
       </c>
       <c r="F7" s="3">
-        <v>2308717.48</v>
+        <v>2510139.89</v>
       </c>
       <c r="G7" s="3">
-        <v>1014025.41</v>
+        <v>1077520.98</v>
       </c>
       <c r="H7" s="3">
-        <v>3322742.89</v>
+        <v>3587660.87</v>
       </c>
       <c r="I7" s="3">
-        <v>73.24</v>
+        <v>79.08</v>
       </c>
       <c r="J7" s="3">
-        <v>-1214224.63</v>
+        <v>-949306.65</v>
       </c>
       <c r="K7" s="3">
-        <v>89314.19</v>
+        <v>102647.62</v>
       </c>
       <c r="L7" s="3">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>765</v>
+        <v>1307</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>766</v>
+        <v>1308</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>767</v>
+        <v>1309</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>768</v>
+        <v>1310</v>
       </c>
       <c r="E8" s="3">
         <v>7177495.92</v>
       </c>
       <c r="F8" s="3">
-        <v>4127264.82</v>
+        <v>4326822.39</v>
       </c>
       <c r="G8" s="3">
-        <v>1273507.93</v>
+        <v>1092009.24</v>
       </c>
       <c r="H8" s="3">
-        <v>5400772.75</v>
+        <v>5418831.63</v>
       </c>
       <c r="I8" s="3">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="J8" s="3">
-        <v>-1776723.17</v>
+        <v>-1758664.29</v>
       </c>
       <c r="K8" s="3">
-        <v>100092.65</v>
+        <v>112169.81</v>
       </c>
       <c r="L8" s="3">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>769</v>
+        <v>1311</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>770</v>
+        <v>1312</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>771</v>
+        <v>1313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>772</v>
+        <v>1314</v>
       </c>
       <c r="E9" s="3">
         <v>6405049.98</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1315" count="1315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1857" count="1857">
   <si>
     <t>Region</t>
   </si>
@@ -6805,6 +6805,4884 @@
         <rFont val="Helvetica"/>
       </rPr>
       <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
     </r>
   </si>
   <si>
@@ -12358,7 +17236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:V52"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -12419,40 +17297,40 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1028</v>
+        <v>1570</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1029</v>
+        <v>1571</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1030</v>
+        <v>1572</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1031</v>
+        <v>1573</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1032</v>
+        <v>1574</v>
       </c>
       <c r="F2" s="3">
         <v>747825.09</v>
       </c>
       <c r="G2" s="3">
-        <v>433335.2</v>
+        <v>441503.81</v>
       </c>
       <c r="H2" s="3">
-        <v>196201.49</v>
+        <v>202726.94</v>
       </c>
       <c r="I2" s="3">
-        <v>629536.69</v>
+        <v>644230.75</v>
       </c>
       <c r="J2" s="3">
-        <v>84.18</v>
+        <v>86.15</v>
       </c>
       <c r="K2" s="3">
-        <v>-118288.4</v>
+        <v>-103594.34</v>
       </c>
       <c r="L2" s="3">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="M2" s="3">
         <v>13001.24</v>
@@ -12460,409 +17338,409 @@
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>1033</v>
+        <v>1575</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1034</v>
+        <v>1576</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1035</v>
+        <v>1577</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1036</v>
+        <v>1578</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1037</v>
+        <v>1579</v>
       </c>
       <c r="F3" s="3">
         <v>755003.49</v>
       </c>
       <c r="G3" s="3">
-        <v>356000.98</v>
+        <v>368509.79</v>
       </c>
       <c r="H3" s="3">
-        <v>274374.86</v>
+        <v>282837.68</v>
       </c>
       <c r="I3" s="3">
-        <v>630375.84</v>
+        <v>651347.47</v>
       </c>
       <c r="J3" s="3">
-        <v>83.49</v>
+        <v>86.27</v>
       </c>
       <c r="K3" s="3">
-        <v>-124627.65</v>
+        <v>-103656.02</v>
       </c>
       <c r="L3" s="3">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M3" s="3">
-        <v>8112.89</v>
+        <v>8146.61</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>1038</v>
+        <v>1580</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1039</v>
+        <v>1581</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1040</v>
+        <v>1582</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1041</v>
+        <v>1583</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1042</v>
+        <v>1584</v>
       </c>
       <c r="F4" s="3">
         <v>664724.91</v>
       </c>
       <c r="G4" s="3">
-        <v>401266.61</v>
+        <v>417473.07</v>
       </c>
       <c r="H4" s="3">
-        <v>226635.15</v>
+        <v>231241.19</v>
       </c>
       <c r="I4" s="3">
-        <v>627901.76</v>
+        <v>648714.26</v>
       </c>
       <c r="J4" s="3">
-        <v>94.46</v>
+        <v>97.59</v>
       </c>
       <c r="K4" s="3">
-        <v>-36823.15</v>
+        <v>-16010.65</v>
       </c>
       <c r="L4" s="3">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="M4" s="3">
-        <v>15630.2</v>
+        <v>15960.0</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>1043</v>
+        <v>1585</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1044</v>
+        <v>1586</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1045</v>
+        <v>1587</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1046</v>
+        <v>1588</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1047</v>
+        <v>1589</v>
       </c>
       <c r="F5" s="3">
         <v>745422.79</v>
       </c>
       <c r="G5" s="3">
-        <v>317514.42</v>
+        <v>330813.87</v>
       </c>
       <c r="H5" s="3">
-        <v>221782.22</v>
+        <v>228412.34</v>
       </c>
       <c r="I5" s="3">
-        <v>539296.64</v>
+        <v>559226.21</v>
       </c>
       <c r="J5" s="3">
-        <v>72.35</v>
+        <v>75.02</v>
       </c>
       <c r="K5" s="3">
-        <v>-206126.15</v>
+        <v>-186196.58</v>
       </c>
       <c r="L5" s="3">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="M5" s="3">
-        <v>18120.3</v>
+        <v>18873.6</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>1048</v>
+        <v>1590</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1049</v>
+        <v>1591</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1050</v>
+        <v>1592</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1051</v>
+        <v>1593</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1052</v>
+        <v>1594</v>
       </c>
       <c r="F6" s="3">
         <v>750633.4</v>
       </c>
       <c r="G6" s="3">
-        <v>503665.43</v>
+        <v>522738.61</v>
       </c>
       <c r="H6" s="3">
-        <v>233464.17</v>
+        <v>241147.93</v>
       </c>
       <c r="I6" s="3">
-        <v>737129.6</v>
+        <v>763886.54</v>
       </c>
       <c r="J6" s="3">
-        <v>98.2</v>
+        <v>101.77</v>
       </c>
       <c r="K6" s="3">
-        <v>-13503.8</v>
+        <v>13253.14</v>
       </c>
       <c r="L6" s="3">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="M6" s="3">
-        <v>18828.78</v>
+        <v>19905.22</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>1053</v>
+        <v>1595</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1054</v>
+        <v>1596</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1055</v>
+        <v>1597</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1056</v>
+        <v>1598</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1057</v>
+        <v>1599</v>
       </c>
       <c r="F7" s="3">
         <v>804591.82</v>
       </c>
       <c r="G7" s="3">
-        <v>310652.86</v>
+        <v>333709.75</v>
       </c>
       <c r="H7" s="3">
-        <v>216466.54</v>
+        <v>211275.31</v>
       </c>
       <c r="I7" s="3">
-        <v>527119.4</v>
+        <v>544985.06</v>
       </c>
       <c r="J7" s="3">
-        <v>65.51</v>
+        <v>67.73</v>
       </c>
       <c r="K7" s="3">
-        <v>-277472.42</v>
+        <v>-259606.76</v>
       </c>
       <c r="L7" s="3">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="M7" s="3">
-        <v>11278.51</v>
+        <v>11953.51</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>1058</v>
+        <v>1600</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1059</v>
+        <v>1601</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1060</v>
+        <v>1602</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1061</v>
+        <v>1603</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1062</v>
+        <v>1604</v>
       </c>
       <c r="F8" s="3">
         <v>726832.71</v>
       </c>
       <c r="G8" s="3">
-        <v>281204.5</v>
+        <v>299388.8</v>
       </c>
       <c r="H8" s="3">
-        <v>174721.77</v>
+        <v>177206.25</v>
       </c>
       <c r="I8" s="3">
-        <v>455926.27</v>
+        <v>476595.05</v>
       </c>
       <c r="J8" s="3">
-        <v>62.73</v>
+        <v>65.57</v>
       </c>
       <c r="K8" s="3">
-        <v>-270906.44</v>
+        <v>-250237.66</v>
       </c>
       <c r="L8" s="3">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="M8" s="3">
-        <v>2474.76</v>
+        <v>2901.44</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>1063</v>
+        <v>1605</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1064</v>
+        <v>1606</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1065</v>
+        <v>1607</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1066</v>
+        <v>1608</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1067</v>
+        <v>1609</v>
       </c>
       <c r="F9" s="3">
         <v>741741.03</v>
       </c>
       <c r="G9" s="3">
-        <v>393574.77</v>
+        <v>413158.92</v>
       </c>
       <c r="H9" s="3">
-        <v>199162.37</v>
+        <v>203127.53</v>
       </c>
       <c r="I9" s="3">
-        <v>592737.14</v>
+        <v>616286.45</v>
       </c>
       <c r="J9" s="3">
-        <v>79.91</v>
+        <v>83.09</v>
       </c>
       <c r="K9" s="3">
-        <v>-149003.89</v>
+        <v>-125454.58</v>
       </c>
       <c r="L9" s="3">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="M9" s="3">
-        <v>13247.78</v>
+        <v>13840.72</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>1068</v>
+        <v>1610</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1069</v>
+        <v>1611</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1070</v>
+        <v>1612</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1071</v>
+        <v>1613</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1072</v>
+        <v>1614</v>
       </c>
       <c r="F10" s="3">
         <v>859984.15</v>
       </c>
       <c r="G10" s="3">
-        <v>420196.37</v>
+        <v>438610.36</v>
       </c>
       <c r="H10" s="3">
-        <v>241191.95</v>
+        <v>272896.72</v>
       </c>
       <c r="I10" s="3">
-        <v>661388.32</v>
+        <v>711507.08</v>
       </c>
       <c r="J10" s="3">
-        <v>76.91</v>
+        <v>82.73</v>
       </c>
       <c r="K10" s="3">
-        <v>-198595.83</v>
+        <v>-148477.07</v>
       </c>
       <c r="L10" s="3">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="M10" s="3">
-        <v>15467.44</v>
+        <v>16230.96</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>1073</v>
+        <v>1615</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1074</v>
+        <v>1616</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1075</v>
+        <v>1617</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1076</v>
+        <v>1618</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1077</v>
+        <v>1619</v>
       </c>
       <c r="F11" s="3">
         <v>903047.31</v>
       </c>
       <c r="G11" s="3">
-        <v>363634.16</v>
+        <v>380004.89</v>
       </c>
       <c r="H11" s="3">
-        <v>184170.36</v>
+        <v>178232.3</v>
       </c>
       <c r="I11" s="3">
-        <v>547804.52</v>
+        <v>558237.19</v>
       </c>
       <c r="J11" s="3">
-        <v>60.66</v>
+        <v>61.82</v>
       </c>
       <c r="K11" s="3">
-        <v>-355242.79</v>
+        <v>-344810.12</v>
       </c>
       <c r="L11" s="3">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="M11" s="3">
-        <v>13495.5</v>
+        <v>14586.3</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>1078</v>
+        <v>1620</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1079</v>
+        <v>1621</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1080</v>
+        <v>1622</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1081</v>
+        <v>1623</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1082</v>
+        <v>1624</v>
       </c>
       <c r="F12" s="3">
         <v>775221.33</v>
       </c>
       <c r="G12" s="3">
-        <v>413873.87</v>
+        <v>431993.63</v>
       </c>
       <c r="H12" s="3">
-        <v>201452.32</v>
+        <v>204271.1</v>
       </c>
       <c r="I12" s="3">
-        <v>615326.19</v>
+        <v>636264.73</v>
       </c>
       <c r="J12" s="3">
-        <v>79.37</v>
+        <v>82.08</v>
       </c>
       <c r="K12" s="3">
-        <v>-159895.14</v>
+        <v>-138956.6</v>
       </c>
       <c r="L12" s="3">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="M12" s="3">
         <v>7660.09</v>
@@ -12870,40 +17748,40 @@
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>1083</v>
+        <v>1625</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1084</v>
+        <v>1626</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1085</v>
+        <v>1627</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1086</v>
+        <v>1628</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1087</v>
+        <v>1629</v>
       </c>
       <c r="F13" s="3">
         <v>808635.23</v>
       </c>
       <c r="G13" s="3">
-        <v>430439.35</v>
+        <v>447572.93</v>
       </c>
       <c r="H13" s="3">
-        <v>222332.37</v>
+        <v>220771.34</v>
       </c>
       <c r="I13" s="3">
-        <v>652771.72</v>
+        <v>668344.27</v>
       </c>
       <c r="J13" s="3">
-        <v>80.73</v>
+        <v>82.65</v>
       </c>
       <c r="K13" s="3">
-        <v>-155863.51</v>
+        <v>-140290.96</v>
       </c>
       <c r="L13" s="3">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M13" s="3">
         <v>8334.11</v>
@@ -12911,163 +17789,163 @@
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>1088</v>
+        <v>1630</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1089</v>
+        <v>1631</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1090</v>
+        <v>1632</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1091</v>
+        <v>1633</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1092</v>
+        <v>1634</v>
       </c>
       <c r="F14" s="3">
         <v>773239.07</v>
       </c>
       <c r="G14" s="3">
-        <v>339605.28</v>
+        <v>348416.77</v>
       </c>
       <c r="H14" s="3">
-        <v>271917.34</v>
+        <v>279948.77</v>
       </c>
       <c r="I14" s="3">
-        <v>611522.62</v>
+        <v>628365.54</v>
       </c>
       <c r="J14" s="3">
-        <v>79.09</v>
+        <v>81.26</v>
       </c>
       <c r="K14" s="3">
-        <v>-161716.45</v>
+        <v>-144873.53</v>
       </c>
       <c r="L14" s="3">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M14" s="3">
-        <v>8220.8</v>
+        <v>8679.8</v>
       </c>
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>1093</v>
+        <v>1635</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1094</v>
+        <v>1636</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1095</v>
+        <v>1637</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1096</v>
+        <v>1638</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1097</v>
+        <v>1639</v>
       </c>
       <c r="F15" s="3">
         <v>788718.67</v>
       </c>
       <c r="G15" s="3">
-        <v>245089.78</v>
+        <v>254504.76</v>
       </c>
       <c r="H15" s="3">
-        <v>252408.27</v>
+        <v>262486.01</v>
       </c>
       <c r="I15" s="3">
-        <v>497498.05</v>
+        <v>516990.77</v>
       </c>
       <c r="J15" s="3">
-        <v>63.08</v>
+        <v>65.55</v>
       </c>
       <c r="K15" s="3">
-        <v>-291220.62</v>
+        <v>-271727.9</v>
       </c>
       <c r="L15" s="3">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="M15" s="3">
-        <v>11703.66</v>
+        <v>11754.24</v>
       </c>
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>1098</v>
+        <v>1640</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1099</v>
+        <v>1641</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1100</v>
+        <v>1642</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1101</v>
+        <v>1643</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1102</v>
+        <v>1644</v>
       </c>
       <c r="F16" s="3">
         <v>757031.95</v>
       </c>
       <c r="G16" s="3">
-        <v>204003.16</v>
+        <v>211873.41</v>
       </c>
       <c r="H16" s="3">
-        <v>158761.67</v>
+        <v>162552.31</v>
       </c>
       <c r="I16" s="3">
-        <v>362764.83</v>
+        <v>374425.72</v>
       </c>
       <c r="J16" s="3">
-        <v>47.92</v>
+        <v>49.46</v>
       </c>
       <c r="K16" s="3">
-        <v>-394267.12</v>
+        <v>-382606.23</v>
       </c>
       <c r="L16" s="3">
         <v>1.47</v>
       </c>
       <c r="M16" s="3">
-        <v>5337.74</v>
+        <v>5487.66</v>
       </c>
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>1103</v>
+        <v>1645</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1104</v>
+        <v>1646</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1105</v>
+        <v>1647</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1106</v>
+        <v>1648</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1107</v>
+        <v>1649</v>
       </c>
       <c r="F17" s="3">
         <v>792097.85</v>
       </c>
       <c r="G17" s="3">
-        <v>253932.12</v>
+        <v>261921.32</v>
       </c>
       <c r="H17" s="3">
-        <v>218726.29</v>
+        <v>216912.54</v>
       </c>
       <c r="I17" s="3">
-        <v>472658.41</v>
+        <v>478833.86</v>
       </c>
       <c r="J17" s="3">
-        <v>59.67</v>
+        <v>60.45</v>
       </c>
       <c r="K17" s="3">
-        <v>-319439.44</v>
+        <v>-313263.99</v>
       </c>
       <c r="L17" s="3">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="M17" s="3">
         <v>14489.96</v>
@@ -13075,19 +17953,19 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>1108</v>
+        <v>1650</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1109</v>
+        <v>1651</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1110</v>
+        <v>1652</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1111</v>
+        <v>1653</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1112</v>
+        <v>1654</v>
       </c>
       <c r="F18" s="3">
         <v>1027095.81</v>
@@ -13116,19 +17994,19 @@
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>1113</v>
+        <v>1655</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1114</v>
+        <v>1656</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1115</v>
+        <v>1657</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1116</v>
+        <v>1658</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1117</v>
+        <v>1659</v>
       </c>
       <c r="F19" s="3">
         <v>863850.75</v>
@@ -13157,19 +18035,19 @@
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>1118</v>
+        <v>1660</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1119</v>
+        <v>1661</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1120</v>
+        <v>1662</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1121</v>
+        <v>1663</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1122</v>
+        <v>1664</v>
       </c>
       <c r="F20" s="3">
         <v>1246040.32</v>
@@ -13198,163 +18076,163 @@
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>1123</v>
+        <v>1665</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1124</v>
+        <v>1666</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1125</v>
+        <v>1667</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1126</v>
+        <v>1668</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1127</v>
+        <v>1669</v>
       </c>
       <c r="F21" s="3">
         <v>875303.02</v>
       </c>
       <c r="G21" s="3">
-        <v>648246.35</v>
+        <v>672212.88</v>
       </c>
       <c r="H21" s="3">
-        <v>105734.14</v>
+        <v>94759.99</v>
       </c>
       <c r="I21" s="3">
-        <v>753980.49</v>
+        <v>766972.87</v>
       </c>
       <c r="J21" s="3">
-        <v>86.14</v>
+        <v>87.62</v>
       </c>
       <c r="K21" s="3">
-        <v>-121322.53</v>
+        <v>-108330.15</v>
       </c>
       <c r="L21" s="3">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="M21" s="3">
-        <v>16187.85</v>
+        <v>16975.05</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>1128</v>
+        <v>1670</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1129</v>
+        <v>1671</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1130</v>
+        <v>1672</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1131</v>
+        <v>1673</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1132</v>
+        <v>1674</v>
       </c>
       <c r="F22" s="3">
         <v>859661.34</v>
       </c>
       <c r="G22" s="3">
-        <v>645099.24</v>
+        <v>670597.42</v>
       </c>
       <c r="H22" s="3">
-        <v>145871.87</v>
+        <v>138563.32</v>
       </c>
       <c r="I22" s="3">
-        <v>790971.11</v>
+        <v>809160.74</v>
       </c>
       <c r="J22" s="3">
-        <v>92.01</v>
+        <v>94.13</v>
       </c>
       <c r="K22" s="3">
-        <v>-68690.23</v>
+        <v>-50500.6</v>
       </c>
       <c r="L22" s="3">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="M22" s="3">
-        <v>24300.43</v>
+        <v>26115.72</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>1133</v>
+        <v>1675</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1134</v>
+        <v>1676</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1135</v>
+        <v>1677</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1136</v>
+        <v>1678</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1137</v>
+        <v>1679</v>
       </c>
       <c r="F23" s="3">
         <v>867257.37</v>
       </c>
       <c r="G23" s="3">
-        <v>699295.26</v>
+        <v>729552.33</v>
       </c>
       <c r="H23" s="3">
-        <v>139289.13</v>
+        <v>135881.86</v>
       </c>
       <c r="I23" s="3">
-        <v>838584.39</v>
+        <v>865434.19</v>
       </c>
       <c r="J23" s="3">
-        <v>96.69</v>
+        <v>99.79</v>
       </c>
       <c r="K23" s="3">
-        <v>-28672.98</v>
+        <v>-1823.18</v>
       </c>
       <c r="L23" s="3">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="M23" s="3">
-        <v>14994.16</v>
+        <v>15942.78</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>1138</v>
+        <v>1680</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1139</v>
+        <v>1681</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1140</v>
+        <v>1682</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1141</v>
+        <v>1683</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1142</v>
+        <v>1684</v>
       </c>
       <c r="F24" s="3">
         <v>778641.12</v>
       </c>
       <c r="G24" s="3">
-        <v>603872.26</v>
+        <v>625242.42</v>
       </c>
       <c r="H24" s="3">
-        <v>102576.19</v>
+        <v>100878.57</v>
       </c>
       <c r="I24" s="3">
-        <v>706448.45</v>
+        <v>726120.99</v>
       </c>
       <c r="J24" s="3">
-        <v>90.73</v>
+        <v>93.25</v>
       </c>
       <c r="K24" s="3">
-        <v>-72192.67</v>
+        <v>-52520.13</v>
       </c>
       <c r="L24" s="3">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="M24" s="3">
         <v>22140.44</v>
@@ -13362,347 +18240,347 @@
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>1143</v>
+        <v>1685</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1144</v>
+        <v>1686</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1145</v>
+        <v>1687</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1146</v>
+        <v>1688</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1147</v>
+        <v>1689</v>
       </c>
       <c r="F25" s="3">
         <v>979868.9</v>
       </c>
       <c r="G25" s="3">
-        <v>587644.12</v>
+        <v>610061.4</v>
       </c>
       <c r="H25" s="3">
-        <v>194303.87</v>
+        <v>197295.59</v>
       </c>
       <c r="I25" s="3">
-        <v>781947.99</v>
+        <v>807356.99</v>
       </c>
       <c r="J25" s="3">
-        <v>79.8</v>
+        <v>82.39</v>
       </c>
       <c r="K25" s="3">
-        <v>-197920.91</v>
+        <v>-172511.91</v>
       </c>
       <c r="L25" s="3">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M25" s="3">
-        <v>14086.82</v>
+        <v>15719.02</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>1148</v>
+        <v>1690</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1149</v>
+        <v>1691</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1150</v>
+        <v>1692</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1151</v>
+        <v>1693</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1152</v>
+        <v>1694</v>
       </c>
       <c r="F26" s="3">
         <v>1011213.65</v>
       </c>
       <c r="G26" s="3">
-        <v>428934.18</v>
+        <v>453115.42</v>
       </c>
       <c r="H26" s="3">
-        <v>159920.62</v>
+        <v>151022.32</v>
       </c>
       <c r="I26" s="3">
-        <v>588854.8</v>
+        <v>604137.74</v>
       </c>
       <c r="J26" s="3">
-        <v>58.23</v>
+        <v>59.74</v>
       </c>
       <c r="K26" s="3">
-        <v>-422358.85</v>
+        <v>-407075.91</v>
       </c>
       <c r="L26" s="3">
-        <v>4.34</v>
+        <v>4.89</v>
       </c>
       <c r="M26" s="3">
-        <v>25561.99</v>
+        <v>29543.21</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>1153</v>
+        <v>1695</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1154</v>
+        <v>1696</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1155</v>
+        <v>1697</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1156</v>
+        <v>1698</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1157</v>
+        <v>1699</v>
       </c>
       <c r="F27" s="3">
         <v>905279.17</v>
       </c>
       <c r="G27" s="3">
-        <v>561447.94</v>
+        <v>590979.48</v>
       </c>
       <c r="H27" s="3">
-        <v>167639.85</v>
+        <v>160309.48</v>
       </c>
       <c r="I27" s="3">
-        <v>729087.79</v>
+        <v>751288.96</v>
       </c>
       <c r="J27" s="3">
-        <v>80.54</v>
+        <v>82.99</v>
       </c>
       <c r="K27" s="3">
-        <v>-176191.38</v>
+        <v>-153990.21</v>
       </c>
       <c r="L27" s="3">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="M27" s="3">
-        <v>14637.65</v>
+        <v>16982.7</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>1158</v>
+        <v>1700</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1159</v>
+        <v>1701</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1160</v>
+        <v>1702</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1161</v>
+        <v>1703</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1162</v>
+        <v>1704</v>
       </c>
       <c r="F28" s="3">
         <v>948604.6</v>
       </c>
       <c r="G28" s="3">
-        <v>509852.33</v>
+        <v>579107.48</v>
       </c>
       <c r="H28" s="3">
-        <v>168250.34</v>
+        <v>117087.12</v>
       </c>
       <c r="I28" s="3">
-        <v>678102.67</v>
+        <v>696194.6</v>
       </c>
       <c r="J28" s="3">
-        <v>71.48</v>
+        <v>73.39</v>
       </c>
       <c r="K28" s="3">
-        <v>-270501.93</v>
+        <v>-252410.0</v>
       </c>
       <c r="L28" s="3">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="M28" s="3">
-        <v>12526.98</v>
+        <v>14790.72</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>1163</v>
+        <v>1705</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1164</v>
+        <v>1706</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1165</v>
+        <v>1707</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1166</v>
+        <v>1708</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1167</v>
+        <v>1709</v>
       </c>
       <c r="F29" s="3">
         <v>824118.89</v>
       </c>
       <c r="G29" s="3">
-        <v>492157.73</v>
+        <v>519742.87</v>
       </c>
       <c r="H29" s="3">
-        <v>135763.44</v>
+        <v>127399.62</v>
       </c>
       <c r="I29" s="3">
-        <v>627921.17</v>
+        <v>647142.49</v>
       </c>
       <c r="J29" s="3">
-        <v>76.19</v>
+        <v>78.53</v>
       </c>
       <c r="K29" s="3">
-        <v>-196197.72</v>
+        <v>-176976.4</v>
       </c>
       <c r="L29" s="3">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="M29" s="3">
-        <v>17901.53</v>
+        <v>18576.2</v>
       </c>
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>1168</v>
+        <v>1710</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1169</v>
+        <v>1711</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1170</v>
+        <v>1712</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1171</v>
+        <v>1713</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1172</v>
+        <v>1714</v>
       </c>
       <c r="F30" s="3">
         <v>877850.52</v>
       </c>
       <c r="G30" s="3">
-        <v>682732.01</v>
+        <v>714196.09</v>
       </c>
       <c r="H30" s="3">
-        <v>157754.94</v>
+        <v>162472.78</v>
       </c>
       <c r="I30" s="3">
-        <v>840486.95</v>
+        <v>876668.87</v>
       </c>
       <c r="J30" s="3">
-        <v>95.74</v>
+        <v>99.87</v>
       </c>
       <c r="K30" s="3">
-        <v>-37363.57</v>
+        <v>-1181.65</v>
       </c>
       <c r="L30" s="3">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="M30" s="3">
-        <v>18740.24</v>
+        <v>20014.92</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>1173</v>
+        <v>1715</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1174</v>
+        <v>1716</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1175</v>
+        <v>1717</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1176</v>
+        <v>1718</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1177</v>
+        <v>1719</v>
       </c>
       <c r="F31" s="3">
         <v>990466.72</v>
       </c>
       <c r="G31" s="3">
-        <v>634450.62</v>
+        <v>667452.99</v>
       </c>
       <c r="H31" s="3">
-        <v>163426.52</v>
+        <v>161275.68</v>
       </c>
       <c r="I31" s="3">
-        <v>797877.14</v>
+        <v>828728.67</v>
       </c>
       <c r="J31" s="3">
-        <v>80.56</v>
+        <v>83.67</v>
       </c>
       <c r="K31" s="3">
-        <v>-192589.58</v>
+        <v>-161738.05</v>
       </c>
       <c r="L31" s="3">
-        <v>4.11</v>
+        <v>4.26</v>
       </c>
       <c r="M31" s="3">
-        <v>32803.64</v>
+        <v>35300.34</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>1178</v>
+        <v>1720</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1179</v>
+        <v>1721</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1180</v>
+        <v>1722</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1181</v>
+        <v>1723</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1182</v>
+        <v>1724</v>
       </c>
       <c r="F32" s="3">
         <v>892245.98</v>
       </c>
       <c r="G32" s="3">
-        <v>544226.1</v>
+        <v>568975.96</v>
       </c>
       <c r="H32" s="3">
-        <v>153077.58</v>
+        <v>150729.68</v>
       </c>
       <c r="I32" s="3">
-        <v>697303.68</v>
+        <v>719705.64</v>
       </c>
       <c r="J32" s="3">
-        <v>78.15</v>
+        <v>80.66</v>
       </c>
       <c r="K32" s="3">
-        <v>-194942.3</v>
+        <v>-172540.34</v>
       </c>
       <c r="L32" s="3">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="M32" s="3">
-        <v>26384.82</v>
+        <v>27252.79</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>1183</v>
+        <v>1725</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1184</v>
+        <v>1726</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1185</v>
+        <v>1727</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1186</v>
+        <v>1728</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1187</v>
+        <v>1729</v>
       </c>
       <c r="F33" s="3">
         <v>1265248.83</v>
@@ -13711,19 +18589,19 @@
         <v>664527.91</v>
       </c>
       <c r="H33" s="3">
-        <v>308019.73</v>
+        <v>398529.71</v>
       </c>
       <c r="I33" s="3">
-        <v>972547.64</v>
+        <v>1063057.62</v>
       </c>
       <c r="J33" s="3">
-        <v>76.87</v>
+        <v>84.02</v>
       </c>
       <c r="K33" s="3">
-        <v>-292701.19</v>
+        <v>-202191.21</v>
       </c>
       <c r="L33" s="3">
-        <v>4.33</v>
+        <v>3.96</v>
       </c>
       <c r="M33" s="3">
         <v>42135.7</v>
@@ -13731,19 +18609,19 @@
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>1188</v>
+        <v>1730</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1189</v>
+        <v>1731</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1190</v>
+        <v>1732</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1191</v>
+        <v>1733</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1192</v>
+        <v>1734</v>
       </c>
       <c r="F34" s="3">
         <v>1062018.28</v>
@@ -13752,19 +18630,19 @@
         <v>593694.76</v>
       </c>
       <c r="H34" s="3">
-        <v>46572.5</v>
+        <v>107931.98</v>
       </c>
       <c r="I34" s="3">
-        <v>640267.26</v>
+        <v>701626.74</v>
       </c>
       <c r="J34" s="3">
-        <v>60.29</v>
+        <v>66.07</v>
       </c>
       <c r="K34" s="3">
-        <v>-421751.02</v>
+        <v>-360391.54</v>
       </c>
       <c r="L34" s="3">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="M34" s="3">
         <v>21447.8</v>
@@ -13772,19 +18650,19 @@
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>1193</v>
+        <v>1735</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1194</v>
+        <v>1736</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1195</v>
+        <v>1737</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1196</v>
+        <v>1738</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1197</v>
+        <v>1739</v>
       </c>
       <c r="F35" s="3">
         <v>1027050.57</v>
@@ -13793,19 +18671,19 @@
         <v>646905.99</v>
       </c>
       <c r="H35" s="3">
-        <v>78544.2</v>
+        <v>159704.08</v>
       </c>
       <c r="I35" s="3">
-        <v>725450.19</v>
+        <v>806610.07</v>
       </c>
       <c r="J35" s="3">
-        <v>70.63</v>
+        <v>78.54</v>
       </c>
       <c r="K35" s="3">
-        <v>-301600.38</v>
+        <v>-220440.5</v>
       </c>
       <c r="L35" s="3">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="M35" s="3">
         <v>22989.71</v>
@@ -13813,28 +18691,28 @@
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>1198</v>
+        <v>1740</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1199</v>
+        <v>1741</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1200</v>
+        <v>1742</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1201</v>
+        <v>1743</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1202</v>
+        <v>1744</v>
       </c>
       <c r="F36" s="3">
         <v>1150571.33</v>
       </c>
       <c r="G36" s="3">
-        <v>756420.19</v>
+        <v>760419.63</v>
       </c>
       <c r="H36" s="3">
-        <v>303154.11</v>
+        <v>299154.67</v>
       </c>
       <c r="I36" s="3">
         <v>1059574.3</v>
@@ -13854,28 +18732,28 @@
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>1203</v>
+        <v>1745</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1204</v>
+        <v>1746</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1205</v>
+        <v>1747</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1206</v>
+        <v>1748</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1207</v>
+        <v>1749</v>
       </c>
       <c r="F37" s="3">
         <v>1374896.6</v>
       </c>
       <c r="G37" s="3">
-        <v>708178.88</v>
+        <v>713711.82</v>
       </c>
       <c r="H37" s="3">
-        <v>291642.97</v>
+        <v>286110.03</v>
       </c>
       <c r="I37" s="3">
         <v>999821.85</v>
@@ -13895,28 +18773,28 @@
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>1208</v>
+        <v>1750</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1209</v>
+        <v>1751</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1210</v>
+        <v>1752</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1211</v>
+        <v>1753</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1212</v>
+        <v>1754</v>
       </c>
       <c r="F38" s="3">
         <v>904558.95</v>
       </c>
       <c r="G38" s="3">
-        <v>536752.81</v>
+        <v>540284.31</v>
       </c>
       <c r="H38" s="3">
-        <v>245612.05</v>
+        <v>242080.55</v>
       </c>
       <c r="I38" s="3">
         <v>782364.86</v>
@@ -13936,28 +18814,28 @@
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>1213</v>
+        <v>1755</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1214</v>
+        <v>1756</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1215</v>
+        <v>1757</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1216</v>
+        <v>1758</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1217</v>
+        <v>1759</v>
       </c>
       <c r="F39" s="3">
         <v>1106940.64</v>
       </c>
       <c r="G39" s="3">
-        <v>508788.01</v>
+        <v>511089.55</v>
       </c>
       <c r="H39" s="3">
-        <v>237111.85</v>
+        <v>234810.31</v>
       </c>
       <c r="I39" s="3">
         <v>745899.86</v>
@@ -13977,19 +18855,19 @@
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>1218</v>
+        <v>1760</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1219</v>
+        <v>1761</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1220</v>
+        <v>1762</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1221</v>
+        <v>1763</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1222</v>
+        <v>1764</v>
       </c>
       <c r="F40" s="3">
         <v>887573.45</v>
@@ -13998,19 +18876,19 @@
         <v>457043.02</v>
       </c>
       <c r="H40" s="3">
-        <v>110925.96</v>
+        <v>141323.92</v>
       </c>
       <c r="I40" s="3">
-        <v>567968.98</v>
+        <v>598366.94</v>
       </c>
       <c r="J40" s="3">
-        <v>63.99</v>
+        <v>67.42</v>
       </c>
       <c r="K40" s="3">
-        <v>-319604.47</v>
+        <v>-289206.51</v>
       </c>
       <c r="L40" s="3">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="M40" s="3">
         <v>7048.51</v>
@@ -14018,19 +18896,19 @@
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>1223</v>
+        <v>1765</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1224</v>
+        <v>1766</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1225</v>
+        <v>1767</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1226</v>
+        <v>1768</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1227</v>
+        <v>1769</v>
       </c>
       <c r="F41" s="3">
         <v>1236217.2</v>
@@ -14039,19 +18917,19 @@
         <v>628068.11</v>
       </c>
       <c r="H41" s="3">
-        <v>181378.27</v>
+        <v>222457.47</v>
       </c>
       <c r="I41" s="3">
-        <v>809446.38</v>
+        <v>850525.58</v>
       </c>
       <c r="J41" s="3">
-        <v>65.48</v>
+        <v>68.8</v>
       </c>
       <c r="K41" s="3">
-        <v>-426770.82</v>
+        <v>-385691.62</v>
       </c>
       <c r="L41" s="3">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="M41" s="3">
         <v>26896.64</v>
@@ -14059,19 +18937,19 @@
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>1228</v>
+        <v>1770</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1229</v>
+        <v>1771</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1230</v>
+        <v>1772</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1231</v>
+        <v>1773</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1232</v>
+        <v>1774</v>
       </c>
       <c r="F42" s="3">
         <v>912015.93</v>
@@ -14080,19 +18958,19 @@
         <v>538954.43</v>
       </c>
       <c r="H42" s="3">
-        <v>159630.38</v>
+        <v>205434.89</v>
       </c>
       <c r="I42" s="3">
-        <v>698584.81</v>
+        <v>744389.32</v>
       </c>
       <c r="J42" s="3">
-        <v>76.6</v>
+        <v>81.62</v>
       </c>
       <c r="K42" s="3">
-        <v>-213431.12</v>
+        <v>-167626.61</v>
       </c>
       <c r="L42" s="3">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="M42" s="3">
         <v>14747.12</v>
@@ -14100,19 +18978,19 @@
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>1233</v>
+        <v>1775</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1234</v>
+        <v>1776</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1235</v>
+        <v>1777</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1236</v>
+        <v>1778</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1237</v>
+        <v>1779</v>
       </c>
       <c r="F43" s="3">
         <v>1043081.21</v>
@@ -14121,19 +18999,19 @@
         <v>759332.15</v>
       </c>
       <c r="H43" s="3">
-        <v>181868.85</v>
+        <v>227799.38</v>
       </c>
       <c r="I43" s="3">
-        <v>941201.0</v>
+        <v>987131.53</v>
       </c>
       <c r="J43" s="3">
-        <v>90.23</v>
+        <v>94.64</v>
       </c>
       <c r="K43" s="3">
-        <v>-101880.21</v>
+        <v>-55949.68</v>
       </c>
       <c r="L43" s="3">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="M43" s="3">
         <v>20597.93</v>
@@ -14141,371 +19019,371 @@
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>1238</v>
+        <v>1780</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1239</v>
+        <v>1781</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1240</v>
+        <v>1782</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1241</v>
+        <v>1783</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1242</v>
+        <v>1784</v>
       </c>
       <c r="F44" s="3">
         <v>1113507.9</v>
       </c>
       <c r="G44" s="3">
-        <v>610519.31</v>
+        <v>728967.84</v>
       </c>
       <c r="H44" s="3">
-        <v>174890.04</v>
+        <v>121585.49</v>
       </c>
       <c r="I44" s="3">
-        <v>785409.35</v>
+        <v>850553.33</v>
       </c>
       <c r="J44" s="3">
-        <v>70.53</v>
+        <v>76.39</v>
       </c>
       <c r="K44" s="3">
-        <v>-328098.55</v>
+        <v>-262954.57</v>
       </c>
       <c r="L44" s="3">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="M44" s="3">
-        <v>16611.34</v>
+        <v>19632.92</v>
       </c>
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>1243</v>
+        <v>1785</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1244</v>
+        <v>1786</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1245</v>
+        <v>1787</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1246</v>
+        <v>1788</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1247</v>
+        <v>1789</v>
       </c>
       <c r="F45" s="3">
         <v>918319.81</v>
       </c>
       <c r="G45" s="3">
-        <v>632676.37</v>
+        <v>728801.52</v>
       </c>
       <c r="H45" s="3">
-        <v>155347.39</v>
+        <v>112671.28</v>
       </c>
       <c r="I45" s="3">
-        <v>788023.76</v>
+        <v>841472.8</v>
       </c>
       <c r="J45" s="3">
-        <v>85.81</v>
+        <v>91.63</v>
       </c>
       <c r="K45" s="3">
-        <v>-130296.05</v>
+        <v>-76847.01</v>
       </c>
       <c r="L45" s="3">
         <v>1.55</v>
       </c>
       <c r="M45" s="3">
-        <v>12200.15</v>
+        <v>13001.83</v>
       </c>
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>1248</v>
+        <v>1790</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1249</v>
+        <v>1791</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1250</v>
+        <v>1792</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1251</v>
+        <v>1793</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1252</v>
+        <v>1794</v>
       </c>
       <c r="F46" s="3">
         <v>1066780.42</v>
       </c>
       <c r="G46" s="3">
-        <v>700229.0</v>
+        <v>784900.21</v>
       </c>
       <c r="H46" s="3">
-        <v>127968.35</v>
+        <v>116963.56</v>
       </c>
       <c r="I46" s="3">
-        <v>828197.35</v>
+        <v>901863.77</v>
       </c>
       <c r="J46" s="3">
-        <v>77.64</v>
+        <v>84.54</v>
       </c>
       <c r="K46" s="3">
-        <v>-238583.07</v>
+        <v>-164916.65</v>
       </c>
       <c r="L46" s="3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M46" s="3">
-        <v>14068.12</v>
+        <v>15407.32</v>
       </c>
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>1253</v>
+        <v>1795</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1254</v>
+        <v>1796</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1255</v>
+        <v>1797</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1256</v>
+        <v>1798</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1257</v>
+        <v>1799</v>
       </c>
       <c r="F47" s="3">
         <v>1336954.46</v>
       </c>
       <c r="G47" s="3">
-        <v>426103.49</v>
+        <v>478076.29</v>
       </c>
       <c r="H47" s="3">
-        <v>334968.86</v>
+        <v>343180.31</v>
       </c>
       <c r="I47" s="3">
-        <v>761072.35</v>
+        <v>821256.6</v>
       </c>
       <c r="J47" s="3">
-        <v>56.93</v>
+        <v>61.43</v>
       </c>
       <c r="K47" s="3">
-        <v>-575882.11</v>
+        <v>-515697.86</v>
       </c>
       <c r="L47" s="3">
-        <v>3.01</v>
+        <v>3.26</v>
       </c>
       <c r="M47" s="3">
-        <v>22942.59</v>
+        <v>26763.01</v>
       </c>
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>1258</v>
+        <v>1800</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1259</v>
+        <v>1801</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1260</v>
+        <v>1802</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1261</v>
+        <v>1803</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1262</v>
+        <v>1804</v>
       </c>
       <c r="F48" s="3">
         <v>1022376.56</v>
       </c>
       <c r="G48" s="3">
-        <v>364309.9</v>
+        <v>410886.57</v>
       </c>
       <c r="H48" s="3">
-        <v>196619.56</v>
+        <v>198751.32</v>
       </c>
       <c r="I48" s="3">
-        <v>560929.46</v>
+        <v>609637.89</v>
       </c>
       <c r="J48" s="3">
-        <v>54.87</v>
+        <v>59.63</v>
       </c>
       <c r="K48" s="3">
-        <v>-461447.1</v>
+        <v>-412738.67</v>
       </c>
       <c r="L48" s="3">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="M48" s="3">
-        <v>18249.36</v>
+        <v>19710.24</v>
       </c>
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>1263</v>
+        <v>1805</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1264</v>
+        <v>1806</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1265</v>
+        <v>1807</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1266</v>
+        <v>1808</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1267</v>
+        <v>1809</v>
       </c>
       <c r="F49" s="3">
         <v>972020.19</v>
       </c>
       <c r="G49" s="3">
-        <v>437419.04</v>
+        <v>505461.32</v>
       </c>
       <c r="H49" s="3">
-        <v>228871.67</v>
+        <v>217317.93</v>
       </c>
       <c r="I49" s="3">
-        <v>666290.71</v>
+        <v>722779.25</v>
       </c>
       <c r="J49" s="3">
-        <v>68.55</v>
+        <v>74.36</v>
       </c>
       <c r="K49" s="3">
-        <v>-305729.48</v>
+        <v>-249240.94</v>
       </c>
       <c r="L49" s="3">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="M49" s="3">
-        <v>17023.85</v>
+        <v>19303.38</v>
       </c>
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>1268</v>
+        <v>1810</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1269</v>
+        <v>1811</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1270</v>
+        <v>1812</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1271</v>
+        <v>1813</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1272</v>
+        <v>1814</v>
       </c>
       <c r="F50" s="3">
         <v>963790.11</v>
       </c>
       <c r="G50" s="3">
-        <v>428712.74</v>
+        <v>479055.55</v>
       </c>
       <c r="H50" s="3">
-        <v>219677.56</v>
+        <v>254935.65</v>
       </c>
       <c r="I50" s="3">
-        <v>648390.3</v>
+        <v>733991.2</v>
       </c>
       <c r="J50" s="3">
-        <v>67.28</v>
+        <v>76.16</v>
       </c>
       <c r="K50" s="3">
-        <v>-315399.81</v>
+        <v>-229798.91</v>
       </c>
       <c r="L50" s="3">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="M50" s="3">
-        <v>27010.91</v>
+        <v>28562.97</v>
       </c>
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>1273</v>
+        <v>1815</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1274</v>
+        <v>1816</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1275</v>
+        <v>1817</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1276</v>
+        <v>1818</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1277</v>
+        <v>1819</v>
       </c>
       <c r="F51" s="3">
         <v>954958.72</v>
       </c>
       <c r="G51" s="3">
-        <v>548398.72</v>
+        <v>622601.3</v>
       </c>
       <c r="H51" s="3">
-        <v>177454.38</v>
+        <v>157050.0</v>
       </c>
       <c r="I51" s="3">
-        <v>725853.1</v>
+        <v>779651.3</v>
       </c>
       <c r="J51" s="3">
-        <v>76.01</v>
+        <v>81.64</v>
       </c>
       <c r="K51" s="3">
-        <v>-229105.62</v>
+        <v>-175307.42</v>
       </c>
       <c r="L51" s="3">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M51" s="3">
-        <v>23047.94</v>
+        <v>24977.02</v>
       </c>
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>1278</v>
+        <v>1820</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1279</v>
+        <v>1821</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1280</v>
+        <v>1822</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1281</v>
+        <v>1823</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1282</v>
+        <v>1824</v>
       </c>
       <c r="F52" s="3">
         <v>1154949.94</v>
       </c>
       <c r="G52" s="3">
-        <v>556971.85</v>
+        <v>629136.95</v>
       </c>
       <c r="H52" s="3">
-        <v>213580.22</v>
+        <v>234890.5</v>
       </c>
       <c r="I52" s="3">
-        <v>770552.07</v>
+        <v>864027.45</v>
       </c>
       <c r="J52" s="3">
-        <v>66.72</v>
+        <v>74.81</v>
       </c>
       <c r="K52" s="3">
-        <v>-384397.87</v>
+        <v>-290922.49</v>
       </c>
       <c r="L52" s="3">
-        <v>6.35</v>
+        <v>5.92</v>
       </c>
       <c r="M52" s="3">
-        <v>48900.67</v>
+        <v>51132.27</v>
       </c>
     </row>
   </sheetData>
@@ -14515,7 +19393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -14565,215 +19443,215 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>1283</v>
+        <v>1825</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1284</v>
+        <v>1826</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1285</v>
+        <v>1827</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1286</v>
+        <v>1828</v>
       </c>
       <c r="E2" s="3">
         <v>5936775.24</v>
       </c>
       <c r="F2" s="3">
-        <v>2997214.77</v>
+        <v>3127296.62</v>
       </c>
       <c r="G2" s="3">
-        <v>1742808.57</v>
+        <v>1777975.18</v>
       </c>
       <c r="H2" s="3">
-        <v>4740023.34</v>
+        <v>4905271.8</v>
       </c>
       <c r="I2" s="3">
-        <v>79.84</v>
+        <v>82.63</v>
       </c>
       <c r="J2" s="3">
-        <v>-1196751.9</v>
+        <v>-1031503.44</v>
       </c>
       <c r="K2" s="3">
-        <v>100694.46</v>
+        <v>104582.34</v>
       </c>
       <c r="L2" s="3">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>1287</v>
+        <v>1829</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1288</v>
+        <v>1830</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1289</v>
+        <v>1831</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1290</v>
+        <v>1832</v>
       </c>
       <c r="E3" s="3">
         <v>3346888.02</v>
       </c>
       <c r="F3" s="3">
-        <v>1628143.75</v>
+        <v>1698181.81</v>
       </c>
       <c r="G3" s="3">
-        <v>849147.0</v>
+        <v>876171.46</v>
       </c>
       <c r="H3" s="3">
-        <v>2477290.75</v>
+        <v>2574353.27</v>
       </c>
       <c r="I3" s="3">
-        <v>74.02</v>
+        <v>76.92</v>
       </c>
       <c r="J3" s="3">
-        <v>-869597.27</v>
+        <v>-772534.75</v>
       </c>
       <c r="K3" s="3">
-        <v>44957.14</v>
+        <v>46811.46</v>
       </c>
       <c r="L3" s="3">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>1291</v>
+        <v>1833</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1292</v>
+        <v>1834</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1293</v>
+        <v>1835</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1294</v>
+        <v>1836</v>
       </c>
       <c r="E4" s="3">
         <v>6248074.42</v>
       </c>
       <c r="F4" s="3">
-        <v>2848442.36</v>
+        <v>2882528.29</v>
       </c>
       <c r="G4" s="3">
-        <v>1454888.41</v>
+        <v>1474974.46</v>
       </c>
       <c r="H4" s="3">
-        <v>4303330.77</v>
+        <v>4357502.75</v>
       </c>
       <c r="I4" s="3">
-        <v>68.87</v>
+        <v>69.74</v>
       </c>
       <c r="J4" s="3">
-        <v>-1944743.65</v>
+        <v>-1890571.67</v>
       </c>
       <c r="K4" s="3">
-        <v>160191.2</v>
+        <v>160850.7</v>
       </c>
       <c r="L4" s="3">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>1295</v>
+        <v>1837</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1296</v>
+        <v>1838</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1297</v>
+        <v>1839</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1298</v>
+        <v>1840</v>
       </c>
       <c r="E5" s="3">
         <v>7225829.17</v>
       </c>
       <c r="F5" s="3">
-        <v>4684391.67</v>
+        <v>4930868.83</v>
       </c>
       <c r="G5" s="3">
-        <v>1183585.99</v>
+        <v>1095798.25</v>
       </c>
       <c r="H5" s="3">
-        <v>5867977.66</v>
+        <v>6026667.08</v>
       </c>
       <c r="I5" s="3">
-        <v>81.21</v>
+        <v>83.4</v>
       </c>
       <c r="J5" s="3">
-        <v>-1357851.51</v>
+        <v>-1199162.09</v>
       </c>
       <c r="K5" s="3">
-        <v>144436.32</v>
+        <v>158209.65</v>
       </c>
       <c r="L5" s="3">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>1299</v>
+        <v>1841</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1300</v>
+        <v>1842</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1301</v>
+        <v>1843</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1302</v>
+        <v>1844</v>
       </c>
       <c r="E6" s="3">
         <v>6938999.79</v>
       </c>
       <c r="F6" s="3">
-        <v>4258695.12</v>
+        <v>4375496.57</v>
       </c>
       <c r="G6" s="3">
-        <v>1043158.91</v>
+        <v>1268043.52</v>
       </c>
       <c r="H6" s="3">
-        <v>5301854.03</v>
+        <v>5643540.09</v>
       </c>
       <c r="I6" s="3">
-        <v>76.41</v>
+        <v>81.33</v>
       </c>
       <c r="J6" s="3">
-        <v>-1637145.76</v>
+        <v>-1295459.7</v>
       </c>
       <c r="K6" s="3">
-        <v>182403.43</v>
+        <v>187717.46</v>
       </c>
       <c r="L6" s="3">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>1303</v>
+        <v>1845</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1304</v>
+        <v>1846</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1305</v>
+        <v>1847</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1306</v>
+        <v>1848</v>
       </c>
       <c r="E7" s="3">
         <v>4536967.52</v>
       </c>
       <c r="F7" s="3">
-        <v>2510139.89</v>
+        <v>2525505.31</v>
       </c>
       <c r="G7" s="3">
-        <v>1077520.98</v>
+        <v>1062155.56</v>
       </c>
       <c r="H7" s="3">
         <v>3587660.87</v>
@@ -14793,78 +19671,78 @@
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>1307</v>
+        <v>1849</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1308</v>
+        <v>1850</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1309</v>
+        <v>1851</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1310</v>
+        <v>1852</v>
       </c>
       <c r="E8" s="3">
         <v>7177495.92</v>
       </c>
       <c r="F8" s="3">
-        <v>4326822.39</v>
+        <v>4626067.28</v>
       </c>
       <c r="G8" s="3">
-        <v>1092009.24</v>
+        <v>1148235.99</v>
       </c>
       <c r="H8" s="3">
-        <v>5418831.63</v>
+        <v>5774303.27</v>
       </c>
       <c r="I8" s="3">
-        <v>75.5</v>
+        <v>80.45</v>
       </c>
       <c r="J8" s="3">
-        <v>-1758664.29</v>
+        <v>-1403192.65</v>
       </c>
       <c r="K8" s="3">
-        <v>112169.81</v>
+        <v>117332.27</v>
       </c>
       <c r="L8" s="3">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>1311</v>
+        <v>1853</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1312</v>
+        <v>1854</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1313</v>
+        <v>1855</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1314</v>
+        <v>1856</v>
       </c>
       <c r="E9" s="3">
         <v>6405049.98</v>
       </c>
       <c r="F9" s="3">
-        <v>2761915.74</v>
+        <v>3125217.98</v>
       </c>
       <c r="G9" s="3">
-        <v>1371172.25</v>
+        <v>1406125.71</v>
       </c>
       <c r="H9" s="3">
-        <v>4133087.99</v>
+        <v>4531343.69</v>
       </c>
       <c r="I9" s="3">
-        <v>64.53</v>
+        <v>70.75</v>
       </c>
       <c r="J9" s="3">
-        <v>-2271961.99</v>
+        <v>-1873706.29</v>
       </c>
       <c r="K9" s="3">
-        <v>157175.32</v>
+        <v>170448.89</v>
       </c>
       <c r="L9" s="3">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1857" count="1857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2399" count="2399">
   <si>
     <t>Region</t>
   </si>
@@ -6805,6 +6805,4884 @@
         <rFont val="Helvetica"/>
       </rPr>
       <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
     </r>
   </si>
   <si>
@@ -16860,7 +21738,7 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -16870,6 +21748,10 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -16925,11 +21807,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -16937,9 +21828,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17236,7 +22124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -17297,532 +22185,532 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1570</v>
+        <v>2112</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1571</v>
+        <v>2113</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1572</v>
+        <v>2114</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1573</v>
+        <v>2115</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1574</v>
+        <v>2116</v>
       </c>
       <c r="F2" s="3">
         <v>747825.09</v>
       </c>
       <c r="G2" s="3">
-        <v>441503.81</v>
+        <v>459372.09</v>
       </c>
       <c r="H2" s="3">
-        <v>202726.94</v>
+        <v>189231.72</v>
       </c>
       <c r="I2" s="3">
-        <v>644230.75</v>
+        <v>648603.81</v>
       </c>
       <c r="J2" s="3">
-        <v>86.15</v>
+        <v>86.73</v>
       </c>
       <c r="K2" s="3">
-        <v>-103594.34</v>
+        <v>-99221.28</v>
       </c>
       <c r="L2" s="3">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="M2" s="3">
-        <v>13001.24</v>
+        <v>13519.24</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>1575</v>
+        <v>2117</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1576</v>
+        <v>2118</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1577</v>
+        <v>2119</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1578</v>
+        <v>2120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1579</v>
+        <v>2121</v>
       </c>
       <c r="F3" s="3">
         <v>755003.49</v>
       </c>
       <c r="G3" s="3">
-        <v>368509.79</v>
+        <v>398938.35</v>
       </c>
       <c r="H3" s="3">
-        <v>282837.68</v>
+        <v>258264.74</v>
       </c>
       <c r="I3" s="3">
-        <v>651347.47</v>
+        <v>657203.09</v>
       </c>
       <c r="J3" s="3">
-        <v>86.27</v>
+        <v>87.05</v>
       </c>
       <c r="K3" s="3">
-        <v>-103656.02</v>
+        <v>-97800.4</v>
       </c>
       <c r="L3" s="3">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="M3" s="3">
-        <v>8146.61</v>
+        <v>9550.02</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>1580</v>
+        <v>2122</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1581</v>
+        <v>2123</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1582</v>
+        <v>2124</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1583</v>
+        <v>2125</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1584</v>
+        <v>2126</v>
       </c>
       <c r="F4" s="3">
         <v>664724.91</v>
       </c>
       <c r="G4" s="3">
-        <v>417473.07</v>
+        <v>459171.19</v>
       </c>
       <c r="H4" s="3">
-        <v>231241.19</v>
+        <v>193309.94</v>
       </c>
       <c r="I4" s="3">
-        <v>648714.26</v>
+        <v>652481.13</v>
       </c>
       <c r="J4" s="3">
-        <v>97.59</v>
+        <v>98.16</v>
       </c>
       <c r="K4" s="3">
-        <v>-16010.65</v>
+        <v>-12243.78</v>
       </c>
       <c r="L4" s="3">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="M4" s="3">
-        <v>15960.0</v>
+        <v>17957.37</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>1585</v>
+        <v>2127</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1586</v>
+        <v>2128</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1587</v>
+        <v>2129</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1588</v>
+        <v>2130</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1589</v>
+        <v>2131</v>
       </c>
       <c r="F5" s="3">
         <v>745422.79</v>
       </c>
       <c r="G5" s="3">
-        <v>330813.87</v>
+        <v>375613.39</v>
       </c>
       <c r="H5" s="3">
-        <v>228412.34</v>
+        <v>194997.13</v>
       </c>
       <c r="I5" s="3">
-        <v>559226.21</v>
+        <v>570610.52</v>
       </c>
       <c r="J5" s="3">
-        <v>75.02</v>
+        <v>76.55</v>
       </c>
       <c r="K5" s="3">
-        <v>-186196.58</v>
+        <v>-174812.27</v>
       </c>
       <c r="L5" s="3">
-        <v>3.37</v>
+        <v>3.66</v>
       </c>
       <c r="M5" s="3">
-        <v>18873.6</v>
+        <v>20884.05</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>1590</v>
+        <v>2132</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1591</v>
+        <v>2133</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1592</v>
+        <v>2134</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1593</v>
+        <v>2135</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1594</v>
+        <v>2136</v>
       </c>
       <c r="F6" s="3">
         <v>750633.4</v>
       </c>
       <c r="G6" s="3">
-        <v>522738.61</v>
+        <v>549530.36</v>
       </c>
       <c r="H6" s="3">
-        <v>241147.93</v>
+        <v>237940.7</v>
       </c>
       <c r="I6" s="3">
-        <v>763886.54</v>
+        <v>787471.06</v>
       </c>
       <c r="J6" s="3">
-        <v>101.77</v>
+        <v>104.91</v>
       </c>
       <c r="K6" s="3">
-        <v>13253.14</v>
+        <v>36837.66</v>
       </c>
       <c r="L6" s="3">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="M6" s="3">
-        <v>19905.22</v>
+        <v>21026.3</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>1595</v>
+        <v>2137</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1596</v>
+        <v>2138</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1597</v>
+        <v>2139</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1598</v>
+        <v>2140</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1599</v>
+        <v>2141</v>
       </c>
       <c r="F7" s="3">
         <v>804591.82</v>
       </c>
       <c r="G7" s="3">
-        <v>333709.75</v>
+        <v>358616.15</v>
       </c>
       <c r="H7" s="3">
-        <v>211275.31</v>
+        <v>204931.13</v>
       </c>
       <c r="I7" s="3">
-        <v>544985.06</v>
+        <v>563547.28</v>
       </c>
       <c r="J7" s="3">
-        <v>67.73</v>
+        <v>70.04</v>
       </c>
       <c r="K7" s="3">
-        <v>-259606.76</v>
+        <v>-241044.54</v>
       </c>
       <c r="L7" s="3">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="M7" s="3">
-        <v>11953.51</v>
+        <v>12373.41</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>1600</v>
+        <v>2142</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1601</v>
+        <v>2143</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1602</v>
+        <v>2144</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1603</v>
+        <v>2145</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1604</v>
+        <v>2146</v>
       </c>
       <c r="F8" s="3">
         <v>726832.71</v>
       </c>
       <c r="G8" s="3">
-        <v>299388.8</v>
+        <v>313512.82</v>
       </c>
       <c r="H8" s="3">
-        <v>177206.25</v>
+        <v>172785.87</v>
       </c>
       <c r="I8" s="3">
-        <v>476595.05</v>
+        <v>486298.69</v>
       </c>
       <c r="J8" s="3">
-        <v>65.57</v>
+        <v>66.91</v>
       </c>
       <c r="K8" s="3">
-        <v>-250237.66</v>
+        <v>-240534.02</v>
       </c>
       <c r="L8" s="3">
         <v>0.61</v>
       </c>
       <c r="M8" s="3">
-        <v>2901.44</v>
+        <v>2976.4</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>1605</v>
+        <v>2147</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1606</v>
+        <v>2148</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1607</v>
+        <v>2149</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1608</v>
+        <v>2150</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1609</v>
+        <v>2151</v>
       </c>
       <c r="F9" s="3">
         <v>741741.03</v>
       </c>
       <c r="G9" s="3">
-        <v>413158.92</v>
+        <v>432349.73</v>
       </c>
       <c r="H9" s="3">
-        <v>203127.53</v>
+        <v>196899.78</v>
       </c>
       <c r="I9" s="3">
-        <v>616286.45</v>
+        <v>629249.51</v>
       </c>
       <c r="J9" s="3">
-        <v>83.09</v>
+        <v>84.83</v>
       </c>
       <c r="K9" s="3">
-        <v>-125454.58</v>
+        <v>-112491.52</v>
       </c>
       <c r="L9" s="3">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="M9" s="3">
-        <v>13840.72</v>
+        <v>14680.36</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>1610</v>
+        <v>2152</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1611</v>
+        <v>2153</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1612</v>
+        <v>2154</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1613</v>
+        <v>2155</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1614</v>
+        <v>2156</v>
       </c>
       <c r="F10" s="3">
         <v>859984.15</v>
       </c>
       <c r="G10" s="3">
-        <v>438610.36</v>
+        <v>469529.82</v>
       </c>
       <c r="H10" s="3">
-        <v>272896.72</v>
+        <v>233187.21</v>
       </c>
       <c r="I10" s="3">
-        <v>711507.08</v>
+        <v>702717.03</v>
       </c>
       <c r="J10" s="3">
-        <v>82.73</v>
+        <v>81.71</v>
       </c>
       <c r="K10" s="3">
-        <v>-148477.07</v>
+        <v>-157267.12</v>
       </c>
       <c r="L10" s="3">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="M10" s="3">
-        <v>16230.96</v>
+        <v>16724.64</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>1615</v>
+        <v>2157</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1616</v>
+        <v>2158</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1617</v>
+        <v>2159</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1618</v>
+        <v>2160</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1619</v>
+        <v>2161</v>
       </c>
       <c r="F11" s="3">
         <v>903047.31</v>
       </c>
       <c r="G11" s="3">
-        <v>380004.89</v>
+        <v>396468.12</v>
       </c>
       <c r="H11" s="3">
-        <v>178232.3</v>
+        <v>192768.16</v>
       </c>
       <c r="I11" s="3">
-        <v>558237.19</v>
+        <v>589236.28</v>
       </c>
       <c r="J11" s="3">
-        <v>61.82</v>
+        <v>65.25</v>
       </c>
       <c r="K11" s="3">
-        <v>-344810.12</v>
+        <v>-313811.03</v>
       </c>
       <c r="L11" s="3">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="M11" s="3">
-        <v>14586.3</v>
+        <v>15508.35</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>1620</v>
+        <v>2162</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1621</v>
+        <v>2163</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1622</v>
+        <v>2164</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1623</v>
+        <v>2165</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1624</v>
+        <v>2166</v>
       </c>
       <c r="F12" s="3">
         <v>775221.33</v>
       </c>
       <c r="G12" s="3">
-        <v>431993.63</v>
+        <v>458533.89</v>
       </c>
       <c r="H12" s="3">
-        <v>204271.1</v>
+        <v>196413.06</v>
       </c>
       <c r="I12" s="3">
-        <v>636264.73</v>
+        <v>654946.95</v>
       </c>
       <c r="J12" s="3">
-        <v>82.08</v>
+        <v>84.49</v>
       </c>
       <c r="K12" s="3">
-        <v>-138956.6</v>
+        <v>-120274.38</v>
       </c>
       <c r="L12" s="3">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M12" s="3">
-        <v>7660.09</v>
+        <v>8156.59</v>
       </c>
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>1625</v>
+        <v>2167</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1626</v>
+        <v>2168</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1627</v>
+        <v>2169</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1628</v>
+        <v>2170</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1629</v>
+        <v>2171</v>
       </c>
       <c r="F13" s="3">
         <v>808635.23</v>
       </c>
       <c r="G13" s="3">
-        <v>447572.93</v>
+        <v>469605.41</v>
       </c>
       <c r="H13" s="3">
-        <v>220771.34</v>
+        <v>216662.05</v>
       </c>
       <c r="I13" s="3">
-        <v>668344.27</v>
+        <v>686267.46</v>
       </c>
       <c r="J13" s="3">
-        <v>82.65</v>
+        <v>84.87</v>
       </c>
       <c r="K13" s="3">
-        <v>-140290.96</v>
+        <v>-122367.77</v>
       </c>
       <c r="L13" s="3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M13" s="3">
-        <v>8334.11</v>
+        <v>8859.07</v>
       </c>
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>1630</v>
+        <v>2172</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1631</v>
+        <v>2173</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1632</v>
+        <v>2174</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1633</v>
+        <v>2175</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1634</v>
+        <v>2176</v>
       </c>
       <c r="F14" s="3">
         <v>773239.07</v>
       </c>
       <c r="G14" s="3">
-        <v>348416.77</v>
+        <v>368178.7</v>
       </c>
       <c r="H14" s="3">
-        <v>279948.77</v>
+        <v>283276.91</v>
       </c>
       <c r="I14" s="3">
-        <v>628365.54</v>
+        <v>651455.61</v>
       </c>
       <c r="J14" s="3">
-        <v>81.26</v>
+        <v>84.25</v>
       </c>
       <c r="K14" s="3">
-        <v>-144873.53</v>
+        <v>-121783.46</v>
       </c>
       <c r="L14" s="3">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M14" s="3">
         <v>8679.8</v>
@@ -17830,40 +22718,40 @@
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>1635</v>
+        <v>2177</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1636</v>
+        <v>2178</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1637</v>
+        <v>2179</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1638</v>
+        <v>2180</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1639</v>
+        <v>2181</v>
       </c>
       <c r="F15" s="3">
         <v>788718.67</v>
       </c>
       <c r="G15" s="3">
-        <v>254504.76</v>
+        <v>277942.26</v>
       </c>
       <c r="H15" s="3">
-        <v>262486.01</v>
+        <v>251652.16</v>
       </c>
       <c r="I15" s="3">
-        <v>516990.77</v>
+        <v>529594.42</v>
       </c>
       <c r="J15" s="3">
-        <v>65.55</v>
+        <v>67.15</v>
       </c>
       <c r="K15" s="3">
-        <v>-271727.9</v>
+        <v>-259124.25</v>
       </c>
       <c r="L15" s="3">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="M15" s="3">
         <v>11754.24</v>
@@ -17871,40 +22759,40 @@
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>1640</v>
+        <v>2182</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1641</v>
+        <v>2183</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1642</v>
+        <v>2184</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1643</v>
+        <v>2185</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1644</v>
+        <v>2186</v>
       </c>
       <c r="F16" s="3">
         <v>757031.95</v>
       </c>
       <c r="G16" s="3">
-        <v>211873.41</v>
+        <v>223831.92</v>
       </c>
       <c r="H16" s="3">
-        <v>162552.31</v>
+        <v>159293.15</v>
       </c>
       <c r="I16" s="3">
-        <v>374425.72</v>
+        <v>383125.07</v>
       </c>
       <c r="J16" s="3">
-        <v>49.46</v>
+        <v>50.61</v>
       </c>
       <c r="K16" s="3">
-        <v>-382606.23</v>
+        <v>-373906.88</v>
       </c>
       <c r="L16" s="3">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M16" s="3">
         <v>5487.66</v>
@@ -17912,40 +22800,40 @@
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>1645</v>
+        <v>2187</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1646</v>
+        <v>2188</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1647</v>
+        <v>2189</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1648</v>
+        <v>2190</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1649</v>
+        <v>2191</v>
       </c>
       <c r="F17" s="3">
         <v>792097.85</v>
       </c>
       <c r="G17" s="3">
-        <v>261921.32</v>
+        <v>274923.29</v>
       </c>
       <c r="H17" s="3">
-        <v>216912.54</v>
+        <v>216712.45</v>
       </c>
       <c r="I17" s="3">
-        <v>478833.86</v>
+        <v>491635.74</v>
       </c>
       <c r="J17" s="3">
-        <v>60.45</v>
+        <v>62.07</v>
       </c>
       <c r="K17" s="3">
-        <v>-313263.99</v>
+        <v>-300462.11</v>
       </c>
       <c r="L17" s="3">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="M17" s="3">
         <v>14489.96</v>
@@ -17953,942 +22841,942 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>1650</v>
+        <v>2192</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1651</v>
+        <v>2193</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1652</v>
+        <v>2194</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1653</v>
+        <v>2195</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1654</v>
+        <v>2196</v>
       </c>
       <c r="F18" s="3">
         <v>1027095.81</v>
       </c>
       <c r="G18" s="3">
-        <v>595477.93</v>
+        <v>659233.34</v>
       </c>
       <c r="H18" s="3">
-        <v>152981.57</v>
+        <v>143119.47</v>
       </c>
       <c r="I18" s="3">
-        <v>748459.5</v>
+        <v>802352.81</v>
       </c>
       <c r="J18" s="3">
-        <v>72.87</v>
+        <v>78.12</v>
       </c>
       <c r="K18" s="3">
-        <v>-278636.31</v>
+        <v>-224743.0</v>
       </c>
       <c r="L18" s="3">
-        <v>5.66</v>
+        <v>5.8</v>
       </c>
       <c r="M18" s="3">
-        <v>42329.63</v>
+        <v>46525.89</v>
       </c>
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>1655</v>
+        <v>2197</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1656</v>
+        <v>2198</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1657</v>
+        <v>2199</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1658</v>
+        <v>2200</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1659</v>
+        <v>2201</v>
       </c>
       <c r="F19" s="3">
         <v>863850.75</v>
       </c>
       <c r="G19" s="3">
-        <v>586071.53</v>
+        <v>678043.84</v>
       </c>
       <c r="H19" s="3">
-        <v>177201.17</v>
+        <v>120388.91</v>
       </c>
       <c r="I19" s="3">
-        <v>763272.7</v>
+        <v>798432.75</v>
       </c>
       <c r="J19" s="3">
-        <v>88.36</v>
+        <v>92.43</v>
       </c>
       <c r="K19" s="3">
-        <v>-100578.05</v>
+        <v>-65418.0</v>
       </c>
       <c r="L19" s="3">
-        <v>4.71</v>
+        <v>4.95</v>
       </c>
       <c r="M19" s="3">
-        <v>35969.66</v>
+        <v>39516.78</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>1660</v>
+        <v>2202</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1661</v>
+        <v>2203</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1662</v>
+        <v>2204</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1663</v>
+        <v>2205</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1664</v>
+        <v>2206</v>
       </c>
       <c r="F20" s="3">
         <v>1246040.32</v>
       </c>
       <c r="G20" s="3">
-        <v>624262.57</v>
+        <v>694380.26</v>
       </c>
       <c r="H20" s="3">
-        <v>222892.1</v>
+        <v>193396.09</v>
       </c>
       <c r="I20" s="3">
-        <v>847154.67</v>
+        <v>887776.35</v>
       </c>
       <c r="J20" s="3">
-        <v>67.99</v>
+        <v>71.25</v>
       </c>
       <c r="K20" s="3">
-        <v>-398885.65</v>
+        <v>-358263.97</v>
       </c>
       <c r="L20" s="3">
-        <v>4.97</v>
+        <v>5.21</v>
       </c>
       <c r="M20" s="3">
-        <v>42139.75</v>
+        <v>46228.85</v>
       </c>
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>1665</v>
+        <v>2207</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1666</v>
+        <v>2208</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1667</v>
+        <v>2209</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1668</v>
+        <v>2210</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1669</v>
+        <v>2211</v>
       </c>
       <c r="F21" s="3">
         <v>875303.02</v>
       </c>
       <c r="G21" s="3">
-        <v>672212.88</v>
+        <v>715534.48</v>
       </c>
       <c r="H21" s="3">
-        <v>94759.99</v>
+        <v>112397.74</v>
       </c>
       <c r="I21" s="3">
-        <v>766972.87</v>
+        <v>827932.22</v>
       </c>
       <c r="J21" s="3">
-        <v>87.62</v>
+        <v>94.59</v>
       </c>
       <c r="K21" s="3">
-        <v>-108330.15</v>
+        <v>-47370.8</v>
       </c>
       <c r="L21" s="3">
         <v>2.21</v>
       </c>
       <c r="M21" s="3">
-        <v>16975.05</v>
+        <v>18258.99</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>1670</v>
+        <v>2212</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1671</v>
+        <v>2213</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1672</v>
+        <v>2214</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1673</v>
+        <v>2215</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1674</v>
+        <v>2216</v>
       </c>
       <c r="F22" s="3">
         <v>859661.34</v>
       </c>
       <c r="G22" s="3">
-        <v>670597.42</v>
+        <v>711727.72</v>
       </c>
       <c r="H22" s="3">
-        <v>138563.32</v>
+        <v>164084.87</v>
       </c>
       <c r="I22" s="3">
-        <v>809160.74</v>
+        <v>875812.59</v>
       </c>
       <c r="J22" s="3">
-        <v>94.13</v>
+        <v>101.88</v>
       </c>
       <c r="K22" s="3">
-        <v>-50500.6</v>
+        <v>16151.25</v>
       </c>
       <c r="L22" s="3">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="M22" s="3">
-        <v>26115.72</v>
+        <v>26736.84</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>1675</v>
+        <v>2217</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1676</v>
+        <v>2218</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1677</v>
+        <v>2219</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1678</v>
+        <v>2220</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1679</v>
+        <v>2221</v>
       </c>
       <c r="F23" s="3">
         <v>867257.37</v>
       </c>
       <c r="G23" s="3">
-        <v>729552.33</v>
+        <v>770752.11</v>
       </c>
       <c r="H23" s="3">
-        <v>135881.86</v>
+        <v>187114.27</v>
       </c>
       <c r="I23" s="3">
-        <v>865434.19</v>
+        <v>957866.38</v>
       </c>
       <c r="J23" s="3">
-        <v>99.79</v>
+        <v>110.45</v>
       </c>
       <c r="K23" s="3">
-        <v>-1823.18</v>
+        <v>90609.01</v>
       </c>
       <c r="L23" s="3">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="M23" s="3">
-        <v>15942.78</v>
+        <v>16632.62</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>1680</v>
+        <v>2222</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1681</v>
+        <v>2223</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1682</v>
+        <v>2224</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1683</v>
+        <v>2225</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1684</v>
+        <v>2226</v>
       </c>
       <c r="F24" s="3">
         <v>778641.12</v>
       </c>
       <c r="G24" s="3">
-        <v>625242.42</v>
+        <v>649508.54</v>
       </c>
       <c r="H24" s="3">
-        <v>100878.57</v>
+        <v>108891.43</v>
       </c>
       <c r="I24" s="3">
-        <v>726120.99</v>
+        <v>758399.97</v>
       </c>
       <c r="J24" s="3">
-        <v>93.25</v>
+        <v>97.4</v>
       </c>
       <c r="K24" s="3">
-        <v>-52520.13</v>
+        <v>-20241.15</v>
       </c>
       <c r="L24" s="3">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="M24" s="3">
-        <v>22140.44</v>
+        <v>22252.88</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>1685</v>
+        <v>2227</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1686</v>
+        <v>2228</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1687</v>
+        <v>2229</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1688</v>
+        <v>2230</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1689</v>
+        <v>2231</v>
       </c>
       <c r="F25" s="3">
         <v>979868.9</v>
       </c>
       <c r="G25" s="3">
-        <v>610061.4</v>
+        <v>643823.44</v>
       </c>
       <c r="H25" s="3">
-        <v>197295.59</v>
+        <v>180193.8</v>
       </c>
       <c r="I25" s="3">
-        <v>807356.99</v>
+        <v>824017.24</v>
       </c>
       <c r="J25" s="3">
-        <v>82.39</v>
+        <v>84.09</v>
       </c>
       <c r="K25" s="3">
-        <v>-172511.91</v>
+        <v>-155851.66</v>
       </c>
       <c r="L25" s="3">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="M25" s="3">
-        <v>15719.02</v>
+        <v>17002.12</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>1690</v>
+        <v>2232</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1691</v>
+        <v>2233</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1692</v>
+        <v>2234</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1693</v>
+        <v>2235</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1694</v>
+        <v>2236</v>
       </c>
       <c r="F26" s="3">
         <v>1011213.65</v>
       </c>
       <c r="G26" s="3">
-        <v>453115.42</v>
+        <v>480794.75</v>
       </c>
       <c r="H26" s="3">
-        <v>151022.32</v>
+        <v>137989.41</v>
       </c>
       <c r="I26" s="3">
-        <v>604137.74</v>
+        <v>618784.16</v>
       </c>
       <c r="J26" s="3">
-        <v>59.74</v>
+        <v>61.19</v>
       </c>
       <c r="K26" s="3">
-        <v>-407075.91</v>
+        <v>-392429.49</v>
       </c>
       <c r="L26" s="3">
-        <v>4.89</v>
+        <v>4.94</v>
       </c>
       <c r="M26" s="3">
-        <v>29543.21</v>
+        <v>30598.03</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>1695</v>
+        <v>2237</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1696</v>
+        <v>2238</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1697</v>
+        <v>2239</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1698</v>
+        <v>2240</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1699</v>
+        <v>2241</v>
       </c>
       <c r="F27" s="3">
         <v>905279.17</v>
       </c>
       <c r="G27" s="3">
-        <v>590979.48</v>
+        <v>633506.66</v>
       </c>
       <c r="H27" s="3">
-        <v>160309.48</v>
+        <v>148914.09</v>
       </c>
       <c r="I27" s="3">
-        <v>751288.96</v>
+        <v>782420.75</v>
       </c>
       <c r="J27" s="3">
-        <v>82.99</v>
+        <v>86.43</v>
       </c>
       <c r="K27" s="3">
-        <v>-153990.21</v>
+        <v>-122858.42</v>
       </c>
       <c r="L27" s="3">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="M27" s="3">
-        <v>16982.7</v>
+        <v>20013.19</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>1700</v>
+        <v>2242</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1701</v>
+        <v>2243</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1702</v>
+        <v>2244</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1703</v>
+        <v>2245</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1704</v>
+        <v>2246</v>
       </c>
       <c r="F28" s="3">
         <v>948604.6</v>
       </c>
       <c r="G28" s="3">
-        <v>579107.48</v>
+        <v>612158.8</v>
       </c>
       <c r="H28" s="3">
-        <v>117087.12</v>
+        <v>100950.4</v>
       </c>
       <c r="I28" s="3">
-        <v>696194.6</v>
+        <v>713109.2</v>
       </c>
       <c r="J28" s="3">
-        <v>73.39</v>
+        <v>75.17</v>
       </c>
       <c r="K28" s="3">
-        <v>-252410.0</v>
+        <v>-235495.4</v>
       </c>
       <c r="L28" s="3">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="M28" s="3">
-        <v>14790.72</v>
+        <v>17702.93</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>1705</v>
+        <v>2247</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1706</v>
+        <v>2248</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1707</v>
+        <v>2249</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1708</v>
+        <v>2250</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1709</v>
+        <v>2251</v>
       </c>
       <c r="F29" s="3">
         <v>824118.89</v>
       </c>
       <c r="G29" s="3">
-        <v>519742.87</v>
+        <v>564719.99</v>
       </c>
       <c r="H29" s="3">
-        <v>127399.62</v>
+        <v>127482.13</v>
       </c>
       <c r="I29" s="3">
-        <v>647142.49</v>
+        <v>692202.12</v>
       </c>
       <c r="J29" s="3">
-        <v>78.53</v>
+        <v>83.99</v>
       </c>
       <c r="K29" s="3">
-        <v>-176976.4</v>
+        <v>-131916.77</v>
       </c>
       <c r="L29" s="3">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="M29" s="3">
-        <v>18576.2</v>
+        <v>18801.2</v>
       </c>
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>1710</v>
+        <v>2252</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1711</v>
+        <v>2253</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1712</v>
+        <v>2254</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1713</v>
+        <v>2255</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1714</v>
+        <v>2256</v>
       </c>
       <c r="F30" s="3">
         <v>877850.52</v>
       </c>
       <c r="G30" s="3">
-        <v>714196.09</v>
+        <v>774156.33</v>
       </c>
       <c r="H30" s="3">
-        <v>162472.78</v>
+        <v>166991.45</v>
       </c>
       <c r="I30" s="3">
-        <v>876668.87</v>
+        <v>941147.78</v>
       </c>
       <c r="J30" s="3">
-        <v>99.87</v>
+        <v>107.21</v>
       </c>
       <c r="K30" s="3">
-        <v>-1181.65</v>
+        <v>63297.26</v>
       </c>
       <c r="L30" s="3">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="M30" s="3">
-        <v>20014.92</v>
+        <v>20869.72</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>1715</v>
+        <v>2257</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1716</v>
+        <v>2258</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1717</v>
+        <v>2259</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1718</v>
+        <v>2260</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1719</v>
+        <v>2261</v>
       </c>
       <c r="F31" s="3">
         <v>990466.72</v>
       </c>
       <c r="G31" s="3">
-        <v>667452.99</v>
+        <v>734747.08</v>
       </c>
       <c r="H31" s="3">
-        <v>161275.68</v>
+        <v>131839.19</v>
       </c>
       <c r="I31" s="3">
-        <v>828728.67</v>
+        <v>866586.27</v>
       </c>
       <c r="J31" s="3">
-        <v>83.67</v>
+        <v>87.49</v>
       </c>
       <c r="K31" s="3">
-        <v>-161738.05</v>
+        <v>-123880.45</v>
       </c>
       <c r="L31" s="3">
-        <v>4.26</v>
+        <v>4.11</v>
       </c>
       <c r="M31" s="3">
-        <v>35300.34</v>
+        <v>35615.04</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>1720</v>
+        <v>2262</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1721</v>
+        <v>2263</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1722</v>
+        <v>2264</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1723</v>
+        <v>2265</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1724</v>
+        <v>2266</v>
       </c>
       <c r="F32" s="3">
         <v>892245.98</v>
       </c>
       <c r="G32" s="3">
-        <v>568975.96</v>
+        <v>615840.67</v>
       </c>
       <c r="H32" s="3">
-        <v>150729.68</v>
+        <v>138614.9</v>
       </c>
       <c r="I32" s="3">
-        <v>719705.64</v>
+        <v>754455.57</v>
       </c>
       <c r="J32" s="3">
-        <v>80.66</v>
+        <v>84.56</v>
       </c>
       <c r="K32" s="3">
-        <v>-172540.34</v>
+        <v>-137790.41</v>
       </c>
       <c r="L32" s="3">
-        <v>3.79</v>
+        <v>3.68</v>
       </c>
       <c r="M32" s="3">
-        <v>27252.79</v>
+        <v>27746.47</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>1725</v>
+        <v>2267</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1726</v>
+        <v>2268</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1727</v>
+        <v>2269</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1728</v>
+        <v>2270</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1729</v>
+        <v>2271</v>
       </c>
       <c r="F33" s="3">
         <v>1265248.83</v>
       </c>
       <c r="G33" s="3">
-        <v>664527.91</v>
+        <v>693248.22</v>
       </c>
       <c r="H33" s="3">
-        <v>398529.71</v>
+        <v>367507.94</v>
       </c>
       <c r="I33" s="3">
-        <v>1063057.62</v>
+        <v>1060756.16</v>
       </c>
       <c r="J33" s="3">
-        <v>84.02</v>
+        <v>83.84</v>
       </c>
       <c r="K33" s="3">
-        <v>-202191.21</v>
+        <v>-204492.67</v>
       </c>
       <c r="L33" s="3">
-        <v>3.96</v>
+        <v>4.19</v>
       </c>
       <c r="M33" s="3">
-        <v>42135.7</v>
+        <v>44437.16</v>
       </c>
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>1730</v>
+        <v>2272</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1731</v>
+        <v>2273</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1732</v>
+        <v>2274</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1733</v>
+        <v>2275</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1734</v>
+        <v>2276</v>
       </c>
       <c r="F34" s="3">
         <v>1062018.28</v>
       </c>
       <c r="G34" s="3">
-        <v>593694.76</v>
+        <v>621544.23</v>
       </c>
       <c r="H34" s="3">
-        <v>107931.98</v>
+        <v>79415.25</v>
       </c>
       <c r="I34" s="3">
-        <v>701626.74</v>
+        <v>700959.48</v>
       </c>
       <c r="J34" s="3">
-        <v>66.07</v>
+        <v>66.0</v>
       </c>
       <c r="K34" s="3">
-        <v>-360391.54</v>
+        <v>-361058.8</v>
       </c>
       <c r="L34" s="3">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="M34" s="3">
-        <v>21447.8</v>
+        <v>22115.06</v>
       </c>
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>1735</v>
+        <v>2277</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1736</v>
+        <v>2278</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1737</v>
+        <v>2279</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1738</v>
+        <v>2280</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1739</v>
+        <v>2281</v>
       </c>
       <c r="F35" s="3">
         <v>1027050.57</v>
       </c>
       <c r="G35" s="3">
-        <v>646905.99</v>
+        <v>681746.53</v>
       </c>
       <c r="H35" s="3">
-        <v>159704.08</v>
+        <v>124481.34</v>
       </c>
       <c r="I35" s="3">
-        <v>806610.07</v>
+        <v>806227.87</v>
       </c>
       <c r="J35" s="3">
-        <v>78.54</v>
+        <v>78.5</v>
       </c>
       <c r="K35" s="3">
-        <v>-220440.5</v>
+        <v>-220822.7</v>
       </c>
       <c r="L35" s="3">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M35" s="3">
-        <v>22989.71</v>
+        <v>23371.91</v>
       </c>
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>1740</v>
+        <v>2282</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1741</v>
+        <v>2283</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1742</v>
+        <v>2284</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1743</v>
+        <v>2285</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1744</v>
+        <v>2286</v>
       </c>
       <c r="F36" s="3">
         <v>1150571.33</v>
       </c>
       <c r="G36" s="3">
-        <v>760419.63</v>
+        <v>839015.34</v>
       </c>
       <c r="H36" s="3">
-        <v>299154.67</v>
+        <v>310624.67</v>
       </c>
       <c r="I36" s="3">
-        <v>1059574.3</v>
+        <v>1149640.01</v>
       </c>
       <c r="J36" s="3">
-        <v>92.09</v>
+        <v>99.92</v>
       </c>
       <c r="K36" s="3">
-        <v>-90997.03</v>
+        <v>-931.32</v>
       </c>
       <c r="L36" s="3">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="M36" s="3">
-        <v>26971.06</v>
+        <v>27854.26</v>
       </c>
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>1745</v>
+        <v>2287</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1746</v>
+        <v>2288</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1747</v>
+        <v>2289</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1748</v>
+        <v>2290</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1749</v>
+        <v>2291</v>
       </c>
       <c r="F37" s="3">
         <v>1374896.6</v>
       </c>
       <c r="G37" s="3">
-        <v>713711.82</v>
+        <v>780551.93</v>
       </c>
       <c r="H37" s="3">
-        <v>286110.03</v>
+        <v>310955.73</v>
       </c>
       <c r="I37" s="3">
-        <v>999821.85</v>
+        <v>1091507.66</v>
       </c>
       <c r="J37" s="3">
-        <v>72.72</v>
+        <v>79.39</v>
       </c>
       <c r="K37" s="3">
-        <v>-375074.75</v>
+        <v>-283388.94</v>
       </c>
       <c r="L37" s="3">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="M37" s="3">
-        <v>32842.86</v>
+        <v>34884.94</v>
       </c>
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>1750</v>
+        <v>2292</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1751</v>
+        <v>2293</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1752</v>
+        <v>2294</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1753</v>
+        <v>2295</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1754</v>
+        <v>2296</v>
       </c>
       <c r="F38" s="3">
         <v>904558.95</v>
       </c>
       <c r="G38" s="3">
-        <v>540284.31</v>
+        <v>608063.05</v>
       </c>
       <c r="H38" s="3">
-        <v>242080.55</v>
+        <v>253546.47</v>
       </c>
       <c r="I38" s="3">
-        <v>782364.86</v>
+        <v>861609.52</v>
       </c>
       <c r="J38" s="3">
-        <v>86.49</v>
+        <v>95.25</v>
       </c>
       <c r="K38" s="3">
-        <v>-122194.09</v>
+        <v>-42949.43</v>
       </c>
       <c r="L38" s="3">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="M38" s="3">
-        <v>19098.98</v>
+        <v>22022.51</v>
       </c>
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>1755</v>
+        <v>2297</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1756</v>
+        <v>2298</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1757</v>
+        <v>2299</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1758</v>
+        <v>2300</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1759</v>
+        <v>2301</v>
       </c>
       <c r="F39" s="3">
         <v>1106940.64</v>
       </c>
       <c r="G39" s="3">
-        <v>511089.55</v>
+        <v>568015.83</v>
       </c>
       <c r="H39" s="3">
-        <v>234810.31</v>
+        <v>227527.86</v>
       </c>
       <c r="I39" s="3">
-        <v>745899.86</v>
+        <v>795543.69</v>
       </c>
       <c r="J39" s="3">
-        <v>67.38</v>
+        <v>71.87</v>
       </c>
       <c r="K39" s="3">
-        <v>-361040.78</v>
+        <v>-311396.95</v>
       </c>
       <c r="L39" s="3">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="M39" s="3">
-        <v>23734.72</v>
+        <v>25996.48</v>
       </c>
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>1760</v>
+        <v>2302</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1761</v>
+        <v>2303</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1762</v>
+        <v>2304</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1763</v>
+        <v>2305</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1764</v>
+        <v>2306</v>
       </c>
       <c r="F40" s="3">
         <v>887573.45</v>
       </c>
       <c r="G40" s="3">
-        <v>457043.02</v>
+        <v>489079.14</v>
       </c>
       <c r="H40" s="3">
-        <v>141323.92</v>
+        <v>114968.4</v>
       </c>
       <c r="I40" s="3">
-        <v>598366.94</v>
+        <v>604047.54</v>
       </c>
       <c r="J40" s="3">
-        <v>67.42</v>
+        <v>68.06</v>
       </c>
       <c r="K40" s="3">
-        <v>-289206.51</v>
+        <v>-283525.91</v>
       </c>
       <c r="L40" s="3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M40" s="3">
         <v>7048.51</v>
@@ -18896,265 +23784,265 @@
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>1765</v>
+        <v>2307</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1766</v>
+        <v>2308</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1767</v>
+        <v>2309</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1768</v>
+        <v>2310</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1769</v>
+        <v>2311</v>
       </c>
       <c r="F41" s="3">
         <v>1236217.2</v>
       </c>
       <c r="G41" s="3">
-        <v>628068.11</v>
+        <v>676823.79</v>
       </c>
       <c r="H41" s="3">
-        <v>222457.47</v>
+        <v>207290.98</v>
       </c>
       <c r="I41" s="3">
-        <v>850525.58</v>
+        <v>884114.77</v>
       </c>
       <c r="J41" s="3">
-        <v>68.8</v>
+        <v>71.52</v>
       </c>
       <c r="K41" s="3">
-        <v>-385691.62</v>
+        <v>-352102.43</v>
       </c>
       <c r="L41" s="3">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="M41" s="3">
-        <v>26896.64</v>
+        <v>27346.64</v>
       </c>
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>1770</v>
+        <v>2312</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1771</v>
+        <v>2313</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1772</v>
+        <v>2314</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1773</v>
+        <v>2315</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1774</v>
+        <v>2316</v>
       </c>
       <c r="F42" s="3">
         <v>912015.93</v>
       </c>
       <c r="G42" s="3">
-        <v>538954.43</v>
+        <v>587792.49</v>
       </c>
       <c r="H42" s="3">
-        <v>205434.89</v>
+        <v>160736.22</v>
       </c>
       <c r="I42" s="3">
-        <v>744389.32</v>
+        <v>748528.71</v>
       </c>
       <c r="J42" s="3">
-        <v>81.62</v>
+        <v>82.07</v>
       </c>
       <c r="K42" s="3">
-        <v>-167626.61</v>
+        <v>-163487.22</v>
       </c>
       <c r="L42" s="3">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="M42" s="3">
-        <v>14747.12</v>
+        <v>16545.38</v>
       </c>
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>1775</v>
+        <v>2317</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1776</v>
+        <v>2318</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1777</v>
+        <v>2319</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1778</v>
+        <v>2320</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1779</v>
+        <v>2321</v>
       </c>
       <c r="F43" s="3">
         <v>1043081.21</v>
       </c>
       <c r="G43" s="3">
-        <v>759332.15</v>
+        <v>819628.36</v>
       </c>
       <c r="H43" s="3">
-        <v>227799.38</v>
+        <v>179481.77</v>
       </c>
       <c r="I43" s="3">
-        <v>987131.53</v>
+        <v>999110.13</v>
       </c>
       <c r="J43" s="3">
-        <v>94.64</v>
+        <v>95.78</v>
       </c>
       <c r="K43" s="3">
-        <v>-55949.68</v>
+        <v>-43971.08</v>
       </c>
       <c r="L43" s="3">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="M43" s="3">
-        <v>20597.93</v>
+        <v>21771.84</v>
       </c>
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>1780</v>
+        <v>2322</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1781</v>
+        <v>2323</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1782</v>
+        <v>2324</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1783</v>
+        <v>2325</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1784</v>
+        <v>2326</v>
       </c>
       <c r="F44" s="3">
         <v>1113507.9</v>
       </c>
       <c r="G44" s="3">
-        <v>728967.84</v>
+        <v>781600.92</v>
       </c>
       <c r="H44" s="3">
-        <v>121585.49</v>
+        <v>53419.93</v>
       </c>
       <c r="I44" s="3">
-        <v>850553.33</v>
+        <v>835020.85</v>
       </c>
       <c r="J44" s="3">
-        <v>76.39</v>
+        <v>74.99</v>
       </c>
       <c r="K44" s="3">
-        <v>-262954.57</v>
+        <v>-278487.05</v>
       </c>
       <c r="L44" s="3">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="M44" s="3">
-        <v>19632.92</v>
+        <v>21480.48</v>
       </c>
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>1785</v>
+        <v>2327</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1786</v>
+        <v>2328</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1787</v>
+        <v>2329</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1788</v>
+        <v>2330</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1789</v>
+        <v>2331</v>
       </c>
       <c r="F45" s="3">
         <v>918319.81</v>
       </c>
       <c r="G45" s="3">
-        <v>728801.52</v>
+        <v>771617.57</v>
       </c>
       <c r="H45" s="3">
-        <v>112671.28</v>
+        <v>58420.56</v>
       </c>
       <c r="I45" s="3">
-        <v>841472.8</v>
+        <v>830038.13</v>
       </c>
       <c r="J45" s="3">
-        <v>91.63</v>
+        <v>90.39</v>
       </c>
       <c r="K45" s="3">
-        <v>-76847.01</v>
+        <v>-88281.68</v>
       </c>
       <c r="L45" s="3">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="M45" s="3">
-        <v>13001.83</v>
+        <v>14538.38</v>
       </c>
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>1790</v>
+        <v>2332</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1791</v>
+        <v>2333</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1792</v>
+        <v>2334</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1793</v>
+        <v>2335</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1794</v>
+        <v>2336</v>
       </c>
       <c r="F46" s="3">
         <v>1066780.42</v>
       </c>
       <c r="G46" s="3">
-        <v>784900.21</v>
+        <v>842779.71</v>
       </c>
       <c r="H46" s="3">
-        <v>116963.56</v>
+        <v>41957.94</v>
       </c>
       <c r="I46" s="3">
-        <v>901863.77</v>
+        <v>884737.65</v>
       </c>
       <c r="J46" s="3">
-        <v>84.54</v>
+        <v>82.94</v>
       </c>
       <c r="K46" s="3">
-        <v>-164916.65</v>
+        <v>-182042.77</v>
       </c>
       <c r="L46" s="3">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="M46" s="3">
-        <v>15407.32</v>
+        <v>19313.76</v>
       </c>
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>1795</v>
+        <v>2337</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1796</v>
+        <v>2338</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1797</v>
+        <v>2339</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1798</v>
+        <v>2340</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1799</v>
+        <v>2341</v>
       </c>
       <c r="F47" s="3">
         <v>1336954.46</v>
@@ -19183,19 +24071,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>1800</v>
+        <v>2342</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1801</v>
+        <v>2343</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1802</v>
+        <v>2344</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1803</v>
+        <v>2345</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1804</v>
+        <v>2346</v>
       </c>
       <c r="F48" s="3">
         <v>1022376.56</v>
@@ -19224,19 +24112,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>1805</v>
+        <v>2347</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1806</v>
+        <v>2348</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1807</v>
+        <v>2349</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1808</v>
+        <v>2350</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1809</v>
+        <v>2351</v>
       </c>
       <c r="F49" s="3">
         <v>972020.19</v>
@@ -19265,19 +24153,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>1810</v>
+        <v>2352</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1811</v>
+        <v>2353</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1812</v>
+        <v>2354</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1813</v>
+        <v>2355</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1814</v>
+        <v>2356</v>
       </c>
       <c r="F50" s="3">
         <v>963790.11</v>
@@ -19306,19 +24194,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>1815</v>
+        <v>2357</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1816</v>
+        <v>2358</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1817</v>
+        <v>2359</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1818</v>
+        <v>2360</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1819</v>
+        <v>2361</v>
       </c>
       <c r="F51" s="3">
         <v>954958.72</v>
@@ -19347,19 +24235,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>1820</v>
+        <v>2362</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1821</v>
+        <v>2363</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1822</v>
+        <v>2364</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1823</v>
+        <v>2365</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1824</v>
+        <v>2366</v>
       </c>
       <c r="F52" s="3">
         <v>1154949.94</v>
@@ -19393,7 +24281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -19442,306 +24330,306 @@
       </c>
     </row>
     <row r="2" spans="8:8" ht="36.7">
-      <c r="A2" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1826</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1827</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1828</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="A2" s="5" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2369</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="E2" s="6">
         <v>5936775.24</v>
       </c>
-      <c r="F2" s="3">
-        <v>3127296.62</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1777975.18</v>
-      </c>
-      <c r="H2" s="3">
-        <v>4905271.8</v>
-      </c>
-      <c r="I2" s="3">
-        <v>82.63</v>
-      </c>
-      <c r="J2" s="3">
-        <v>-1031503.44</v>
-      </c>
-      <c r="K2" s="3">
-        <v>104582.34</v>
-      </c>
-      <c r="L2" s="3">
-        <v>2.13</v>
+      <c r="F2" s="6">
+        <v>3347104.08</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1648777.66</v>
+      </c>
+      <c r="H2" s="6">
+        <v>4995881.74</v>
+      </c>
+      <c r="I2" s="6">
+        <v>84.15</v>
+      </c>
+      <c r="J2" s="6">
+        <v>-940893.5</v>
+      </c>
+      <c r="K2" s="6">
+        <v>112967.15</v>
+      </c>
+      <c r="L2" s="6">
+        <v>2.26</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
-      <c r="A3" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1831</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="A3" s="5" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2374</v>
+      </c>
+      <c r="E3" s="6">
         <v>3346888.02</v>
       </c>
-      <c r="F3" s="3">
-        <v>1698181.81</v>
-      </c>
-      <c r="G3" s="3">
-        <v>876171.46</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2574353.27</v>
-      </c>
-      <c r="I3" s="3">
-        <v>76.92</v>
-      </c>
-      <c r="J3" s="3">
-        <v>-772534.75</v>
-      </c>
-      <c r="K3" s="3">
-        <v>46811.46</v>
-      </c>
-      <c r="L3" s="3">
-        <v>1.82</v>
+      <c r="F3" s="6">
+        <v>1794137.23</v>
+      </c>
+      <c r="G3" s="6">
+        <v>803526.2</v>
+      </c>
+      <c r="H3" s="6">
+        <v>2597663.43</v>
+      </c>
+      <c r="I3" s="6">
+        <v>77.61</v>
+      </c>
+      <c r="J3" s="6">
+        <v>-749224.59</v>
+      </c>
+      <c r="K3" s="6">
+        <v>49248.65</v>
+      </c>
+      <c r="L3" s="6">
+        <v>1.9</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
-      <c r="A4" s="2" t="s">
-        <v>1833</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1834</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1835</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1836</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="A4" s="5" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2376</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E4" s="6">
         <v>6248074.42</v>
       </c>
-      <c r="F4" s="3">
-        <v>2882528.29</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1474974.46</v>
-      </c>
-      <c r="H4" s="3">
-        <v>4357502.75</v>
-      </c>
-      <c r="I4" s="3">
-        <v>69.74</v>
-      </c>
-      <c r="J4" s="3">
-        <v>-1890571.67</v>
-      </c>
-      <c r="K4" s="3">
-        <v>160850.7</v>
-      </c>
-      <c r="L4" s="3">
-        <v>3.69</v>
+      <c r="F4" s="6">
+        <v>3176533.61</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1367839.15</v>
+      </c>
+      <c r="H4" s="6">
+        <v>4544372.76</v>
+      </c>
+      <c r="I4" s="6">
+        <v>72.73</v>
+      </c>
+      <c r="J4" s="6">
+        <v>-1703701.66</v>
+      </c>
+      <c r="K4" s="6">
+        <v>172683.18</v>
+      </c>
+      <c r="L4" s="6">
+        <v>3.8</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
-      <c r="A5" s="2" t="s">
-        <v>1837</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1838</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1840</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="A5" s="5" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E5" s="6">
         <v>7225829.17</v>
       </c>
-      <c r="F5" s="3">
-        <v>4930868.83</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1095798.25</v>
-      </c>
-      <c r="H5" s="3">
-        <v>6026667.08</v>
-      </c>
-      <c r="I5" s="3">
-        <v>83.4</v>
-      </c>
-      <c r="J5" s="3">
-        <v>-1199162.09</v>
-      </c>
-      <c r="K5" s="3">
-        <v>158209.65</v>
-      </c>
-      <c r="L5" s="3">
-        <v>2.63</v>
+      <c r="F5" s="6">
+        <v>5217806.5</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1042517.18</v>
+      </c>
+      <c r="H5" s="6">
+        <v>6260323.68</v>
+      </c>
+      <c r="I5" s="6">
+        <v>86.64</v>
+      </c>
+      <c r="J5" s="6">
+        <v>-965505.49</v>
+      </c>
+      <c r="K5" s="6">
+        <v>169197.61</v>
+      </c>
+      <c r="L5" s="6">
+        <v>2.7</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
-      <c r="A6" s="2" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1843</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1844</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="A6" s="5" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>2385</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>2386</v>
+      </c>
+      <c r="E6" s="6">
         <v>6938999.79</v>
       </c>
-      <c r="F6" s="3">
-        <v>4375496.57</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1268043.52</v>
-      </c>
-      <c r="H6" s="3">
-        <v>5643540.09</v>
-      </c>
-      <c r="I6" s="3">
-        <v>81.33</v>
-      </c>
-      <c r="J6" s="3">
-        <v>-1295459.7</v>
-      </c>
-      <c r="K6" s="3">
-        <v>187717.46</v>
-      </c>
-      <c r="L6" s="3">
-        <v>3.33</v>
+      <c r="F6" s="6">
+        <v>4686003.05</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1136332.19</v>
+      </c>
+      <c r="H6" s="6">
+        <v>5822335.24</v>
+      </c>
+      <c r="I6" s="6">
+        <v>83.91</v>
+      </c>
+      <c r="J6" s="6">
+        <v>-1116664.55</v>
+      </c>
+      <c r="K6" s="6">
+        <v>192956.56</v>
+      </c>
+      <c r="L6" s="6">
+        <v>3.31</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
-      <c r="A7" s="2" t="s">
-        <v>1845</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1846</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1848</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="A7" s="5" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E7" s="6">
         <v>4536967.52</v>
       </c>
-      <c r="F7" s="3">
-        <v>2525505.31</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1062155.56</v>
-      </c>
-      <c r="H7" s="3">
-        <v>3587660.87</v>
-      </c>
-      <c r="I7" s="3">
-        <v>79.08</v>
-      </c>
-      <c r="J7" s="3">
-        <v>-949306.65</v>
-      </c>
-      <c r="K7" s="3">
-        <v>102647.62</v>
-      </c>
-      <c r="L7" s="3">
-        <v>2.86</v>
+      <c r="F7" s="6">
+        <v>2795646.15</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1102654.73</v>
+      </c>
+      <c r="H7" s="6">
+        <v>3898300.88</v>
+      </c>
+      <c r="I7" s="6">
+        <v>85.92</v>
+      </c>
+      <c r="J7" s="6">
+        <v>-638666.64</v>
+      </c>
+      <c r="K7" s="6">
+        <v>110758.19</v>
+      </c>
+      <c r="L7" s="6">
+        <v>2.84</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
-      <c r="A8" s="2" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1850</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1852</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="A8" s="5" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E8" s="6">
         <v>7177495.92</v>
       </c>
-      <c r="F8" s="3">
-        <v>4626067.28</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1148235.99</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5774303.27</v>
-      </c>
-      <c r="I8" s="3">
-        <v>80.45</v>
-      </c>
-      <c r="J8" s="3">
-        <v>-1403192.65</v>
-      </c>
-      <c r="K8" s="3">
-        <v>117332.27</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2.03</v>
+      <c r="F8" s="6">
+        <v>4969321.98</v>
+      </c>
+      <c r="G8" s="6">
+        <v>816275.8</v>
+      </c>
+      <c r="H8" s="6">
+        <v>5785597.78</v>
+      </c>
+      <c r="I8" s="6">
+        <v>80.61</v>
+      </c>
+      <c r="J8" s="6">
+        <v>-1391898.14</v>
+      </c>
+      <c r="K8" s="6">
+        <v>128044.99</v>
+      </c>
+      <c r="L8" s="6">
+        <v>2.21</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
-      <c r="A9" s="2" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1854</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1855</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="A9" s="5" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>2398</v>
+      </c>
+      <c r="E9" s="6">
         <v>6405049.98</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="6">
         <v>3125217.98</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="6">
         <v>1406125.71</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="6">
         <v>4531343.69</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="6">
         <v>70.75</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="6">
         <v>-1873706.29</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="6">
         <v>170448.89</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="6">
         <v>3.76</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2399" count="2399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2941" count="2941">
   <si>
     <t>Region</t>
   </si>
@@ -21439,6 +21439,4884 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
     </r>
   </si>
   <si>
@@ -22124,7 +27002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:AB52"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -22185,655 +27063,655 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>2112</v>
+        <v>2654</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2113</v>
+        <v>2655</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2114</v>
+        <v>2656</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2115</v>
+        <v>2657</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2116</v>
+        <v>2658</v>
       </c>
       <c r="F2" s="3">
-        <v>747825.09</v>
+        <v>745422.79</v>
       </c>
       <c r="G2" s="3">
-        <v>459372.09</v>
+        <v>525292.5</v>
       </c>
       <c r="H2" s="3">
-        <v>189231.72</v>
+        <v>77428.21</v>
       </c>
       <c r="I2" s="3">
-        <v>648603.81</v>
+        <v>602720.71</v>
       </c>
       <c r="J2" s="3">
-        <v>86.73</v>
+        <v>80.86</v>
       </c>
       <c r="K2" s="3">
-        <v>-99221.28</v>
+        <v>-142702.08</v>
       </c>
       <c r="L2" s="3">
-        <v>2.08</v>
+        <v>3.99</v>
       </c>
       <c r="M2" s="3">
-        <v>13519.24</v>
+        <v>24070.05</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>2117</v>
+        <v>2659</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2118</v>
+        <v>2660</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2119</v>
+        <v>2661</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>2120</v>
+        <v>2662</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2121</v>
+        <v>2663</v>
       </c>
       <c r="F3" s="3">
         <v>755003.49</v>
       </c>
       <c r="G3" s="3">
-        <v>398938.35</v>
+        <v>612234.58</v>
       </c>
       <c r="H3" s="3">
-        <v>258264.74</v>
+        <v>83037.21</v>
       </c>
       <c r="I3" s="3">
-        <v>657203.09</v>
+        <v>695271.79</v>
       </c>
       <c r="J3" s="3">
-        <v>87.05</v>
+        <v>92.09</v>
       </c>
       <c r="K3" s="3">
-        <v>-97800.4</v>
+        <v>-59731.7</v>
       </c>
       <c r="L3" s="3">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
       <c r="M3" s="3">
-        <v>9550.02</v>
+        <v>13029.03</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2122</v>
+        <v>2664</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2123</v>
+        <v>2665</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2124</v>
+        <v>2666</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>2125</v>
+        <v>2667</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2126</v>
+        <v>2668</v>
       </c>
       <c r="F4" s="3">
         <v>664724.91</v>
       </c>
       <c r="G4" s="3">
-        <v>459171.19</v>
+        <v>636483.74</v>
       </c>
       <c r="H4" s="3">
-        <v>193309.94</v>
+        <v>49765.59</v>
       </c>
       <c r="I4" s="3">
-        <v>652481.13</v>
+        <v>686249.33</v>
       </c>
       <c r="J4" s="3">
-        <v>98.16</v>
+        <v>103.24</v>
       </c>
       <c r="K4" s="3">
-        <v>-12243.78</v>
+        <v>21524.42</v>
       </c>
       <c r="L4" s="3">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="M4" s="3">
-        <v>17957.37</v>
+        <v>19084.44</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>2127</v>
+        <v>2669</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2128</v>
+        <v>2670</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2129</v>
+        <v>2671</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>2130</v>
+        <v>2672</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>2131</v>
+        <v>2673</v>
       </c>
       <c r="F5" s="3">
-        <v>745422.79</v>
+        <v>747825.09</v>
       </c>
       <c r="G5" s="3">
-        <v>375613.39</v>
+        <v>561580.58</v>
       </c>
       <c r="H5" s="3">
-        <v>194997.13</v>
+        <v>117224.63</v>
       </c>
       <c r="I5" s="3">
-        <v>570610.52</v>
+        <v>678805.21</v>
       </c>
       <c r="J5" s="3">
-        <v>76.55</v>
+        <v>90.77</v>
       </c>
       <c r="K5" s="3">
-        <v>-174812.27</v>
+        <v>-69019.88</v>
       </c>
       <c r="L5" s="3">
-        <v>3.66</v>
+        <v>2.71</v>
       </c>
       <c r="M5" s="3">
-        <v>20884.05</v>
+        <v>18391.79</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>2132</v>
+        <v>2674</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2133</v>
+        <v>2675</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2134</v>
+        <v>2676</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>2135</v>
+        <v>2677</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>2136</v>
+        <v>2678</v>
       </c>
       <c r="F6" s="3">
         <v>750633.4</v>
       </c>
       <c r="G6" s="3">
-        <v>549530.36</v>
+        <v>798046.78</v>
       </c>
       <c r="H6" s="3">
-        <v>237940.7</v>
+        <v>28424.91</v>
       </c>
       <c r="I6" s="3">
-        <v>787471.06</v>
+        <v>826471.69</v>
       </c>
       <c r="J6" s="3">
-        <v>104.91</v>
+        <v>110.1</v>
       </c>
       <c r="K6" s="3">
-        <v>36837.66</v>
+        <v>75838.29</v>
       </c>
       <c r="L6" s="3">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="M6" s="3">
-        <v>21026.3</v>
+        <v>21639.95</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>2137</v>
+        <v>2679</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2138</v>
+        <v>2680</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>2139</v>
+        <v>2681</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>2140</v>
+        <v>2682</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>2141</v>
+        <v>2683</v>
       </c>
       <c r="F7" s="3">
         <v>804591.82</v>
       </c>
       <c r="G7" s="3">
-        <v>358616.15</v>
+        <v>568343.09</v>
       </c>
       <c r="H7" s="3">
-        <v>204931.13</v>
+        <v>17270.56</v>
       </c>
       <c r="I7" s="3">
-        <v>563547.28</v>
+        <v>585613.65</v>
       </c>
       <c r="J7" s="3">
-        <v>70.04</v>
+        <v>72.78</v>
       </c>
       <c r="K7" s="3">
-        <v>-241044.54</v>
+        <v>-218978.17</v>
       </c>
       <c r="L7" s="3">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="M7" s="3">
-        <v>12373.41</v>
+        <v>14980.55</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>2142</v>
+        <v>2684</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>2143</v>
+        <v>2685</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2144</v>
+        <v>2686</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>2145</v>
+        <v>2687</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>2146</v>
+        <v>2688</v>
       </c>
       <c r="F8" s="3">
-        <v>726832.71</v>
+        <v>741741.03</v>
       </c>
       <c r="G8" s="3">
-        <v>313512.82</v>
+        <v>637343.82</v>
       </c>
       <c r="H8" s="3">
-        <v>172785.87</v>
+        <v>22881.83</v>
       </c>
       <c r="I8" s="3">
-        <v>486298.69</v>
+        <v>660225.65</v>
       </c>
       <c r="J8" s="3">
-        <v>66.91</v>
+        <v>89.01</v>
       </c>
       <c r="K8" s="3">
-        <v>-240534.02</v>
+        <v>-81515.38</v>
       </c>
       <c r="L8" s="3">
-        <v>0.61</v>
+        <v>2.62</v>
       </c>
       <c r="M8" s="3">
-        <v>2976.4</v>
+        <v>17292.99</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>2147</v>
+        <v>2689</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>2148</v>
+        <v>2690</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2149</v>
+        <v>2691</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>2150</v>
+        <v>2692</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>2151</v>
+        <v>2693</v>
       </c>
       <c r="F9" s="3">
-        <v>741741.03</v>
+        <v>726832.71</v>
       </c>
       <c r="G9" s="3">
-        <v>432349.73</v>
+        <v>483732.62</v>
       </c>
       <c r="H9" s="3">
-        <v>196899.78</v>
+        <v>9511.88</v>
       </c>
       <c r="I9" s="3">
-        <v>629249.51</v>
+        <v>493244.5</v>
       </c>
       <c r="J9" s="3">
-        <v>84.83</v>
+        <v>67.86</v>
       </c>
       <c r="K9" s="3">
-        <v>-112491.52</v>
+        <v>-233588.21</v>
       </c>
       <c r="L9" s="3">
-        <v>2.33</v>
+        <v>0.99</v>
       </c>
       <c r="M9" s="3">
-        <v>14680.36</v>
+        <v>4899.7</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>2152</v>
+        <v>2694</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>2153</v>
+        <v>2695</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2154</v>
+        <v>2696</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>2155</v>
+        <v>2697</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>2156</v>
+        <v>2698</v>
       </c>
       <c r="F10" s="3">
         <v>859984.15</v>
       </c>
       <c r="G10" s="3">
-        <v>469529.82</v>
+        <v>600319.26</v>
       </c>
       <c r="H10" s="3">
-        <v>233187.21</v>
+        <v>167479.95</v>
       </c>
       <c r="I10" s="3">
-        <v>702717.03</v>
+        <v>767799.21</v>
       </c>
       <c r="J10" s="3">
-        <v>81.71</v>
+        <v>89.28</v>
       </c>
       <c r="K10" s="3">
-        <v>-157267.12</v>
+        <v>-92184.94</v>
       </c>
       <c r="L10" s="3">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="M10" s="3">
-        <v>16724.64</v>
+        <v>21910.4</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>2157</v>
+        <v>2699</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>2158</v>
+        <v>2700</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2159</v>
+        <v>2701</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>2160</v>
+        <v>2702</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>2161</v>
+        <v>2703</v>
       </c>
       <c r="F11" s="3">
         <v>903047.31</v>
       </c>
       <c r="G11" s="3">
-        <v>396468.12</v>
+        <v>487455.39</v>
       </c>
       <c r="H11" s="3">
-        <v>192768.16</v>
+        <v>133850.1</v>
       </c>
       <c r="I11" s="3">
-        <v>589236.28</v>
+        <v>621305.49</v>
       </c>
       <c r="J11" s="3">
-        <v>65.25</v>
+        <v>68.8</v>
       </c>
       <c r="K11" s="3">
-        <v>-313811.03</v>
+        <v>-281741.82</v>
       </c>
       <c r="L11" s="3">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="M11" s="3">
-        <v>15508.35</v>
+        <v>19545.35</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>2162</v>
+        <v>2704</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>2163</v>
+        <v>2705</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>2164</v>
+        <v>2706</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>2165</v>
+        <v>2707</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>2166</v>
+        <v>2708</v>
       </c>
       <c r="F12" s="3">
         <v>775221.33</v>
       </c>
       <c r="G12" s="3">
-        <v>458533.89</v>
+        <v>557189.82</v>
       </c>
       <c r="H12" s="3">
-        <v>196413.06</v>
+        <v>142022.02</v>
       </c>
       <c r="I12" s="3">
-        <v>654946.95</v>
+        <v>699211.84</v>
       </c>
       <c r="J12" s="3">
-        <v>84.49</v>
+        <v>90.2</v>
       </c>
       <c r="K12" s="3">
-        <v>-120274.38</v>
+        <v>-76009.49</v>
       </c>
       <c r="L12" s="3">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="M12" s="3">
-        <v>8156.59</v>
+        <v>10391.92</v>
       </c>
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>2167</v>
+        <v>2709</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2168</v>
+        <v>2710</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2169</v>
+        <v>2711</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>2170</v>
+        <v>2712</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>2171</v>
+        <v>2713</v>
       </c>
       <c r="F13" s="3">
         <v>808635.23</v>
       </c>
       <c r="G13" s="3">
-        <v>469605.41</v>
+        <v>552982.26</v>
       </c>
       <c r="H13" s="3">
-        <v>216662.05</v>
+        <v>152208.58</v>
       </c>
       <c r="I13" s="3">
-        <v>686267.46</v>
+        <v>705190.84</v>
       </c>
       <c r="J13" s="3">
-        <v>84.87</v>
+        <v>87.21</v>
       </c>
       <c r="K13" s="3">
-        <v>-122367.77</v>
+        <v>-103444.39</v>
       </c>
       <c r="L13" s="3">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="M13" s="3">
-        <v>8859.07</v>
+        <v>15500.04</v>
       </c>
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>2172</v>
+        <v>2714</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>2173</v>
+        <v>2715</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>2174</v>
+        <v>2716</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>2175</v>
+        <v>2717</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>2176</v>
+        <v>2718</v>
       </c>
       <c r="F14" s="3">
         <v>773239.07</v>
       </c>
       <c r="G14" s="3">
-        <v>368178.7</v>
+        <v>655574.49</v>
       </c>
       <c r="H14" s="3">
-        <v>283276.91</v>
+        <v>22797.12</v>
       </c>
       <c r="I14" s="3">
-        <v>651455.61</v>
+        <v>678371.61</v>
       </c>
       <c r="J14" s="3">
-        <v>84.25</v>
+        <v>87.73</v>
       </c>
       <c r="K14" s="3">
-        <v>-121783.46</v>
+        <v>-94867.46</v>
       </c>
       <c r="L14" s="3">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="M14" s="3">
-        <v>8679.8</v>
+        <v>10788.94</v>
       </c>
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>2177</v>
+        <v>2719</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>2178</v>
+        <v>2720</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>2179</v>
+        <v>2721</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>2180</v>
+        <v>2722</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>2181</v>
+        <v>2723</v>
       </c>
       <c r="F15" s="3">
         <v>788718.67</v>
       </c>
       <c r="G15" s="3">
-        <v>277942.26</v>
+        <v>528483.58</v>
       </c>
       <c r="H15" s="3">
-        <v>251652.16</v>
+        <v>14811.11</v>
       </c>
       <c r="I15" s="3">
-        <v>529594.42</v>
+        <v>543294.69</v>
       </c>
       <c r="J15" s="3">
-        <v>67.15</v>
+        <v>68.88</v>
       </c>
       <c r="K15" s="3">
-        <v>-259124.25</v>
+        <v>-245423.98</v>
       </c>
       <c r="L15" s="3">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="M15" s="3">
-        <v>11754.24</v>
+        <v>13572.04</v>
       </c>
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>2182</v>
+        <v>2724</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>2183</v>
+        <v>2725</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>2184</v>
+        <v>2726</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>2185</v>
+        <v>2727</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>2186</v>
+        <v>2728</v>
       </c>
       <c r="F16" s="3">
         <v>757031.95</v>
       </c>
       <c r="G16" s="3">
-        <v>223831.92</v>
+        <v>385369.53</v>
       </c>
       <c r="H16" s="3">
-        <v>159293.15</v>
+        <v>8113.29</v>
       </c>
       <c r="I16" s="3">
-        <v>383125.07</v>
+        <v>393482.82</v>
       </c>
       <c r="J16" s="3">
-        <v>50.61</v>
+        <v>51.98</v>
       </c>
       <c r="K16" s="3">
-        <v>-373906.88</v>
+        <v>-363549.13</v>
       </c>
       <c r="L16" s="3">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="M16" s="3">
-        <v>5487.66</v>
+        <v>6163.66</v>
       </c>
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>2187</v>
+        <v>2729</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>2188</v>
+        <v>2730</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2189</v>
+        <v>2731</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>2190</v>
+        <v>2732</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>2191</v>
+        <v>2733</v>
       </c>
       <c r="F17" s="3">
         <v>792097.85</v>
       </c>
       <c r="G17" s="3">
-        <v>274923.29</v>
+        <v>499203.64</v>
       </c>
       <c r="H17" s="3">
-        <v>216712.45</v>
+        <v>7492.55</v>
       </c>
       <c r="I17" s="3">
-        <v>491635.74</v>
+        <v>506696.19</v>
       </c>
       <c r="J17" s="3">
-        <v>62.07</v>
+        <v>63.97</v>
       </c>
       <c r="K17" s="3">
-        <v>-300462.11</v>
+        <v>-285401.66</v>
       </c>
       <c r="L17" s="3">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="M17" s="3">
         <v>14489.96</v>
@@ -22841,327 +27719,327 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>2192</v>
+        <v>2734</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>2193</v>
+        <v>2735</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2194</v>
+        <v>2736</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>2195</v>
+        <v>2737</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>2196</v>
+        <v>2738</v>
       </c>
       <c r="F18" s="3">
         <v>1027095.81</v>
       </c>
       <c r="G18" s="3">
-        <v>659233.34</v>
+        <v>799165.91</v>
       </c>
       <c r="H18" s="3">
-        <v>143119.47</v>
+        <v>88810.95</v>
       </c>
       <c r="I18" s="3">
-        <v>802352.81</v>
+        <v>887976.86</v>
       </c>
       <c r="J18" s="3">
-        <v>78.12</v>
+        <v>86.46</v>
       </c>
       <c r="K18" s="3">
-        <v>-224743.0</v>
+        <v>-139118.95</v>
       </c>
       <c r="L18" s="3">
-        <v>5.8</v>
+        <v>5.54</v>
       </c>
       <c r="M18" s="3">
-        <v>46525.89</v>
+        <v>49187.79</v>
       </c>
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>2197</v>
+        <v>2739</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>2198</v>
+        <v>2740</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>2199</v>
+        <v>2741</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>2200</v>
+        <v>2742</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>2201</v>
+        <v>2743</v>
       </c>
       <c r="F19" s="3">
-        <v>863850.75</v>
+        <v>1246040.32</v>
       </c>
       <c r="G19" s="3">
-        <v>678043.84</v>
+        <v>884510.57</v>
       </c>
       <c r="H19" s="3">
-        <v>120388.91</v>
+        <v>94593.21</v>
       </c>
       <c r="I19" s="3">
-        <v>798432.75</v>
+        <v>979103.78</v>
       </c>
       <c r="J19" s="3">
-        <v>92.43</v>
+        <v>78.58</v>
       </c>
       <c r="K19" s="3">
-        <v>-65418.0</v>
+        <v>-266936.54</v>
       </c>
       <c r="L19" s="3">
-        <v>4.95</v>
+        <v>5.06</v>
       </c>
       <c r="M19" s="3">
-        <v>39516.78</v>
+        <v>49494.63</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>2202</v>
+        <v>2744</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>2203</v>
+        <v>2745</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>2204</v>
+        <v>2746</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>2205</v>
+        <v>2747</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>2206</v>
+        <v>2748</v>
       </c>
       <c r="F20" s="3">
-        <v>1246040.32</v>
+        <v>863850.75</v>
       </c>
       <c r="G20" s="3">
-        <v>694380.26</v>
+        <v>796405.03</v>
       </c>
       <c r="H20" s="3">
-        <v>193396.09</v>
+        <v>75215.64</v>
       </c>
       <c r="I20" s="3">
-        <v>887776.35</v>
+        <v>871620.67</v>
       </c>
       <c r="J20" s="3">
-        <v>71.25</v>
+        <v>100.9</v>
       </c>
       <c r="K20" s="3">
-        <v>-358263.97</v>
+        <v>7769.92</v>
       </c>
       <c r="L20" s="3">
-        <v>5.21</v>
+        <v>4.77</v>
       </c>
       <c r="M20" s="3">
-        <v>46228.85</v>
+        <v>41544.5</v>
       </c>
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>2207</v>
+        <v>2749</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>2208</v>
+        <v>2750</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>2209</v>
+        <v>2751</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>2210</v>
+        <v>2752</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>2211</v>
+        <v>2753</v>
       </c>
       <c r="F21" s="3">
         <v>875303.02</v>
       </c>
       <c r="G21" s="3">
-        <v>715534.48</v>
+        <v>814370.32</v>
       </c>
       <c r="H21" s="3">
-        <v>112397.74</v>
+        <v>49461.77</v>
       </c>
       <c r="I21" s="3">
-        <v>827932.22</v>
+        <v>863832.09</v>
       </c>
       <c r="J21" s="3">
-        <v>94.59</v>
+        <v>98.69</v>
       </c>
       <c r="K21" s="3">
-        <v>-47370.8</v>
+        <v>-11470.93</v>
       </c>
       <c r="L21" s="3">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="M21" s="3">
-        <v>18258.99</v>
+        <v>18933.99</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>2212</v>
+        <v>2754</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>2213</v>
+        <v>2755</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>2214</v>
+        <v>2756</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>2215</v>
+        <v>2757</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>2216</v>
+        <v>2758</v>
       </c>
       <c r="F22" s="3">
         <v>859661.34</v>
       </c>
       <c r="G22" s="3">
-        <v>711727.72</v>
+        <v>839949.34</v>
       </c>
       <c r="H22" s="3">
-        <v>164084.87</v>
+        <v>88657.54</v>
       </c>
       <c r="I22" s="3">
-        <v>875812.59</v>
+        <v>928606.88</v>
       </c>
       <c r="J22" s="3">
-        <v>101.88</v>
+        <v>108.02</v>
       </c>
       <c r="K22" s="3">
-        <v>16151.25</v>
+        <v>68945.54</v>
       </c>
       <c r="L22" s="3">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="M22" s="3">
-        <v>26736.84</v>
+        <v>27636.44</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>2217</v>
+        <v>2759</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>2218</v>
+        <v>2760</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>2219</v>
+        <v>2761</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>2220</v>
+        <v>2762</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>2221</v>
+        <v>2763</v>
       </c>
       <c r="F23" s="3">
         <v>867257.37</v>
       </c>
       <c r="G23" s="3">
-        <v>770752.11</v>
+        <v>945748.57</v>
       </c>
       <c r="H23" s="3">
-        <v>187114.27</v>
+        <v>74261.75</v>
       </c>
       <c r="I23" s="3">
-        <v>957866.38</v>
+        <v>1020010.32</v>
       </c>
       <c r="J23" s="3">
-        <v>110.45</v>
+        <v>117.61</v>
       </c>
       <c r="K23" s="3">
-        <v>90609.01</v>
+        <v>152752.95</v>
       </c>
       <c r="L23" s="3">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="M23" s="3">
-        <v>16632.62</v>
+        <v>17252.74</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>2222</v>
+        <v>2764</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>2223</v>
+        <v>2765</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>2224</v>
+        <v>2766</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>2225</v>
+        <v>2767</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>2226</v>
+        <v>2768</v>
       </c>
       <c r="F24" s="3">
         <v>778641.12</v>
       </c>
       <c r="G24" s="3">
-        <v>649508.54</v>
+        <v>745963.94</v>
       </c>
       <c r="H24" s="3">
-        <v>108891.43</v>
+        <v>56782.59</v>
       </c>
       <c r="I24" s="3">
-        <v>758399.97</v>
+        <v>802746.53</v>
       </c>
       <c r="J24" s="3">
-        <v>97.4</v>
+        <v>103.1</v>
       </c>
       <c r="K24" s="3">
-        <v>-20241.15</v>
+        <v>24105.41</v>
       </c>
       <c r="L24" s="3">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="M24" s="3">
-        <v>22252.88</v>
+        <v>23266.35</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>2227</v>
+        <v>2769</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>2228</v>
+        <v>2770</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>2229</v>
+        <v>2771</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>2230</v>
+        <v>2772</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>2231</v>
+        <v>2773</v>
       </c>
       <c r="F25" s="3">
         <v>979868.9</v>
       </c>
       <c r="G25" s="3">
-        <v>643823.44</v>
+        <v>836212.36</v>
       </c>
       <c r="H25" s="3">
-        <v>180193.8</v>
+        <v>25581.03</v>
       </c>
       <c r="I25" s="3">
-        <v>824017.24</v>
+        <v>861793.39</v>
       </c>
       <c r="J25" s="3">
-        <v>84.09</v>
+        <v>87.95</v>
       </c>
       <c r="K25" s="3">
-        <v>-155851.66</v>
+        <v>-118075.51</v>
       </c>
       <c r="L25" s="3">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="M25" s="3">
         <v>17002.12</v>
@@ -23169,40 +28047,40 @@
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>2232</v>
+        <v>2774</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>2233</v>
+        <v>2775</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>2234</v>
+        <v>2776</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>2235</v>
+        <v>2777</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>2236</v>
+        <v>2778</v>
       </c>
       <c r="F26" s="3">
         <v>1011213.65</v>
       </c>
       <c r="G26" s="3">
-        <v>480794.75</v>
+        <v>632796.21</v>
       </c>
       <c r="H26" s="3">
-        <v>137989.41</v>
+        <v>25600.35</v>
       </c>
       <c r="I26" s="3">
-        <v>618784.16</v>
+        <v>658396.56</v>
       </c>
       <c r="J26" s="3">
-        <v>61.19</v>
+        <v>65.11</v>
       </c>
       <c r="K26" s="3">
-        <v>-392429.49</v>
+        <v>-352817.09</v>
       </c>
       <c r="L26" s="3">
-        <v>4.94</v>
+        <v>4.65</v>
       </c>
       <c r="M26" s="3">
         <v>30598.03</v>
@@ -23210,1068 +28088,1068 @@
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>2237</v>
+        <v>2779</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>2238</v>
+        <v>2780</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>2239</v>
+        <v>2781</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>2240</v>
+        <v>2782</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>2241</v>
+        <v>2783</v>
       </c>
       <c r="F27" s="3">
         <v>905279.17</v>
       </c>
       <c r="G27" s="3">
-        <v>633506.66</v>
+        <v>801848.44</v>
       </c>
       <c r="H27" s="3">
-        <v>148914.09</v>
+        <v>37848.41</v>
       </c>
       <c r="I27" s="3">
-        <v>782420.75</v>
+        <v>839696.85</v>
       </c>
       <c r="J27" s="3">
-        <v>86.43</v>
+        <v>92.76</v>
       </c>
       <c r="K27" s="3">
-        <v>-122858.42</v>
+        <v>-65582.32</v>
       </c>
       <c r="L27" s="3">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="M27" s="3">
-        <v>20013.19</v>
+        <v>20970.26</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>2242</v>
+        <v>2784</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>2243</v>
+        <v>2785</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>2244</v>
+        <v>2786</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>2245</v>
+        <v>2787</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>2246</v>
+        <v>2788</v>
       </c>
       <c r="F28" s="3">
         <v>948604.6</v>
       </c>
       <c r="G28" s="3">
-        <v>612158.8</v>
+        <v>728516.6</v>
       </c>
       <c r="H28" s="3">
-        <v>100950.4</v>
+        <v>23384.23</v>
       </c>
       <c r="I28" s="3">
-        <v>713109.2</v>
+        <v>751900.83</v>
       </c>
       <c r="J28" s="3">
-        <v>75.17</v>
+        <v>79.26</v>
       </c>
       <c r="K28" s="3">
-        <v>-235495.4</v>
+        <v>-196703.77</v>
       </c>
       <c r="L28" s="3">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="M28" s="3">
-        <v>17702.93</v>
+        <v>18017.81</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>2247</v>
+        <v>2789</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>2248</v>
+        <v>2790</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>2249</v>
+        <v>2791</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>2250</v>
+        <v>2792</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>2251</v>
+        <v>2793</v>
       </c>
       <c r="F29" s="3">
         <v>824118.89</v>
       </c>
       <c r="G29" s="3">
-        <v>564719.99</v>
+        <v>707538.01</v>
       </c>
       <c r="H29" s="3">
-        <v>127482.13</v>
+        <v>54751.85</v>
       </c>
       <c r="I29" s="3">
-        <v>692202.12</v>
+        <v>762289.86</v>
       </c>
       <c r="J29" s="3">
-        <v>83.99</v>
+        <v>92.5</v>
       </c>
       <c r="K29" s="3">
-        <v>-131916.77</v>
+        <v>-61829.03</v>
       </c>
       <c r="L29" s="3">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="M29" s="3">
-        <v>18801.2</v>
+        <v>23444.98</v>
       </c>
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>2252</v>
+        <v>2794</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>2253</v>
+        <v>2795</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>2254</v>
+        <v>2796</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>2255</v>
+        <v>2797</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>2256</v>
+        <v>2798</v>
       </c>
       <c r="F30" s="3">
         <v>877850.52</v>
       </c>
       <c r="G30" s="3">
-        <v>774156.33</v>
+        <v>964322.22</v>
       </c>
       <c r="H30" s="3">
-        <v>166991.45</v>
+        <v>55991.22</v>
       </c>
       <c r="I30" s="3">
-        <v>941147.78</v>
+        <v>1020313.44</v>
       </c>
       <c r="J30" s="3">
-        <v>107.21</v>
+        <v>116.23</v>
       </c>
       <c r="K30" s="3">
-        <v>63297.26</v>
+        <v>142462.92</v>
       </c>
       <c r="L30" s="3">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="M30" s="3">
-        <v>20869.72</v>
+        <v>22787.64</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>2257</v>
+        <v>2799</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>2258</v>
+        <v>2800</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>2259</v>
+        <v>2801</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>2260</v>
+        <v>2802</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>2261</v>
+        <v>2803</v>
       </c>
       <c r="F31" s="3">
         <v>990466.72</v>
       </c>
       <c r="G31" s="3">
-        <v>734747.08</v>
+        <v>885177.18</v>
       </c>
       <c r="H31" s="3">
-        <v>131839.19</v>
+        <v>46576.06</v>
       </c>
       <c r="I31" s="3">
-        <v>866586.27</v>
+        <v>931753.24</v>
       </c>
       <c r="J31" s="3">
-        <v>87.49</v>
+        <v>94.07</v>
       </c>
       <c r="K31" s="3">
-        <v>-123880.45</v>
+        <v>-58713.48</v>
       </c>
       <c r="L31" s="3">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="M31" s="3">
-        <v>35615.04</v>
+        <v>39114.52</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>2262</v>
+        <v>2804</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>2263</v>
+        <v>2805</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>2264</v>
+        <v>2806</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>2265</v>
+        <v>2807</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>2266</v>
+        <v>2808</v>
       </c>
       <c r="F32" s="3">
         <v>892245.98</v>
       </c>
       <c r="G32" s="3">
-        <v>615840.67</v>
+        <v>767978.5</v>
       </c>
       <c r="H32" s="3">
-        <v>138614.9</v>
+        <v>45543.1</v>
       </c>
       <c r="I32" s="3">
-        <v>754455.57</v>
+        <v>813521.6</v>
       </c>
       <c r="J32" s="3">
-        <v>84.56</v>
+        <v>91.18</v>
       </c>
       <c r="K32" s="3">
-        <v>-137790.41</v>
+        <v>-78724.38</v>
       </c>
       <c r="L32" s="3">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="M32" s="3">
-        <v>27746.47</v>
+        <v>29366.2</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>2267</v>
+        <v>2809</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>2268</v>
+        <v>2810</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>2269</v>
+        <v>2811</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>2270</v>
+        <v>2812</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>2271</v>
+        <v>2813</v>
       </c>
       <c r="F33" s="3">
         <v>1265248.83</v>
       </c>
       <c r="G33" s="3">
-        <v>693248.22</v>
+        <v>1127548.09</v>
       </c>
       <c r="H33" s="3">
-        <v>367507.94</v>
+        <v>61482.55</v>
       </c>
       <c r="I33" s="3">
-        <v>1060756.16</v>
+        <v>1189030.64</v>
       </c>
       <c r="J33" s="3">
-        <v>83.84</v>
+        <v>93.98</v>
       </c>
       <c r="K33" s="3">
-        <v>-204492.67</v>
+        <v>-76218.19</v>
       </c>
       <c r="L33" s="3">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="M33" s="3">
-        <v>44437.16</v>
+        <v>48720.71</v>
       </c>
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>2272</v>
+        <v>2814</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2273</v>
+        <v>2815</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>2274</v>
+        <v>2816</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>2275</v>
+        <v>2817</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>2276</v>
+        <v>2818</v>
       </c>
       <c r="F34" s="3">
         <v>1062018.28</v>
       </c>
       <c r="G34" s="3">
-        <v>621544.23</v>
+        <v>769054.14</v>
       </c>
       <c r="H34" s="3">
-        <v>79415.25</v>
+        <v>50820.42</v>
       </c>
       <c r="I34" s="3">
-        <v>700959.48</v>
+        <v>819874.56</v>
       </c>
       <c r="J34" s="3">
-        <v>66.0</v>
+        <v>77.2</v>
       </c>
       <c r="K34" s="3">
-        <v>-361058.8</v>
+        <v>-242143.72</v>
       </c>
       <c r="L34" s="3">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="M34" s="3">
-        <v>22115.06</v>
+        <v>23235.9</v>
       </c>
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>2277</v>
+        <v>2819</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2278</v>
+        <v>2820</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>2279</v>
+        <v>2821</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>2280</v>
+        <v>2822</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>2281</v>
+        <v>2823</v>
       </c>
       <c r="F35" s="3">
         <v>1027050.57</v>
       </c>
       <c r="G35" s="3">
-        <v>681746.53</v>
+        <v>893271.52</v>
       </c>
       <c r="H35" s="3">
-        <v>124481.34</v>
+        <v>64893.0</v>
       </c>
       <c r="I35" s="3">
-        <v>806227.87</v>
+        <v>958164.52</v>
       </c>
       <c r="J35" s="3">
-        <v>78.5</v>
+        <v>93.29</v>
       </c>
       <c r="K35" s="3">
-        <v>-220822.7</v>
+        <v>-68886.05</v>
       </c>
       <c r="L35" s="3">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="M35" s="3">
-        <v>23371.91</v>
+        <v>28049.78</v>
       </c>
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>2282</v>
+        <v>2824</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>2283</v>
+        <v>2825</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>2284</v>
+        <v>2826</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>2285</v>
+        <v>2827</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>2286</v>
+        <v>2828</v>
       </c>
       <c r="F36" s="3">
         <v>1150571.33</v>
       </c>
       <c r="G36" s="3">
-        <v>839015.34</v>
+        <v>1163274.65</v>
       </c>
       <c r="H36" s="3">
-        <v>310624.67</v>
+        <v>78889.36</v>
       </c>
       <c r="I36" s="3">
-        <v>1149640.01</v>
+        <v>1242164.01</v>
       </c>
       <c r="J36" s="3">
-        <v>99.92</v>
+        <v>107.96</v>
       </c>
       <c r="K36" s="3">
-        <v>-931.32</v>
+        <v>91592.68</v>
       </c>
       <c r="L36" s="3">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="M36" s="3">
-        <v>27854.26</v>
+        <v>28586.7</v>
       </c>
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>2287</v>
+        <v>2829</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2288</v>
+        <v>2830</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>2289</v>
+        <v>2831</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>2290</v>
+        <v>2832</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>2291</v>
+        <v>2833</v>
       </c>
       <c r="F37" s="3">
-        <v>1374896.6</v>
+        <v>904558.95</v>
       </c>
       <c r="G37" s="3">
-        <v>780551.93</v>
+        <v>863685.14</v>
       </c>
       <c r="H37" s="3">
-        <v>310955.73</v>
+        <v>43154.47</v>
       </c>
       <c r="I37" s="3">
-        <v>1091507.66</v>
+        <v>906839.61</v>
       </c>
       <c r="J37" s="3">
-        <v>79.39</v>
+        <v>100.25</v>
       </c>
       <c r="K37" s="3">
-        <v>-283388.94</v>
+        <v>2280.66</v>
       </c>
       <c r="L37" s="3">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M37" s="3">
-        <v>34884.94</v>
+        <v>22258.61</v>
       </c>
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>2292</v>
+        <v>2834</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2293</v>
+        <v>2835</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>2294</v>
+        <v>2836</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>2295</v>
+        <v>2837</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>2296</v>
+        <v>2838</v>
       </c>
       <c r="F38" s="3">
-        <v>904558.95</v>
+        <v>1106940.64</v>
       </c>
       <c r="G38" s="3">
-        <v>608063.05</v>
+        <v>797158.58</v>
       </c>
       <c r="H38" s="3">
-        <v>253546.47</v>
+        <v>47814.8</v>
       </c>
       <c r="I38" s="3">
-        <v>861609.52</v>
+        <v>844973.38</v>
       </c>
       <c r="J38" s="3">
-        <v>95.25</v>
+        <v>76.33</v>
       </c>
       <c r="K38" s="3">
-        <v>-42949.43</v>
+        <v>-261967.26</v>
       </c>
       <c r="L38" s="3">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="M38" s="3">
-        <v>22022.51</v>
+        <v>26877.41</v>
       </c>
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>2297</v>
+        <v>2839</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>2298</v>
+        <v>2840</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>2299</v>
+        <v>2841</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>2300</v>
+        <v>2842</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>2301</v>
+        <v>2843</v>
       </c>
       <c r="F39" s="3">
-        <v>1106940.64</v>
+        <v>1374896.6</v>
       </c>
       <c r="G39" s="3">
-        <v>568015.83</v>
+        <v>1108340.03</v>
       </c>
       <c r="H39" s="3">
-        <v>227527.86</v>
+        <v>93670.91</v>
       </c>
       <c r="I39" s="3">
-        <v>795543.69</v>
+        <v>1202010.94</v>
       </c>
       <c r="J39" s="3">
-        <v>71.87</v>
+        <v>87.43</v>
       </c>
       <c r="K39" s="3">
-        <v>-311396.95</v>
+        <v>-172885.66</v>
       </c>
       <c r="L39" s="3">
-        <v>3.27</v>
+        <v>3.13</v>
       </c>
       <c r="M39" s="3">
-        <v>25996.48</v>
+        <v>37639.5</v>
       </c>
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>2302</v>
+        <v>2844</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>2303</v>
+        <v>2845</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>2304</v>
+        <v>2846</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>2305</v>
+        <v>2847</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>2306</v>
+        <v>2848</v>
       </c>
       <c r="F40" s="3">
         <v>887573.45</v>
       </c>
       <c r="G40" s="3">
-        <v>489079.14</v>
+        <v>595721.97</v>
       </c>
       <c r="H40" s="3">
-        <v>114968.4</v>
+        <v>79758.01</v>
       </c>
       <c r="I40" s="3">
-        <v>604047.54</v>
+        <v>675479.98</v>
       </c>
       <c r="J40" s="3">
-        <v>68.06</v>
+        <v>76.1</v>
       </c>
       <c r="K40" s="3">
-        <v>-283525.91</v>
+        <v>-212093.47</v>
       </c>
       <c r="L40" s="3">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="M40" s="3">
-        <v>7048.51</v>
+        <v>7363.39</v>
       </c>
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>2307</v>
+        <v>2849</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>2308</v>
+        <v>2850</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>2309</v>
+        <v>2851</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>2310</v>
+        <v>2852</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>2311</v>
+        <v>2853</v>
       </c>
       <c r="F41" s="3">
-        <v>1236217.2</v>
+        <v>912015.93</v>
       </c>
       <c r="G41" s="3">
-        <v>676823.79</v>
+        <v>697279.24</v>
       </c>
       <c r="H41" s="3">
-        <v>207290.98</v>
+        <v>122534.91</v>
       </c>
       <c r="I41" s="3">
-        <v>884114.77</v>
+        <v>819814.15</v>
       </c>
       <c r="J41" s="3">
-        <v>71.52</v>
+        <v>89.89</v>
       </c>
       <c r="K41" s="3">
-        <v>-352102.43</v>
+        <v>-92201.78</v>
       </c>
       <c r="L41" s="3">
-        <v>3.09</v>
+        <v>2.07</v>
       </c>
       <c r="M41" s="3">
-        <v>27346.64</v>
+        <v>16972.68</v>
       </c>
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>2312</v>
+        <v>2854</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>2313</v>
+        <v>2855</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>2314</v>
+        <v>2856</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>2315</v>
+        <v>2857</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>2316</v>
+        <v>2858</v>
       </c>
       <c r="F42" s="3">
-        <v>912015.93</v>
+        <v>1236217.2</v>
       </c>
       <c r="G42" s="3">
-        <v>587792.49</v>
+        <v>823191.81</v>
       </c>
       <c r="H42" s="3">
-        <v>160736.22</v>
+        <v>138738.63</v>
       </c>
       <c r="I42" s="3">
-        <v>748528.71</v>
+        <v>961930.44</v>
       </c>
       <c r="J42" s="3">
-        <v>82.07</v>
+        <v>77.81</v>
       </c>
       <c r="K42" s="3">
-        <v>-163487.22</v>
+        <v>-274286.76</v>
       </c>
       <c r="L42" s="3">
-        <v>2.21</v>
+        <v>3.05</v>
       </c>
       <c r="M42" s="3">
-        <v>16545.38</v>
+        <v>29359.82</v>
       </c>
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>2317</v>
+        <v>2859</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>2318</v>
+        <v>2860</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>2319</v>
+        <v>2861</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>2320</v>
+        <v>2862</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>2321</v>
+        <v>2863</v>
       </c>
       <c r="F43" s="3">
         <v>1043081.21</v>
       </c>
       <c r="G43" s="3">
-        <v>819628.36</v>
+        <v>961464.47</v>
       </c>
       <c r="H43" s="3">
-        <v>179481.77</v>
+        <v>120162.6</v>
       </c>
       <c r="I43" s="3">
-        <v>999110.13</v>
+        <v>1081627.07</v>
       </c>
       <c r="J43" s="3">
-        <v>95.78</v>
+        <v>103.7</v>
       </c>
       <c r="K43" s="3">
-        <v>-43971.08</v>
+        <v>38545.86</v>
       </c>
       <c r="L43" s="3">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="M43" s="3">
-        <v>21771.84</v>
+        <v>23111.7</v>
       </c>
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>2322</v>
+        <v>2864</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>2323</v>
+        <v>2865</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>2324</v>
+        <v>2866</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>2325</v>
+        <v>2867</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>2326</v>
+        <v>2868</v>
       </c>
       <c r="F44" s="3">
         <v>1113507.9</v>
       </c>
       <c r="G44" s="3">
-        <v>781600.92</v>
+        <v>953689.92</v>
       </c>
       <c r="H44" s="3">
-        <v>53419.93</v>
+        <v>0.0</v>
       </c>
       <c r="I44" s="3">
-        <v>835020.85</v>
+        <v>953689.92</v>
       </c>
       <c r="J44" s="3">
-        <v>74.99</v>
+        <v>85.65</v>
       </c>
       <c r="K44" s="3">
-        <v>-278487.05</v>
+        <v>-159817.98</v>
       </c>
       <c r="L44" s="3">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="M44" s="3">
-        <v>21480.48</v>
+        <v>25364.88</v>
       </c>
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>2327</v>
+        <v>2869</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>2328</v>
+        <v>2870</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>2329</v>
+        <v>2871</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>2330</v>
+        <v>2872</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>2331</v>
+        <v>2873</v>
       </c>
       <c r="F45" s="3">
-        <v>918319.81</v>
+        <v>1066780.42</v>
       </c>
       <c r="G45" s="3">
-        <v>771617.57</v>
+        <v>962983.14</v>
       </c>
       <c r="H45" s="3">
-        <v>58420.56</v>
+        <v>0.0</v>
       </c>
       <c r="I45" s="3">
-        <v>830038.13</v>
+        <v>962983.14</v>
       </c>
       <c r="J45" s="3">
-        <v>90.39</v>
+        <v>90.27</v>
       </c>
       <c r="K45" s="3">
-        <v>-88281.68</v>
+        <v>-103797.28</v>
       </c>
       <c r="L45" s="3">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="M45" s="3">
-        <v>14538.38</v>
+        <v>21738.48</v>
       </c>
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>2332</v>
+        <v>2874</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>2333</v>
+        <v>2875</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>2334</v>
+        <v>2876</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>2335</v>
+        <v>2877</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>2336</v>
+        <v>2878</v>
       </c>
       <c r="F46" s="3">
-        <v>1066780.42</v>
+        <v>918319.81</v>
       </c>
       <c r="G46" s="3">
-        <v>842779.71</v>
+        <v>889388.08</v>
       </c>
       <c r="H46" s="3">
-        <v>41957.94</v>
+        <v>0.0</v>
       </c>
       <c r="I46" s="3">
-        <v>884737.65</v>
+        <v>889388.08</v>
       </c>
       <c r="J46" s="3">
-        <v>82.94</v>
+        <v>96.85</v>
       </c>
       <c r="K46" s="3">
-        <v>-182042.77</v>
+        <v>-28931.73</v>
       </c>
       <c r="L46" s="3">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="M46" s="3">
-        <v>19313.76</v>
+        <v>17481.66</v>
       </c>
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>2337</v>
+        <v>2879</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>2338</v>
+        <v>2880</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>2339</v>
+        <v>2881</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>2340</v>
+        <v>2882</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>2341</v>
+        <v>2883</v>
       </c>
       <c r="F47" s="3">
-        <v>1336954.46</v>
+        <v>972020.19</v>
       </c>
       <c r="G47" s="3">
-        <v>478076.29</v>
+        <v>771853.61</v>
       </c>
       <c r="H47" s="3">
-        <v>343180.31</v>
+        <v>0.0</v>
       </c>
       <c r="I47" s="3">
-        <v>821256.6</v>
+        <v>771853.61</v>
       </c>
       <c r="J47" s="3">
-        <v>61.43</v>
+        <v>79.41</v>
       </c>
       <c r="K47" s="3">
-        <v>-515697.86</v>
+        <v>-200166.58</v>
       </c>
       <c r="L47" s="3">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="M47" s="3">
-        <v>26763.01</v>
+        <v>22049.22</v>
       </c>
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>2342</v>
+        <v>2884</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>2343</v>
+        <v>2885</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>2344</v>
+        <v>2886</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>2345</v>
+        <v>2887</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>2346</v>
+        <v>2888</v>
       </c>
       <c r="F48" s="3">
         <v>1022376.56</v>
       </c>
       <c r="G48" s="3">
-        <v>410886.57</v>
+        <v>649753.47</v>
       </c>
       <c r="H48" s="3">
-        <v>198751.32</v>
+        <v>0.0</v>
       </c>
       <c r="I48" s="3">
-        <v>609637.89</v>
+        <v>649753.47</v>
       </c>
       <c r="J48" s="3">
-        <v>59.63</v>
+        <v>63.55</v>
       </c>
       <c r="K48" s="3">
-        <v>-412738.67</v>
+        <v>-372623.09</v>
       </c>
       <c r="L48" s="3">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="M48" s="3">
-        <v>19710.24</v>
+        <v>22729.34</v>
       </c>
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>2347</v>
+        <v>2889</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>2348</v>
+        <v>2890</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>2349</v>
+        <v>2891</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>2350</v>
+        <v>2892</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>2351</v>
+        <v>2893</v>
       </c>
       <c r="F49" s="3">
-        <v>972020.19</v>
+        <v>1336954.46</v>
       </c>
       <c r="G49" s="3">
-        <v>505461.32</v>
+        <v>864778.92</v>
       </c>
       <c r="H49" s="3">
-        <v>217317.93</v>
+        <v>0.0</v>
       </c>
       <c r="I49" s="3">
-        <v>722779.25</v>
+        <v>864778.92</v>
       </c>
       <c r="J49" s="3">
-        <v>74.36</v>
+        <v>64.68</v>
       </c>
       <c r="K49" s="3">
-        <v>-249240.94</v>
+        <v>-472175.54</v>
       </c>
       <c r="L49" s="3">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="M49" s="3">
-        <v>19303.38</v>
+        <v>29094.57</v>
       </c>
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>2352</v>
+        <v>2894</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>2353</v>
+        <v>2895</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>2354</v>
+        <v>2896</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>2355</v>
+        <v>2897</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>2356</v>
+        <v>2898</v>
       </c>
       <c r="F50" s="3">
-        <v>963790.11</v>
+        <v>954958.72</v>
       </c>
       <c r="G50" s="3">
-        <v>479055.55</v>
+        <v>844607.91</v>
       </c>
       <c r="H50" s="3">
-        <v>254935.65</v>
+        <v>0.0</v>
       </c>
       <c r="I50" s="3">
-        <v>733991.2</v>
+        <v>844607.91</v>
       </c>
       <c r="J50" s="3">
-        <v>76.16</v>
+        <v>88.44</v>
       </c>
       <c r="K50" s="3">
-        <v>-229798.91</v>
+        <v>-110350.81</v>
       </c>
       <c r="L50" s="3">
-        <v>3.89</v>
+        <v>3.64</v>
       </c>
       <c r="M50" s="3">
-        <v>28562.97</v>
+        <v>30735.02</v>
       </c>
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>2357</v>
+        <v>2899</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>2358</v>
+        <v>2900</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>2359</v>
+        <v>2901</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>2360</v>
+        <v>2902</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>2361</v>
+        <v>2903</v>
       </c>
       <c r="F51" s="3">
-        <v>954958.72</v>
+        <v>1154949.94</v>
       </c>
       <c r="G51" s="3">
-        <v>622601.3</v>
+        <v>918689.07</v>
       </c>
       <c r="H51" s="3">
-        <v>157050.0</v>
+        <v>0.0</v>
       </c>
       <c r="I51" s="3">
-        <v>779651.3</v>
+        <v>918689.07</v>
       </c>
       <c r="J51" s="3">
-        <v>81.64</v>
+        <v>79.54</v>
       </c>
       <c r="K51" s="3">
-        <v>-175307.42</v>
+        <v>-236260.87</v>
       </c>
       <c r="L51" s="3">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="M51" s="3">
-        <v>24977.02</v>
+        <v>61575.16</v>
       </c>
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>2362</v>
+        <v>2904</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>2363</v>
+        <v>2905</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>2364</v>
+        <v>2906</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>2365</v>
+        <v>2907</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>2366</v>
+        <v>2908</v>
       </c>
       <c r="F52" s="3">
-        <v>1154949.94</v>
+        <v>963790.11</v>
       </c>
       <c r="G52" s="3">
-        <v>629136.95</v>
+        <v>774813.88</v>
       </c>
       <c r="H52" s="3">
-        <v>234890.5</v>
+        <v>0.0</v>
       </c>
       <c r="I52" s="3">
-        <v>864027.45</v>
+        <v>774813.88</v>
       </c>
       <c r="J52" s="3">
-        <v>74.81</v>
+        <v>80.39</v>
       </c>
       <c r="K52" s="3">
-        <v>-290922.49</v>
+        <v>-188976.23</v>
       </c>
       <c r="L52" s="3">
-        <v>5.92</v>
+        <v>5.08</v>
       </c>
       <c r="M52" s="3">
-        <v>51132.27</v>
+        <v>39336.87</v>
       </c>
     </row>
   </sheetData>
@@ -24281,7 +29159,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -24331,189 +29209,189 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="5" t="s">
-        <v>2367</v>
+        <v>2909</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>2368</v>
+        <v>2910</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>2369</v>
+        <v>2911</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>2370</v>
+        <v>2912</v>
       </c>
       <c r="E2" s="6">
         <v>5936775.24</v>
       </c>
       <c r="F2" s="6">
-        <v>3347104.08</v>
+        <v>4823057.7</v>
       </c>
       <c r="G2" s="6">
-        <v>1648777.66</v>
+        <v>405544.82</v>
       </c>
       <c r="H2" s="6">
-        <v>4995881.74</v>
+        <v>5228602.52</v>
       </c>
       <c r="I2" s="6">
-        <v>84.15</v>
+        <v>88.07</v>
       </c>
       <c r="J2" s="6">
-        <v>-940893.5</v>
+        <v>-708172.72</v>
       </c>
       <c r="K2" s="6">
-        <v>112967.15</v>
+        <v>133388.49</v>
       </c>
       <c r="L2" s="6">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="5" t="s">
-        <v>2371</v>
+        <v>2913</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2372</v>
+        <v>2914</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>2373</v>
+        <v>2915</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>2374</v>
+        <v>2916</v>
       </c>
       <c r="E3" s="6">
         <v>3346888.02</v>
       </c>
       <c r="F3" s="6">
-        <v>1794137.23</v>
+        <v>2197946.73</v>
       </c>
       <c r="G3" s="6">
-        <v>803526.2</v>
+        <v>595560.65</v>
       </c>
       <c r="H3" s="6">
-        <v>2597663.43</v>
+        <v>2793507.38</v>
       </c>
       <c r="I3" s="6">
-        <v>77.61</v>
+        <v>83.47</v>
       </c>
       <c r="J3" s="6">
-        <v>-749224.59</v>
+        <v>-553380.64</v>
       </c>
       <c r="K3" s="6">
-        <v>49248.65</v>
+        <v>67347.72</v>
       </c>
       <c r="L3" s="6">
-        <v>1.9</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="5" t="s">
-        <v>2375</v>
+        <v>2917</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>2376</v>
+        <v>2918</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2377</v>
+        <v>2919</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>2378</v>
+        <v>2920</v>
       </c>
       <c r="E4" s="6">
         <v>6248074.42</v>
       </c>
       <c r="F4" s="6">
-        <v>3176533.61</v>
+        <v>4548712.75</v>
       </c>
       <c r="G4" s="6">
-        <v>1367839.15</v>
+        <v>311833.87</v>
       </c>
       <c r="H4" s="6">
-        <v>4544372.76</v>
+        <v>4860546.62</v>
       </c>
       <c r="I4" s="6">
-        <v>72.73</v>
+        <v>77.79</v>
       </c>
       <c r="J4" s="6">
-        <v>-1703701.66</v>
+        <v>-1387527.8</v>
       </c>
       <c r="K4" s="6">
-        <v>172683.18</v>
+        <v>185241.51</v>
       </c>
       <c r="L4" s="6">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="5" t="s">
-        <v>2379</v>
+        <v>2921</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>2380</v>
+        <v>2922</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>2381</v>
+        <v>2923</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>2382</v>
+        <v>2924</v>
       </c>
       <c r="E5" s="6">
         <v>7225829.17</v>
       </c>
       <c r="F5" s="6">
-        <v>5217806.5</v>
+        <v>6345405.77</v>
       </c>
       <c r="G5" s="6">
-        <v>1042517.18</v>
+        <v>381577.67</v>
       </c>
       <c r="H5" s="6">
-        <v>6260323.68</v>
+        <v>6726983.44</v>
       </c>
       <c r="I5" s="6">
-        <v>86.64</v>
+        <v>93.1</v>
       </c>
       <c r="J5" s="6">
-        <v>-965505.49</v>
+        <v>-498845.73</v>
       </c>
       <c r="K5" s="6">
-        <v>169197.61</v>
+        <v>173677.73</v>
       </c>
       <c r="L5" s="6">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="5" t="s">
-        <v>2383</v>
+        <v>2925</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>2384</v>
+        <v>2926</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>2385</v>
+        <v>2927</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>2386</v>
+        <v>2928</v>
       </c>
       <c r="E6" s="6">
         <v>6938999.79</v>
       </c>
       <c r="F6" s="6">
-        <v>4686003.05</v>
+        <v>6114889.65</v>
       </c>
       <c r="G6" s="6">
-        <v>1136332.19</v>
+        <v>380058.19</v>
       </c>
       <c r="H6" s="6">
-        <v>5822335.24</v>
+        <v>6494947.84</v>
       </c>
       <c r="I6" s="6">
-        <v>83.91</v>
+        <v>93.6</v>
       </c>
       <c r="J6" s="6">
-        <v>-1116664.55</v>
+        <v>-444051.95</v>
       </c>
       <c r="K6" s="6">
-        <v>192956.56</v>
+        <v>214719.73</v>
       </c>
       <c r="L6" s="6">
         <v>3.31</v>
@@ -24521,116 +29399,116 @@
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="5" t="s">
-        <v>2387</v>
+        <v>2929</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2388</v>
+        <v>2930</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>2389</v>
+        <v>2931</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2390</v>
+        <v>2932</v>
       </c>
       <c r="E7" s="6">
         <v>4536967.52</v>
       </c>
       <c r="F7" s="6">
-        <v>2795646.15</v>
+        <v>3932458.4</v>
       </c>
       <c r="G7" s="6">
-        <v>1102654.73</v>
+        <v>263529.54</v>
       </c>
       <c r="H7" s="6">
-        <v>3898300.88</v>
+        <v>4195987.94</v>
       </c>
       <c r="I7" s="6">
-        <v>85.92</v>
+        <v>92.48</v>
       </c>
       <c r="J7" s="6">
-        <v>-638666.64</v>
+        <v>-340979.58</v>
       </c>
       <c r="K7" s="6">
-        <v>110758.19</v>
+        <v>115362.22</v>
       </c>
       <c r="L7" s="6">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="5" t="s">
-        <v>2391</v>
+        <v>2933</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>2392</v>
+        <v>2934</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>2393</v>
+        <v>2935</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>2394</v>
+        <v>2936</v>
       </c>
       <c r="E8" s="6">
         <v>7177495.92</v>
       </c>
       <c r="F8" s="6">
-        <v>4969321.98</v>
+        <v>5883718.63</v>
       </c>
       <c r="G8" s="6">
-        <v>816275.8</v>
+        <v>461194.15</v>
       </c>
       <c r="H8" s="6">
-        <v>5785597.78</v>
+        <v>6344912.78</v>
       </c>
       <c r="I8" s="6">
-        <v>80.61</v>
+        <v>88.4</v>
       </c>
       <c r="J8" s="6">
-        <v>-1391898.14</v>
+        <v>-832583.14</v>
       </c>
       <c r="K8" s="6">
-        <v>128044.99</v>
+        <v>141392.61</v>
       </c>
       <c r="L8" s="6">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="5" t="s">
-        <v>2395</v>
+        <v>2937</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>2396</v>
+        <v>2938</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>2397</v>
+        <v>2939</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>2398</v>
+        <v>2940</v>
       </c>
       <c r="E9" s="6">
         <v>6405049.98</v>
       </c>
       <c r="F9" s="6">
-        <v>3125217.98</v>
+        <v>4824496.86</v>
       </c>
       <c r="G9" s="6">
-        <v>1406125.71</v>
+        <v>0.0</v>
       </c>
       <c r="H9" s="6">
-        <v>4531343.69</v>
+        <v>4824496.86</v>
       </c>
       <c r="I9" s="6">
-        <v>70.75</v>
+        <v>75.32</v>
       </c>
       <c r="J9" s="6">
-        <v>-1873706.29</v>
+        <v>-1580553.12</v>
       </c>
       <c r="K9" s="6">
-        <v>170448.89</v>
+        <v>205520.18</v>
       </c>
       <c r="L9" s="6">
-        <v>3.76</v>
+        <v>4.26</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2941" count="2941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3228" count="3228">
   <si>
     <t>Region</t>
   </si>
@@ -25912,6 +25912,2589 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
     </r>
   </si>
   <si>
@@ -26616,7 +29199,7 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -26626,10 +29209,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -26685,20 +29264,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26706,6 +29276,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -27002,7 +29575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AB52"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -27063,81 +29636,81 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>2654</v>
+        <v>2941</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2655</v>
+        <v>2942</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2656</v>
+        <v>2943</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2657</v>
+        <v>2944</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2658</v>
+        <v>2945</v>
       </c>
       <c r="F2" s="3">
-        <v>745422.79</v>
+        <v>747825.09</v>
       </c>
       <c r="G2" s="3">
-        <v>525292.5</v>
+        <v>655581.7</v>
       </c>
       <c r="H2" s="3">
-        <v>77428.21</v>
+        <v>41704.79</v>
       </c>
       <c r="I2" s="3">
-        <v>602720.71</v>
+        <v>697286.49</v>
       </c>
       <c r="J2" s="3">
-        <v>80.86</v>
+        <v>93.24</v>
       </c>
       <c r="K2" s="3">
-        <v>-142702.08</v>
+        <v>-50538.6</v>
       </c>
       <c r="L2" s="3">
-        <v>3.99</v>
+        <v>2.64</v>
       </c>
       <c r="M2" s="3">
-        <v>24070.05</v>
+        <v>18391.79</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>2659</v>
+        <v>2946</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2660</v>
+        <v>2947</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2661</v>
+        <v>2948</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>2662</v>
+        <v>2949</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2663</v>
+        <v>2950</v>
       </c>
       <c r="F3" s="3">
         <v>755003.49</v>
       </c>
       <c r="G3" s="3">
-        <v>612234.58</v>
+        <v>683410.87</v>
       </c>
       <c r="H3" s="3">
-        <v>83037.21</v>
+        <v>31596.01</v>
       </c>
       <c r="I3" s="3">
-        <v>695271.79</v>
+        <v>715006.88</v>
       </c>
       <c r="J3" s="3">
-        <v>92.09</v>
+        <v>94.7</v>
       </c>
       <c r="K3" s="3">
-        <v>-59731.7</v>
+        <v>-39996.61</v>
       </c>
       <c r="L3" s="3">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="M3" s="3">
         <v>13029.03</v>
@@ -27145,122 +29718,122 @@
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2664</v>
+        <v>2951</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2665</v>
+        <v>2952</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2666</v>
+        <v>2953</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>2667</v>
+        <v>2954</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2668</v>
+        <v>2955</v>
       </c>
       <c r="F4" s="3">
         <v>664724.91</v>
       </c>
       <c r="G4" s="3">
-        <v>636483.74</v>
+        <v>674116.41</v>
       </c>
       <c r="H4" s="3">
-        <v>49765.59</v>
+        <v>38629.41</v>
       </c>
       <c r="I4" s="3">
-        <v>686249.33</v>
+        <v>712745.82</v>
       </c>
       <c r="J4" s="3">
-        <v>103.24</v>
+        <v>107.22</v>
       </c>
       <c r="K4" s="3">
-        <v>21524.42</v>
+        <v>48020.91</v>
       </c>
       <c r="L4" s="3">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="M4" s="3">
-        <v>19084.44</v>
+        <v>20002.44</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>2669</v>
+        <v>2956</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2670</v>
+        <v>2957</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2671</v>
+        <v>2958</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>2672</v>
+        <v>2959</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>2673</v>
+        <v>2960</v>
       </c>
       <c r="F5" s="3">
-        <v>747825.09</v>
+        <v>745422.79</v>
       </c>
       <c r="G5" s="3">
-        <v>561580.58</v>
+        <v>591356.73</v>
       </c>
       <c r="H5" s="3">
-        <v>117224.63</v>
+        <v>39555.92</v>
       </c>
       <c r="I5" s="3">
-        <v>678805.21</v>
+        <v>630912.65</v>
       </c>
       <c r="J5" s="3">
-        <v>90.77</v>
+        <v>84.64</v>
       </c>
       <c r="K5" s="3">
-        <v>-69019.88</v>
+        <v>-114510.14</v>
       </c>
       <c r="L5" s="3">
-        <v>2.71</v>
+        <v>4.15</v>
       </c>
       <c r="M5" s="3">
-        <v>18391.79</v>
+        <v>26206.95</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>2674</v>
+        <v>2961</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2675</v>
+        <v>2962</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2676</v>
+        <v>2963</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>2677</v>
+        <v>2964</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>2678</v>
+        <v>2965</v>
       </c>
       <c r="F6" s="3">
         <v>750633.4</v>
       </c>
       <c r="G6" s="3">
-        <v>798046.78</v>
+        <v>805478.98</v>
       </c>
       <c r="H6" s="3">
-        <v>28424.91</v>
+        <v>42450.95</v>
       </c>
       <c r="I6" s="3">
-        <v>826471.69</v>
+        <v>847929.93</v>
       </c>
       <c r="J6" s="3">
-        <v>110.1</v>
+        <v>112.96</v>
       </c>
       <c r="K6" s="3">
-        <v>75838.29</v>
+        <v>97296.53</v>
       </c>
       <c r="L6" s="3">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="M6" s="3">
         <v>21639.95</v>
@@ -27268,40 +29841,40 @@
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>2679</v>
+        <v>2966</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2680</v>
+        <v>2967</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>2681</v>
+        <v>2968</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>2682</v>
+        <v>2969</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>2683</v>
+        <v>2970</v>
       </c>
       <c r="F7" s="3">
         <v>804591.82</v>
       </c>
       <c r="G7" s="3">
-        <v>568343.09</v>
+        <v>577215.0</v>
       </c>
       <c r="H7" s="3">
-        <v>17270.56</v>
+        <v>30075.2</v>
       </c>
       <c r="I7" s="3">
-        <v>585613.65</v>
+        <v>607290.2</v>
       </c>
       <c r="J7" s="3">
-        <v>72.78</v>
+        <v>75.48</v>
       </c>
       <c r="K7" s="3">
-        <v>-218978.17</v>
+        <v>-197301.62</v>
       </c>
       <c r="L7" s="3">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="M7" s="3">
         <v>14980.55</v>
@@ -27309,122 +29882,122 @@
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>2684</v>
+        <v>2971</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>2685</v>
+        <v>2972</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2686</v>
+        <v>2973</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>2687</v>
+        <v>2974</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>2688</v>
+        <v>2975</v>
       </c>
       <c r="F8" s="3">
-        <v>741741.03</v>
+        <v>726832.71</v>
       </c>
       <c r="G8" s="3">
-        <v>637343.82</v>
+        <v>488727.0</v>
       </c>
       <c r="H8" s="3">
-        <v>22881.83</v>
+        <v>18342.48</v>
       </c>
       <c r="I8" s="3">
-        <v>660225.65</v>
+        <v>507069.48</v>
       </c>
       <c r="J8" s="3">
-        <v>89.01</v>
+        <v>69.76</v>
       </c>
       <c r="K8" s="3">
-        <v>-81515.38</v>
+        <v>-219763.23</v>
       </c>
       <c r="L8" s="3">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="M8" s="3">
-        <v>17292.99</v>
+        <v>5237.7</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>2689</v>
+        <v>2976</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>2690</v>
+        <v>2977</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2691</v>
+        <v>2978</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>2692</v>
+        <v>2979</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>2693</v>
+        <v>2980</v>
       </c>
       <c r="F9" s="3">
-        <v>726832.71</v>
+        <v>741741.03</v>
       </c>
       <c r="G9" s="3">
-        <v>483732.62</v>
+        <v>644342.27</v>
       </c>
       <c r="H9" s="3">
-        <v>9511.88</v>
+        <v>35734.57</v>
       </c>
       <c r="I9" s="3">
-        <v>493244.5</v>
+        <v>680076.84</v>
       </c>
       <c r="J9" s="3">
-        <v>67.86</v>
+        <v>91.69</v>
       </c>
       <c r="K9" s="3">
-        <v>-233588.21</v>
+        <v>-61664.19</v>
       </c>
       <c r="L9" s="3">
-        <v>0.99</v>
+        <v>2.54</v>
       </c>
       <c r="M9" s="3">
-        <v>4899.7</v>
+        <v>17292.99</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>2694</v>
+        <v>2981</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>2695</v>
+        <v>2982</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2696</v>
+        <v>2983</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>2697</v>
+        <v>2984</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>2698</v>
+        <v>2985</v>
       </c>
       <c r="F10" s="3">
         <v>859984.15</v>
       </c>
       <c r="G10" s="3">
-        <v>600319.26</v>
+        <v>752750.75</v>
       </c>
       <c r="H10" s="3">
-        <v>167479.95</v>
+        <v>34504.71</v>
       </c>
       <c r="I10" s="3">
-        <v>767799.21</v>
+        <v>787255.46</v>
       </c>
       <c r="J10" s="3">
-        <v>89.28</v>
+        <v>91.54</v>
       </c>
       <c r="K10" s="3">
-        <v>-92184.94</v>
+        <v>-72728.69</v>
       </c>
       <c r="L10" s="3">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="M10" s="3">
         <v>21910.4</v>
@@ -27432,81 +30005,81 @@
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>2699</v>
+        <v>2986</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>2700</v>
+        <v>2987</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2701</v>
+        <v>2988</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>2702</v>
+        <v>2989</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>2703</v>
+        <v>2990</v>
       </c>
       <c r="F11" s="3">
         <v>903047.31</v>
       </c>
       <c r="G11" s="3">
-        <v>487455.39</v>
+        <v>614366.64</v>
       </c>
       <c r="H11" s="3">
-        <v>133850.1</v>
+        <v>23187.51</v>
       </c>
       <c r="I11" s="3">
-        <v>621305.49</v>
+        <v>637554.15</v>
       </c>
       <c r="J11" s="3">
-        <v>68.8</v>
+        <v>70.6</v>
       </c>
       <c r="K11" s="3">
-        <v>-281741.82</v>
+        <v>-265493.16</v>
       </c>
       <c r="L11" s="3">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="M11" s="3">
-        <v>19545.35</v>
+        <v>20669.75</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>2704</v>
+        <v>2991</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>2705</v>
+        <v>2992</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>2706</v>
+        <v>2993</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>2707</v>
+        <v>2994</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>2708</v>
+        <v>2995</v>
       </c>
       <c r="F12" s="3">
         <v>775221.33</v>
       </c>
       <c r="G12" s="3">
-        <v>557189.82</v>
+        <v>683686.72</v>
       </c>
       <c r="H12" s="3">
-        <v>142022.02</v>
+        <v>38581.92</v>
       </c>
       <c r="I12" s="3">
-        <v>699211.84</v>
+        <v>722268.64</v>
       </c>
       <c r="J12" s="3">
-        <v>90.2</v>
+        <v>93.17</v>
       </c>
       <c r="K12" s="3">
-        <v>-76009.49</v>
+        <v>-52952.69</v>
       </c>
       <c r="L12" s="3">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="M12" s="3">
         <v>10391.92</v>
@@ -27514,40 +30087,40 @@
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>2709</v>
+        <v>2996</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2710</v>
+        <v>2997</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2711</v>
+        <v>2998</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>2712</v>
+        <v>2999</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>2713</v>
+        <v>3000</v>
       </c>
       <c r="F13" s="3">
         <v>808635.23</v>
       </c>
       <c r="G13" s="3">
-        <v>552982.26</v>
+        <v>695145.3</v>
       </c>
       <c r="H13" s="3">
-        <v>152208.58</v>
+        <v>26970.53</v>
       </c>
       <c r="I13" s="3">
-        <v>705190.84</v>
+        <v>722115.83</v>
       </c>
       <c r="J13" s="3">
-        <v>87.21</v>
+        <v>89.3</v>
       </c>
       <c r="K13" s="3">
-        <v>-103444.39</v>
+        <v>-86519.4</v>
       </c>
       <c r="L13" s="3">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M13" s="3">
         <v>15500.04</v>
@@ -27555,798 +30128,798 @@
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>2714</v>
+        <v>3001</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>2715</v>
+        <v>3002</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>2716</v>
+        <v>3003</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>2717</v>
+        <v>3004</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>2718</v>
+        <v>3005</v>
       </c>
       <c r="F14" s="3">
         <v>773239.07</v>
       </c>
       <c r="G14" s="3">
-        <v>655574.49</v>
+        <v>666364.32</v>
       </c>
       <c r="H14" s="3">
-        <v>22797.12</v>
+        <v>44180.95</v>
       </c>
       <c r="I14" s="3">
-        <v>678371.61</v>
+        <v>710545.27</v>
       </c>
       <c r="J14" s="3">
-        <v>87.73</v>
+        <v>91.89</v>
       </c>
       <c r="K14" s="3">
-        <v>-94867.46</v>
+        <v>-62693.8</v>
       </c>
       <c r="L14" s="3">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="M14" s="3">
-        <v>10788.94</v>
+        <v>11696.14</v>
       </c>
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>2719</v>
+        <v>3006</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>2720</v>
+        <v>3007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>2721</v>
+        <v>3008</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>2722</v>
+        <v>3009</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>2723</v>
+        <v>3010</v>
       </c>
       <c r="F15" s="3">
         <v>788718.67</v>
       </c>
       <c r="G15" s="3">
-        <v>528483.58</v>
+        <v>539242.33</v>
       </c>
       <c r="H15" s="3">
-        <v>14811.11</v>
+        <v>18838.33</v>
       </c>
       <c r="I15" s="3">
-        <v>543294.69</v>
+        <v>558080.66</v>
       </c>
       <c r="J15" s="3">
-        <v>68.88</v>
+        <v>70.76</v>
       </c>
       <c r="K15" s="3">
-        <v>-245423.98</v>
+        <v>-230638.01</v>
       </c>
       <c r="L15" s="3">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="M15" s="3">
-        <v>13572.04</v>
+        <v>13872.04</v>
       </c>
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>2724</v>
+        <v>3011</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>2725</v>
+        <v>3012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>2726</v>
+        <v>3013</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>2727</v>
+        <v>3014</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>2728</v>
+        <v>3015</v>
       </c>
       <c r="F16" s="3">
         <v>757031.95</v>
       </c>
       <c r="G16" s="3">
-        <v>385369.53</v>
+        <v>390950.89</v>
       </c>
       <c r="H16" s="3">
-        <v>8113.29</v>
+        <v>16655.99</v>
       </c>
       <c r="I16" s="3">
-        <v>393482.82</v>
+        <v>407606.88</v>
       </c>
       <c r="J16" s="3">
-        <v>51.98</v>
+        <v>53.84</v>
       </c>
       <c r="K16" s="3">
-        <v>-363549.13</v>
+        <v>-349425.07</v>
       </c>
       <c r="L16" s="3">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M16" s="3">
-        <v>6163.66</v>
+        <v>6500.98</v>
       </c>
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>2729</v>
+        <v>3016</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>2730</v>
+        <v>3017</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2731</v>
+        <v>3018</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>2732</v>
+        <v>3019</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>2733</v>
+        <v>3020</v>
       </c>
       <c r="F17" s="3">
         <v>792097.85</v>
       </c>
       <c r="G17" s="3">
-        <v>499203.64</v>
+        <v>504088.82</v>
       </c>
       <c r="H17" s="3">
-        <v>7492.55</v>
+        <v>21971.51</v>
       </c>
       <c r="I17" s="3">
-        <v>506696.19</v>
+        <v>526060.33</v>
       </c>
       <c r="J17" s="3">
-        <v>63.97</v>
+        <v>66.41</v>
       </c>
       <c r="K17" s="3">
-        <v>-285401.66</v>
+        <v>-266037.52</v>
       </c>
       <c r="L17" s="3">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="M17" s="3">
-        <v>14489.96</v>
+        <v>14827.46</v>
       </c>
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>2734</v>
+        <v>3021</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>2735</v>
+        <v>3022</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2736</v>
+        <v>3023</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>2737</v>
+        <v>3024</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>2738</v>
+        <v>3025</v>
       </c>
       <c r="F18" s="3">
         <v>1027095.81</v>
       </c>
       <c r="G18" s="3">
-        <v>799165.91</v>
+        <v>850624.05</v>
       </c>
       <c r="H18" s="3">
-        <v>88810.95</v>
+        <v>33466.66</v>
       </c>
       <c r="I18" s="3">
-        <v>887976.86</v>
+        <v>884090.71</v>
       </c>
       <c r="J18" s="3">
-        <v>86.46</v>
+        <v>86.08</v>
       </c>
       <c r="K18" s="3">
-        <v>-139118.95</v>
+        <v>-143005.1</v>
       </c>
       <c r="L18" s="3">
-        <v>5.54</v>
+        <v>6.0</v>
       </c>
       <c r="M18" s="3">
-        <v>49187.79</v>
+        <v>53073.94</v>
       </c>
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>2739</v>
+        <v>3026</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>2740</v>
+        <v>3027</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>2741</v>
+        <v>3028</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>2742</v>
+        <v>3029</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>2743</v>
+        <v>3030</v>
       </c>
       <c r="F19" s="3">
-        <v>1246040.32</v>
+        <v>863850.75</v>
       </c>
       <c r="G19" s="3">
-        <v>884510.57</v>
+        <v>821602.18</v>
       </c>
       <c r="H19" s="3">
-        <v>94593.21</v>
+        <v>49430.99</v>
       </c>
       <c r="I19" s="3">
-        <v>979103.78</v>
+        <v>871033.17</v>
       </c>
       <c r="J19" s="3">
-        <v>78.58</v>
+        <v>100.83</v>
       </c>
       <c r="K19" s="3">
-        <v>-266936.54</v>
+        <v>7182.42</v>
       </c>
       <c r="L19" s="3">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="M19" s="3">
-        <v>49494.63</v>
+        <v>42132.0</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>2744</v>
+        <v>3031</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>2745</v>
+        <v>3032</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>2746</v>
+        <v>3033</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>2747</v>
+        <v>3034</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>2748</v>
+        <v>3035</v>
       </c>
       <c r="F20" s="3">
-        <v>863850.75</v>
+        <v>1246040.32</v>
       </c>
       <c r="G20" s="3">
-        <v>796405.03</v>
+        <v>933140.79</v>
       </c>
       <c r="H20" s="3">
-        <v>75215.64</v>
+        <v>45213.39</v>
       </c>
       <c r="I20" s="3">
-        <v>871620.67</v>
+        <v>978354.18</v>
       </c>
       <c r="J20" s="3">
-        <v>100.9</v>
+        <v>78.52</v>
       </c>
       <c r="K20" s="3">
-        <v>7769.92</v>
+        <v>-267686.14</v>
       </c>
       <c r="L20" s="3">
-        <v>4.77</v>
+        <v>5.14</v>
       </c>
       <c r="M20" s="3">
-        <v>41544.5</v>
+        <v>50244.23</v>
       </c>
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>2749</v>
+        <v>3036</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>2750</v>
+        <v>3037</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>2751</v>
+        <v>3038</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>2752</v>
+        <v>3039</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>2753</v>
+        <v>3040</v>
       </c>
       <c r="F21" s="3">
         <v>875303.02</v>
       </c>
       <c r="G21" s="3">
-        <v>814370.32</v>
+        <v>841202.64</v>
       </c>
       <c r="H21" s="3">
-        <v>49461.77</v>
+        <v>68524.25</v>
       </c>
       <c r="I21" s="3">
-        <v>863832.09</v>
+        <v>909726.89</v>
       </c>
       <c r="J21" s="3">
-        <v>98.69</v>
+        <v>103.93</v>
       </c>
       <c r="K21" s="3">
-        <v>-11470.93</v>
+        <v>34423.87</v>
       </c>
       <c r="L21" s="3">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="M21" s="3">
-        <v>18933.99</v>
+        <v>19654.59</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>2754</v>
+        <v>3041</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>2755</v>
+        <v>3042</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>2756</v>
+        <v>3043</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>2757</v>
+        <v>3044</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>2758</v>
+        <v>3045</v>
       </c>
       <c r="F22" s="3">
         <v>859661.34</v>
       </c>
       <c r="G22" s="3">
-        <v>839949.34</v>
+        <v>901965.23</v>
       </c>
       <c r="H22" s="3">
-        <v>88657.54</v>
+        <v>45759.58</v>
       </c>
       <c r="I22" s="3">
-        <v>928606.88</v>
+        <v>947724.81</v>
       </c>
       <c r="J22" s="3">
-        <v>108.02</v>
+        <v>110.24</v>
       </c>
       <c r="K22" s="3">
-        <v>68945.54</v>
+        <v>88063.47</v>
       </c>
       <c r="L22" s="3">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="M22" s="3">
-        <v>27636.44</v>
+        <v>28130.12</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>2759</v>
+        <v>3046</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>2760</v>
+        <v>3047</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>2761</v>
+        <v>3048</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>2762</v>
+        <v>3049</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>2763</v>
+        <v>3050</v>
       </c>
       <c r="F23" s="3">
         <v>867257.37</v>
       </c>
       <c r="G23" s="3">
-        <v>945748.57</v>
+        <v>985570.39</v>
       </c>
       <c r="H23" s="3">
-        <v>74261.75</v>
+        <v>69440.81</v>
       </c>
       <c r="I23" s="3">
-        <v>1020010.32</v>
+        <v>1055011.2</v>
       </c>
       <c r="J23" s="3">
-        <v>117.61</v>
+        <v>121.65</v>
       </c>
       <c r="K23" s="3">
-        <v>152752.95</v>
+        <v>187753.83</v>
       </c>
       <c r="L23" s="3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="M23" s="3">
-        <v>17252.74</v>
+        <v>17612.59</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>2764</v>
+        <v>3051</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>2765</v>
+        <v>3052</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>2766</v>
+        <v>3053</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>2767</v>
+        <v>3054</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>2768</v>
+        <v>3055</v>
       </c>
       <c r="F24" s="3">
         <v>778641.12</v>
       </c>
       <c r="G24" s="3">
-        <v>745963.94</v>
+        <v>781097.23</v>
       </c>
       <c r="H24" s="3">
-        <v>56782.59</v>
+        <v>96024.32</v>
       </c>
       <c r="I24" s="3">
-        <v>802746.53</v>
+        <v>877121.55</v>
       </c>
       <c r="J24" s="3">
-        <v>103.1</v>
+        <v>112.65</v>
       </c>
       <c r="K24" s="3">
-        <v>24105.41</v>
+        <v>98480.43</v>
       </c>
       <c r="L24" s="3">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="M24" s="3">
-        <v>23266.35</v>
+        <v>23809.95</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>2769</v>
+        <v>3056</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>2770</v>
+        <v>3057</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>2771</v>
+        <v>3058</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>2772</v>
+        <v>3059</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>2773</v>
+        <v>3060</v>
       </c>
       <c r="F25" s="3">
         <v>979868.9</v>
       </c>
       <c r="G25" s="3">
-        <v>836212.36</v>
+        <v>844110.19</v>
       </c>
       <c r="H25" s="3">
-        <v>25581.03</v>
+        <v>47149.72</v>
       </c>
       <c r="I25" s="3">
-        <v>861793.39</v>
+        <v>891259.91</v>
       </c>
       <c r="J25" s="3">
-        <v>87.95</v>
+        <v>90.96</v>
       </c>
       <c r="K25" s="3">
-        <v>-118075.51</v>
+        <v>-88608.99</v>
       </c>
       <c r="L25" s="3">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="M25" s="3">
-        <v>17002.12</v>
+        <v>19044.38</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>2774</v>
+        <v>3061</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>2775</v>
+        <v>3062</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>2776</v>
+        <v>3063</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>2777</v>
+        <v>3064</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>2778</v>
+        <v>3065</v>
       </c>
       <c r="F26" s="3">
         <v>1011213.65</v>
       </c>
       <c r="G26" s="3">
-        <v>632796.21</v>
+        <v>643661.88</v>
       </c>
       <c r="H26" s="3">
-        <v>25600.35</v>
+        <v>38011.06</v>
       </c>
       <c r="I26" s="3">
-        <v>658396.56</v>
+        <v>681672.94</v>
       </c>
       <c r="J26" s="3">
-        <v>65.11</v>
+        <v>67.41</v>
       </c>
       <c r="K26" s="3">
-        <v>-352817.09</v>
+        <v>-329540.71</v>
       </c>
       <c r="L26" s="3">
-        <v>4.65</v>
+        <v>4.53</v>
       </c>
       <c r="M26" s="3">
-        <v>30598.03</v>
+        <v>30913.03</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>2779</v>
+        <v>3066</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>2780</v>
+        <v>3067</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>2781</v>
+        <v>3068</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>2782</v>
+        <v>3069</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>2783</v>
+        <v>3070</v>
       </c>
       <c r="F27" s="3">
         <v>905279.17</v>
       </c>
       <c r="G27" s="3">
-        <v>801848.44</v>
+        <v>806536.45</v>
       </c>
       <c r="H27" s="3">
-        <v>37848.41</v>
+        <v>57277.0</v>
       </c>
       <c r="I27" s="3">
-        <v>839696.85</v>
+        <v>863813.45</v>
       </c>
       <c r="J27" s="3">
-        <v>92.76</v>
+        <v>95.42</v>
       </c>
       <c r="K27" s="3">
-        <v>-65582.32</v>
+        <v>-41465.72</v>
       </c>
       <c r="L27" s="3">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="M27" s="3">
-        <v>20970.26</v>
+        <v>21675.14</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>2784</v>
+        <v>3071</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>2785</v>
+        <v>3072</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>2786</v>
+        <v>3073</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>2787</v>
+        <v>3074</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>2788</v>
+        <v>3075</v>
       </c>
       <c r="F28" s="3">
         <v>948604.6</v>
       </c>
       <c r="G28" s="3">
-        <v>728516.6</v>
+        <v>737187.19</v>
       </c>
       <c r="H28" s="3">
-        <v>23384.23</v>
+        <v>30832.94</v>
       </c>
       <c r="I28" s="3">
-        <v>751900.83</v>
+        <v>768020.13</v>
       </c>
       <c r="J28" s="3">
-        <v>79.26</v>
+        <v>80.96</v>
       </c>
       <c r="K28" s="3">
-        <v>-196703.77</v>
+        <v>-180584.47</v>
       </c>
       <c r="L28" s="3">
         <v>2.4</v>
       </c>
       <c r="M28" s="3">
-        <v>18017.81</v>
+        <v>18468.25</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>2789</v>
+        <v>3076</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>2790</v>
+        <v>3077</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>2791</v>
+        <v>3078</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>2792</v>
+        <v>3079</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>2793</v>
+        <v>3080</v>
       </c>
       <c r="F29" s="3">
         <v>824118.89</v>
       </c>
       <c r="G29" s="3">
-        <v>707538.01</v>
+        <v>723438.06</v>
       </c>
       <c r="H29" s="3">
-        <v>54751.85</v>
+        <v>55586.45</v>
       </c>
       <c r="I29" s="3">
-        <v>762289.86</v>
+        <v>779024.51</v>
       </c>
       <c r="J29" s="3">
-        <v>92.5</v>
+        <v>94.53</v>
       </c>
       <c r="K29" s="3">
-        <v>-61829.03</v>
+        <v>-45094.38</v>
       </c>
       <c r="L29" s="3">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="M29" s="3">
-        <v>23444.98</v>
+        <v>25657.71</v>
       </c>
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>2794</v>
+        <v>3081</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>2795</v>
+        <v>3082</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>2796</v>
+        <v>3083</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>2797</v>
+        <v>3084</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>2798</v>
+        <v>3085</v>
       </c>
       <c r="F30" s="3">
         <v>877850.52</v>
       </c>
       <c r="G30" s="3">
-        <v>964322.22</v>
+        <v>991324.46</v>
       </c>
       <c r="H30" s="3">
-        <v>55991.22</v>
+        <v>55837.2</v>
       </c>
       <c r="I30" s="3">
-        <v>1020313.44</v>
+        <v>1047161.66</v>
       </c>
       <c r="J30" s="3">
-        <v>116.23</v>
+        <v>119.29</v>
       </c>
       <c r="K30" s="3">
-        <v>142462.92</v>
+        <v>169311.14</v>
       </c>
       <c r="L30" s="3">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="M30" s="3">
-        <v>22787.64</v>
+        <v>25087.58</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>2799</v>
+        <v>3086</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>2800</v>
+        <v>3087</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>2801</v>
+        <v>3088</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>2802</v>
+        <v>3089</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>2803</v>
+        <v>3090</v>
       </c>
       <c r="F31" s="3">
         <v>990466.72</v>
       </c>
       <c r="G31" s="3">
-        <v>885177.18</v>
+        <v>909348.03</v>
       </c>
       <c r="H31" s="3">
-        <v>46576.06</v>
+        <v>49477.69</v>
       </c>
       <c r="I31" s="3">
-        <v>931753.24</v>
+        <v>958825.72</v>
       </c>
       <c r="J31" s="3">
-        <v>94.07</v>
+        <v>96.81</v>
       </c>
       <c r="K31" s="3">
-        <v>-58713.48</v>
+        <v>-31641.0</v>
       </c>
       <c r="L31" s="3">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="M31" s="3">
-        <v>39114.52</v>
+        <v>40927.52</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>2804</v>
+        <v>3091</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>2805</v>
+        <v>3092</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>2806</v>
+        <v>3093</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>2807</v>
+        <v>3094</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>2808</v>
+        <v>3095</v>
       </c>
       <c r="F32" s="3">
         <v>892245.98</v>
       </c>
       <c r="G32" s="3">
-        <v>767978.5</v>
+        <v>788431.63</v>
       </c>
       <c r="H32" s="3">
-        <v>45543.1</v>
+        <v>42221.1</v>
       </c>
       <c r="I32" s="3">
-        <v>813521.6</v>
+        <v>830652.73</v>
       </c>
       <c r="J32" s="3">
-        <v>91.18</v>
+        <v>93.1</v>
       </c>
       <c r="K32" s="3">
-        <v>-78724.38</v>
+        <v>-61593.25</v>
       </c>
       <c r="L32" s="3">
-        <v>3.61</v>
+        <v>4.0</v>
       </c>
       <c r="M32" s="3">
-        <v>29366.2</v>
+        <v>33240.16</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>2809</v>
+        <v>3096</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>2810</v>
+        <v>3097</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>2811</v>
+        <v>3098</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>2812</v>
+        <v>3099</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>2813</v>
+        <v>3100</v>
       </c>
       <c r="F33" s="3">
         <v>1265248.83</v>
@@ -28375,19 +30948,19 @@
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>2814</v>
+        <v>3101</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2815</v>
+        <v>3102</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>2816</v>
+        <v>3103</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>2817</v>
+        <v>3104</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>2818</v>
+        <v>3105</v>
       </c>
       <c r="F34" s="3">
         <v>1062018.28</v>
@@ -28416,19 +30989,19 @@
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>2819</v>
+        <v>3106</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2820</v>
+        <v>3107</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>2821</v>
+        <v>3108</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>2822</v>
+        <v>3109</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>2823</v>
+        <v>3110</v>
       </c>
       <c r="F35" s="3">
         <v>1027050.57</v>
@@ -28457,19 +31030,19 @@
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>2824</v>
+        <v>3111</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>2825</v>
+        <v>3112</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>2826</v>
+        <v>3113</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>2827</v>
+        <v>3114</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>2828</v>
+        <v>3115</v>
       </c>
       <c r="F36" s="3">
         <v>1150571.33</v>
@@ -28498,142 +31071,142 @@
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>2829</v>
+        <v>3116</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2830</v>
+        <v>3117</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>2831</v>
+        <v>3118</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>2832</v>
+        <v>3119</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>2833</v>
+        <v>3120</v>
       </c>
       <c r="F37" s="3">
-        <v>904558.95</v>
+        <v>1374896.6</v>
       </c>
       <c r="G37" s="3">
-        <v>863685.14</v>
+        <v>1108340.03</v>
       </c>
       <c r="H37" s="3">
-        <v>43154.47</v>
+        <v>93670.91</v>
       </c>
       <c r="I37" s="3">
-        <v>906839.61</v>
+        <v>1202010.94</v>
       </c>
       <c r="J37" s="3">
-        <v>100.25</v>
+        <v>87.43</v>
       </c>
       <c r="K37" s="3">
-        <v>2280.66</v>
+        <v>-172885.66</v>
       </c>
       <c r="L37" s="3">
-        <v>2.45</v>
+        <v>3.13</v>
       </c>
       <c r="M37" s="3">
-        <v>22258.61</v>
+        <v>37639.5</v>
       </c>
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>2834</v>
+        <v>3121</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2835</v>
+        <v>3122</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>2836</v>
+        <v>3123</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>2837</v>
+        <v>3124</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>2838</v>
+        <v>3125</v>
       </c>
       <c r="F38" s="3">
-        <v>1106940.64</v>
+        <v>904558.95</v>
       </c>
       <c r="G38" s="3">
-        <v>797158.58</v>
+        <v>863685.14</v>
       </c>
       <c r="H38" s="3">
-        <v>47814.8</v>
+        <v>43154.47</v>
       </c>
       <c r="I38" s="3">
-        <v>844973.38</v>
+        <v>906839.61</v>
       </c>
       <c r="J38" s="3">
-        <v>76.33</v>
+        <v>100.25</v>
       </c>
       <c r="K38" s="3">
-        <v>-261967.26</v>
+        <v>2280.66</v>
       </c>
       <c r="L38" s="3">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="M38" s="3">
-        <v>26877.41</v>
+        <v>22258.61</v>
       </c>
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>2839</v>
+        <v>3126</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>2840</v>
+        <v>3127</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>2841</v>
+        <v>3128</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>2842</v>
+        <v>3129</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>2843</v>
+        <v>3130</v>
       </c>
       <c r="F39" s="3">
-        <v>1374896.6</v>
+        <v>1106940.64</v>
       </c>
       <c r="G39" s="3">
-        <v>1108340.03</v>
+        <v>797158.58</v>
       </c>
       <c r="H39" s="3">
-        <v>93670.91</v>
+        <v>47814.8</v>
       </c>
       <c r="I39" s="3">
-        <v>1202010.94</v>
+        <v>844973.38</v>
       </c>
       <c r="J39" s="3">
-        <v>87.43</v>
+        <v>76.33</v>
       </c>
       <c r="K39" s="3">
-        <v>-172885.66</v>
+        <v>-261967.26</v>
       </c>
       <c r="L39" s="3">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M39" s="3">
-        <v>37639.5</v>
+        <v>26877.41</v>
       </c>
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>2844</v>
+        <v>3131</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>2845</v>
+        <v>3132</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>2846</v>
+        <v>3133</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>2847</v>
+        <v>3134</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>2848</v>
+        <v>3135</v>
       </c>
       <c r="F40" s="3">
         <v>887573.45</v>
@@ -28662,142 +31235,142 @@
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>2849</v>
+        <v>3136</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>2850</v>
+        <v>3137</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>2851</v>
+        <v>3138</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>2852</v>
+        <v>3139</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>2853</v>
+        <v>3140</v>
       </c>
       <c r="F41" s="3">
-        <v>912015.93</v>
+        <v>1043081.21</v>
       </c>
       <c r="G41" s="3">
-        <v>697279.24</v>
+        <v>961464.47</v>
       </c>
       <c r="H41" s="3">
-        <v>122534.91</v>
+        <v>120162.6</v>
       </c>
       <c r="I41" s="3">
-        <v>819814.15</v>
+        <v>1081627.07</v>
       </c>
       <c r="J41" s="3">
-        <v>89.89</v>
+        <v>103.7</v>
       </c>
       <c r="K41" s="3">
-        <v>-92201.78</v>
+        <v>38545.86</v>
       </c>
       <c r="L41" s="3">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="M41" s="3">
-        <v>16972.68</v>
+        <v>23111.7</v>
       </c>
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>2854</v>
+        <v>3141</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>2855</v>
+        <v>3142</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>2856</v>
+        <v>3143</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>2857</v>
+        <v>3144</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>2858</v>
+        <v>3145</v>
       </c>
       <c r="F42" s="3">
-        <v>1236217.2</v>
+        <v>912015.93</v>
       </c>
       <c r="G42" s="3">
-        <v>823191.81</v>
+        <v>697279.24</v>
       </c>
       <c r="H42" s="3">
-        <v>138738.63</v>
+        <v>122534.91</v>
       </c>
       <c r="I42" s="3">
-        <v>961930.44</v>
+        <v>819814.15</v>
       </c>
       <c r="J42" s="3">
-        <v>77.81</v>
+        <v>89.89</v>
       </c>
       <c r="K42" s="3">
-        <v>-274286.76</v>
+        <v>-92201.78</v>
       </c>
       <c r="L42" s="3">
-        <v>3.05</v>
+        <v>2.07</v>
       </c>
       <c r="M42" s="3">
-        <v>29359.82</v>
+        <v>16972.68</v>
       </c>
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>2859</v>
+        <v>3146</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>2860</v>
+        <v>3147</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>2861</v>
+        <v>3148</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>2862</v>
+        <v>3149</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>2863</v>
+        <v>3150</v>
       </c>
       <c r="F43" s="3">
-        <v>1043081.21</v>
+        <v>1236217.2</v>
       </c>
       <c r="G43" s="3">
-        <v>961464.47</v>
+        <v>823191.81</v>
       </c>
       <c r="H43" s="3">
-        <v>120162.6</v>
+        <v>138738.63</v>
       </c>
       <c r="I43" s="3">
-        <v>1081627.07</v>
+        <v>961930.44</v>
       </c>
       <c r="J43" s="3">
-        <v>103.7</v>
+        <v>77.81</v>
       </c>
       <c r="K43" s="3">
-        <v>38545.86</v>
+        <v>-274286.76</v>
       </c>
       <c r="L43" s="3">
-        <v>2.14</v>
+        <v>3.05</v>
       </c>
       <c r="M43" s="3">
-        <v>23111.7</v>
+        <v>29359.82</v>
       </c>
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>2864</v>
+        <v>3151</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>2865</v>
+        <v>3152</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>2866</v>
+        <v>3153</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>2867</v>
+        <v>3154</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>2868</v>
+        <v>3155</v>
       </c>
       <c r="F44" s="3">
         <v>1113507.9</v>
@@ -28826,19 +31399,19 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>2869</v>
+        <v>3156</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>2870</v>
+        <v>3157</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>2871</v>
+        <v>3158</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>2872</v>
+        <v>3159</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>2873</v>
+        <v>3160</v>
       </c>
       <c r="F45" s="3">
         <v>1066780.42</v>
@@ -28867,19 +31440,19 @@
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>2874</v>
+        <v>3161</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>2875</v>
+        <v>3162</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>2876</v>
+        <v>3163</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>2877</v>
+        <v>3164</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>2878</v>
+        <v>3165</v>
       </c>
       <c r="F46" s="3">
         <v>918319.81</v>
@@ -28908,19 +31481,19 @@
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>2879</v>
+        <v>3166</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>2880</v>
+        <v>3167</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>2881</v>
+        <v>3168</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>2882</v>
+        <v>3169</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>2883</v>
+        <v>3170</v>
       </c>
       <c r="F47" s="3">
         <v>972020.19</v>
@@ -28949,19 +31522,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>2884</v>
+        <v>3171</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>2885</v>
+        <v>3172</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>2886</v>
+        <v>3173</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>2887</v>
+        <v>3174</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>2888</v>
+        <v>3175</v>
       </c>
       <c r="F48" s="3">
         <v>1022376.56</v>
@@ -28990,19 +31563,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>2889</v>
+        <v>3176</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>2890</v>
+        <v>3177</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>2891</v>
+        <v>3178</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>2892</v>
+        <v>3179</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>2893</v>
+        <v>3180</v>
       </c>
       <c r="F49" s="3">
         <v>1336954.46</v>
@@ -29031,19 +31604,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>2894</v>
+        <v>3181</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>2895</v>
+        <v>3182</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>2896</v>
+        <v>3183</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>2897</v>
+        <v>3184</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>2898</v>
+        <v>3185</v>
       </c>
       <c r="F50" s="3">
         <v>954958.72</v>
@@ -29072,19 +31645,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>2899</v>
+        <v>3186</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>2900</v>
+        <v>3187</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>2901</v>
+        <v>3188</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>2902</v>
+        <v>3189</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>2903</v>
+        <v>3190</v>
       </c>
       <c r="F51" s="3">
         <v>1154949.94</v>
@@ -29113,19 +31686,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>2904</v>
+        <v>3191</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>2905</v>
+        <v>3192</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>2906</v>
+        <v>3193</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>2907</v>
+        <v>3194</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>2908</v>
+        <v>3195</v>
       </c>
       <c r="F52" s="3">
         <v>963790.11</v>
@@ -29159,7 +31732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -29208,306 +31781,306 @@
       </c>
     </row>
     <row r="2" spans="8:8" ht="36.7">
-      <c r="A2" s="5" t="s">
-        <v>2909</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>2910</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>2911</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>2912</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="A2" s="2" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3197</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3198</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3199</v>
+      </c>
+      <c r="E2" s="3">
         <v>5936775.24</v>
       </c>
-      <c r="F2" s="6">
-        <v>4823057.7</v>
-      </c>
-      <c r="G2" s="6">
-        <v>405544.82</v>
-      </c>
-      <c r="H2" s="6">
-        <v>5228602.52</v>
-      </c>
-      <c r="I2" s="6">
-        <v>88.07</v>
-      </c>
-      <c r="J2" s="6">
-        <v>-708172.72</v>
-      </c>
-      <c r="K2" s="6">
-        <v>133388.49</v>
-      </c>
-      <c r="L2" s="6">
-        <v>2.55</v>
+      <c r="F2" s="3">
+        <v>5120228.97</v>
+      </c>
+      <c r="G2" s="3">
+        <v>278089.33</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5398318.3</v>
+      </c>
+      <c r="I2" s="3">
+        <v>90.93</v>
+      </c>
+      <c r="J2" s="3">
+        <v>-538456.94</v>
+      </c>
+      <c r="K2" s="3">
+        <v>136781.39</v>
+      </c>
+      <c r="L2" s="3">
+        <v>2.53</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
-      <c r="A3" s="5" t="s">
-        <v>2913</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>2914</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2915</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>2916</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="A3" s="2" t="s">
+        <v>3200</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3201</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3202</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3203</v>
+      </c>
+      <c r="E3" s="3">
         <v>3346888.02</v>
       </c>
-      <c r="F3" s="6">
-        <v>2197946.73</v>
-      </c>
-      <c r="G3" s="6">
-        <v>595560.65</v>
-      </c>
-      <c r="H3" s="6">
-        <v>2793507.38</v>
-      </c>
-      <c r="I3" s="6">
-        <v>83.47</v>
-      </c>
-      <c r="J3" s="6">
-        <v>-553380.64</v>
-      </c>
-      <c r="K3" s="6">
-        <v>67347.72</v>
-      </c>
-      <c r="L3" s="6">
-        <v>2.41</v>
+      <c r="F3" s="3">
+        <v>2745949.41</v>
+      </c>
+      <c r="G3" s="3">
+        <v>123244.66</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2869194.07</v>
+      </c>
+      <c r="I3" s="3">
+        <v>85.73</v>
+      </c>
+      <c r="J3" s="3">
+        <v>-477693.95</v>
+      </c>
+      <c r="K3" s="3">
+        <v>68472.12</v>
+      </c>
+      <c r="L3" s="3">
+        <v>2.39</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
-      <c r="A4" s="5" t="s">
-        <v>2917</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>2918</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>2919</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>2920</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="A4" s="2" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3205</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3206</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>3207</v>
+      </c>
+      <c r="E4" s="3">
         <v>6248074.42</v>
       </c>
-      <c r="F4" s="6">
-        <v>4548712.75</v>
-      </c>
-      <c r="G4" s="6">
-        <v>311833.87</v>
-      </c>
-      <c r="H4" s="6">
-        <v>4860546.62</v>
-      </c>
-      <c r="I4" s="6">
-        <v>77.79</v>
-      </c>
-      <c r="J4" s="6">
-        <v>-1387527.8</v>
-      </c>
-      <c r="K4" s="6">
-        <v>185241.51</v>
-      </c>
-      <c r="L4" s="6">
-        <v>3.81</v>
+      <c r="F4" s="3">
+        <v>4706013.38</v>
+      </c>
+      <c r="G4" s="3">
+        <v>229757.82</v>
+      </c>
+      <c r="H4" s="3">
+        <v>4935771.2</v>
+      </c>
+      <c r="I4" s="3">
+        <v>79.0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>-1312303.22</v>
+      </c>
+      <c r="K4" s="3">
+        <v>192346.78</v>
+      </c>
+      <c r="L4" s="3">
+        <v>3.9</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
-      <c r="A5" s="5" t="s">
-        <v>2921</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>2922</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>2923</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>2924</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="A5" s="2" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>3211</v>
+      </c>
+      <c r="E5" s="3">
         <v>7225829.17</v>
       </c>
-      <c r="F5" s="6">
-        <v>6345405.77</v>
-      </c>
-      <c r="G5" s="6">
-        <v>381577.67</v>
-      </c>
-      <c r="H5" s="6">
-        <v>6726983.44</v>
-      </c>
-      <c r="I5" s="6">
-        <v>93.1</v>
-      </c>
-      <c r="J5" s="6">
-        <v>-498845.73</v>
-      </c>
-      <c r="K5" s="6">
-        <v>173677.73</v>
-      </c>
-      <c r="L5" s="6">
-        <v>2.58</v>
+      <c r="F5" s="3">
+        <v>6541331.2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>453019.68</v>
+      </c>
+      <c r="H5" s="3">
+        <v>6994350.88</v>
+      </c>
+      <c r="I5" s="3">
+        <v>96.8</v>
+      </c>
+      <c r="J5" s="3">
+        <v>-231478.29</v>
+      </c>
+      <c r="K5" s="3">
+        <v>179308.04</v>
+      </c>
+      <c r="L5" s="3">
+        <v>2.56</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
-      <c r="A6" s="5" t="s">
-        <v>2925</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>2926</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>2927</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>2928</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="A6" s="2" t="s">
+        <v>3212</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3213</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3214</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>3215</v>
+      </c>
+      <c r="E6" s="3">
         <v>6938999.79</v>
       </c>
-      <c r="F6" s="6">
-        <v>6114889.65</v>
-      </c>
-      <c r="G6" s="6">
-        <v>380058.19</v>
-      </c>
-      <c r="H6" s="6">
-        <v>6494947.84</v>
-      </c>
-      <c r="I6" s="6">
-        <v>93.6</v>
-      </c>
-      <c r="J6" s="6">
-        <v>-444051.95</v>
-      </c>
-      <c r="K6" s="6">
-        <v>214719.73</v>
-      </c>
-      <c r="L6" s="6">
-        <v>3.31</v>
+      <c r="F6" s="3">
+        <v>6202415.92</v>
+      </c>
+      <c r="G6" s="3">
+        <v>380318.41</v>
+      </c>
+      <c r="H6" s="3">
+        <v>6582734.33</v>
+      </c>
+      <c r="I6" s="3">
+        <v>94.87</v>
+      </c>
+      <c r="J6" s="3">
+        <v>-356265.46</v>
+      </c>
+      <c r="K6" s="3">
+        <v>224919.36</v>
+      </c>
+      <c r="L6" s="3">
+        <v>3.42</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
-      <c r="A7" s="5" t="s">
-        <v>2929</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>2931</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>2932</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="A7" s="2" t="s">
+        <v>3216</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>3217</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3218</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>3219</v>
+      </c>
+      <c r="E7" s="3">
         <v>4536967.52</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>3932458.4</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <v>263529.54</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="3">
         <v>4195987.94</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="3">
         <v>92.48</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="3">
         <v>-340979.58</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="3">
         <v>115362.22</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="3">
         <v>2.75</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
-      <c r="A8" s="5" t="s">
-        <v>2933</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>2934</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>2935</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>2936</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="A8" s="2" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>3223</v>
+      </c>
+      <c r="E8" s="3">
         <v>7177495.92</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3">
         <v>5883718.63</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="3">
         <v>461194.15</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="3">
         <v>6344912.78</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="3">
         <v>88.4</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="3">
         <v>-832583.14</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="3">
         <v>141392.61</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="3">
         <v>2.23</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
-      <c r="A9" s="5" t="s">
-        <v>2937</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>2938</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>2939</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>2940</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="A9" s="2" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>3225</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>3226</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>3227</v>
+      </c>
+      <c r="E9" s="3">
         <v>6405049.98</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="3">
         <v>4824496.86</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="3">
         <v>0.0</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="3">
         <v>4824496.86</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="3">
         <v>75.32</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="3">
         <v>-1580553.12</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="3">
         <v>205520.18</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="3">
         <v>4.26</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="territory-wise-MPE-sales-achiev" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3228" count="3228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3770" count="3770">
   <si>
     <t>Region</t>
   </si>
@@ -29188,6 +29188,4884 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
     </r>
   </si>
 </sst>
@@ -29575,7 +34453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AE52"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -29636,245 +34514,245 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>2941</v>
+        <v>3515</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2942</v>
+        <v>3516</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2943</v>
+        <v>3517</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2944</v>
+        <v>3518</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2945</v>
+        <v>3519</v>
       </c>
       <c r="F2" s="3">
         <v>747825.09</v>
       </c>
       <c r="G2" s="3">
-        <v>655581.7</v>
+        <v>695442.28</v>
       </c>
       <c r="H2" s="3">
-        <v>41704.79</v>
+        <v>26449.88</v>
       </c>
       <c r="I2" s="3">
-        <v>697286.49</v>
+        <v>721892.16</v>
       </c>
       <c r="J2" s="3">
-        <v>93.24</v>
+        <v>96.53</v>
       </c>
       <c r="K2" s="3">
-        <v>-50538.6</v>
+        <v>-25932.93</v>
       </c>
       <c r="L2" s="3">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="M2" s="3">
-        <v>18391.79</v>
+        <v>20236.01</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>2946</v>
+        <v>3520</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2947</v>
+        <v>3521</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2948</v>
+        <v>3522</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>2949</v>
+        <v>3523</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2950</v>
+        <v>3524</v>
       </c>
       <c r="F3" s="3">
         <v>755003.49</v>
       </c>
       <c r="G3" s="3">
-        <v>683410.87</v>
+        <v>713751.3</v>
       </c>
       <c r="H3" s="3">
-        <v>31596.01</v>
+        <v>16278.41</v>
       </c>
       <c r="I3" s="3">
-        <v>715006.88</v>
+        <v>730029.71</v>
       </c>
       <c r="J3" s="3">
-        <v>94.7</v>
+        <v>96.69</v>
       </c>
       <c r="K3" s="3">
-        <v>-39996.61</v>
+        <v>-24973.78</v>
       </c>
       <c r="L3" s="3">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="M3" s="3">
-        <v>13029.03</v>
+        <v>14374.56</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2951</v>
+        <v>3525</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2952</v>
+        <v>3526</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2953</v>
+        <v>3527</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>2954</v>
+        <v>3528</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2955</v>
+        <v>3529</v>
       </c>
       <c r="F4" s="3">
         <v>664724.91</v>
       </c>
       <c r="G4" s="3">
-        <v>674116.41</v>
+        <v>711498.47</v>
       </c>
       <c r="H4" s="3">
-        <v>38629.41</v>
+        <v>24746.31</v>
       </c>
       <c r="I4" s="3">
-        <v>712745.82</v>
+        <v>736244.78</v>
       </c>
       <c r="J4" s="3">
-        <v>107.22</v>
+        <v>110.76</v>
       </c>
       <c r="K4" s="3">
-        <v>48020.91</v>
+        <v>71519.87</v>
       </c>
       <c r="L4" s="3">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="M4" s="3">
-        <v>20002.44</v>
+        <v>21249.8</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>2956</v>
+        <v>3530</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2957</v>
+        <v>3531</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2958</v>
+        <v>3532</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>2959</v>
+        <v>3533</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>2960</v>
+        <v>3534</v>
       </c>
       <c r="F5" s="3">
         <v>745422.79</v>
       </c>
       <c r="G5" s="3">
-        <v>591356.73</v>
+        <v>630271.37</v>
       </c>
       <c r="H5" s="3">
-        <v>39555.92</v>
+        <v>84589.46</v>
       </c>
       <c r="I5" s="3">
-        <v>630912.65</v>
+        <v>714860.83</v>
       </c>
       <c r="J5" s="3">
-        <v>84.64</v>
+        <v>95.9</v>
       </c>
       <c r="K5" s="3">
-        <v>-114510.14</v>
+        <v>-30561.96</v>
       </c>
       <c r="L5" s="3">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="M5" s="3">
-        <v>26206.95</v>
+        <v>26902.2</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>2961</v>
+        <v>3535</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2962</v>
+        <v>3536</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2963</v>
+        <v>3537</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>2964</v>
+        <v>3538</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>2965</v>
+        <v>3539</v>
       </c>
       <c r="F6" s="3">
         <v>750633.4</v>
       </c>
       <c r="G6" s="3">
-        <v>805478.98</v>
+        <v>847498.11</v>
       </c>
       <c r="H6" s="3">
-        <v>42450.95</v>
+        <v>26655.78</v>
       </c>
       <c r="I6" s="3">
-        <v>847929.93</v>
+        <v>874153.89</v>
       </c>
       <c r="J6" s="3">
-        <v>112.96</v>
+        <v>116.46</v>
       </c>
       <c r="K6" s="3">
-        <v>97296.53</v>
+        <v>123520.49</v>
       </c>
       <c r="L6" s="3">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="M6" s="3">
-        <v>21639.95</v>
+        <v>22071.77</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>2966</v>
+        <v>3540</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2967</v>
+        <v>3541</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>2968</v>
+        <v>3542</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>2969</v>
+        <v>3543</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>2970</v>
+        <v>3544</v>
       </c>
       <c r="F7" s="3">
         <v>804591.82</v>
       </c>
       <c r="G7" s="3">
-        <v>577215.0</v>
+        <v>607387.34</v>
       </c>
       <c r="H7" s="3">
-        <v>30075.2</v>
+        <v>23579.58</v>
       </c>
       <c r="I7" s="3">
-        <v>607290.2</v>
+        <v>630966.92</v>
       </c>
       <c r="J7" s="3">
-        <v>75.48</v>
+        <v>78.42</v>
       </c>
       <c r="K7" s="3">
-        <v>-197301.62</v>
+        <v>-173624.9</v>
       </c>
       <c r="L7" s="3">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="M7" s="3">
         <v>14980.55</v>
@@ -29882,40 +34760,40 @@
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>2971</v>
+        <v>3545</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>2972</v>
+        <v>3546</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2973</v>
+        <v>3547</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>2974</v>
+        <v>3548</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>2975</v>
+        <v>3549</v>
       </c>
       <c r="F8" s="3">
         <v>726832.71</v>
       </c>
       <c r="G8" s="3">
-        <v>488727.0</v>
+        <v>509693.18</v>
       </c>
       <c r="H8" s="3">
-        <v>18342.48</v>
+        <v>207116.17</v>
       </c>
       <c r="I8" s="3">
-        <v>507069.48</v>
+        <v>716809.35</v>
       </c>
       <c r="J8" s="3">
-        <v>69.76</v>
+        <v>98.62</v>
       </c>
       <c r="K8" s="3">
-        <v>-219763.23</v>
+        <v>-10023.36</v>
       </c>
       <c r="L8" s="3">
-        <v>1.03</v>
+        <v>0.73</v>
       </c>
       <c r="M8" s="3">
         <v>5237.7</v>
@@ -29923,245 +34801,245 @@
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>2976</v>
+        <v>3550</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>2977</v>
+        <v>3551</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2978</v>
+        <v>3552</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>2979</v>
+        <v>3553</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>2980</v>
+        <v>3554</v>
       </c>
       <c r="F9" s="3">
         <v>741741.03</v>
       </c>
       <c r="G9" s="3">
-        <v>644342.27</v>
+        <v>678245.67</v>
       </c>
       <c r="H9" s="3">
-        <v>35734.57</v>
+        <v>20637.31</v>
       </c>
       <c r="I9" s="3">
-        <v>680076.84</v>
+        <v>698882.98</v>
       </c>
       <c r="J9" s="3">
-        <v>91.69</v>
+        <v>94.22</v>
       </c>
       <c r="K9" s="3">
-        <v>-61664.19</v>
+        <v>-42858.05</v>
       </c>
       <c r="L9" s="3">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="M9" s="3">
-        <v>17292.99</v>
+        <v>19286.07</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>2981</v>
+        <v>3555</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>2982</v>
+        <v>3556</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2983</v>
+        <v>3557</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>2984</v>
+        <v>3558</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>2985</v>
+        <v>3559</v>
       </c>
       <c r="F10" s="3">
         <v>859984.15</v>
       </c>
       <c r="G10" s="3">
-        <v>752750.75</v>
+        <v>786199.35</v>
       </c>
       <c r="H10" s="3">
-        <v>34504.71</v>
+        <v>35010.34</v>
       </c>
       <c r="I10" s="3">
-        <v>787255.46</v>
+        <v>821209.69</v>
       </c>
       <c r="J10" s="3">
-        <v>91.54</v>
+        <v>95.49</v>
       </c>
       <c r="K10" s="3">
-        <v>-72728.69</v>
+        <v>-38774.46</v>
       </c>
       <c r="L10" s="3">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="M10" s="3">
-        <v>21910.4</v>
+        <v>23083.45</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>2986</v>
+        <v>3560</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>2987</v>
+        <v>3561</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2988</v>
+        <v>3562</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>2989</v>
+        <v>3563</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>2990</v>
+        <v>3564</v>
       </c>
       <c r="F11" s="3">
         <v>903047.31</v>
       </c>
       <c r="G11" s="3">
-        <v>614366.64</v>
+        <v>636994.45</v>
       </c>
       <c r="H11" s="3">
-        <v>23187.51</v>
+        <v>28182.08</v>
       </c>
       <c r="I11" s="3">
-        <v>637554.15</v>
+        <v>665176.53</v>
       </c>
       <c r="J11" s="3">
-        <v>70.6</v>
+        <v>73.66</v>
       </c>
       <c r="K11" s="3">
-        <v>-265493.16</v>
+        <v>-237870.78</v>
       </c>
       <c r="L11" s="3">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="M11" s="3">
-        <v>20669.75</v>
+        <v>21299.6</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>2991</v>
+        <v>3565</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>2992</v>
+        <v>3566</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>2993</v>
+        <v>3567</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>2994</v>
+        <v>3568</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>2995</v>
+        <v>3569</v>
       </c>
       <c r="F12" s="3">
         <v>775221.33</v>
       </c>
       <c r="G12" s="3">
-        <v>683686.72</v>
+        <v>721871.24</v>
       </c>
       <c r="H12" s="3">
-        <v>38581.92</v>
+        <v>50352.04</v>
       </c>
       <c r="I12" s="3">
-        <v>722268.64</v>
+        <v>772223.28</v>
       </c>
       <c r="J12" s="3">
-        <v>93.17</v>
+        <v>99.61</v>
       </c>
       <c r="K12" s="3">
-        <v>-52952.69</v>
+        <v>-2998.05</v>
       </c>
       <c r="L12" s="3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M12" s="3">
-        <v>10391.92</v>
+        <v>10789.32</v>
       </c>
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>2996</v>
+        <v>3570</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2997</v>
+        <v>3571</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2998</v>
+        <v>3572</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>2999</v>
+        <v>3573</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>3000</v>
+        <v>3574</v>
       </c>
       <c r="F13" s="3">
         <v>808635.23</v>
       </c>
       <c r="G13" s="3">
-        <v>695145.3</v>
+        <v>764345.37</v>
       </c>
       <c r="H13" s="3">
-        <v>26970.53</v>
+        <v>37393.0</v>
       </c>
       <c r="I13" s="3">
-        <v>722115.83</v>
+        <v>801738.37</v>
       </c>
       <c r="J13" s="3">
-        <v>89.3</v>
+        <v>99.15</v>
       </c>
       <c r="K13" s="3">
-        <v>-86519.4</v>
+        <v>-6896.86</v>
       </c>
       <c r="L13" s="3">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="M13" s="3">
-        <v>15500.04</v>
+        <v>17462.55</v>
       </c>
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>3001</v>
+        <v>3575</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>3002</v>
+        <v>3576</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>3003</v>
+        <v>3577</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>3004</v>
+        <v>3578</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>3005</v>
+        <v>3579</v>
       </c>
       <c r="F14" s="3">
         <v>773239.07</v>
       </c>
       <c r="G14" s="3">
-        <v>666364.32</v>
+        <v>710545.27</v>
       </c>
       <c r="H14" s="3">
-        <v>44180.95</v>
+        <v>21048.89</v>
       </c>
       <c r="I14" s="3">
-        <v>710545.27</v>
+        <v>731594.16</v>
       </c>
       <c r="J14" s="3">
-        <v>91.89</v>
+        <v>94.61</v>
       </c>
       <c r="K14" s="3">
-        <v>-62693.8</v>
+        <v>-41644.91</v>
       </c>
       <c r="L14" s="3">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="M14" s="3">
         <v>11696.14</v>
@@ -30169,40 +35047,40 @@
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>3006</v>
+        <v>3580</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>3007</v>
+        <v>3581</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>3008</v>
+        <v>3582</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>3009</v>
+        <v>3583</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>3010</v>
+        <v>3584</v>
       </c>
       <c r="F15" s="3">
         <v>788718.67</v>
       </c>
       <c r="G15" s="3">
-        <v>539242.33</v>
+        <v>558215.59</v>
       </c>
       <c r="H15" s="3">
-        <v>18838.33</v>
+        <v>8474.84</v>
       </c>
       <c r="I15" s="3">
-        <v>558080.66</v>
+        <v>566690.43</v>
       </c>
       <c r="J15" s="3">
-        <v>70.76</v>
+        <v>71.85</v>
       </c>
       <c r="K15" s="3">
-        <v>-230638.01</v>
+        <v>-222028.24</v>
       </c>
       <c r="L15" s="3">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="M15" s="3">
         <v>13872.04</v>
@@ -30210,40 +35088,40 @@
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>3011</v>
+        <v>3585</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>3012</v>
+        <v>3586</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>3013</v>
+        <v>3587</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>3014</v>
+        <v>3588</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>3015</v>
+        <v>3589</v>
       </c>
       <c r="F16" s="3">
         <v>757031.95</v>
       </c>
       <c r="G16" s="3">
-        <v>390950.89</v>
+        <v>407606.88</v>
       </c>
       <c r="H16" s="3">
-        <v>16655.99</v>
+        <v>10731.44</v>
       </c>
       <c r="I16" s="3">
-        <v>407606.88</v>
+        <v>418338.32</v>
       </c>
       <c r="J16" s="3">
-        <v>53.84</v>
+        <v>55.26</v>
       </c>
       <c r="K16" s="3">
-        <v>-349425.07</v>
+        <v>-338693.63</v>
       </c>
       <c r="L16" s="3">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="M16" s="3">
         <v>6500.98</v>
@@ -30251,40 +35129,40 @@
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>3016</v>
+        <v>3590</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>3017</v>
+        <v>3591</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>3018</v>
+        <v>3592</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>3019</v>
+        <v>3593</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>3020</v>
+        <v>3594</v>
       </c>
       <c r="F17" s="3">
         <v>792097.85</v>
       </c>
       <c r="G17" s="3">
-        <v>504088.82</v>
+        <v>526141.28</v>
       </c>
       <c r="H17" s="3">
-        <v>21971.51</v>
+        <v>12843.78</v>
       </c>
       <c r="I17" s="3">
-        <v>526060.33</v>
+        <v>538985.06</v>
       </c>
       <c r="J17" s="3">
-        <v>66.41</v>
+        <v>68.05</v>
       </c>
       <c r="K17" s="3">
-        <v>-266037.52</v>
+        <v>-253112.79</v>
       </c>
       <c r="L17" s="3">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M17" s="3">
         <v>14827.46</v>
@@ -30292,1085 +35170,1085 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>3021</v>
+        <v>3595</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>3022</v>
+        <v>3596</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>3023</v>
+        <v>3597</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>3024</v>
+        <v>3598</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>3025</v>
+        <v>3599</v>
       </c>
       <c r="F18" s="3">
-        <v>1027095.81</v>
+        <v>1246040.32</v>
       </c>
       <c r="G18" s="3">
-        <v>850624.05</v>
+        <v>974359.82</v>
       </c>
       <c r="H18" s="3">
-        <v>33466.66</v>
+        <v>0.0</v>
       </c>
       <c r="I18" s="3">
-        <v>884090.71</v>
+        <v>974359.82</v>
       </c>
       <c r="J18" s="3">
-        <v>86.08</v>
+        <v>78.2</v>
       </c>
       <c r="K18" s="3">
-        <v>-143005.1</v>
+        <v>-271680.5</v>
       </c>
       <c r="L18" s="3">
-        <v>6.0</v>
+        <v>5.57</v>
       </c>
       <c r="M18" s="3">
-        <v>53073.94</v>
+        <v>54238.59</v>
       </c>
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>3026</v>
+        <v>3600</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>3027</v>
+        <v>3601</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>3028</v>
+        <v>3602</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>3029</v>
+        <v>3603</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>3030</v>
+        <v>3604</v>
       </c>
       <c r="F19" s="3">
         <v>863850.75</v>
       </c>
       <c r="G19" s="3">
-        <v>821602.18</v>
+        <v>868539.33</v>
       </c>
       <c r="H19" s="3">
-        <v>49430.99</v>
+        <v>0.0</v>
       </c>
       <c r="I19" s="3">
-        <v>871033.17</v>
+        <v>868539.33</v>
       </c>
       <c r="J19" s="3">
-        <v>100.83</v>
+        <v>100.54</v>
       </c>
       <c r="K19" s="3">
-        <v>7182.42</v>
+        <v>4688.58</v>
       </c>
       <c r="L19" s="3">
-        <v>4.84</v>
+        <v>5.14</v>
       </c>
       <c r="M19" s="3">
-        <v>42132.0</v>
+        <v>44625.84</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>3031</v>
+        <v>3605</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>3032</v>
+        <v>3606</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>3033</v>
+        <v>3607</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>3034</v>
+        <v>3608</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>3035</v>
+        <v>3609</v>
       </c>
       <c r="F20" s="3">
-        <v>1246040.32</v>
+        <v>1027095.81</v>
       </c>
       <c r="G20" s="3">
-        <v>933140.79</v>
+        <v>882298.55</v>
       </c>
       <c r="H20" s="3">
-        <v>45213.39</v>
+        <v>0.0</v>
       </c>
       <c r="I20" s="3">
-        <v>978354.18</v>
+        <v>882298.55</v>
       </c>
       <c r="J20" s="3">
-        <v>78.52</v>
+        <v>85.9</v>
       </c>
       <c r="K20" s="3">
-        <v>-267686.14</v>
+        <v>-144797.26</v>
       </c>
       <c r="L20" s="3">
-        <v>5.14</v>
+        <v>6.22</v>
       </c>
       <c r="M20" s="3">
-        <v>50244.23</v>
+        <v>54866.1</v>
       </c>
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>3036</v>
+        <v>3610</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>3037</v>
+        <v>3611</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>3038</v>
+        <v>3612</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>3039</v>
+        <v>3613</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>3040</v>
+        <v>3614</v>
       </c>
       <c r="F21" s="3">
         <v>875303.02</v>
       </c>
       <c r="G21" s="3">
-        <v>841202.64</v>
+        <v>900300.6</v>
       </c>
       <c r="H21" s="3">
-        <v>68524.25</v>
+        <v>25850.98</v>
       </c>
       <c r="I21" s="3">
-        <v>909726.89</v>
+        <v>926151.58</v>
       </c>
       <c r="J21" s="3">
-        <v>103.93</v>
+        <v>105.81</v>
       </c>
       <c r="K21" s="3">
-        <v>34423.87</v>
+        <v>50848.56</v>
       </c>
       <c r="L21" s="3">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="M21" s="3">
-        <v>19654.59</v>
+        <v>20527.29</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>3041</v>
+        <v>3615</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>3042</v>
+        <v>3616</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>3043</v>
+        <v>3617</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>3044</v>
+        <v>3618</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>3045</v>
+        <v>3619</v>
       </c>
       <c r="F22" s="3">
         <v>859661.34</v>
       </c>
       <c r="G22" s="3">
-        <v>901965.23</v>
+        <v>936800.79</v>
       </c>
       <c r="H22" s="3">
-        <v>45759.58</v>
+        <v>27166.56</v>
       </c>
       <c r="I22" s="3">
-        <v>947724.81</v>
+        <v>963967.35</v>
       </c>
       <c r="J22" s="3">
-        <v>110.24</v>
+        <v>112.13</v>
       </c>
       <c r="K22" s="3">
-        <v>88063.47</v>
+        <v>104306.01</v>
       </c>
       <c r="L22" s="3">
         <v>2.97</v>
       </c>
       <c r="M22" s="3">
-        <v>28130.12</v>
+        <v>28623.8</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>3046</v>
+        <v>3620</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>3047</v>
+        <v>3621</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>3048</v>
+        <v>3622</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>3049</v>
+        <v>3623</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>3050</v>
+        <v>3624</v>
       </c>
       <c r="F23" s="3">
         <v>867257.37</v>
       </c>
       <c r="G23" s="3">
-        <v>985570.39</v>
+        <v>1047710.53</v>
       </c>
       <c r="H23" s="3">
-        <v>69440.81</v>
+        <v>22914.83</v>
       </c>
       <c r="I23" s="3">
-        <v>1055011.2</v>
+        <v>1070625.36</v>
       </c>
       <c r="J23" s="3">
-        <v>121.65</v>
+        <v>123.45</v>
       </c>
       <c r="K23" s="3">
-        <v>187753.83</v>
+        <v>203367.99</v>
       </c>
       <c r="L23" s="3">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="M23" s="3">
-        <v>17612.59</v>
+        <v>18733.0</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>3051</v>
+        <v>3625</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>3052</v>
+        <v>3626</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>3053</v>
+        <v>3627</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>3054</v>
+        <v>3628</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>3055</v>
+        <v>3629</v>
       </c>
       <c r="F24" s="3">
         <v>778641.12</v>
       </c>
       <c r="G24" s="3">
-        <v>781097.23</v>
+        <v>867594.02</v>
       </c>
       <c r="H24" s="3">
-        <v>96024.32</v>
+        <v>24914.81</v>
       </c>
       <c r="I24" s="3">
-        <v>877121.55</v>
+        <v>892508.83</v>
       </c>
       <c r="J24" s="3">
-        <v>112.65</v>
+        <v>114.62</v>
       </c>
       <c r="K24" s="3">
-        <v>98480.43</v>
+        <v>113867.71</v>
       </c>
       <c r="L24" s="3">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="M24" s="3">
-        <v>23809.95</v>
+        <v>25522.15</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>3056</v>
+        <v>3630</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>3057</v>
+        <v>3631</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>3058</v>
+        <v>3632</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>3059</v>
+        <v>3633</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>3060</v>
+        <v>3634</v>
       </c>
       <c r="F25" s="3">
         <v>979868.9</v>
       </c>
       <c r="G25" s="3">
-        <v>844110.19</v>
+        <v>889518.35</v>
       </c>
       <c r="H25" s="3">
-        <v>47149.72</v>
+        <v>23025.26</v>
       </c>
       <c r="I25" s="3">
-        <v>891259.91</v>
+        <v>912543.61</v>
       </c>
       <c r="J25" s="3">
-        <v>90.96</v>
+        <v>93.13</v>
       </c>
       <c r="K25" s="3">
-        <v>-88608.99</v>
+        <v>-67325.29</v>
       </c>
       <c r="L25" s="3">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="M25" s="3">
-        <v>19044.38</v>
+        <v>20888.48</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>3061</v>
+        <v>3635</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>3062</v>
+        <v>3636</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>3063</v>
+        <v>3637</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>3064</v>
+        <v>3638</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>3065</v>
+        <v>3639</v>
       </c>
       <c r="F26" s="3">
         <v>1011213.65</v>
       </c>
       <c r="G26" s="3">
-        <v>643661.88</v>
+        <v>681350.17</v>
       </c>
       <c r="H26" s="3">
-        <v>38011.06</v>
+        <v>25124.42</v>
       </c>
       <c r="I26" s="3">
-        <v>681672.94</v>
+        <v>706474.59</v>
       </c>
       <c r="J26" s="3">
-        <v>67.41</v>
+        <v>69.86</v>
       </c>
       <c r="K26" s="3">
-        <v>-329540.71</v>
+        <v>-304739.06</v>
       </c>
       <c r="L26" s="3">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="M26" s="3">
-        <v>30913.03</v>
+        <v>31406.71</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>3066</v>
+        <v>3640</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>3067</v>
+        <v>3641</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>3068</v>
+        <v>3642</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>3069</v>
+        <v>3643</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>3070</v>
+        <v>3644</v>
       </c>
       <c r="F27" s="3">
         <v>905279.17</v>
       </c>
       <c r="G27" s="3">
-        <v>806536.45</v>
+        <v>862278.67</v>
       </c>
       <c r="H27" s="3">
-        <v>57277.0</v>
+        <v>25788.79</v>
       </c>
       <c r="I27" s="3">
-        <v>863813.45</v>
+        <v>888067.46</v>
       </c>
       <c r="J27" s="3">
-        <v>95.42</v>
+        <v>98.1</v>
       </c>
       <c r="K27" s="3">
-        <v>-41465.72</v>
+        <v>-17211.71</v>
       </c>
       <c r="L27" s="3">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="M27" s="3">
-        <v>21675.14</v>
+        <v>23209.92</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>3071</v>
+        <v>3645</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>3072</v>
+        <v>3646</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>3073</v>
+        <v>3647</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>3074</v>
+        <v>3648</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>3075</v>
+        <v>3649</v>
       </c>
       <c r="F28" s="3">
         <v>948604.6</v>
       </c>
       <c r="G28" s="3">
-        <v>737187.19</v>
+        <v>766067.13</v>
       </c>
       <c r="H28" s="3">
-        <v>30832.94</v>
+        <v>28950.43</v>
       </c>
       <c r="I28" s="3">
-        <v>768020.13</v>
+        <v>795017.56</v>
       </c>
       <c r="J28" s="3">
-        <v>80.96</v>
+        <v>83.81</v>
       </c>
       <c r="K28" s="3">
-        <v>-180584.47</v>
+        <v>-153587.04</v>
       </c>
       <c r="L28" s="3">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="M28" s="3">
-        <v>18468.25</v>
+        <v>20421.25</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>3076</v>
+        <v>3650</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>3077</v>
+        <v>3651</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>3078</v>
+        <v>3652</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>3079</v>
+        <v>3653</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>3080</v>
+        <v>3654</v>
       </c>
       <c r="F29" s="3">
         <v>824118.89</v>
       </c>
       <c r="G29" s="3">
-        <v>723438.06</v>
+        <v>775122.68</v>
       </c>
       <c r="H29" s="3">
-        <v>55586.45</v>
+        <v>15101.4</v>
       </c>
       <c r="I29" s="3">
-        <v>779024.51</v>
+        <v>790224.08</v>
       </c>
       <c r="J29" s="3">
-        <v>94.53</v>
+        <v>95.89</v>
       </c>
       <c r="K29" s="3">
-        <v>-45094.38</v>
+        <v>-33894.81</v>
       </c>
       <c r="L29" s="3">
-        <v>3.29</v>
+        <v>3.74</v>
       </c>
       <c r="M29" s="3">
-        <v>25657.71</v>
+        <v>29559.53</v>
       </c>
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>3081</v>
+        <v>3655</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>3082</v>
+        <v>3656</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>3083</v>
+        <v>3657</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>3084</v>
+        <v>3658</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>3085</v>
+        <v>3659</v>
       </c>
       <c r="F30" s="3">
         <v>877850.52</v>
       </c>
       <c r="G30" s="3">
-        <v>991324.46</v>
+        <v>1046888.05</v>
       </c>
       <c r="H30" s="3">
-        <v>55837.2</v>
+        <v>24752.52</v>
       </c>
       <c r="I30" s="3">
-        <v>1047161.66</v>
+        <v>1071640.57</v>
       </c>
       <c r="J30" s="3">
-        <v>119.29</v>
+        <v>122.08</v>
       </c>
       <c r="K30" s="3">
-        <v>169311.14</v>
+        <v>193790.05</v>
       </c>
       <c r="L30" s="3">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="M30" s="3">
-        <v>25087.58</v>
+        <v>25361.2</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>3086</v>
+        <v>3660</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>3087</v>
+        <v>3661</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>3088</v>
+        <v>3662</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>3089</v>
+        <v>3663</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>3090</v>
+        <v>3664</v>
       </c>
       <c r="F31" s="3">
         <v>990466.72</v>
       </c>
       <c r="G31" s="3">
-        <v>909348.03</v>
+        <v>957160.48</v>
       </c>
       <c r="H31" s="3">
-        <v>49477.69</v>
+        <v>24894.19</v>
       </c>
       <c r="I31" s="3">
-        <v>958825.72</v>
+        <v>982054.67</v>
       </c>
       <c r="J31" s="3">
-        <v>96.81</v>
+        <v>99.15</v>
       </c>
       <c r="K31" s="3">
-        <v>-31641.0</v>
+        <v>-8412.05</v>
       </c>
       <c r="L31" s="3">
-        <v>4.27</v>
+        <v>4.34</v>
       </c>
       <c r="M31" s="3">
-        <v>40927.52</v>
+        <v>42652.12</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>3091</v>
+        <v>3665</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>3092</v>
+        <v>3666</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>3093</v>
+        <v>3667</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>3094</v>
+        <v>3668</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>3095</v>
+        <v>3669</v>
       </c>
       <c r="F32" s="3">
         <v>892245.98</v>
       </c>
       <c r="G32" s="3">
-        <v>788431.63</v>
+        <v>828839.88</v>
       </c>
       <c r="H32" s="3">
-        <v>42221.1</v>
+        <v>30410.74</v>
       </c>
       <c r="I32" s="3">
-        <v>830652.73</v>
+        <v>859250.62</v>
       </c>
       <c r="J32" s="3">
-        <v>93.1</v>
+        <v>96.3</v>
       </c>
       <c r="K32" s="3">
-        <v>-61593.25</v>
+        <v>-32995.36</v>
       </c>
       <c r="L32" s="3">
-        <v>4.0</v>
+        <v>4.09</v>
       </c>
       <c r="M32" s="3">
-        <v>33240.16</v>
+        <v>35151.96</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>3096</v>
+        <v>3670</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>3097</v>
+        <v>3671</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>3098</v>
+        <v>3672</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>3099</v>
+        <v>3673</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>3100</v>
+        <v>3674</v>
       </c>
       <c r="F33" s="3">
         <v>1265248.83</v>
       </c>
       <c r="G33" s="3">
-        <v>1127548.09</v>
+        <v>1186111.24</v>
       </c>
       <c r="H33" s="3">
-        <v>61482.55</v>
+        <v>0.0</v>
       </c>
       <c r="I33" s="3">
-        <v>1189030.64</v>
+        <v>1186111.24</v>
       </c>
       <c r="J33" s="3">
-        <v>93.98</v>
+        <v>93.75</v>
       </c>
       <c r="K33" s="3">
-        <v>-76218.19</v>
+        <v>-79137.59</v>
       </c>
       <c r="L33" s="3">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="M33" s="3">
-        <v>48720.71</v>
+        <v>51640.11</v>
       </c>
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>3101</v>
+        <v>3675</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>3102</v>
+        <v>3676</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>3103</v>
+        <v>3677</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>3104</v>
+        <v>3678</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>3105</v>
+        <v>3679</v>
       </c>
       <c r="F34" s="3">
         <v>1062018.28</v>
       </c>
       <c r="G34" s="3">
-        <v>769054.14</v>
+        <v>818423.62</v>
       </c>
       <c r="H34" s="3">
-        <v>50820.42</v>
+        <v>0.0</v>
       </c>
       <c r="I34" s="3">
-        <v>819874.56</v>
+        <v>818423.62</v>
       </c>
       <c r="J34" s="3">
-        <v>77.2</v>
+        <v>77.06</v>
       </c>
       <c r="K34" s="3">
-        <v>-242143.72</v>
+        <v>-243594.66</v>
       </c>
       <c r="L34" s="3">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="M34" s="3">
-        <v>23235.9</v>
+        <v>24686.84</v>
       </c>
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>3106</v>
+        <v>3680</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>3107</v>
+        <v>3681</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>3108</v>
+        <v>3682</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>3109</v>
+        <v>3683</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>3110</v>
+        <v>3684</v>
       </c>
       <c r="F35" s="3">
         <v>1027050.57</v>
       </c>
       <c r="G35" s="3">
-        <v>893271.52</v>
+        <v>957122.48</v>
       </c>
       <c r="H35" s="3">
-        <v>64893.0</v>
+        <v>0.0</v>
       </c>
       <c r="I35" s="3">
-        <v>958164.52</v>
+        <v>957122.48</v>
       </c>
       <c r="J35" s="3">
-        <v>93.29</v>
+        <v>93.19</v>
       </c>
       <c r="K35" s="3">
-        <v>-68886.05</v>
+        <v>-69928.09</v>
       </c>
       <c r="L35" s="3">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="M35" s="3">
-        <v>28049.78</v>
+        <v>29091.82</v>
       </c>
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>3111</v>
+        <v>3685</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>3112</v>
+        <v>3686</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>3113</v>
+        <v>3687</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>3114</v>
+        <v>3688</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>3115</v>
+        <v>3689</v>
       </c>
       <c r="F36" s="3">
         <v>1150571.33</v>
       </c>
       <c r="G36" s="3">
-        <v>1163274.65</v>
+        <v>1241173.41</v>
       </c>
       <c r="H36" s="3">
-        <v>78889.36</v>
+        <v>5845.98</v>
       </c>
       <c r="I36" s="3">
-        <v>1242164.01</v>
+        <v>1247019.39</v>
       </c>
       <c r="J36" s="3">
-        <v>107.96</v>
+        <v>108.38</v>
       </c>
       <c r="K36" s="3">
-        <v>91592.68</v>
+        <v>96448.06</v>
       </c>
       <c r="L36" s="3">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="M36" s="3">
-        <v>28586.7</v>
+        <v>29577.3</v>
       </c>
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>3116</v>
+        <v>3690</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>3117</v>
+        <v>3691</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>3118</v>
+        <v>3692</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>3119</v>
+        <v>3693</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>3120</v>
+        <v>3694</v>
       </c>
       <c r="F37" s="3">
         <v>1374896.6</v>
       </c>
       <c r="G37" s="3">
-        <v>1108340.03</v>
+        <v>1196555.47</v>
       </c>
       <c r="H37" s="3">
-        <v>93670.91</v>
+        <v>2990.6</v>
       </c>
       <c r="I37" s="3">
-        <v>1202010.94</v>
+        <v>1199546.07</v>
       </c>
       <c r="J37" s="3">
-        <v>87.43</v>
+        <v>87.25</v>
       </c>
       <c r="K37" s="3">
-        <v>-172885.66</v>
+        <v>-175350.53</v>
       </c>
       <c r="L37" s="3">
-        <v>3.13</v>
+        <v>3.59</v>
       </c>
       <c r="M37" s="3">
-        <v>37639.5</v>
+        <v>43094.97</v>
       </c>
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>3121</v>
+        <v>3695</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>3122</v>
+        <v>3696</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>3123</v>
+        <v>3697</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>3124</v>
+        <v>3698</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>3125</v>
+        <v>3699</v>
       </c>
       <c r="F38" s="3">
         <v>904558.95</v>
       </c>
       <c r="G38" s="3">
-        <v>863685.14</v>
+        <v>906029.61</v>
       </c>
       <c r="H38" s="3">
-        <v>43154.47</v>
+        <v>1289.72</v>
       </c>
       <c r="I38" s="3">
-        <v>906839.61</v>
+        <v>907319.33</v>
       </c>
       <c r="J38" s="3">
-        <v>100.25</v>
+        <v>100.31</v>
       </c>
       <c r="K38" s="3">
-        <v>2280.66</v>
+        <v>2760.38</v>
       </c>
       <c r="L38" s="3">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="M38" s="3">
-        <v>22258.61</v>
+        <v>23068.61</v>
       </c>
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>3126</v>
+        <v>3700</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>3127</v>
+        <v>3701</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>3128</v>
+        <v>3702</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>3129</v>
+        <v>3703</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>3130</v>
+        <v>3704</v>
       </c>
       <c r="F39" s="3">
         <v>1106940.64</v>
       </c>
       <c r="G39" s="3">
-        <v>797158.58</v>
+        <v>843722.5</v>
       </c>
       <c r="H39" s="3">
-        <v>47814.8</v>
+        <v>4016.48</v>
       </c>
       <c r="I39" s="3">
-        <v>844973.38</v>
+        <v>847738.98</v>
       </c>
       <c r="J39" s="3">
-        <v>76.33</v>
+        <v>76.58</v>
       </c>
       <c r="K39" s="3">
-        <v>-261967.26</v>
+        <v>-259201.66</v>
       </c>
       <c r="L39" s="3">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="M39" s="3">
-        <v>26877.41</v>
+        <v>28128.29</v>
       </c>
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>3131</v>
+        <v>3705</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>3132</v>
+        <v>3706</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>3133</v>
+        <v>3707</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>3134</v>
+        <v>3708</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>3135</v>
+        <v>3709</v>
       </c>
       <c r="F40" s="3">
         <v>887573.45</v>
       </c>
       <c r="G40" s="3">
-        <v>595721.97</v>
+        <v>638994.52</v>
       </c>
       <c r="H40" s="3">
-        <v>79758.01</v>
+        <v>74540.29</v>
       </c>
       <c r="I40" s="3">
-        <v>675479.98</v>
+        <v>713534.81</v>
       </c>
       <c r="J40" s="3">
-        <v>76.1</v>
+        <v>80.39</v>
       </c>
       <c r="K40" s="3">
-        <v>-212093.47</v>
+        <v>-174038.64</v>
       </c>
       <c r="L40" s="3">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="M40" s="3">
-        <v>7363.39</v>
+        <v>9269.82</v>
       </c>
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>3136</v>
+        <v>3710</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>3137</v>
+        <v>3711</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>3138</v>
+        <v>3712</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>3139</v>
+        <v>3713</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>3140</v>
+        <v>3714</v>
       </c>
       <c r="F41" s="3">
-        <v>1043081.21</v>
+        <v>1236217.2</v>
       </c>
       <c r="G41" s="3">
-        <v>961464.47</v>
+        <v>891448.78</v>
       </c>
       <c r="H41" s="3">
-        <v>120162.6</v>
+        <v>128957.41</v>
       </c>
       <c r="I41" s="3">
-        <v>1081627.07</v>
+        <v>1020406.19</v>
       </c>
       <c r="J41" s="3">
-        <v>103.7</v>
+        <v>82.54</v>
       </c>
       <c r="K41" s="3">
-        <v>38545.86</v>
+        <v>-215811.01</v>
       </c>
       <c r="L41" s="3">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="M41" s="3">
-        <v>23111.7</v>
+        <v>31589.7</v>
       </c>
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>3141</v>
+        <v>3715</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>3142</v>
+        <v>3716</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>3143</v>
+        <v>3717</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>3144</v>
+        <v>3718</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>3145</v>
+        <v>3719</v>
       </c>
       <c r="F42" s="3">
         <v>912015.93</v>
       </c>
       <c r="G42" s="3">
-        <v>697279.24</v>
+        <v>775151.29</v>
       </c>
       <c r="H42" s="3">
-        <v>122534.91</v>
+        <v>97952.88</v>
       </c>
       <c r="I42" s="3">
-        <v>819814.15</v>
+        <v>873104.17</v>
       </c>
       <c r="J42" s="3">
-        <v>89.89</v>
+        <v>95.73</v>
       </c>
       <c r="K42" s="3">
-        <v>-92201.78</v>
+        <v>-38911.76</v>
       </c>
       <c r="L42" s="3">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="M42" s="3">
-        <v>16972.68</v>
+        <v>22234.76</v>
       </c>
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>3146</v>
+        <v>3720</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>3147</v>
+        <v>3721</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>3148</v>
+        <v>3722</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>3149</v>
+        <v>3723</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>3150</v>
+        <v>3724</v>
       </c>
       <c r="F43" s="3">
-        <v>1236217.2</v>
+        <v>1043081.21</v>
       </c>
       <c r="G43" s="3">
-        <v>823191.81</v>
+        <v>1042914.54</v>
       </c>
       <c r="H43" s="3">
-        <v>138738.63</v>
+        <v>110919.27</v>
       </c>
       <c r="I43" s="3">
-        <v>961930.44</v>
+        <v>1153833.81</v>
       </c>
       <c r="J43" s="3">
-        <v>77.81</v>
+        <v>110.62</v>
       </c>
       <c r="K43" s="3">
-        <v>-274286.76</v>
+        <v>110752.6</v>
       </c>
       <c r="L43" s="3">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="M43" s="3">
-        <v>29359.82</v>
+        <v>24211.54</v>
       </c>
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>3151</v>
+        <v>3725</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>3152</v>
+        <v>3726</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>3153</v>
+        <v>3727</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>3154</v>
+        <v>3728</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>3155</v>
+        <v>3729</v>
       </c>
       <c r="F44" s="3">
         <v>1113507.9</v>
@@ -31379,19 +36257,19 @@
         <v>953689.92</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0</v>
+        <v>117276.5</v>
       </c>
       <c r="I44" s="3">
-        <v>953689.92</v>
+        <v>1070966.42</v>
       </c>
       <c r="J44" s="3">
-        <v>85.65</v>
+        <v>96.18</v>
       </c>
       <c r="K44" s="3">
-        <v>-159817.98</v>
+        <v>-42541.48</v>
       </c>
       <c r="L44" s="3">
-        <v>2.66</v>
+        <v>2.37</v>
       </c>
       <c r="M44" s="3">
         <v>25364.88</v>
@@ -31399,142 +36277,142 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>3156</v>
+        <v>3730</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>3157</v>
+        <v>3731</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>3158</v>
+        <v>3732</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>3159</v>
+        <v>3733</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>3160</v>
+        <v>3734</v>
       </c>
       <c r="F45" s="3">
-        <v>1066780.42</v>
+        <v>918319.81</v>
       </c>
       <c r="G45" s="3">
-        <v>962983.14</v>
+        <v>889388.08</v>
       </c>
       <c r="H45" s="3">
-        <v>0.0</v>
+        <v>92479.56</v>
       </c>
       <c r="I45" s="3">
-        <v>962983.14</v>
+        <v>981867.64</v>
       </c>
       <c r="J45" s="3">
-        <v>90.27</v>
+        <v>106.92</v>
       </c>
       <c r="K45" s="3">
-        <v>-103797.28</v>
+        <v>63547.83</v>
       </c>
       <c r="L45" s="3">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="M45" s="3">
-        <v>21738.48</v>
+        <v>17481.66</v>
       </c>
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>3161</v>
+        <v>3735</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>3162</v>
+        <v>3736</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>3163</v>
+        <v>3737</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>3164</v>
+        <v>3738</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>3165</v>
+        <v>3739</v>
       </c>
       <c r="F46" s="3">
-        <v>918319.81</v>
+        <v>1066780.42</v>
       </c>
       <c r="G46" s="3">
-        <v>889388.08</v>
+        <v>962983.14</v>
       </c>
       <c r="H46" s="3">
-        <v>0.0</v>
+        <v>111006.01</v>
       </c>
       <c r="I46" s="3">
-        <v>889388.08</v>
+        <v>1073989.15</v>
       </c>
       <c r="J46" s="3">
-        <v>96.85</v>
+        <v>100.68</v>
       </c>
       <c r="K46" s="3">
-        <v>-28931.73</v>
+        <v>7208.73</v>
       </c>
       <c r="L46" s="3">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="M46" s="3">
-        <v>17481.66</v>
+        <v>21738.48</v>
       </c>
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>3166</v>
+        <v>3740</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>3167</v>
+        <v>3741</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>3168</v>
+        <v>3742</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>3169</v>
+        <v>3743</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>3170</v>
+        <v>3744</v>
       </c>
       <c r="F47" s="3">
-        <v>972020.19</v>
+        <v>1336954.46</v>
       </c>
       <c r="G47" s="3">
-        <v>771853.61</v>
+        <v>864778.92</v>
       </c>
       <c r="H47" s="3">
-        <v>0.0</v>
+        <v>92191.71</v>
       </c>
       <c r="I47" s="3">
-        <v>771853.61</v>
+        <v>956970.63</v>
       </c>
       <c r="J47" s="3">
-        <v>79.41</v>
+        <v>71.58</v>
       </c>
       <c r="K47" s="3">
-        <v>-200166.58</v>
+        <v>-379983.83</v>
       </c>
       <c r="L47" s="3">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="M47" s="3">
-        <v>22049.22</v>
+        <v>29094.57</v>
       </c>
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>3171</v>
+        <v>3745</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>3172</v>
+        <v>3746</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>3173</v>
+        <v>3747</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>3174</v>
+        <v>3748</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>3175</v>
+        <v>3749</v>
       </c>
       <c r="F48" s="3">
         <v>1022376.56</v>
@@ -31543,19 +36421,19 @@
         <v>649753.47</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0</v>
+        <v>88429.8</v>
       </c>
       <c r="I48" s="3">
-        <v>649753.47</v>
+        <v>738183.27</v>
       </c>
       <c r="J48" s="3">
-        <v>63.55</v>
+        <v>72.2</v>
       </c>
       <c r="K48" s="3">
-        <v>-372623.09</v>
+        <v>-284193.29</v>
       </c>
       <c r="L48" s="3">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="M48" s="3">
         <v>22729.34</v>
@@ -31563,166 +36441,166 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>3176</v>
+        <v>3750</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>3177</v>
+        <v>3751</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>3178</v>
+        <v>3752</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>3179</v>
+        <v>3753</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>3180</v>
+        <v>3754</v>
       </c>
       <c r="F49" s="3">
-        <v>1336954.46</v>
+        <v>972020.19</v>
       </c>
       <c r="G49" s="3">
-        <v>864778.92</v>
+        <v>771853.61</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0</v>
+        <v>116010.92</v>
       </c>
       <c r="I49" s="3">
-        <v>864778.92</v>
+        <v>887864.53</v>
       </c>
       <c r="J49" s="3">
-        <v>64.68</v>
+        <v>91.34</v>
       </c>
       <c r="K49" s="3">
-        <v>-472175.54</v>
+        <v>-84155.66</v>
       </c>
       <c r="L49" s="3">
-        <v>3.36</v>
+        <v>2.48</v>
       </c>
       <c r="M49" s="3">
-        <v>29094.57</v>
+        <v>22049.22</v>
       </c>
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>3181</v>
+        <v>3755</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>3182</v>
+        <v>3756</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>3183</v>
+        <v>3757</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>3184</v>
+        <v>3758</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>3185</v>
+        <v>3759</v>
       </c>
       <c r="F50" s="3">
-        <v>954958.72</v>
+        <v>963790.11</v>
       </c>
       <c r="G50" s="3">
-        <v>844607.91</v>
+        <v>774813.88</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0</v>
+        <v>117534.11</v>
       </c>
       <c r="I50" s="3">
-        <v>844607.91</v>
+        <v>892347.99</v>
       </c>
       <c r="J50" s="3">
-        <v>88.44</v>
+        <v>92.59</v>
       </c>
       <c r="K50" s="3">
-        <v>-110350.81</v>
+        <v>-71442.12</v>
       </c>
       <c r="L50" s="3">
-        <v>3.64</v>
+        <v>4.41</v>
       </c>
       <c r="M50" s="3">
-        <v>30735.02</v>
+        <v>39336.87</v>
       </c>
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>3186</v>
+        <v>3760</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>3187</v>
+        <v>3761</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>3188</v>
+        <v>3762</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>3189</v>
+        <v>3763</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>3190</v>
+        <v>3764</v>
       </c>
       <c r="F51" s="3">
-        <v>1154949.94</v>
+        <v>954958.72</v>
       </c>
       <c r="G51" s="3">
-        <v>918689.07</v>
+        <v>844607.91</v>
       </c>
       <c r="H51" s="3">
-        <v>0.0</v>
+        <v>82005.2</v>
       </c>
       <c r="I51" s="3">
-        <v>918689.07</v>
+        <v>926613.11</v>
       </c>
       <c r="J51" s="3">
-        <v>79.54</v>
+        <v>97.03</v>
       </c>
       <c r="K51" s="3">
-        <v>-236260.87</v>
+        <v>-28345.61</v>
       </c>
       <c r="L51" s="3">
-        <v>6.7</v>
+        <v>3.32</v>
       </c>
       <c r="M51" s="3">
-        <v>61575.16</v>
+        <v>30735.02</v>
       </c>
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>3191</v>
+        <v>3765</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>3192</v>
+        <v>3766</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>3193</v>
+        <v>3767</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>3194</v>
+        <v>3768</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>3195</v>
+        <v>3769</v>
       </c>
       <c r="F52" s="3">
-        <v>963790.11</v>
+        <v>1154949.94</v>
       </c>
       <c r="G52" s="3">
-        <v>774813.88</v>
+        <v>918689.07</v>
       </c>
       <c r="H52" s="3">
-        <v>0.0</v>
+        <v>72336.06</v>
       </c>
       <c r="I52" s="3">
-        <v>774813.88</v>
+        <v>991025.13</v>
       </c>
       <c r="J52" s="3">
-        <v>80.39</v>
+        <v>85.81</v>
       </c>
       <c r="K52" s="3">
-        <v>-188976.23</v>
+        <v>-163924.81</v>
       </c>
       <c r="L52" s="3">
-        <v>5.08</v>
+        <v>6.21</v>
       </c>
       <c r="M52" s="3">
-        <v>39336.87</v>
+        <v>61575.16</v>
       </c>
     </row>
   </sheetData>
@@ -31732,7 +36610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -31782,282 +36660,282 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>3196</v>
+        <v>3483</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3197</v>
+        <v>3484</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3198</v>
+        <v>3485</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3199</v>
+        <v>3486</v>
       </c>
       <c r="E2" s="3">
         <v>5936775.24</v>
       </c>
       <c r="F2" s="3">
-        <v>5120228.97</v>
+        <v>5393787.71</v>
       </c>
       <c r="G2" s="3">
-        <v>278089.33</v>
+        <v>430052.89</v>
       </c>
       <c r="H2" s="3">
-        <v>5398318.3</v>
+        <v>5823840.6</v>
       </c>
       <c r="I2" s="3">
-        <v>90.93</v>
+        <v>98.1</v>
       </c>
       <c r="J2" s="3">
-        <v>-538456.94</v>
+        <v>-112934.64</v>
       </c>
       <c r="K2" s="3">
-        <v>136781.39</v>
+        <v>144338.65</v>
       </c>
       <c r="L2" s="3">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>3200</v>
+        <v>3487</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3201</v>
+        <v>3488</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3202</v>
+        <v>3489</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>3203</v>
+        <v>3490</v>
       </c>
       <c r="E3" s="3">
         <v>3346888.02</v>
       </c>
       <c r="F3" s="3">
-        <v>2745949.41</v>
+        <v>2909410.41</v>
       </c>
       <c r="G3" s="3">
-        <v>123244.66</v>
+        <v>150937.46</v>
       </c>
       <c r="H3" s="3">
-        <v>2869194.07</v>
+        <v>3060347.87</v>
       </c>
       <c r="I3" s="3">
-        <v>85.73</v>
+        <v>91.44</v>
       </c>
       <c r="J3" s="3">
-        <v>-477693.95</v>
+        <v>-286540.15</v>
       </c>
       <c r="K3" s="3">
-        <v>68472.12</v>
+        <v>72634.93</v>
       </c>
       <c r="L3" s="3">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>3204</v>
+        <v>3491</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3205</v>
+        <v>3492</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3206</v>
+        <v>3493</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>3207</v>
+        <v>3494</v>
       </c>
       <c r="E4" s="3">
         <v>6248074.42</v>
       </c>
       <c r="F4" s="3">
-        <v>4706013.38</v>
+        <v>4927706.71</v>
       </c>
       <c r="G4" s="3">
-        <v>229757.82</v>
+        <v>53098.95</v>
       </c>
       <c r="H4" s="3">
-        <v>4935771.2</v>
+        <v>4980805.66</v>
       </c>
       <c r="I4" s="3">
-        <v>79.0</v>
+        <v>79.72</v>
       </c>
       <c r="J4" s="3">
-        <v>-1312303.22</v>
+        <v>-1267268.76</v>
       </c>
       <c r="K4" s="3">
-        <v>192346.78</v>
+        <v>200627.14</v>
       </c>
       <c r="L4" s="3">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>3208</v>
+        <v>3495</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>3209</v>
+        <v>3496</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3210</v>
+        <v>3497</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>3211</v>
+        <v>3498</v>
       </c>
       <c r="E5" s="3">
         <v>7225829.17</v>
       </c>
       <c r="F5" s="3">
-        <v>6541331.2</v>
+        <v>6951620.25</v>
       </c>
       <c r="G5" s="3">
-        <v>453019.68</v>
+        <v>203736.07</v>
       </c>
       <c r="H5" s="3">
-        <v>6994350.88</v>
+        <v>7155356.32</v>
       </c>
       <c r="I5" s="3">
-        <v>96.8</v>
+        <v>99.02</v>
       </c>
       <c r="J5" s="3">
-        <v>-231478.29</v>
+        <v>-70472.85</v>
       </c>
       <c r="K5" s="3">
-        <v>179308.04</v>
+        <v>189332.59</v>
       </c>
       <c r="L5" s="3">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>3212</v>
+        <v>3499</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>3213</v>
+        <v>3500</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3214</v>
+        <v>3501</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>3215</v>
+        <v>3502</v>
       </c>
       <c r="E6" s="3">
         <v>6938999.79</v>
       </c>
       <c r="F6" s="3">
-        <v>6202415.92</v>
+        <v>6569668.43</v>
       </c>
       <c r="G6" s="3">
-        <v>380318.41</v>
+        <v>95158.85</v>
       </c>
       <c r="H6" s="3">
-        <v>6582734.33</v>
+        <v>6664827.28</v>
       </c>
       <c r="I6" s="3">
-        <v>94.87</v>
+        <v>96.05</v>
       </c>
       <c r="J6" s="3">
-        <v>-356265.46</v>
+        <v>-274172.51</v>
       </c>
       <c r="K6" s="3">
-        <v>224919.36</v>
+        <v>238143.58</v>
       </c>
       <c r="L6" s="3">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>3216</v>
+        <v>3503</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>3217</v>
+        <v>3504</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>3218</v>
+        <v>3505</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>3219</v>
+        <v>3506</v>
       </c>
       <c r="E7" s="3">
         <v>4536967.52</v>
       </c>
       <c r="F7" s="3">
-        <v>3932458.4</v>
+        <v>4187480.99</v>
       </c>
       <c r="G7" s="3">
-        <v>263529.54</v>
+        <v>14142.78</v>
       </c>
       <c r="H7" s="3">
-        <v>4195987.94</v>
+        <v>4201623.77</v>
       </c>
       <c r="I7" s="3">
-        <v>92.48</v>
+        <v>92.61</v>
       </c>
       <c r="J7" s="3">
-        <v>-340979.58</v>
+        <v>-335343.75</v>
       </c>
       <c r="K7" s="3">
-        <v>115362.22</v>
+        <v>123869.17</v>
       </c>
       <c r="L7" s="3">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>3220</v>
+        <v>3507</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>3221</v>
+        <v>3508</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>3222</v>
+        <v>3509</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>3223</v>
+        <v>3510</v>
       </c>
       <c r="E8" s="3">
         <v>7177495.92</v>
       </c>
       <c r="F8" s="3">
-        <v>5883718.63</v>
+        <v>6154570.27</v>
       </c>
       <c r="G8" s="3">
-        <v>461194.15</v>
+        <v>733131.92</v>
       </c>
       <c r="H8" s="3">
-        <v>6344912.78</v>
+        <v>6887702.19</v>
       </c>
       <c r="I8" s="3">
-        <v>88.4</v>
+        <v>95.96</v>
       </c>
       <c r="J8" s="3">
-        <v>-832583.14</v>
+        <v>-289793.73</v>
       </c>
       <c r="K8" s="3">
-        <v>141392.61</v>
+        <v>151890.84</v>
       </c>
       <c r="L8" s="3">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>3224</v>
+        <v>3511</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>3225</v>
+        <v>3512</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>3226</v>
+        <v>3513</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>3227</v>
+        <v>3514</v>
       </c>
       <c r="E9" s="3">
         <v>6405049.98</v>
@@ -32066,22 +36944,22 @@
         <v>4824496.86</v>
       </c>
       <c r="G9" s="3">
-        <v>0.0</v>
+        <v>568507.8</v>
       </c>
       <c r="H9" s="3">
-        <v>4824496.86</v>
+        <v>5393004.66</v>
       </c>
       <c r="I9" s="3">
-        <v>75.32</v>
+        <v>84.2</v>
       </c>
       <c r="J9" s="3">
-        <v>-1580553.12</v>
+        <v>-1012045.32</v>
       </c>
       <c r="K9" s="3">
         <v>205520.18</v>
       </c>
       <c r="L9" s="3">
-        <v>4.26</v>
+        <v>3.81</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="territory-wise-MPE-sales-achiev" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6044" count="6044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6060" count="6060">
   <si>
     <t>Region</t>
   </si>
@@ -54646,6 +54646,150 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>July'26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Aug'26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Total Product</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>BPL Product</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rx Share (%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Total Product</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>BPL Product</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rx Share (%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>July'26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Aug'26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Value Share (%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Value Share (%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>July'26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Aug'26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Value Share (%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Value Share (%)</t>
     </r>
   </si>
 </sst>
@@ -54660,7 +54804,7 @@
     <numFmt numFmtId="10" formatCode="0.00%"/>
     <numFmt numFmtId="2" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -54678,6 +54822,10 @@
     <font>
       <name val="Calibri"/>
       <b/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
     <font>
@@ -54729,7 +54877,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -54753,13 +54901,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -54780,7 +54921,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -54793,26 +54934,17 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
@@ -54820,43 +54952,70 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
@@ -55154,7 +55313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ397"/>
+  <dimension ref="A1:AK397"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -61631,7 +61790,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AE36"/>
+  <dimension ref="A1:AF36"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -62729,3475 +62888,5303 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Z78"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
+  <cols>
+    <col min="9" max="9" customWidth="1" width="5.8984375" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="13" ht="24.95" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="8:8" ht="16.25">
+      <c r="J1" s="13" t="s">
+        <v>6044</v>
+      </c>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13" t="s">
+        <v>6045</v>
+      </c>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+    </row>
+    <row r="2" spans="8:8" s="14" ht="24.85" customFormat="1">
+      <c r="A2" s="15" t="s">
         <v>4793</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>4794</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>4795</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D2" s="15" t="s">
         <v>4796</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>4797</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>4798</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>4799</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H2" s="17" t="s">
         <v>4800</v>
       </c>
+      <c r="J2" s="18" t="s">
+        <v>6046</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>6047</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>6048</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>6049</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>6050</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>6051</v>
+      </c>
     </row>
-    <row r="2" spans="8:8">
-      <c r="A2" s="17" t="s">
+    <row r="3" spans="8:8" ht="16.25">
+      <c r="A3" s="20" t="s">
         <v>3787</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B3" s="20" t="s">
         <v>3788</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C3" s="21" t="s">
         <v>3789</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D3" s="21" t="s">
         <v>3790</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E3" s="21" t="s">
         <v>3791</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F3" s="22">
         <v>2966.0</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G3" s="22">
         <v>273.0</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H3" s="23">
         <v>0.09204315576534053</v>
       </c>
+      <c r="J3" s="24">
+        <v>10812.0</v>
+      </c>
+      <c r="K3" s="24">
+        <v>938.0</v>
+      </c>
+      <c r="L3" s="25">
+        <v>0.08675545689974103</v>
+      </c>
+      <c r="M3" s="24">
+        <v>11092.0</v>
+      </c>
+      <c r="N3" s="24">
+        <v>1021.0</v>
+      </c>
+      <c r="O3" s="25">
+        <v>0.09204832311575911</v>
+      </c>
     </row>
-    <row r="3" spans="8:8">
-      <c r="A3" s="17" t="s">
+    <row r="4" spans="8:8" ht="24.85">
+      <c r="A4" s="20" t="s">
         <v>3792</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B4" s="20" t="s">
         <v>3793</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C4" s="26" t="s">
         <v>3794</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D4" s="26" t="s">
         <v>3795</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E4" s="26" t="s">
         <v>3796</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F4" s="22">
         <v>698.0</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G4" s="22">
         <v>45.0</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H4" s="23">
         <v>0.06446991404011461</v>
       </c>
-    </row>
-    <row r="4" spans="8:8">
-      <c r="A4" s="17" t="s">
-        <v>3797</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>3798</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>3799</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>3800</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>3801</v>
-      </c>
-      <c r="F4" s="19">
-        <v>56.0</v>
-      </c>
-      <c r="G4" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="H4" s="20">
-        <v>0.017857142857142856</v>
+      <c r="J4" s="24">
+        <v>3158.0</v>
+      </c>
+      <c r="K4" s="24">
+        <v>271.0</v>
+      </c>
+      <c r="L4" s="25">
+        <v>0.08581380620645979</v>
+      </c>
+      <c r="M4" s="24">
+        <v>3358.0</v>
+      </c>
+      <c r="N4" s="24">
+        <v>307.0</v>
+      </c>
+      <c r="O4" s="25">
+        <v>0.09142346634901727</v>
       </c>
     </row>
     <row r="5" spans="8:8">
-      <c r="A5" s="17" t="s">
-        <v>3802</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>3803</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>3804</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>3805</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>3806</v>
-      </c>
-      <c r="F5" s="19">
-        <v>11.75</v>
-      </c>
-      <c r="G5" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="20">
-        <v>0.0</v>
+      <c r="A5" s="20" t="s">
+        <v>3797</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>3798</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>3799</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>3800</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>3801</v>
+      </c>
+      <c r="F5" s="22">
+        <v>56.0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="J5" s="24">
+        <v>640.0</v>
+      </c>
+      <c r="K5" s="24">
+        <v>55.0</v>
+      </c>
+      <c r="L5" s="25">
+        <v>0.0859375</v>
+      </c>
+      <c r="M5" s="24">
+        <v>409.0</v>
+      </c>
+      <c r="N5" s="24">
+        <v>41.0</v>
+      </c>
+      <c r="O5" s="25">
+        <v>0.10024449877750612</v>
       </c>
     </row>
     <row r="6" spans="8:8">
-      <c r="A6" s="17" t="s">
-        <v>3807</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>3808</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>3809</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>3810</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>3811</v>
-      </c>
-      <c r="F6" s="19">
-        <v>10.75</v>
-      </c>
-      <c r="G6" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="H6" s="20">
-        <v>0.09302325581395349</v>
+      <c r="A6" s="20" t="s">
+        <v>3802</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>3803</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>3804</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>3805</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>3806</v>
+      </c>
+      <c r="F6" s="22">
+        <v>11.75</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="24">
+        <v>153.75</v>
+      </c>
+      <c r="K6" s="24">
+        <v>17.0</v>
+      </c>
+      <c r="L6" s="25">
+        <v>0.11056910569105691</v>
+      </c>
+      <c r="M6" s="24">
+        <v>101.25</v>
+      </c>
+      <c r="N6" s="24">
+        <v>9.0</v>
+      </c>
+      <c r="O6" s="25">
+        <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="7" spans="8:8">
-      <c r="A7" s="17" t="s">
-        <v>3812</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>3813</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>3814</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>3815</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>3816</v>
-      </c>
-      <c r="F7" s="19">
-        <v>12.75</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="20">
-        <v>0.0</v>
+      <c r="A7" s="20" t="s">
+        <v>3807</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>3808</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>3809</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>3810</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>3811</v>
+      </c>
+      <c r="F7" s="22">
+        <v>10.75</v>
+      </c>
+      <c r="G7" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="23">
+        <v>0.09302325581395349</v>
+      </c>
+      <c r="J7" s="24">
+        <v>98.25</v>
+      </c>
+      <c r="K7" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="L7" s="25">
+        <v>0.11195928753180662</v>
+      </c>
+      <c r="M7" s="24">
+        <v>54.75</v>
+      </c>
+      <c r="N7" s="24">
+        <v>6.0</v>
+      </c>
+      <c r="O7" s="25">
+        <v>0.1095890410958904</v>
       </c>
     </row>
     <row r="8" spans="8:8">
-      <c r="A8" s="17" t="s">
-        <v>3817</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>3818</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>3819</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>3820</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>3821</v>
-      </c>
-      <c r="F8" s="19">
-        <v>20.75</v>
-      </c>
-      <c r="G8" s="19">
+      <c r="A8" s="20" t="s">
+        <v>3812</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>3813</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>3814</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>3815</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>3816</v>
+      </c>
+      <c r="F8" s="22">
+        <v>12.75</v>
+      </c>
+      <c r="G8" s="22">
         <v>0.0</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="23">
         <v>0.0</v>
+      </c>
+      <c r="J8" s="24">
+        <v>149.75</v>
+      </c>
+      <c r="K8" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="L8" s="25">
+        <v>0.07345575959933222</v>
+      </c>
+      <c r="M8" s="24">
+        <v>117.75</v>
+      </c>
+      <c r="N8" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="O8" s="25">
+        <v>0.12738853503184713</v>
       </c>
     </row>
     <row r="9" spans="8:8">
-      <c r="A9" s="17" t="s">
-        <v>3822</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>3823</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>3824</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>3825</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>3826</v>
-      </c>
-      <c r="F9" s="19">
-        <v>642.0</v>
-      </c>
-      <c r="G9" s="19">
-        <v>44.0</v>
-      </c>
-      <c r="H9" s="20">
-        <v>0.06853582554517133</v>
+      <c r="A9" s="20" t="s">
+        <v>3817</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>3818</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>3819</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>3820</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>3821</v>
+      </c>
+      <c r="F9" s="22">
+        <v>20.75</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="24">
+        <v>238.25</v>
+      </c>
+      <c r="K9" s="24">
+        <v>16.0</v>
+      </c>
+      <c r="L9" s="25">
+        <v>0.06715634837355719</v>
+      </c>
+      <c r="M9" s="24">
+        <v>135.25</v>
+      </c>
+      <c r="N9" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="O9" s="25">
+        <v>0.08133086876155268</v>
       </c>
     </row>
     <row r="10" spans="8:8">
-      <c r="A10" s="17" t="s">
-        <v>3827</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>3828</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>3829</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>3830</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>3831</v>
-      </c>
-      <c r="F10" s="19">
-        <v>182.5</v>
-      </c>
-      <c r="G10" s="19">
-        <v>16.0</v>
-      </c>
-      <c r="H10" s="20">
-        <v>0.08767123287671233</v>
+      <c r="A10" s="20" t="s">
+        <v>3822</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>3823</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>3824</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>3825</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>3826</v>
+      </c>
+      <c r="F10" s="22">
+        <v>642.0</v>
+      </c>
+      <c r="G10" s="22">
+        <v>44.0</v>
+      </c>
+      <c r="H10" s="23">
+        <v>0.06853582554517133</v>
+      </c>
+      <c r="J10" s="24">
+        <v>2518.0</v>
+      </c>
+      <c r="K10" s="24">
+        <v>216.0</v>
+      </c>
+      <c r="L10" s="25">
+        <v>0.0857823669579031</v>
+      </c>
+      <c r="M10" s="24">
+        <v>2949.0</v>
+      </c>
+      <c r="N10" s="24">
+        <v>266.0</v>
+      </c>
+      <c r="O10" s="25">
+        <v>0.09020006781959987</v>
       </c>
     </row>
     <row r="11" spans="8:8">
-      <c r="A11" s="17" t="s">
-        <v>3832</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>3833</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>3834</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>3835</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>3836</v>
-      </c>
-      <c r="F11" s="19">
-        <v>95.5</v>
-      </c>
-      <c r="G11" s="19">
-        <v>10.0</v>
-      </c>
-      <c r="H11" s="20">
-        <v>0.10471204188481675</v>
+      <c r="A11" s="20" t="s">
+        <v>3827</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>3828</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>3829</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>3830</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>3831</v>
+      </c>
+      <c r="F11" s="22">
+        <v>182.5</v>
+      </c>
+      <c r="G11" s="22">
+        <v>16.0</v>
+      </c>
+      <c r="H11" s="23">
+        <v>0.08767123287671233</v>
+      </c>
+      <c r="J11" s="24">
+        <v>727.5</v>
+      </c>
+      <c r="K11" s="24">
+        <v>82.0</v>
+      </c>
+      <c r="L11" s="25">
+        <v>0.11271477663230241</v>
+      </c>
+      <c r="M11" s="24">
+        <v>878.75</v>
+      </c>
+      <c r="N11" s="24">
+        <v>114.0</v>
+      </c>
+      <c r="O11" s="25">
+        <v>0.12972972972972974</v>
       </c>
     </row>
     <row r="12" spans="8:8">
-      <c r="A12" s="17" t="s">
-        <v>3837</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>3838</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>3839</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>3840</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>3841</v>
-      </c>
-      <c r="F12" s="19">
-        <v>139.0</v>
-      </c>
-      <c r="G12" s="19">
-        <v>5.0</v>
-      </c>
-      <c r="H12" s="20">
-        <v>0.03597122302158273</v>
+      <c r="A12" s="20" t="s">
+        <v>3832</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>3833</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>3834</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>3835</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>3836</v>
+      </c>
+      <c r="F12" s="22">
+        <v>95.5</v>
+      </c>
+      <c r="G12" s="22">
+        <v>10.0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>0.10471204188481675</v>
+      </c>
+      <c r="J12" s="24">
+        <v>362.5</v>
+      </c>
+      <c r="K12" s="24">
+        <v>46.0</v>
+      </c>
+      <c r="L12" s="25">
+        <v>0.12689655172413794</v>
+      </c>
+      <c r="M12" s="24">
+        <v>421.25</v>
+      </c>
+      <c r="N12" s="24">
+        <v>54.0</v>
+      </c>
+      <c r="O12" s="25">
+        <v>0.1281899109792285</v>
       </c>
     </row>
     <row r="13" spans="8:8">
-      <c r="A13" s="17" t="s">
-        <v>3842</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>3843</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>3844</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>3845</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>3846</v>
-      </c>
-      <c r="F13" s="19">
-        <v>225.0</v>
-      </c>
-      <c r="G13" s="19">
-        <v>13.0</v>
-      </c>
-      <c r="H13" s="20">
-        <v>0.057777777777777775</v>
+      <c r="A13" s="20" t="s">
+        <v>3837</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>3838</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>3839</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>3840</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>3841</v>
+      </c>
+      <c r="F13" s="22">
+        <v>139.0</v>
+      </c>
+      <c r="G13" s="22">
+        <v>5.0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>0.03597122302158273</v>
+      </c>
+      <c r="J13" s="24">
+        <v>602.0</v>
+      </c>
+      <c r="K13" s="24">
+        <v>31.0</v>
+      </c>
+      <c r="L13" s="25">
+        <v>0.05149501661129568</v>
+      </c>
+      <c r="M13" s="24">
+        <v>662.75</v>
+      </c>
+      <c r="N13" s="24">
+        <v>31.0</v>
+      </c>
+      <c r="O13" s="25">
+        <v>0.046774801961523955</v>
       </c>
     </row>
     <row r="14" spans="8:8">
-      <c r="A14" s="17" t="s">
-        <v>3847</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>3848</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>3849</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>3850</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>3851</v>
-      </c>
-      <c r="F14" s="19">
-        <v>301.0</v>
-      </c>
-      <c r="G14" s="19">
-        <v>17.0</v>
-      </c>
-      <c r="H14" s="20">
-        <v>0.05647840531561462</v>
+      <c r="A14" s="20" t="s">
+        <v>3842</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>3843</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>3845</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>3846</v>
+      </c>
+      <c r="F14" s="22">
+        <v>225.0</v>
+      </c>
+      <c r="G14" s="22">
+        <v>13.0</v>
+      </c>
+      <c r="H14" s="23">
+        <v>0.057777777777777775</v>
+      </c>
+      <c r="J14" s="24">
+        <v>826.0</v>
+      </c>
+      <c r="K14" s="24">
+        <v>57.0</v>
+      </c>
+      <c r="L14" s="25">
+        <v>0.06900726392251816</v>
+      </c>
+      <c r="M14" s="24">
+        <v>986.25</v>
+      </c>
+      <c r="N14" s="24">
+        <v>67.0</v>
+      </c>
+      <c r="O14" s="25">
+        <v>0.0679340937896071</v>
       </c>
     </row>
     <row r="15" spans="8:8">
-      <c r="A15" s="17" t="s">
-        <v>3852</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>3853</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>3854</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>3855</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>3856</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="A15" s="20" t="s">
+        <v>3847</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>3848</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>3849</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>3850</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>3851</v>
+      </c>
+      <c r="F15" s="22">
         <v>301.0</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="22">
         <v>17.0</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="23">
         <v>0.05647840531561462</v>
+      </c>
+      <c r="J15" s="24">
+        <v>1008.0</v>
+      </c>
+      <c r="K15" s="24">
+        <v>56.0</v>
+      </c>
+      <c r="L15" s="25">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="M15" s="24">
+        <v>931.0</v>
+      </c>
+      <c r="N15" s="24">
+        <v>72.0</v>
+      </c>
+      <c r="O15" s="25">
+        <v>0.07733619763694952</v>
       </c>
     </row>
     <row r="16" spans="8:8">
-      <c r="A16" s="17" t="s">
-        <v>3857</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>3858</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>3859</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>3860</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>3861</v>
-      </c>
-      <c r="F16" s="19">
-        <v>84.75</v>
-      </c>
-      <c r="G16" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="H16" s="20">
-        <v>0.02359882005899705</v>
+      <c r="A16" s="20" t="s">
+        <v>3852</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>3853</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>3854</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>3855</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>3856</v>
+      </c>
+      <c r="F16" s="22">
+        <v>301.0</v>
+      </c>
+      <c r="G16" s="22">
+        <v>17.0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>0.05647840531561462</v>
+      </c>
+      <c r="J16" s="24">
+        <v>1008.0</v>
+      </c>
+      <c r="K16" s="24">
+        <v>56.0</v>
+      </c>
+      <c r="L16" s="25">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="M16" s="24">
+        <v>931.0</v>
+      </c>
+      <c r="N16" s="24">
+        <v>72.0</v>
+      </c>
+      <c r="O16" s="25">
+        <v>0.07733619763694952</v>
       </c>
     </row>
     <row r="17" spans="8:8">
-      <c r="A17" s="17" t="s">
-        <v>3862</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>3863</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>3864</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>3865</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>3866</v>
-      </c>
-      <c r="F17" s="19">
-        <v>50.25</v>
-      </c>
-      <c r="G17" s="19">
-        <v>7.0</v>
-      </c>
-      <c r="H17" s="20">
-        <v>0.13930348258706468</v>
+      <c r="A17" s="20" t="s">
+        <v>3857</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>3858</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>3859</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>3860</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>3861</v>
+      </c>
+      <c r="F17" s="22">
+        <v>84.75</v>
+      </c>
+      <c r="G17" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H17" s="23">
+        <v>0.02359882005899705</v>
+      </c>
+      <c r="J17" s="24">
+        <v>265.5</v>
+      </c>
+      <c r="K17" s="24">
+        <v>16.0</v>
+      </c>
+      <c r="L17" s="25">
+        <v>0.060263653483992465</v>
+      </c>
+      <c r="M17" s="24">
+        <v>231.75</v>
+      </c>
+      <c r="N17" s="24">
+        <v>17.0</v>
+      </c>
+      <c r="O17" s="25">
+        <v>0.07335490830636461</v>
       </c>
     </row>
     <row r="18" spans="8:8">
-      <c r="A18" s="17" t="s">
-        <v>3867</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>3868</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>3869</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>3870</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>3871</v>
-      </c>
-      <c r="F18" s="19">
-        <v>68.25</v>
-      </c>
-      <c r="G18" s="19">
-        <v>6.0</v>
-      </c>
-      <c r="H18" s="20">
-        <v>0.08791208791208792</v>
+      <c r="A18" s="20" t="s">
+        <v>3862</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>3863</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>3864</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>3865</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>3866</v>
+      </c>
+      <c r="F18" s="22">
+        <v>50.25</v>
+      </c>
+      <c r="G18" s="22">
+        <v>7.0</v>
+      </c>
+      <c r="H18" s="23">
+        <v>0.13930348258706468</v>
+      </c>
+      <c r="J18" s="24">
+        <v>162.5</v>
+      </c>
+      <c r="K18" s="24">
+        <v>13.0</v>
+      </c>
+      <c r="L18" s="25">
+        <v>0.08</v>
+      </c>
+      <c r="M18" s="24">
+        <v>165.75</v>
+      </c>
+      <c r="N18" s="24">
+        <v>19.0</v>
+      </c>
+      <c r="O18" s="25">
+        <v>0.11463046757164404</v>
       </c>
     </row>
     <row r="19" spans="8:8">
-      <c r="A19" s="17" t="s">
-        <v>3872</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>3873</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>3874</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>3875</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>3876</v>
-      </c>
-      <c r="F19" s="19">
-        <v>97.75</v>
-      </c>
-      <c r="G19" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="H19" s="20">
-        <v>0.020460358056265986</v>
+      <c r="A19" s="20" t="s">
+        <v>3867</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>3868</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>3870</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>3871</v>
+      </c>
+      <c r="F19" s="22">
+        <v>68.25</v>
+      </c>
+      <c r="G19" s="22">
+        <v>6.0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>0.08791208791208792</v>
+      </c>
+      <c r="J19" s="24">
+        <v>212.0</v>
+      </c>
+      <c r="K19" s="24">
+        <v>9.0</v>
+      </c>
+      <c r="L19" s="25">
+        <v>0.04245283018867924</v>
+      </c>
+      <c r="M19" s="24">
+        <v>208.75</v>
+      </c>
+      <c r="N19" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="O19" s="25">
+        <v>0.0718562874251497</v>
       </c>
     </row>
     <row r="20" spans="8:8">
-      <c r="A20" s="17" t="s">
-        <v>3877</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>3878</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>3879</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>3880</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>3881</v>
-      </c>
-      <c r="F20" s="19">
-        <v>73.0</v>
-      </c>
-      <c r="G20" s="19">
-        <v>5.0</v>
-      </c>
-      <c r="H20" s="20">
-        <v>0.0684931506849315</v>
+      <c r="A20" s="20" t="s">
+        <v>3872</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>3873</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>3874</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>3875</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>3876</v>
+      </c>
+      <c r="F20" s="22">
+        <v>97.75</v>
+      </c>
+      <c r="G20" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>0.020460358056265986</v>
+      </c>
+      <c r="J20" s="24">
+        <v>368.0</v>
+      </c>
+      <c r="K20" s="24">
+        <v>18.0</v>
+      </c>
+      <c r="L20" s="25">
+        <v>0.04891304347826087</v>
+      </c>
+      <c r="M20" s="24">
+        <v>324.75</v>
+      </c>
+      <c r="N20" s="24">
+        <v>21.0</v>
+      </c>
+      <c r="O20" s="25">
+        <v>0.06466512702078522</v>
       </c>
     </row>
     <row r="21" spans="8:8">
-      <c r="A21" s="17" t="s">
-        <v>3882</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>3883</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>3884</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>3885</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>3886</v>
-      </c>
-      <c r="F21" s="19">
+      <c r="A21" s="20" t="s">
+        <v>3877</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>3878</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>3879</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>3880</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>3881</v>
+      </c>
+      <c r="F21" s="22">
         <v>73.0</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="22">
         <v>5.0</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="23">
         <v>0.0684931506849315</v>
+      </c>
+      <c r="J21" s="24">
+        <v>495.0</v>
+      </c>
+      <c r="K21" s="24">
+        <v>37.0</v>
+      </c>
+      <c r="L21" s="25">
+        <v>0.07474747474747474</v>
+      </c>
+      <c r="M21" s="24">
+        <v>399.0</v>
+      </c>
+      <c r="N21" s="24">
+        <v>31.0</v>
+      </c>
+      <c r="O21" s="25">
+        <v>0.07769423558897243</v>
       </c>
     </row>
     <row r="22" spans="8:8">
-      <c r="A22" s="17" t="s">
-        <v>3887</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>3888</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>3889</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>3890</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>3891</v>
-      </c>
-      <c r="F22" s="19">
-        <v>17.5</v>
-      </c>
-      <c r="G22" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="H22" s="20">
-        <v>0.11428571428571428</v>
+      <c r="A22" s="20" t="s">
+        <v>3882</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>3883</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>3884</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>3885</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>3886</v>
+      </c>
+      <c r="F22" s="22">
+        <v>73.0</v>
+      </c>
+      <c r="G22" s="22">
+        <v>5.0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>0.0684931506849315</v>
+      </c>
+      <c r="J22" s="24">
+        <v>495.0</v>
+      </c>
+      <c r="K22" s="24">
+        <v>37.0</v>
+      </c>
+      <c r="L22" s="25">
+        <v>0.07474747474747474</v>
+      </c>
+      <c r="M22" s="24">
+        <v>392.0</v>
+      </c>
+      <c r="N22" s="24">
+        <v>31.0</v>
+      </c>
+      <c r="O22" s="25">
+        <v>0.07908163265306123</v>
       </c>
     </row>
     <row r="23" spans="8:8">
-      <c r="A23" s="17" t="s">
-        <v>3892</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>3893</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>3894</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>3895</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>3896</v>
-      </c>
-      <c r="F23" s="19">
-        <v>14.0</v>
-      </c>
-      <c r="G23" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="20">
-        <v>0.0</v>
+      <c r="A23" s="20" t="s">
+        <v>3887</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>3888</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>3889</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>3890</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>3891</v>
+      </c>
+      <c r="F23" s="22">
+        <v>17.5</v>
+      </c>
+      <c r="G23" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="J23" s="24">
+        <v>140.5</v>
+      </c>
+      <c r="K23" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="L23" s="25">
+        <v>0.07829181494661921</v>
+      </c>
+      <c r="M23" s="24">
+        <v>108.75</v>
+      </c>
+      <c r="N23" s="24">
+        <v>9.0</v>
+      </c>
+      <c r="O23" s="25">
+        <v>0.08275862068965517</v>
       </c>
     </row>
     <row r="24" spans="8:8">
-      <c r="A24" s="17" t="s">
-        <v>3897</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>3898</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>3899</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>3900</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>3901</v>
-      </c>
-      <c r="F24" s="19">
-        <v>11.5</v>
-      </c>
-      <c r="G24" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="H24" s="20">
-        <v>0.17391304347826086</v>
+      <c r="A24" s="20" t="s">
+        <v>3892</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>3893</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>3895</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>3896</v>
+      </c>
+      <c r="F24" s="22">
+        <v>14.0</v>
+      </c>
+      <c r="G24" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J24" s="24">
+        <v>87.5</v>
+      </c>
+      <c r="K24" s="24">
+        <v>12.0</v>
+      </c>
+      <c r="L24" s="25">
+        <v>0.13714285714285715</v>
+      </c>
+      <c r="M24" s="24">
+        <v>63.75</v>
+      </c>
+      <c r="N24" s="24">
+        <v>12.0</v>
+      </c>
+      <c r="O24" s="25">
+        <v>0.18823529411764706</v>
       </c>
     </row>
     <row r="25" spans="8:8">
-      <c r="A25" s="17" t="s">
-        <v>3902</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>3903</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>3904</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>3905</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>3906</v>
-      </c>
-      <c r="F25" s="19">
-        <v>30.0</v>
-      </c>
-      <c r="G25" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="H25" s="20">
-        <v>0.03333333333333333</v>
+      <c r="A25" s="20" t="s">
+        <v>3897</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>3898</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>3899</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>3900</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>3901</v>
+      </c>
+      <c r="F25" s="22">
+        <v>11.5</v>
+      </c>
+      <c r="G25" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H25" s="23">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="J25" s="24">
+        <v>101.0</v>
+      </c>
+      <c r="K25" s="24">
+        <v>6.0</v>
+      </c>
+      <c r="L25" s="25">
+        <v>0.0594059405940594</v>
+      </c>
+      <c r="M25" s="24">
+        <v>77.75</v>
+      </c>
+      <c r="N25" s="24">
+        <v>6.0</v>
+      </c>
+      <c r="O25" s="25">
+        <v>0.07717041800643087</v>
       </c>
     </row>
     <row r="26" spans="8:8">
-      <c r="A26" s="17" t="s">
-        <v>3907</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>3908</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>3909</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>3910</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>3911</v>
-      </c>
-      <c r="F26" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="G26" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="20">
-        <v>0.0</v>
+      <c r="A26" s="20" t="s">
+        <v>3902</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>3903</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>3904</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>3905</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>3906</v>
+      </c>
+      <c r="F26" s="22">
+        <v>30.0</v>
+      </c>
+      <c r="G26" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="H26" s="23">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="J26" s="24">
+        <v>166.0</v>
+      </c>
+      <c r="K26" s="24">
+        <v>8.0</v>
+      </c>
+      <c r="L26" s="25">
+        <v>0.04819277108433735</v>
+      </c>
+      <c r="M26" s="24">
+        <v>141.75</v>
+      </c>
+      <c r="N26" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="O26" s="25">
+        <v>0.02821869488536155</v>
       </c>
     </row>
     <row r="27" spans="8:8">
-      <c r="A27" s="17" t="s">
-        <v>3912</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>3913</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>3914</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>3915</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>3916</v>
-      </c>
-      <c r="F27" s="19">
+      <c r="A27" s="20" t="s">
+        <v>3907</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>3908</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>3909</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>3910</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>3911</v>
+      </c>
+      <c r="F27" s="22">
         <v>0.0</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="22">
         <v>0.0</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J27" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="M27" s="24">
+        <v>7.0</v>
+      </c>
+      <c r="N27" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="28" spans="8:8">
-      <c r="A28" s="17" t="s">
-        <v>3917</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>3918</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>3919</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>3920</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>3921</v>
-      </c>
-      <c r="F28" s="19">
+      <c r="A28" s="20" t="s">
+        <v>3912</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>3913</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>3914</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>3915</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>3916</v>
+      </c>
+      <c r="F28" s="22">
         <v>0.0</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="22">
         <v>0.0</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J28" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="M28" s="24">
+        <v>2.0</v>
+      </c>
+      <c r="N28" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="29" spans="8:8">
-      <c r="A29" s="17" t="s">
-        <v>3922</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>3923</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>3924</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>3925</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>3926</v>
-      </c>
-      <c r="F29" s="19">
+      <c r="A29" s="20" t="s">
+        <v>3917</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>3918</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>3919</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>3920</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>3921</v>
+      </c>
+      <c r="F29" s="22">
         <v>0.0</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="22">
         <v>0.0</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J29" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="M29" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="N29" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="30" spans="8:8">
-      <c r="A30" s="17" t="s">
-        <v>3927</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>3928</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>3929</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>3930</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>3931</v>
-      </c>
-      <c r="F30" s="19">
-        <v>513.0</v>
-      </c>
-      <c r="G30" s="19">
-        <v>49.0</v>
-      </c>
-      <c r="H30" s="20">
-        <v>0.09551656920077972</v>
+      <c r="A30" s="20" t="s">
+        <v>3922</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>3923</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>3924</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>3925</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>3926</v>
+      </c>
+      <c r="F30" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J30" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="M30" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="N30" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="25">
+        <v>0.0</v>
       </c>
     </row>
     <row r="31" spans="8:8">
-      <c r="A31" s="17" t="s">
-        <v>3932</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>3933</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>3934</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>3935</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>3936</v>
-      </c>
-      <c r="F31" s="19">
-        <v>396.0</v>
-      </c>
-      <c r="G31" s="19">
-        <v>43.0</v>
-      </c>
-      <c r="H31" s="20">
-        <v>0.10858585858585859</v>
+      <c r="A31" s="20" t="s">
+        <v>3927</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>3928</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>3929</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>3930</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>3931</v>
+      </c>
+      <c r="F31" s="22">
+        <v>513.0</v>
+      </c>
+      <c r="G31" s="22">
+        <v>49.0</v>
+      </c>
+      <c r="H31" s="23">
+        <v>0.09551656920077972</v>
+      </c>
+      <c r="J31" s="24">
+        <v>2095.0</v>
+      </c>
+      <c r="K31" s="24">
+        <v>184.0</v>
+      </c>
+      <c r="L31" s="25">
+        <v>0.08782816229116945</v>
+      </c>
+      <c r="M31" s="24">
+        <v>1776.0</v>
+      </c>
+      <c r="N31" s="24">
+        <v>149.0</v>
+      </c>
+      <c r="O31" s="25">
+        <v>0.0838963963963964</v>
       </c>
     </row>
     <row r="32" spans="8:8">
-      <c r="A32" s="17" t="s">
-        <v>3937</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>3938</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>3939</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>3940</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>3941</v>
-      </c>
-      <c r="F32" s="19">
-        <v>116.25</v>
-      </c>
-      <c r="G32" s="19">
-        <v>10.0</v>
-      </c>
-      <c r="H32" s="20">
-        <v>0.08602150537634409</v>
+      <c r="A32" s="20" t="s">
+        <v>3932</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>3933</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>3934</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>3935</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>3936</v>
+      </c>
+      <c r="F32" s="22">
+        <v>396.0</v>
+      </c>
+      <c r="G32" s="22">
+        <v>43.0</v>
+      </c>
+      <c r="H32" s="23">
+        <v>0.10858585858585859</v>
+      </c>
+      <c r="J32" s="24">
+        <v>1549.0</v>
+      </c>
+      <c r="K32" s="24">
+        <v>142.0</v>
+      </c>
+      <c r="L32" s="25">
+        <v>0.09167204648160103</v>
+      </c>
+      <c r="M32" s="24">
+        <v>1387.0</v>
+      </c>
+      <c r="N32" s="24">
+        <v>103.0</v>
+      </c>
+      <c r="O32" s="25">
+        <v>0.07426099495313626</v>
       </c>
     </row>
     <row r="33" spans="8:8">
-      <c r="A33" s="17" t="s">
-        <v>3942</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>3943</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>3944</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>3945</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>3946</v>
-      </c>
-      <c r="F33" s="19">
-        <v>55.75</v>
-      </c>
-      <c r="G33" s="19">
+      <c r="A33" s="20" t="s">
+        <v>3937</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>3938</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>3939</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>3940</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>3941</v>
+      </c>
+      <c r="F33" s="22">
+        <v>116.25</v>
+      </c>
+      <c r="G33" s="22">
         <v>10.0</v>
       </c>
-      <c r="H33" s="20">
-        <v>0.17937219730941703</v>
+      <c r="H33" s="23">
+        <v>0.08602150537634409</v>
+      </c>
+      <c r="J33" s="24">
+        <v>430.75</v>
+      </c>
+      <c r="K33" s="24">
+        <v>40.0</v>
+      </c>
+      <c r="L33" s="25">
+        <v>0.09286128845037725</v>
+      </c>
+      <c r="M33" s="24">
+        <v>381.25</v>
+      </c>
+      <c r="N33" s="24">
+        <v>23.0</v>
+      </c>
+      <c r="O33" s="25">
+        <v>0.06032786885245902</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="A34" s="17" t="s">
-        <v>3947</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>3948</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>3949</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>3950</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>3951</v>
-      </c>
-      <c r="F34" s="19">
-        <v>90.25</v>
-      </c>
-      <c r="G34" s="19">
-        <v>7.0</v>
-      </c>
-      <c r="H34" s="20">
-        <v>0.07756232686980609</v>
+      <c r="A34" s="20" t="s">
+        <v>3942</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>3943</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>3944</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>3945</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>3946</v>
+      </c>
+      <c r="F34" s="22">
+        <v>55.75</v>
+      </c>
+      <c r="G34" s="22">
+        <v>10.0</v>
+      </c>
+      <c r="H34" s="23">
+        <v>0.17937219730941703</v>
+      </c>
+      <c r="J34" s="24">
+        <v>243.25</v>
+      </c>
+      <c r="K34" s="24">
+        <v>40.0</v>
+      </c>
+      <c r="L34" s="25">
+        <v>0.1644398766700925</v>
+      </c>
+      <c r="M34" s="24">
+        <v>221.25</v>
+      </c>
+      <c r="N34" s="24">
+        <v>30.0</v>
+      </c>
+      <c r="O34" s="25">
+        <v>0.13559322033898305</v>
       </c>
     </row>
     <row r="35" spans="8:8">
-      <c r="A35" s="17" t="s">
-        <v>3952</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>3953</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>3954</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>3955</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>3956</v>
-      </c>
-      <c r="F35" s="19">
-        <v>133.75</v>
-      </c>
-      <c r="G35" s="19">
-        <v>16.0</v>
-      </c>
-      <c r="H35" s="20">
-        <v>0.11962616822429907</v>
+      <c r="A35" s="20" t="s">
+        <v>3947</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>3948</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>3949</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>3950</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>3951</v>
+      </c>
+      <c r="F35" s="22">
+        <v>90.25</v>
+      </c>
+      <c r="G35" s="22">
+        <v>7.0</v>
+      </c>
+      <c r="H35" s="23">
+        <v>0.07756232686980609</v>
+      </c>
+      <c r="J35" s="24">
+        <v>356.25</v>
+      </c>
+      <c r="K35" s="24">
+        <v>24.0</v>
+      </c>
+      <c r="L35" s="25">
+        <v>0.06736842105263158</v>
+      </c>
+      <c r="M35" s="24">
+        <v>318.25</v>
+      </c>
+      <c r="N35" s="24">
+        <v>20.0</v>
+      </c>
+      <c r="O35" s="25">
+        <v>0.06284367635506677</v>
       </c>
     </row>
     <row r="36" spans="8:8">
-      <c r="A36" s="17" t="s">
-        <v>3957</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>3958</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>3959</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>3960</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>3961</v>
-      </c>
-      <c r="F36" s="19">
-        <v>117.0</v>
-      </c>
-      <c r="G36" s="19">
-        <v>6.0</v>
-      </c>
-      <c r="H36" s="20">
-        <v>0.05128205128205128</v>
+      <c r="A36" s="20" t="s">
+        <v>3952</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>3953</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>3954</v>
+      </c>
+      <c r="D36" s="27" t="s">
+        <v>3955</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>3956</v>
+      </c>
+      <c r="F36" s="22">
+        <v>133.75</v>
+      </c>
+      <c r="G36" s="22">
+        <v>16.0</v>
+      </c>
+      <c r="H36" s="23">
+        <v>0.11962616822429907</v>
+      </c>
+      <c r="J36" s="24">
+        <v>518.75</v>
+      </c>
+      <c r="K36" s="24">
+        <v>38.0</v>
+      </c>
+      <c r="L36" s="25">
+        <v>0.07325301204819278</v>
+      </c>
+      <c r="M36" s="24">
+        <v>466.25</v>
+      </c>
+      <c r="N36" s="24">
+        <v>30.0</v>
+      </c>
+      <c r="O36" s="25">
+        <v>0.064343163538874</v>
       </c>
     </row>
     <row r="37" spans="8:8">
-      <c r="A37" s="17" t="s">
-        <v>3962</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>3963</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>3964</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>3965</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>3966</v>
-      </c>
-      <c r="F37" s="19">
-        <v>26.25</v>
-      </c>
-      <c r="G37" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="H37" s="20">
-        <v>0.0380952380952381</v>
+      <c r="A37" s="20" t="s">
+        <v>3957</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>3958</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>3959</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>3960</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>3961</v>
+      </c>
+      <c r="F37" s="22">
+        <v>117.0</v>
+      </c>
+      <c r="G37" s="22">
+        <v>6.0</v>
+      </c>
+      <c r="H37" s="23">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="J37" s="24">
+        <v>546.0</v>
+      </c>
+      <c r="K37" s="24">
+        <v>42.0</v>
+      </c>
+      <c r="L37" s="25">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="M37" s="24">
+        <v>389.0</v>
+      </c>
+      <c r="N37" s="24">
+        <v>46.0</v>
+      </c>
+      <c r="O37" s="25">
+        <v>0.11825192802056556</v>
       </c>
     </row>
     <row r="38" spans="8:8">
-      <c r="A38" s="17" t="s">
-        <v>3967</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>3968</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>3969</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>3970</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>3971</v>
-      </c>
-      <c r="F38" s="19">
-        <v>14.25</v>
-      </c>
-      <c r="G38" s="19">
+      <c r="A38" s="20" t="s">
+        <v>3962</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>3963</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>3964</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>3965</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>3966</v>
+      </c>
+      <c r="F38" s="22">
+        <v>26.25</v>
+      </c>
+      <c r="G38" s="22">
         <v>1.0</v>
       </c>
-      <c r="H38" s="20">
-        <v>0.07017543859649122</v>
+      <c r="H38" s="23">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="J38" s="24">
+        <v>143.25</v>
+      </c>
+      <c r="K38" s="24">
+        <v>17.0</v>
+      </c>
+      <c r="L38" s="25">
+        <v>0.11867364746945899</v>
+      </c>
+      <c r="M38" s="24">
+        <v>99.25</v>
+      </c>
+      <c r="N38" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="O38" s="25">
+        <v>0.15113350125944586</v>
       </c>
     </row>
     <row r="39" spans="8:8">
-      <c r="A39" s="17" t="s">
-        <v>3972</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>3973</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>3974</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>3975</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>3976</v>
-      </c>
-      <c r="F39" s="19">
-        <v>28.25</v>
-      </c>
-      <c r="G39" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="H39" s="20">
-        <v>0.07079646017699115</v>
+      <c r="A39" s="20" t="s">
+        <v>3967</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>3968</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>3969</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>3970</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>3971</v>
+      </c>
+      <c r="F39" s="22">
+        <v>14.25</v>
+      </c>
+      <c r="G39" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="H39" s="23">
+        <v>0.07017543859649122</v>
+      </c>
+      <c r="J39" s="24">
+        <v>81.25</v>
+      </c>
+      <c r="K39" s="24">
+        <v>7.0</v>
+      </c>
+      <c r="L39" s="25">
+        <v>0.08615384615384615</v>
+      </c>
+      <c r="M39" s="24">
+        <v>63.75</v>
+      </c>
+      <c r="N39" s="24">
+        <v>12.0</v>
+      </c>
+      <c r="O39" s="25">
+        <v>0.18823529411764706</v>
       </c>
     </row>
     <row r="40" spans="8:8">
-      <c r="A40" s="17" t="s">
-        <v>3977</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>3978</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>3979</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>3980</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>3981</v>
-      </c>
-      <c r="F40" s="19">
-        <v>48.25</v>
-      </c>
-      <c r="G40" s="19">
+      <c r="A40" s="20" t="s">
+        <v>3972</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>3973</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>3974</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>3976</v>
+      </c>
+      <c r="F40" s="22">
+        <v>28.25</v>
+      </c>
+      <c r="G40" s="22">
         <v>2.0</v>
       </c>
-      <c r="H40" s="20">
-        <v>0.04145077720207254</v>
+      <c r="H40" s="23">
+        <v>0.07079646017699115</v>
+      </c>
+      <c r="J40" s="24">
+        <v>117.25</v>
+      </c>
+      <c r="K40" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="L40" s="25">
+        <v>0.03411513859275053</v>
+      </c>
+      <c r="M40" s="24">
+        <v>88.75</v>
+      </c>
+      <c r="N40" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="O40" s="25">
+        <v>0.056338028169014086</v>
       </c>
     </row>
     <row r="41" spans="8:8">
-      <c r="A41" s="17" t="s">
-        <v>3982</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>3983</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>3984</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>3985</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>3986</v>
-      </c>
-      <c r="F41" s="19">
-        <v>403.0</v>
-      </c>
-      <c r="G41" s="19">
-        <v>50.0</v>
-      </c>
-      <c r="H41" s="20">
-        <v>0.12406947890818859</v>
+      <c r="A41" s="20" t="s">
+        <v>3977</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>3978</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>3979</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>3980</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>3981</v>
+      </c>
+      <c r="F41" s="22">
+        <v>48.25</v>
+      </c>
+      <c r="G41" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H41" s="23">
+        <v>0.04145077720207254</v>
+      </c>
+      <c r="J41" s="24">
+        <v>204.25</v>
+      </c>
+      <c r="K41" s="24">
+        <v>14.0</v>
+      </c>
+      <c r="L41" s="25">
+        <v>0.06854345165238677</v>
+      </c>
+      <c r="M41" s="24">
+        <v>137.25</v>
+      </c>
+      <c r="N41" s="24">
+        <v>14.0</v>
+      </c>
+      <c r="O41" s="25">
+        <v>0.10200364298724955</v>
       </c>
     </row>
     <row r="42" spans="8:8">
-      <c r="A42" s="17" t="s">
-        <v>3987</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>3988</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>3989</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>3990</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>3991</v>
-      </c>
-      <c r="F42" s="19">
-        <v>85.0</v>
-      </c>
-      <c r="G42" s="19">
-        <v>12.0</v>
-      </c>
-      <c r="H42" s="20">
-        <v>0.1411764705882353</v>
+      <c r="A42" s="20" t="s">
+        <v>3982</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>3983</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>3984</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>3985</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>3986</v>
+      </c>
+      <c r="F42" s="22">
+        <v>403.0</v>
+      </c>
+      <c r="G42" s="22">
+        <v>50.0</v>
+      </c>
+      <c r="H42" s="23">
+        <v>0.12406947890818859</v>
+      </c>
+      <c r="J42" s="24">
+        <v>1468.0</v>
+      </c>
+      <c r="K42" s="24">
+        <v>124.0</v>
+      </c>
+      <c r="L42" s="25">
+        <v>0.08446866485013624</v>
+      </c>
+      <c r="M42" s="24">
+        <v>1163.0</v>
+      </c>
+      <c r="N42" s="24">
+        <v>92.0</v>
+      </c>
+      <c r="O42" s="25">
+        <v>0.07910576096302666</v>
       </c>
     </row>
     <row r="43" spans="8:8">
-      <c r="A43" s="17" t="s">
-        <v>3992</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>3993</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>3994</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>3995</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>3996</v>
-      </c>
-      <c r="F43" s="19">
-        <v>25.5</v>
-      </c>
-      <c r="G43" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="H43" s="20">
-        <v>0.11764705882352941</v>
+      <c r="A43" s="20" t="s">
+        <v>3987</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>3988</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>3989</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>3990</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>3991</v>
+      </c>
+      <c r="F43" s="22">
+        <v>85.0</v>
+      </c>
+      <c r="G43" s="22">
+        <v>12.0</v>
+      </c>
+      <c r="H43" s="23">
+        <v>0.1411764705882353</v>
+      </c>
+      <c r="J43" s="24">
+        <v>861.0</v>
+      </c>
+      <c r="K43" s="24">
+        <v>81.0</v>
+      </c>
+      <c r="L43" s="25">
+        <v>0.09407665505226481</v>
+      </c>
+      <c r="M43" s="24">
+        <v>666.0</v>
+      </c>
+      <c r="N43" s="24">
+        <v>58.0</v>
+      </c>
+      <c r="O43" s="25">
+        <v>0.08708708708708708</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="A44" s="17" t="s">
-        <v>3997</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>3998</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>3999</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>4000</v>
-      </c>
-      <c r="E44" s="22" t="s">
-        <v>4001</v>
-      </c>
-      <c r="F44" s="19">
-        <v>10.0</v>
-      </c>
-      <c r="G44" s="19">
-        <v>4.0</v>
-      </c>
-      <c r="H44" s="20">
-        <v>0.4</v>
+      <c r="A44" s="20" t="s">
+        <v>3992</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>3993</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>3994</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>3995</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>3996</v>
+      </c>
+      <c r="F44" s="22">
+        <v>25.5</v>
+      </c>
+      <c r="G44" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="H44" s="23">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="J44" s="24">
+        <v>210.0</v>
+      </c>
+      <c r="K44" s="24">
+        <v>18.0</v>
+      </c>
+      <c r="L44" s="25">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="M44" s="24">
+        <v>183.0</v>
+      </c>
+      <c r="N44" s="24">
+        <v>13.0</v>
+      </c>
+      <c r="O44" s="25">
+        <v>0.07103825136612021</v>
       </c>
     </row>
     <row r="45" spans="8:8">
-      <c r="A45" s="17" t="s">
-        <v>4002</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>4003</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>4004</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>4005</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>4006</v>
-      </c>
-      <c r="F45" s="19">
-        <v>17.5</v>
-      </c>
-      <c r="G45" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="H45" s="20">
-        <v>0.17142857142857143</v>
+      <c r="A45" s="20" t="s">
+        <v>3997</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>3998</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>3999</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>4000</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>4001</v>
+      </c>
+      <c r="F45" s="22">
+        <v>10.0</v>
+      </c>
+      <c r="G45" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="H45" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="J45" s="24">
+        <v>120.0</v>
+      </c>
+      <c r="K45" s="24">
+        <v>28.0</v>
+      </c>
+      <c r="L45" s="25">
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="M45" s="24">
+        <v>85.5</v>
+      </c>
+      <c r="N45" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="O45" s="25">
+        <v>0.17543859649122806</v>
       </c>
     </row>
     <row r="46" spans="8:8">
-      <c r="A46" s="17" t="s">
-        <v>4007</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>4008</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>4009</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>4010</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>4011</v>
-      </c>
-      <c r="F46" s="19">
-        <v>32.0</v>
-      </c>
-      <c r="G46" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="H46" s="20">
-        <v>0.0625</v>
+      <c r="A46" s="20" t="s">
+        <v>4002</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>4003</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>4004</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>4005</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>4006</v>
+      </c>
+      <c r="F46" s="22">
+        <v>17.5</v>
+      </c>
+      <c r="G46" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="H46" s="23">
+        <v>0.17142857142857143</v>
+      </c>
+      <c r="J46" s="24">
+        <v>185.0</v>
+      </c>
+      <c r="K46" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="L46" s="25">
+        <v>0.021621621621621623</v>
+      </c>
+      <c r="M46" s="24">
+        <v>141.0</v>
+      </c>
+      <c r="N46" s="24">
+        <v>10.0</v>
+      </c>
+      <c r="O46" s="25">
+        <v>0.07092198581560284</v>
       </c>
     </row>
     <row r="47" spans="8:8">
-      <c r="A47" s="17" t="s">
-        <v>4012</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>4013</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>4014</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>4015</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>4016</v>
-      </c>
-      <c r="F47" s="19">
-        <v>318.0</v>
-      </c>
-      <c r="G47" s="19">
-        <v>38.0</v>
-      </c>
-      <c r="H47" s="20">
-        <v>0.11949685534591195</v>
+      <c r="A47" s="20" t="s">
+        <v>4007</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>4008</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>4009</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>4010</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>4011</v>
+      </c>
+      <c r="F47" s="22">
+        <v>32.0</v>
+      </c>
+      <c r="G47" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H47" s="23">
+        <v>0.0625</v>
+      </c>
+      <c r="J47" s="24">
+        <v>346.0</v>
+      </c>
+      <c r="K47" s="24">
+        <v>31.0</v>
+      </c>
+      <c r="L47" s="25">
+        <v>0.08959537572254335</v>
+      </c>
+      <c r="M47" s="24">
+        <v>256.5</v>
+      </c>
+      <c r="N47" s="24">
+        <v>20.0</v>
+      </c>
+      <c r="O47" s="25">
+        <v>0.07797270955165692</v>
       </c>
     </row>
     <row r="48" spans="8:8">
-      <c r="A48" s="17" t="s">
-        <v>4017</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>4018</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>4019</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>4020</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>4021</v>
-      </c>
-      <c r="F48" s="19">
-        <v>100.0</v>
-      </c>
-      <c r="G48" s="19">
-        <v>10.0</v>
-      </c>
-      <c r="H48" s="20">
-        <v>0.1</v>
+      <c r="A48" s="20" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>4014</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>4015</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>4016</v>
+      </c>
+      <c r="F48" s="22">
+        <v>318.0</v>
+      </c>
+      <c r="G48" s="22">
+        <v>38.0</v>
+      </c>
+      <c r="H48" s="23">
+        <v>0.11949685534591195</v>
+      </c>
+      <c r="J48" s="24">
+        <v>607.0</v>
+      </c>
+      <c r="K48" s="24">
+        <v>43.0</v>
+      </c>
+      <c r="L48" s="25">
+        <v>0.07084019769357495</v>
+      </c>
+      <c r="M48" s="24">
+        <v>497.0</v>
+      </c>
+      <c r="N48" s="24">
+        <v>34.0</v>
+      </c>
+      <c r="O48" s="25">
+        <v>0.06841046277665996</v>
       </c>
     </row>
     <row r="49" spans="8:8">
-      <c r="A49" s="17" t="s">
-        <v>4022</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>4023</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>4024</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>4025</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>4026</v>
-      </c>
-      <c r="F49" s="19">
-        <v>89.0</v>
-      </c>
-      <c r="G49" s="19">
-        <v>8.0</v>
-      </c>
-      <c r="H49" s="20">
-        <v>0.0898876404494382</v>
+      <c r="A49" s="20" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>4018</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>4019</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>4020</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>4021</v>
+      </c>
+      <c r="F49" s="22">
+        <v>100.0</v>
+      </c>
+      <c r="G49" s="22">
+        <v>10.0</v>
+      </c>
+      <c r="H49" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="J49" s="24">
+        <v>172.83333333333334</v>
+      </c>
+      <c r="K49" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="L49" s="25">
+        <v>0.06364513018322082</v>
+      </c>
+      <c r="M49" s="24">
+        <v>138.0</v>
+      </c>
+      <c r="N49" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="O49" s="25">
+        <v>0.07971014492753623</v>
       </c>
     </row>
     <row r="50" spans="8:8">
-      <c r="A50" s="17" t="s">
-        <v>4027</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>4028</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>4029</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>4030</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>4031</v>
-      </c>
-      <c r="F50" s="19">
-        <v>129.0</v>
-      </c>
-      <c r="G50" s="19">
-        <v>20.0</v>
-      </c>
-      <c r="H50" s="20">
-        <v>0.15503875968992248</v>
+      <c r="A50" s="20" t="s">
+        <v>4022</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>4023</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>4024</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>4025</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>4026</v>
+      </c>
+      <c r="F50" s="22">
+        <v>89.0</v>
+      </c>
+      <c r="G50" s="22">
+        <v>8.0</v>
+      </c>
+      <c r="H50" s="23">
+        <v>0.0898876404494382</v>
+      </c>
+      <c r="J50" s="24">
+        <v>186.83333333333334</v>
+      </c>
+      <c r="K50" s="24">
+        <v>17.0</v>
+      </c>
+      <c r="L50" s="25">
+        <v>0.09099018733273863</v>
+      </c>
+      <c r="M50" s="24">
+        <v>148.0</v>
+      </c>
+      <c r="N50" s="24">
+        <v>7.0</v>
+      </c>
+      <c r="O50" s="25">
+        <v>0.0472972972972973</v>
       </c>
     </row>
     <row r="51" spans="8:8">
-      <c r="A51" s="17" t="s">
-        <v>4032</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>4033</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>4034</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>4035</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>4036</v>
-      </c>
-      <c r="F51" s="19">
-        <v>350.0</v>
-      </c>
-      <c r="G51" s="19">
-        <v>38.0</v>
-      </c>
-      <c r="H51" s="20">
-        <v>0.10857142857142857</v>
+      <c r="A51" s="20" t="s">
+        <v>4027</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>4028</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>4029</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>4030</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>4031</v>
+      </c>
+      <c r="F51" s="22">
+        <v>129.0</v>
+      </c>
+      <c r="G51" s="22">
+        <v>20.0</v>
+      </c>
+      <c r="H51" s="23">
+        <v>0.15503875968992248</v>
+      </c>
+      <c r="J51" s="24">
+        <v>247.33333333333334</v>
+      </c>
+      <c r="K51" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="L51" s="25">
+        <v>0.060646900269541774</v>
+      </c>
+      <c r="M51" s="24">
+        <v>211.0</v>
+      </c>
+      <c r="N51" s="24">
+        <v>16.0</v>
+      </c>
+      <c r="O51" s="25">
+        <v>0.07582938388625593</v>
       </c>
     </row>
     <row r="52" spans="8:8">
-      <c r="A52" s="17" t="s">
-        <v>4037</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>4038</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>4039</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>4040</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>4041</v>
-      </c>
-      <c r="F52" s="19">
+      <c r="A52" s="20" t="s">
+        <v>4032</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>4033</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>4034</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>4035</v>
+      </c>
+      <c r="E52" s="26" t="s">
+        <v>4036</v>
+      </c>
+      <c r="F52" s="22">
         <v>350.0</v>
       </c>
-      <c r="G52" s="19">
+      <c r="G52" s="22">
         <v>38.0</v>
       </c>
-      <c r="H52" s="20">
+      <c r="H52" s="23">
         <v>0.10857142857142857</v>
+      </c>
+      <c r="J52" s="24">
+        <v>782.0</v>
+      </c>
+      <c r="K52" s="24">
+        <v>75.0</v>
+      </c>
+      <c r="L52" s="25">
+        <v>0.0959079283887468</v>
+      </c>
+      <c r="M52" s="24">
+        <v>1374.0</v>
+      </c>
+      <c r="N52" s="24">
+        <v>125.0</v>
+      </c>
+      <c r="O52" s="25">
+        <v>0.09097525473071325</v>
       </c>
     </row>
     <row r="53" spans="8:8">
-      <c r="A53" s="17" t="s">
-        <v>4042</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>4043</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>4044</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>4045</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>4046</v>
-      </c>
-      <c r="F53" s="19">
-        <v>91.5</v>
-      </c>
-      <c r="G53" s="19">
-        <v>7.0</v>
-      </c>
-      <c r="H53" s="20">
-        <v>0.07650273224043716</v>
+      <c r="A53" s="20" t="s">
+        <v>4037</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>4038</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>4039</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>4040</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>4041</v>
+      </c>
+      <c r="F53" s="22">
+        <v>350.0</v>
+      </c>
+      <c r="G53" s="22">
+        <v>38.0</v>
+      </c>
+      <c r="H53" s="23">
+        <v>0.10857142857142857</v>
+      </c>
+      <c r="J53" s="24">
+        <v>782.0</v>
+      </c>
+      <c r="K53" s="24">
+        <v>75.0</v>
+      </c>
+      <c r="L53" s="25">
+        <v>0.0959079283887468</v>
+      </c>
+      <c r="M53" s="24">
+        <v>1374.0</v>
+      </c>
+      <c r="N53" s="24">
+        <v>125.0</v>
+      </c>
+      <c r="O53" s="25">
+        <v>0.09097525473071325</v>
       </c>
     </row>
     <row r="54" spans="8:8">
-      <c r="A54" s="17" t="s">
-        <v>4047</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>4048</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>4049</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>4050</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>4051</v>
-      </c>
-      <c r="F54" s="19">
-        <v>44.0</v>
-      </c>
-      <c r="G54" s="19">
-        <v>8.0</v>
-      </c>
-      <c r="H54" s="20">
-        <v>0.18181818181818182</v>
+      <c r="A54" s="20" t="s">
+        <v>4042</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>4043</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>4044</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>4045</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>4046</v>
+      </c>
+      <c r="F54" s="22">
+        <v>91.5</v>
+      </c>
+      <c r="G54" s="22">
+        <v>7.0</v>
+      </c>
+      <c r="H54" s="23">
+        <v>0.07650273224043716</v>
+      </c>
+      <c r="J54" s="24">
+        <v>233.75</v>
+      </c>
+      <c r="K54" s="24">
+        <v>24.0</v>
+      </c>
+      <c r="L54" s="25">
+        <v>0.10267379679144385</v>
+      </c>
+      <c r="M54" s="24">
+        <v>415.0</v>
+      </c>
+      <c r="N54" s="24">
+        <v>28.0</v>
+      </c>
+      <c r="O54" s="25">
+        <v>0.06746987951807229</v>
       </c>
     </row>
     <row r="55" spans="8:8">
-      <c r="A55" s="17" t="s">
-        <v>4052</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>4053</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>4054</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>4055</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>4056</v>
-      </c>
-      <c r="F55" s="19">
-        <v>86.5</v>
-      </c>
-      <c r="G55" s="19">
-        <v>6.0</v>
-      </c>
-      <c r="H55" s="20">
-        <v>0.06936416184971098</v>
+      <c r="A55" s="20" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>4048</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>4049</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>4050</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>4051</v>
+      </c>
+      <c r="F55" s="22">
+        <v>44.0</v>
+      </c>
+      <c r="G55" s="22">
+        <v>8.0</v>
+      </c>
+      <c r="H55" s="23">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="J55" s="24">
+        <v>115.75</v>
+      </c>
+      <c r="K55" s="24">
+        <v>21.0</v>
+      </c>
+      <c r="L55" s="25">
+        <v>0.18142548596112312</v>
+      </c>
+      <c r="M55" s="24">
+        <v>167.5</v>
+      </c>
+      <c r="N55" s="24">
+        <v>27.0</v>
+      </c>
+      <c r="O55" s="25">
+        <v>0.16119402985074627</v>
       </c>
     </row>
     <row r="56" spans="8:8">
-      <c r="A56" s="17" t="s">
-        <v>4057</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>4058</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>4059</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>4060</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>4061</v>
-      </c>
-      <c r="F56" s="19">
-        <v>128.0</v>
-      </c>
-      <c r="G56" s="19">
-        <v>17.0</v>
-      </c>
-      <c r="H56" s="20">
-        <v>0.1328125</v>
+      <c r="A56" s="20" t="s">
+        <v>4052</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>4053</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>4054</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>4055</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>4056</v>
+      </c>
+      <c r="F56" s="22">
+        <v>86.5</v>
+      </c>
+      <c r="G56" s="22">
+        <v>6.0</v>
+      </c>
+      <c r="H56" s="23">
+        <v>0.06936416184971098</v>
+      </c>
+      <c r="J56" s="24">
+        <v>158.75</v>
+      </c>
+      <c r="K56" s="24">
+        <v>6.0</v>
+      </c>
+      <c r="L56" s="25">
+        <v>0.03779527559055118</v>
+      </c>
+      <c r="M56" s="24">
+        <v>256.0</v>
+      </c>
+      <c r="N56" s="24">
+        <v>12.0</v>
+      </c>
+      <c r="O56" s="25">
+        <v>0.046875</v>
       </c>
     </row>
     <row r="57" spans="8:8">
-      <c r="A57" s="17" t="s">
-        <v>4062</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>4063</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>4064</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>4065</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>4066</v>
-      </c>
-      <c r="F57" s="19">
-        <v>268.0</v>
-      </c>
-      <c r="G57" s="19">
-        <v>27.0</v>
-      </c>
-      <c r="H57" s="20">
-        <v>0.10074626865671642</v>
+      <c r="A57" s="20" t="s">
+        <v>4057</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>4058</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>4059</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>4060</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>4061</v>
+      </c>
+      <c r="F57" s="22">
+        <v>128.0</v>
+      </c>
+      <c r="G57" s="22">
+        <v>17.0</v>
+      </c>
+      <c r="H57" s="23">
+        <v>0.1328125</v>
+      </c>
+      <c r="J57" s="24">
+        <v>273.75</v>
+      </c>
+      <c r="K57" s="24">
+        <v>24.0</v>
+      </c>
+      <c r="L57" s="25">
+        <v>0.08767123287671233</v>
+      </c>
+      <c r="M57" s="24">
+        <v>535.5</v>
+      </c>
+      <c r="N57" s="24">
+        <v>58.0</v>
+      </c>
+      <c r="O57" s="25">
+        <v>0.10830999066293184</v>
       </c>
     </row>
     <row r="58" spans="8:8">
-      <c r="A58" s="17" t="s">
-        <v>4067</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>4068</v>
-      </c>
-      <c r="C58" s="22" t="s">
-        <v>4069</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>4070</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>4071</v>
-      </c>
-      <c r="F58" s="19">
-        <v>251.0</v>
-      </c>
-      <c r="G58" s="19">
-        <v>25.0</v>
-      </c>
-      <c r="H58" s="20">
-        <v>0.099601593625498</v>
+      <c r="A58" s="20" t="s">
+        <v>4062</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>4063</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>4064</v>
+      </c>
+      <c r="D58" s="26" t="s">
+        <v>4065</v>
+      </c>
+      <c r="E58" s="26" t="s">
+        <v>4066</v>
+      </c>
+      <c r="F58" s="22">
+        <v>268.0</v>
+      </c>
+      <c r="G58" s="22">
+        <v>27.0</v>
+      </c>
+      <c r="H58" s="23">
+        <v>0.10074626865671642</v>
+      </c>
+      <c r="J58" s="24">
+        <v>514.0</v>
+      </c>
+      <c r="K58" s="24">
+        <v>51.0</v>
+      </c>
+      <c r="L58" s="25">
+        <v>0.09922178988326848</v>
+      </c>
+      <c r="M58" s="24">
+        <v>802.0</v>
+      </c>
+      <c r="N58" s="24">
+        <v>75.0</v>
+      </c>
+      <c r="O58" s="25">
+        <v>0.09351620947630923</v>
       </c>
     </row>
     <row r="59" spans="8:8">
-      <c r="A59" s="17" t="s">
-        <v>4072</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>4073</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>4074</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>4075</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>4076</v>
-      </c>
-      <c r="F59" s="19">
-        <v>74.75</v>
-      </c>
-      <c r="G59" s="19">
-        <v>6.0</v>
-      </c>
-      <c r="H59" s="20">
-        <v>0.0802675585284281</v>
+      <c r="A59" s="20" t="s">
+        <v>4067</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>4068</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>4069</v>
+      </c>
+      <c r="D59" s="27" t="s">
+        <v>4070</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>4071</v>
+      </c>
+      <c r="F59" s="22">
+        <v>251.0</v>
+      </c>
+      <c r="G59" s="22">
+        <v>25.0</v>
+      </c>
+      <c r="H59" s="23">
+        <v>0.099601593625498</v>
+      </c>
+      <c r="J59" s="24">
+        <v>499.0</v>
+      </c>
+      <c r="K59" s="24">
+        <v>50.0</v>
+      </c>
+      <c r="L59" s="25">
+        <v>0.10020040080160321</v>
+      </c>
+      <c r="M59" s="24">
+        <v>763.0</v>
+      </c>
+      <c r="N59" s="24">
+        <v>68.0</v>
+      </c>
+      <c r="O59" s="25">
+        <v>0.0891218872870249</v>
       </c>
     </row>
     <row r="60" spans="8:8">
-      <c r="A60" s="17" t="s">
-        <v>4077</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>4078</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>4079</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>4080</v>
-      </c>
-      <c r="E60" s="22" t="s">
-        <v>4081</v>
-      </c>
-      <c r="F60" s="19">
-        <v>27.75</v>
-      </c>
-      <c r="G60" s="19">
-        <v>4.0</v>
-      </c>
-      <c r="H60" s="20">
-        <v>0.14414414414414414</v>
+      <c r="A60" s="20" t="s">
+        <v>4072</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>4073</v>
+      </c>
+      <c r="C60" s="27" t="s">
+        <v>4074</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>4075</v>
+      </c>
+      <c r="E60" s="27" t="s">
+        <v>4076</v>
+      </c>
+      <c r="F60" s="22">
+        <v>74.75</v>
+      </c>
+      <c r="G60" s="22">
+        <v>6.0</v>
+      </c>
+      <c r="H60" s="23">
+        <v>0.0802675585284281</v>
+      </c>
+      <c r="J60" s="24">
+        <v>149.75</v>
+      </c>
+      <c r="K60" s="24">
+        <v>16.0</v>
+      </c>
+      <c r="L60" s="25">
+        <v>0.10684474123539232</v>
+      </c>
+      <c r="M60" s="24">
+        <v>234.75</v>
+      </c>
+      <c r="N60" s="24">
+        <v>25.0</v>
+      </c>
+      <c r="O60" s="25">
+        <v>0.10649627263045794</v>
       </c>
     </row>
     <row r="61" spans="8:8">
-      <c r="A61" s="17" t="s">
-        <v>4082</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>4083</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>4084</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>4085</v>
-      </c>
-      <c r="E61" s="22" t="s">
-        <v>4086</v>
-      </c>
-      <c r="F61" s="19">
-        <v>53.25</v>
-      </c>
-      <c r="G61" s="19">
+      <c r="A61" s="20" t="s">
+        <v>4077</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>4078</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>4079</v>
+      </c>
+      <c r="D61" s="27" t="s">
+        <v>4080</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>4081</v>
+      </c>
+      <c r="F61" s="22">
+        <v>27.75</v>
+      </c>
+      <c r="G61" s="22">
         <v>4.0</v>
       </c>
-      <c r="H61" s="20">
-        <v>0.07511737089201878</v>
+      <c r="H61" s="23">
+        <v>0.14414414414414414</v>
+      </c>
+      <c r="J61" s="24">
+        <v>54.75</v>
+      </c>
+      <c r="K61" s="24">
+        <v>10.0</v>
+      </c>
+      <c r="L61" s="25">
+        <v>0.182648401826484</v>
+      </c>
+      <c r="M61" s="24">
+        <v>116.25</v>
+      </c>
+      <c r="N61" s="24">
+        <v>19.0</v>
+      </c>
+      <c r="O61" s="25">
+        <v>0.16344086021505377</v>
       </c>
     </row>
     <row r="62" spans="8:8">
-      <c r="A62" s="17" t="s">
-        <v>4087</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>4088</v>
-      </c>
-      <c r="C62" s="22" t="s">
-        <v>4089</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>4090</v>
-      </c>
-      <c r="E62" s="22" t="s">
-        <v>4091</v>
-      </c>
-      <c r="F62" s="19">
-        <v>95.25</v>
-      </c>
-      <c r="G62" s="19">
+      <c r="A62" s="20" t="s">
+        <v>4082</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>4083</v>
+      </c>
+      <c r="C62" s="27" t="s">
+        <v>4084</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>4085</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>4086</v>
+      </c>
+      <c r="F62" s="22">
+        <v>53.25</v>
+      </c>
+      <c r="G62" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="H62" s="23">
+        <v>0.07511737089201878</v>
+      </c>
+      <c r="J62" s="24">
+        <v>122.75</v>
+      </c>
+      <c r="K62" s="24">
+        <v>12.0</v>
+      </c>
+      <c r="L62" s="25">
+        <v>0.09775967413441955</v>
+      </c>
+      <c r="M62" s="24">
+        <v>160.75</v>
+      </c>
+      <c r="N62" s="24">
         <v>11.0</v>
       </c>
-      <c r="H62" s="20">
-        <v>0.11548556430446194</v>
+      <c r="O62" s="25">
+        <v>0.06842923794712286</v>
       </c>
     </row>
     <row r="63" spans="8:8">
-      <c r="A63" s="17" t="s">
-        <v>4092</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>4093</v>
-      </c>
-      <c r="C63" s="22" t="s">
-        <v>4094</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>4095</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>4096</v>
-      </c>
-      <c r="F63" s="19">
-        <v>17.0</v>
-      </c>
-      <c r="G63" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="H63" s="20">
-        <v>0.11764705882352941</v>
+      <c r="A63" s="20" t="s">
+        <v>4087</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>4088</v>
+      </c>
+      <c r="C63" s="27" t="s">
+        <v>4089</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>4090</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>4091</v>
+      </c>
+      <c r="F63" s="22">
+        <v>95.25</v>
+      </c>
+      <c r="G63" s="22">
+        <v>11.0</v>
+      </c>
+      <c r="H63" s="23">
+        <v>0.11548556430446194</v>
+      </c>
+      <c r="J63" s="24">
+        <v>171.75</v>
+      </c>
+      <c r="K63" s="24">
+        <v>12.0</v>
+      </c>
+      <c r="L63" s="25">
+        <v>0.06986899563318777</v>
+      </c>
+      <c r="M63" s="24">
+        <v>251.25</v>
+      </c>
+      <c r="N63" s="24">
+        <v>13.0</v>
+      </c>
+      <c r="O63" s="25">
+        <v>0.051741293532338306</v>
       </c>
     </row>
     <row r="64" spans="8:8">
-      <c r="A64" s="17" t="s">
-        <v>4097</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>4098</v>
-      </c>
-      <c r="C64" s="22" t="s">
-        <v>4099</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>4100</v>
-      </c>
-      <c r="E64" s="22" t="s">
-        <v>4101</v>
-      </c>
-      <c r="F64" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="G64" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="H64" s="20">
-        <v>0.0</v>
+      <c r="A64" s="20" t="s">
+        <v>4092</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>4093</v>
+      </c>
+      <c r="C64" s="27" t="s">
+        <v>4094</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>4095</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>4096</v>
+      </c>
+      <c r="F64" s="22">
+        <v>17.0</v>
+      </c>
+      <c r="G64" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H64" s="23">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="J64" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="K64" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="L64" s="25">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="M64" s="24">
+        <v>39.0</v>
+      </c>
+      <c r="N64" s="24">
+        <v>7.0</v>
+      </c>
+      <c r="O64" s="25">
+        <v>0.1794871794871795</v>
       </c>
     </row>
     <row r="65" spans="8:8">
-      <c r="A65" s="17" t="s">
-        <v>4102</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>4103</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>4104</v>
-      </c>
-      <c r="D65" s="22" t="s">
-        <v>4105</v>
-      </c>
-      <c r="E65" s="22" t="s">
-        <v>4106</v>
-      </c>
-      <c r="F65" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="G65" s="19">
+      <c r="A65" s="20" t="s">
+        <v>4097</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>4098</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>4099</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>4100</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>4101</v>
+      </c>
+      <c r="F65" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="G65" s="22">
         <v>0.0</v>
       </c>
-      <c r="H65" s="20">
+      <c r="H65" s="23">
         <v>0.0</v>
+      </c>
+      <c r="J65" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="K65" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="L65" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="M65" s="24">
+        <v>11.166666666666666</v>
+      </c>
+      <c r="N65" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="O65" s="25">
+        <v>0.08955223880597016</v>
       </c>
     </row>
     <row r="66" spans="8:8">
-      <c r="A66" s="17" t="s">
-        <v>4107</v>
-      </c>
-      <c r="B66" s="17" t="s">
-        <v>4108</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>4109</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>4110</v>
-      </c>
-      <c r="E66" s="22" t="s">
-        <v>4111</v>
-      </c>
-      <c r="F66" s="19">
-        <v>12.0</v>
-      </c>
-      <c r="G66" s="19">
+      <c r="A66" s="20" t="s">
+        <v>4102</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>4103</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>4104</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>4105</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>4106</v>
+      </c>
+      <c r="F66" s="22">
         <v>2.0</v>
       </c>
-      <c r="H66" s="20">
-        <v>0.16666666666666666</v>
+      <c r="G66" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="H66" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J66" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="K66" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="L66" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="M66" s="24">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="N66" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="O66" s="25">
+        <v>0.24657534246575344</v>
       </c>
     </row>
     <row r="67" spans="8:8">
-      <c r="A67" s="17" t="s">
-        <v>4112</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>4113</v>
-      </c>
-      <c r="C67" s="21" t="s">
-        <v>4114</v>
-      </c>
-      <c r="D67" s="21" t="s">
-        <v>4115</v>
-      </c>
-      <c r="E67" s="21" t="s">
-        <v>4116</v>
-      </c>
-      <c r="F67" s="19">
-        <v>360.0</v>
-      </c>
-      <c r="G67" s="19">
-        <v>42.0</v>
-      </c>
-      <c r="H67" s="20">
-        <v>0.11666666666666667</v>
+      <c r="A67" s="20" t="s">
+        <v>4107</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>4108</v>
+      </c>
+      <c r="C67" s="27" t="s">
+        <v>4109</v>
+      </c>
+      <c r="D67" s="27" t="s">
+        <v>4110</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>4111</v>
+      </c>
+      <c r="F67" s="22">
+        <v>12.0</v>
+      </c>
+      <c r="G67" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H67" s="23">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="J67" s="24">
+        <v>9.0</v>
+      </c>
+      <c r="K67" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="L67" s="25">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="M67" s="24">
+        <v>15.666666666666666</v>
+      </c>
+      <c r="N67" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="O67" s="25">
+        <v>0.19148936170212766</v>
       </c>
     </row>
     <row r="68" spans="8:8">
-      <c r="A68" s="17" t="s">
-        <v>4117</v>
-      </c>
-      <c r="B68" s="17" t="s">
-        <v>4118</v>
-      </c>
-      <c r="C68" s="22" t="s">
-        <v>4119</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>4120</v>
-      </c>
-      <c r="E68" s="22" t="s">
-        <v>4121</v>
-      </c>
-      <c r="F68" s="19">
+      <c r="A68" s="20" t="s">
+        <v>4112</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>4113</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>4114</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>4115</v>
+      </c>
+      <c r="E68" s="26" t="s">
+        <v>4116</v>
+      </c>
+      <c r="F68" s="22">
         <v>360.0</v>
       </c>
-      <c r="G68" s="19">
+      <c r="G68" s="22">
         <v>42.0</v>
       </c>
-      <c r="H68" s="20">
+      <c r="H68" s="23">
         <v>0.11666666666666667</v>
+      </c>
+      <c r="J68" s="24">
+        <v>1292.0</v>
+      </c>
+      <c r="K68" s="24">
+        <v>140.0</v>
+      </c>
+      <c r="L68" s="25">
+        <v>0.10835913312693499</v>
+      </c>
+      <c r="M68" s="24">
+        <v>1289.0</v>
+      </c>
+      <c r="N68" s="24">
+        <v>170.0</v>
+      </c>
+      <c r="O68" s="25">
+        <v>0.13188518231186966</v>
       </c>
     </row>
     <row r="69" spans="8:8">
-      <c r="A69" s="17" t="s">
-        <v>4122</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>4123</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>4124</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>4125</v>
-      </c>
-      <c r="E69" s="22" t="s">
-        <v>4126</v>
-      </c>
-      <c r="F69" s="19">
-        <v>107.33333333333334</v>
-      </c>
-      <c r="G69" s="19">
-        <v>8.0</v>
-      </c>
-      <c r="H69" s="20">
-        <v>0.07453416149068322</v>
+      <c r="A69" s="20" t="s">
+        <v>4117</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>4118</v>
+      </c>
+      <c r="C69" s="27" t="s">
+        <v>4119</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>4120</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>4121</v>
+      </c>
+      <c r="F69" s="22">
+        <v>360.0</v>
+      </c>
+      <c r="G69" s="22">
+        <v>42.0</v>
+      </c>
+      <c r="H69" s="23">
+        <v>0.11666666666666667</v>
+      </c>
+      <c r="J69" s="24">
+        <v>1249.0</v>
+      </c>
+      <c r="K69" s="24">
+        <v>132.0</v>
+      </c>
+      <c r="L69" s="25">
+        <v>0.10568454763811048</v>
+      </c>
+      <c r="M69" s="24">
+        <v>1264.0</v>
+      </c>
+      <c r="N69" s="24">
+        <v>165.0</v>
+      </c>
+      <c r="O69" s="25">
+        <v>0.1305379746835443</v>
       </c>
     </row>
     <row r="70" spans="8:8">
-      <c r="A70" s="17" t="s">
-        <v>4127</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>4128</v>
-      </c>
-      <c r="C70" s="22" t="s">
-        <v>4129</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>4130</v>
-      </c>
-      <c r="E70" s="22" t="s">
-        <v>4131</v>
-      </c>
-      <c r="F70" s="19">
-        <v>115.33333333333334</v>
-      </c>
-      <c r="G70" s="19">
-        <v>20.0</v>
-      </c>
-      <c r="H70" s="20">
-        <v>0.17341040462427745</v>
+      <c r="A70" s="20" t="s">
+        <v>4122</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>4123</v>
+      </c>
+      <c r="C70" s="27" t="s">
+        <v>4124</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>4125</v>
+      </c>
+      <c r="E70" s="27" t="s">
+        <v>4126</v>
+      </c>
+      <c r="F70" s="22">
+        <v>107.33333333333334</v>
+      </c>
+      <c r="G70" s="22">
+        <v>8.0</v>
+      </c>
+      <c r="H70" s="23">
+        <v>0.07453416149068322</v>
+      </c>
+      <c r="J70" s="24">
+        <v>438.5</v>
+      </c>
+      <c r="K70" s="24">
+        <v>67.0</v>
+      </c>
+      <c r="L70" s="25">
+        <v>0.15279361459521096</v>
+      </c>
+      <c r="M70" s="24">
+        <v>452.6666666666667</v>
+      </c>
+      <c r="N70" s="24">
+        <v>69.0</v>
+      </c>
+      <c r="O70" s="25">
+        <v>0.1524300441826215</v>
       </c>
     </row>
     <row r="71" spans="8:8">
-      <c r="A71" s="17" t="s">
-        <v>4132</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>4133</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>4134</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>4135</v>
-      </c>
-      <c r="E71" s="22" t="s">
-        <v>4136</v>
-      </c>
-      <c r="F71" s="19">
-        <v>137.33333333333334</v>
-      </c>
-      <c r="G71" s="19">
-        <v>14.0</v>
-      </c>
-      <c r="H71" s="20">
-        <v>0.10194174757281553</v>
+      <c r="A71" s="20" t="s">
+        <v>4127</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>4128</v>
+      </c>
+      <c r="C71" s="27" t="s">
+        <v>4129</v>
+      </c>
+      <c r="D71" s="27" t="s">
+        <v>4130</v>
+      </c>
+      <c r="E71" s="27" t="s">
+        <v>4131</v>
+      </c>
+      <c r="F71" s="22">
+        <v>115.33333333333334</v>
+      </c>
+      <c r="G71" s="22">
+        <v>20.0</v>
+      </c>
+      <c r="H71" s="23">
+        <v>0.17341040462427745</v>
+      </c>
+      <c r="J71" s="24">
+        <v>350.5</v>
+      </c>
+      <c r="K71" s="24">
+        <v>30.0</v>
+      </c>
+      <c r="L71" s="25">
+        <v>0.08559201141226819</v>
+      </c>
+      <c r="M71" s="24">
+        <v>372.6666666666667</v>
+      </c>
+      <c r="N71" s="24">
+        <v>70.0</v>
+      </c>
+      <c r="O71" s="25">
+        <v>0.1878354203935599</v>
       </c>
     </row>
     <row r="72" spans="8:8">
-      <c r="A72" s="17" t="s">
-        <v>4137</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>4138</v>
-      </c>
-      <c r="C72" s="22" t="s">
-        <v>4139</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>4140</v>
-      </c>
-      <c r="E72" s="22" t="s">
-        <v>4141</v>
-      </c>
-      <c r="F72" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="G72" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="H72" s="20">
-        <v>0.0</v>
+      <c r="A72" s="20" t="s">
+        <v>4132</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>4133</v>
+      </c>
+      <c r="C72" s="27" t="s">
+        <v>4134</v>
+      </c>
+      <c r="D72" s="27" t="s">
+        <v>4135</v>
+      </c>
+      <c r="E72" s="27" t="s">
+        <v>4136</v>
+      </c>
+      <c r="F72" s="22">
+        <v>137.33333333333334</v>
+      </c>
+      <c r="G72" s="22">
+        <v>14.0</v>
+      </c>
+      <c r="H72" s="23">
+        <v>0.10194174757281553</v>
+      </c>
+      <c r="J72" s="24">
+        <v>460.0</v>
+      </c>
+      <c r="K72" s="24">
+        <v>35.0</v>
+      </c>
+      <c r="L72" s="25">
+        <v>0.07608695652173914</v>
+      </c>
+      <c r="M72" s="24">
+        <v>438.6666666666667</v>
+      </c>
+      <c r="N72" s="24">
+        <v>26.0</v>
+      </c>
+      <c r="O72" s="25">
+        <v>0.05927051671732522</v>
       </c>
     </row>
     <row r="73" spans="8:8">
-      <c r="A73" s="17" t="s">
-        <v>4142</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>4143</v>
-      </c>
-      <c r="C73" s="22" t="s">
-        <v>4144</v>
-      </c>
-      <c r="D73" s="22" t="s">
-        <v>4145</v>
-      </c>
-      <c r="E73" s="22" t="s">
-        <v>4146</v>
-      </c>
-      <c r="F73" s="19">
+      <c r="A73" s="20" t="s">
+        <v>4137</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>4138</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>4139</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>4140</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>4141</v>
+      </c>
+      <c r="F73" s="22">
         <v>0.0</v>
       </c>
-      <c r="G73" s="19">
+      <c r="G73" s="22">
         <v>0.0</v>
       </c>
-      <c r="H73" s="20">
+      <c r="H73" s="23">
         <v>0.0</v>
+      </c>
+      <c r="J73" s="24">
+        <v>43.0</v>
+      </c>
+      <c r="K73" s="24">
+        <v>8.0</v>
+      </c>
+      <c r="L73" s="25">
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="M73" s="24">
+        <v>25.0</v>
+      </c>
+      <c r="N73" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="O73" s="25">
+        <v>0.2</v>
       </c>
     </row>
     <row r="74" spans="8:8">
-      <c r="A74" s="17" t="s">
-        <v>4147</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>4148</v>
-      </c>
-      <c r="C74" s="22" t="s">
-        <v>4149</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>4150</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>4151</v>
-      </c>
-      <c r="F74" s="19">
+      <c r="A74" s="20" t="s">
+        <v>4142</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>4143</v>
+      </c>
+      <c r="C74" s="27" t="s">
+        <v>4144</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>4145</v>
+      </c>
+      <c r="E74" s="27" t="s">
+        <v>4146</v>
+      </c>
+      <c r="F74" s="22">
         <v>0.0</v>
       </c>
-      <c r="G74" s="19">
+      <c r="G74" s="22">
         <v>0.0</v>
       </c>
-      <c r="H74" s="20">
+      <c r="H74" s="23">
         <v>0.0</v>
+      </c>
+      <c r="J74" s="24">
+        <v>14.666666666666666</v>
+      </c>
+      <c r="K74" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="L74" s="25">
+        <v>0.20454545454545456</v>
+      </c>
+      <c r="M74" s="24">
+        <v>8.0</v>
+      </c>
+      <c r="N74" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="O74" s="25">
+        <v>0.125</v>
       </c>
     </row>
     <row r="75" spans="8:8">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="20" t="s">
+        <v>4147</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>4148</v>
+      </c>
+      <c r="C75" s="27" t="s">
+        <v>4149</v>
+      </c>
+      <c r="D75" s="27" t="s">
+        <v>4150</v>
+      </c>
+      <c r="E75" s="27" t="s">
+        <v>4151</v>
+      </c>
+      <c r="F75" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="G75" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="H75" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J75" s="24">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="K75" s="24">
+        <v>2.0</v>
+      </c>
+      <c r="L75" s="25">
+        <v>0.17142857142857143</v>
+      </c>
+      <c r="M75" s="24">
+        <v>6.0</v>
+      </c>
+      <c r="N75" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="O75" s="25">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="76" spans="8:8">
+      <c r="A76" s="20" t="s">
         <v>4152</v>
       </c>
-      <c r="B75" s="17" t="s">
+      <c r="B76" s="20" t="s">
         <v>4153</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C76" s="27" t="s">
         <v>4154</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D76" s="27" t="s">
         <v>4155</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E76" s="27" t="s">
         <v>4156</v>
       </c>
-      <c r="F75" s="19">
+      <c r="F76" s="22">
         <v>0.0</v>
       </c>
-      <c r="G75" s="19">
+      <c r="G76" s="22">
         <v>0.0</v>
       </c>
-      <c r="H75" s="20">
+      <c r="H76" s="23">
         <v>0.0</v>
+      </c>
+      <c r="J76" s="24">
+        <v>16.666666666666668</v>
+      </c>
+      <c r="K76" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="L76" s="25">
+        <v>0.18</v>
+      </c>
+      <c r="M76" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="N76" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="O76" s="25">
+        <v>0.36363636363636365</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:O1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
-    <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="24"/>
-    <col min="4" max="4" customWidth="1" bestFit="1" width="10.0" style="24"/>
-    <col min="5" max="5" customWidth="1" bestFit="1" width="10.0" style="24"/>
-    <col min="6" max="6" customWidth="1" bestFit="1" width="11.503906" style="24"/>
-    <col min="7" max="7" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="8" max="8" customWidth="1" bestFit="1" width="10.0" style="0"/>
+    <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="29"/>
+    <col min="4" max="4" customWidth="1" bestFit="1" width="10.0" style="29"/>
+    <col min="5" max="5" customWidth="1" bestFit="1" width="10.0" style="29"/>
+    <col min="6" max="6" customWidth="1" bestFit="1" width="11.503906" style="29"/>
+    <col min="7" max="7" customWidth="1" width="4.5039062" style="0"/>
+    <col min="8" max="8" customWidth="1" bestFit="1" width="10.0" style="30"/>
+    <col min="9" max="9" customWidth="1" bestFit="1" width="10.0" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="13" ht="25.4" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="8:8" ht="16.25">
+      <c r="H1" s="13" t="s">
+        <v>6056</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>6057</v>
+      </c>
+    </row>
+    <row r="2" spans="8:8" s="14" ht="25.4" customFormat="1">
+      <c r="A2" s="15" t="s">
         <v>4801</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>4802</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>4803</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D2" s="15" t="s">
         <v>4804</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>4805</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>4806</v>
       </c>
+      <c r="H2" s="18" t="s">
+        <v>6058</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>6059</v>
+      </c>
     </row>
-    <row r="2" spans="8:8">
-      <c r="A2" s="17" t="s">
+    <row r="3" spans="8:8" ht="16.25">
+      <c r="A3" s="20" t="s">
         <v>4168</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B3" s="20" t="s">
         <v>4169</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C3" s="27" t="s">
         <v>4170</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D3" s="27" t="s">
         <v>4171</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E3" s="27" t="s">
         <v>4172</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F3" s="23">
         <v>0.09627801560897269</v>
       </c>
-    </row>
-    <row r="3" spans="8:8">
-      <c r="A3" s="17" t="s">
-        <v>4173</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>4174</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>4175</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>4176</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>4177</v>
-      </c>
-      <c r="F3" s="20">
-        <v>0.04513756911443717</v>
+      <c r="H3" s="25">
+        <v>0.06098160086707704</v>
+      </c>
+      <c r="I3" s="25">
+        <v>0.06246258875303785</v>
       </c>
     </row>
     <row r="4" spans="8:8">
-      <c r="A4" s="17" t="s">
-        <v>4178</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>4179</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>4180</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>4181</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>4182</v>
-      </c>
-      <c r="F4" s="20">
-        <v>0.1068098034259732</v>
+      <c r="A4" s="20" t="s">
+        <v>4173</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>4174</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>4175</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>4176</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>4177</v>
+      </c>
+      <c r="F4" s="23">
+        <v>0.04513756911443717</v>
+      </c>
+      <c r="H4" s="25">
+        <v>0.0551699464275635</v>
+      </c>
+      <c r="I4" s="25">
+        <v>0.04675928649471554</v>
       </c>
     </row>
     <row r="5" spans="8:8">
-      <c r="A5" s="17" t="s">
-        <v>4183</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>4184</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>4185</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>4186</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>4187</v>
-      </c>
-      <c r="F5" s="20">
-        <v>0.0</v>
+      <c r="A5" s="20" t="s">
+        <v>4178</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>4179</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>4180</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>4181</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>4182</v>
+      </c>
+      <c r="F5" s="23">
+        <v>0.1068098034259732</v>
+      </c>
+      <c r="H5" s="25">
+        <v>0.06414128809467869</v>
+      </c>
+      <c r="I5" s="25">
+        <v>0.07402333756046449</v>
       </c>
     </row>
     <row r="6" spans="8:8">
-      <c r="A6" s="17" t="s">
-        <v>4188</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>4189</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>4190</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>4191</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>4192</v>
-      </c>
-      <c r="F6" s="20">
-        <v>0.4974717254649712</v>
+      <c r="A6" s="20" t="s">
+        <v>4183</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>4184</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>4185</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>4186</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>4187</v>
+      </c>
+      <c r="F6" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="25">
+        <v>0.07817601341354315</v>
+      </c>
+      <c r="I6" s="25">
+        <v>0.06474326844267664</v>
       </c>
     </row>
     <row r="7" spans="8:8">
-      <c r="A7" s="17" t="s">
-        <v>4193</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>4194</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>4195</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>4196</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>4197</v>
-      </c>
-      <c r="F7" s="20">
-        <v>0.0</v>
+      <c r="A7" s="20" t="s">
+        <v>4188</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>4189</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>4191</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>4192</v>
+      </c>
+      <c r="F7" s="23">
+        <v>0.4974717254649712</v>
+      </c>
+      <c r="H7" s="25">
+        <v>0.0454531374055001</v>
+      </c>
+      <c r="I7" s="25">
+        <v>0.04008696459825768</v>
       </c>
     </row>
     <row r="8" spans="8:8">
-      <c r="A8" s="17" t="s">
-        <v>4198</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>4199</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>4200</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>4201</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>4202</v>
-      </c>
-      <c r="F8" s="25">
+      <c r="A8" s="20" t="s">
+        <v>4193</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>4194</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>4195</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>4196</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>4197</v>
+      </c>
+      <c r="F8" s="23">
         <v>0.0</v>
+      </c>
+      <c r="H8" s="25">
+        <v>0.05462346874149627</v>
+      </c>
+      <c r="I8" s="25">
+        <v>0.0794785869965411</v>
       </c>
     </row>
     <row r="9" spans="8:8">
-      <c r="A9" s="17" t="s">
-        <v>4203</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>4204</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>4205</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>4206</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>4207</v>
-      </c>
-      <c r="F9" s="20">
-        <v>0.03770547184323618</v>
+      <c r="A9" s="20" t="s">
+        <v>4198</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>4199</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>4200</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>4201</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>4202</v>
+      </c>
+      <c r="F9" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="25">
+        <v>0.0703472500051208</v>
+      </c>
+      <c r="I9" s="25">
+        <v>0.08782358651523879</v>
       </c>
     </row>
     <row r="10" spans="8:8">
-      <c r="A10" s="17" t="s">
-        <v>4208</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>4209</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>4210</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>4211</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>4212</v>
-      </c>
-      <c r="F10" s="20">
-        <v>0.03326895576826878</v>
+      <c r="A10" s="20" t="s">
+        <v>4203</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>4204</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>4205</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>4206</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>4207</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.03770547184323618</v>
+      </c>
+      <c r="H10" s="25">
+        <v>0.05259384427639548</v>
+      </c>
+      <c r="I10" s="25">
+        <v>0.04246826119336062</v>
       </c>
     </row>
     <row r="11" spans="8:8">
-      <c r="A11" s="17" t="s">
-        <v>4213</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>4214</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>4215</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>4216</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>4217</v>
-      </c>
-      <c r="F11" s="20">
-        <v>0.02836302688327537</v>
+      <c r="A11" s="20" t="s">
+        <v>4208</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>4209</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>4210</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>4211</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>4212</v>
+      </c>
+      <c r="F11" s="23">
+        <v>0.03326895576826878</v>
+      </c>
+      <c r="H11" s="25">
+        <v>0.037722930031919004</v>
+      </c>
+      <c r="I11" s="25">
+        <v>0.02485526343572443</v>
       </c>
     </row>
     <row r="12" spans="8:8">
-      <c r="A12" s="17" t="s">
-        <v>4218</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>4219</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>4220</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>4221</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>4222</v>
-      </c>
-      <c r="F12" s="20">
-        <v>0.03192152835974302</v>
+      <c r="A12" s="20" t="s">
+        <v>4213</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>4214</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>4215</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>4216</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>4217</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.02836302688327537</v>
+      </c>
+      <c r="H12" s="25">
+        <v>0.06281704102885162</v>
+      </c>
+      <c r="I12" s="25">
+        <v>0.04713649467462683</v>
       </c>
     </row>
     <row r="13" spans="8:8">
-      <c r="A13" s="17" t="s">
-        <v>4223</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>4224</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>4225</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>4226</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>4227</v>
-      </c>
-      <c r="F13" s="20">
-        <v>0.049977596444282325</v>
+      <c r="A13" s="20" t="s">
+        <v>4218</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>4219</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>4220</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>4221</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>4222</v>
+      </c>
+      <c r="F13" s="23">
+        <v>0.03192152835974302</v>
+      </c>
+      <c r="H13" s="25">
+        <v>0.03158221984527825</v>
+      </c>
+      <c r="I13" s="25">
+        <v>0.038737081085029185</v>
       </c>
     </row>
     <row r="14" spans="8:8">
-      <c r="A14" s="17" t="s">
-        <v>4228</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>4229</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>4230</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>4231</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>4232</v>
-      </c>
-      <c r="F14" s="20">
-        <v>0.04514883199157655</v>
+      <c r="A14" s="20" t="s">
+        <v>4223</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>4224</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>4225</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>4226</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>4227</v>
+      </c>
+      <c r="F14" s="23">
+        <v>0.049977596444282325</v>
+      </c>
+      <c r="H14" s="25">
+        <v>0.07417183953936354</v>
+      </c>
+      <c r="I14" s="25">
+        <v>0.05722459419992368</v>
       </c>
     </row>
     <row r="15" spans="8:8">
-      <c r="A15" s="17" t="s">
-        <v>4233</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>4234</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>4235</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>4236</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>4237</v>
-      </c>
-      <c r="F15" s="20">
+      <c r="A15" s="20" t="s">
+        <v>4228</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>4229</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>4230</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>4231</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>4232</v>
+      </c>
+      <c r="F15" s="23">
         <v>0.04514883199157655</v>
+      </c>
+      <c r="H15" s="25">
+        <v>0.04259452558342196</v>
+      </c>
+      <c r="I15" s="25">
+        <v>0.058783948573643725</v>
       </c>
     </row>
     <row r="16" spans="8:8">
-      <c r="A16" s="17" t="s">
-        <v>4238</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>4239</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>4240</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>4241</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>4242</v>
-      </c>
-      <c r="F16" s="20">
-        <v>0.0343253182802941</v>
+      <c r="A16" s="20" t="s">
+        <v>4233</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>4234</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>4235</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>4236</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>4237</v>
+      </c>
+      <c r="F16" s="23">
+        <v>0.04514883199157655</v>
+      </c>
+      <c r="H16" s="25">
+        <v>0.04259452558342196</v>
+      </c>
+      <c r="I16" s="25">
+        <v>0.058783948573643725</v>
       </c>
     </row>
     <row r="17" spans="8:8">
-      <c r="A17" s="17" t="s">
-        <v>4243</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>4244</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>4245</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>4246</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>4247</v>
-      </c>
-      <c r="F17" s="20">
-        <v>0.089205053980151</v>
+      <c r="A17" s="20" t="s">
+        <v>4238</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>4239</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>4240</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>4241</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>4242</v>
+      </c>
+      <c r="F17" s="23">
+        <v>0.0343253182802941</v>
+      </c>
+      <c r="H17" s="25">
+        <v>0.03723844758914133</v>
+      </c>
+      <c r="I17" s="25">
+        <v>0.03756208611040777</v>
       </c>
     </row>
     <row r="18" spans="8:8">
-      <c r="A18" s="17" t="s">
-        <v>4248</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>4249</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>4250</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>4251</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>4252</v>
-      </c>
-      <c r="F18" s="20">
-        <v>0.058589781996075306</v>
+      <c r="A18" s="20" t="s">
+        <v>4243</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>4244</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>4245</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>4246</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>4247</v>
+      </c>
+      <c r="F18" s="23">
+        <v>0.089205053980151</v>
+      </c>
+      <c r="H18" s="25">
+        <v>0.05457987347785562</v>
+      </c>
+      <c r="I18" s="25">
+        <v>0.06830659841434439</v>
       </c>
     </row>
     <row r="19" spans="8:8">
-      <c r="A19" s="17" t="s">
-        <v>4253</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>4254</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>4255</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>4256</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>4257</v>
-      </c>
-      <c r="F19" s="20">
-        <v>0.013068239536623043</v>
+      <c r="A19" s="20" t="s">
+        <v>4248</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>4249</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>4250</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>4251</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>4252</v>
+      </c>
+      <c r="F19" s="23">
+        <v>0.058589781996075306</v>
+      </c>
+      <c r="H19" s="25">
+        <v>0.028415486056884025</v>
+      </c>
+      <c r="I19" s="25">
+        <v>0.050046347980965265</v>
       </c>
     </row>
     <row r="20" spans="8:8">
-      <c r="A20" s="17" t="s">
-        <v>4258</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>4259</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>4260</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>4261</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>4262</v>
-      </c>
-      <c r="F20" s="20">
-        <v>0.08802778366085617</v>
+      <c r="A20" s="20" t="s">
+        <v>4253</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>4254</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>4255</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>4256</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>4257</v>
+      </c>
+      <c r="F20" s="23">
+        <v>0.013068239536623043</v>
+      </c>
+      <c r="H20" s="25">
+        <v>0.050309064302250586</v>
+      </c>
+      <c r="I20" s="25">
+        <v>0.07196147723029654</v>
       </c>
     </row>
     <row r="21" spans="8:8">
-      <c r="A21" s="17" t="s">
-        <v>4263</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>4264</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>4265</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>4266</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>4267</v>
-      </c>
-      <c r="F21" s="20">
+      <c r="A21" s="20" t="s">
+        <v>4258</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>4259</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>4260</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>4261</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>4262</v>
+      </c>
+      <c r="F21" s="23">
         <v>0.08802778366085617</v>
+      </c>
+      <c r="H21" s="25">
+        <v>0.06275887670528484</v>
+      </c>
+      <c r="I21" s="25">
+        <v>0.054176976817070684</v>
       </c>
     </row>
     <row r="22" spans="8:8">
-      <c r="A22" s="17" t="s">
-        <v>4268</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>4269</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>4270</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>4271</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>4272</v>
-      </c>
-      <c r="F22" s="20">
-        <v>0.08608722382907374</v>
+      <c r="A22" s="20" t="s">
+        <v>4263</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>4264</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>4265</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>4266</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>4267</v>
+      </c>
+      <c r="F22" s="23">
+        <v>0.08802778366085617</v>
+      </c>
+      <c r="H22" s="25">
+        <v>0.06275887670528484</v>
+      </c>
+      <c r="I22" s="25">
+        <v>0.05608399679724047</v>
       </c>
     </row>
     <row r="23" spans="8:8">
-      <c r="A23" s="17" t="s">
-        <v>4273</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>4274</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>4275</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>4276</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>4277</v>
-      </c>
-      <c r="F23" s="20">
-        <v>0.0</v>
+      <c r="A23" s="20" t="s">
+        <v>4268</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>4269</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>4270</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>4271</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>4272</v>
+      </c>
+      <c r="F23" s="23">
+        <v>0.08608722382907374</v>
+      </c>
+      <c r="H23" s="25">
+        <v>0.0718865217868037</v>
+      </c>
+      <c r="I23" s="25">
+        <v>0.05940452691638236</v>
       </c>
     </row>
     <row r="24" spans="8:8">
-      <c r="A24" s="17" t="s">
-        <v>4278</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>4279</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>4280</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>4281</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>4282</v>
-      </c>
-      <c r="F24" s="20">
-        <v>0.24325029499677026</v>
+      <c r="A24" s="20" t="s">
+        <v>4273</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>4274</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>4275</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>4276</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>4277</v>
+      </c>
+      <c r="F24" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="25">
+        <v>0.0838434280324384</v>
+      </c>
+      <c r="I24" s="25">
+        <v>0.059165453683191045</v>
       </c>
     </row>
     <row r="25" spans="8:8">
-      <c r="A25" s="17" t="s">
-        <v>4283</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>4284</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>4285</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>4286</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>4287</v>
-      </c>
-      <c r="F25" s="20">
-        <v>0.043805906832283165</v>
+      <c r="A25" s="20" t="s">
+        <v>4278</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>4279</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>4280</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>4281</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>4282</v>
+      </c>
+      <c r="F25" s="23">
+        <v>0.24325029499677026</v>
+      </c>
+      <c r="H25" s="25">
+        <v>0.04958406058859932</v>
+      </c>
+      <c r="I25" s="25">
+        <v>0.09228080207276627</v>
       </c>
     </row>
     <row r="26" spans="8:8">
-      <c r="A26" s="17" t="s">
-        <v>4288</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>4289</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>4290</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>4291</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>4292</v>
-      </c>
-      <c r="F26" s="20">
-        <v>0.0</v>
+      <c r="A26" s="20" t="s">
+        <v>4283</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>4284</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>4285</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>4286</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>4287</v>
+      </c>
+      <c r="F26" s="23">
+        <v>0.043805906832283165</v>
+      </c>
+      <c r="H26" s="25">
+        <v>0.05325235163529225</v>
+      </c>
+      <c r="I26" s="25">
+        <v>0.024332784347365563</v>
       </c>
     </row>
     <row r="27" spans="8:8">
-      <c r="A27" s="17" t="s">
-        <v>4293</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>4294</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>4295</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>4296</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>4297</v>
-      </c>
-      <c r="F27" s="20">
+      <c r="A27" s="20" t="s">
+        <v>4288</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>4289</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>4290</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>4291</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>4292</v>
+      </c>
+      <c r="F27" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="28" spans="8:8">
-      <c r="A28" s="17" t="s">
-        <v>4298</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>4299</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>4300</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>4301</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>4302</v>
-      </c>
-      <c r="F28" s="20">
+      <c r="A28" s="20" t="s">
+        <v>4293</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>4294</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>4295</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>4296</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>4297</v>
+      </c>
+      <c r="F28" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="29" spans="8:8">
-      <c r="A29" s="17" t="s">
-        <v>4303</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>4304</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>4305</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>4306</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>4307</v>
-      </c>
-      <c r="F29" s="20">
+      <c r="A29" s="20" t="s">
+        <v>4298</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>4299</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>4300</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>4301</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>4302</v>
+      </c>
+      <c r="F29" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="H29" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="I29" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="30" spans="8:8">
-      <c r="A30" s="17" t="s">
-        <v>4308</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>4309</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>4310</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>4311</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>4312</v>
-      </c>
-      <c r="F30" s="20">
-        <v>0.1023947561236618</v>
+      <c r="A30" s="20" t="s">
+        <v>4303</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>4304</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>4305</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>4306</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>4307</v>
+      </c>
+      <c r="F30" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="I30" s="25">
+        <v>0.0</v>
       </c>
     </row>
     <row r="31" spans="8:8">
-      <c r="A31" s="17" t="s">
-        <v>4313</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>4314</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>4315</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>4316</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>4317</v>
-      </c>
-      <c r="F31" s="20">
-        <v>0.11721712394652918</v>
+      <c r="A31" s="20" t="s">
+        <v>4308</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>4309</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>4310</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>4311</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>4312</v>
+      </c>
+      <c r="F31" s="23">
+        <v>0.1023947561236618</v>
+      </c>
+      <c r="H31" s="25">
+        <v>0.06686510248145955</v>
+      </c>
+      <c r="I31" s="25">
+        <v>0.07112212963675735</v>
       </c>
     </row>
     <row r="32" spans="8:8">
-      <c r="A32" s="17" t="s">
-        <v>4318</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>4319</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>4320</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>4321</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>4322</v>
-      </c>
-      <c r="F32" s="20">
-        <v>0.03819078865635482</v>
+      <c r="A32" s="20" t="s">
+        <v>4313</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>4314</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>4315</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>4316</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>4317</v>
+      </c>
+      <c r="F32" s="23">
+        <v>0.11721712394652918</v>
+      </c>
+      <c r="H32" s="25">
+        <v>0.06964091791545708</v>
+      </c>
+      <c r="I32" s="25">
+        <v>0.05785872607590887</v>
       </c>
     </row>
     <row r="33" spans="8:8">
-      <c r="A33" s="17" t="s">
-        <v>4323</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>4324</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>4325</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>4326</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>4327</v>
-      </c>
-      <c r="F33" s="20">
-        <v>0.24274910491866208</v>
+      <c r="A33" s="20" t="s">
+        <v>4318</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>4319</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>4320</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>4321</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>4322</v>
+      </c>
+      <c r="F33" s="23">
+        <v>0.03819078865635482</v>
+      </c>
+      <c r="H33" s="25">
+        <v>0.06082120689025663</v>
+      </c>
+      <c r="I33" s="25">
+        <v>0.03663356294202617</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="A34" s="17" t="s">
-        <v>4328</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>4329</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>4330</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>4331</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>4332</v>
-      </c>
-      <c r="F34" s="20">
-        <v>0.07485565274108441</v>
+      <c r="A34" s="20" t="s">
+        <v>4323</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>4324</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>4325</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>4326</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>4327</v>
+      </c>
+      <c r="F34" s="23">
+        <v>0.24274910491866208</v>
+      </c>
+      <c r="H34" s="25">
+        <v>0.1201040948033431</v>
+      </c>
+      <c r="I34" s="25">
+        <v>0.10842236131585735</v>
       </c>
     </row>
     <row r="35" spans="8:8">
-      <c r="A35" s="17" t="s">
-        <v>4333</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>4334</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>4335</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>4336</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>4337</v>
-      </c>
-      <c r="F35" s="20">
-        <v>0.15066877055215233</v>
+      <c r="A35" s="20" t="s">
+        <v>4328</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>4329</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>4330</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>4331</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>4332</v>
+      </c>
+      <c r="F35" s="23">
+        <v>0.07485565274108441</v>
+      </c>
+      <c r="H35" s="25">
+        <v>0.03790015110298493</v>
+      </c>
+      <c r="I35" s="25">
+        <v>0.053604881478763675</v>
       </c>
     </row>
     <row r="36" spans="8:8">
-      <c r="A36" s="17" t="s">
-        <v>4338</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>4339</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>4340</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>4341</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>4342</v>
-      </c>
-      <c r="F36" s="20">
-        <v>0.04501552432303537</v>
+      <c r="A36" s="20" t="s">
+        <v>4333</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>4334</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>4335</v>
+      </c>
+      <c r="D36" s="27" t="s">
+        <v>4336</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>4337</v>
+      </c>
+      <c r="F36" s="23">
+        <v>0.15066877055215233</v>
+      </c>
+      <c r="H36" s="25">
+        <v>0.07597722869424497</v>
+      </c>
+      <c r="I36" s="25">
+        <v>0.052780880384555945</v>
       </c>
     </row>
     <row r="37" spans="8:8">
-      <c r="A37" s="17" t="s">
-        <v>4343</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>4344</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>4345</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>4346</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>4347</v>
-      </c>
-      <c r="F37" s="20">
-        <v>0.013286438677101588</v>
+      <c r="A37" s="20" t="s">
+        <v>4338</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>4339</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>4340</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>4341</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>4342</v>
+      </c>
+      <c r="F37" s="23">
+        <v>0.04501552432303537</v>
+      </c>
+      <c r="H37" s="25">
+        <v>0.05768390535317222</v>
+      </c>
+      <c r="I37" s="25">
+        <v>0.11788345290127854</v>
       </c>
     </row>
     <row r="38" spans="8:8">
-      <c r="A38" s="17" t="s">
-        <v>4348</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>4349</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>4350</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>4351</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>4352</v>
-      </c>
-      <c r="F38" s="20">
-        <v>0.04458891937310925</v>
+      <c r="A38" s="20" t="s">
+        <v>4343</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>4344</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>4345</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>4346</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>4347</v>
+      </c>
+      <c r="F38" s="23">
+        <v>0.013286438677101588</v>
+      </c>
+      <c r="H38" s="25">
+        <v>0.060179134125691515</v>
+      </c>
+      <c r="I38" s="25">
+        <v>0.06788764771337627</v>
       </c>
     </row>
     <row r="39" spans="8:8">
-      <c r="A39" s="17" t="s">
-        <v>4353</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>4354</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>4355</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>4356</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>4357</v>
-      </c>
-      <c r="F39" s="20">
-        <v>0.07860187538750195</v>
+      <c r="A39" s="20" t="s">
+        <v>4348</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>4349</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>4350</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>4351</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>4352</v>
+      </c>
+      <c r="F39" s="23">
+        <v>0.04458891937310925</v>
+      </c>
+      <c r="H39" s="25">
+        <v>0.041275589812516306</v>
+      </c>
+      <c r="I39" s="25">
+        <v>0.08188823956694011</v>
       </c>
     </row>
     <row r="40" spans="8:8">
-      <c r="A40" s="17" t="s">
-        <v>4358</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>4359</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>4360</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>4361</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>4362</v>
-      </c>
-      <c r="F40" s="20">
-        <v>0.04123044497519338</v>
+      <c r="A40" s="20" t="s">
+        <v>4353</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>4354</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>4355</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>4356</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>4357</v>
+      </c>
+      <c r="F40" s="23">
+        <v>0.07860187538750195</v>
+      </c>
+      <c r="H40" s="25">
+        <v>0.071851834469613</v>
+      </c>
+      <c r="I40" s="25">
+        <v>0.10873273434506832</v>
       </c>
     </row>
     <row r="41" spans="8:8">
-      <c r="A41" s="17" t="s">
-        <v>4363</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>4364</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>4365</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>4366</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>4367</v>
-      </c>
-      <c r="F41" s="20">
-        <v>0.09878683471386894</v>
+      <c r="A41" s="20" t="s">
+        <v>4358</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>4360</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>4361</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>4362</v>
+      </c>
+      <c r="F41" s="23">
+        <v>0.04123044497519338</v>
+      </c>
+      <c r="H41" s="25">
+        <v>0.05386528971488993</v>
+      </c>
+      <c r="I41" s="25">
+        <v>0.1588581228501085</v>
       </c>
     </row>
     <row r="42" spans="8:8">
-      <c r="A42" s="17" t="s">
-        <v>4368</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>4369</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>4370</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>4371</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>4372</v>
-      </c>
-      <c r="F42" s="20">
-        <v>0.10405747094225257</v>
+      <c r="A42" s="20" t="s">
+        <v>4363</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>4364</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>4365</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>4366</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>4367</v>
+      </c>
+      <c r="F42" s="23">
+        <v>0.09878683471386894</v>
+      </c>
+      <c r="H42" s="25">
+        <v>0.05880860180475631</v>
+      </c>
+      <c r="I42" s="25">
+        <v>0.06146650371058642</v>
       </c>
     </row>
     <row r="43" spans="8:8">
-      <c r="A43" s="17" t="s">
-        <v>4373</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>4374</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>4375</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>4376</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>4377</v>
-      </c>
-      <c r="F43" s="20">
-        <v>0.006144336801960007</v>
+      <c r="A43" s="20" t="s">
+        <v>4368</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>4369</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>4370</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>4371</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>4372</v>
+      </c>
+      <c r="F43" s="23">
+        <v>0.10405747094225257</v>
+      </c>
+      <c r="H43" s="25">
+        <v>0.07033997723848215</v>
+      </c>
+      <c r="I43" s="25">
+        <v>0.07225610267122516</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="A44" s="17" t="s">
-        <v>4378</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>4379</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>4380</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>4381</v>
-      </c>
-      <c r="E44" s="22" t="s">
-        <v>4382</v>
-      </c>
-      <c r="F44" s="20">
-        <v>0.4935409261254934</v>
+      <c r="A44" s="20" t="s">
+        <v>4373</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>4374</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>4375</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>4376</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>4377</v>
+      </c>
+      <c r="F44" s="23">
+        <v>0.006144336801960007</v>
+      </c>
+      <c r="H44" s="25">
+        <v>0.05309210228122905</v>
+      </c>
+      <c r="I44" s="25">
+        <v>0.03360894551733227</v>
       </c>
     </row>
     <row r="45" spans="8:8">
-      <c r="A45" s="17" t="s">
-        <v>4383</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>4384</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>4385</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>4386</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>4387</v>
-      </c>
-      <c r="F45" s="20">
-        <v>0.12983263516201407</v>
+      <c r="A45" s="20" t="s">
+        <v>4378</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>4379</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>4380</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>4381</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>4382</v>
+      </c>
+      <c r="F45" s="23">
+        <v>0.4935409261254934</v>
+      </c>
+      <c r="H45" s="25">
+        <v>0.08764286200574223</v>
+      </c>
+      <c r="I45" s="25">
+        <v>0.11453382467468572</v>
       </c>
     </row>
     <row r="46" spans="8:8">
-      <c r="A46" s="17" t="s">
-        <v>4388</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>4389</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>4390</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>4391</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>4392</v>
-      </c>
-      <c r="F46" s="20">
-        <v>0.0579088394667248</v>
+      <c r="A46" s="20" t="s">
+        <v>4383</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>4384</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>4385</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>4386</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>4387</v>
+      </c>
+      <c r="F46" s="23">
+        <v>0.12983263516201407</v>
+      </c>
+      <c r="H46" s="25">
+        <v>0.05437549225888266</v>
+      </c>
+      <c r="I46" s="25">
+        <v>0.06437634460103164</v>
       </c>
     </row>
     <row r="47" spans="8:8">
-      <c r="A47" s="17" t="s">
-        <v>4393</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>4394</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>4395</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>4396</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>4397</v>
-      </c>
-      <c r="F47" s="20">
-        <v>0.0969647866414151</v>
+      <c r="A47" s="20" t="s">
+        <v>4388</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>4389</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>4390</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>4391</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>4392</v>
+      </c>
+      <c r="F47" s="23">
+        <v>0.0579088394667248</v>
+      </c>
+      <c r="H47" s="25">
+        <v>0.08030535556111061</v>
+      </c>
+      <c r="I47" s="25">
+        <v>0.0846230492134316</v>
       </c>
     </row>
     <row r="48" spans="8:8">
-      <c r="A48" s="17" t="s">
-        <v>4398</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>4399</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>4400</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>4401</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>4402</v>
-      </c>
-      <c r="F48" s="20">
-        <v>0.02665574181408414</v>
+      <c r="A48" s="20" t="s">
+        <v>4393</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>4394</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>4395</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>4396</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>4397</v>
+      </c>
+      <c r="F48" s="23">
+        <v>0.0969647866414151</v>
+      </c>
+      <c r="H48" s="25">
+        <v>0.04027813545296318</v>
+      </c>
+      <c r="I48" s="25">
+        <v>0.046699467127821054</v>
       </c>
     </row>
     <row r="49" spans="8:8">
-      <c r="A49" s="17" t="s">
-        <v>4403</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>4404</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>4405</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>4406</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>4407</v>
-      </c>
-      <c r="F49" s="20">
-        <v>0.0759864721107569</v>
+      <c r="A49" s="20" t="s">
+        <v>4398</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>4399</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>4400</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>4401</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>4402</v>
+      </c>
+      <c r="F49" s="23">
+        <v>0.02665574181408414</v>
+      </c>
+      <c r="H49" s="25">
+        <v>0.04147625000783528</v>
+      </c>
+      <c r="I49" s="25">
+        <v>0.027512414832243946</v>
       </c>
     </row>
     <row r="50" spans="8:8">
-      <c r="A50" s="17" t="s">
-        <v>4408</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>4409</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>4410</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>4411</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>4412</v>
-      </c>
-      <c r="F50" s="20">
-        <v>0.15957197157637068</v>
+      <c r="A50" s="20" t="s">
+        <v>4403</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>4404</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>4405</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>4406</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>4407</v>
+      </c>
+      <c r="F50" s="23">
+        <v>0.0759864721107569</v>
+      </c>
+      <c r="H50" s="25">
+        <v>0.05113228792699242</v>
+      </c>
+      <c r="I50" s="25">
+        <v>0.050680015976223416</v>
       </c>
     </row>
     <row r="51" spans="8:8">
-      <c r="A51" s="17" t="s">
-        <v>4413</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>4414</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>4415</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>4416</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>4417</v>
-      </c>
-      <c r="F51" s="20">
-        <v>0.2507032227940145</v>
+      <c r="A51" s="20" t="s">
+        <v>4408</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>4409</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>4410</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>4411</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>4412</v>
+      </c>
+      <c r="F51" s="23">
+        <v>0.15957197157637068</v>
+      </c>
+      <c r="H51" s="25">
+        <v>0.032603277647457754</v>
+      </c>
+      <c r="I51" s="25">
+        <v>0.05486264596332969</v>
       </c>
     </row>
     <row r="52" spans="8:8">
-      <c r="A52" s="17" t="s">
-        <v>4418</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>4419</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>4420</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>4421</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>4422</v>
-      </c>
-      <c r="F52" s="20">
+      <c r="A52" s="20" t="s">
+        <v>4413</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>4414</v>
+      </c>
+      <c r="C52" s="27" t="s">
+        <v>4415</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>4416</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>4417</v>
+      </c>
+      <c r="F52" s="23">
         <v>0.2507032227940145</v>
+      </c>
+      <c r="H52" s="25">
+        <v>0.051747299673365346</v>
+      </c>
+      <c r="I52" s="25">
+        <v>0.07990646637851548</v>
       </c>
     </row>
     <row r="53" spans="8:8">
-      <c r="A53" s="17" t="s">
-        <v>4423</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>4424</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>4425</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>4426</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>4427</v>
-      </c>
-      <c r="F53" s="20">
-        <v>0.0411232061341156</v>
+      <c r="A53" s="20" t="s">
+        <v>4418</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>4419</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>4420</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>4421</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>4422</v>
+      </c>
+      <c r="F53" s="23">
+        <v>0.2507032227940145</v>
+      </c>
+      <c r="H53" s="25">
+        <v>0.051747299673365346</v>
+      </c>
+      <c r="I53" s="25">
+        <v>0.07990646637851548</v>
       </c>
     </row>
     <row r="54" spans="8:8">
-      <c r="A54" s="17" t="s">
-        <v>4428</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>4429</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>4430</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>4431</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>4432</v>
-      </c>
-      <c r="F54" s="20">
-        <v>0.6586724207510878</v>
+      <c r="A54" s="20" t="s">
+        <v>4423</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>4424</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>4425</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>4426</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>4427</v>
+      </c>
+      <c r="F54" s="23">
+        <v>0.0411232061341156</v>
+      </c>
+      <c r="H54" s="25">
+        <v>0.03864478289872982</v>
+      </c>
+      <c r="I54" s="25">
+        <v>0.032310045960774435</v>
       </c>
     </row>
     <row r="55" spans="8:8">
-      <c r="A55" s="17" t="s">
-        <v>4433</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>4434</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>4435</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>4436</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>4437</v>
-      </c>
-      <c r="F55" s="20">
-        <v>0.2541951255595723</v>
+      <c r="A55" s="20" t="s">
+        <v>4428</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>4429</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>4430</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>4431</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>4432</v>
+      </c>
+      <c r="F55" s="23">
+        <v>0.6586724207510878</v>
+      </c>
+      <c r="H55" s="25">
+        <v>0.08776981781203018</v>
+      </c>
+      <c r="I55" s="25">
+        <v>0.17117918011917638</v>
       </c>
     </row>
     <row r="56" spans="8:8">
-      <c r="A56" s="17" t="s">
-        <v>4438</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>4439</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>4440</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>4441</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>4442</v>
-      </c>
-      <c r="F56" s="20">
-        <v>0.09015370419977155</v>
+      <c r="A56" s="20" t="s">
+        <v>4433</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>4434</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>4435</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>4436</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>4437</v>
+      </c>
+      <c r="F56" s="23">
+        <v>0.2541951255595723</v>
+      </c>
+      <c r="H56" s="25">
+        <v>0.028959293489646237</v>
+      </c>
+      <c r="I56" s="25">
+        <v>0.03903079636113687</v>
       </c>
     </row>
     <row r="57" spans="8:8">
-      <c r="A57" s="17" t="s">
-        <v>4443</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>4444</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>4445</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>4446</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>4447</v>
-      </c>
-      <c r="F57" s="20">
-        <v>0.0786667059743622</v>
+      <c r="A57" s="20" t="s">
+        <v>4438</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>4440</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>4441</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>4442</v>
+      </c>
+      <c r="F57" s="23">
+        <v>0.09015370419977155</v>
+      </c>
+      <c r="H57" s="25">
+        <v>0.061063635455106</v>
+      </c>
+      <c r="I57" s="25">
+        <v>0.10325711086494252</v>
       </c>
     </row>
     <row r="58" spans="8:8">
-      <c r="A58" s="17" t="s">
-        <v>4448</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>4449</v>
-      </c>
-      <c r="C58" s="22" t="s">
-        <v>4450</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>4451</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>4452</v>
-      </c>
-      <c r="F58" s="20">
-        <v>0.08017893290579836</v>
+      <c r="A58" s="20" t="s">
+        <v>4443</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>4444</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>4445</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>4446</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>4447</v>
+      </c>
+      <c r="F58" s="23">
+        <v>0.0786667059743622</v>
+      </c>
+      <c r="H58" s="25">
+        <v>0.07112602009100809</v>
+      </c>
+      <c r="I58" s="25">
+        <v>0.07470977550717703</v>
       </c>
     </row>
     <row r="59" spans="8:8">
-      <c r="A59" s="17" t="s">
-        <v>4453</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>4454</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>4455</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>4456</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>4457</v>
-      </c>
-      <c r="F59" s="20">
-        <v>0.056276173244985024</v>
+      <c r="A59" s="20" t="s">
+        <v>4448</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>4449</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>4450</v>
+      </c>
+      <c r="D59" s="27" t="s">
+        <v>4451</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>4452</v>
+      </c>
+      <c r="F59" s="23">
+        <v>0.08017893290579836</v>
+      </c>
+      <c r="H59" s="25">
+        <v>0.07383819857319583</v>
+      </c>
+      <c r="I59" s="25">
+        <v>0.06989554884783775</v>
       </c>
     </row>
     <row r="60" spans="8:8">
-      <c r="A60" s="17" t="s">
-        <v>4458</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>4459</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>4460</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>4461</v>
-      </c>
-      <c r="E60" s="22" t="s">
-        <v>4462</v>
-      </c>
-      <c r="F60" s="20">
-        <v>0.06146532366083644</v>
+      <c r="A60" s="20" t="s">
+        <v>4453</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>4454</v>
+      </c>
+      <c r="C60" s="27" t="s">
+        <v>4455</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>4456</v>
+      </c>
+      <c r="E60" s="27" t="s">
+        <v>4457</v>
+      </c>
+      <c r="F60" s="23">
+        <v>0.056276173244985024</v>
+      </c>
+      <c r="H60" s="25">
+        <v>0.05791045472890207</v>
+      </c>
+      <c r="I60" s="25">
+        <v>0.04546405580036862</v>
       </c>
     </row>
     <row r="61" spans="8:8">
-      <c r="A61" s="17" t="s">
-        <v>4463</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>4464</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>4465</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>4466</v>
-      </c>
-      <c r="E61" s="22" t="s">
-        <v>4467</v>
-      </c>
-      <c r="F61" s="20">
-        <v>0.022320430435404343</v>
+      <c r="A61" s="20" t="s">
+        <v>4458</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>4459</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>4460</v>
+      </c>
+      <c r="D61" s="27" t="s">
+        <v>4461</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>4462</v>
+      </c>
+      <c r="F61" s="23">
+        <v>0.06146532366083644</v>
+      </c>
+      <c r="H61" s="25">
+        <v>0.09966135113269331</v>
+      </c>
+      <c r="I61" s="25">
+        <v>0.10930817695977806</v>
       </c>
     </row>
     <row r="62" spans="8:8">
-      <c r="A62" s="17" t="s">
-        <v>4468</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>4469</v>
-      </c>
-      <c r="C62" s="22" t="s">
-        <v>4470</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>4471</v>
-      </c>
-      <c r="E62" s="22" t="s">
-        <v>4472</v>
-      </c>
-      <c r="F62" s="20">
-        <v>0.14093604025149037</v>
+      <c r="A62" s="20" t="s">
+        <v>4463</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>4464</v>
+      </c>
+      <c r="C62" s="27" t="s">
+        <v>4465</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>4466</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>4467</v>
+      </c>
+      <c r="F62" s="23">
+        <v>0.022320430435404343</v>
+      </c>
+      <c r="H62" s="25">
+        <v>0.08123188562332694</v>
+      </c>
+      <c r="I62" s="25">
+        <v>0.10115762124373626</v>
       </c>
     </row>
     <row r="63" spans="8:8">
-      <c r="A63" s="17" t="s">
-        <v>4473</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>4474</v>
-      </c>
-      <c r="C63" s="22" t="s">
-        <v>4475</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>4476</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>4477</v>
-      </c>
-      <c r="F63" s="20">
-        <v>0.03700954980255676</v>
+      <c r="A63" s="20" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>4469</v>
+      </c>
+      <c r="C63" s="27" t="s">
+        <v>4470</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>4471</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>4472</v>
+      </c>
+      <c r="F63" s="23">
+        <v>0.14093604025149037</v>
+      </c>
+      <c r="H63" s="25">
+        <v>0.07346979799641581</v>
+      </c>
+      <c r="I63" s="25">
+        <v>0.050394613702806346</v>
       </c>
     </row>
     <row r="64" spans="8:8">
-      <c r="A64" s="17" t="s">
-        <v>4478</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>4479</v>
-      </c>
-      <c r="C64" s="22" t="s">
-        <v>4480</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>4481</v>
-      </c>
-      <c r="E64" s="22" t="s">
-        <v>4482</v>
-      </c>
-      <c r="F64" s="20">
-        <v>0.0</v>
+      <c r="A64" s="20" t="s">
+        <v>4473</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>4474</v>
+      </c>
+      <c r="C64" s="27" t="s">
+        <v>4475</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>4476</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>4477</v>
+      </c>
+      <c r="F64" s="23">
+        <v>0.03700954980255676</v>
+      </c>
+      <c r="H64" s="25">
+        <v>0.006138075483457187</v>
+      </c>
+      <c r="I64" s="25">
+        <v>0.15708337096028557</v>
       </c>
     </row>
     <row r="65" spans="8:8">
-      <c r="A65" s="17" t="s">
-        <v>4483</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>4484</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>4485</v>
-      </c>
-      <c r="D65" s="22" t="s">
-        <v>4486</v>
-      </c>
-      <c r="E65" s="22" t="s">
-        <v>4487</v>
-      </c>
-      <c r="F65" s="20">
+      <c r="A65" s="20" t="s">
+        <v>4478</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>4479</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>4480</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>4481</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>4482</v>
+      </c>
+      <c r="F65" s="23">
         <v>0.0</v>
+      </c>
+      <c r="H65" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="I65" s="25">
+        <v>0.06305363229838544</v>
       </c>
     </row>
     <row r="66" spans="8:8">
-      <c r="A66" s="17" t="s">
-        <v>4488</v>
-      </c>
-      <c r="B66" s="17" t="s">
-        <v>4489</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>4490</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>4491</v>
-      </c>
-      <c r="E66" s="22" t="s">
-        <v>4492</v>
-      </c>
-      <c r="F66" s="20">
-        <v>0.04691637428963245</v>
+      <c r="A66" s="20" t="s">
+        <v>4483</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>4484</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>4485</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>4486</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>4487</v>
+      </c>
+      <c r="F66" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="H66" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="I66" s="25">
+        <v>0.21887591244542312</v>
       </c>
     </row>
     <row r="67" spans="8:8">
-      <c r="A67" s="17" t="s">
-        <v>4493</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>4494</v>
-      </c>
-      <c r="C67" s="22" t="s">
-        <v>4495</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>4496</v>
-      </c>
-      <c r="E67" s="22" t="s">
-        <v>4497</v>
-      </c>
-      <c r="F67" s="20">
-        <v>0.06913138761678468</v>
+      <c r="A67" s="20" t="s">
+        <v>4488</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>4489</v>
+      </c>
+      <c r="C67" s="27" t="s">
+        <v>4490</v>
+      </c>
+      <c r="D67" s="27" t="s">
+        <v>4491</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>4492</v>
+      </c>
+      <c r="F67" s="23">
+        <v>0.04691637428963245</v>
+      </c>
+      <c r="H67" s="25">
+        <v>0.00992930222684575</v>
+      </c>
+      <c r="I67" s="25">
+        <v>0.15444178277810133</v>
       </c>
     </row>
     <row r="68" spans="8:8">
-      <c r="A68" s="17" t="s">
-        <v>4498</v>
-      </c>
-      <c r="B68" s="17" t="s">
-        <v>4499</v>
-      </c>
-      <c r="C68" s="22" t="s">
-        <v>4500</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>4501</v>
-      </c>
-      <c r="E68" s="22" t="s">
-        <v>4502</v>
-      </c>
-      <c r="F68" s="20">
+      <c r="A68" s="20" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>4494</v>
+      </c>
+      <c r="C68" s="27" t="s">
+        <v>4495</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>4496</v>
+      </c>
+      <c r="E68" s="27" t="s">
+        <v>4497</v>
+      </c>
+      <c r="F68" s="23">
         <v>0.06913138761678468</v>
+      </c>
+      <c r="H68" s="25">
+        <v>0.0815567276804826</v>
+      </c>
+      <c r="I68" s="25">
+        <v>0.07307568961057789</v>
       </c>
     </row>
     <row r="69" spans="8:8">
-      <c r="A69" s="17" t="s">
-        <v>4503</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>4504</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>4505</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>4506</v>
-      </c>
-      <c r="E69" s="22" t="s">
-        <v>4507</v>
-      </c>
-      <c r="F69" s="20">
-        <v>0.034892710518697696</v>
+      <c r="A69" s="20" t="s">
+        <v>4498</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>4499</v>
+      </c>
+      <c r="C69" s="27" t="s">
+        <v>4500</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>4501</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>4502</v>
+      </c>
+      <c r="F69" s="23">
+        <v>0.06913138761678468</v>
+      </c>
+      <c r="H69" s="25">
+        <v>0.07821810662619413</v>
+      </c>
+      <c r="I69" s="25">
+        <v>0.06971091136783561</v>
       </c>
     </row>
     <row r="70" spans="8:8">
-      <c r="A70" s="17" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>4509</v>
-      </c>
-      <c r="C70" s="22" t="s">
-        <v>4510</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>4511</v>
-      </c>
-      <c r="E70" s="22" t="s">
-        <v>4512</v>
-      </c>
-      <c r="F70" s="20">
-        <v>0.07300762171565071</v>
+      <c r="A70" s="20" t="s">
+        <v>4503</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C70" s="27" t="s">
+        <v>4505</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>4506</v>
+      </c>
+      <c r="E70" s="27" t="s">
+        <v>4507</v>
+      </c>
+      <c r="F70" s="23">
+        <v>0.034892710518697696</v>
+      </c>
+      <c r="H70" s="25">
+        <v>0.07632021177610046</v>
+      </c>
+      <c r="I70" s="25">
+        <v>0.07690532478043993</v>
       </c>
     </row>
     <row r="71" spans="8:8">
-      <c r="A71" s="17" t="s">
-        <v>4513</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>4514</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>4515</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>4516</v>
-      </c>
-      <c r="E71" s="22" t="s">
-        <v>4517</v>
-      </c>
-      <c r="F71" s="20">
-        <v>0.0901066156417462</v>
+      <c r="A71" s="20" t="s">
+        <v>4508</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>4509</v>
+      </c>
+      <c r="C71" s="27" t="s">
+        <v>4510</v>
+      </c>
+      <c r="D71" s="27" t="s">
+        <v>4511</v>
+      </c>
+      <c r="E71" s="27" t="s">
+        <v>4512</v>
+      </c>
+      <c r="F71" s="23">
+        <v>0.07300762171565071</v>
+      </c>
+      <c r="H71" s="25">
+        <v>0.04669245019606618</v>
+      </c>
+      <c r="I71" s="25">
+        <v>0.08796038555838961</v>
       </c>
     </row>
     <row r="72" spans="8:8">
-      <c r="A72" s="17" t="s">
-        <v>4518</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>4519</v>
-      </c>
-      <c r="C72" s="22" t="s">
-        <v>4520</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>4521</v>
-      </c>
-      <c r="E72" s="22" t="s">
-        <v>4522</v>
-      </c>
-      <c r="F72" s="20">
-        <v>0.0</v>
+      <c r="A72" s="20" t="s">
+        <v>4513</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>4514</v>
+      </c>
+      <c r="C72" s="27" t="s">
+        <v>4515</v>
+      </c>
+      <c r="D72" s="27" t="s">
+        <v>4516</v>
+      </c>
+      <c r="E72" s="27" t="s">
+        <v>4517</v>
+      </c>
+      <c r="F72" s="23">
+        <v>0.0901066156417462</v>
+      </c>
+      <c r="H72" s="25">
+        <v>0.10076366875278608</v>
+      </c>
+      <c r="I72" s="25">
+        <v>0.048452251636374295</v>
       </c>
     </row>
     <row r="73" spans="8:8">
-      <c r="A73" s="17" t="s">
-        <v>4523</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>4524</v>
-      </c>
-      <c r="C73" s="22" t="s">
-        <v>4525</v>
-      </c>
-      <c r="D73" s="22" t="s">
-        <v>4526</v>
-      </c>
-      <c r="E73" s="22" t="s">
-        <v>4527</v>
-      </c>
-      <c r="F73" s="20">
+      <c r="A73" s="20" t="s">
+        <v>4518</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>4519</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>4520</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>4521</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>4522</v>
+      </c>
+      <c r="F73" s="23">
         <v>0.0</v>
+      </c>
+      <c r="H73" s="25">
+        <v>0.19678892697655986</v>
+      </c>
+      <c r="I73" s="25">
+        <v>0.2489440150482115</v>
       </c>
     </row>
     <row r="74" spans="8:8">
-      <c r="A74" s="17" t="s">
-        <v>4528</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>4529</v>
-      </c>
-      <c r="C74" s="22" t="s">
-        <v>4530</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>4531</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>4532</v>
-      </c>
-      <c r="F74" s="20">
+      <c r="A74" s="20" t="s">
+        <v>4523</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>4524</v>
+      </c>
+      <c r="C74" s="27" t="s">
+        <v>4525</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>4526</v>
+      </c>
+      <c r="E74" s="27" t="s">
+        <v>4527</v>
+      </c>
+      <c r="F74" s="23">
         <v>0.0</v>
+      </c>
+      <c r="H74" s="25">
+        <v>0.10311697230790394</v>
+      </c>
+      <c r="I74" s="25">
+        <v>0.009813048169297308</v>
       </c>
     </row>
     <row r="75" spans="8:8">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="20" t="s">
+        <v>4528</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>4529</v>
+      </c>
+      <c r="C75" s="27" t="s">
+        <v>4530</v>
+      </c>
+      <c r="D75" s="27" t="s">
+        <v>4531</v>
+      </c>
+      <c r="E75" s="27" t="s">
+        <v>4532</v>
+      </c>
+      <c r="F75" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="H75" s="25">
+        <v>0.19123018093987426</v>
+      </c>
+      <c r="I75" s="25">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="76" spans="8:8">
+      <c r="A76" s="20" t="s">
         <v>4533</v>
       </c>
-      <c r="B75" s="17" t="s">
+      <c r="B76" s="20" t="s">
         <v>4534</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C76" s="27" t="s">
         <v>4535</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D76" s="27" t="s">
         <v>4536</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E76" s="27" t="s">
         <v>4537</v>
       </c>
-      <c r="F75" s="20">
+      <c r="F76" s="23">
         <v>0.0</v>
+      </c>
+      <c r="H76" s="25">
+        <v>0.2890112246526713</v>
+      </c>
+      <c r="I76" s="25">
+        <v>0.4258120563350069</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="territory-wise-MPE-sales-achiev" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7531" count="7531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7818" count="7818">
   <si>
     <t>Region</t>
   </si>
@@ -65208,6 +65208,2589 @@
         <rFont val="Helvetica"/>
       </rPr>
       <t>Return Perc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
     </r>
   </si>
   <si>
@@ -68602,7 +71185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN397"/>
+  <dimension ref="A1:AO397"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -68663,122 +71246,122 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>7244</v>
+        <v>7531</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7245</v>
+        <v>7532</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7246</v>
+        <v>7533</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7247</v>
+        <v>7534</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7248</v>
+        <v>7535</v>
       </c>
       <c r="F2" s="3">
         <v>787067.06</v>
       </c>
       <c r="G2" s="3">
-        <v>4809.61</v>
+        <v>22610.52</v>
       </c>
       <c r="H2" s="3">
         <v>89418.63</v>
       </c>
       <c r="I2" s="3">
-        <v>94228.24</v>
+        <v>112029.15</v>
       </c>
       <c r="J2" s="3">
-        <v>11.97</v>
+        <v>14.23</v>
       </c>
       <c r="K2" s="3">
-        <v>-692838.82</v>
+        <v>-675037.91</v>
       </c>
       <c r="L2" s="3">
-        <v>0.0</v>
+        <v>0.15</v>
       </c>
       <c r="M2" s="3">
-        <v>0.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>7249</v>
+        <v>7536</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7250</v>
+        <v>7537</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7251</v>
+        <v>7538</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7252</v>
+        <v>7539</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7253</v>
+        <v>7540</v>
       </c>
       <c r="F3" s="3">
         <v>792403.1</v>
       </c>
       <c r="G3" s="3">
-        <v>4330.26</v>
+        <v>9485.33</v>
       </c>
       <c r="H3" s="3">
         <v>98339.8</v>
       </c>
       <c r="I3" s="3">
-        <v>102670.06</v>
+        <v>107825.13</v>
       </c>
       <c r="J3" s="3">
-        <v>12.96</v>
+        <v>13.61</v>
       </c>
       <c r="K3" s="3">
-        <v>-689733.04</v>
+        <v>-684577.97</v>
       </c>
       <c r="L3" s="3">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="M3" s="3">
-        <v>134.94</v>
+        <v>322.44</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>7254</v>
+        <v>7541</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7255</v>
+        <v>7542</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7256</v>
+        <v>7543</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7257</v>
+        <v>7544</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7258</v>
+        <v>7545</v>
       </c>
       <c r="F4" s="3">
         <v>672792.28</v>
       </c>
       <c r="G4" s="3">
-        <v>4262.48</v>
+        <v>15997.29</v>
       </c>
       <c r="H4" s="3">
         <v>81133.07</v>
       </c>
       <c r="I4" s="3">
-        <v>85395.55</v>
+        <v>97130.36</v>
       </c>
       <c r="J4" s="3">
-        <v>12.69</v>
+        <v>14.44</v>
       </c>
       <c r="K4" s="3">
-        <v>-587396.73</v>
+        <v>-575661.92</v>
       </c>
       <c r="L4" s="3">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="M4" s="3">
         <v>314.88</v>
@@ -68786,81 +71369,81 @@
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>7259</v>
+        <v>7546</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7260</v>
+        <v>7547</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7261</v>
+        <v>7548</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7262</v>
+        <v>7549</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7263</v>
+        <v>7550</v>
       </c>
       <c r="F5" s="3">
         <v>740010.55</v>
       </c>
       <c r="G5" s="3">
-        <v>2654.23</v>
+        <v>10423.72</v>
       </c>
       <c r="H5" s="3">
         <v>84208.71</v>
       </c>
       <c r="I5" s="3">
-        <v>86862.94</v>
+        <v>94632.43</v>
       </c>
       <c r="J5" s="3">
-        <v>11.74</v>
+        <v>12.79</v>
       </c>
       <c r="K5" s="3">
-        <v>-653147.61</v>
+        <v>-645378.12</v>
       </c>
       <c r="L5" s="3">
-        <v>0.0</v>
+        <v>0.66</v>
       </c>
       <c r="M5" s="3">
-        <v>0.0</v>
+        <v>623.93</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>7264</v>
+        <v>7551</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7265</v>
+        <v>7552</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7266</v>
+        <v>7553</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7267</v>
+        <v>7554</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7268</v>
+        <v>7555</v>
       </c>
       <c r="F6" s="3">
         <v>763526.5</v>
       </c>
       <c r="G6" s="3">
-        <v>11501.96</v>
+        <v>32715.15</v>
       </c>
       <c r="H6" s="3">
         <v>103282.95</v>
       </c>
       <c r="I6" s="3">
-        <v>114784.91</v>
+        <v>135998.1</v>
       </c>
       <c r="J6" s="3">
-        <v>15.03</v>
+        <v>17.81</v>
       </c>
       <c r="K6" s="3">
-        <v>-648741.59</v>
+        <v>-627528.4</v>
       </c>
       <c r="L6" s="3">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="M6" s="3">
         <v>314.88</v>
@@ -68868,242 +71451,242 @@
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>7269</v>
+        <v>7556</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7270</v>
+        <v>7557</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7271</v>
+        <v>7558</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7272</v>
+        <v>7559</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>7273</v>
+        <v>7560</v>
       </c>
       <c r="F7" s="3">
         <v>803185.79</v>
       </c>
       <c r="G7" s="3">
-        <v>8501.32</v>
+        <v>35717.17</v>
       </c>
       <c r="H7" s="3">
         <v>133070.66</v>
       </c>
       <c r="I7" s="3">
-        <v>141571.98</v>
+        <v>168787.83</v>
       </c>
       <c r="J7" s="3">
-        <v>17.63</v>
+        <v>21.01</v>
       </c>
       <c r="K7" s="3">
-        <v>-661613.81</v>
+        <v>-634397.96</v>
       </c>
       <c r="L7" s="3">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="M7" s="3">
-        <v>562.5</v>
+        <v>1058.75</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>7274</v>
+        <v>7561</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7275</v>
+        <v>7562</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>7276</v>
+        <v>7563</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7277</v>
+        <v>7564</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>7278</v>
+        <v>7565</v>
       </c>
       <c r="F8" s="3">
         <v>770724.92</v>
       </c>
       <c r="G8" s="3">
-        <v>5574.17</v>
+        <v>35721.45</v>
       </c>
       <c r="H8" s="3">
         <v>92043.57</v>
       </c>
       <c r="I8" s="3">
-        <v>97617.74</v>
+        <v>127765.02</v>
       </c>
       <c r="J8" s="3">
-        <v>12.67</v>
+        <v>16.58</v>
       </c>
       <c r="K8" s="3">
-        <v>-673107.18</v>
+        <v>-642959.9</v>
       </c>
       <c r="L8" s="3">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="M8" s="3">
-        <v>168.66</v>
+        <v>281.1</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>7279</v>
+        <v>7566</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7280</v>
+        <v>7567</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>7281</v>
+        <v>7568</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7282</v>
+        <v>7569</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>7283</v>
+        <v>7570</v>
       </c>
       <c r="F9" s="3">
         <v>774607.3</v>
       </c>
       <c r="G9" s="3">
-        <v>7687.28</v>
+        <v>48164.83</v>
       </c>
       <c r="H9" s="3">
-        <v>118405.77</v>
+        <v>118225.77</v>
       </c>
       <c r="I9" s="3">
-        <v>126093.05</v>
+        <v>166390.6</v>
       </c>
       <c r="J9" s="3">
-        <v>16.28</v>
+        <v>21.48</v>
       </c>
       <c r="K9" s="3">
-        <v>-648514.25</v>
+        <v>-608216.7</v>
       </c>
       <c r="L9" s="3">
-        <v>0.0</v>
+        <v>0.19</v>
       </c>
       <c r="M9" s="3">
-        <v>0.0</v>
+        <v>311.09</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>7284</v>
+        <v>7571</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>7285</v>
+        <v>7572</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>7286</v>
+        <v>7573</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7287</v>
+        <v>7574</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>7288</v>
+        <v>7575</v>
       </c>
       <c r="F10" s="3">
         <v>900349.47</v>
       </c>
       <c r="G10" s="3">
-        <v>2196.58</v>
+        <v>14671.04</v>
       </c>
       <c r="H10" s="3">
-        <v>148228.88</v>
+        <v>167117.72</v>
       </c>
       <c r="I10" s="3">
-        <v>150425.46</v>
+        <v>181788.76</v>
       </c>
       <c r="J10" s="3">
-        <v>16.71</v>
+        <v>20.19</v>
       </c>
       <c r="K10" s="3">
-        <v>-749924.01</v>
+        <v>-718560.71</v>
       </c>
       <c r="L10" s="3">
-        <v>0.0</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="3">
-        <v>0.0</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>7289</v>
+        <v>7576</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>7290</v>
+        <v>7577</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>7291</v>
+        <v>7578</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7292</v>
+        <v>7579</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>7293</v>
+        <v>7580</v>
       </c>
       <c r="F11" s="3">
         <v>901291.26</v>
       </c>
       <c r="G11" s="3">
-        <v>555.33</v>
+        <v>12764.54</v>
       </c>
       <c r="H11" s="3">
-        <v>118155.16</v>
+        <v>121139.26</v>
       </c>
       <c r="I11" s="3">
-        <v>118710.49</v>
+        <v>133903.8</v>
       </c>
       <c r="J11" s="3">
-        <v>13.17</v>
+        <v>14.86</v>
       </c>
       <c r="K11" s="3">
-        <v>-782580.77</v>
+        <v>-767387.46</v>
       </c>
       <c r="L11" s="3">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="M11" s="3">
-        <v>0.0</v>
+        <v>666.66</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>7294</v>
+        <v>7581</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>7295</v>
+        <v>7582</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>7296</v>
+        <v>7583</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7297</v>
+        <v>7584</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>7298</v>
+        <v>7585</v>
       </c>
       <c r="F12" s="3">
         <v>790977.36</v>
       </c>
       <c r="G12" s="3">
-        <v>1215.89</v>
+        <v>24548.16</v>
       </c>
       <c r="H12" s="3">
-        <v>110793.19</v>
+        <v>156642.64</v>
       </c>
       <c r="I12" s="3">
-        <v>112009.08</v>
+        <v>181190.8</v>
       </c>
       <c r="J12" s="3">
-        <v>14.16</v>
+        <v>22.91</v>
       </c>
       <c r="K12" s="3">
-        <v>-678968.28</v>
+        <v>-609786.56</v>
       </c>
       <c r="L12" s="3">
         <v>0.0</v>
@@ -69114,78 +71697,78 @@
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>7299</v>
+        <v>7586</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7300</v>
+        <v>7587</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>7301</v>
+        <v>7588</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7302</v>
+        <v>7589</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>7303</v>
+        <v>7590</v>
       </c>
       <c r="F13" s="3">
         <v>848180.28</v>
       </c>
       <c r="G13" s="3">
-        <v>1821.84</v>
+        <v>26789.23</v>
       </c>
       <c r="H13" s="3">
-        <v>137956.04</v>
+        <v>143057.84</v>
       </c>
       <c r="I13" s="3">
-        <v>139777.88</v>
+        <v>169847.07</v>
       </c>
       <c r="J13" s="3">
-        <v>16.48</v>
+        <v>20.02</v>
       </c>
       <c r="K13" s="3">
-        <v>-708402.4</v>
+        <v>-678333.21</v>
       </c>
       <c r="L13" s="3">
-        <v>0.0</v>
+        <v>0.1</v>
       </c>
       <c r="M13" s="3">
-        <v>0.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>7304</v>
+        <v>7591</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>7305</v>
+        <v>7592</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>7306</v>
+        <v>7593</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7307</v>
+        <v>7594</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>7308</v>
+        <v>7595</v>
       </c>
       <c r="F14" s="3">
         <v>788558.37</v>
       </c>
       <c r="G14" s="3">
-        <v>5395.38</v>
+        <v>18141.36</v>
       </c>
       <c r="H14" s="3">
         <v>141225.52</v>
       </c>
       <c r="I14" s="3">
-        <v>146620.9</v>
+        <v>159366.88</v>
       </c>
       <c r="J14" s="3">
-        <v>18.59</v>
+        <v>20.21</v>
       </c>
       <c r="K14" s="3">
-        <v>-641937.47</v>
+        <v>-629191.49</v>
       </c>
       <c r="L14" s="3">
         <v>0.0</v>
@@ -69196,37 +71779,37 @@
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>7309</v>
+        <v>7596</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>7310</v>
+        <v>7597</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>7311</v>
+        <v>7598</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7312</v>
+        <v>7599</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>7313</v>
+        <v>7600</v>
       </c>
       <c r="F15" s="3">
         <v>816369.33</v>
       </c>
       <c r="G15" s="3">
-        <v>4474.0</v>
+        <v>8193.21</v>
       </c>
       <c r="H15" s="3">
         <v>114399.26</v>
       </c>
       <c r="I15" s="3">
-        <v>118873.26</v>
+        <v>122592.47</v>
       </c>
       <c r="J15" s="3">
-        <v>14.56</v>
+        <v>15.02</v>
       </c>
       <c r="K15" s="3">
-        <v>-697496.07</v>
+        <v>-693776.86</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -69237,37 +71820,37 @@
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>7314</v>
+        <v>7601</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>7315</v>
+        <v>7602</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>7316</v>
+        <v>7603</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7317</v>
+        <v>7604</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>7318</v>
+        <v>7605</v>
       </c>
       <c r="F16" s="3">
         <v>792760.6</v>
       </c>
       <c r="G16" s="3">
-        <v>3953.14</v>
+        <v>11500.41</v>
       </c>
       <c r="H16" s="3">
         <v>65935.56</v>
       </c>
       <c r="I16" s="3">
-        <v>69888.7</v>
+        <v>77435.97</v>
       </c>
       <c r="J16" s="3">
-        <v>8.82</v>
+        <v>9.77</v>
       </c>
       <c r="K16" s="3">
-        <v>-722871.9</v>
+        <v>-715324.63</v>
       </c>
       <c r="L16" s="3">
         <v>0.0</v>
@@ -69278,245 +71861,245 @@
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>7319</v>
+        <v>7606</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>7320</v>
+        <v>7607</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>7321</v>
+        <v>7608</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7322</v>
+        <v>7609</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>7323</v>
+        <v>7610</v>
       </c>
       <c r="F17" s="3">
         <v>786604.47</v>
       </c>
       <c r="G17" s="3">
-        <v>5493.0</v>
+        <v>9305.61</v>
       </c>
       <c r="H17" s="3">
         <v>88183.85</v>
       </c>
       <c r="I17" s="3">
-        <v>93676.85</v>
+        <v>97489.46</v>
       </c>
       <c r="J17" s="3">
-        <v>11.91</v>
+        <v>12.39</v>
       </c>
       <c r="K17" s="3">
-        <v>-692927.62</v>
+        <v>-689115.01</v>
       </c>
       <c r="L17" s="3">
-        <v>0.0</v>
+        <v>0.22</v>
       </c>
       <c r="M17" s="3">
-        <v>0.0</v>
+        <v>213.65</v>
       </c>
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>7324</v>
+        <v>7611</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>7325</v>
+        <v>7612</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>7326</v>
+        <v>7613</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7327</v>
+        <v>7614</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>7328</v>
+        <v>7615</v>
       </c>
       <c r="F18" s="3">
         <v>1063383.58</v>
       </c>
       <c r="G18" s="3">
-        <v>1370.76</v>
+        <v>26704.0</v>
       </c>
       <c r="H18" s="3">
         <v>73085.44</v>
       </c>
       <c r="I18" s="3">
-        <v>74456.2</v>
+        <v>99789.44</v>
       </c>
       <c r="J18" s="3">
-        <v>7.0</v>
+        <v>9.38</v>
       </c>
       <c r="K18" s="3">
-        <v>-988927.38</v>
+        <v>-963594.14</v>
       </c>
       <c r="L18" s="3">
-        <v>0.0</v>
+        <v>1.66</v>
       </c>
       <c r="M18" s="3">
-        <v>0.0</v>
+        <v>1655.78</v>
       </c>
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>7329</v>
+        <v>7616</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>7330</v>
+        <v>7617</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>7331</v>
+        <v>7618</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7332</v>
+        <v>7619</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>7333</v>
+        <v>7620</v>
       </c>
       <c r="F19" s="3">
         <v>886606.12</v>
       </c>
       <c r="G19" s="3">
-        <v>4130.42</v>
+        <v>26706.76</v>
       </c>
       <c r="H19" s="3">
         <v>62470.28</v>
       </c>
       <c r="I19" s="3">
-        <v>66600.7</v>
+        <v>89177.04</v>
       </c>
       <c r="J19" s="3">
-        <v>7.51</v>
+        <v>10.06</v>
       </c>
       <c r="K19" s="3">
-        <v>-820005.42</v>
+        <v>-797429.08</v>
       </c>
       <c r="L19" s="3">
-        <v>0.0</v>
+        <v>0.58</v>
       </c>
       <c r="M19" s="3">
-        <v>0.0</v>
+        <v>517.16</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>7334</v>
+        <v>7621</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>7335</v>
+        <v>7622</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>7336</v>
+        <v>7623</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7337</v>
+        <v>7624</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>7338</v>
+        <v>7625</v>
       </c>
       <c r="F20" s="3">
         <v>1264233.6</v>
       </c>
       <c r="G20" s="3">
-        <v>6353.97</v>
+        <v>36368.63</v>
       </c>
       <c r="H20" s="3">
         <v>138961.04</v>
       </c>
       <c r="I20" s="3">
-        <v>145315.01</v>
+        <v>175329.67</v>
       </c>
       <c r="J20" s="3">
-        <v>11.49</v>
+        <v>13.87</v>
       </c>
       <c r="K20" s="3">
-        <v>-1118918.59</v>
+        <v>-1088903.93</v>
       </c>
       <c r="L20" s="3">
-        <v>0.0</v>
+        <v>0.77</v>
       </c>
       <c r="M20" s="3">
-        <v>0.0</v>
+        <v>1349.88</v>
       </c>
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>7339</v>
+        <v>7626</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>7340</v>
+        <v>7627</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>7341</v>
+        <v>7628</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7342</v>
+        <v>7629</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>7343</v>
+        <v>7630</v>
       </c>
       <c r="F21" s="3">
         <v>873034.8</v>
       </c>
       <c r="G21" s="3">
-        <v>14517.09</v>
+        <v>39029.82</v>
       </c>
       <c r="H21" s="3">
         <v>98496.83</v>
       </c>
       <c r="I21" s="3">
-        <v>113013.92</v>
+        <v>137526.65</v>
       </c>
       <c r="J21" s="3">
-        <v>12.94</v>
+        <v>15.75</v>
       </c>
       <c r="K21" s="3">
-        <v>-760020.88</v>
+        <v>-735508.15</v>
       </c>
       <c r="L21" s="3">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="M21" s="3">
-        <v>432.6</v>
+        <v>632.0</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>7344</v>
+        <v>7631</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>7345</v>
+        <v>7632</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>7346</v>
+        <v>7633</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7347</v>
+        <v>7634</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>7348</v>
+        <v>7635</v>
       </c>
       <c r="F22" s="3">
         <v>891542.61</v>
       </c>
       <c r="G22" s="3">
-        <v>15686.17</v>
+        <v>26668.05</v>
       </c>
       <c r="H22" s="3">
         <v>94585.55</v>
       </c>
       <c r="I22" s="3">
-        <v>110271.72</v>
+        <v>121253.6</v>
       </c>
       <c r="J22" s="3">
-        <v>12.37</v>
+        <v>13.6</v>
       </c>
       <c r="K22" s="3">
-        <v>-781270.89</v>
+        <v>-770289.01</v>
       </c>
       <c r="L22" s="3">
-        <v>0.69</v>
+        <v>0.62</v>
       </c>
       <c r="M22" s="3">
         <v>756.08</v>
@@ -69524,40 +72107,40 @@
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>7349</v>
+        <v>7636</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>7350</v>
+        <v>7637</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>7351</v>
+        <v>7638</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7352</v>
+        <v>7639</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>7353</v>
+        <v>7640</v>
       </c>
       <c r="F23" s="3">
         <v>876168.01</v>
       </c>
       <c r="G23" s="3">
-        <v>24119.16</v>
+        <v>48820.8</v>
       </c>
       <c r="H23" s="3">
         <v>101248.54</v>
       </c>
       <c r="I23" s="3">
-        <v>125367.7</v>
+        <v>150069.34</v>
       </c>
       <c r="J23" s="3">
-        <v>14.31</v>
+        <v>17.13</v>
       </c>
       <c r="K23" s="3">
-        <v>-750800.31</v>
+        <v>-726098.67</v>
       </c>
       <c r="L23" s="3">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="M23" s="3">
         <v>2042.88</v>
@@ -69565,40 +72148,40 @@
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>7354</v>
+        <v>7641</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>7355</v>
+        <v>7642</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>7356</v>
+        <v>7643</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7357</v>
+        <v>7644</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>7358</v>
+        <v>7645</v>
       </c>
       <c r="F24" s="3">
         <v>821118.86</v>
       </c>
       <c r="G24" s="3">
-        <v>14761.52</v>
+        <v>58901.1</v>
       </c>
       <c r="H24" s="3">
         <v>91149.4</v>
       </c>
       <c r="I24" s="3">
-        <v>105910.92</v>
+        <v>150050.5</v>
       </c>
       <c r="J24" s="3">
-        <v>12.9</v>
+        <v>18.27</v>
       </c>
       <c r="K24" s="3">
-        <v>-715207.94</v>
+        <v>-671068.36</v>
       </c>
       <c r="L24" s="3">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="M24" s="3">
         <v>450.0</v>
@@ -69606,78 +72189,78 @@
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>7359</v>
+        <v>7646</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>7360</v>
+        <v>7647</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>7361</v>
+        <v>7648</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7362</v>
+        <v>7649</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>7363</v>
+        <v>7650</v>
       </c>
       <c r="F25" s="3">
         <v>969063.25</v>
       </c>
       <c r="G25" s="3">
-        <v>11128.05</v>
+        <v>17209.34</v>
       </c>
       <c r="H25" s="3">
         <v>123904.28</v>
       </c>
       <c r="I25" s="3">
-        <v>135032.33</v>
+        <v>141113.62</v>
       </c>
       <c r="J25" s="3">
-        <v>13.93</v>
+        <v>14.56</v>
       </c>
       <c r="K25" s="3">
-        <v>-834030.92</v>
+        <v>-827949.63</v>
       </c>
       <c r="L25" s="3">
-        <v>0.0</v>
+        <v>0.19</v>
       </c>
       <c r="M25" s="3">
-        <v>0.0</v>
+        <v>270.62</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>7364</v>
+        <v>7651</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>7365</v>
+        <v>7652</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>7366</v>
+        <v>7653</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7367</v>
+        <v>7654</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>7368</v>
+        <v>7655</v>
       </c>
       <c r="F26" s="3">
         <v>1050193.29</v>
       </c>
       <c r="G26" s="3">
-        <v>1131.87</v>
+        <v>15510.96</v>
       </c>
       <c r="H26" s="3">
         <v>105801.47</v>
       </c>
       <c r="I26" s="3">
-        <v>106933.34</v>
+        <v>121312.43</v>
       </c>
       <c r="J26" s="3">
-        <v>10.18</v>
+        <v>11.55</v>
       </c>
       <c r="K26" s="3">
-        <v>-943259.95</v>
+        <v>-928880.86</v>
       </c>
       <c r="L26" s="3">
         <v>0.0</v>
@@ -69688,37 +72271,37 @@
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>7369</v>
+        <v>7656</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>7370</v>
+        <v>7657</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>7371</v>
+        <v>7658</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7372</v>
+        <v>7659</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>7373</v>
+        <v>7660</v>
       </c>
       <c r="F27" s="3">
         <v>919135.8</v>
       </c>
       <c r="G27" s="3">
-        <v>14461.78</v>
+        <v>33840.82</v>
       </c>
       <c r="H27" s="3">
         <v>100044.49</v>
       </c>
       <c r="I27" s="3">
-        <v>114506.27</v>
+        <v>133885.31</v>
       </c>
       <c r="J27" s="3">
-        <v>12.46</v>
+        <v>14.57</v>
       </c>
       <c r="K27" s="3">
-        <v>-804629.53</v>
+        <v>-785250.49</v>
       </c>
       <c r="L27" s="3">
         <v>0.0</v>
@@ -69729,37 +72312,37 @@
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>7374</v>
+        <v>7661</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>7375</v>
+        <v>7662</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>7376</v>
+        <v>7663</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7377</v>
+        <v>7664</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>7378</v>
+        <v>7665</v>
       </c>
       <c r="F28" s="3">
         <v>1002913.88</v>
       </c>
       <c r="G28" s="3">
-        <v>20912.91</v>
+        <v>48604.28</v>
       </c>
       <c r="H28" s="3">
         <v>86637.52</v>
       </c>
       <c r="I28" s="3">
-        <v>107550.43</v>
+        <v>135241.8</v>
       </c>
       <c r="J28" s="3">
-        <v>10.72</v>
+        <v>13.48</v>
       </c>
       <c r="K28" s="3">
-        <v>-895363.45</v>
+        <v>-867672.08</v>
       </c>
       <c r="L28" s="3">
         <v>0.0</v>
@@ -69770,183 +72353,183 @@
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>7379</v>
+        <v>7666</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>7380</v>
+        <v>7667</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>7381</v>
+        <v>7668</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7382</v>
+        <v>7669</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>7383</v>
+        <v>7670</v>
       </c>
       <c r="F29" s="3">
         <v>872858.67</v>
       </c>
       <c r="G29" s="3">
-        <v>16192.78</v>
+        <v>68310.49</v>
       </c>
       <c r="H29" s="3">
         <v>68421.25</v>
       </c>
       <c r="I29" s="3">
-        <v>84614.03</v>
+        <v>136731.74</v>
       </c>
       <c r="J29" s="3">
-        <v>9.69</v>
+        <v>15.66</v>
       </c>
       <c r="K29" s="3">
-        <v>-788244.64</v>
+        <v>-736126.93</v>
       </c>
       <c r="L29" s="3">
-        <v>0.0</v>
+        <v>2.31</v>
       </c>
       <c r="M29" s="3">
-        <v>0.0</v>
+        <v>3160.24</v>
       </c>
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>7384</v>
+        <v>7671</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>7385</v>
+        <v>7672</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>7386</v>
+        <v>7673</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7387</v>
+        <v>7674</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>7388</v>
+        <v>7675</v>
       </c>
       <c r="F30" s="3">
         <v>890266.15</v>
       </c>
       <c r="G30" s="3">
-        <v>5606.25</v>
+        <v>26009.38</v>
       </c>
       <c r="H30" s="3">
         <v>88308.16</v>
       </c>
       <c r="I30" s="3">
-        <v>93914.41</v>
+        <v>114317.54</v>
       </c>
       <c r="J30" s="3">
-        <v>10.55</v>
+        <v>12.84</v>
       </c>
       <c r="K30" s="3">
-        <v>-796351.74</v>
+        <v>-775948.61</v>
       </c>
       <c r="L30" s="3">
-        <v>0.34</v>
+        <v>3.34</v>
       </c>
       <c r="M30" s="3">
-        <v>314.88</v>
+        <v>3817.82</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>7389</v>
+        <v>7676</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>7390</v>
+        <v>7677</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>7391</v>
+        <v>7678</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7392</v>
+        <v>7679</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>7393</v>
+        <v>7680</v>
       </c>
       <c r="F31" s="3">
         <v>984099.44</v>
       </c>
       <c r="G31" s="3">
-        <v>16841.51</v>
+        <v>48144.95</v>
       </c>
       <c r="H31" s="3">
         <v>82948.15</v>
       </c>
       <c r="I31" s="3">
-        <v>99789.66</v>
+        <v>131093.1</v>
       </c>
       <c r="J31" s="3">
-        <v>10.14</v>
+        <v>13.32</v>
       </c>
       <c r="K31" s="3">
-        <v>-884309.78</v>
+        <v>-853006.34</v>
       </c>
       <c r="L31" s="3">
-        <v>0.0</v>
+        <v>0.81</v>
       </c>
       <c r="M31" s="3">
-        <v>0.0</v>
+        <v>1056.67</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>7394</v>
+        <v>7681</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>7395</v>
+        <v>7682</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>7396</v>
+        <v>7683</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7397</v>
+        <v>7684</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>7398</v>
+        <v>7685</v>
       </c>
       <c r="F32" s="3">
         <v>926984.47</v>
       </c>
       <c r="G32" s="3">
-        <v>7877.45</v>
+        <v>28000.6</v>
       </c>
       <c r="H32" s="3">
         <v>77532.72</v>
       </c>
       <c r="I32" s="3">
-        <v>85410.17</v>
+        <v>105533.32</v>
       </c>
       <c r="J32" s="3">
-        <v>9.21</v>
+        <v>11.38</v>
       </c>
       <c r="K32" s="3">
-        <v>-841574.3</v>
+        <v>-821451.15</v>
       </c>
       <c r="L32" s="3">
-        <v>0.0</v>
+        <v>2.56</v>
       </c>
       <c r="M32" s="3">
-        <v>0.0</v>
+        <v>2701.92</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>7399</v>
+        <v>7686</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>7400</v>
+        <v>7687</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>7401</v>
+        <v>7688</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7402</v>
+        <v>7689</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>7403</v>
+        <v>7690</v>
       </c>
       <c r="F33" s="3">
         <v>1288411.21</v>
@@ -69975,19 +72558,19 @@
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>7404</v>
+        <v>7691</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>7405</v>
+        <v>7692</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>7406</v>
+        <v>7693</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7407</v>
+        <v>7694</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>7408</v>
+        <v>7695</v>
       </c>
       <c r="F34" s="3">
         <v>1074641.52</v>
@@ -70016,19 +72599,19 @@
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>7409</v>
+        <v>7696</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>7410</v>
+        <v>7697</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>7411</v>
+        <v>7698</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7412</v>
+        <v>7699</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>7413</v>
+        <v>7700</v>
       </c>
       <c r="F35" s="3">
         <v>1054434.17</v>
@@ -70057,37 +72640,37 @@
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>7414</v>
+        <v>7701</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>7415</v>
+        <v>7702</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>7416</v>
+        <v>7703</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7417</v>
+        <v>7704</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>7418</v>
+        <v>7705</v>
       </c>
       <c r="F36" s="3">
         <v>1145461.66</v>
       </c>
       <c r="G36" s="3">
-        <v>0.0</v>
+        <v>64037.52</v>
       </c>
       <c r="H36" s="3">
         <v>239523.78</v>
       </c>
       <c r="I36" s="3">
-        <v>239523.78</v>
+        <v>303561.3</v>
       </c>
       <c r="J36" s="3">
-        <v>20.91</v>
+        <v>26.5</v>
       </c>
       <c r="K36" s="3">
-        <v>-905937.88</v>
+        <v>-841900.36</v>
       </c>
       <c r="L36" s="3">
         <v>0.0</v>
@@ -70098,306 +72681,306 @@
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>7419</v>
+        <v>7706</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>7420</v>
+        <v>7707</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>7421</v>
+        <v>7708</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7422</v>
+        <v>7709</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>7423</v>
+        <v>7710</v>
       </c>
       <c r="F37" s="3">
         <v>1392111.83</v>
       </c>
       <c r="G37" s="3">
-        <v>0.0</v>
+        <v>68365.21</v>
       </c>
       <c r="H37" s="3">
         <v>249013.7</v>
       </c>
       <c r="I37" s="3">
-        <v>249013.7</v>
+        <v>317378.91</v>
       </c>
       <c r="J37" s="3">
-        <v>17.89</v>
+        <v>22.8</v>
       </c>
       <c r="K37" s="3">
-        <v>-1143098.13</v>
+        <v>-1074732.92</v>
       </c>
       <c r="L37" s="3">
-        <v>0.0</v>
+        <v>0.53</v>
       </c>
       <c r="M37" s="3">
-        <v>0.0</v>
+        <v>1681.08</v>
       </c>
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>7424</v>
+        <v>7711</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>7425</v>
+        <v>7712</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>7426</v>
+        <v>7713</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7427</v>
+        <v>7714</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>7428</v>
+        <v>7715</v>
       </c>
       <c r="F38" s="3">
         <v>958935.26</v>
       </c>
       <c r="G38" s="3">
-        <v>0.0</v>
+        <v>67438.92</v>
       </c>
       <c r="H38" s="3">
         <v>173016.09</v>
       </c>
       <c r="I38" s="3">
-        <v>173016.09</v>
+        <v>240455.01</v>
       </c>
       <c r="J38" s="3">
-        <v>18.04</v>
+        <v>25.08</v>
       </c>
       <c r="K38" s="3">
-        <v>-785919.17</v>
+        <v>-718480.25</v>
       </c>
       <c r="L38" s="3">
-        <v>0.0</v>
+        <v>3.67</v>
       </c>
       <c r="M38" s="3">
-        <v>0.0</v>
+        <v>8834.08</v>
       </c>
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>7429</v>
+        <v>7716</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>7430</v>
+        <v>7717</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>7431</v>
+        <v>7718</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>7432</v>
+        <v>7719</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>7433</v>
+        <v>7720</v>
       </c>
       <c r="F39" s="3">
         <v>1141876.38</v>
       </c>
       <c r="G39" s="3">
-        <v>0.0</v>
+        <v>44569.73</v>
       </c>
       <c r="H39" s="3">
         <v>176272.69</v>
       </c>
       <c r="I39" s="3">
-        <v>176272.69</v>
+        <v>220842.42</v>
       </c>
       <c r="J39" s="3">
-        <v>15.44</v>
+        <v>19.34</v>
       </c>
       <c r="K39" s="3">
-        <v>-965603.69</v>
+        <v>-921033.96</v>
       </c>
       <c r="L39" s="3">
-        <v>0.0</v>
+        <v>0.79</v>
       </c>
       <c r="M39" s="3">
-        <v>0.0</v>
+        <v>1737.16</v>
       </c>
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>7434</v>
+        <v>7721</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>7435</v>
+        <v>7722</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>7436</v>
+        <v>7723</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7437</v>
+        <v>7724</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>7438</v>
+        <v>7725</v>
       </c>
       <c r="F40" s="3">
         <v>936014.91</v>
       </c>
       <c r="G40" s="3">
-        <v>0.0</v>
+        <v>13613.38</v>
       </c>
       <c r="H40" s="3">
-        <v>82452.8</v>
+        <v>120794.54</v>
       </c>
       <c r="I40" s="3">
-        <v>82452.8</v>
+        <v>134407.92</v>
       </c>
       <c r="J40" s="3">
-        <v>8.81</v>
+        <v>14.36</v>
       </c>
       <c r="K40" s="3">
-        <v>-853562.11</v>
+        <v>-801606.99</v>
       </c>
       <c r="L40" s="3">
-        <v>0.0</v>
+        <v>0.2</v>
       </c>
       <c r="M40" s="3">
-        <v>0.0</v>
+        <v>269.86</v>
       </c>
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>7439</v>
+        <v>7726</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>7440</v>
+        <v>7727</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>7441</v>
+        <v>7728</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7442</v>
+        <v>7729</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>7443</v>
+        <v>7730</v>
       </c>
       <c r="F41" s="3">
         <v>1227064.36</v>
       </c>
       <c r="G41" s="3">
-        <v>0.0</v>
+        <v>1879.74</v>
       </c>
       <c r="H41" s="3">
-        <v>125224.51</v>
+        <v>180608.37</v>
       </c>
       <c r="I41" s="3">
-        <v>125224.51</v>
+        <v>182488.11</v>
       </c>
       <c r="J41" s="3">
-        <v>10.21</v>
+        <v>14.87</v>
       </c>
       <c r="K41" s="3">
-        <v>-1101839.85</v>
+        <v>-1044576.25</v>
       </c>
       <c r="L41" s="3">
-        <v>0.0</v>
+        <v>0.43</v>
       </c>
       <c r="M41" s="3">
-        <v>0.0</v>
+        <v>787.2</v>
       </c>
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>7444</v>
+        <v>7731</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>7445</v>
+        <v>7732</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>7446</v>
+        <v>7733</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>7447</v>
+        <v>7734</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>7448</v>
+        <v>7735</v>
       </c>
       <c r="F42" s="3">
         <v>940955.58</v>
       </c>
       <c r="G42" s="3">
-        <v>0.0</v>
+        <v>8712.75</v>
       </c>
       <c r="H42" s="3">
-        <v>148594.87</v>
+        <v>198402.78</v>
       </c>
       <c r="I42" s="3">
-        <v>148594.87</v>
+        <v>207115.53</v>
       </c>
       <c r="J42" s="3">
-        <v>15.79</v>
+        <v>22.01</v>
       </c>
       <c r="K42" s="3">
-        <v>-792360.71</v>
+        <v>-733840.05</v>
       </c>
       <c r="L42" s="3">
-        <v>0.0</v>
+        <v>0.54</v>
       </c>
       <c r="M42" s="3">
-        <v>0.0</v>
+        <v>1115.9</v>
       </c>
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>7449</v>
+        <v>7736</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>7450</v>
+        <v>7737</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>7451</v>
+        <v>7738</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>7452</v>
+        <v>7739</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>7453</v>
+        <v>7740</v>
       </c>
       <c r="F43" s="3">
         <v>1062667.74</v>
       </c>
       <c r="G43" s="3">
-        <v>0.0</v>
+        <v>6305.99</v>
       </c>
       <c r="H43" s="3">
-        <v>148019.5</v>
+        <v>222238.85</v>
       </c>
       <c r="I43" s="3">
-        <v>148019.5</v>
+        <v>228544.84</v>
       </c>
       <c r="J43" s="3">
-        <v>13.93</v>
+        <v>21.51</v>
       </c>
       <c r="K43" s="3">
-        <v>-914648.24</v>
+        <v>-834122.9</v>
       </c>
       <c r="L43" s="3">
-        <v>0.0</v>
+        <v>0.42</v>
       </c>
       <c r="M43" s="3">
-        <v>0.0</v>
+        <v>958.12</v>
       </c>
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>7454</v>
+        <v>7741</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>7455</v>
+        <v>7742</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>7456</v>
+        <v>7743</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7457</v>
+        <v>7744</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>7458</v>
+        <v>7745</v>
       </c>
       <c r="F44" s="3">
         <v>1129524.64</v>
@@ -70426,19 +73009,19 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>7459</v>
+        <v>7746</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>7460</v>
+        <v>7747</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>7461</v>
+        <v>7748</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7462</v>
+        <v>7749</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>7463</v>
+        <v>7750</v>
       </c>
       <c r="F45" s="3">
         <v>931654.84</v>
@@ -70467,19 +73050,19 @@
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>7464</v>
+        <v>7751</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>7465</v>
+        <v>7752</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>7466</v>
+        <v>7753</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>7467</v>
+        <v>7754</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>7468</v>
+        <v>7755</v>
       </c>
       <c r="F46" s="3">
         <v>1096879.63</v>
@@ -70508,19 +73091,19 @@
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>7469</v>
+        <v>7756</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>7470</v>
+        <v>7757</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>7471</v>
+        <v>7758</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>7472</v>
+        <v>7759</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>7473</v>
+        <v>7760</v>
       </c>
       <c r="F47" s="3">
         <v>1362950.73</v>
@@ -70549,19 +73132,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>7474</v>
+        <v>7761</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>7475</v>
+        <v>7762</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>7476</v>
+        <v>7763</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>7477</v>
+        <v>7764</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>7478</v>
+        <v>7765</v>
       </c>
       <c r="F48" s="3">
         <v>1050721.66</v>
@@ -70590,19 +73173,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>7479</v>
+        <v>7766</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>7480</v>
+        <v>7767</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>7481</v>
+        <v>7768</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7482</v>
+        <v>7769</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>7483</v>
+        <v>7770</v>
       </c>
       <c r="F49" s="3">
         <v>989655.83</v>
@@ -70611,16 +73194,16 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="3">
-        <v>193487.7</v>
+        <v>193562.66</v>
       </c>
       <c r="I49" s="3">
-        <v>193487.7</v>
+        <v>193562.66</v>
       </c>
       <c r="J49" s="3">
-        <v>19.55</v>
+        <v>19.56</v>
       </c>
       <c r="K49" s="3">
-        <v>-796168.13</v>
+        <v>-796093.17</v>
       </c>
       <c r="L49" s="3">
         <v>0.0</v>
@@ -70631,19 +73214,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>7484</v>
+        <v>7771</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>7485</v>
+        <v>7772</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>7486</v>
+        <v>7773</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>7487</v>
+        <v>7774</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>7488</v>
+        <v>7775</v>
       </c>
       <c r="F50" s="3">
         <v>978747.3</v>
@@ -70672,19 +73255,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>7489</v>
+        <v>7776</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>7490</v>
+        <v>7777</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>7491</v>
+        <v>7778</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>7492</v>
+        <v>7779</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>7493</v>
+        <v>7780</v>
       </c>
       <c r="F51" s="3">
         <v>983156.92</v>
@@ -70713,19 +73296,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>7494</v>
+        <v>7781</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>7495</v>
+        <v>7782</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>7496</v>
+        <v>7783</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7497</v>
+        <v>7784</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>7498</v>
+        <v>7785</v>
       </c>
       <c r="F52" s="3">
         <v>1178421.11</v>
@@ -77229,7 +79812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AJ49"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -77279,282 +79862,282 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>7499</v>
+        <v>7786</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7500</v>
+        <v>7787</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7501</v>
+        <v>7788</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7502</v>
+        <v>7789</v>
       </c>
       <c r="E2" s="3">
         <v>6104317.5</v>
       </c>
       <c r="F2" s="3">
-        <v>23975.86</v>
+        <v>210835.44</v>
       </c>
       <c r="G2" s="3">
-        <v>799903.17</v>
+        <v>799723.17</v>
       </c>
       <c r="H2" s="3">
-        <v>823879.03</v>
+        <v>1010558.61</v>
       </c>
       <c r="I2" s="3">
-        <v>13.5</v>
+        <v>16.55</v>
       </c>
       <c r="J2" s="3">
-        <v>-5280438.47</v>
+        <v>-5093758.89</v>
       </c>
       <c r="K2" s="3">
-        <v>449.82</v>
+        <v>3396.07</v>
       </c>
       <c r="L2" s="3">
-        <v>0.05</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>7503</v>
+        <v>7790</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7504</v>
+        <v>7791</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7505</v>
+        <v>7792</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7506</v>
+        <v>7793</v>
       </c>
       <c r="E3" s="3">
         <v>3440798.37</v>
       </c>
       <c r="F3" s="3">
-        <v>1174.8</v>
+        <v>78772.98</v>
       </c>
       <c r="G3" s="3">
         <v>587957.47</v>
       </c>
       <c r="H3" s="3">
-        <v>589132.27</v>
+        <v>666730.45</v>
       </c>
       <c r="I3" s="3">
-        <v>17.12</v>
+        <v>19.38</v>
       </c>
       <c r="J3" s="3">
-        <v>-2851666.1</v>
+        <v>-2774067.92</v>
       </c>
       <c r="K3" s="3">
-        <v>0.0</v>
+        <v>1023.16</v>
       </c>
       <c r="L3" s="3">
-        <v>0.0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>7507</v>
+        <v>7794</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7508</v>
+        <v>7795</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7509</v>
+        <v>7796</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7510</v>
+        <v>7797</v>
       </c>
       <c r="E4" s="3">
         <v>6398516.07</v>
       </c>
       <c r="F4" s="3">
-        <v>13096.53</v>
+        <v>136919.99</v>
       </c>
       <c r="G4" s="3">
         <v>684260.95</v>
       </c>
       <c r="H4" s="3">
-        <v>697357.48</v>
+        <v>821180.94</v>
       </c>
       <c r="I4" s="3">
-        <v>10.9</v>
+        <v>12.83</v>
       </c>
       <c r="J4" s="3">
-        <v>-5701158.59</v>
+        <v>-5577335.13</v>
       </c>
       <c r="K4" s="3">
-        <v>0.0</v>
+        <v>3736.47</v>
       </c>
       <c r="L4" s="3">
-        <v>0.0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>7511</v>
+        <v>7798</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7512</v>
+        <v>7799</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7513</v>
+        <v>7800</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7514</v>
+        <v>7801</v>
       </c>
       <c r="E5" s="3">
         <v>7403170.5</v>
       </c>
       <c r="F5" s="3">
-        <v>95820.4</v>
+        <v>288585.18</v>
       </c>
       <c r="G5" s="3">
         <v>801868.09</v>
       </c>
       <c r="H5" s="3">
-        <v>897688.49</v>
+        <v>1090453.27</v>
       </c>
       <c r="I5" s="3">
-        <v>12.13</v>
+        <v>14.73</v>
       </c>
       <c r="J5" s="3">
-        <v>-6505482.01</v>
+        <v>-6312717.23</v>
       </c>
       <c r="K5" s="3">
-        <v>2305.28</v>
+        <v>4151.58</v>
       </c>
       <c r="L5" s="3">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>7515</v>
+        <v>7802</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7516</v>
+        <v>7803</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7517</v>
+        <v>7804</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7518</v>
+        <v>7805</v>
       </c>
       <c r="E6" s="3">
         <v>7091695.63</v>
       </c>
       <c r="F6" s="3">
-        <v>26340.5</v>
+        <v>170465.41</v>
       </c>
       <c r="G6" s="3">
         <v>892634.71</v>
       </c>
       <c r="H6" s="3">
-        <v>918975.21</v>
+        <v>1063100.12</v>
       </c>
       <c r="I6" s="3">
-        <v>12.96</v>
+        <v>14.99</v>
       </c>
       <c r="J6" s="3">
-        <v>-6172720.42</v>
+        <v>-6028595.51</v>
       </c>
       <c r="K6" s="3">
-        <v>314.88</v>
+        <v>10736.65</v>
       </c>
       <c r="L6" s="3">
-        <v>0.03</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>7519</v>
+        <v>7806</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7520</v>
+        <v>7807</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7521</v>
+        <v>7808</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7522</v>
+        <v>7809</v>
       </c>
       <c r="E7" s="3">
         <v>4638385.13</v>
       </c>
       <c r="F7" s="3">
-        <v>0.0</v>
+        <v>244411.38</v>
       </c>
       <c r="G7" s="3">
         <v>837826.26</v>
       </c>
       <c r="H7" s="3">
-        <v>837826.26</v>
+        <v>1082237.64</v>
       </c>
       <c r="I7" s="3">
-        <v>18.06</v>
+        <v>23.33</v>
       </c>
       <c r="J7" s="3">
-        <v>-3800558.87</v>
+        <v>-3556147.49</v>
       </c>
       <c r="K7" s="3">
-        <v>0.0</v>
+        <v>12252.32</v>
       </c>
       <c r="L7" s="3">
-        <v>0.0</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>7523</v>
+        <v>7810</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7524</v>
+        <v>7811</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>7525</v>
+        <v>7812</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7526</v>
+        <v>7813</v>
       </c>
       <c r="E8" s="3">
         <v>7324761.7</v>
       </c>
       <c r="F8" s="3">
-        <v>0.0</v>
+        <v>30511.86</v>
       </c>
       <c r="G8" s="3">
         <v>1072827.05</v>
       </c>
       <c r="H8" s="3">
-        <v>1072827.05</v>
+        <v>1103338.91</v>
       </c>
       <c r="I8" s="3">
-        <v>14.65</v>
+        <v>15.06</v>
       </c>
       <c r="J8" s="3">
-        <v>-6251934.65</v>
+        <v>-6221422.79</v>
       </c>
       <c r="K8" s="3">
-        <v>0.0</v>
+        <v>3131.08</v>
       </c>
       <c r="L8" s="3">
-        <v>0.0</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>7527</v>
+        <v>7814</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7528</v>
+        <v>7815</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>7529</v>
+        <v>7816</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7530</v>
+        <v>7817</v>
       </c>
       <c r="E9" s="3">
         <v>6543653.55</v>
@@ -77563,16 +80146,16 @@
         <v>0.0</v>
       </c>
       <c r="G9" s="3">
-        <v>1058699.28</v>
+        <v>1058774.24</v>
       </c>
       <c r="H9" s="3">
-        <v>1058699.28</v>
+        <v>1058774.24</v>
       </c>
       <c r="I9" s="3">
         <v>16.18</v>
       </c>
       <c r="J9" s="3">
-        <v>-5484954.27</v>
+        <v>-5484879.31</v>
       </c>
       <c r="K9" s="3">
         <v>0.0</v>
@@ -78686,7 +81269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AD78"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="9" max="9" customWidth="1" width="5.8984375" style="0"/>
@@ -82015,7 +84598,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="29"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8392" count="8392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8934" count="8934">
   <si>
     <t>Region</t>
   </si>
@@ -73245,6 +73245,4884 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
     </r>
   </si>
   <si>
@@ -76351,7 +81229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR397"/>
+  <dimension ref="A1:AS397"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -76412,40 +81290,40 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>8105</v>
+        <v>8647</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8106</v>
+        <v>8648</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8107</v>
+        <v>8649</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8108</v>
+        <v>8650</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8109</v>
+        <v>8651</v>
       </c>
       <c r="F2" s="3">
         <v>787067.06</v>
       </c>
       <c r="G2" s="3">
-        <v>38644.61</v>
+        <v>38658.11</v>
       </c>
       <c r="H2" s="3">
-        <v>217897.88</v>
+        <v>211705.54</v>
       </c>
       <c r="I2" s="3">
-        <v>256542.49</v>
+        <v>250363.65</v>
       </c>
       <c r="J2" s="3">
-        <v>32.59</v>
+        <v>31.81</v>
       </c>
       <c r="K2" s="3">
-        <v>-530524.57</v>
+        <v>-536703.41</v>
       </c>
       <c r="L2" s="3">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="M2" s="3">
         <v>1469.11</v>
@@ -76453,19 +81331,19 @@
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>8110</v>
+        <v>8652</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8111</v>
+        <v>8653</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8112</v>
+        <v>8654</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8113</v>
+        <v>8655</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8114</v>
+        <v>8656</v>
       </c>
       <c r="F3" s="3">
         <v>792403.1</v>
@@ -76474,19 +81352,19 @@
         <v>27660.32</v>
       </c>
       <c r="H3" s="3">
-        <v>229282.71</v>
+        <v>246369.89</v>
       </c>
       <c r="I3" s="3">
-        <v>256943.03</v>
+        <v>274030.21</v>
       </c>
       <c r="J3" s="3">
-        <v>32.43</v>
+        <v>34.58</v>
       </c>
       <c r="K3" s="3">
-        <v>-535460.07</v>
+        <v>-518372.89</v>
       </c>
       <c r="L3" s="3">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="M3" s="3">
         <v>2871.24</v>
@@ -76494,19 +81372,19 @@
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>8115</v>
+        <v>8657</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8116</v>
+        <v>8658</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8117</v>
+        <v>8659</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8118</v>
+        <v>8660</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8119</v>
+        <v>8661</v>
       </c>
       <c r="F4" s="3">
         <v>672792.28</v>
@@ -76515,19 +81393,19 @@
         <v>46596.63</v>
       </c>
       <c r="H4" s="3">
-        <v>175860.56</v>
+        <v>188414.7</v>
       </c>
       <c r="I4" s="3">
-        <v>222457.19</v>
+        <v>235011.33</v>
       </c>
       <c r="J4" s="3">
-        <v>33.06</v>
+        <v>34.93</v>
       </c>
       <c r="K4" s="3">
-        <v>-450335.09</v>
+        <v>-437780.95</v>
       </c>
       <c r="L4" s="3">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="M4" s="3">
         <v>570.14</v>
@@ -76535,60 +81413,60 @@
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>8120</v>
+        <v>8662</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8121</v>
+        <v>8663</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8122</v>
+        <v>8664</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8123</v>
+        <v>8665</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8124</v>
+        <v>8666</v>
       </c>
       <c r="F5" s="3">
         <v>740010.55</v>
       </c>
       <c r="G5" s="3">
-        <v>32176.07</v>
+        <v>32232.32</v>
       </c>
       <c r="H5" s="3">
-        <v>152014.71</v>
+        <v>153252.61</v>
       </c>
       <c r="I5" s="3">
-        <v>184190.78</v>
+        <v>185484.93</v>
       </c>
       <c r="J5" s="3">
-        <v>24.89</v>
+        <v>25.07</v>
       </c>
       <c r="K5" s="3">
-        <v>-555819.77</v>
+        <v>-554525.62</v>
       </c>
       <c r="L5" s="3">
-        <v>0.49</v>
+        <v>1.59</v>
       </c>
       <c r="M5" s="3">
-        <v>893.93</v>
+        <v>2955.43</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>8125</v>
+        <v>8667</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8126</v>
+        <v>8668</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8127</v>
+        <v>8669</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8128</v>
+        <v>8670</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8129</v>
+        <v>8671</v>
       </c>
       <c r="F6" s="3">
         <v>763526.5</v>
@@ -76597,19 +81475,19 @@
         <v>68095.72</v>
       </c>
       <c r="H6" s="3">
-        <v>193207.68</v>
+        <v>221141.93</v>
       </c>
       <c r="I6" s="3">
-        <v>261303.4</v>
+        <v>289237.65</v>
       </c>
       <c r="J6" s="3">
-        <v>34.22</v>
+        <v>37.88</v>
       </c>
       <c r="K6" s="3">
-        <v>-502223.1</v>
+        <v>-474288.85</v>
       </c>
       <c r="L6" s="3">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M6" s="3">
         <v>1433.5</v>
@@ -76617,40 +81495,40 @@
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>8130</v>
+        <v>8672</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8131</v>
+        <v>8673</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8132</v>
+        <v>8674</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8133</v>
+        <v>8675</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8134</v>
+        <v>8676</v>
       </c>
       <c r="F7" s="3">
         <v>803185.79</v>
       </c>
       <c r="G7" s="3">
-        <v>59431.3</v>
+        <v>59532.55</v>
       </c>
       <c r="H7" s="3">
-        <v>203593.59</v>
+        <v>217364.92</v>
       </c>
       <c r="I7" s="3">
-        <v>263024.89</v>
+        <v>276897.47</v>
       </c>
       <c r="J7" s="3">
-        <v>32.75</v>
+        <v>34.47</v>
       </c>
       <c r="K7" s="3">
-        <v>-540160.9</v>
+        <v>-526288.32</v>
       </c>
       <c r="L7" s="3">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="M7" s="3">
         <v>1058.75</v>
@@ -76658,40 +81536,40 @@
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>8135</v>
+        <v>8677</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8136</v>
+        <v>8678</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8137</v>
+        <v>8679</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8138</v>
+        <v>8680</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8139</v>
+        <v>8681</v>
       </c>
       <c r="F8" s="3">
         <v>770724.92</v>
       </c>
       <c r="G8" s="3">
-        <v>51037.21</v>
+        <v>61556.31</v>
       </c>
       <c r="H8" s="3">
-        <v>159876.78</v>
+        <v>165578.71</v>
       </c>
       <c r="I8" s="3">
-        <v>210913.99</v>
+        <v>227135.02</v>
       </c>
       <c r="J8" s="3">
-        <v>27.37</v>
+        <v>29.47</v>
       </c>
       <c r="K8" s="3">
-        <v>-559810.93</v>
+        <v>-543589.9</v>
       </c>
       <c r="L8" s="3">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M8" s="3">
         <v>416.1</v>
@@ -76699,19 +81577,19 @@
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>8140</v>
+        <v>8682</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8141</v>
+        <v>8683</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8142</v>
+        <v>8684</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8143</v>
+        <v>8685</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8144</v>
+        <v>8686</v>
       </c>
       <c r="F9" s="3">
         <v>774607.3</v>
@@ -76720,19 +81598,19 @@
         <v>78172.63</v>
       </c>
       <c r="H9" s="3">
-        <v>147120.14</v>
+        <v>163931.41</v>
       </c>
       <c r="I9" s="3">
-        <v>225292.77</v>
+        <v>242104.04</v>
       </c>
       <c r="J9" s="3">
-        <v>29.08</v>
+        <v>31.26</v>
       </c>
       <c r="K9" s="3">
-        <v>-549314.53</v>
+        <v>-532503.26</v>
       </c>
       <c r="L9" s="3">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="M9" s="3">
         <v>311.09</v>
@@ -76740,19 +81618,19 @@
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>8145</v>
+        <v>8687</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8146</v>
+        <v>8688</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8147</v>
+        <v>8689</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8148</v>
+        <v>8690</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8149</v>
+        <v>8691</v>
       </c>
       <c r="F10" s="3">
         <v>900349.47</v>
@@ -76761,16 +81639,16 @@
         <v>35590.42</v>
       </c>
       <c r="H10" s="3">
-        <v>201185.28</v>
+        <v>199914.14</v>
       </c>
       <c r="I10" s="3">
-        <v>236775.7</v>
+        <v>235504.56</v>
       </c>
       <c r="J10" s="3">
-        <v>26.3</v>
+        <v>26.16</v>
       </c>
       <c r="K10" s="3">
-        <v>-663573.77</v>
+        <v>-664844.91</v>
       </c>
       <c r="L10" s="3">
         <v>0.29</v>
@@ -76781,60 +81659,60 @@
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>8150</v>
+        <v>8692</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8151</v>
+        <v>8693</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8152</v>
+        <v>8694</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8153</v>
+        <v>8695</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8154</v>
+        <v>8696</v>
       </c>
       <c r="F11" s="3">
         <v>901291.26</v>
       </c>
       <c r="G11" s="3">
-        <v>33572.23</v>
+        <v>33645.35</v>
       </c>
       <c r="H11" s="3">
-        <v>159082.21</v>
+        <v>158531.88</v>
       </c>
       <c r="I11" s="3">
-        <v>192654.44</v>
+        <v>192177.23</v>
       </c>
       <c r="J11" s="3">
-        <v>21.38</v>
+        <v>21.32</v>
       </c>
       <c r="K11" s="3">
-        <v>-708636.82</v>
+        <v>-709114.03</v>
       </c>
       <c r="L11" s="3">
-        <v>0.46</v>
+        <v>1.54</v>
       </c>
       <c r="M11" s="3">
-        <v>891.66</v>
+        <v>2953.16</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>8155</v>
+        <v>8697</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8156</v>
+        <v>8698</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8157</v>
+        <v>8699</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8158</v>
+        <v>8700</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8159</v>
+        <v>8701</v>
       </c>
       <c r="F12" s="3">
         <v>790977.36</v>
@@ -76843,19 +81721,19 @@
         <v>56436.01</v>
       </c>
       <c r="H12" s="3">
-        <v>204486.16</v>
+        <v>209988.65</v>
       </c>
       <c r="I12" s="3">
-        <v>260922.17</v>
+        <v>266424.66</v>
       </c>
       <c r="J12" s="3">
-        <v>32.99</v>
+        <v>33.68</v>
       </c>
       <c r="K12" s="3">
-        <v>-530055.19</v>
+        <v>-524552.7</v>
       </c>
       <c r="L12" s="3">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="M12" s="3">
         <v>1402.08</v>
@@ -76863,40 +81741,40 @@
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>8160</v>
+        <v>8702</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>8161</v>
+        <v>8703</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8162</v>
+        <v>8704</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8163</v>
+        <v>8705</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8164</v>
+        <v>8706</v>
       </c>
       <c r="F13" s="3">
         <v>848180.28</v>
       </c>
       <c r="G13" s="3">
-        <v>47105.49</v>
+        <v>47123.04</v>
       </c>
       <c r="H13" s="3">
-        <v>215407.68</v>
+        <v>204956.28</v>
       </c>
       <c r="I13" s="3">
-        <v>262513.17</v>
+        <v>252079.32</v>
       </c>
       <c r="J13" s="3">
-        <v>30.95</v>
+        <v>29.72</v>
       </c>
       <c r="K13" s="3">
-        <v>-585667.11</v>
+        <v>-596100.96</v>
       </c>
       <c r="L13" s="3">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="M13" s="3">
         <v>1581.61</v>
@@ -76904,19 +81782,19 @@
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>8165</v>
+        <v>8707</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>8166</v>
+        <v>8708</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8167</v>
+        <v>8709</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8168</v>
+        <v>8710</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8169</v>
+        <v>8711</v>
       </c>
       <c r="F14" s="3">
         <v>788558.37</v>
@@ -76925,16 +81803,16 @@
         <v>48905.58</v>
       </c>
       <c r="H14" s="3">
-        <v>204802.65</v>
+        <v>214656.14</v>
       </c>
       <c r="I14" s="3">
-        <v>253708.23</v>
+        <v>263561.72</v>
       </c>
       <c r="J14" s="3">
-        <v>32.17</v>
+        <v>33.42</v>
       </c>
       <c r="K14" s="3">
-        <v>-534850.14</v>
+        <v>-524996.65</v>
       </c>
       <c r="L14" s="3">
         <v>0.0</v>
@@ -76945,19 +81823,19 @@
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>8170</v>
+        <v>8712</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>8171</v>
+        <v>8713</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8172</v>
+        <v>8714</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8173</v>
+        <v>8715</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8174</v>
+        <v>8716</v>
       </c>
       <c r="F15" s="3">
         <v>816369.33</v>
@@ -76966,16 +81844,16 @@
         <v>25638.43</v>
       </c>
       <c r="H15" s="3">
-        <v>176345.64</v>
+        <v>186211.81</v>
       </c>
       <c r="I15" s="3">
-        <v>201984.07</v>
+        <v>211850.24</v>
       </c>
       <c r="J15" s="3">
-        <v>24.74</v>
+        <v>25.95</v>
       </c>
       <c r="K15" s="3">
-        <v>-614385.26</v>
+        <v>-604519.09</v>
       </c>
       <c r="L15" s="3">
         <v>0.1</v>
@@ -76986,37 +81864,37 @@
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>8175</v>
+        <v>8717</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>8176</v>
+        <v>8718</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8177</v>
+        <v>8719</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8178</v>
+        <v>8720</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>8179</v>
+        <v>8721</v>
       </c>
       <c r="F16" s="3">
         <v>792760.6</v>
       </c>
       <c r="G16" s="3">
-        <v>31450.57</v>
+        <v>31470.82</v>
       </c>
       <c r="H16" s="3">
-        <v>103042.31</v>
+        <v>103574.73</v>
       </c>
       <c r="I16" s="3">
-        <v>134492.88</v>
+        <v>135045.55</v>
       </c>
       <c r="J16" s="3">
-        <v>16.97</v>
+        <v>17.03</v>
       </c>
       <c r="K16" s="3">
-        <v>-658267.72</v>
+        <v>-657715.05</v>
       </c>
       <c r="L16" s="3">
         <v>0.47</v>
@@ -77027,40 +81905,40 @@
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>8180</v>
+        <v>8722</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>8181</v>
+        <v>8723</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8182</v>
+        <v>8724</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8183</v>
+        <v>8725</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>8184</v>
+        <v>8726</v>
       </c>
       <c r="F17" s="3">
         <v>786604.47</v>
       </c>
       <c r="G17" s="3">
-        <v>32508.73</v>
+        <v>32593.1</v>
       </c>
       <c r="H17" s="3">
-        <v>122141.29</v>
+        <v>129889.61</v>
       </c>
       <c r="I17" s="3">
-        <v>154650.02</v>
+        <v>162482.71</v>
       </c>
       <c r="J17" s="3">
-        <v>19.66</v>
+        <v>20.66</v>
       </c>
       <c r="K17" s="3">
-        <v>-631954.45</v>
+        <v>-624121.76</v>
       </c>
       <c r="L17" s="3">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="M17" s="3">
         <v>213.65</v>
@@ -77068,19 +81946,19 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>8185</v>
+        <v>8727</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>8186</v>
+        <v>8728</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8187</v>
+        <v>8729</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8188</v>
+        <v>8730</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>8189</v>
+        <v>8731</v>
       </c>
       <c r="F18" s="3">
         <v>1063383.58</v>
@@ -77109,19 +81987,19 @@
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>8190</v>
+        <v>8732</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>8191</v>
+        <v>8733</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8192</v>
+        <v>8734</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8193</v>
+        <v>8735</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>8194</v>
+        <v>8736</v>
       </c>
       <c r="F19" s="3">
         <v>886606.12</v>
@@ -77150,19 +82028,19 @@
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>8195</v>
+        <v>8737</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>8196</v>
+        <v>8738</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8197</v>
+        <v>8739</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8198</v>
+        <v>8740</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>8199</v>
+        <v>8741</v>
       </c>
       <c r="F20" s="3">
         <v>1264233.6</v>
@@ -77191,40 +82069,40 @@
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>8200</v>
+        <v>8742</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>8201</v>
+        <v>8743</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8202</v>
+        <v>8744</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8203</v>
+        <v>8745</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>8204</v>
+        <v>8746</v>
       </c>
       <c r="F21" s="3">
         <v>873034.8</v>
       </c>
       <c r="G21" s="3">
-        <v>90055.25</v>
+        <v>90134.0</v>
       </c>
       <c r="H21" s="3">
-        <v>114134.07</v>
+        <v>130073.2</v>
       </c>
       <c r="I21" s="3">
-        <v>204189.32</v>
+        <v>220207.2</v>
       </c>
       <c r="J21" s="3">
-        <v>23.39</v>
+        <v>25.22</v>
       </c>
       <c r="K21" s="3">
-        <v>-668845.48</v>
+        <v>-652827.6</v>
       </c>
       <c r="L21" s="3">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="M21" s="3">
         <v>1501.34</v>
@@ -77232,19 +82110,19 @@
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>8205</v>
+        <v>8747</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>8206</v>
+        <v>8748</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8207</v>
+        <v>8749</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8208</v>
+        <v>8750</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>8209</v>
+        <v>8751</v>
       </c>
       <c r="F22" s="3">
         <v>891542.61</v>
@@ -77253,19 +82131,19 @@
         <v>73912.8</v>
       </c>
       <c r="H22" s="3">
-        <v>124068.27</v>
+        <v>141106.72</v>
       </c>
       <c r="I22" s="3">
-        <v>197981.07</v>
+        <v>215019.52</v>
       </c>
       <c r="J22" s="3">
-        <v>22.21</v>
+        <v>24.12</v>
       </c>
       <c r="K22" s="3">
-        <v>-693561.54</v>
+        <v>-676523.09</v>
       </c>
       <c r="L22" s="3">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="M22" s="3">
         <v>3274.64</v>
@@ -77273,19 +82151,19 @@
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>8210</v>
+        <v>8752</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>8211</v>
+        <v>8753</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8212</v>
+        <v>8754</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8213</v>
+        <v>8755</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>8214</v>
+        <v>8756</v>
       </c>
       <c r="F23" s="3">
         <v>876168.01</v>
@@ -77294,19 +82172,19 @@
         <v>96000.87</v>
       </c>
       <c r="H23" s="3">
-        <v>130029.25</v>
+        <v>151944.27</v>
       </c>
       <c r="I23" s="3">
-        <v>226030.12</v>
+        <v>247945.14</v>
       </c>
       <c r="J23" s="3">
-        <v>25.8</v>
+        <v>28.3</v>
       </c>
       <c r="K23" s="3">
-        <v>-650137.89</v>
+        <v>-628222.87</v>
       </c>
       <c r="L23" s="3">
-        <v>5.27</v>
+        <v>4.8</v>
       </c>
       <c r="M23" s="3">
         <v>11904.62</v>
@@ -77314,40 +82192,40 @@
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>8215</v>
+        <v>8757</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>8216</v>
+        <v>8758</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8217</v>
+        <v>8759</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8218</v>
+        <v>8760</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>8219</v>
+        <v>8761</v>
       </c>
       <c r="F24" s="3">
         <v>821118.86</v>
       </c>
       <c r="G24" s="3">
-        <v>101602.71</v>
+        <v>101621.61</v>
       </c>
       <c r="H24" s="3">
-        <v>167391.55</v>
+        <v>185035.47</v>
       </c>
       <c r="I24" s="3">
-        <v>268994.26</v>
+        <v>286657.08</v>
       </c>
       <c r="J24" s="3">
-        <v>32.76</v>
+        <v>34.91</v>
       </c>
       <c r="K24" s="3">
-        <v>-552124.6</v>
+        <v>-534461.78</v>
       </c>
       <c r="L24" s="3">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="M24" s="3">
         <v>1035.0</v>
@@ -77355,40 +82233,40 @@
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>8220</v>
+        <v>8762</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>8221</v>
+        <v>8763</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8222</v>
+        <v>8764</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8223</v>
+        <v>8765</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>8224</v>
+        <v>8766</v>
       </c>
       <c r="F25" s="3">
         <v>969063.25</v>
       </c>
       <c r="G25" s="3">
-        <v>52189.53</v>
+        <v>52296.41</v>
       </c>
       <c r="H25" s="3">
-        <v>132389.85</v>
+        <v>135557.77</v>
       </c>
       <c r="I25" s="3">
-        <v>184579.38</v>
+        <v>187854.18</v>
       </c>
       <c r="J25" s="3">
-        <v>19.05</v>
+        <v>19.39</v>
       </c>
       <c r="K25" s="3">
-        <v>-784483.87</v>
+        <v>-781209.07</v>
       </c>
       <c r="L25" s="3">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="M25" s="3">
         <v>270.62</v>
@@ -77396,19 +82274,19 @@
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>8225</v>
+        <v>8767</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>8226</v>
+        <v>8768</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8227</v>
+        <v>8769</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8228</v>
+        <v>8770</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>8229</v>
+        <v>8771</v>
       </c>
       <c r="F26" s="3">
         <v>1050193.29</v>
@@ -77417,19 +82295,19 @@
         <v>53865.75</v>
       </c>
       <c r="H26" s="3">
-        <v>96954.25</v>
+        <v>111543.21</v>
       </c>
       <c r="I26" s="3">
-        <v>150820.0</v>
+        <v>165408.96</v>
       </c>
       <c r="J26" s="3">
-        <v>14.36</v>
+        <v>15.75</v>
       </c>
       <c r="K26" s="3">
-        <v>-899373.29</v>
+        <v>-884784.33</v>
       </c>
       <c r="L26" s="3">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="M26" s="3">
         <v>767.41</v>
@@ -77437,19 +82315,19 @@
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>8230</v>
+        <v>8772</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>8231</v>
+        <v>8773</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8232</v>
+        <v>8774</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8233</v>
+        <v>8775</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>8234</v>
+        <v>8776</v>
       </c>
       <c r="F27" s="3">
         <v>919135.8</v>
@@ -77458,19 +82336,19 @@
         <v>85140.6</v>
       </c>
       <c r="H27" s="3">
-        <v>118379.68</v>
+        <v>133384.15</v>
       </c>
       <c r="I27" s="3">
-        <v>203520.28</v>
+        <v>218524.75</v>
       </c>
       <c r="J27" s="3">
-        <v>22.14</v>
+        <v>23.78</v>
       </c>
       <c r="K27" s="3">
-        <v>-715615.52</v>
+        <v>-700611.05</v>
       </c>
       <c r="L27" s="3">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="M27" s="3">
         <v>2307.36</v>
@@ -77478,37 +82356,37 @@
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>8235</v>
+        <v>8777</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>8236</v>
+        <v>8778</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8237</v>
+        <v>8779</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8238</v>
+        <v>8780</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>8239</v>
+        <v>8781</v>
       </c>
       <c r="F28" s="3">
         <v>1002913.88</v>
       </c>
       <c r="G28" s="3">
-        <v>90756.98</v>
+        <v>90782.63</v>
       </c>
       <c r="H28" s="3">
-        <v>114351.54</v>
+        <v>115690.42</v>
       </c>
       <c r="I28" s="3">
-        <v>205108.52</v>
+        <v>206473.05</v>
       </c>
       <c r="J28" s="3">
-        <v>20.45</v>
+        <v>20.59</v>
       </c>
       <c r="K28" s="3">
-        <v>-797805.36</v>
+        <v>-796440.83</v>
       </c>
       <c r="L28" s="3">
         <v>0.08</v>
@@ -77519,40 +82397,40 @@
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>8240</v>
+        <v>8782</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>8241</v>
+        <v>8783</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8242</v>
+        <v>8784</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8243</v>
+        <v>8785</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>8244</v>
+        <v>8786</v>
       </c>
       <c r="F29" s="3">
         <v>872858.67</v>
       </c>
       <c r="G29" s="3">
-        <v>100208.87</v>
+        <v>100223.72</v>
       </c>
       <c r="H29" s="3">
-        <v>122440.9</v>
+        <v>146927.63</v>
       </c>
       <c r="I29" s="3">
-        <v>222649.77</v>
+        <v>247151.35</v>
       </c>
       <c r="J29" s="3">
-        <v>25.51</v>
+        <v>28.32</v>
       </c>
       <c r="K29" s="3">
-        <v>-650208.9</v>
+        <v>-625707.32</v>
       </c>
       <c r="L29" s="3">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="M29" s="3">
         <v>5252.76</v>
@@ -77560,19 +82438,19 @@
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>8245</v>
+        <v>8787</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>8246</v>
+        <v>8788</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8247</v>
+        <v>8789</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8248</v>
+        <v>8790</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>8249</v>
+        <v>8791</v>
       </c>
       <c r="F30" s="3">
         <v>890266.15</v>
@@ -77581,19 +82459,19 @@
         <v>72192.29</v>
       </c>
       <c r="H30" s="3">
-        <v>174554.97</v>
+        <v>162273.91</v>
       </c>
       <c r="I30" s="3">
-        <v>246747.26</v>
+        <v>234466.2</v>
       </c>
       <c r="J30" s="3">
-        <v>27.72</v>
+        <v>26.34</v>
       </c>
       <c r="K30" s="3">
-        <v>-643518.89</v>
+        <v>-655799.95</v>
       </c>
       <c r="L30" s="3">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="M30" s="3">
         <v>4432.55</v>
@@ -77601,37 +82479,37 @@
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>8250</v>
+        <v>8792</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>8251</v>
+        <v>8793</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8252</v>
+        <v>8794</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8253</v>
+        <v>8795</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>8254</v>
+        <v>8796</v>
       </c>
       <c r="F31" s="3">
         <v>984099.44</v>
       </c>
       <c r="G31" s="3">
-        <v>91783.97</v>
+        <v>91845.85</v>
       </c>
       <c r="H31" s="3">
-        <v>154313.67</v>
+        <v>155604.55</v>
       </c>
       <c r="I31" s="3">
-        <v>246097.64</v>
+        <v>247450.4</v>
       </c>
       <c r="J31" s="3">
-        <v>25.01</v>
+        <v>25.14</v>
       </c>
       <c r="K31" s="3">
-        <v>-738001.8</v>
+        <v>-736649.04</v>
       </c>
       <c r="L31" s="3">
         <v>1.03</v>
@@ -77642,19 +82520,19 @@
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>8255</v>
+        <v>8797</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>8256</v>
+        <v>8798</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8257</v>
+        <v>8799</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8258</v>
+        <v>8800</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>8259</v>
+        <v>8801</v>
       </c>
       <c r="F32" s="3">
         <v>926984.47</v>
@@ -77663,19 +82541,19 @@
         <v>55818.6</v>
       </c>
       <c r="H32" s="3">
-        <v>113766.06</v>
+        <v>124668.36</v>
       </c>
       <c r="I32" s="3">
-        <v>169584.66</v>
+        <v>180486.96</v>
       </c>
       <c r="J32" s="3">
-        <v>18.29</v>
+        <v>19.47</v>
       </c>
       <c r="K32" s="3">
-        <v>-757399.81</v>
+        <v>-746497.51</v>
       </c>
       <c r="L32" s="3">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="M32" s="3">
         <v>2701.92</v>
@@ -77683,19 +82561,19 @@
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>8260</v>
+        <v>8802</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>8261</v>
+        <v>8803</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8262</v>
+        <v>8804</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8263</v>
+        <v>8805</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>8264</v>
+        <v>8806</v>
       </c>
       <c r="F33" s="3">
         <v>1288411.21</v>
@@ -77704,19 +82582,19 @@
         <v>79351.96</v>
       </c>
       <c r="H33" s="3">
-        <v>358498.38</v>
+        <v>332714.96</v>
       </c>
       <c r="I33" s="3">
-        <v>437850.34</v>
+        <v>412066.92</v>
       </c>
       <c r="J33" s="3">
-        <v>33.98</v>
+        <v>31.98</v>
       </c>
       <c r="K33" s="3">
-        <v>-850560.87</v>
+        <v>-876344.29</v>
       </c>
       <c r="L33" s="3">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="M33" s="3">
         <v>3933.78</v>
@@ -77724,19 +82602,19 @@
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>8265</v>
+        <v>8807</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>8266</v>
+        <v>8808</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8267</v>
+        <v>8809</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8268</v>
+        <v>8810</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>8269</v>
+        <v>8811</v>
       </c>
       <c r="F34" s="3">
         <v>1074641.52</v>
@@ -77745,19 +82623,19 @@
         <v>58011.41</v>
       </c>
       <c r="H34" s="3">
-        <v>101010.32</v>
+        <v>81586.27</v>
       </c>
       <c r="I34" s="3">
-        <v>159021.73</v>
+        <v>139597.68</v>
       </c>
       <c r="J34" s="3">
-        <v>14.8</v>
+        <v>12.99</v>
       </c>
       <c r="K34" s="3">
-        <v>-915619.79</v>
+        <v>-935043.84</v>
       </c>
       <c r="L34" s="3">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="M34" s="3">
         <v>2037.62</v>
@@ -77765,19 +82643,19 @@
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>8270</v>
+        <v>8812</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>8271</v>
+        <v>8813</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8272</v>
+        <v>8814</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8273</v>
+        <v>8815</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>8274</v>
+        <v>8816</v>
       </c>
       <c r="F35" s="3">
         <v>1054434.17</v>
@@ -77786,19 +82664,19 @@
         <v>68757.77</v>
       </c>
       <c r="H35" s="3">
-        <v>134324.74</v>
+        <v>115017.09</v>
       </c>
       <c r="I35" s="3">
-        <v>203082.51</v>
+        <v>183774.86</v>
       </c>
       <c r="J35" s="3">
-        <v>19.26</v>
+        <v>17.43</v>
       </c>
       <c r="K35" s="3">
-        <v>-851351.66</v>
+        <v>-870659.31</v>
       </c>
       <c r="L35" s="3">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="M35" s="3">
         <v>3100.82</v>
@@ -77806,19 +82684,19 @@
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>8275</v>
+        <v>8817</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>8276</v>
+        <v>8818</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8277</v>
+        <v>8819</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8278</v>
+        <v>8820</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>8279</v>
+        <v>8821</v>
       </c>
       <c r="F36" s="3">
         <v>1145461.66</v>
@@ -77827,19 +82705,19 @@
         <v>119959.46</v>
       </c>
       <c r="H36" s="3">
-        <v>286058.64</v>
+        <v>243072.59</v>
       </c>
       <c r="I36" s="3">
-        <v>406018.1</v>
+        <v>363032.05</v>
       </c>
       <c r="J36" s="3">
-        <v>35.45</v>
+        <v>31.69</v>
       </c>
       <c r="K36" s="3">
-        <v>-739443.56</v>
+        <v>-782429.61</v>
       </c>
       <c r="L36" s="3">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="M36" s="3">
         <v>288.0</v>
@@ -77847,19 +82725,19 @@
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>8280</v>
+        <v>8822</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>8281</v>
+        <v>8823</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8282</v>
+        <v>8824</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8283</v>
+        <v>8825</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>8284</v>
+        <v>8826</v>
       </c>
       <c r="F37" s="3">
         <v>1392111.83</v>
@@ -77868,19 +82746,19 @@
         <v>112984.5</v>
       </c>
       <c r="H37" s="3">
-        <v>322665.18</v>
+        <v>250247.02</v>
       </c>
       <c r="I37" s="3">
-        <v>435649.68</v>
+        <v>363231.52</v>
       </c>
       <c r="J37" s="3">
-        <v>31.29</v>
+        <v>26.09</v>
       </c>
       <c r="K37" s="3">
-        <v>-956462.15</v>
+        <v>-1028880.31</v>
       </c>
       <c r="L37" s="3">
-        <v>0.58</v>
+        <v>0.69</v>
       </c>
       <c r="M37" s="3">
         <v>2505.48</v>
@@ -77888,19 +82766,19 @@
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>8285</v>
+        <v>8827</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>8286</v>
+        <v>8828</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8287</v>
+        <v>8829</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8288</v>
+        <v>8830</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>8289</v>
+        <v>8831</v>
       </c>
       <c r="F38" s="3">
         <v>958935.26</v>
@@ -77909,19 +82787,19 @@
         <v>101907.15</v>
       </c>
       <c r="H38" s="3">
-        <v>223792.87</v>
+        <v>173199.37</v>
       </c>
       <c r="I38" s="3">
-        <v>325700.02</v>
+        <v>275106.52</v>
       </c>
       <c r="J38" s="3">
-        <v>33.96</v>
+        <v>28.69</v>
       </c>
       <c r="K38" s="3">
-        <v>-633235.24</v>
+        <v>-683828.74</v>
       </c>
       <c r="L38" s="3">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="M38" s="3">
         <v>8946.52</v>
@@ -77929,19 +82807,19 @@
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>8290</v>
+        <v>8832</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>8291</v>
+        <v>8833</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8292</v>
+        <v>8834</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8293</v>
+        <v>8835</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>8294</v>
+        <v>8836</v>
       </c>
       <c r="F39" s="3">
         <v>1141876.38</v>
@@ -77950,19 +82828,19 @@
         <v>82003.1</v>
       </c>
       <c r="H39" s="3">
-        <v>225550.26</v>
+        <v>174548.79</v>
       </c>
       <c r="I39" s="3">
-        <v>307553.36</v>
+        <v>256551.89</v>
       </c>
       <c r="J39" s="3">
-        <v>26.93</v>
+        <v>22.47</v>
       </c>
       <c r="K39" s="3">
-        <v>-834323.02</v>
+        <v>-885324.49</v>
       </c>
       <c r="L39" s="3">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="M39" s="3">
         <v>1887.06</v>
@@ -77970,19 +82848,19 @@
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>8295</v>
+        <v>8837</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>8296</v>
+        <v>8838</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8297</v>
+        <v>8839</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8298</v>
+        <v>8840</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>8299</v>
+        <v>8841</v>
       </c>
       <c r="F40" s="3">
         <v>936014.91</v>
@@ -77991,19 +82869,19 @@
         <v>54415.3</v>
       </c>
       <c r="H40" s="3">
-        <v>123695.18</v>
+        <v>120480.13</v>
       </c>
       <c r="I40" s="3">
-        <v>178110.48</v>
+        <v>174895.43</v>
       </c>
       <c r="J40" s="3">
-        <v>19.03</v>
+        <v>18.69</v>
       </c>
       <c r="K40" s="3">
-        <v>-757904.43</v>
+        <v>-761119.48</v>
       </c>
       <c r="L40" s="3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="M40" s="3">
         <v>1839.64</v>
@@ -78011,19 +82889,19 @@
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>8300</v>
+        <v>8842</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>8301</v>
+        <v>8843</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8302</v>
+        <v>8844</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8303</v>
+        <v>8845</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>8304</v>
+        <v>8846</v>
       </c>
       <c r="F41" s="3">
         <v>1227064.36</v>
@@ -78032,19 +82910,19 @@
         <v>64931.52</v>
       </c>
       <c r="H41" s="3">
-        <v>191837.15</v>
+        <v>174224.68</v>
       </c>
       <c r="I41" s="3">
-        <v>256768.67</v>
+        <v>239156.2</v>
       </c>
       <c r="J41" s="3">
-        <v>20.93</v>
+        <v>19.49</v>
       </c>
       <c r="K41" s="3">
-        <v>-970295.69</v>
+        <v>-987908.16</v>
       </c>
       <c r="L41" s="3">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="M41" s="3">
         <v>3795.92</v>
@@ -78052,19 +82930,19 @@
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>8305</v>
+        <v>8847</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>8306</v>
+        <v>8848</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8307</v>
+        <v>8849</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8308</v>
+        <v>8850</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>8309</v>
+        <v>8851</v>
       </c>
       <c r="F42" s="3">
         <v>940955.58</v>
@@ -78073,19 +82951,19 @@
         <v>65070.28</v>
       </c>
       <c r="H42" s="3">
-        <v>202705.49</v>
+        <v>199828.65</v>
       </c>
       <c r="I42" s="3">
-        <v>267775.77</v>
+        <v>264898.93</v>
       </c>
       <c r="J42" s="3">
-        <v>28.46</v>
+        <v>28.15</v>
       </c>
       <c r="K42" s="3">
-        <v>-673179.81</v>
+        <v>-676056.65</v>
       </c>
       <c r="L42" s="3">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="M42" s="3">
         <v>2063.02</v>
@@ -78093,19 +82971,19 @@
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>8310</v>
+        <v>8852</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>8311</v>
+        <v>8853</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8312</v>
+        <v>8854</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8313</v>
+        <v>8855</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>8314</v>
+        <v>8856</v>
       </c>
       <c r="F43" s="3">
         <v>1062667.74</v>
@@ -78114,19 +82992,19 @@
         <v>84326.96</v>
       </c>
       <c r="H43" s="3">
-        <v>224679.11</v>
+        <v>212155.25</v>
       </c>
       <c r="I43" s="3">
-        <v>309006.07</v>
+        <v>296482.21</v>
       </c>
       <c r="J43" s="3">
-        <v>29.08</v>
+        <v>27.9</v>
       </c>
       <c r="K43" s="3">
-        <v>-753661.67</v>
+        <v>-766185.53</v>
       </c>
       <c r="L43" s="3">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="M43" s="3">
         <v>2184.5</v>
@@ -78134,19 +83012,19 @@
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>8315</v>
+        <v>8857</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>8316</v>
+        <v>8858</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8317</v>
+        <v>8859</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8318</v>
+        <v>8860</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>8319</v>
+        <v>8861</v>
       </c>
       <c r="F44" s="3">
         <v>1129524.64</v>
@@ -78155,19 +83033,19 @@
         <v>61686.32</v>
       </c>
       <c r="H44" s="3">
-        <v>36698.11</v>
+        <v>143843.46</v>
       </c>
       <c r="I44" s="3">
-        <v>98384.43</v>
+        <v>205529.78</v>
       </c>
       <c r="J44" s="3">
-        <v>8.71</v>
+        <v>18.2</v>
       </c>
       <c r="K44" s="3">
-        <v>-1031140.21</v>
+        <v>-923994.86</v>
       </c>
       <c r="L44" s="3">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="M44" s="3">
         <v>495.0</v>
@@ -78175,19 +83053,19 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>8320</v>
+        <v>8862</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>8321</v>
+        <v>8863</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8322</v>
+        <v>8864</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8323</v>
+        <v>8865</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>8324</v>
+        <v>8866</v>
       </c>
       <c r="F45" s="3">
         <v>931654.84</v>
@@ -78196,19 +83074,19 @@
         <v>87560.54</v>
       </c>
       <c r="H45" s="3">
-        <v>38026.85</v>
+        <v>131486.65</v>
       </c>
       <c r="I45" s="3">
-        <v>125587.39</v>
+        <v>219047.19</v>
       </c>
       <c r="J45" s="3">
-        <v>13.48</v>
+        <v>23.51</v>
       </c>
       <c r="K45" s="3">
-        <v>-806067.45</v>
+        <v>-712607.65</v>
       </c>
       <c r="L45" s="3">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="M45" s="3">
         <v>187.4</v>
@@ -78216,19 +83094,19 @@
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>8325</v>
+        <v>8867</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>8326</v>
+        <v>8868</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8327</v>
+        <v>8869</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8328</v>
+        <v>8870</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>8329</v>
+        <v>8871</v>
       </c>
       <c r="F46" s="3">
         <v>1096879.63</v>
@@ -78237,19 +83115,19 @@
         <v>91387.31</v>
       </c>
       <c r="H46" s="3">
-        <v>33436.5</v>
+        <v>142734.85</v>
       </c>
       <c r="I46" s="3">
-        <v>124823.81</v>
+        <v>234122.16</v>
       </c>
       <c r="J46" s="3">
-        <v>11.38</v>
+        <v>21.34</v>
       </c>
       <c r="K46" s="3">
-        <v>-972055.82</v>
+        <v>-862757.47</v>
       </c>
       <c r="L46" s="3">
-        <v>1.05</v>
+        <v>0.56</v>
       </c>
       <c r="M46" s="3">
         <v>1304.48</v>
@@ -78257,19 +83135,19 @@
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>8330</v>
+        <v>8872</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>8331</v>
+        <v>8873</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8332</v>
+        <v>8874</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8333</v>
+        <v>8875</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>8334</v>
+        <v>8876</v>
       </c>
       <c r="F47" s="3">
         <v>1362950.73</v>
@@ -78278,19 +83156,19 @@
         <v>39867.42</v>
       </c>
       <c r="H47" s="3">
-        <v>211809.03</v>
+        <v>334800.43</v>
       </c>
       <c r="I47" s="3">
-        <v>251676.45</v>
+        <v>374667.85</v>
       </c>
       <c r="J47" s="3">
-        <v>18.47</v>
+        <v>27.49</v>
       </c>
       <c r="K47" s="3">
-        <v>-1111274.28</v>
+        <v>-988282.88</v>
       </c>
       <c r="L47" s="3">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="M47" s="3">
         <v>1762.5</v>
@@ -78298,19 +83176,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>8335</v>
+        <v>8877</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>8336</v>
+        <v>8878</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8337</v>
+        <v>8879</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8338</v>
+        <v>8880</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>8339</v>
+        <v>8881</v>
       </c>
       <c r="F48" s="3">
         <v>1050721.66</v>
@@ -78319,19 +83197,19 @@
         <v>40030.13</v>
       </c>
       <c r="H48" s="3">
-        <v>96310.52</v>
+        <v>173035.57</v>
       </c>
       <c r="I48" s="3">
-        <v>136340.65</v>
+        <v>213065.7</v>
       </c>
       <c r="J48" s="3">
-        <v>12.98</v>
+        <v>20.28</v>
       </c>
       <c r="K48" s="3">
-        <v>-914381.01</v>
+        <v>-837655.96</v>
       </c>
       <c r="L48" s="3">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="M48" s="3">
         <v>449.88</v>
@@ -78339,19 +83217,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>8340</v>
+        <v>8882</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>8341</v>
+        <v>8883</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8342</v>
+        <v>8884</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8343</v>
+        <v>8885</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>8344</v>
+        <v>8886</v>
       </c>
       <c r="F49" s="3">
         <v>989655.83</v>
@@ -78360,19 +83238,19 @@
         <v>64599.38</v>
       </c>
       <c r="H49" s="3">
-        <v>127617.04</v>
+        <v>218954.51</v>
       </c>
       <c r="I49" s="3">
-        <v>192216.42</v>
+        <v>283553.89</v>
       </c>
       <c r="J49" s="3">
-        <v>19.42</v>
+        <v>28.65</v>
       </c>
       <c r="K49" s="3">
-        <v>-797439.41</v>
+        <v>-706101.94</v>
       </c>
       <c r="L49" s="3">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="M49" s="3">
         <v>1346.24</v>
@@ -78380,19 +83258,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>8345</v>
+        <v>8887</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>8346</v>
+        <v>8888</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>8347</v>
+        <v>8889</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8348</v>
+        <v>8890</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>8349</v>
+        <v>8891</v>
       </c>
       <c r="F50" s="3">
         <v>978747.3</v>
@@ -78401,19 +83279,19 @@
         <v>54461.86</v>
       </c>
       <c r="H50" s="3">
-        <v>151549.59</v>
+        <v>271432.04</v>
       </c>
       <c r="I50" s="3">
-        <v>206011.45</v>
+        <v>325893.9</v>
       </c>
       <c r="J50" s="3">
-        <v>21.05</v>
+        <v>33.3</v>
       </c>
       <c r="K50" s="3">
-        <v>-772735.85</v>
+        <v>-652853.4</v>
       </c>
       <c r="L50" s="3">
-        <v>3.22</v>
+        <v>2.04</v>
       </c>
       <c r="M50" s="3">
         <v>6643.58</v>
@@ -78421,19 +83299,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>8350</v>
+        <v>8892</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>8351</v>
+        <v>8893</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>8352</v>
+        <v>8894</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>8353</v>
+        <v>8895</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>8354</v>
+        <v>8896</v>
       </c>
       <c r="F51" s="3">
         <v>983156.92</v>
@@ -78442,19 +83320,19 @@
         <v>31943.92</v>
       </c>
       <c r="H51" s="3">
-        <v>94761.14</v>
+        <v>147923.33</v>
       </c>
       <c r="I51" s="3">
-        <v>126705.06</v>
+        <v>179867.25</v>
       </c>
       <c r="J51" s="3">
-        <v>12.89</v>
+        <v>18.29</v>
       </c>
       <c r="K51" s="3">
-        <v>-856451.86</v>
+        <v>-803289.67</v>
       </c>
       <c r="L51" s="3">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="M51" s="3">
         <v>512.28</v>
@@ -78462,19 +83340,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>8355</v>
+        <v>8897</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>8356</v>
+        <v>8898</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>8357</v>
+        <v>8899</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8358</v>
+        <v>8900</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>8359</v>
+        <v>8901</v>
       </c>
       <c r="F52" s="3">
         <v>1178421.11</v>
@@ -78483,25 +83361,25 @@
         <v>32942.61</v>
       </c>
       <c r="H52" s="3">
-        <v>100754.8</v>
+        <v>237941.14</v>
       </c>
       <c r="I52" s="3">
-        <v>133697.41</v>
+        <v>270883.75</v>
       </c>
       <c r="J52" s="3">
-        <v>11.35</v>
+        <v>22.99</v>
       </c>
       <c r="K52" s="3">
-        <v>-1044723.7</v>
+        <v>-907537.36</v>
       </c>
       <c r="L52" s="3">
-        <v>1.29</v>
+        <v>0.64</v>
       </c>
       <c r="M52" s="3">
         <v>1727.2</v>
       </c>
     </row>
-    <row r="56" spans="8:8">
+    <row r="56" spans="8:8" ht="16.25">
       <c r="A56" s="4" t="s">
         <v>5397</v>
       </c>
@@ -84978,7 +89856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -85028,16 +89906,16 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>8360</v>
+        <v>8902</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8361</v>
+        <v>8903</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8362</v>
+        <v>8904</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8363</v>
+        <v>8905</v>
       </c>
       <c r="E2" s="3">
         <v>6104317.5</v>
@@ -85046,36 +89924,36 @@
         <v>412504.59</v>
       </c>
       <c r="G2" s="3">
-        <v>1478854.05</v>
+        <v>1567759.71</v>
       </c>
       <c r="H2" s="3">
-        <v>1891358.64</v>
+        <v>1980264.3</v>
       </c>
       <c r="I2" s="3">
-        <v>30.98</v>
+        <v>32.44</v>
       </c>
       <c r="J2" s="3">
-        <v>-4212958.86</v>
+        <v>-4124053.2</v>
       </c>
       <c r="K2" s="3">
         <v>11085.36</v>
       </c>
       <c r="L2" s="3">
-        <v>0.59</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>8364</v>
+        <v>8906</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8365</v>
+        <v>8907</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8366</v>
+        <v>8908</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8367</v>
+        <v>8909</v>
       </c>
       <c r="E3" s="3">
         <v>3440798.37</v>
@@ -85084,36 +89962,36 @@
         <v>172794.82</v>
       </c>
       <c r="G3" s="3">
-        <v>780161.33</v>
+        <v>773390.95</v>
       </c>
       <c r="H3" s="3">
-        <v>952956.15</v>
+        <v>946185.77</v>
       </c>
       <c r="I3" s="3">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="J3" s="3">
-        <v>-2487842.22</v>
+        <v>-2494612.6</v>
       </c>
       <c r="K3" s="3">
         <v>6618.03</v>
       </c>
       <c r="L3" s="3">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>8368</v>
+        <v>8910</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8369</v>
+        <v>8911</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8370</v>
+        <v>8912</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8371</v>
+        <v>8913</v>
       </c>
       <c r="E4" s="3">
         <v>6398516.07</v>
@@ -85122,36 +90000,36 @@
         <v>471262.52</v>
       </c>
       <c r="G4" s="3">
-        <v>880848.65</v>
+        <v>908849.05</v>
       </c>
       <c r="H4" s="3">
-        <v>1352111.17</v>
+        <v>1380111.57</v>
       </c>
       <c r="I4" s="3">
-        <v>21.13</v>
+        <v>21.57</v>
       </c>
       <c r="J4" s="3">
-        <v>-5046404.9</v>
+        <v>-5018404.5</v>
       </c>
       <c r="K4" s="3">
         <v>8625.75</v>
       </c>
       <c r="L4" s="3">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>8372</v>
+        <v>8914</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8373</v>
+        <v>8915</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8374</v>
+        <v>8916</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8375</v>
+        <v>8917</v>
       </c>
       <c r="E5" s="3">
         <v>7403170.5</v>
@@ -85160,36 +90038,36 @@
         <v>643754.68</v>
       </c>
       <c r="G5" s="3">
-        <v>997698.45</v>
+        <v>1104335.21</v>
       </c>
       <c r="H5" s="3">
-        <v>1641453.13</v>
+        <v>1748089.89</v>
       </c>
       <c r="I5" s="3">
-        <v>22.17</v>
+        <v>23.61</v>
       </c>
       <c r="J5" s="3">
-        <v>-5761717.37</v>
+        <v>-5655080.61</v>
       </c>
       <c r="K5" s="3">
         <v>21218.41</v>
       </c>
       <c r="L5" s="3">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>8376</v>
+        <v>8918</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8377</v>
+        <v>8919</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8378</v>
+        <v>8920</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8379</v>
+        <v>8921</v>
       </c>
       <c r="E6" s="3">
         <v>7091695.63</v>
@@ -85198,36 +90076,36 @@
         <v>526201.6</v>
       </c>
       <c r="G6" s="3">
-        <v>1158909.04</v>
+        <v>1118792.77</v>
       </c>
       <c r="H6" s="3">
-        <v>1685110.64</v>
+        <v>1644994.37</v>
       </c>
       <c r="I6" s="3">
-        <v>23.76</v>
+        <v>23.2</v>
       </c>
       <c r="J6" s="3">
-        <v>-5406584.99</v>
+        <v>-5446701.26</v>
       </c>
       <c r="K6" s="3">
         <v>23998.72</v>
       </c>
       <c r="L6" s="3">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>8380</v>
+        <v>8922</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8381</v>
+        <v>8923</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8382</v>
+        <v>8924</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8383</v>
+        <v>8925</v>
       </c>
       <c r="E7" s="3">
         <v>4638385.13</v>
@@ -85236,36 +90114,36 @@
         <v>416854.21</v>
       </c>
       <c r="G7" s="3">
-        <v>1058066.95</v>
+        <v>841067.77</v>
       </c>
       <c r="H7" s="3">
-        <v>1474921.16</v>
+        <v>1257921.98</v>
       </c>
       <c r="I7" s="3">
-        <v>31.8</v>
+        <v>27.12</v>
       </c>
       <c r="J7" s="3">
-        <v>-3163463.97</v>
+        <v>-3380463.15</v>
       </c>
       <c r="K7" s="3">
         <v>13627.06</v>
       </c>
       <c r="L7" s="3">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>8384</v>
+        <v>8926</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8385</v>
+        <v>8927</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8386</v>
+        <v>8928</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8387</v>
+        <v>8929</v>
       </c>
       <c r="E8" s="3">
         <v>7324761.7</v>
@@ -85274,36 +90152,36 @@
         <v>509378.23</v>
       </c>
       <c r="G8" s="3">
-        <v>851078.39</v>
+        <v>1124753.67</v>
       </c>
       <c r="H8" s="3">
-        <v>1360456.62</v>
+        <v>1634131.9</v>
       </c>
       <c r="I8" s="3">
-        <v>18.57</v>
+        <v>22.31</v>
       </c>
       <c r="J8" s="3">
-        <v>-5964305.08</v>
+        <v>-5690629.8</v>
       </c>
       <c r="K8" s="3">
         <v>11869.96</v>
       </c>
       <c r="L8" s="3">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>8388</v>
+        <v>8930</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8389</v>
+        <v>8931</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8390</v>
+        <v>8932</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8391</v>
+        <v>8933</v>
       </c>
       <c r="E9" s="3">
         <v>6543653.55</v>
@@ -85312,22 +90190,22 @@
         <v>263845.32</v>
       </c>
       <c r="G9" s="3">
-        <v>782802.12</v>
+        <v>1384087.02</v>
       </c>
       <c r="H9" s="3">
-        <v>1046647.44</v>
+        <v>1647932.34</v>
       </c>
       <c r="I9" s="3">
-        <v>15.99</v>
+        <v>25.18</v>
       </c>
       <c r="J9" s="3">
-        <v>-5497006.11</v>
+        <v>-4895721.21</v>
       </c>
       <c r="K9" s="3">
         <v>12441.68</v>
       </c>
       <c r="L9" s="3">
-        <v>1.19</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13" spans="8:8">
@@ -86435,7 +91313,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AG78"/>
+  <dimension ref="A1:AH78"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="9" max="9" customWidth="1" width="5.8984375" style="0"/>
@@ -89764,7 +94642,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:X79"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="29"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="territory-wise-MPE-sales-achiev" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8934" count="8934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9221" count="9221">
   <si>
     <t>Region</t>
   </si>
@@ -78123,6 +78123,2589 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
     </r>
   </si>
   <si>
@@ -81229,7 +83812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS397"/>
+  <dimension ref="A1:AT397"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
@@ -81290,40 +83873,40 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>8647</v>
+        <v>8934</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8648</v>
+        <v>8935</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8649</v>
+        <v>8936</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8650</v>
+        <v>8937</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8651</v>
+        <v>8938</v>
       </c>
       <c r="F2" s="3">
         <v>787067.06</v>
       </c>
       <c r="G2" s="3">
-        <v>38658.11</v>
+        <v>74792.48</v>
       </c>
       <c r="H2" s="3">
-        <v>211705.54</v>
+        <v>230763.24</v>
       </c>
       <c r="I2" s="3">
-        <v>250363.65</v>
+        <v>305555.72</v>
       </c>
       <c r="J2" s="3">
-        <v>31.81</v>
+        <v>38.82</v>
       </c>
       <c r="K2" s="3">
-        <v>-536703.41</v>
+        <v>-481511.34</v>
       </c>
       <c r="L2" s="3">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="M2" s="3">
         <v>1469.11</v>
@@ -81331,368 +83914,368 @@
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>8652</v>
+        <v>8939</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8653</v>
+        <v>8940</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8654</v>
+        <v>8941</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8655</v>
+        <v>8942</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8656</v>
+        <v>8943</v>
       </c>
       <c r="F3" s="3">
         <v>792403.1</v>
       </c>
       <c r="G3" s="3">
-        <v>27660.32</v>
+        <v>42530.13</v>
       </c>
       <c r="H3" s="3">
-        <v>246369.89</v>
+        <v>257923.78</v>
       </c>
       <c r="I3" s="3">
-        <v>274030.21</v>
+        <v>300453.91</v>
       </c>
       <c r="J3" s="3">
-        <v>34.58</v>
+        <v>37.92</v>
       </c>
       <c r="K3" s="3">
-        <v>-518372.89</v>
+        <v>-491949.19</v>
       </c>
       <c r="L3" s="3">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="M3" s="3">
-        <v>2871.24</v>
+        <v>4145.64</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>8657</v>
+        <v>8944</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8658</v>
+        <v>8945</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8659</v>
+        <v>8946</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8660</v>
+        <v>8947</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8661</v>
+        <v>8948</v>
       </c>
       <c r="F4" s="3">
         <v>672792.28</v>
       </c>
       <c r="G4" s="3">
-        <v>46596.63</v>
+        <v>74978.0</v>
       </c>
       <c r="H4" s="3">
-        <v>188414.7</v>
+        <v>177006.88</v>
       </c>
       <c r="I4" s="3">
-        <v>235011.33</v>
+        <v>251984.88</v>
       </c>
       <c r="J4" s="3">
-        <v>34.93</v>
+        <v>37.45</v>
       </c>
       <c r="K4" s="3">
-        <v>-437780.95</v>
+        <v>-420807.4</v>
       </c>
       <c r="L4" s="3">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="M4" s="3">
-        <v>570.14</v>
+        <v>924.38</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>8662</v>
+        <v>8949</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8663</v>
+        <v>8950</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8664</v>
+        <v>8951</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8665</v>
+        <v>8952</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8666</v>
+        <v>8953</v>
       </c>
       <c r="F5" s="3">
         <v>740010.55</v>
       </c>
       <c r="G5" s="3">
-        <v>32232.32</v>
+        <v>50866.97</v>
       </c>
       <c r="H5" s="3">
-        <v>153252.61</v>
+        <v>189399.19</v>
       </c>
       <c r="I5" s="3">
-        <v>185484.93</v>
+        <v>240266.16</v>
       </c>
       <c r="J5" s="3">
-        <v>25.07</v>
+        <v>32.47</v>
       </c>
       <c r="K5" s="3">
-        <v>-554525.62</v>
+        <v>-499744.39</v>
       </c>
       <c r="L5" s="3">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="M5" s="3">
-        <v>2955.43</v>
+        <v>3243.43</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>8667</v>
+        <v>8954</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8668</v>
+        <v>8955</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8669</v>
+        <v>8956</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8670</v>
+        <v>8957</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8671</v>
+        <v>8958</v>
       </c>
       <c r="F6" s="3">
         <v>763526.5</v>
       </c>
       <c r="G6" s="3">
-        <v>68095.72</v>
+        <v>97493.26</v>
       </c>
       <c r="H6" s="3">
-        <v>221141.93</v>
+        <v>196422.97</v>
       </c>
       <c r="I6" s="3">
-        <v>289237.65</v>
+        <v>293916.23</v>
       </c>
       <c r="J6" s="3">
-        <v>37.88</v>
+        <v>38.49</v>
       </c>
       <c r="K6" s="3">
-        <v>-474288.85</v>
+        <v>-469610.27</v>
       </c>
       <c r="L6" s="3">
-        <v>0.5</v>
+        <v>1.26</v>
       </c>
       <c r="M6" s="3">
-        <v>1433.5</v>
+        <v>3692.16</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>8672</v>
+        <v>8959</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8673</v>
+        <v>8960</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8674</v>
+        <v>8961</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8675</v>
+        <v>8962</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8676</v>
+        <v>8963</v>
       </c>
       <c r="F7" s="3">
         <v>803185.79</v>
       </c>
       <c r="G7" s="3">
-        <v>59532.55</v>
+        <v>69330.79</v>
       </c>
       <c r="H7" s="3">
-        <v>217364.92</v>
+        <v>211828.14</v>
       </c>
       <c r="I7" s="3">
-        <v>276897.47</v>
+        <v>281158.93</v>
       </c>
       <c r="J7" s="3">
-        <v>34.47</v>
+        <v>35.01</v>
       </c>
       <c r="K7" s="3">
-        <v>-526288.32</v>
+        <v>-522026.86</v>
       </c>
       <c r="L7" s="3">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
       <c r="M7" s="3">
-        <v>1058.75</v>
+        <v>2306.55</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>8677</v>
+        <v>8964</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8678</v>
+        <v>8965</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8679</v>
+        <v>8966</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8680</v>
+        <v>8967</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8681</v>
+        <v>8968</v>
       </c>
       <c r="F8" s="3">
         <v>770724.92</v>
       </c>
       <c r="G8" s="3">
-        <v>61556.31</v>
+        <v>88001.57</v>
       </c>
       <c r="H8" s="3">
-        <v>165578.71</v>
+        <v>146983.2</v>
       </c>
       <c r="I8" s="3">
-        <v>227135.02</v>
+        <v>234984.77</v>
       </c>
       <c r="J8" s="3">
-        <v>29.47</v>
+        <v>30.49</v>
       </c>
       <c r="K8" s="3">
-        <v>-543589.9</v>
+        <v>-535740.15</v>
       </c>
       <c r="L8" s="3">
-        <v>0.18</v>
+        <v>0.89</v>
       </c>
       <c r="M8" s="3">
-        <v>416.1</v>
+        <v>2102.7</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>8682</v>
+        <v>8969</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8683</v>
+        <v>8970</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8684</v>
+        <v>8971</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8685</v>
+        <v>8972</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8686</v>
+        <v>8973</v>
       </c>
       <c r="F9" s="3">
         <v>774607.3</v>
       </c>
       <c r="G9" s="3">
-        <v>78172.63</v>
+        <v>88380.37</v>
       </c>
       <c r="H9" s="3">
-        <v>163931.41</v>
+        <v>158620.68</v>
       </c>
       <c r="I9" s="3">
-        <v>242104.04</v>
+        <v>247001.05</v>
       </c>
       <c r="J9" s="3">
-        <v>31.26</v>
+        <v>31.89</v>
       </c>
       <c r="K9" s="3">
-        <v>-532503.26</v>
+        <v>-527606.25</v>
       </c>
       <c r="L9" s="3">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="M9" s="3">
-        <v>311.09</v>
+        <v>622.18</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>8687</v>
+        <v>8974</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8688</v>
+        <v>8975</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8689</v>
+        <v>8976</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8690</v>
+        <v>8977</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8691</v>
+        <v>8978</v>
       </c>
       <c r="F10" s="3">
         <v>900349.47</v>
       </c>
       <c r="G10" s="3">
-        <v>35590.42</v>
+        <v>50453.71</v>
       </c>
       <c r="H10" s="3">
-        <v>199914.14</v>
+        <v>206706.79</v>
       </c>
       <c r="I10" s="3">
-        <v>235504.56</v>
+        <v>257160.5</v>
       </c>
       <c r="J10" s="3">
-        <v>26.16</v>
+        <v>28.56</v>
       </c>
       <c r="K10" s="3">
-        <v>-664844.91</v>
+        <v>-643188.97</v>
       </c>
       <c r="L10" s="3">
-        <v>0.29</v>
+        <v>0.95</v>
       </c>
       <c r="M10" s="3">
-        <v>681.18</v>
+        <v>2449.26</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>8692</v>
+        <v>8979</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8693</v>
+        <v>8980</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8694</v>
+        <v>8981</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8695</v>
+        <v>8982</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8696</v>
+        <v>8983</v>
       </c>
       <c r="F11" s="3">
         <v>901291.26</v>
       </c>
       <c r="G11" s="3">
-        <v>33645.35</v>
+        <v>51308.25</v>
       </c>
       <c r="H11" s="3">
-        <v>158531.88</v>
+        <v>162956.72</v>
       </c>
       <c r="I11" s="3">
-        <v>192177.23</v>
+        <v>214264.97</v>
       </c>
       <c r="J11" s="3">
-        <v>21.32</v>
+        <v>23.77</v>
       </c>
       <c r="K11" s="3">
-        <v>-709114.03</v>
+        <v>-687026.29</v>
       </c>
       <c r="L11" s="3">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="M11" s="3">
         <v>2953.16</v>
@@ -81700,204 +84283,204 @@
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>8697</v>
+        <v>8984</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8698</v>
+        <v>8985</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8699</v>
+        <v>8986</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8700</v>
+        <v>8987</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8701</v>
+        <v>8988</v>
       </c>
       <c r="F12" s="3">
         <v>790977.36</v>
       </c>
       <c r="G12" s="3">
-        <v>56436.01</v>
+        <v>82514.05</v>
       </c>
       <c r="H12" s="3">
-        <v>209988.65</v>
+        <v>204426.28</v>
       </c>
       <c r="I12" s="3">
-        <v>266424.66</v>
+        <v>286940.33</v>
       </c>
       <c r="J12" s="3">
-        <v>33.68</v>
+        <v>36.28</v>
       </c>
       <c r="K12" s="3">
-        <v>-524552.7</v>
+        <v>-504037.03</v>
       </c>
       <c r="L12" s="3">
-        <v>0.53</v>
+        <v>0.96</v>
       </c>
       <c r="M12" s="3">
-        <v>1402.08</v>
+        <v>2757.04</v>
       </c>
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>8702</v>
+        <v>8989</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>8703</v>
+        <v>8990</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8704</v>
+        <v>8991</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8705</v>
+        <v>8992</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8706</v>
+        <v>8993</v>
       </c>
       <c r="F13" s="3">
         <v>848180.28</v>
       </c>
       <c r="G13" s="3">
-        <v>47123.04</v>
+        <v>76623.41</v>
       </c>
       <c r="H13" s="3">
-        <v>204956.28</v>
+        <v>237063.28</v>
       </c>
       <c r="I13" s="3">
-        <v>252079.32</v>
+        <v>313686.69</v>
       </c>
       <c r="J13" s="3">
-        <v>29.72</v>
+        <v>36.98</v>
       </c>
       <c r="K13" s="3">
-        <v>-596100.96</v>
+        <v>-534493.59</v>
       </c>
       <c r="L13" s="3">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="M13" s="3">
-        <v>1581.61</v>
+        <v>1637.83</v>
       </c>
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>8707</v>
+        <v>8994</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>8708</v>
+        <v>8995</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8709</v>
+        <v>8996</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8710</v>
+        <v>8997</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8711</v>
+        <v>8998</v>
       </c>
       <c r="F14" s="3">
         <v>788558.37</v>
       </c>
       <c r="G14" s="3">
-        <v>48905.58</v>
+        <v>75201.92</v>
       </c>
       <c r="H14" s="3">
-        <v>214656.14</v>
+        <v>193997.36</v>
       </c>
       <c r="I14" s="3">
-        <v>263561.72</v>
+        <v>269199.28</v>
       </c>
       <c r="J14" s="3">
-        <v>33.42</v>
+        <v>34.14</v>
       </c>
       <c r="K14" s="3">
-        <v>-524996.65</v>
+        <v>-519359.09</v>
       </c>
       <c r="L14" s="3">
-        <v>0.0</v>
+        <v>0.06</v>
       </c>
       <c r="M14" s="3">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>8712</v>
+        <v>8999</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>8713</v>
+        <v>9000</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8714</v>
+        <v>9001</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8715</v>
+        <v>9002</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8716</v>
+        <v>9003</v>
       </c>
       <c r="F15" s="3">
         <v>816369.33</v>
       </c>
       <c r="G15" s="3">
-        <v>25638.43</v>
+        <v>37489.35</v>
       </c>
       <c r="H15" s="3">
-        <v>186211.81</v>
+        <v>178240.7</v>
       </c>
       <c r="I15" s="3">
-        <v>211850.24</v>
+        <v>215730.05</v>
       </c>
       <c r="J15" s="3">
-        <v>25.95</v>
+        <v>26.43</v>
       </c>
       <c r="K15" s="3">
-        <v>-604519.09</v>
+        <v>-600639.28</v>
       </c>
       <c r="L15" s="3">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="M15" s="3">
-        <v>209.9</v>
+        <v>547.1</v>
       </c>
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>8717</v>
+        <v>9004</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>8718</v>
+        <v>9005</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8719</v>
+        <v>9006</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8720</v>
+        <v>9007</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>8721</v>
+        <v>9008</v>
       </c>
       <c r="F16" s="3">
         <v>792760.6</v>
       </c>
       <c r="G16" s="3">
-        <v>31470.82</v>
+        <v>53265.32</v>
       </c>
       <c r="H16" s="3">
-        <v>103574.73</v>
+        <v>90097.28</v>
       </c>
       <c r="I16" s="3">
-        <v>135045.55</v>
+        <v>143362.6</v>
       </c>
       <c r="J16" s="3">
-        <v>17.03</v>
+        <v>18.08</v>
       </c>
       <c r="K16" s="3">
-        <v>-657715.05</v>
+        <v>-649398.0</v>
       </c>
       <c r="L16" s="3">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="M16" s="3">
         <v>630.0</v>
@@ -81905,37 +84488,37 @@
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>8722</v>
+        <v>9009</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>8723</v>
+        <v>9010</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8724</v>
+        <v>9011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8725</v>
+        <v>9012</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>8726</v>
+        <v>9013</v>
       </c>
       <c r="F17" s="3">
         <v>786604.47</v>
       </c>
       <c r="G17" s="3">
-        <v>32593.1</v>
+        <v>45208.2</v>
       </c>
       <c r="H17" s="3">
-        <v>129889.61</v>
+        <v>121828.81</v>
       </c>
       <c r="I17" s="3">
-        <v>162482.71</v>
+        <v>167037.01</v>
       </c>
       <c r="J17" s="3">
-        <v>20.66</v>
+        <v>21.24</v>
       </c>
       <c r="K17" s="3">
-        <v>-624121.76</v>
+        <v>-619567.46</v>
       </c>
       <c r="L17" s="3">
         <v>0.13</v>
@@ -81946,19 +84529,19 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>8727</v>
+        <v>9014</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>8728</v>
+        <v>9015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8729</v>
+        <v>9016</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8730</v>
+        <v>9017</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>8731</v>
+        <v>9018</v>
       </c>
       <c r="F18" s="3">
         <v>1063383.58</v>
@@ -81987,19 +84570,19 @@
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>8732</v>
+        <v>9019</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>8733</v>
+        <v>9020</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8734</v>
+        <v>9021</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8735</v>
+        <v>9022</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>8736</v>
+        <v>9023</v>
       </c>
       <c r="F19" s="3">
         <v>886606.12</v>
@@ -82028,19 +84611,19 @@
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>8737</v>
+        <v>9024</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>8738</v>
+        <v>9025</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8739</v>
+        <v>9026</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8740</v>
+        <v>9027</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>8741</v>
+        <v>9028</v>
       </c>
       <c r="F20" s="3">
         <v>1264233.6</v>
@@ -82069,245 +84652,245 @@
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>8742</v>
+        <v>9029</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>8743</v>
+        <v>9030</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8744</v>
+        <v>9031</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8745</v>
+        <v>9032</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>8746</v>
+        <v>9033</v>
       </c>
       <c r="F21" s="3">
         <v>873034.8</v>
       </c>
       <c r="G21" s="3">
-        <v>90134.0</v>
+        <v>124059.98</v>
       </c>
       <c r="H21" s="3">
-        <v>130073.2</v>
+        <v>103176.39</v>
       </c>
       <c r="I21" s="3">
-        <v>220207.2</v>
+        <v>227236.37</v>
       </c>
       <c r="J21" s="3">
-        <v>25.22</v>
+        <v>26.03</v>
       </c>
       <c r="K21" s="3">
-        <v>-652827.6</v>
+        <v>-645798.43</v>
       </c>
       <c r="L21" s="3">
-        <v>0.68</v>
+        <v>0.99</v>
       </c>
       <c r="M21" s="3">
-        <v>1501.34</v>
+        <v>2250.94</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>8747</v>
+        <v>9034</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>8748</v>
+        <v>9035</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8749</v>
+        <v>9036</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8750</v>
+        <v>9037</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>8751</v>
+        <v>9038</v>
       </c>
       <c r="F22" s="3">
         <v>891542.61</v>
       </c>
       <c r="G22" s="3">
-        <v>73912.8</v>
+        <v>119754.31</v>
       </c>
       <c r="H22" s="3">
-        <v>141106.72</v>
+        <v>99825.89</v>
       </c>
       <c r="I22" s="3">
-        <v>215019.52</v>
+        <v>219580.2</v>
       </c>
       <c r="J22" s="3">
-        <v>24.12</v>
+        <v>24.63</v>
       </c>
       <c r="K22" s="3">
-        <v>-676523.09</v>
+        <v>-671962.41</v>
       </c>
       <c r="L22" s="3">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="M22" s="3">
-        <v>3274.64</v>
+        <v>4030.72</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>8752</v>
+        <v>9039</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>8753</v>
+        <v>9040</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8754</v>
+        <v>9041</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8755</v>
+        <v>9042</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>8756</v>
+        <v>9043</v>
       </c>
       <c r="F23" s="3">
         <v>876168.01</v>
       </c>
       <c r="G23" s="3">
-        <v>96000.87</v>
+        <v>139685.64</v>
       </c>
       <c r="H23" s="3">
-        <v>151944.27</v>
+        <v>117236.76</v>
       </c>
       <c r="I23" s="3">
-        <v>247945.14</v>
+        <v>256922.4</v>
       </c>
       <c r="J23" s="3">
-        <v>28.3</v>
+        <v>29.32</v>
       </c>
       <c r="K23" s="3">
-        <v>-628222.87</v>
+        <v>-619245.61</v>
       </c>
       <c r="L23" s="3">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="M23" s="3">
-        <v>11904.62</v>
+        <v>12678.5</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>8757</v>
+        <v>9044</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>8758</v>
+        <v>9045</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8759</v>
+        <v>9046</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8760</v>
+        <v>9047</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>8761</v>
+        <v>9048</v>
       </c>
       <c r="F24" s="3">
         <v>821118.86</v>
       </c>
       <c r="G24" s="3">
-        <v>101621.61</v>
+        <v>190365.98</v>
       </c>
       <c r="H24" s="3">
-        <v>185035.47</v>
+        <v>99699.11</v>
       </c>
       <c r="I24" s="3">
-        <v>286657.08</v>
+        <v>290065.09</v>
       </c>
       <c r="J24" s="3">
-        <v>34.91</v>
+        <v>35.33</v>
       </c>
       <c r="K24" s="3">
-        <v>-534461.78</v>
+        <v>-531053.77</v>
       </c>
       <c r="L24" s="3">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="M24" s="3">
-        <v>1035.0</v>
+        <v>1102.46</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>8762</v>
+        <v>9049</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>8763</v>
+        <v>9050</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8764</v>
+        <v>9051</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8765</v>
+        <v>9052</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>8766</v>
+        <v>9053</v>
       </c>
       <c r="F25" s="3">
         <v>969063.25</v>
       </c>
       <c r="G25" s="3">
-        <v>52296.41</v>
+        <v>70234.43</v>
       </c>
       <c r="H25" s="3">
-        <v>135557.77</v>
+        <v>126649.84</v>
       </c>
       <c r="I25" s="3">
-        <v>187854.18</v>
+        <v>196884.27</v>
       </c>
       <c r="J25" s="3">
-        <v>19.39</v>
+        <v>20.32</v>
       </c>
       <c r="K25" s="3">
-        <v>-781209.07</v>
+        <v>-772178.98</v>
       </c>
       <c r="L25" s="3">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="M25" s="3">
-        <v>270.62</v>
+        <v>974.74</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>8767</v>
+        <v>9054</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>8768</v>
+        <v>9055</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8769</v>
+        <v>9056</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8770</v>
+        <v>9057</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>8771</v>
+        <v>9058</v>
       </c>
       <c r="F26" s="3">
         <v>1050193.29</v>
       </c>
       <c r="G26" s="3">
-        <v>53865.75</v>
+        <v>65642.47</v>
       </c>
       <c r="H26" s="3">
-        <v>111543.21</v>
+        <v>106257.97</v>
       </c>
       <c r="I26" s="3">
-        <v>165408.96</v>
+        <v>171900.44</v>
       </c>
       <c r="J26" s="3">
-        <v>15.75</v>
+        <v>16.37</v>
       </c>
       <c r="K26" s="3">
-        <v>-884784.33</v>
+        <v>-878292.85</v>
       </c>
       <c r="L26" s="3">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="M26" s="3">
         <v>767.41</v>
@@ -82315,122 +84898,122 @@
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>8772</v>
+        <v>9059</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>8773</v>
+        <v>9060</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8774</v>
+        <v>9061</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8775</v>
+        <v>9062</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>8776</v>
+        <v>9063</v>
       </c>
       <c r="F27" s="3">
         <v>919135.8</v>
       </c>
       <c r="G27" s="3">
-        <v>85140.6</v>
+        <v>117635.64</v>
       </c>
       <c r="H27" s="3">
-        <v>133384.15</v>
+        <v>113456.99</v>
       </c>
       <c r="I27" s="3">
-        <v>218524.75</v>
+        <v>231092.63</v>
       </c>
       <c r="J27" s="3">
-        <v>23.78</v>
+        <v>25.14</v>
       </c>
       <c r="K27" s="3">
-        <v>-700611.05</v>
+        <v>-688043.17</v>
       </c>
       <c r="L27" s="3">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="M27" s="3">
-        <v>2307.36</v>
+        <v>2992.92</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>8777</v>
+        <v>9064</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>8778</v>
+        <v>9065</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8779</v>
+        <v>9066</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8780</v>
+        <v>9067</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>8781</v>
+        <v>9068</v>
       </c>
       <c r="F28" s="3">
         <v>1002913.88</v>
       </c>
       <c r="G28" s="3">
-        <v>90782.63</v>
+        <v>127230.73</v>
       </c>
       <c r="H28" s="3">
-        <v>115690.42</v>
+        <v>95723.32</v>
       </c>
       <c r="I28" s="3">
-        <v>206473.05</v>
+        <v>222954.05</v>
       </c>
       <c r="J28" s="3">
-        <v>20.59</v>
+        <v>22.23</v>
       </c>
       <c r="K28" s="3">
-        <v>-796440.83</v>
+        <v>-779959.83</v>
       </c>
       <c r="L28" s="3">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="M28" s="3">
-        <v>157.42</v>
+        <v>568.13</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>8782</v>
+        <v>9069</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>8783</v>
+        <v>9070</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8784</v>
+        <v>9071</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8785</v>
+        <v>9072</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>8786</v>
+        <v>9073</v>
       </c>
       <c r="F29" s="3">
         <v>872858.67</v>
       </c>
       <c r="G29" s="3">
-        <v>100223.72</v>
+        <v>148555.88</v>
       </c>
       <c r="H29" s="3">
-        <v>146927.63</v>
+        <v>113629.75</v>
       </c>
       <c r="I29" s="3">
-        <v>247151.35</v>
+        <v>262185.63</v>
       </c>
       <c r="J29" s="3">
-        <v>28.32</v>
+        <v>30.04</v>
       </c>
       <c r="K29" s="3">
-        <v>-625707.32</v>
+        <v>-610673.04</v>
       </c>
       <c r="L29" s="3">
-        <v>2.13</v>
+        <v>2.0</v>
       </c>
       <c r="M29" s="3">
         <v>5252.76</v>
@@ -82438,409 +85021,409 @@
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>8787</v>
+        <v>9074</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>8788</v>
+        <v>9075</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8789</v>
+        <v>9076</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8790</v>
+        <v>9077</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>8791</v>
+        <v>9078</v>
       </c>
       <c r="F30" s="3">
         <v>890266.15</v>
       </c>
       <c r="G30" s="3">
-        <v>72192.29</v>
+        <v>159115.84</v>
       </c>
       <c r="H30" s="3">
-        <v>162273.91</v>
+        <v>120977.64</v>
       </c>
       <c r="I30" s="3">
-        <v>234466.2</v>
+        <v>280093.48</v>
       </c>
       <c r="J30" s="3">
-        <v>26.34</v>
+        <v>31.46</v>
       </c>
       <c r="K30" s="3">
-        <v>-655799.95</v>
+        <v>-610172.67</v>
       </c>
       <c r="L30" s="3">
         <v>1.89</v>
       </c>
       <c r="M30" s="3">
-        <v>4432.55</v>
+        <v>5294.43</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>8792</v>
+        <v>9079</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>8793</v>
+        <v>9080</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8794</v>
+        <v>9081</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8795</v>
+        <v>9082</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>8796</v>
+        <v>9083</v>
       </c>
       <c r="F31" s="3">
         <v>984099.44</v>
       </c>
       <c r="G31" s="3">
-        <v>91845.85</v>
+        <v>158104.72</v>
       </c>
       <c r="H31" s="3">
-        <v>155604.55</v>
+        <v>114540.89</v>
       </c>
       <c r="I31" s="3">
-        <v>247450.4</v>
+        <v>272645.61</v>
       </c>
       <c r="J31" s="3">
-        <v>25.14</v>
+        <v>27.71</v>
       </c>
       <c r="K31" s="3">
-        <v>-736649.04</v>
+        <v>-711453.83</v>
       </c>
       <c r="L31" s="3">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="M31" s="3">
-        <v>2539.27</v>
+        <v>2696.77</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>8797</v>
+        <v>9084</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>8798</v>
+        <v>9085</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8799</v>
+        <v>9086</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8800</v>
+        <v>9087</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>8801</v>
+        <v>9088</v>
       </c>
       <c r="F32" s="3">
         <v>926984.47</v>
       </c>
       <c r="G32" s="3">
-        <v>55818.6</v>
+        <v>92561.56</v>
       </c>
       <c r="H32" s="3">
-        <v>124668.36</v>
+        <v>106538.64</v>
       </c>
       <c r="I32" s="3">
-        <v>180486.96</v>
+        <v>199100.2</v>
       </c>
       <c r="J32" s="3">
-        <v>19.47</v>
+        <v>21.48</v>
       </c>
       <c r="K32" s="3">
-        <v>-746497.51</v>
+        <v>-727884.27</v>
       </c>
       <c r="L32" s="3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M32" s="3">
-        <v>2701.92</v>
+        <v>3039.12</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>8802</v>
+        <v>9089</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>8803</v>
+        <v>9090</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8804</v>
+        <v>9091</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8805</v>
+        <v>9092</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>8806</v>
+        <v>9093</v>
       </c>
       <c r="F33" s="3">
         <v>1288411.21</v>
       </c>
       <c r="G33" s="3">
-        <v>79351.96</v>
+        <v>156304.39</v>
       </c>
       <c r="H33" s="3">
-        <v>332714.96</v>
+        <v>278445.95</v>
       </c>
       <c r="I33" s="3">
-        <v>412066.92</v>
+        <v>434750.34</v>
       </c>
       <c r="J33" s="3">
-        <v>31.98</v>
+        <v>33.74</v>
       </c>
       <c r="K33" s="3">
-        <v>-876344.29</v>
+        <v>-853660.87</v>
       </c>
       <c r="L33" s="3">
-        <v>0.95</v>
+        <v>1.62</v>
       </c>
       <c r="M33" s="3">
-        <v>3933.78</v>
+        <v>7033.78</v>
       </c>
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>8807</v>
+        <v>9094</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>8808</v>
+        <v>9095</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8809</v>
+        <v>9096</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8810</v>
+        <v>9097</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>8811</v>
+        <v>9098</v>
       </c>
       <c r="F34" s="3">
         <v>1074641.52</v>
       </c>
       <c r="G34" s="3">
-        <v>58011.41</v>
+        <v>113994.62</v>
       </c>
       <c r="H34" s="3">
-        <v>81586.27</v>
+        <v>43873.15</v>
       </c>
       <c r="I34" s="3">
-        <v>139597.68</v>
+        <v>157867.77</v>
       </c>
       <c r="J34" s="3">
-        <v>12.99</v>
+        <v>14.69</v>
       </c>
       <c r="K34" s="3">
-        <v>-935043.84</v>
+        <v>-916773.75</v>
       </c>
       <c r="L34" s="3">
-        <v>1.46</v>
+        <v>2.02</v>
       </c>
       <c r="M34" s="3">
-        <v>2037.62</v>
+        <v>3191.58</v>
       </c>
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>8812</v>
+        <v>9099</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>8813</v>
+        <v>9100</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8814</v>
+        <v>9101</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8815</v>
+        <v>9102</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>8816</v>
+        <v>9103</v>
       </c>
       <c r="F35" s="3">
         <v>1054434.17</v>
       </c>
       <c r="G35" s="3">
-        <v>68757.77</v>
+        <v>118884.48</v>
       </c>
       <c r="H35" s="3">
-        <v>115017.09</v>
+        <v>83815.83</v>
       </c>
       <c r="I35" s="3">
-        <v>183774.86</v>
+        <v>202700.31</v>
       </c>
       <c r="J35" s="3">
-        <v>17.43</v>
+        <v>19.22</v>
       </c>
       <c r="K35" s="3">
-        <v>-870659.31</v>
+        <v>-851733.86</v>
       </c>
       <c r="L35" s="3">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="M35" s="3">
-        <v>3100.82</v>
+        <v>3483.02</v>
       </c>
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>8817</v>
+        <v>9104</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>8818</v>
+        <v>9105</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8819</v>
+        <v>9106</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8820</v>
+        <v>9107</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>8821</v>
+        <v>9108</v>
       </c>
       <c r="F36" s="3">
         <v>1145461.66</v>
       </c>
       <c r="G36" s="3">
-        <v>119959.46</v>
+        <v>169772.88</v>
       </c>
       <c r="H36" s="3">
         <v>243072.59</v>
       </c>
       <c r="I36" s="3">
-        <v>363032.05</v>
+        <v>412845.47</v>
       </c>
       <c r="J36" s="3">
-        <v>31.69</v>
+        <v>36.04</v>
       </c>
       <c r="K36" s="3">
-        <v>-782429.61</v>
+        <v>-732616.19</v>
       </c>
       <c r="L36" s="3">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="M36" s="3">
-        <v>288.0</v>
+        <v>829.3</v>
       </c>
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>8822</v>
+        <v>9109</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>8823</v>
+        <v>9110</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8824</v>
+        <v>9111</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8825</v>
+        <v>9112</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>8826</v>
+        <v>9113</v>
       </c>
       <c r="F37" s="3">
         <v>1392111.83</v>
       </c>
       <c r="G37" s="3">
-        <v>112984.5</v>
+        <v>191039.98</v>
       </c>
       <c r="H37" s="3">
         <v>250247.02</v>
       </c>
       <c r="I37" s="3">
-        <v>363231.52</v>
+        <v>441287.0</v>
       </c>
       <c r="J37" s="3">
-        <v>26.09</v>
+        <v>31.7</v>
       </c>
       <c r="K37" s="3">
-        <v>-1028880.31</v>
+        <v>-950824.83</v>
       </c>
       <c r="L37" s="3">
-        <v>0.69</v>
+        <v>0.58</v>
       </c>
       <c r="M37" s="3">
-        <v>2505.48</v>
+        <v>2557.96</v>
       </c>
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>8827</v>
+        <v>9114</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>8828</v>
+        <v>9115</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8829</v>
+        <v>9116</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8830</v>
+        <v>9117</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>8831</v>
+        <v>9118</v>
       </c>
       <c r="F38" s="3">
         <v>958935.26</v>
       </c>
       <c r="G38" s="3">
-        <v>101907.15</v>
+        <v>154831.79</v>
       </c>
       <c r="H38" s="3">
         <v>173199.37</v>
       </c>
       <c r="I38" s="3">
-        <v>275106.52</v>
+        <v>328031.16</v>
       </c>
       <c r="J38" s="3">
-        <v>28.69</v>
+        <v>34.21</v>
       </c>
       <c r="K38" s="3">
-        <v>-683828.74</v>
+        <v>-630904.1</v>
       </c>
       <c r="L38" s="3">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="M38" s="3">
-        <v>8946.52</v>
+        <v>9284.52</v>
       </c>
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>8832</v>
+        <v>9119</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>8833</v>
+        <v>9120</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8834</v>
+        <v>9121</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8835</v>
+        <v>9122</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>8836</v>
+        <v>9123</v>
       </c>
       <c r="F39" s="3">
         <v>1141876.38</v>
       </c>
       <c r="G39" s="3">
-        <v>82003.1</v>
+        <v>136054.71</v>
       </c>
       <c r="H39" s="3">
         <v>174548.79</v>
       </c>
       <c r="I39" s="3">
-        <v>256551.89</v>
+        <v>310603.5</v>
       </c>
       <c r="J39" s="3">
-        <v>22.47</v>
+        <v>27.2</v>
       </c>
       <c r="K39" s="3">
-        <v>-885324.49</v>
+        <v>-831272.88</v>
       </c>
       <c r="L39" s="3">
-        <v>0.74</v>
+        <v>0.61</v>
       </c>
       <c r="M39" s="3">
         <v>1887.06</v>
@@ -82848,40 +85431,40 @@
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>8837</v>
+        <v>9124</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>8838</v>
+        <v>9125</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8839</v>
+        <v>9126</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8840</v>
+        <v>9127</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>8841</v>
+        <v>9128</v>
       </c>
       <c r="F40" s="3">
         <v>936014.91</v>
       </c>
       <c r="G40" s="3">
-        <v>54415.3</v>
+        <v>93162.12</v>
       </c>
       <c r="H40" s="3">
-        <v>120480.13</v>
+        <v>84948.36</v>
       </c>
       <c r="I40" s="3">
-        <v>174895.43</v>
+        <v>178110.48</v>
       </c>
       <c r="J40" s="3">
-        <v>18.69</v>
+        <v>19.03</v>
       </c>
       <c r="K40" s="3">
-        <v>-761119.48</v>
+        <v>-757904.43</v>
       </c>
       <c r="L40" s="3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="M40" s="3">
         <v>1839.64</v>
@@ -82889,142 +85472,142 @@
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>8842</v>
+        <v>9129</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>8843</v>
+        <v>9130</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8844</v>
+        <v>9131</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8845</v>
+        <v>9132</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>8846</v>
+        <v>9133</v>
       </c>
       <c r="F41" s="3">
         <v>1227064.36</v>
       </c>
       <c r="G41" s="3">
-        <v>64931.52</v>
+        <v>123930.86</v>
       </c>
       <c r="H41" s="3">
-        <v>174224.68</v>
+        <v>130616.01</v>
       </c>
       <c r="I41" s="3">
-        <v>239156.2</v>
+        <v>254546.87</v>
       </c>
       <c r="J41" s="3">
-        <v>19.49</v>
+        <v>20.74</v>
       </c>
       <c r="K41" s="3">
-        <v>-987908.16</v>
+        <v>-972517.49</v>
       </c>
       <c r="L41" s="3">
-        <v>1.59</v>
+        <v>2.36</v>
       </c>
       <c r="M41" s="3">
-        <v>3795.92</v>
+        <v>6017.72</v>
       </c>
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>8847</v>
+        <v>9134</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>8848</v>
+        <v>9135</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8849</v>
+        <v>9136</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8850</v>
+        <v>9137</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>8851</v>
+        <v>9138</v>
       </c>
       <c r="F42" s="3">
         <v>940955.58</v>
       </c>
       <c r="G42" s="3">
-        <v>65070.28</v>
+        <v>115591.01</v>
       </c>
       <c r="H42" s="3">
-        <v>199828.65</v>
+        <v>149966.88</v>
       </c>
       <c r="I42" s="3">
-        <v>264898.93</v>
+        <v>265557.89</v>
       </c>
       <c r="J42" s="3">
-        <v>28.15</v>
+        <v>28.22</v>
       </c>
       <c r="K42" s="3">
-        <v>-676056.65</v>
+        <v>-675397.69</v>
       </c>
       <c r="L42" s="3">
-        <v>0.78</v>
+        <v>1.61</v>
       </c>
       <c r="M42" s="3">
-        <v>2063.02</v>
+        <v>4280.9</v>
       </c>
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>8852</v>
+        <v>9139</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>8853</v>
+        <v>9140</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8854</v>
+        <v>9141</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8855</v>
+        <v>9142</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>8856</v>
+        <v>9143</v>
       </c>
       <c r="F43" s="3">
         <v>1062667.74</v>
       </c>
       <c r="G43" s="3">
-        <v>84326.96</v>
+        <v>152361.5</v>
       </c>
       <c r="H43" s="3">
-        <v>212155.25</v>
+        <v>155092.67</v>
       </c>
       <c r="I43" s="3">
-        <v>296482.21</v>
+        <v>307454.17</v>
       </c>
       <c r="J43" s="3">
-        <v>27.9</v>
+        <v>28.93</v>
       </c>
       <c r="K43" s="3">
-        <v>-766185.53</v>
+        <v>-755213.57</v>
       </c>
       <c r="L43" s="3">
-        <v>0.74</v>
+        <v>1.22</v>
       </c>
       <c r="M43" s="3">
-        <v>2184.5</v>
+        <v>3736.4</v>
       </c>
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>8857</v>
+        <v>9144</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>8858</v>
+        <v>9145</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8859</v>
+        <v>9146</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8860</v>
+        <v>9147</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>8861</v>
+        <v>9148</v>
       </c>
       <c r="F44" s="3">
         <v>1129524.64</v>
@@ -83053,19 +85636,19 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>8862</v>
+        <v>9149</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>8863</v>
+        <v>9150</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8864</v>
+        <v>9151</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8865</v>
+        <v>9152</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>8866</v>
+        <v>9153</v>
       </c>
       <c r="F45" s="3">
         <v>931654.84</v>
@@ -83094,19 +85677,19 @@
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>8867</v>
+        <v>9154</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>8868</v>
+        <v>9155</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8869</v>
+        <v>9156</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8870</v>
+        <v>9157</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>8871</v>
+        <v>9158</v>
       </c>
       <c r="F46" s="3">
         <v>1096879.63</v>
@@ -83135,19 +85718,19 @@
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>8872</v>
+        <v>9159</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>8873</v>
+        <v>9160</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8874</v>
+        <v>9161</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8875</v>
+        <v>9162</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>8876</v>
+        <v>9163</v>
       </c>
       <c r="F47" s="3">
         <v>1362950.73</v>
@@ -83176,19 +85759,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>8877</v>
+        <v>9164</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>8878</v>
+        <v>9165</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8879</v>
+        <v>9166</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8880</v>
+        <v>9167</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>8881</v>
+        <v>9168</v>
       </c>
       <c r="F48" s="3">
         <v>1050721.66</v>
@@ -83217,19 +85800,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>8882</v>
+        <v>9169</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>8883</v>
+        <v>9170</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8884</v>
+        <v>9171</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8885</v>
+        <v>9172</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>8886</v>
+        <v>9173</v>
       </c>
       <c r="F49" s="3">
         <v>989655.83</v>
@@ -83258,19 +85841,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>8887</v>
+        <v>9174</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>8888</v>
+        <v>9175</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>8889</v>
+        <v>9176</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8890</v>
+        <v>9177</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>8891</v>
+        <v>9178</v>
       </c>
       <c r="F50" s="3">
         <v>978747.3</v>
@@ -83299,19 +85882,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>8892</v>
+        <v>9179</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>8893</v>
+        <v>9180</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>8894</v>
+        <v>9181</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>8895</v>
+        <v>9182</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>8896</v>
+        <v>9183</v>
       </c>
       <c r="F51" s="3">
         <v>983156.92</v>
@@ -83340,19 +85923,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>8897</v>
+        <v>9184</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>8898</v>
+        <v>9185</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>8899</v>
+        <v>9186</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8900</v>
+        <v>9187</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>8901</v>
+        <v>9188</v>
       </c>
       <c r="F52" s="3">
         <v>1178421.11</v>
@@ -83379,7 +85962,7 @@
         <v>1727.2</v>
       </c>
     </row>
-    <row r="56" spans="8:8" ht="16.25">
+    <row r="56" spans="8:8">
       <c r="A56" s="4" t="s">
         <v>5397</v>
       </c>
@@ -89856,7 +92439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AO49"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -89906,282 +92489,282 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>8902</v>
+        <v>9189</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8903</v>
+        <v>9190</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8904</v>
+        <v>9191</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8905</v>
+        <v>9192</v>
       </c>
       <c r="E2" s="3">
         <v>6104317.5</v>
       </c>
       <c r="F2" s="3">
-        <v>412504.59</v>
+        <v>586373.57</v>
       </c>
       <c r="G2" s="3">
-        <v>1567759.71</v>
+        <v>1568948.07</v>
       </c>
       <c r="H2" s="3">
-        <v>1980264.3</v>
+        <v>2155321.64</v>
       </c>
       <c r="I2" s="3">
-        <v>32.44</v>
+        <v>35.31</v>
       </c>
       <c r="J2" s="3">
-        <v>-4124053.2</v>
+        <v>-3948995.86</v>
       </c>
       <c r="K2" s="3">
-        <v>11085.36</v>
+        <v>18506.15</v>
       </c>
       <c r="L2" s="3">
-        <v>0.56</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>8906</v>
+        <v>9193</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8907</v>
+        <v>9194</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8908</v>
+        <v>9195</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8909</v>
+        <v>9196</v>
       </c>
       <c r="E3" s="3">
         <v>3440798.37</v>
       </c>
       <c r="F3" s="3">
-        <v>172794.82</v>
+        <v>260899.42</v>
       </c>
       <c r="G3" s="3">
-        <v>773390.95</v>
+        <v>811153.07</v>
       </c>
       <c r="H3" s="3">
-        <v>946185.77</v>
+        <v>1072052.49</v>
       </c>
       <c r="I3" s="3">
-        <v>27.5</v>
+        <v>31.16</v>
       </c>
       <c r="J3" s="3">
-        <v>-2494612.6</v>
+        <v>-2368745.88</v>
       </c>
       <c r="K3" s="3">
-        <v>6618.03</v>
+        <v>9797.29</v>
       </c>
       <c r="L3" s="3">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>8910</v>
+        <v>9197</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8911</v>
+        <v>9198</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8912</v>
+        <v>9199</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8913</v>
+        <v>9200</v>
       </c>
       <c r="E4" s="3">
         <v>6398516.07</v>
       </c>
       <c r="F4" s="3">
-        <v>471262.52</v>
+        <v>543819.37</v>
       </c>
       <c r="G4" s="3">
-        <v>908849.05</v>
+        <v>860105.11</v>
       </c>
       <c r="H4" s="3">
-        <v>1380111.57</v>
+        <v>1403924.48</v>
       </c>
       <c r="I4" s="3">
-        <v>21.57</v>
+        <v>21.94</v>
       </c>
       <c r="J4" s="3">
-        <v>-5018404.5</v>
+        <v>-4994591.59</v>
       </c>
       <c r="K4" s="3">
-        <v>8625.75</v>
+        <v>9112.95</v>
       </c>
       <c r="L4" s="3">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>8914</v>
+        <v>9201</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8915</v>
+        <v>9202</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8916</v>
+        <v>9203</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8917</v>
+        <v>9204</v>
       </c>
       <c r="E5" s="3">
         <v>7403170.5</v>
       </c>
       <c r="F5" s="3">
-        <v>643754.68</v>
+        <v>954609.18</v>
       </c>
       <c r="G5" s="3">
-        <v>1104335.21</v>
+        <v>862026.26</v>
       </c>
       <c r="H5" s="3">
-        <v>1748089.89</v>
+        <v>1816635.44</v>
       </c>
       <c r="I5" s="3">
-        <v>23.61</v>
+        <v>24.54</v>
       </c>
       <c r="J5" s="3">
-        <v>-5655080.61</v>
+        <v>-5586535.06</v>
       </c>
       <c r="K5" s="3">
-        <v>21218.41</v>
+        <v>25365.82</v>
       </c>
       <c r="L5" s="3">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>8918</v>
+        <v>9205</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8919</v>
+        <v>9206</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8920</v>
+        <v>9207</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8921</v>
+        <v>9208</v>
       </c>
       <c r="E6" s="3">
         <v>7091695.63</v>
       </c>
       <c r="F6" s="3">
-        <v>526201.6</v>
+        <v>947521.49</v>
       </c>
       <c r="G6" s="3">
-        <v>1118792.77</v>
+        <v>861821.85</v>
       </c>
       <c r="H6" s="3">
-        <v>1644994.37</v>
+        <v>1809343.34</v>
       </c>
       <c r="I6" s="3">
-        <v>23.2</v>
+        <v>25.51</v>
       </c>
       <c r="J6" s="3">
-        <v>-5446701.26</v>
+        <v>-5282352.29</v>
       </c>
       <c r="K6" s="3">
-        <v>23998.72</v>
+        <v>29991.46</v>
       </c>
       <c r="L6" s="3">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>8922</v>
+        <v>9209</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8923</v>
+        <v>9210</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8924</v>
+        <v>9211</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8925</v>
+        <v>9212</v>
       </c>
       <c r="E7" s="3">
         <v>4638385.13</v>
       </c>
       <c r="F7" s="3">
-        <v>416854.21</v>
+        <v>651699.36</v>
       </c>
       <c r="G7" s="3">
         <v>841067.77</v>
       </c>
       <c r="H7" s="3">
-        <v>1257921.98</v>
+        <v>1492767.13</v>
       </c>
       <c r="I7" s="3">
-        <v>27.12</v>
+        <v>32.18</v>
       </c>
       <c r="J7" s="3">
-        <v>-3380463.15</v>
+        <v>-3145618.0</v>
       </c>
       <c r="K7" s="3">
-        <v>13627.06</v>
+        <v>14558.84</v>
       </c>
       <c r="L7" s="3">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>8926</v>
+        <v>9213</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8927</v>
+        <v>9214</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8928</v>
+        <v>9215</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8929</v>
+        <v>9216</v>
       </c>
       <c r="E8" s="3">
         <v>7324761.7</v>
       </c>
       <c r="F8" s="3">
-        <v>509378.23</v>
+        <v>725679.66</v>
       </c>
       <c r="G8" s="3">
-        <v>1124753.67</v>
+        <v>938688.88</v>
       </c>
       <c r="H8" s="3">
-        <v>1634131.9</v>
+        <v>1664368.54</v>
       </c>
       <c r="I8" s="3">
-        <v>22.31</v>
+        <v>22.72</v>
       </c>
       <c r="J8" s="3">
-        <v>-5690629.8</v>
+        <v>-5660393.16</v>
       </c>
       <c r="K8" s="3">
-        <v>11869.96</v>
+        <v>17861.54</v>
       </c>
       <c r="L8" s="3">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>8930</v>
+        <v>9217</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8931</v>
+        <v>9218</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8932</v>
+        <v>9219</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8933</v>
+        <v>9220</v>
       </c>
       <c r="E9" s="3">
         <v>6543653.55</v>
@@ -91313,7 +93896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH78"/>
+  <dimension ref="A1:AI78"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="9" max="9" customWidth="1" width="5.8984375" style="0"/>
@@ -94642,7 +97225,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X79"/>
+  <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="29"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9508" count="9508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9795" count="9795">
   <si>
     <t>Region</t>
   </si>
@@ -78123,6 +78123,2589 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
     </r>
   </si>
   <si>
@@ -86007,7 +88590,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -86080,10 +88663,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -86106,9 +88689,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -86405,13 +88985,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AV397"/>
+  <dimension ref="A1:AX397"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
-    <col min="1" max="1" customWidth="1" bestFit="1" width="12.449219" style="0"/>
+    <col min="1" max="1" customWidth="1" width="9.8828125" style="0"/>
     <col min="2" max="2" customWidth="1" bestFit="1" width="10.089844" style="0"/>
-    <col min="3" max="3" customWidth="1" bestFit="1" width="21.90625" style="0"/>
-    <col min="4" max="4" customWidth="1" bestFit="1" width="43.179688" style="0"/>
+    <col min="3" max="3" customWidth="1" width="11.6640625" style="0"/>
+    <col min="4" max="4" customWidth="1" width="31.992188" style="0"/>
     <col min="5" max="5" customWidth="1" bestFit="1" width="13.636719" style="0"/>
     <col min="6" max="6" customWidth="1" bestFit="1" width="23.089844" style="0"/>
     <col min="7" max="7" customWidth="1" bestFit="1" width="21.90625" style="0"/>
@@ -86466,40 +89046,40 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>9221</v>
+        <v>9508</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9222</v>
+        <v>9509</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9223</v>
+        <v>9510</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9224</v>
+        <v>9511</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9225</v>
+        <v>9512</v>
       </c>
       <c r="F2" s="3">
         <v>787067.06</v>
       </c>
       <c r="G2" s="3">
-        <v>89450.74</v>
+        <v>93585.25</v>
       </c>
       <c r="H2" s="3">
-        <v>239590.73</v>
+        <v>257760.86</v>
       </c>
       <c r="I2" s="3">
-        <v>329041.47</v>
+        <v>351346.11</v>
       </c>
       <c r="J2" s="3">
-        <v>41.81</v>
+        <v>44.64</v>
       </c>
       <c r="K2" s="3">
-        <v>-458025.59</v>
+        <v>-435720.95</v>
       </c>
       <c r="L2" s="3">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="M2" s="3">
         <v>1693.99</v>
@@ -86507,40 +89087,40 @@
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>9226</v>
+        <v>9513</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9227</v>
+        <v>9514</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9228</v>
+        <v>9515</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9229</v>
+        <v>9516</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9230</v>
+        <v>9517</v>
       </c>
       <c r="F3" s="3">
         <v>792403.1</v>
       </c>
       <c r="G3" s="3">
-        <v>70015.96</v>
+        <v>85324.55</v>
       </c>
       <c r="H3" s="3">
-        <v>258759.26</v>
+        <v>244497.3</v>
       </c>
       <c r="I3" s="3">
-        <v>328775.22</v>
+        <v>329821.85</v>
       </c>
       <c r="J3" s="3">
-        <v>41.49</v>
+        <v>41.62</v>
       </c>
       <c r="K3" s="3">
-        <v>-463627.88</v>
+        <v>-462581.25</v>
       </c>
       <c r="L3" s="3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M3" s="3">
         <v>4258.14</v>
@@ -86548,40 +89128,40 @@
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>9231</v>
+        <v>9518</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9232</v>
+        <v>9519</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9233</v>
+        <v>9520</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9234</v>
+        <v>9521</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>9235</v>
+        <v>9522</v>
       </c>
       <c r="F4" s="3">
         <v>672792.28</v>
       </c>
       <c r="G4" s="3">
-        <v>94920.98</v>
+        <v>100124.15</v>
       </c>
       <c r="H4" s="3">
-        <v>190959.92</v>
+        <v>189853.27</v>
       </c>
       <c r="I4" s="3">
-        <v>285880.9</v>
+        <v>289977.42</v>
       </c>
       <c r="J4" s="3">
-        <v>42.49</v>
+        <v>43.1</v>
       </c>
       <c r="K4" s="3">
-        <v>-386911.38</v>
+        <v>-382814.86</v>
       </c>
       <c r="L4" s="3">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="M4" s="3">
         <v>1140.29</v>
@@ -86589,40 +89169,40 @@
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>9236</v>
+        <v>9523</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9237</v>
+        <v>9524</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9238</v>
+        <v>9525</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9239</v>
+        <v>9526</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9240</v>
+        <v>9527</v>
       </c>
       <c r="F5" s="3">
         <v>740010.55</v>
       </c>
       <c r="G5" s="3">
-        <v>94942.01</v>
+        <v>99550.52</v>
       </c>
       <c r="H5" s="3">
-        <v>168326.81</v>
+        <v>165753.68</v>
       </c>
       <c r="I5" s="3">
-        <v>263268.82</v>
+        <v>265304.2</v>
       </c>
       <c r="J5" s="3">
-        <v>35.58</v>
+        <v>35.85</v>
       </c>
       <c r="K5" s="3">
-        <v>-476741.73</v>
+        <v>-474706.35</v>
       </c>
       <c r="L5" s="3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M5" s="3">
         <v>3243.43</v>
@@ -86630,40 +89210,40 @@
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>9241</v>
+        <v>9528</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9242</v>
+        <v>9529</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9243</v>
+        <v>9530</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9244</v>
+        <v>9531</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9245</v>
+        <v>9532</v>
       </c>
       <c r="F6" s="3">
         <v>763526.5</v>
       </c>
       <c r="G6" s="3">
-        <v>126782.41</v>
+        <v>128639.45</v>
       </c>
       <c r="H6" s="3">
-        <v>195609.51</v>
+        <v>197551.54</v>
       </c>
       <c r="I6" s="3">
-        <v>322391.92</v>
+        <v>326190.99</v>
       </c>
       <c r="J6" s="3">
-        <v>42.22</v>
+        <v>42.72</v>
       </c>
       <c r="K6" s="3">
-        <v>-441134.58</v>
+        <v>-437335.51</v>
       </c>
       <c r="L6" s="3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="M6" s="3">
         <v>3692.16</v>
@@ -86671,37 +89251,37 @@
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>9246</v>
+        <v>9533</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9247</v>
+        <v>9534</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9248</v>
+        <v>9535</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9249</v>
+        <v>9536</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>9250</v>
+        <v>9537</v>
       </c>
       <c r="F7" s="3">
         <v>803185.79</v>
       </c>
       <c r="G7" s="3">
-        <v>85688.9</v>
+        <v>85867.01</v>
       </c>
       <c r="H7" s="3">
-        <v>213814.58</v>
+        <v>213148.68</v>
       </c>
       <c r="I7" s="3">
-        <v>299503.48</v>
+        <v>299015.69</v>
       </c>
       <c r="J7" s="3">
-        <v>37.29</v>
+        <v>37.23</v>
       </c>
       <c r="K7" s="3">
-        <v>-503682.31</v>
+        <v>-504170.1</v>
       </c>
       <c r="L7" s="3">
         <v>0.77</v>
@@ -86712,40 +89292,40 @@
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>9251</v>
+        <v>9538</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9252</v>
+        <v>9539</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9253</v>
+        <v>9540</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9254</v>
+        <v>9541</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>9255</v>
+        <v>9542</v>
       </c>
       <c r="F8" s="3">
         <v>770724.92</v>
       </c>
       <c r="G8" s="3">
-        <v>100724.22</v>
+        <v>101586.84</v>
       </c>
       <c r="H8" s="3">
-        <v>147369.63</v>
+        <v>153793.48</v>
       </c>
       <c r="I8" s="3">
-        <v>248093.85</v>
+        <v>255380.32</v>
       </c>
       <c r="J8" s="3">
-        <v>32.19</v>
+        <v>33.14</v>
       </c>
       <c r="K8" s="3">
-        <v>-522631.07</v>
+        <v>-515344.6</v>
       </c>
       <c r="L8" s="3">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="M8" s="3">
         <v>2732.7</v>
@@ -86753,40 +89333,40 @@
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>9256</v>
+        <v>9543</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9257</v>
+        <v>9544</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9258</v>
+        <v>9545</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9259</v>
+        <v>9546</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>9260</v>
+        <v>9547</v>
       </c>
       <c r="F9" s="3">
         <v>774607.3</v>
       </c>
       <c r="G9" s="3">
-        <v>104524.96</v>
+        <v>105041.27</v>
       </c>
       <c r="H9" s="3">
-        <v>153187.21</v>
+        <v>161448.46</v>
       </c>
       <c r="I9" s="3">
-        <v>257712.17</v>
+        <v>266489.73</v>
       </c>
       <c r="J9" s="3">
-        <v>33.27</v>
+        <v>34.4</v>
       </c>
       <c r="K9" s="3">
-        <v>-516895.13</v>
+        <v>-508117.57</v>
       </c>
       <c r="L9" s="3">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="M9" s="3">
         <v>1041.98</v>
@@ -86794,40 +89374,40 @@
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>9261</v>
+        <v>9548</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9262</v>
+        <v>9549</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9263</v>
+        <v>9550</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9264</v>
+        <v>9551</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>9265</v>
+        <v>9552</v>
       </c>
       <c r="F10" s="3">
         <v>900349.47</v>
       </c>
       <c r="G10" s="3">
-        <v>62738.78</v>
+        <v>63374.07</v>
       </c>
       <c r="H10" s="3">
-        <v>216633.64</v>
+        <v>225971.36</v>
       </c>
       <c r="I10" s="3">
-        <v>279372.42</v>
+        <v>289345.43</v>
       </c>
       <c r="J10" s="3">
-        <v>31.03</v>
+        <v>32.14</v>
       </c>
       <c r="K10" s="3">
-        <v>-620977.05</v>
+        <v>-611004.04</v>
       </c>
       <c r="L10" s="3">
-        <v>1.04</v>
+        <v>1.0</v>
       </c>
       <c r="M10" s="3">
         <v>2898.96</v>
@@ -86835,81 +89415,81 @@
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>9266</v>
+        <v>9553</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9267</v>
+        <v>9554</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9268</v>
+        <v>9555</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9269</v>
+        <v>9556</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>9270</v>
+        <v>9557</v>
       </c>
       <c r="F11" s="3">
         <v>901291.26</v>
       </c>
       <c r="G11" s="3">
-        <v>66124.49</v>
+        <v>66541.13</v>
       </c>
       <c r="H11" s="3">
-        <v>175637.65</v>
+        <v>183784.49</v>
       </c>
       <c r="I11" s="3">
-        <v>241762.14</v>
+        <v>250325.62</v>
       </c>
       <c r="J11" s="3">
-        <v>26.82</v>
+        <v>27.77</v>
       </c>
       <c r="K11" s="3">
-        <v>-659529.12</v>
+        <v>-650965.64</v>
       </c>
       <c r="L11" s="3">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="M11" s="3">
-        <v>2953.16</v>
+        <v>3897.26</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>9271</v>
+        <v>9558</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>9272</v>
+        <v>9559</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9273</v>
+        <v>9560</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9274</v>
+        <v>9561</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>9275</v>
+        <v>9562</v>
       </c>
       <c r="F12" s="3">
         <v>790977.36</v>
       </c>
       <c r="G12" s="3">
-        <v>104493.51</v>
+        <v>106758.49</v>
       </c>
       <c r="H12" s="3">
-        <v>211842.16</v>
+        <v>224784.4</v>
       </c>
       <c r="I12" s="3">
-        <v>316335.67</v>
+        <v>331542.89</v>
       </c>
       <c r="J12" s="3">
-        <v>39.99</v>
+        <v>41.92</v>
       </c>
       <c r="K12" s="3">
-        <v>-474641.69</v>
+        <v>-459434.47</v>
       </c>
       <c r="L12" s="3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="M12" s="3">
         <v>3347.75</v>
@@ -86917,40 +89497,40 @@
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>9276</v>
+        <v>9563</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9277</v>
+        <v>9564</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9278</v>
+        <v>9565</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9279</v>
+        <v>9566</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>9280</v>
+        <v>9567</v>
       </c>
       <c r="F13" s="3">
         <v>848180.28</v>
       </c>
       <c r="G13" s="3">
-        <v>93068.2</v>
+        <v>93691.2</v>
       </c>
       <c r="H13" s="3">
-        <v>246051.57</v>
+        <v>273783.88</v>
       </c>
       <c r="I13" s="3">
-        <v>339119.77</v>
+        <v>367475.08</v>
       </c>
       <c r="J13" s="3">
-        <v>39.98</v>
+        <v>43.33</v>
       </c>
       <c r="K13" s="3">
-        <v>-509060.51</v>
+        <v>-480705.2</v>
       </c>
       <c r="L13" s="3">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="M13" s="3">
         <v>3047.31</v>
@@ -86958,40 +89538,40 @@
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>9281</v>
+        <v>9568</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9282</v>
+        <v>9569</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9283</v>
+        <v>9570</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9284</v>
+        <v>9571</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>9285</v>
+        <v>9572</v>
       </c>
       <c r="F14" s="3">
         <v>788558.37</v>
       </c>
       <c r="G14" s="3">
-        <v>90644.22</v>
+        <v>92191.75</v>
       </c>
       <c r="H14" s="3">
-        <v>194494.9</v>
+        <v>216176.15</v>
       </c>
       <c r="I14" s="3">
-        <v>285139.12</v>
+        <v>308367.9</v>
       </c>
       <c r="J14" s="3">
-        <v>36.16</v>
+        <v>39.11</v>
       </c>
       <c r="K14" s="3">
-        <v>-503419.25</v>
+        <v>-480190.47</v>
       </c>
       <c r="L14" s="3">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="M14" s="3">
         <v>1050.0</v>
@@ -86999,40 +89579,40 @@
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>9286</v>
+        <v>9573</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9287</v>
+        <v>9574</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9288</v>
+        <v>9575</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9289</v>
+        <v>9576</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>9290</v>
+        <v>9577</v>
       </c>
       <c r="F15" s="3">
         <v>816369.33</v>
       </c>
       <c r="G15" s="3">
-        <v>51810.44</v>
+        <v>52240.7</v>
       </c>
       <c r="H15" s="3">
-        <v>176120.24</v>
+        <v>185531.23</v>
       </c>
       <c r="I15" s="3">
-        <v>227930.68</v>
+        <v>237771.93</v>
       </c>
       <c r="J15" s="3">
-        <v>27.92</v>
+        <v>29.13</v>
       </c>
       <c r="K15" s="3">
-        <v>-588438.65</v>
+        <v>-578597.4</v>
       </c>
       <c r="L15" s="3">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="M15" s="3">
         <v>547.1</v>
@@ -87040,40 +89620,40 @@
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>9291</v>
+        <v>9578</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>9292</v>
+        <v>9579</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9293</v>
+        <v>9580</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9294</v>
+        <v>9581</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>9295</v>
+        <v>9582</v>
       </c>
       <c r="F16" s="3">
         <v>792760.6</v>
       </c>
       <c r="G16" s="3">
-        <v>63952.26</v>
+        <v>64671.11</v>
       </c>
       <c r="H16" s="3">
-        <v>97547.55</v>
+        <v>117780.64</v>
       </c>
       <c r="I16" s="3">
-        <v>161499.81</v>
+        <v>182451.75</v>
       </c>
       <c r="J16" s="3">
-        <v>20.37</v>
+        <v>23.01</v>
       </c>
       <c r="K16" s="3">
-        <v>-631260.79</v>
+        <v>-610308.85</v>
       </c>
       <c r="L16" s="3">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="M16" s="3">
         <v>630.0</v>
@@ -87081,40 +89661,40 @@
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>9296</v>
+        <v>9583</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>9297</v>
+        <v>9584</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9298</v>
+        <v>9585</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9299</v>
+        <v>9586</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>9300</v>
+        <v>9587</v>
       </c>
       <c r="F17" s="3">
         <v>786604.47</v>
       </c>
       <c r="G17" s="3">
-        <v>57077.93</v>
+        <v>57226.35</v>
       </c>
       <c r="H17" s="3">
-        <v>118719.82</v>
+        <v>144462.53</v>
       </c>
       <c r="I17" s="3">
-        <v>175797.75</v>
+        <v>201688.88</v>
       </c>
       <c r="J17" s="3">
-        <v>22.35</v>
+        <v>25.64</v>
       </c>
       <c r="K17" s="3">
-        <v>-610806.72</v>
+        <v>-584915.59</v>
       </c>
       <c r="L17" s="3">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="M17" s="3">
         <v>776.15</v>
@@ -87122,163 +89702,163 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>9301</v>
+        <v>9588</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>9302</v>
+        <v>9589</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9303</v>
+        <v>9590</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9304</v>
+        <v>9591</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>9305</v>
+        <v>9592</v>
       </c>
       <c r="F18" s="3">
         <v>1063383.58</v>
       </c>
       <c r="G18" s="3">
-        <v>103566.22</v>
+        <v>150131.14</v>
       </c>
       <c r="H18" s="3">
-        <v>157398.3</v>
+        <v>73085.44</v>
       </c>
       <c r="I18" s="3">
-        <v>260964.52</v>
+        <v>223216.58</v>
       </c>
       <c r="J18" s="3">
-        <v>24.54</v>
+        <v>20.99</v>
       </c>
       <c r="K18" s="3">
-        <v>-802419.06</v>
+        <v>-840167.0</v>
       </c>
       <c r="L18" s="3">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="M18" s="3">
-        <v>3008.1</v>
+        <v>3270.5</v>
       </c>
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>9306</v>
+        <v>9593</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>9307</v>
+        <v>9594</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9308</v>
+        <v>9595</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9309</v>
+        <v>9596</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>9310</v>
+        <v>9597</v>
       </c>
       <c r="F19" s="3">
         <v>886606.12</v>
       </c>
       <c r="G19" s="3">
-        <v>101572.59</v>
+        <v>141511.62</v>
       </c>
       <c r="H19" s="3">
-        <v>148698.17</v>
+        <v>62470.28</v>
       </c>
       <c r="I19" s="3">
-        <v>250270.76</v>
+        <v>203981.9</v>
       </c>
       <c r="J19" s="3">
-        <v>28.23</v>
+        <v>23.01</v>
       </c>
       <c r="K19" s="3">
-        <v>-636335.36</v>
+        <v>-682624.22</v>
       </c>
       <c r="L19" s="3">
-        <v>0.94</v>
+        <v>1.68</v>
       </c>
       <c r="M19" s="3">
-        <v>2354.16</v>
+        <v>3433.68</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>9311</v>
+        <v>9598</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>9312</v>
+        <v>9599</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9313</v>
+        <v>9600</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9314</v>
+        <v>9601</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>9315</v>
+        <v>9602</v>
       </c>
       <c r="F20" s="3">
         <v>1264233.6</v>
       </c>
       <c r="G20" s="3">
-        <v>127515.77</v>
+        <v>173656.82</v>
       </c>
       <c r="H20" s="3">
-        <v>215861.3</v>
+        <v>138961.04</v>
       </c>
       <c r="I20" s="3">
-        <v>343377.07</v>
+        <v>312617.86</v>
       </c>
       <c r="J20" s="3">
-        <v>27.16</v>
+        <v>24.73</v>
       </c>
       <c r="K20" s="3">
-        <v>-920856.53</v>
+        <v>-951615.74</v>
       </c>
       <c r="L20" s="3">
-        <v>0.64</v>
+        <v>1.36</v>
       </c>
       <c r="M20" s="3">
-        <v>2209.94</v>
+        <v>4236.86</v>
       </c>
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>9316</v>
+        <v>9603</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>9317</v>
+        <v>9604</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9318</v>
+        <v>9605</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9319</v>
+        <v>9606</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>9320</v>
+        <v>9607</v>
       </c>
       <c r="F21" s="3">
         <v>873034.8</v>
       </c>
       <c r="G21" s="3">
-        <v>147898.83</v>
+        <v>148370.34</v>
       </c>
       <c r="H21" s="3">
-        <v>149171.47</v>
+        <v>152475.53</v>
       </c>
       <c r="I21" s="3">
-        <v>297070.3</v>
+        <v>300845.87</v>
       </c>
       <c r="J21" s="3">
-        <v>34.03</v>
+        <v>34.46</v>
       </c>
       <c r="K21" s="3">
-        <v>-575964.5</v>
+        <v>-572188.93</v>
       </c>
       <c r="L21" s="3">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="M21" s="3">
         <v>2250.94</v>
@@ -87286,40 +89866,40 @@
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>9321</v>
+        <v>9608</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9322</v>
+        <v>9609</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9323</v>
+        <v>9610</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9324</v>
+        <v>9611</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>9325</v>
+        <v>9612</v>
       </c>
       <c r="F22" s="3">
         <v>891542.61</v>
       </c>
       <c r="G22" s="3">
-        <v>140744.62</v>
+        <v>141146.19</v>
       </c>
       <c r="H22" s="3">
-        <v>112045.78</v>
+        <v>118952.04</v>
       </c>
       <c r="I22" s="3">
-        <v>252790.4</v>
+        <v>260098.23</v>
       </c>
       <c r="J22" s="3">
-        <v>28.35</v>
+        <v>29.17</v>
       </c>
       <c r="K22" s="3">
-        <v>-638752.21</v>
+        <v>-631444.38</v>
       </c>
       <c r="L22" s="3">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="M22" s="3">
         <v>5617.68</v>
@@ -87327,40 +89907,40 @@
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>9326</v>
+        <v>9613</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9327</v>
+        <v>9614</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9328</v>
+        <v>9615</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9329</v>
+        <v>9616</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>9330</v>
+        <v>9617</v>
       </c>
       <c r="F23" s="3">
         <v>876168.01</v>
       </c>
       <c r="G23" s="3">
-        <v>170867.16</v>
+        <v>175205.45</v>
       </c>
       <c r="H23" s="3">
-        <v>135903.11</v>
+        <v>142852.85</v>
       </c>
       <c r="I23" s="3">
-        <v>306770.27</v>
+        <v>318058.3</v>
       </c>
       <c r="J23" s="3">
-        <v>35.01</v>
+        <v>36.3</v>
       </c>
       <c r="K23" s="3">
-        <v>-569397.74</v>
+        <v>-558109.71</v>
       </c>
       <c r="L23" s="3">
-        <v>4.5</v>
+        <v>4.34</v>
       </c>
       <c r="M23" s="3">
         <v>13817.64</v>
@@ -87368,40 +89948,40 @@
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>9331</v>
+        <v>9618</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9332</v>
+        <v>9619</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9333</v>
+        <v>9620</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9334</v>
+        <v>9621</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>9335</v>
+        <v>9622</v>
       </c>
       <c r="F24" s="3">
         <v>821118.86</v>
       </c>
       <c r="G24" s="3">
-        <v>211533.11</v>
+        <v>214067.35</v>
       </c>
       <c r="H24" s="3">
-        <v>110285.07</v>
+        <v>199282.36</v>
       </c>
       <c r="I24" s="3">
-        <v>321818.18</v>
+        <v>413349.71</v>
       </c>
       <c r="J24" s="3">
-        <v>39.19</v>
+        <v>50.34</v>
       </c>
       <c r="K24" s="3">
-        <v>-499300.68</v>
+        <v>-407769.15</v>
       </c>
       <c r="L24" s="3">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="M24" s="3">
         <v>1440.46</v>
@@ -87409,37 +89989,37 @@
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>9336</v>
+        <v>9623</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>9337</v>
+        <v>9624</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9338</v>
+        <v>9625</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9339</v>
+        <v>9626</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>9340</v>
+        <v>9627</v>
       </c>
       <c r="F25" s="3">
         <v>969063.25</v>
       </c>
       <c r="G25" s="3">
-        <v>83300.73</v>
+        <v>87224.69</v>
       </c>
       <c r="H25" s="3">
-        <v>146882.69</v>
+        <v>144340.85</v>
       </c>
       <c r="I25" s="3">
-        <v>230183.42</v>
+        <v>231565.54</v>
       </c>
       <c r="J25" s="3">
-        <v>23.75</v>
+        <v>23.9</v>
       </c>
       <c r="K25" s="3">
-        <v>-738879.83</v>
+        <v>-737497.71</v>
       </c>
       <c r="L25" s="3">
         <v>0.42</v>
@@ -87450,40 +90030,40 @@
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>9341</v>
+        <v>9628</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>9342</v>
+        <v>9629</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9343</v>
+        <v>9630</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9344</v>
+        <v>9631</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>9345</v>
+        <v>9632</v>
       </c>
       <c r="F26" s="3">
         <v>1050193.29</v>
       </c>
       <c r="G26" s="3">
-        <v>86555.82</v>
+        <v>90777.65</v>
       </c>
       <c r="H26" s="3">
-        <v>110041.49</v>
+        <v>101617.08</v>
       </c>
       <c r="I26" s="3">
-        <v>196597.31</v>
+        <v>192394.73</v>
       </c>
       <c r="J26" s="3">
-        <v>18.72</v>
+        <v>18.32</v>
       </c>
       <c r="K26" s="3">
-        <v>-853595.98</v>
+        <v>-857798.56</v>
       </c>
       <c r="L26" s="3">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="M26" s="3">
         <v>1235.86</v>
@@ -87491,40 +90071,40 @@
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>9346</v>
+        <v>9633</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>9347</v>
+        <v>9634</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9348</v>
+        <v>9635</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9349</v>
+        <v>9636</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>9350</v>
+        <v>9637</v>
       </c>
       <c r="F27" s="3">
         <v>919135.8</v>
       </c>
       <c r="G27" s="3">
-        <v>146781.8</v>
+        <v>153785.94</v>
       </c>
       <c r="H27" s="3">
-        <v>129239.25</v>
+        <v>126474.91</v>
       </c>
       <c r="I27" s="3">
-        <v>276021.05</v>
+        <v>280260.85</v>
       </c>
       <c r="J27" s="3">
-        <v>30.03</v>
+        <v>30.49</v>
       </c>
       <c r="K27" s="3">
-        <v>-643114.75</v>
+        <v>-638874.95</v>
       </c>
       <c r="L27" s="3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="M27" s="3">
         <v>2992.92</v>
@@ -87532,40 +90112,40 @@
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>9351</v>
+        <v>9638</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>9352</v>
+        <v>9639</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9353</v>
+        <v>9640</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>9354</v>
+        <v>9641</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>9355</v>
+        <v>9642</v>
       </c>
       <c r="F28" s="3">
         <v>1002913.88</v>
       </c>
       <c r="G28" s="3">
-        <v>145984.8</v>
+        <v>147322.65</v>
       </c>
       <c r="H28" s="3">
-        <v>102949.02</v>
+        <v>109519.74</v>
       </c>
       <c r="I28" s="3">
-        <v>248933.82</v>
+        <v>256842.39</v>
       </c>
       <c r="J28" s="3">
-        <v>24.82</v>
+        <v>25.61</v>
       </c>
       <c r="K28" s="3">
-        <v>-753980.06</v>
+        <v>-746071.49</v>
       </c>
       <c r="L28" s="3">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="M28" s="3">
         <v>568.13</v>
@@ -87573,40 +90153,40 @@
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>9356</v>
+        <v>9643</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>9357</v>
+        <v>9644</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9358</v>
+        <v>9645</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9359</v>
+        <v>9646</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>9360</v>
+        <v>9647</v>
       </c>
       <c r="F29" s="3">
         <v>872858.67</v>
       </c>
       <c r="G29" s="3">
-        <v>185535.97</v>
+        <v>208038.92</v>
       </c>
       <c r="H29" s="3">
-        <v>120283.87</v>
+        <v>126562.99</v>
       </c>
       <c r="I29" s="3">
-        <v>305819.84</v>
+        <v>334601.91</v>
       </c>
       <c r="J29" s="3">
-        <v>35.04</v>
+        <v>38.33</v>
       </c>
       <c r="K29" s="3">
-        <v>-567038.83</v>
+        <v>-538256.76</v>
       </c>
       <c r="L29" s="3">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="M29" s="3">
         <v>5477.76</v>
@@ -87614,40 +90194,40 @@
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>9361</v>
+        <v>9648</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>9362</v>
+        <v>9649</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9363</v>
+        <v>9650</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>9364</v>
+        <v>9651</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>9365</v>
+        <v>9652</v>
       </c>
       <c r="F30" s="3">
         <v>890266.15</v>
       </c>
       <c r="G30" s="3">
-        <v>190751.0</v>
+        <v>194270.77</v>
       </c>
       <c r="H30" s="3">
-        <v>118505.42</v>
+        <v>125357.29</v>
       </c>
       <c r="I30" s="3">
-        <v>309256.42</v>
+        <v>319628.06</v>
       </c>
       <c r="J30" s="3">
-        <v>34.74</v>
+        <v>35.9</v>
       </c>
       <c r="K30" s="3">
-        <v>-581009.73</v>
+        <v>-570638.09</v>
       </c>
       <c r="L30" s="3">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="M30" s="3">
         <v>5294.43</v>
@@ -87655,40 +90235,40 @@
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>9366</v>
+        <v>9653</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>9367</v>
+        <v>9654</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9368</v>
+        <v>9655</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9369</v>
+        <v>9656</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>9370</v>
+        <v>9657</v>
       </c>
       <c r="F31" s="3">
         <v>984099.44</v>
       </c>
       <c r="G31" s="3">
-        <v>179883.75</v>
+        <v>180438.01</v>
       </c>
       <c r="H31" s="3">
-        <v>112778.03</v>
+        <v>131907.34</v>
       </c>
       <c r="I31" s="3">
-        <v>292661.78</v>
+        <v>312345.35</v>
       </c>
       <c r="J31" s="3">
-        <v>29.74</v>
+        <v>31.74</v>
       </c>
       <c r="K31" s="3">
-        <v>-691437.66</v>
+        <v>-671754.09</v>
       </c>
       <c r="L31" s="3">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="M31" s="3">
         <v>2696.77</v>
@@ -87696,40 +90276,40 @@
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>9371</v>
+        <v>9658</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>9372</v>
+        <v>9659</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9373</v>
+        <v>9660</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>9374</v>
+        <v>9661</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>9375</v>
+        <v>9662</v>
       </c>
       <c r="F32" s="3">
         <v>926984.47</v>
       </c>
       <c r="G32" s="3">
-        <v>118803.16</v>
+        <v>120106.05</v>
       </c>
       <c r="H32" s="3">
-        <v>95501.12</v>
+        <v>104841.73</v>
       </c>
       <c r="I32" s="3">
-        <v>214304.28</v>
+        <v>224947.78</v>
       </c>
       <c r="J32" s="3">
-        <v>23.12</v>
+        <v>24.27</v>
       </c>
       <c r="K32" s="3">
-        <v>-712680.19</v>
+        <v>-702036.69</v>
       </c>
       <c r="L32" s="3">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="M32" s="3">
         <v>5512.72</v>
@@ -87737,19 +90317,19 @@
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>9376</v>
+        <v>9663</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>9377</v>
+        <v>9664</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9378</v>
+        <v>9665</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>9379</v>
+        <v>9666</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>9380</v>
+        <v>9667</v>
       </c>
       <c r="F33" s="3">
         <v>1288411.21</v>
@@ -87758,19 +90338,19 @@
         <v>156304.39</v>
       </c>
       <c r="H33" s="3">
-        <v>278445.95</v>
+        <v>401861.18</v>
       </c>
       <c r="I33" s="3">
-        <v>434750.34</v>
+        <v>558165.57</v>
       </c>
       <c r="J33" s="3">
-        <v>33.74</v>
+        <v>43.32</v>
       </c>
       <c r="K33" s="3">
-        <v>-853660.87</v>
+        <v>-730245.64</v>
       </c>
       <c r="L33" s="3">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="M33" s="3">
         <v>7033.78</v>
@@ -87778,19 +90358,19 @@
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>9381</v>
+        <v>9668</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>9382</v>
+        <v>9669</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9383</v>
+        <v>9670</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>9384</v>
+        <v>9671</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>9385</v>
+        <v>9672</v>
       </c>
       <c r="F34" s="3">
         <v>1074641.52</v>
@@ -87799,19 +90379,19 @@
         <v>113994.62</v>
       </c>
       <c r="H34" s="3">
-        <v>43873.15</v>
+        <v>146689.37</v>
       </c>
       <c r="I34" s="3">
-        <v>157867.77</v>
+        <v>260683.99</v>
       </c>
       <c r="J34" s="3">
-        <v>14.69</v>
+        <v>24.26</v>
       </c>
       <c r="K34" s="3">
-        <v>-916773.75</v>
+        <v>-813957.53</v>
       </c>
       <c r="L34" s="3">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M34" s="3">
         <v>3191.58</v>
@@ -87819,19 +90399,19 @@
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>9386</v>
+        <v>9673</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>9387</v>
+        <v>9674</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9388</v>
+        <v>9675</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>9389</v>
+        <v>9676</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>9390</v>
+        <v>9677</v>
       </c>
       <c r="F35" s="3">
         <v>1054434.17</v>
@@ -87840,19 +90420,19 @@
         <v>118884.48</v>
       </c>
       <c r="H35" s="3">
-        <v>83815.83</v>
+        <v>209727.62</v>
       </c>
       <c r="I35" s="3">
-        <v>202700.31</v>
+        <v>328612.1</v>
       </c>
       <c r="J35" s="3">
-        <v>19.22</v>
+        <v>31.16</v>
       </c>
       <c r="K35" s="3">
-        <v>-851733.86</v>
+        <v>-725822.07</v>
       </c>
       <c r="L35" s="3">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="M35" s="3">
         <v>3483.02</v>
@@ -87860,19 +90440,19 @@
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>9391</v>
+        <v>9678</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>9392</v>
+        <v>9679</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9393</v>
+        <v>9680</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>9394</v>
+        <v>9681</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>9395</v>
+        <v>9682</v>
       </c>
       <c r="F36" s="3">
         <v>1145461.66</v>
@@ -87881,19 +90461,19 @@
         <v>176420.95</v>
       </c>
       <c r="H36" s="3">
-        <v>320886.08</v>
+        <v>235703.92</v>
       </c>
       <c r="I36" s="3">
-        <v>497307.03</v>
+        <v>412124.87</v>
       </c>
       <c r="J36" s="3">
-        <v>43.42</v>
+        <v>35.98</v>
       </c>
       <c r="K36" s="3">
-        <v>-648154.63</v>
+        <v>-733336.79</v>
       </c>
       <c r="L36" s="3">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="M36" s="3">
         <v>1549.9</v>
@@ -87901,19 +90481,19 @@
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>9396</v>
+        <v>9683</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>9397</v>
+        <v>9684</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9398</v>
+        <v>9685</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>9399</v>
+        <v>9686</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>9400</v>
+        <v>9687</v>
       </c>
       <c r="F37" s="3">
         <v>1392111.83</v>
@@ -87922,19 +90502,19 @@
         <v>193545.7</v>
       </c>
       <c r="H37" s="3">
-        <v>340613.62</v>
+        <v>244557.22</v>
       </c>
       <c r="I37" s="3">
-        <v>534159.32</v>
+        <v>438102.92</v>
       </c>
       <c r="J37" s="3">
-        <v>38.37</v>
+        <v>31.47</v>
       </c>
       <c r="K37" s="3">
-        <v>-857952.51</v>
+        <v>-954008.91</v>
       </c>
       <c r="L37" s="3">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="M37" s="3">
         <v>5742.04</v>
@@ -87942,19 +90522,19 @@
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>9401</v>
+        <v>9688</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>9402</v>
+        <v>9689</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9403</v>
+        <v>9690</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>9404</v>
+        <v>9691</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>9405</v>
+        <v>9692</v>
       </c>
       <c r="F38" s="3">
         <v>958935.26</v>
@@ -87963,19 +90543,19 @@
         <v>156601.17</v>
       </c>
       <c r="H38" s="3">
-        <v>230606.57</v>
+        <v>170530.23</v>
       </c>
       <c r="I38" s="3">
-        <v>387207.74</v>
+        <v>327131.4</v>
       </c>
       <c r="J38" s="3">
-        <v>40.38</v>
+        <v>34.11</v>
       </c>
       <c r="K38" s="3">
-        <v>-571727.52</v>
+        <v>-631803.86</v>
       </c>
       <c r="L38" s="3">
-        <v>2.63</v>
+        <v>3.11</v>
       </c>
       <c r="M38" s="3">
         <v>10184.28</v>
@@ -87983,19 +90563,19 @@
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>9406</v>
+        <v>9693</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>9407</v>
+        <v>9694</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9408</v>
+        <v>9695</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>9409</v>
+        <v>9696</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>9410</v>
+        <v>9697</v>
       </c>
       <c r="F39" s="3">
         <v>1141876.38</v>
@@ -88004,19 +90584,19 @@
         <v>138311.37</v>
       </c>
       <c r="H39" s="3">
-        <v>226894.68</v>
+        <v>171498.65</v>
       </c>
       <c r="I39" s="3">
-        <v>365206.05</v>
+        <v>309810.02</v>
       </c>
       <c r="J39" s="3">
-        <v>31.98</v>
+        <v>27.13</v>
       </c>
       <c r="K39" s="3">
-        <v>-776670.33</v>
+        <v>-832066.36</v>
       </c>
       <c r="L39" s="3">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="M39" s="3">
         <v>2680.54</v>
@@ -88024,69 +90604,69 @@
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>9411</v>
+        <v>9698</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>9412</v>
+        <v>9699</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9413</v>
+        <v>9700</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>9414</v>
+        <v>9701</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>9415</v>
+        <v>9702</v>
       </c>
       <c r="F40" s="3">
         <v>936014.91</v>
       </c>
       <c r="G40" s="3">
-        <v>93162.12</v>
+        <v>110831.18</v>
       </c>
       <c r="H40" s="3">
-        <v>159701.24</v>
+        <v>141379.3</v>
       </c>
       <c r="I40" s="3">
-        <v>252863.36</v>
+        <v>252210.48</v>
       </c>
       <c r="J40" s="3">
-        <v>27.01</v>
+        <v>26.95</v>
       </c>
       <c r="K40" s="3">
-        <v>-683151.55</v>
+        <v>-683804.43</v>
       </c>
       <c r="L40" s="3">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="M40" s="3">
-        <v>1839.64</v>
+        <v>2492.52</v>
       </c>
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>9416</v>
+        <v>9703</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>9417</v>
+        <v>9704</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9418</v>
+        <v>9705</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>9419</v>
+        <v>9706</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>9420</v>
+        <v>9707</v>
       </c>
       <c r="F41" s="3">
         <v>1227064.36</v>
       </c>
       <c r="G41" s="3">
-        <v>123930.86</v>
+        <v>131488.88</v>
       </c>
       <c r="H41" s="3">
-        <v>212412.03</v>
+        <v>204854.01</v>
       </c>
       <c r="I41" s="3">
         <v>336342.89</v>
@@ -88106,28 +90686,28 @@
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>9421</v>
+        <v>9708</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>9422</v>
+        <v>9709</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9423</v>
+        <v>9710</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>9424</v>
+        <v>9711</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>9425</v>
+        <v>9712</v>
       </c>
       <c r="F42" s="3">
         <v>940955.58</v>
       </c>
       <c r="G42" s="3">
-        <v>115591.01</v>
+        <v>120584.39</v>
       </c>
       <c r="H42" s="3">
-        <v>225097.31</v>
+        <v>220103.93</v>
       </c>
       <c r="I42" s="3">
         <v>340688.32</v>
@@ -88147,28 +90727,28 @@
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>9426</v>
+        <v>9713</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>9427</v>
+        <v>9714</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9428</v>
+        <v>9715</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9429</v>
+        <v>9716</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>9430</v>
+        <v>9717</v>
       </c>
       <c r="F43" s="3">
         <v>1062667.74</v>
       </c>
       <c r="G43" s="3">
-        <v>152361.5</v>
+        <v>162301.94</v>
       </c>
       <c r="H43" s="3">
-        <v>270816.77</v>
+        <v>260876.33</v>
       </c>
       <c r="I43" s="3">
         <v>423178.27</v>
@@ -88188,19 +90768,19 @@
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>9431</v>
+        <v>9718</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>9432</v>
+        <v>9719</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9433</v>
+        <v>9720</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>9434</v>
+        <v>9721</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>9435</v>
+        <v>9722</v>
       </c>
       <c r="F44" s="3">
         <v>1129524.64</v>
@@ -88209,19 +90789,19 @@
         <v>167781.87</v>
       </c>
       <c r="H44" s="3">
-        <v>36698.11</v>
+        <v>146963.98</v>
       </c>
       <c r="I44" s="3">
-        <v>204479.98</v>
+        <v>314745.85</v>
       </c>
       <c r="J44" s="3">
-        <v>18.1</v>
+        <v>27.87</v>
       </c>
       <c r="K44" s="3">
-        <v>-925044.66</v>
+        <v>-814778.79</v>
       </c>
       <c r="L44" s="3">
-        <v>0.76</v>
+        <v>0.49</v>
       </c>
       <c r="M44" s="3">
         <v>1544.8</v>
@@ -88229,19 +90809,19 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>9436</v>
+        <v>9723</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>9437</v>
+        <v>9724</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9438</v>
+        <v>9725</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>9439</v>
+        <v>9726</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>9440</v>
+        <v>9727</v>
       </c>
       <c r="F45" s="3">
         <v>931654.84</v>
@@ -88250,19 +90830,19 @@
         <v>180278.21</v>
       </c>
       <c r="H45" s="3">
-        <v>38026.85</v>
+        <v>133808.49</v>
       </c>
       <c r="I45" s="3">
-        <v>218305.06</v>
+        <v>314086.7</v>
       </c>
       <c r="J45" s="3">
-        <v>23.43</v>
+        <v>33.71</v>
       </c>
       <c r="K45" s="3">
-        <v>-713349.78</v>
+        <v>-617568.14</v>
       </c>
       <c r="L45" s="3">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="M45" s="3">
         <v>929.53</v>
@@ -88270,19 +90850,19 @@
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>9441</v>
+        <v>9728</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>9442</v>
+        <v>9729</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9443</v>
+        <v>9730</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>9444</v>
+        <v>9731</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>9445</v>
+        <v>9732</v>
       </c>
       <c r="F46" s="3">
         <v>1096879.63</v>
@@ -88291,19 +90871,19 @@
         <v>198485.41</v>
       </c>
       <c r="H46" s="3">
-        <v>33436.5</v>
+        <v>121591.15</v>
       </c>
       <c r="I46" s="3">
-        <v>231921.91</v>
+        <v>320076.56</v>
       </c>
       <c r="J46" s="3">
-        <v>21.14</v>
+        <v>29.18</v>
       </c>
       <c r="K46" s="3">
-        <v>-864957.72</v>
+        <v>-776803.07</v>
       </c>
       <c r="L46" s="3">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="M46" s="3">
         <v>3504.73</v>
@@ -88311,19 +90891,19 @@
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>9446</v>
+        <v>9733</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>9447</v>
+        <v>9734</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9448</v>
+        <v>9735</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>9449</v>
+        <v>9736</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>9450</v>
+        <v>9737</v>
       </c>
       <c r="F47" s="3">
         <v>1362950.73</v>
@@ -88332,19 +90912,19 @@
         <v>132758.57</v>
       </c>
       <c r="H47" s="3">
-        <v>238768.78</v>
+        <v>316062.44</v>
       </c>
       <c r="I47" s="3">
-        <v>371527.35</v>
+        <v>448821.01</v>
       </c>
       <c r="J47" s="3">
-        <v>27.26</v>
+        <v>32.93</v>
       </c>
       <c r="K47" s="3">
-        <v>-991423.38</v>
+        <v>-914129.72</v>
       </c>
       <c r="L47" s="3">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="M47" s="3">
         <v>4903.0</v>
@@ -88352,19 +90932,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>9451</v>
+        <v>9738</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>9452</v>
+        <v>9739</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9453</v>
+        <v>9740</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>9454</v>
+        <v>9741</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>9455</v>
+        <v>9742</v>
       </c>
       <c r="F48" s="3">
         <v>1050721.66</v>
@@ -88373,19 +90953,19 @@
         <v>92522.65</v>
       </c>
       <c r="H48" s="3">
-        <v>117566.05</v>
+        <v>172431.53</v>
       </c>
       <c r="I48" s="3">
-        <v>210088.7</v>
+        <v>264954.18</v>
       </c>
       <c r="J48" s="3">
-        <v>19.99</v>
+        <v>25.22</v>
       </c>
       <c r="K48" s="3">
-        <v>-840632.96</v>
+        <v>-785767.48</v>
       </c>
       <c r="L48" s="3">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="M48" s="3">
         <v>3426.88</v>
@@ -88393,19 +90973,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>9456</v>
+        <v>9743</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>9457</v>
+        <v>9744</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9458</v>
+        <v>9745</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9459</v>
+        <v>9746</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>9460</v>
+        <v>9747</v>
       </c>
       <c r="F49" s="3">
         <v>989655.83</v>
@@ -88414,19 +90994,19 @@
         <v>136143.76</v>
       </c>
       <c r="H49" s="3">
-        <v>145616.13</v>
+        <v>211972.59</v>
       </c>
       <c r="I49" s="3">
-        <v>281759.89</v>
+        <v>348116.35</v>
       </c>
       <c r="J49" s="3">
-        <v>28.47</v>
+        <v>35.18</v>
       </c>
       <c r="K49" s="3">
-        <v>-707895.94</v>
+        <v>-641539.48</v>
       </c>
       <c r="L49" s="3">
-        <v>1.11</v>
+        <v>0.9</v>
       </c>
       <c r="M49" s="3">
         <v>3140.24</v>
@@ -88434,19 +91014,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>9461</v>
+        <v>9748</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>9462</v>
+        <v>9749</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9463</v>
+        <v>9750</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>9464</v>
+        <v>9751</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>9465</v>
+        <v>9752</v>
       </c>
       <c r="F50" s="3">
         <v>978747.3</v>
@@ -88455,19 +91035,19 @@
         <v>163099.85</v>
       </c>
       <c r="H50" s="3">
-        <v>152179.35</v>
+        <v>212309.48</v>
       </c>
       <c r="I50" s="3">
-        <v>315279.2</v>
+        <v>375409.33</v>
       </c>
       <c r="J50" s="3">
-        <v>32.21</v>
+        <v>38.36</v>
       </c>
       <c r="K50" s="3">
-        <v>-663468.1</v>
+        <v>-603337.97</v>
       </c>
       <c r="L50" s="3">
-        <v>5.47</v>
+        <v>4.6</v>
       </c>
       <c r="M50" s="3">
         <v>17258.28</v>
@@ -88475,19 +91055,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>9466</v>
+        <v>9753</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>9467</v>
+        <v>9754</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9468</v>
+        <v>9755</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>9469</v>
+        <v>9756</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>9470</v>
+        <v>9757</v>
       </c>
       <c r="F51" s="3">
         <v>983156.92</v>
@@ -88496,19 +91076,19 @@
         <v>79232.18</v>
       </c>
       <c r="H51" s="3">
-        <v>95835.22</v>
+        <v>144866.99</v>
       </c>
       <c r="I51" s="3">
-        <v>175067.4</v>
+        <v>224099.17</v>
       </c>
       <c r="J51" s="3">
-        <v>17.81</v>
+        <v>22.79</v>
       </c>
       <c r="K51" s="3">
-        <v>-808089.52</v>
+        <v>-759057.75</v>
       </c>
       <c r="L51" s="3">
-        <v>3.03</v>
+        <v>2.37</v>
       </c>
       <c r="M51" s="3">
         <v>5312.13</v>
@@ -88516,19 +91096,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>9471</v>
+        <v>9758</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>9472</v>
+        <v>9759</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9473</v>
+        <v>9760</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>9474</v>
+        <v>9761</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>9475</v>
+        <v>9762</v>
       </c>
       <c r="F52" s="3">
         <v>1178421.11</v>
@@ -88537,19 +91117,19 @@
         <v>142341.85</v>
       </c>
       <c r="H52" s="3">
-        <v>124558.5</v>
+        <v>186353.58</v>
       </c>
       <c r="I52" s="3">
-        <v>266900.35</v>
+        <v>328695.43</v>
       </c>
       <c r="J52" s="3">
-        <v>22.65</v>
+        <v>27.89</v>
       </c>
       <c r="K52" s="3">
-        <v>-911520.76</v>
+        <v>-849725.68</v>
       </c>
       <c r="L52" s="3">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="M52" s="3">
         <v>5710.6</v>
@@ -95032,7 +97612,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ49"/>
+  <dimension ref="A1:AS49"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -95082,206 +97662,206 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="14" t="s">
-        <v>9476</v>
+        <v>9763</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>9477</v>
+        <v>9764</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>9478</v>
+        <v>9765</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>9479</v>
+        <v>9766</v>
       </c>
       <c r="E2" s="15">
         <v>6104317.5</v>
       </c>
       <c r="F2" s="15">
-        <v>767574.91</v>
+        <v>799719.03</v>
       </c>
       <c r="G2" s="15">
-        <v>1567617.65</v>
+        <v>1583807.27</v>
       </c>
       <c r="H2" s="15">
-        <v>2335192.56</v>
+        <v>2383526.3</v>
       </c>
       <c r="I2" s="15">
-        <v>38.25</v>
+        <v>39.05</v>
       </c>
       <c r="J2" s="15">
-        <v>-3769124.94</v>
+        <v>-3720791.2</v>
       </c>
       <c r="K2" s="15">
         <v>20109.24</v>
       </c>
       <c r="L2" s="15">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="14" t="s">
-        <v>9480</v>
+        <v>9767</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>9481</v>
+        <v>9768</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>9482</v>
+        <v>9769</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>9483</v>
+        <v>9770</v>
       </c>
       <c r="E3" s="15">
         <v>3440798.37</v>
       </c>
       <c r="F3" s="15">
-        <v>326668.61</v>
+        <v>330364.89</v>
       </c>
       <c r="G3" s="15">
-        <v>850165.02</v>
+        <v>908324.13</v>
       </c>
       <c r="H3" s="15">
-        <v>1176833.63</v>
+        <v>1238689.02</v>
       </c>
       <c r="I3" s="15">
-        <v>34.2</v>
+        <v>36.0</v>
       </c>
       <c r="J3" s="15">
-        <v>-2263964.74</v>
+        <v>-2202109.35</v>
       </c>
       <c r="K3" s="15">
-        <v>12247.18</v>
+        <v>13191.28</v>
       </c>
       <c r="L3" s="15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="14" t="s">
-        <v>9484</v>
+        <v>9771</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>9485</v>
+        <v>9772</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>9486</v>
+        <v>9773</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>9487</v>
+        <v>9774</v>
       </c>
       <c r="E4" s="15">
         <v>6398516.07</v>
       </c>
       <c r="F4" s="15">
-        <v>596420.54</v>
+        <v>731629.49</v>
       </c>
       <c r="G4" s="15">
-        <v>1131097.23</v>
+        <v>938467.32</v>
       </c>
       <c r="H4" s="15">
-        <v>1727517.77</v>
+        <v>1670096.81</v>
       </c>
       <c r="I4" s="15">
-        <v>27.0</v>
+        <v>26.1</v>
       </c>
       <c r="J4" s="15">
-        <v>-4670998.3</v>
+        <v>-4728419.26</v>
       </c>
       <c r="K4" s="15">
-        <v>10575.45</v>
+        <v>13944.29</v>
       </c>
       <c r="L4" s="15">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="14" t="s">
-        <v>9488</v>
+        <v>9775</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>9489</v>
+        <v>9776</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>9490</v>
+        <v>9777</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>9491</v>
+        <v>9778</v>
       </c>
       <c r="E5" s="15">
         <v>7403170.5</v>
       </c>
       <c r="F5" s="15">
-        <v>1134285.31</v>
+        <v>1157900.26</v>
       </c>
       <c r="G5" s="15">
-        <v>996517.89</v>
+        <v>1095515.36</v>
       </c>
       <c r="H5" s="15">
-        <v>2130803.2</v>
+        <v>2253415.62</v>
       </c>
       <c r="I5" s="15">
-        <v>28.78</v>
+        <v>30.44</v>
       </c>
       <c r="J5" s="15">
-        <v>-5272367.3</v>
+        <v>-5149754.88</v>
       </c>
       <c r="K5" s="15">
         <v>28898.37</v>
       </c>
       <c r="L5" s="15">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="14" t="s">
-        <v>9492</v>
+        <v>9779</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>9493</v>
+        <v>9780</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>9494</v>
+        <v>9781</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>9495</v>
+        <v>9782</v>
       </c>
       <c r="E6" s="15">
         <v>7091695.63</v>
       </c>
       <c r="F6" s="15">
-        <v>1064363.52</v>
+        <v>1092037.24</v>
       </c>
       <c r="G6" s="15">
-        <v>853203.36</v>
+        <v>1246947.51</v>
       </c>
       <c r="H6" s="15">
-        <v>1917566.88</v>
+        <v>2338984.75</v>
       </c>
       <c r="I6" s="15">
-        <v>27.04</v>
+        <v>32.98</v>
       </c>
       <c r="J6" s="15">
-        <v>-5174128.75</v>
+        <v>-4752710.88</v>
       </c>
       <c r="K6" s="15">
         <v>32690.06</v>
       </c>
       <c r="L6" s="15">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="14" t="s">
-        <v>9496</v>
+        <v>9783</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>9497</v>
+        <v>9784</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>9498</v>
+        <v>9785</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>9499</v>
+        <v>9786</v>
       </c>
       <c r="E7" s="15">
         <v>4638385.13</v>
@@ -95290,74 +97870,74 @@
         <v>664879.19</v>
       </c>
       <c r="G7" s="15">
-        <v>1119000.95</v>
+        <v>822290.02</v>
       </c>
       <c r="H7" s="15">
-        <v>1783880.14</v>
+        <v>1487169.21</v>
       </c>
       <c r="I7" s="15">
-        <v>38.46</v>
+        <v>32.06</v>
       </c>
       <c r="J7" s="15">
-        <v>-2854504.99</v>
+        <v>-3151215.92</v>
       </c>
       <c r="K7" s="15">
         <v>20156.76</v>
       </c>
       <c r="L7" s="15">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="14" t="s">
-        <v>9500</v>
+        <v>9787</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>9501</v>
+        <v>9788</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>9502</v>
+        <v>9789</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>9503</v>
+        <v>9790</v>
       </c>
       <c r="E8" s="15">
         <v>7324761.7</v>
       </c>
       <c r="F8" s="15">
-        <v>1031590.98</v>
+        <v>1071751.88</v>
       </c>
       <c r="G8" s="15">
-        <v>976188.81</v>
+        <v>1229577.19</v>
       </c>
       <c r="H8" s="15">
-        <v>2007779.79</v>
+        <v>2301329.07</v>
       </c>
       <c r="I8" s="15">
-        <v>27.41</v>
+        <v>31.42</v>
       </c>
       <c r="J8" s="15">
-        <v>-5316981.91</v>
+        <v>-5023432.63</v>
       </c>
       <c r="K8" s="15">
-        <v>21853.72</v>
+        <v>22506.6</v>
       </c>
       <c r="L8" s="15">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="14" t="s">
-        <v>9504</v>
+        <v>9791</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>9505</v>
+        <v>9792</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>9506</v>
+        <v>9793</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>9507</v>
+        <v>9794</v>
       </c>
       <c r="E9" s="15">
         <v>6543653.55</v>
@@ -95366,22 +97946,22 @@
         <v>746098.86</v>
       </c>
       <c r="G9" s="15">
-        <v>874524.03</v>
+        <v>1243996.61</v>
       </c>
       <c r="H9" s="15">
-        <v>1620622.89</v>
+        <v>1990095.47</v>
       </c>
       <c r="I9" s="15">
-        <v>24.77</v>
+        <v>30.41</v>
       </c>
       <c r="J9" s="15">
-        <v>-4923030.66</v>
+        <v>-4553558.08</v>
       </c>
       <c r="K9" s="15">
         <v>39751.13</v>
       </c>
       <c r="L9" s="15">
-        <v>2.45</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="13" spans="8:8">
@@ -96489,7 +99069,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK78"/>
+  <dimension ref="A1:AM78"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="9" max="9" customWidth="1" width="5.8984375" style="0"/>
@@ -96568,13 +99148,13 @@
         <v>3791</v>
       </c>
       <c r="F3" s="24">
-        <v>2966.0</v>
+        <v>2519.0</v>
       </c>
       <c r="G3" s="24">
-        <v>273.0</v>
+        <v>277.0</v>
       </c>
       <c r="H3" s="25">
-        <v>0.09204315576534053</v>
+        <v>0.10996427153632393</v>
       </c>
       <c r="J3" s="26">
         <v>10812.0</v>
@@ -96595,7 +99175,7 @@
         <v>0.09204832311575911</v>
       </c>
     </row>
-    <row r="4" spans="8:8" ht="24.85">
+    <row r="4" spans="8:8" ht="16.25">
       <c r="A4" s="22" t="s">
         <v>3792</v>
       </c>
@@ -96612,13 +99192,13 @@
         <v>3796</v>
       </c>
       <c r="F4" s="24">
-        <v>698.0</v>
+        <v>926.0</v>
       </c>
       <c r="G4" s="24">
-        <v>45.0</v>
+        <v>93.0</v>
       </c>
       <c r="H4" s="25">
-        <v>0.06446991404011461</v>
+        <v>0.10043196544276457</v>
       </c>
       <c r="J4" s="26">
         <v>3158.0</v>
@@ -96656,13 +99236,13 @@
         <v>3801</v>
       </c>
       <c r="F5" s="24">
-        <v>56.0</v>
+        <v>70.0</v>
       </c>
       <c r="G5" s="24">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H5" s="25">
-        <v>0.017857142857142856</v>
+        <v>0.11428571428571428</v>
       </c>
       <c r="J5" s="26">
         <v>640.0</v>
@@ -96700,13 +99280,13 @@
         <v>3806</v>
       </c>
       <c r="F6" s="24">
-        <v>11.75</v>
+        <v>13.25</v>
       </c>
       <c r="G6" s="24">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H6" s="25">
-        <v>0.0</v>
+        <v>0.22641509433962265</v>
       </c>
       <c r="J6" s="26">
         <v>153.75</v>
@@ -96744,13 +99324,13 @@
         <v>3811</v>
       </c>
       <c r="F7" s="24">
-        <v>10.75</v>
+        <v>13.25</v>
       </c>
       <c r="G7" s="24">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H7" s="25">
-        <v>0.09302325581395349</v>
+        <v>0.22641509433962265</v>
       </c>
       <c r="J7" s="26">
         <v>98.25</v>
@@ -96788,7 +99368,7 @@
         <v>3816</v>
       </c>
       <c r="F8" s="24">
-        <v>12.75</v>
+        <v>17.25</v>
       </c>
       <c r="G8" s="24">
         <v>0.0</v>
@@ -96832,13 +99412,13 @@
         <v>3821</v>
       </c>
       <c r="F9" s="24">
-        <v>20.75</v>
+        <v>26.25</v>
       </c>
       <c r="G9" s="24">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H9" s="25">
-        <v>0.0</v>
+        <v>0.0761904761904762</v>
       </c>
       <c r="J9" s="26">
         <v>238.25</v>
@@ -96876,13 +99456,13 @@
         <v>3826</v>
       </c>
       <c r="F10" s="24">
-        <v>642.0</v>
+        <v>856.0</v>
       </c>
       <c r="G10" s="24">
-        <v>44.0</v>
+        <v>85.0</v>
       </c>
       <c r="H10" s="25">
-        <v>0.06853582554517133</v>
+        <v>0.09929906542056074</v>
       </c>
       <c r="J10" s="26">
         <v>2518.0</v>
@@ -96920,13 +99500,13 @@
         <v>3831</v>
       </c>
       <c r="F11" s="24">
-        <v>182.5</v>
+        <v>255.75</v>
       </c>
       <c r="G11" s="24">
-        <v>16.0</v>
+        <v>38.0</v>
       </c>
       <c r="H11" s="25">
-        <v>0.08767123287671233</v>
+        <v>0.14858260019550343</v>
       </c>
       <c r="J11" s="26">
         <v>727.5</v>
@@ -96964,13 +99544,13 @@
         <v>3836</v>
       </c>
       <c r="F12" s="24">
-        <v>95.5</v>
+        <v>141.75</v>
       </c>
       <c r="G12" s="24">
-        <v>10.0</v>
+        <v>19.0</v>
       </c>
       <c r="H12" s="25">
-        <v>0.10471204188481675</v>
+        <v>0.13403880070546736</v>
       </c>
       <c r="J12" s="26">
         <v>362.5</v>
@@ -97008,13 +99588,13 @@
         <v>3841</v>
       </c>
       <c r="F13" s="24">
-        <v>139.0</v>
+        <v>174.25</v>
       </c>
       <c r="G13" s="24">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="H13" s="25">
-        <v>0.03597122302158273</v>
+        <v>0.040172166427546625</v>
       </c>
       <c r="J13" s="26">
         <v>602.0</v>
@@ -97052,13 +99632,13 @@
         <v>3846</v>
       </c>
       <c r="F14" s="24">
-        <v>225.0</v>
+        <v>284.25</v>
       </c>
       <c r="G14" s="24">
-        <v>13.0</v>
+        <v>21.0</v>
       </c>
       <c r="H14" s="25">
-        <v>0.057777777777777775</v>
+        <v>0.07387862796833773</v>
       </c>
       <c r="J14" s="26">
         <v>826.0</v>
@@ -97096,13 +99676,13 @@
         <v>3851</v>
       </c>
       <c r="F15" s="24">
-        <v>301.0</v>
+        <v>155.0</v>
       </c>
       <c r="G15" s="24">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="H15" s="25">
-        <v>0.05647840531561462</v>
+        <v>0.05806451612903226</v>
       </c>
       <c r="J15" s="26">
         <v>1008.0</v>
@@ -97140,13 +99720,13 @@
         <v>3856</v>
       </c>
       <c r="F16" s="24">
-        <v>301.0</v>
+        <v>155.0</v>
       </c>
       <c r="G16" s="24">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="H16" s="25">
-        <v>0.05647840531561462</v>
+        <v>0.05806451612903226</v>
       </c>
       <c r="J16" s="26">
         <v>1008.0</v>
@@ -97184,13 +99764,13 @@
         <v>3861</v>
       </c>
       <c r="F17" s="24">
-        <v>84.75</v>
+        <v>41.5</v>
       </c>
       <c r="G17" s="24">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H17" s="25">
-        <v>0.02359882005899705</v>
+        <v>0.0963855421686747</v>
       </c>
       <c r="J17" s="26">
         <v>265.5</v>
@@ -97228,13 +99808,13 @@
         <v>3866</v>
       </c>
       <c r="F18" s="24">
-        <v>50.25</v>
+        <v>25.0</v>
       </c>
       <c r="G18" s="24">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H18" s="25">
-        <v>0.13930348258706468</v>
+        <v>0.12</v>
       </c>
       <c r="J18" s="26">
         <v>162.5</v>
@@ -97272,13 +99852,13 @@
         <v>3871</v>
       </c>
       <c r="F19" s="24">
-        <v>68.25</v>
+        <v>30.0</v>
       </c>
       <c r="G19" s="24">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H19" s="25">
-        <v>0.08791208791208792</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="J19" s="26">
         <v>212.0</v>
@@ -97316,13 +99896,13 @@
         <v>3876</v>
       </c>
       <c r="F20" s="24">
-        <v>97.75</v>
+        <v>58.5</v>
       </c>
       <c r="G20" s="24">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H20" s="25">
-        <v>0.020460358056265986</v>
+        <v>0.017094017094017096</v>
       </c>
       <c r="J20" s="26">
         <v>368.0</v>
@@ -97360,13 +99940,13 @@
         <v>3881</v>
       </c>
       <c r="F21" s="24">
-        <v>73.0</v>
+        <v>30.0</v>
       </c>
       <c r="G21" s="24">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="H21" s="25">
-        <v>0.0684931506849315</v>
+        <v>0.1</v>
       </c>
       <c r="J21" s="26">
         <v>495.0</v>
@@ -97404,13 +99984,13 @@
         <v>3886</v>
       </c>
       <c r="F22" s="24">
-        <v>73.0</v>
+        <v>30.0</v>
       </c>
       <c r="G22" s="24">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="H22" s="25">
-        <v>0.0684931506849315</v>
+        <v>0.1</v>
       </c>
       <c r="J22" s="26">
         <v>495.0</v>
@@ -97448,13 +100028,13 @@
         <v>3891</v>
       </c>
       <c r="F23" s="24">
-        <v>17.5</v>
+        <v>8.5</v>
       </c>
       <c r="G23" s="24">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H23" s="25">
-        <v>0.11428571428571428</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="J23" s="26">
         <v>140.5</v>
@@ -97492,7 +100072,7 @@
         <v>3896</v>
       </c>
       <c r="F24" s="24">
-        <v>14.0</v>
+        <v>7.5</v>
       </c>
       <c r="G24" s="24">
         <v>0.0</v>
@@ -97536,13 +100116,13 @@
         <v>3901</v>
       </c>
       <c r="F25" s="24">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="G25" s="24">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H25" s="25">
-        <v>0.17391304347826086</v>
+        <v>0.0</v>
       </c>
       <c r="J25" s="26">
         <v>101.0</v>
@@ -97580,13 +100160,13 @@
         <v>3906</v>
       </c>
       <c r="F26" s="24">
-        <v>30.0</v>
+        <v>9.5</v>
       </c>
       <c r="G26" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" s="25">
-        <v>0.03333333333333333</v>
+        <v>0.0</v>
       </c>
       <c r="J26" s="26">
         <v>166.0</v>
@@ -97800,13 +100380,13 @@
         <v>3931</v>
       </c>
       <c r="F31" s="24">
-        <v>513.0</v>
+        <v>209.0</v>
       </c>
       <c r="G31" s="24">
-        <v>49.0</v>
+        <v>31.0</v>
       </c>
       <c r="H31" s="25">
-        <v>0.09551656920077972</v>
+        <v>0.14832535885167464</v>
       </c>
       <c r="J31" s="26">
         <v>2095.0</v>
@@ -97844,13 +100424,13 @@
         <v>3936</v>
       </c>
       <c r="F32" s="24">
-        <v>396.0</v>
+        <v>168.0</v>
       </c>
       <c r="G32" s="24">
-        <v>43.0</v>
+        <v>25.0</v>
       </c>
       <c r="H32" s="25">
-        <v>0.10858585858585859</v>
+        <v>0.1488095238095238</v>
       </c>
       <c r="J32" s="26">
         <v>1549.0</v>
@@ -97888,13 +100468,13 @@
         <v>3941</v>
       </c>
       <c r="F33" s="24">
-        <v>116.25</v>
+        <v>44.75</v>
       </c>
       <c r="G33" s="24">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H33" s="25">
-        <v>0.08602150537634409</v>
+        <v>0.1340782122905028</v>
       </c>
       <c r="J33" s="26">
         <v>430.75</v>
@@ -97932,13 +100512,13 @@
         <v>3946</v>
       </c>
       <c r="F34" s="24">
-        <v>55.75</v>
+        <v>32.75</v>
       </c>
       <c r="G34" s="24">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H34" s="25">
-        <v>0.17937219730941703</v>
+        <v>0.24427480916030533</v>
       </c>
       <c r="J34" s="26">
         <v>243.25</v>
@@ -97976,13 +100556,13 @@
         <v>3951</v>
       </c>
       <c r="F35" s="24">
-        <v>90.25</v>
+        <v>28.75</v>
       </c>
       <c r="G35" s="24">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H35" s="25">
-        <v>0.07756232686980609</v>
+        <v>0.06956521739130435</v>
       </c>
       <c r="J35" s="26">
         <v>356.25</v>
@@ -98020,13 +100600,13 @@
         <v>3956</v>
       </c>
       <c r="F36" s="24">
-        <v>133.75</v>
+        <v>61.75</v>
       </c>
       <c r="G36" s="24">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="H36" s="25">
-        <v>0.11962616822429907</v>
+        <v>0.145748987854251</v>
       </c>
       <c r="J36" s="26">
         <v>518.75</v>
@@ -98064,13 +100644,13 @@
         <v>3961</v>
       </c>
       <c r="F37" s="24">
-        <v>117.0</v>
+        <v>41.0</v>
       </c>
       <c r="G37" s="24">
         <v>6.0</v>
       </c>
       <c r="H37" s="25">
-        <v>0.05128205128205128</v>
+        <v>0.14634146341463414</v>
       </c>
       <c r="J37" s="26">
         <v>546.0</v>
@@ -98108,13 +100688,13 @@
         <v>3966</v>
       </c>
       <c r="F38" s="24">
-        <v>26.25</v>
+        <v>11.5</v>
       </c>
       <c r="G38" s="24">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H38" s="25">
-        <v>0.0380952380952381</v>
+        <v>0.17391304347826086</v>
       </c>
       <c r="J38" s="26">
         <v>143.25</v>
@@ -98152,13 +100732,13 @@
         <v>3971</v>
       </c>
       <c r="F39" s="24">
-        <v>14.25</v>
+        <v>3.5</v>
       </c>
       <c r="G39" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H39" s="25">
-        <v>0.07017543859649122</v>
+        <v>0.0</v>
       </c>
       <c r="J39" s="26">
         <v>81.25</v>
@@ -98196,13 +100776,13 @@
         <v>3976</v>
       </c>
       <c r="F40" s="24">
-        <v>28.25</v>
+        <v>9.5</v>
       </c>
       <c r="G40" s="24">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H40" s="25">
-        <v>0.07079646017699115</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="J40" s="26">
         <v>117.25</v>
@@ -98240,13 +100820,13 @@
         <v>3981</v>
       </c>
       <c r="F41" s="24">
-        <v>48.25</v>
+        <v>16.5</v>
       </c>
       <c r="G41" s="24">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H41" s="25">
-        <v>0.04145077720207254</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="J41" s="26">
         <v>204.25</v>
@@ -98284,13 +100864,13 @@
         <v>3986</v>
       </c>
       <c r="F42" s="24">
-        <v>403.0</v>
+        <v>122.0</v>
       </c>
       <c r="G42" s="24">
-        <v>50.0</v>
+        <v>8.0</v>
       </c>
       <c r="H42" s="25">
-        <v>0.12406947890818859</v>
+        <v>0.06557377049180328</v>
       </c>
       <c r="J42" s="26">
         <v>1468.0</v>
@@ -98328,13 +100908,13 @@
         <v>3991</v>
       </c>
       <c r="F43" s="24">
-        <v>85.0</v>
+        <v>73.0</v>
       </c>
       <c r="G43" s="24">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="H43" s="25">
-        <v>0.1411764705882353</v>
+        <v>0.0821917808219178</v>
       </c>
       <c r="J43" s="26">
         <v>861.0</v>
@@ -98372,13 +100952,13 @@
         <v>3996</v>
       </c>
       <c r="F44" s="24">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
       <c r="G44" s="24">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H44" s="25">
-        <v>0.11764705882352941</v>
+        <v>0.044444444444444446</v>
       </c>
       <c r="J44" s="26">
         <v>210.0</v>
@@ -98416,13 +100996,13 @@
         <v>4001</v>
       </c>
       <c r="F45" s="24">
-        <v>10.0</v>
+        <v>10.5</v>
       </c>
       <c r="G45" s="24">
         <v>4.0</v>
       </c>
       <c r="H45" s="25">
-        <v>0.4</v>
+        <v>0.38095238095238093</v>
       </c>
       <c r="J45" s="26">
         <v>120.0</v>
@@ -98460,13 +101040,13 @@
         <v>4006</v>
       </c>
       <c r="F46" s="24">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="G46" s="24">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H46" s="25">
-        <v>0.17142857142857143</v>
+        <v>0.0</v>
       </c>
       <c r="J46" s="26">
         <v>185.0</v>
@@ -98504,13 +101084,13 @@
         <v>4011</v>
       </c>
       <c r="F47" s="24">
-        <v>32.0</v>
+        <v>28.5</v>
       </c>
       <c r="G47" s="24">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H47" s="25">
-        <v>0.0625</v>
+        <v>0.03508771929824561</v>
       </c>
       <c r="J47" s="26">
         <v>346.0</v>
@@ -98548,13 +101128,13 @@
         <v>4016</v>
       </c>
       <c r="F48" s="24">
-        <v>318.0</v>
+        <v>49.0</v>
       </c>
       <c r="G48" s="24">
-        <v>38.0</v>
+        <v>2.0</v>
       </c>
       <c r="H48" s="25">
-        <v>0.11949685534591195</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="J48" s="26">
         <v>607.0</v>
@@ -98592,13 +101172,13 @@
         <v>4021</v>
       </c>
       <c r="F49" s="24">
-        <v>100.0</v>
+        <v>14.333333333333332</v>
       </c>
       <c r="G49" s="24">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H49" s="25">
-        <v>0.1</v>
+        <v>0.0</v>
       </c>
       <c r="J49" s="26">
         <v>172.83333333333334</v>
@@ -98636,13 +101216,13 @@
         <v>4026</v>
       </c>
       <c r="F50" s="24">
-        <v>89.0</v>
+        <v>11.333333333333332</v>
       </c>
       <c r="G50" s="24">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="H50" s="25">
-        <v>0.0898876404494382</v>
+        <v>0.08823529411764706</v>
       </c>
       <c r="J50" s="26">
         <v>186.83333333333334</v>
@@ -98680,13 +101260,13 @@
         <v>4031</v>
       </c>
       <c r="F51" s="24">
-        <v>129.0</v>
+        <v>23.333333333333332</v>
       </c>
       <c r="G51" s="24">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="H51" s="25">
-        <v>0.15503875968992248</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="J51" s="26">
         <v>247.33333333333334</v>
@@ -98724,13 +101304,13 @@
         <v>4036</v>
       </c>
       <c r="F52" s="24">
-        <v>350.0</v>
+        <v>517.0</v>
       </c>
       <c r="G52" s="24">
-        <v>38.0</v>
+        <v>59.0</v>
       </c>
       <c r="H52" s="25">
-        <v>0.10857142857142857</v>
+        <v>0.11411992263056092</v>
       </c>
       <c r="J52" s="26">
         <v>782.0</v>
@@ -98768,13 +101348,13 @@
         <v>4041</v>
       </c>
       <c r="F53" s="24">
-        <v>350.0</v>
+        <v>517.0</v>
       </c>
       <c r="G53" s="24">
-        <v>38.0</v>
+        <v>59.0</v>
       </c>
       <c r="H53" s="25">
-        <v>0.10857142857142857</v>
+        <v>0.11411992263056092</v>
       </c>
       <c r="J53" s="26">
         <v>782.0</v>
@@ -98812,13 +101392,13 @@
         <v>4046</v>
       </c>
       <c r="F54" s="24">
-        <v>91.5</v>
+        <v>170.25</v>
       </c>
       <c r="G54" s="24">
-        <v>7.0</v>
+        <v>20.0</v>
       </c>
       <c r="H54" s="25">
-        <v>0.07650273224043716</v>
+        <v>0.11747430249632893</v>
       </c>
       <c r="J54" s="26">
         <v>233.75</v>
@@ -98856,13 +101436,13 @@
         <v>4051</v>
       </c>
       <c r="F55" s="24">
-        <v>44.0</v>
+        <v>67.25</v>
       </c>
       <c r="G55" s="24">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="H55" s="25">
-        <v>0.18181818181818182</v>
+        <v>0.17843866171003717</v>
       </c>
       <c r="J55" s="26">
         <v>115.75</v>
@@ -98900,13 +101480,13 @@
         <v>4056</v>
       </c>
       <c r="F56" s="24">
-        <v>86.5</v>
+        <v>92.25</v>
       </c>
       <c r="G56" s="24">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H56" s="25">
-        <v>0.06936416184971098</v>
+        <v>0.05420054200542006</v>
       </c>
       <c r="J56" s="26">
         <v>158.75</v>
@@ -98944,13 +101524,13 @@
         <v>4061</v>
       </c>
       <c r="F57" s="24">
-        <v>128.0</v>
+        <v>187.25</v>
       </c>
       <c r="G57" s="24">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="H57" s="25">
-        <v>0.1328125</v>
+        <v>0.11748998664886515</v>
       </c>
       <c r="J57" s="26">
         <v>273.75</v>
@@ -98988,13 +101568,13 @@
         <v>4066</v>
       </c>
       <c r="F58" s="24">
-        <v>268.0</v>
+        <v>189.0</v>
       </c>
       <c r="G58" s="24">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="H58" s="25">
-        <v>0.10074626865671642</v>
+        <v>0.15873015873015872</v>
       </c>
       <c r="J58" s="26">
         <v>514.0</v>
@@ -99032,13 +101612,13 @@
         <v>4071</v>
       </c>
       <c r="F59" s="24">
-        <v>251.0</v>
+        <v>162.0</v>
       </c>
       <c r="G59" s="24">
         <v>25.0</v>
       </c>
       <c r="H59" s="25">
-        <v>0.099601593625498</v>
+        <v>0.15432098765432098</v>
       </c>
       <c r="J59" s="26">
         <v>499.0</v>
@@ -99076,13 +101656,13 @@
         <v>4076</v>
       </c>
       <c r="F60" s="24">
-        <v>74.75</v>
+        <v>43.75</v>
       </c>
       <c r="G60" s="24">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="H60" s="25">
-        <v>0.0802675585284281</v>
+        <v>0.25142857142857145</v>
       </c>
       <c r="J60" s="26">
         <v>149.75</v>
@@ -99120,13 +101700,13 @@
         <v>4081</v>
       </c>
       <c r="F61" s="24">
-        <v>27.75</v>
+        <v>23.75</v>
       </c>
       <c r="G61" s="24">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H61" s="25">
-        <v>0.14414414414414414</v>
+        <v>0.12631578947368421</v>
       </c>
       <c r="J61" s="26">
         <v>54.75</v>
@@ -99164,13 +101744,13 @@
         <v>4086</v>
       </c>
       <c r="F62" s="24">
-        <v>53.25</v>
+        <v>35.75</v>
       </c>
       <c r="G62" s="24">
         <v>4.0</v>
       </c>
       <c r="H62" s="25">
-        <v>0.07511737089201878</v>
+        <v>0.11188811188811189</v>
       </c>
       <c r="J62" s="26">
         <v>122.75</v>
@@ -99208,13 +101788,13 @@
         <v>4091</v>
       </c>
       <c r="F63" s="24">
-        <v>95.25</v>
+        <v>58.75</v>
       </c>
       <c r="G63" s="24">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="H63" s="25">
-        <v>0.11548556430446194</v>
+        <v>0.11914893617021277</v>
       </c>
       <c r="J63" s="26">
         <v>171.75</v>
@@ -99252,13 +101832,13 @@
         <v>4096</v>
       </c>
       <c r="F64" s="24">
-        <v>17.0</v>
+        <v>27.0</v>
       </c>
       <c r="G64" s="24">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H64" s="25">
-        <v>0.11764705882352941</v>
+        <v>0.18518518518518517</v>
       </c>
       <c r="J64" s="26">
         <v>15.0</v>
@@ -99296,13 +101876,13 @@
         <v>4101</v>
       </c>
       <c r="F65" s="24">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G65" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H65" s="25">
-        <v>0.0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="J65" s="26">
         <v>3.0</v>
@@ -99340,13 +101920,13 @@
         <v>4106</v>
       </c>
       <c r="F66" s="24">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G66" s="24">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H66" s="25">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
       <c r="J66" s="26">
         <v>3.0</v>
@@ -99384,13 +101964,13 @@
         <v>4111</v>
       </c>
       <c r="F67" s="24">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="G67" s="24">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H67" s="25">
-        <v>0.16666666666666666</v>
+        <v>0.125</v>
       </c>
       <c r="J67" s="26">
         <v>9.0</v>
@@ -99428,13 +102008,13 @@
         <v>4116</v>
       </c>
       <c r="F68" s="24">
-        <v>360.0</v>
+        <v>371.0</v>
       </c>
       <c r="G68" s="24">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="H68" s="25">
-        <v>0.11666666666666667</v>
+        <v>0.11859838274932614</v>
       </c>
       <c r="J68" s="26">
         <v>1292.0</v>
@@ -99516,13 +102096,13 @@
         <v>4126</v>
       </c>
       <c r="F70" s="24">
-        <v>107.33333333333334</v>
+        <v>119.33333333333333</v>
       </c>
       <c r="G70" s="24">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H70" s="25">
-        <v>0.07453416149068322</v>
+        <v>0.08379888268156425</v>
       </c>
       <c r="J70" s="26">
         <v>438.5</v>
@@ -99560,13 +102140,13 @@
         <v>4131</v>
       </c>
       <c r="F71" s="24">
-        <v>115.33333333333334</v>
+        <v>125.33333333333333</v>
       </c>
       <c r="G71" s="24">
-        <v>20.0</v>
+        <v>27.0</v>
       </c>
       <c r="H71" s="25">
-        <v>0.17341040462427745</v>
+        <v>0.21542553191489364</v>
       </c>
       <c r="J71" s="26">
         <v>350.5</v>
@@ -99604,13 +102184,13 @@
         <v>4136</v>
       </c>
       <c r="F72" s="24">
-        <v>137.33333333333334</v>
+        <v>115.33333333333333</v>
       </c>
       <c r="G72" s="24">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="H72" s="25">
-        <v>0.10194174757281553</v>
+        <v>0.04335260115606936</v>
       </c>
       <c r="J72" s="26">
         <v>460.0</v>
@@ -99648,13 +102228,13 @@
         <v>4141</v>
       </c>
       <c r="F73" s="24">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G73" s="24">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H73" s="25">
-        <v>0.0</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="J73" s="26">
         <v>43.0</v>
@@ -99692,7 +102272,7 @@
         <v>4146</v>
       </c>
       <c r="F74" s="24">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G74" s="24">
         <v>0.0</v>
@@ -99736,7 +102316,7 @@
         <v>4151</v>
       </c>
       <c r="F75" s="24">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G75" s="24">
         <v>0.0</v>
@@ -99780,13 +102360,13 @@
         <v>4156</v>
       </c>
       <c r="F76" s="24">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G76" s="24">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H76" s="25">
-        <v>0.0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J76" s="26">
         <v>16.666666666666668</v>
@@ -99818,7 +102398,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AA79"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="31"/>
@@ -99881,7 +102461,7 @@
         <v>4172</v>
       </c>
       <c r="F3" s="25">
-        <v>0.09627801560897269</v>
+        <v>0.0714432076295579</v>
       </c>
       <c r="H3" s="27">
         <v>0.06098160086707704</v>
@@ -99907,7 +102487,7 @@
         <v>4177</v>
       </c>
       <c r="F4" s="25">
-        <v>0.04513756911443717</v>
+        <v>0.055007680833526564</v>
       </c>
       <c r="H4" s="27">
         <v>0.0551699464275635</v>
@@ -99933,7 +102513,7 @@
         <v>4182</v>
       </c>
       <c r="F5" s="25">
-        <v>0.1068098034259732</v>
+        <v>0.07474073745054984</v>
       </c>
       <c r="H5" s="27">
         <v>0.06414128809467869</v>
@@ -99959,7 +102539,7 @@
         <v>4187</v>
       </c>
       <c r="F6" s="25">
-        <v>0.0</v>
+        <v>0.13654125990731147</v>
       </c>
       <c r="H6" s="27">
         <v>0.07817601341354315</v>
@@ -99985,7 +102565,7 @@
         <v>4192</v>
       </c>
       <c r="F7" s="25">
-        <v>0.4974717254649712</v>
+        <v>0.0869283199347427</v>
       </c>
       <c r="H7" s="27">
         <v>0.0454531374055001</v>
@@ -100036,8 +102616,8 @@
       <c r="E9" s="29" t="s">
         <v>4202</v>
       </c>
-      <c r="F9" s="33">
-        <v>0.0</v>
+      <c r="F9" s="25">
+        <v>0.09703396470907238</v>
       </c>
       <c r="H9" s="27">
         <v>0.0703472500051208</v>
@@ -100063,7 +102643,7 @@
         <v>4207</v>
       </c>
       <c r="F10" s="25">
-        <v>0.03770547184323618</v>
+        <v>0.05261335214437954</v>
       </c>
       <c r="H10" s="27">
         <v>0.05259384427639548</v>
@@ -100089,7 +102669,7 @@
         <v>4212</v>
       </c>
       <c r="F11" s="25">
-        <v>0.03326895576826878</v>
+        <v>0.04417564635318511</v>
       </c>
       <c r="H11" s="27">
         <v>0.037722930031919004</v>
@@ -100115,7 +102695,7 @@
         <v>4217</v>
       </c>
       <c r="F12" s="25">
-        <v>0.02836302688327537</v>
+        <v>0.09198119603477448</v>
       </c>
       <c r="H12" s="27">
         <v>0.06281704102885162</v>
@@ -100141,7 +102721,7 @@
         <v>4222</v>
       </c>
       <c r="F13" s="25">
-        <v>0.03192152835974302</v>
+        <v>0.01485922200500802</v>
       </c>
       <c r="H13" s="27">
         <v>0.03158221984527825</v>
@@ -100167,7 +102747,7 @@
         <v>4227</v>
       </c>
       <c r="F14" s="25">
-        <v>0.049977596444282325</v>
+        <v>0.06594049607480489</v>
       </c>
       <c r="H14" s="27">
         <v>0.07417183953936354</v>
@@ -100193,7 +102773,7 @@
         <v>4232</v>
       </c>
       <c r="F15" s="25">
-        <v>0.04514883199157655</v>
+        <v>0.0391051294949675</v>
       </c>
       <c r="H15" s="27">
         <v>0.04259452558342196</v>
@@ -100219,7 +102799,7 @@
         <v>4237</v>
       </c>
       <c r="F16" s="25">
-        <v>0.04514883199157655</v>
+        <v>0.0391051294949675</v>
       </c>
       <c r="H16" s="27">
         <v>0.04259452558342196</v>
@@ -100245,7 +102825,7 @@
         <v>4242</v>
       </c>
       <c r="F17" s="25">
-        <v>0.0343253182802941</v>
+        <v>0.030216360899535482</v>
       </c>
       <c r="H17" s="27">
         <v>0.03723844758914133</v>
@@ -100271,7 +102851,7 @@
         <v>4247</v>
       </c>
       <c r="F18" s="25">
-        <v>0.089205053980151</v>
+        <v>0.1029607329650065</v>
       </c>
       <c r="H18" s="27">
         <v>0.05457987347785562</v>
@@ -100297,7 +102877,7 @@
         <v>4252</v>
       </c>
       <c r="F19" s="25">
-        <v>0.058589781996075306</v>
+        <v>0.011241619109808853</v>
       </c>
       <c r="H19" s="27">
         <v>0.028415486056884025</v>
@@ -100323,7 +102903,7 @@
         <v>4257</v>
       </c>
       <c r="F20" s="25">
-        <v>0.013068239536623043</v>
+        <v>0.043858753060495005</v>
       </c>
       <c r="H20" s="27">
         <v>0.050309064302250586</v>
@@ -100349,7 +102929,7 @@
         <v>4262</v>
       </c>
       <c r="F21" s="25">
-        <v>0.08802778366085617</v>
+        <v>0.048940027015205834</v>
       </c>
       <c r="H21" s="27">
         <v>0.06275887670528484</v>
@@ -100375,7 +102955,7 @@
         <v>4267</v>
       </c>
       <c r="F22" s="25">
-        <v>0.08802778366085617</v>
+        <v>0.048940027015205834</v>
       </c>
       <c r="H22" s="27">
         <v>0.06275887670528484</v>
@@ -100401,7 +102981,7 @@
         <v>4272</v>
       </c>
       <c r="F23" s="25">
-        <v>0.08608722382907374</v>
+        <v>0.1616977855127562</v>
       </c>
       <c r="H23" s="27">
         <v>0.0718865217868037</v>
@@ -100453,7 +103033,7 @@
         <v>4282</v>
       </c>
       <c r="F25" s="25">
-        <v>0.24325029499677026</v>
+        <v>0.0</v>
       </c>
       <c r="H25" s="27">
         <v>0.04958406058859932</v>
@@ -100479,7 +103059,7 @@
         <v>4287</v>
       </c>
       <c r="F26" s="25">
-        <v>0.043805906832283165</v>
+        <v>0.0</v>
       </c>
       <c r="H26" s="27">
         <v>0.05325235163529225</v>
@@ -100609,7 +103189,7 @@
         <v>4312</v>
       </c>
       <c r="F31" s="25">
-        <v>0.1023947561236618</v>
+        <v>0.12572993630356574</v>
       </c>
       <c r="H31" s="27">
         <v>0.06686510248145955</v>
@@ -100635,7 +103215,7 @@
         <v>4317</v>
       </c>
       <c r="F32" s="25">
-        <v>0.11721712394652918</v>
+        <v>0.12637571126038125</v>
       </c>
       <c r="H32" s="27">
         <v>0.06964091791545708</v>
@@ -100661,7 +103241,7 @@
         <v>4322</v>
       </c>
       <c r="F33" s="25">
-        <v>0.03819078865635482</v>
+        <v>0.05315996628928036</v>
       </c>
       <c r="H33" s="27">
         <v>0.06082120689025663</v>
@@ -100687,7 +103267,7 @@
         <v>4327</v>
       </c>
       <c r="F34" s="25">
-        <v>0.24274910491866208</v>
+        <v>0.1774868750300987</v>
       </c>
       <c r="H34" s="27">
         <v>0.1201040948033431</v>
@@ -100713,7 +103293,7 @@
         <v>4332</v>
       </c>
       <c r="F35" s="25">
-        <v>0.07485565274108441</v>
+        <v>0.010046861371849266</v>
       </c>
       <c r="H35" s="27">
         <v>0.03790015110298493</v>
@@ -100739,7 +103319,7 @@
         <v>4337</v>
       </c>
       <c r="F36" s="25">
-        <v>0.15066877055215233</v>
+        <v>0.1827577708178128</v>
       </c>
       <c r="H36" s="27">
         <v>0.07597722869424497</v>
@@ -100765,7 +103345,7 @@
         <v>4342</v>
       </c>
       <c r="F37" s="25">
-        <v>0.04501552432303537</v>
+        <v>0.12276548846203432</v>
       </c>
       <c r="H37" s="27">
         <v>0.05768390535317222</v>
@@ -100791,7 +103371,7 @@
         <v>4347</v>
       </c>
       <c r="F38" s="25">
-        <v>0.013286438677101588</v>
+        <v>0.013635875796110801</v>
       </c>
       <c r="H38" s="27">
         <v>0.060179134125691515</v>
@@ -100817,7 +103397,7 @@
         <v>4352</v>
       </c>
       <c r="F39" s="25">
-        <v>0.04458891937310925</v>
+        <v>0.0</v>
       </c>
       <c r="H39" s="27">
         <v>0.041275589812516306</v>
@@ -100843,7 +103423,7 @@
         <v>4357</v>
       </c>
       <c r="F40" s="25">
-        <v>0.07860187538750195</v>
+        <v>0.09664214099611108</v>
       </c>
       <c r="H40" s="27">
         <v>0.071851834469613</v>
@@ -100869,7 +103449,7 @@
         <v>4362</v>
       </c>
       <c r="F41" s="25">
-        <v>0.04123044497519338</v>
+        <v>0.218312017878382</v>
       </c>
       <c r="H41" s="27">
         <v>0.05386528971488993</v>
@@ -100895,7 +103475,7 @@
         <v>4367</v>
       </c>
       <c r="F42" s="25">
-        <v>0.09878683471386894</v>
+        <v>0.004963363369126116</v>
       </c>
       <c r="H42" s="27">
         <v>0.05880860180475631</v>
@@ -100921,7 +103501,7 @@
         <v>4372</v>
       </c>
       <c r="F43" s="25">
-        <v>0.10405747094225257</v>
+        <v>0.00681952004335331</v>
       </c>
       <c r="H43" s="27">
         <v>0.07033997723848215</v>
@@ -100947,7 +103527,7 @@
         <v>4377</v>
       </c>
       <c r="F44" s="25">
-        <v>0.006144336801960007</v>
+        <v>0.010526373510113207</v>
       </c>
       <c r="H44" s="27">
         <v>0.05309210228122905</v>
@@ -100973,7 +103553,7 @@
         <v>4382</v>
       </c>
       <c r="F45" s="25">
-        <v>0.4935409261254934</v>
+        <v>0.04215389736759091</v>
       </c>
       <c r="H45" s="27">
         <v>0.08764286200574223</v>
@@ -100999,7 +103579,7 @@
         <v>4387</v>
       </c>
       <c r="F46" s="25">
-        <v>0.12983263516201407</v>
+        <v>0.0</v>
       </c>
       <c r="H46" s="27">
         <v>0.05437549225888266</v>
@@ -101025,7 +103605,7 @@
         <v>4392</v>
       </c>
       <c r="F47" s="25">
-        <v>0.0579088394667248</v>
+        <v>0.001641915547414574</v>
       </c>
       <c r="H47" s="27">
         <v>0.08030535556111061</v>
@@ -101051,7 +103631,7 @@
         <v>4397</v>
       </c>
       <c r="F48" s="25">
-        <v>0.0969647866414151</v>
+        <v>0.0027989234501122366</v>
       </c>
       <c r="H48" s="27">
         <v>0.04027813545296318</v>
@@ -101077,7 +103657,7 @@
         <v>4402</v>
       </c>
       <c r="F49" s="25">
-        <v>0.02665574181408414</v>
+        <v>0.0</v>
       </c>
       <c r="H49" s="27">
         <v>0.04147625000783528</v>
@@ -101103,7 +103683,7 @@
         <v>4407</v>
       </c>
       <c r="F50" s="25">
-        <v>0.0759864721107569</v>
+        <v>0.0059452605550122505</v>
       </c>
       <c r="H50" s="27">
         <v>0.05113228792699242</v>
@@ -101129,7 +103709,7 @@
         <v>4412</v>
       </c>
       <c r="F51" s="25">
-        <v>0.15957197157637068</v>
+        <v>0.003242415358448011</v>
       </c>
       <c r="H51" s="27">
         <v>0.032603277647457754</v>
@@ -101155,7 +103735,7 @@
         <v>4417</v>
       </c>
       <c r="F52" s="25">
-        <v>0.2507032227940145</v>
+        <v>0.08627699530405306</v>
       </c>
       <c r="H52" s="27">
         <v>0.051747299673365346</v>
@@ -101181,7 +103761,7 @@
         <v>4422</v>
       </c>
       <c r="F53" s="25">
-        <v>0.2507032227940145</v>
+        <v>0.08627699530405306</v>
       </c>
       <c r="H53" s="27">
         <v>0.051747299673365346</v>
@@ -101207,7 +103787,7 @@
         <v>4427</v>
       </c>
       <c r="F54" s="25">
-        <v>0.0411232061341156</v>
+        <v>0.05856550495192613</v>
       </c>
       <c r="H54" s="27">
         <v>0.03864478289872982</v>
@@ -101233,7 +103813,7 @@
         <v>4432</v>
       </c>
       <c r="F55" s="25">
-        <v>0.6586724207510878</v>
+        <v>0.06944001489267275</v>
       </c>
       <c r="H55" s="27">
         <v>0.08776981781203018</v>
@@ -101259,7 +103839,7 @@
         <v>4437</v>
       </c>
       <c r="F56" s="25">
-        <v>0.2541951255595723</v>
+        <v>0.10504546683598373</v>
       </c>
       <c r="H56" s="27">
         <v>0.028959293489646237</v>
@@ -101285,7 +103865,7 @@
         <v>4442</v>
       </c>
       <c r="F57" s="25">
-        <v>0.09015370419977155</v>
+        <v>0.10505320405965639</v>
       </c>
       <c r="H57" s="27">
         <v>0.061063635455106</v>
@@ -101311,7 +103891,7 @@
         <v>4447</v>
       </c>
       <c r="F58" s="25">
-        <v>0.0786667059743622</v>
+        <v>0.12000526950930522</v>
       </c>
       <c r="H58" s="27">
         <v>0.07112602009100809</v>
@@ -101337,7 +103917,7 @@
         <v>4452</v>
       </c>
       <c r="F59" s="25">
-        <v>0.08017893290579836</v>
+        <v>0.11665534964588728</v>
       </c>
       <c r="H59" s="27">
         <v>0.07383819857319583</v>
@@ -101363,7 +103943,7 @@
         <v>4457</v>
       </c>
       <c r="F60" s="25">
-        <v>0.056276173244985024</v>
+        <v>0.1402641753710246</v>
       </c>
       <c r="H60" s="27">
         <v>0.05791045472890207</v>
@@ -101389,7 +103969,7 @@
         <v>4462</v>
       </c>
       <c r="F61" s="25">
-        <v>0.06146532366083644</v>
+        <v>0.13821199061264777</v>
       </c>
       <c r="H61" s="27">
         <v>0.09966135113269331</v>
@@ -101415,7 +103995,7 @@
         <v>4467</v>
       </c>
       <c r="F62" s="25">
-        <v>0.022320430435404343</v>
+        <v>0.07267648865136646</v>
       </c>
       <c r="H62" s="27">
         <v>0.08123188562332694</v>
@@ -101441,7 +104021,7 @@
         <v>4472</v>
       </c>
       <c r="F63" s="25">
-        <v>0.14093604025149037</v>
+        <v>0.12382462987576354</v>
       </c>
       <c r="H63" s="27">
         <v>0.07346979799641581</v>
@@ -101467,7 +104047,7 @@
         <v>4477</v>
       </c>
       <c r="F64" s="25">
-        <v>0.03700954980255676</v>
+        <v>0.13400589010515881</v>
       </c>
       <c r="H64" s="27">
         <v>0.006138075483457187</v>
@@ -101493,7 +104073,7 @@
         <v>4482</v>
       </c>
       <c r="F65" s="25">
-        <v>0.0</v>
+        <v>0.026546295651946546</v>
       </c>
       <c r="H65" s="27">
         <v>0.0</v>
@@ -101519,7 +104099,7 @@
         <v>4487</v>
       </c>
       <c r="F66" s="25">
-        <v>0.0</v>
+        <v>0.34674246754013754</v>
       </c>
       <c r="H66" s="27">
         <v>0.0</v>
@@ -101545,7 +104125,7 @@
         <v>4492</v>
       </c>
       <c r="F67" s="25">
-        <v>0.04691637428963245</v>
+        <v>0.022402005488635468</v>
       </c>
       <c r="H67" s="27">
         <v>0.00992930222684575</v>
@@ -101571,7 +104151,7 @@
         <v>4497</v>
       </c>
       <c r="F68" s="25">
-        <v>0.06913138761678468</v>
+        <v>0.0764321942670123</v>
       </c>
       <c r="H68" s="27">
         <v>0.0815567276804826</v>
@@ -101597,7 +104177,7 @@
         <v>4502</v>
       </c>
       <c r="F69" s="25">
-        <v>0.06913138761678468</v>
+        <v>0.07099396683483267</v>
       </c>
       <c r="H69" s="27">
         <v>0.07821810662619413</v>
@@ -101623,7 +104203,7 @@
         <v>4507</v>
       </c>
       <c r="F70" s="25">
-        <v>0.034892710518697696</v>
+        <v>0.05075301294246951</v>
       </c>
       <c r="H70" s="27">
         <v>0.07632021177610046</v>
@@ -101649,7 +104229,7 @@
         <v>4512</v>
       </c>
       <c r="F71" s="25">
-        <v>0.07300762171565071</v>
+        <v>0.1232999704839467</v>
       </c>
       <c r="H71" s="27">
         <v>0.04669245019606618</v>
@@ -101675,7 +104255,7 @@
         <v>4517</v>
       </c>
       <c r="F72" s="25">
-        <v>0.0901066156417462</v>
+        <v>0.03707050839549364</v>
       </c>
       <c r="H72" s="27">
         <v>0.10076366875278608</v>
@@ -101701,7 +104281,7 @@
         <v>4522</v>
       </c>
       <c r="F73" s="25">
-        <v>0.0</v>
+        <v>0.3138605525440069</v>
       </c>
       <c r="H73" s="27">
         <v>0.19678892697655986</v>
@@ -101779,7 +104359,7 @@
         <v>4537</v>
       </c>
       <c r="F76" s="25">
-        <v>0.0</v>
+        <v>0.4842167531733346</v>
       </c>
       <c r="H76" s="27">
         <v>0.2890112246526713</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10337" count="10337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10369" count="10369">
   <si>
     <t>Region</t>
   </si>
@@ -93333,6 +93333,294 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
     </r>
   </si>
 </sst>
@@ -93347,7 +93635,7 @@
     <numFmt numFmtId="10" formatCode="0.00%"/>
     <numFmt numFmtId="2" formatCode="0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -93361,10 +93649,6 @@
     <font>
       <name val="Calibri"/>
       <b/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <sz val="11"/>
     </font>
     <font>
@@ -93472,7 +93756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -93515,13 +93799,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -93533,43 +93811,43 @@
     <xf numFmtId="10" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -102543,307 +102821,307 @@
       </c>
     </row>
     <row r="2" spans="8:8" ht="36.7">
-      <c r="A2" s="14" t="s">
-        <v>10050</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>10051</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>10052</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>10053</v>
-      </c>
-      <c r="E2" s="15">
+      <c r="A2" s="2" t="s">
+        <v>10337</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10338</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10339</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10340</v>
+      </c>
+      <c r="E2" s="3">
         <v>6104317.5</v>
       </c>
-      <c r="F2" s="15">
-        <v>959021.27</v>
-      </c>
-      <c r="G2" s="15">
-        <v>1817337.72</v>
-      </c>
-      <c r="H2" s="15">
-        <v>2776358.99</v>
-      </c>
-      <c r="I2" s="15">
-        <v>45.48</v>
-      </c>
-      <c r="J2" s="15">
-        <v>-3327958.51</v>
-      </c>
-      <c r="K2" s="15">
-        <v>22928.72</v>
-      </c>
-      <c r="L2" s="15">
-        <v>0.83</v>
+      <c r="F2" s="3">
+        <v>1458257.81</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1524933.81</v>
+      </c>
+      <c r="H2" s="3">
+        <v>2983191.62</v>
+      </c>
+      <c r="I2" s="3">
+        <v>48.87</v>
+      </c>
+      <c r="J2" s="3">
+        <v>-3121125.88</v>
+      </c>
+      <c r="K2" s="3">
+        <v>34750.39</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1.16</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
-      <c r="A3" s="14" t="s">
-        <v>10054</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>10055</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>10056</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>10057</v>
-      </c>
-      <c r="E3" s="15">
+      <c r="A3" s="2" t="s">
+        <v>10341</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10342</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10343</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10344</v>
+      </c>
+      <c r="E3" s="3">
         <v>3440798.37</v>
       </c>
-      <c r="F3" s="15">
-        <v>417821.52</v>
-      </c>
-      <c r="G3" s="15">
-        <v>925222.35</v>
-      </c>
-      <c r="H3" s="15">
-        <v>1343043.87</v>
-      </c>
-      <c r="I3" s="15">
-        <v>39.03</v>
-      </c>
-      <c r="J3" s="15">
-        <v>-2097754.5</v>
-      </c>
-      <c r="K3" s="15">
-        <v>13864.04</v>
-      </c>
-      <c r="L3" s="15">
-        <v>1.03</v>
+      <c r="F3" s="3">
+        <v>559858.59</v>
+      </c>
+      <c r="G3" s="3">
+        <v>863994.97</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1423853.56</v>
+      </c>
+      <c r="I3" s="3">
+        <v>41.38</v>
+      </c>
+      <c r="J3" s="3">
+        <v>-2016944.81</v>
+      </c>
+      <c r="K3" s="3">
+        <v>16613.54</v>
+      </c>
+      <c r="L3" s="3">
+        <v>1.17</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
-      <c r="A4" s="14" t="s">
-        <v>10058</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>10059</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>10060</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>10061</v>
-      </c>
-      <c r="E4" s="15">
+      <c r="A4" s="2" t="s">
+        <v>10345</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10346</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10347</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10348</v>
+      </c>
+      <c r="E4" s="3">
         <v>6398516.07</v>
       </c>
-      <c r="F4" s="15">
-        <v>901953.45</v>
-      </c>
-      <c r="G4" s="15">
-        <v>1143931.17</v>
-      </c>
-      <c r="H4" s="15">
-        <v>2045884.62</v>
-      </c>
-      <c r="I4" s="15">
-        <v>31.97</v>
-      </c>
-      <c r="J4" s="15">
-        <v>-4352631.45</v>
-      </c>
-      <c r="K4" s="15">
-        <v>22634.29</v>
-      </c>
-      <c r="L4" s="15">
-        <v>1.11</v>
+      <c r="F4" s="3">
+        <v>1136619.88</v>
+      </c>
+      <c r="G4" s="3">
+        <v>921227.0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2057846.88</v>
+      </c>
+      <c r="I4" s="3">
+        <v>32.16</v>
+      </c>
+      <c r="J4" s="3">
+        <v>-4340669.19</v>
+      </c>
+      <c r="K4" s="3">
+        <v>38953.45</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1.89</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
-      <c r="A5" s="14" t="s">
-        <v>10062</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>10063</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>10064</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>10065</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="A5" s="2" t="s">
+        <v>10349</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10350</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10351</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10352</v>
+      </c>
+      <c r="E5" s="3">
         <v>7403170.5</v>
       </c>
-      <c r="F5" s="15">
-        <v>1442331.27</v>
-      </c>
-      <c r="G5" s="15">
-        <v>1234186.84</v>
-      </c>
-      <c r="H5" s="15">
-        <v>2676518.11</v>
-      </c>
-      <c r="I5" s="15">
-        <v>36.15</v>
-      </c>
-      <c r="J5" s="15">
-        <v>-4726652.39</v>
-      </c>
-      <c r="K5" s="15">
-        <v>33077.8</v>
-      </c>
-      <c r="L5" s="15">
-        <v>1.24</v>
+      <c r="F5" s="3">
+        <v>1935058.78</v>
+      </c>
+      <c r="G5" s="3">
+        <v>877960.54</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2813019.32</v>
+      </c>
+      <c r="I5" s="3">
+        <v>38.0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>-4590151.18</v>
+      </c>
+      <c r="K5" s="3">
+        <v>47842.94</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1.7</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
-      <c r="A6" s="14" t="s">
-        <v>10066</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>10067</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>10068</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>10069</v>
-      </c>
-      <c r="E6" s="15">
+      <c r="A6" s="2" t="s">
+        <v>10353</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10354</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10355</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10356</v>
+      </c>
+      <c r="E6" s="3">
         <v>7091695.63</v>
       </c>
-      <c r="F6" s="15">
-        <v>1184886.07</v>
-      </c>
-      <c r="G6" s="15">
-        <v>1500789.12</v>
-      </c>
-      <c r="H6" s="15">
-        <v>2685675.19</v>
-      </c>
-      <c r="I6" s="15">
-        <v>37.87</v>
-      </c>
-      <c r="J6" s="15">
-        <v>-4406020.44</v>
-      </c>
-      <c r="K6" s="15">
-        <v>33992.76</v>
-      </c>
-      <c r="L6" s="15">
-        <v>1.27</v>
+      <c r="F6" s="3">
+        <v>1895527.52</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1076616.24</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2972143.76</v>
+      </c>
+      <c r="I6" s="3">
+        <v>41.91</v>
+      </c>
+      <c r="J6" s="3">
+        <v>-4119551.87</v>
+      </c>
+      <c r="K6" s="3">
+        <v>57850.86</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1.95</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
-      <c r="A7" s="14" t="s">
-        <v>10070</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>10071</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>10072</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>10073</v>
-      </c>
-      <c r="E7" s="15">
+      <c r="A7" s="2" t="s">
+        <v>10357</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10358</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10359</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10360</v>
+      </c>
+      <c r="E7" s="3">
         <v>4638385.13</v>
       </c>
-      <c r="F7" s="15">
-        <v>954096.34</v>
-      </c>
-      <c r="G7" s="15">
-        <v>1097402.64</v>
-      </c>
-      <c r="H7" s="15">
-        <v>2051498.98</v>
-      </c>
-      <c r="I7" s="15">
-        <v>44.23</v>
-      </c>
-      <c r="J7" s="15">
-        <v>-2586886.15</v>
-      </c>
-      <c r="K7" s="15">
-        <v>27650.54</v>
-      </c>
-      <c r="L7" s="15">
-        <v>1.35</v>
+      <c r="F7" s="3">
+        <v>1216852.58</v>
+      </c>
+      <c r="G7" s="3">
+        <v>822290.02</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2039142.6</v>
+      </c>
+      <c r="I7" s="3">
+        <v>43.96</v>
+      </c>
+      <c r="J7" s="3">
+        <v>-2599242.53</v>
+      </c>
+      <c r="K7" s="3">
+        <v>40006.92</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1.96</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
-      <c r="A8" s="14" t="s">
-        <v>10074</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>10075</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>10076</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>10077</v>
-      </c>
-      <c r="E8" s="15">
+      <c r="A8" s="2" t="s">
+        <v>10361</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10362</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10363</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10364</v>
+      </c>
+      <c r="E8" s="3">
         <v>7324761.7</v>
       </c>
-      <c r="F8" s="15">
-        <v>1337682.77</v>
-      </c>
-      <c r="G8" s="15">
-        <v>1014429.84</v>
-      </c>
-      <c r="H8" s="15">
-        <v>2352112.61</v>
-      </c>
-      <c r="I8" s="15">
-        <v>32.11</v>
-      </c>
-      <c r="J8" s="15">
-        <v>-4972649.09</v>
-      </c>
-      <c r="K8" s="15">
-        <v>25599.0</v>
-      </c>
-      <c r="L8" s="15">
-        <v>1.09</v>
+      <c r="F8" s="3">
+        <v>1679915.85</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1313116.74</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2993032.59</v>
+      </c>
+      <c r="I8" s="3">
+        <v>40.86</v>
+      </c>
+      <c r="J8" s="3">
+        <v>-4331729.11</v>
+      </c>
+      <c r="K8" s="3">
+        <v>31444.02</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1.05</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
-      <c r="A9" s="14" t="s">
-        <v>10078</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>10079</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>10080</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>10081</v>
-      </c>
-      <c r="E9" s="15">
+      <c r="A9" s="2" t="s">
+        <v>10365</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10366</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10367</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10368</v>
+      </c>
+      <c r="E9" s="3">
         <v>6543653.55</v>
       </c>
-      <c r="F9" s="15">
-        <v>942111.14</v>
-      </c>
-      <c r="G9" s="15">
-        <v>1051328.07</v>
-      </c>
-      <c r="H9" s="15">
-        <v>1993439.21</v>
-      </c>
-      <c r="I9" s="15">
-        <v>30.46</v>
-      </c>
-      <c r="J9" s="15">
-        <v>-4550214.34</v>
-      </c>
-      <c r="K9" s="15">
-        <v>42254.45</v>
-      </c>
-      <c r="L9" s="15">
-        <v>2.12</v>
+      <c r="F9" s="3">
+        <v>1109336.96</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1302693.63</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2412030.59</v>
+      </c>
+      <c r="I9" s="3">
+        <v>36.86</v>
+      </c>
+      <c r="J9" s="3">
+        <v>-4131622.96</v>
+      </c>
+      <c r="K9" s="3">
+        <v>51832.67</v>
+      </c>
+      <c r="L9" s="3">
+        <v>2.15</v>
       </c>
     </row>
     <row r="13" spans="8:8">
@@ -103958,3314 +104236,3314 @@
   </cols>
   <sheetData>
     <row r="1" spans="8:8">
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="14" t="s">
         <v>6044</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16" t="s">
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14" t="s">
         <v>6045</v>
       </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
     </row>
     <row r="2" spans="8:8" ht="24.85" customFormat="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>4793</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>4794</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>4795</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>4796</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>4797</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="16" t="s">
         <v>4798</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="16" t="s">
         <v>4799</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="17" t="s">
         <v>4800</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="18" t="s">
         <v>6046</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="18" t="s">
         <v>6047</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="19" t="s">
         <v>6048</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="18" t="s">
         <v>6049</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="18" t="s">
         <v>6050</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="19" t="s">
         <v>6051</v>
       </c>
     </row>
     <row r="3" spans="8:8">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="20" t="s">
         <v>3787</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>3788</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="21" t="s">
         <v>3789</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>3790</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="21" t="s">
         <v>3791</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <v>2519.0</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <v>277.0</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="23">
         <v>0.10996427153632393</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="24">
         <v>10812.0</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="24">
         <v>938.0</v>
       </c>
-      <c r="L3" s="27">
+      <c r="L3" s="25">
         <v>0.08675545689974103</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="24">
         <v>11092.0</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="24">
         <v>1021.0</v>
       </c>
-      <c r="O3" s="27">
+      <c r="O3" s="25">
         <v>0.09204832311575911</v>
       </c>
     </row>
     <row r="4" spans="8:8">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="20" t="s">
         <v>3792</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>3793</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="26" t="s">
         <v>3794</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="26" t="s">
         <v>3795</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="26" t="s">
         <v>3796</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="22">
         <v>926.0</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <v>93.0</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="23">
         <v>0.10043196544276457</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="24">
         <v>3158.0</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="24">
         <v>271.0</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="25">
         <v>0.08581380620645979</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="24">
         <v>3358.0</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="24">
         <v>307.0</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="25">
         <v>0.09142346634901727</v>
       </c>
     </row>
     <row r="5" spans="8:8">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>3797</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>3798</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="27" t="s">
         <v>3799</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="27" t="s">
         <v>3800</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="27" t="s">
         <v>3801</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <v>70.0</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <v>8.0</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="23">
         <v>0.11428571428571428</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="24">
         <v>640.0</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="24">
         <v>55.0</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="25">
         <v>0.0859375</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="24">
         <v>409.0</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="24">
         <v>41.0</v>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="25">
         <v>0.10024449877750612</v>
       </c>
     </row>
     <row r="6" spans="8:8">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>3802</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>3803</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="27" t="s">
         <v>3804</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="27" t="s">
         <v>3805</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="27" t="s">
         <v>3806</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <v>13.25</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <v>3.0</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="23">
         <v>0.22641509433962265</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="24">
         <v>153.75</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="24">
         <v>17.0</v>
       </c>
-      <c r="L6" s="27">
+      <c r="L6" s="25">
         <v>0.11056910569105691</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="24">
         <v>101.25</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="24">
         <v>9.0</v>
       </c>
-      <c r="O6" s="27">
+      <c r="O6" s="25">
         <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="7" spans="8:8">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="20" t="s">
         <v>3807</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>3808</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="27" t="s">
         <v>3809</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="27" t="s">
         <v>3810</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="27" t="s">
         <v>3811</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <v>13.25</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <v>3.0</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="23">
         <v>0.22641509433962265</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="24">
         <v>98.25</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="24">
         <v>11.0</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="25">
         <v>0.11195928753180662</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="24">
         <v>54.75</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="24">
         <v>6.0</v>
       </c>
-      <c r="O7" s="27">
+      <c r="O7" s="25">
         <v>0.1095890410958904</v>
       </c>
     </row>
     <row r="8" spans="8:8">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="20" t="s">
         <v>3812</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>3813</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="27" t="s">
         <v>3814</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="27" t="s">
         <v>3815</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="27" t="s">
         <v>3816</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <v>17.25</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <v>0.0</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="23">
         <v>0.0</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="24">
         <v>149.75</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="24">
         <v>11.0</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="25">
         <v>0.07345575959933222</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="24">
         <v>117.75</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="24">
         <v>15.0</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="25">
         <v>0.12738853503184713</v>
       </c>
     </row>
     <row r="9" spans="8:8">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>3817</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>3818</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="27" t="s">
         <v>3819</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="27" t="s">
         <v>3820</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="27" t="s">
         <v>3821</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="22">
         <v>26.25</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="22">
         <v>2.0</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="23">
         <v>0.0761904761904762</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="24">
         <v>238.25</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="24">
         <v>16.0</v>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="25">
         <v>0.06715634837355719</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="24">
         <v>135.25</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="24">
         <v>11.0</v>
       </c>
-      <c r="O9" s="27">
+      <c r="O9" s="25">
         <v>0.08133086876155268</v>
       </c>
     </row>
     <row r="10" spans="8:8">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>3822</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>3823</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="27" t="s">
         <v>3824</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="27" t="s">
         <v>3825</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="27" t="s">
         <v>3826</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <v>856.0</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <v>85.0</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="23">
         <v>0.09929906542056074</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="24">
         <v>2518.0</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="24">
         <v>216.0</v>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="25">
         <v>0.0857823669579031</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="24">
         <v>2949.0</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="24">
         <v>266.0</v>
       </c>
-      <c r="O10" s="27">
+      <c r="O10" s="25">
         <v>0.09020006781959987</v>
       </c>
     </row>
     <row r="11" spans="8:8">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="20" t="s">
         <v>3827</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>3828</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="27" t="s">
         <v>3829</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="27" t="s">
         <v>3830</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="27" t="s">
         <v>3831</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <v>255.75</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <v>38.0</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="23">
         <v>0.14858260019550343</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="24">
         <v>727.5</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="24">
         <v>82.0</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="25">
         <v>0.11271477663230241</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="24">
         <v>878.75</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="24">
         <v>114.0</v>
       </c>
-      <c r="O11" s="27">
+      <c r="O11" s="25">
         <v>0.12972972972972974</v>
       </c>
     </row>
     <row r="12" spans="8:8">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="20" t="s">
         <v>3832</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>3833</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="27" t="s">
         <v>3834</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="27" t="s">
         <v>3835</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="27" t="s">
         <v>3836</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="22">
         <v>141.75</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <v>19.0</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="23">
         <v>0.13403880070546736</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="24">
         <v>362.5</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="24">
         <v>46.0</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="25">
         <v>0.12689655172413794</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="24">
         <v>421.25</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="24">
         <v>54.0</v>
       </c>
-      <c r="O12" s="27">
+      <c r="O12" s="25">
         <v>0.1281899109792285</v>
       </c>
     </row>
     <row r="13" spans="8:8">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="20" t="s">
         <v>3837</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>3838</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="27" t="s">
         <v>3839</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="27" t="s">
         <v>3840</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="27" t="s">
         <v>3841</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="22">
         <v>174.25</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="22">
         <v>7.0</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="23">
         <v>0.040172166427546625</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="24">
         <v>602.0</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="24">
         <v>31.0</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="25">
         <v>0.05149501661129568</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="24">
         <v>662.75</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="24">
         <v>31.0</v>
       </c>
-      <c r="O13" s="27">
+      <c r="O13" s="25">
         <v>0.046774801961523955</v>
       </c>
     </row>
     <row r="14" spans="8:8">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="20" t="s">
         <v>3842</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="20" t="s">
         <v>3843</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="27" t="s">
         <v>3844</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="27" t="s">
         <v>3845</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="27" t="s">
         <v>3846</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <v>284.25</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <v>21.0</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="23">
         <v>0.07387862796833773</v>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="24">
         <v>826.0</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="24">
         <v>57.0</v>
       </c>
-      <c r="L14" s="27">
+      <c r="L14" s="25">
         <v>0.06900726392251816</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="24">
         <v>986.25</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="24">
         <v>67.0</v>
       </c>
-      <c r="O14" s="27">
+      <c r="O14" s="25">
         <v>0.0679340937896071</v>
       </c>
     </row>
     <row r="15" spans="8:8">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>3847</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="20" t="s">
         <v>3848</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="26" t="s">
         <v>3849</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="26" t="s">
         <v>3850</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="26" t="s">
         <v>3851</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <v>155.0</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <v>9.0</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="23">
         <v>0.05806451612903226</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="24">
         <v>1008.0</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="24">
         <v>56.0</v>
       </c>
-      <c r="L15" s="27">
+      <c r="L15" s="25">
         <v>0.05555555555555555</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="24">
         <v>931.0</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="24">
         <v>72.0</v>
       </c>
-      <c r="O15" s="27">
+      <c r="O15" s="25">
         <v>0.07733619763694952</v>
       </c>
     </row>
     <row r="16" spans="8:8">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>3852</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="20" t="s">
         <v>3853</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="27" t="s">
         <v>3854</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="27" t="s">
         <v>3855</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="27" t="s">
         <v>3856</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <v>155.0</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <v>9.0</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="23">
         <v>0.05806451612903226</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="24">
         <v>1008.0</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="24">
         <v>56.0</v>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="25">
         <v>0.05555555555555555</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="24">
         <v>931.0</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="24">
         <v>72.0</v>
       </c>
-      <c r="O16" s="27">
+      <c r="O16" s="25">
         <v>0.07733619763694952</v>
       </c>
     </row>
     <row r="17" spans="8:8">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>3857</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="20" t="s">
         <v>3858</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="27" t="s">
         <v>3859</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="27" t="s">
         <v>3860</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="27" t="s">
         <v>3861</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="22">
         <v>41.5</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="22">
         <v>4.0</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="23">
         <v>0.0963855421686747</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="24">
         <v>265.5</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="24">
         <v>16.0</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="25">
         <v>0.060263653483992465</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="24">
         <v>231.75</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="24">
         <v>17.0</v>
       </c>
-      <c r="O17" s="27">
+      <c r="O17" s="25">
         <v>0.07335490830636461</v>
       </c>
     </row>
     <row r="18" spans="8:8">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>3862</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="20" t="s">
         <v>3863</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="27" t="s">
         <v>3864</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="27" t="s">
         <v>3865</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="27" t="s">
         <v>3866</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="22">
         <v>25.0</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="22">
         <v>3.0</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="23">
         <v>0.12</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="24">
         <v>162.5</v>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="24">
         <v>13.0</v>
       </c>
-      <c r="L18" s="27">
+      <c r="L18" s="25">
         <v>0.08</v>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="24">
         <v>165.75</v>
       </c>
-      <c r="N18" s="26">
+      <c r="N18" s="24">
         <v>19.0</v>
       </c>
-      <c r="O18" s="27">
+      <c r="O18" s="25">
         <v>0.11463046757164404</v>
       </c>
     </row>
     <row r="19" spans="8:8">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>3867</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="20" t="s">
         <v>3868</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="27" t="s">
         <v>3869</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="27" t="s">
         <v>3870</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="27" t="s">
         <v>3871</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="22">
         <v>30.0</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="22">
         <v>1.0</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="23">
         <v>0.03333333333333333</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="24">
         <v>212.0</v>
       </c>
-      <c r="K19" s="26">
+      <c r="K19" s="24">
         <v>9.0</v>
       </c>
-      <c r="L19" s="27">
+      <c r="L19" s="25">
         <v>0.04245283018867924</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="24">
         <v>208.75</v>
       </c>
-      <c r="N19" s="26">
+      <c r="N19" s="24">
         <v>15.0</v>
       </c>
-      <c r="O19" s="27">
+      <c r="O19" s="25">
         <v>0.0718562874251497</v>
       </c>
     </row>
     <row r="20" spans="8:8">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>3872</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="20" t="s">
         <v>3873</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="27" t="s">
         <v>3874</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="27" t="s">
         <v>3875</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="27" t="s">
         <v>3876</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="22">
         <v>58.5</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="22">
         <v>1.0</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="23">
         <v>0.017094017094017096</v>
       </c>
-      <c r="J20" s="26">
+      <c r="J20" s="24">
         <v>368.0</v>
       </c>
-      <c r="K20" s="26">
+      <c r="K20" s="24">
         <v>18.0</v>
       </c>
-      <c r="L20" s="27">
+      <c r="L20" s="25">
         <v>0.04891304347826087</v>
       </c>
-      <c r="M20" s="26">
+      <c r="M20" s="24">
         <v>324.75</v>
       </c>
-      <c r="N20" s="26">
+      <c r="N20" s="24">
         <v>21.0</v>
       </c>
-      <c r="O20" s="27">
+      <c r="O20" s="25">
         <v>0.06466512702078522</v>
       </c>
     </row>
     <row r="21" spans="8:8">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>3877</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="20" t="s">
         <v>3878</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="26" t="s">
         <v>3879</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="26" t="s">
         <v>3880</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="26" t="s">
         <v>3881</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="22">
         <v>30.0</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="22">
         <v>3.0</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="23">
         <v>0.1</v>
       </c>
-      <c r="J21" s="26">
+      <c r="J21" s="24">
         <v>495.0</v>
       </c>
-      <c r="K21" s="26">
+      <c r="K21" s="24">
         <v>37.0</v>
       </c>
-      <c r="L21" s="27">
+      <c r="L21" s="25">
         <v>0.07474747474747474</v>
       </c>
-      <c r="M21" s="26">
+      <c r="M21" s="24">
         <v>399.0</v>
       </c>
-      <c r="N21" s="26">
+      <c r="N21" s="24">
         <v>31.0</v>
       </c>
-      <c r="O21" s="27">
+      <c r="O21" s="25">
         <v>0.07769423558897243</v>
       </c>
     </row>
     <row r="22" spans="8:8">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>3882</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="20" t="s">
         <v>3883</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="27" t="s">
         <v>3884</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="27" t="s">
         <v>3885</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="27" t="s">
         <v>3886</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="22">
         <v>30.0</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="22">
         <v>3.0</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="23">
         <v>0.1</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="24">
         <v>495.0</v>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="24">
         <v>37.0</v>
       </c>
-      <c r="L22" s="27">
+      <c r="L22" s="25">
         <v>0.07474747474747474</v>
       </c>
-      <c r="M22" s="26">
+      <c r="M22" s="24">
         <v>392.0</v>
       </c>
-      <c r="N22" s="26">
+      <c r="N22" s="24">
         <v>31.0</v>
       </c>
-      <c r="O22" s="27">
+      <c r="O22" s="25">
         <v>0.07908163265306123</v>
       </c>
     </row>
     <row r="23" spans="8:8">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="20" t="s">
         <v>3887</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="20" t="s">
         <v>3888</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="27" t="s">
         <v>3889</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="27" t="s">
         <v>3890</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="27" t="s">
         <v>3891</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="22">
         <v>8.5</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="22">
         <v>3.0</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="23">
         <v>0.35294117647058826</v>
       </c>
-      <c r="J23" s="26">
+      <c r="J23" s="24">
         <v>140.5</v>
       </c>
-      <c r="K23" s="26">
+      <c r="K23" s="24">
         <v>11.0</v>
       </c>
-      <c r="L23" s="27">
+      <c r="L23" s="25">
         <v>0.07829181494661921</v>
       </c>
-      <c r="M23" s="26">
+      <c r="M23" s="24">
         <v>108.75</v>
       </c>
-      <c r="N23" s="26">
+      <c r="N23" s="24">
         <v>9.0</v>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="25">
         <v>0.08275862068965517</v>
       </c>
     </row>
     <row r="24" spans="8:8">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>3892</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="20" t="s">
         <v>3893</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="27" t="s">
         <v>3894</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="28" t="s">
         <v>3895</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="27" t="s">
         <v>3896</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="22">
         <v>7.5</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="22">
         <v>0.0</v>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="23">
         <v>0.0</v>
       </c>
-      <c r="J24" s="26">
+      <c r="J24" s="24">
         <v>87.5</v>
       </c>
-      <c r="K24" s="26">
+      <c r="K24" s="24">
         <v>12.0</v>
       </c>
-      <c r="L24" s="27">
+      <c r="L24" s="25">
         <v>0.13714285714285715</v>
       </c>
-      <c r="M24" s="26">
+      <c r="M24" s="24">
         <v>63.75</v>
       </c>
-      <c r="N24" s="26">
+      <c r="N24" s="24">
         <v>12.0</v>
       </c>
-      <c r="O24" s="27">
+      <c r="O24" s="25">
         <v>0.18823529411764706</v>
       </c>
     </row>
     <row r="25" spans="8:8">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>3897</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="20" t="s">
         <v>3898</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="27" t="s">
         <v>3899</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="27" t="s">
         <v>3900</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="27" t="s">
         <v>3901</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="22">
         <v>4.5</v>
       </c>
-      <c r="G25" s="24">
+      <c r="G25" s="22">
         <v>0.0</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="23">
         <v>0.0</v>
       </c>
-      <c r="J25" s="26">
+      <c r="J25" s="24">
         <v>101.0</v>
       </c>
-      <c r="K25" s="26">
+      <c r="K25" s="24">
         <v>6.0</v>
       </c>
-      <c r="L25" s="27">
+      <c r="L25" s="25">
         <v>0.0594059405940594</v>
       </c>
-      <c r="M25" s="26">
+      <c r="M25" s="24">
         <v>77.75</v>
       </c>
-      <c r="N25" s="26">
+      <c r="N25" s="24">
         <v>6.0</v>
       </c>
-      <c r="O25" s="27">
+      <c r="O25" s="25">
         <v>0.07717041800643087</v>
       </c>
     </row>
     <row r="26" spans="8:8">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>3902</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="20" t="s">
         <v>3903</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="27" t="s">
         <v>3904</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="27" t="s">
         <v>3905</v>
       </c>
-      <c r="E26" s="29" t="s">
+      <c r="E26" s="27" t="s">
         <v>3906</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="22">
         <v>9.5</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="22">
         <v>0.0</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="23">
         <v>0.0</v>
       </c>
-      <c r="J26" s="26">
+      <c r="J26" s="24">
         <v>166.0</v>
       </c>
-      <c r="K26" s="26">
+      <c r="K26" s="24">
         <v>8.0</v>
       </c>
-      <c r="L26" s="27">
+      <c r="L26" s="25">
         <v>0.04819277108433735</v>
       </c>
-      <c r="M26" s="26">
+      <c r="M26" s="24">
         <v>141.75</v>
       </c>
-      <c r="N26" s="26">
+      <c r="N26" s="24">
         <v>4.0</v>
       </c>
-      <c r="O26" s="27">
+      <c r="O26" s="25">
         <v>0.02821869488536155</v>
       </c>
     </row>
     <row r="27" spans="8:8">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="20" t="s">
         <v>3907</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="20" t="s">
         <v>3908</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="27" t="s">
         <v>3909</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="27" t="s">
         <v>3910</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="27" t="s">
         <v>3911</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="22">
         <v>0.0</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="22">
         <v>0.0</v>
       </c>
-      <c r="H27" s="25">
+      <c r="H27" s="23">
         <v>0.0</v>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="24">
         <v>0.0</v>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="24">
         <v>0.0</v>
       </c>
-      <c r="L27" s="27">
+      <c r="L27" s="25">
         <v>0.0</v>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="24">
         <v>7.0</v>
       </c>
-      <c r="N27" s="26">
+      <c r="N27" s="24">
         <v>0.0</v>
       </c>
-      <c r="O27" s="27">
+      <c r="O27" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="28" spans="8:8">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="20" t="s">
         <v>3912</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="20" t="s">
         <v>3913</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="27" t="s">
         <v>3914</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="27" t="s">
         <v>3915</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="27" t="s">
         <v>3916</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="22">
         <v>0.0</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="22">
         <v>0.0</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="23">
         <v>0.0</v>
       </c>
-      <c r="J28" s="26">
+      <c r="J28" s="24">
         <v>0.0</v>
       </c>
-      <c r="K28" s="26">
+      <c r="K28" s="24">
         <v>0.0</v>
       </c>
-      <c r="L28" s="27">
+      <c r="L28" s="25">
         <v>0.0</v>
       </c>
-      <c r="M28" s="26">
+      <c r="M28" s="24">
         <v>2.0</v>
       </c>
-      <c r="N28" s="26">
+      <c r="N28" s="24">
         <v>0.0</v>
       </c>
-      <c r="O28" s="27">
+      <c r="O28" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="29" spans="8:8">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="20" t="s">
         <v>3917</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="20" t="s">
         <v>3918</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="27" t="s">
         <v>3919</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="D29" s="27" t="s">
         <v>3920</v>
       </c>
-      <c r="E29" s="29" t="s">
+      <c r="E29" s="27" t="s">
         <v>3921</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="22">
         <v>0.0</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="22">
         <v>0.0</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="23">
         <v>0.0</v>
       </c>
-      <c r="J29" s="26">
+      <c r="J29" s="24">
         <v>0.0</v>
       </c>
-      <c r="K29" s="26">
+      <c r="K29" s="24">
         <v>0.0</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="25">
         <v>0.0</v>
       </c>
-      <c r="M29" s="26">
+      <c r="M29" s="24">
         <v>1.0</v>
       </c>
-      <c r="N29" s="26">
+      <c r="N29" s="24">
         <v>0.0</v>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="30" spans="8:8">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="20" t="s">
         <v>3922</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="20" t="s">
         <v>3923</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="27" t="s">
         <v>3924</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D30" s="27" t="s">
         <v>3925</v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="27" t="s">
         <v>3926</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="22">
         <v>0.0</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="22">
         <v>0.0</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="23">
         <v>0.0</v>
       </c>
-      <c r="J30" s="26">
+      <c r="J30" s="24">
         <v>0.0</v>
       </c>
-      <c r="K30" s="26">
+      <c r="K30" s="24">
         <v>0.0</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="25">
         <v>0.0</v>
       </c>
-      <c r="M30" s="26">
+      <c r="M30" s="24">
         <v>4.0</v>
       </c>
-      <c r="N30" s="26">
+      <c r="N30" s="24">
         <v>0.0</v>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="31" spans="8:8">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="20" t="s">
         <v>3927</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="20" t="s">
         <v>3928</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="26" t="s">
         <v>3929</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="26" t="s">
         <v>3930</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="26" t="s">
         <v>3931</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="22">
         <v>209.0</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="22">
         <v>31.0</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="23">
         <v>0.14832535885167464</v>
       </c>
-      <c r="J31" s="26">
+      <c r="J31" s="24">
         <v>2095.0</v>
       </c>
-      <c r="K31" s="26">
+      <c r="K31" s="24">
         <v>184.0</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="25">
         <v>0.08782816229116945</v>
       </c>
-      <c r="M31" s="26">
+      <c r="M31" s="24">
         <v>1776.0</v>
       </c>
-      <c r="N31" s="26">
+      <c r="N31" s="24">
         <v>149.0</v>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="25">
         <v>0.0838963963963964</v>
       </c>
     </row>
     <row r="32" spans="8:8">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="20" t="s">
         <v>3932</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="20" t="s">
         <v>3933</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="27" t="s">
         <v>3934</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D32" s="27" t="s">
         <v>3935</v>
       </c>
-      <c r="E32" s="29" t="s">
+      <c r="E32" s="27" t="s">
         <v>3936</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="22">
         <v>168.0</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="22">
         <v>25.0</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="23">
         <v>0.1488095238095238</v>
       </c>
-      <c r="J32" s="26">
+      <c r="J32" s="24">
         <v>1549.0</v>
       </c>
-      <c r="K32" s="26">
+      <c r="K32" s="24">
         <v>142.0</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="25">
         <v>0.09167204648160103</v>
       </c>
-      <c r="M32" s="26">
+      <c r="M32" s="24">
         <v>1387.0</v>
       </c>
-      <c r="N32" s="26">
+      <c r="N32" s="24">
         <v>103.0</v>
       </c>
-      <c r="O32" s="27">
+      <c r="O32" s="25">
         <v>0.07426099495313626</v>
       </c>
     </row>
     <row r="33" spans="8:8">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="20" t="s">
         <v>3937</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="20" t="s">
         <v>3938</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="27" t="s">
         <v>3939</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="27" t="s">
         <v>3940</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="27" t="s">
         <v>3941</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="22">
         <v>44.75</v>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="22">
         <v>6.0</v>
       </c>
-      <c r="H33" s="25">
+      <c r="H33" s="23">
         <v>0.1340782122905028</v>
       </c>
-      <c r="J33" s="26">
+      <c r="J33" s="24">
         <v>430.75</v>
       </c>
-      <c r="K33" s="26">
+      <c r="K33" s="24">
         <v>40.0</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="25">
         <v>0.09286128845037725</v>
       </c>
-      <c r="M33" s="26">
+      <c r="M33" s="24">
         <v>381.25</v>
       </c>
-      <c r="N33" s="26">
+      <c r="N33" s="24">
         <v>23.0</v>
       </c>
-      <c r="O33" s="27">
+      <c r="O33" s="25">
         <v>0.06032786885245902</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>3942</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="20" t="s">
         <v>3943</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="27" t="s">
         <v>3944</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="27" t="s">
         <v>3945</v>
       </c>
-      <c r="E34" s="29" t="s">
+      <c r="E34" s="27" t="s">
         <v>3946</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="22">
         <v>32.75</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="22">
         <v>8.0</v>
       </c>
-      <c r="H34" s="25">
+      <c r="H34" s="23">
         <v>0.24427480916030533</v>
       </c>
-      <c r="J34" s="26">
+      <c r="J34" s="24">
         <v>243.25</v>
       </c>
-      <c r="K34" s="26">
+      <c r="K34" s="24">
         <v>40.0</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="25">
         <v>0.1644398766700925</v>
       </c>
-      <c r="M34" s="26">
+      <c r="M34" s="24">
         <v>221.25</v>
       </c>
-      <c r="N34" s="26">
+      <c r="N34" s="24">
         <v>30.0</v>
       </c>
-      <c r="O34" s="27">
+      <c r="O34" s="25">
         <v>0.13559322033898305</v>
       </c>
     </row>
     <row r="35" spans="8:8">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="20" t="s">
         <v>3947</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="20" t="s">
         <v>3948</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="27" t="s">
         <v>3949</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="27" t="s">
         <v>3950</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="27" t="s">
         <v>3951</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="22">
         <v>28.75</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="22">
         <v>2.0</v>
       </c>
-      <c r="H35" s="25">
+      <c r="H35" s="23">
         <v>0.06956521739130435</v>
       </c>
-      <c r="J35" s="26">
+      <c r="J35" s="24">
         <v>356.25</v>
       </c>
-      <c r="K35" s="26">
+      <c r="K35" s="24">
         <v>24.0</v>
       </c>
-      <c r="L35" s="27">
+      <c r="L35" s="25">
         <v>0.06736842105263158</v>
       </c>
-      <c r="M35" s="26">
+      <c r="M35" s="24">
         <v>318.25</v>
       </c>
-      <c r="N35" s="26">
+      <c r="N35" s="24">
         <v>20.0</v>
       </c>
-      <c r="O35" s="27">
+      <c r="O35" s="25">
         <v>0.06284367635506677</v>
       </c>
     </row>
     <row r="36" spans="8:8">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="20" t="s">
         <v>3952</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="20" t="s">
         <v>3953</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="27" t="s">
         <v>3954</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="27" t="s">
         <v>3955</v>
       </c>
-      <c r="E36" s="29" t="s">
+      <c r="E36" s="27" t="s">
         <v>3956</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="22">
         <v>61.75</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="22">
         <v>9.0</v>
       </c>
-      <c r="H36" s="25">
+      <c r="H36" s="23">
         <v>0.145748987854251</v>
       </c>
-      <c r="J36" s="26">
+      <c r="J36" s="24">
         <v>518.75</v>
       </c>
-      <c r="K36" s="26">
+      <c r="K36" s="24">
         <v>38.0</v>
       </c>
-      <c r="L36" s="27">
+      <c r="L36" s="25">
         <v>0.07325301204819278</v>
       </c>
-      <c r="M36" s="26">
+      <c r="M36" s="24">
         <v>466.25</v>
       </c>
-      <c r="N36" s="26">
+      <c r="N36" s="24">
         <v>30.0</v>
       </c>
-      <c r="O36" s="27">
+      <c r="O36" s="25">
         <v>0.064343163538874</v>
       </c>
     </row>
     <row r="37" spans="8:8">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="20" t="s">
         <v>3957</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="20" t="s">
         <v>3958</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="27" t="s">
         <v>3959</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="27" t="s">
         <v>3960</v>
       </c>
-      <c r="E37" s="29" t="s">
+      <c r="E37" s="27" t="s">
         <v>3961</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="22">
         <v>41.0</v>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="22">
         <v>6.0</v>
       </c>
-      <c r="H37" s="25">
+      <c r="H37" s="23">
         <v>0.14634146341463414</v>
       </c>
-      <c r="J37" s="26">
+      <c r="J37" s="24">
         <v>546.0</v>
       </c>
-      <c r="K37" s="26">
+      <c r="K37" s="24">
         <v>42.0</v>
       </c>
-      <c r="L37" s="27">
+      <c r="L37" s="25">
         <v>0.07692307692307693</v>
       </c>
-      <c r="M37" s="26">
+      <c r="M37" s="24">
         <v>389.0</v>
       </c>
-      <c r="N37" s="26">
+      <c r="N37" s="24">
         <v>46.0</v>
       </c>
-      <c r="O37" s="27">
+      <c r="O37" s="25">
         <v>0.11825192802056556</v>
       </c>
     </row>
     <row r="38" spans="8:8">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="20" t="s">
         <v>3962</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="20" t="s">
         <v>3963</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="27" t="s">
         <v>3964</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="27" t="s">
         <v>3965</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="27" t="s">
         <v>3966</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="22">
         <v>11.5</v>
       </c>
-      <c r="G38" s="24">
+      <c r="G38" s="22">
         <v>2.0</v>
       </c>
-      <c r="H38" s="25">
+      <c r="H38" s="23">
         <v>0.17391304347826086</v>
       </c>
-      <c r="J38" s="26">
+      <c r="J38" s="24">
         <v>143.25</v>
       </c>
-      <c r="K38" s="26">
+      <c r="K38" s="24">
         <v>17.0</v>
       </c>
-      <c r="L38" s="27">
+      <c r="L38" s="25">
         <v>0.11867364746945899</v>
       </c>
-      <c r="M38" s="26">
+      <c r="M38" s="24">
         <v>99.25</v>
       </c>
-      <c r="N38" s="26">
+      <c r="N38" s="24">
         <v>15.0</v>
       </c>
-      <c r="O38" s="27">
+      <c r="O38" s="25">
         <v>0.15113350125944586</v>
       </c>
     </row>
     <row r="39" spans="8:8">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="20" t="s">
         <v>3967</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="20" t="s">
         <v>3968</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="27" t="s">
         <v>3969</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="27" t="s">
         <v>3970</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="27" t="s">
         <v>3971</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="22">
         <v>3.5</v>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="22">
         <v>0.0</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="23">
         <v>0.0</v>
       </c>
-      <c r="J39" s="26">
+      <c r="J39" s="24">
         <v>81.25</v>
       </c>
-      <c r="K39" s="26">
+      <c r="K39" s="24">
         <v>7.0</v>
       </c>
-      <c r="L39" s="27">
+      <c r="L39" s="25">
         <v>0.08615384615384615</v>
       </c>
-      <c r="M39" s="26">
+      <c r="M39" s="24">
         <v>63.75</v>
       </c>
-      <c r="N39" s="26">
+      <c r="N39" s="24">
         <v>12.0</v>
       </c>
-      <c r="O39" s="27">
+      <c r="O39" s="25">
         <v>0.18823529411764706</v>
       </c>
     </row>
     <row r="40" spans="8:8">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="20" t="s">
         <v>3972</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="20" t="s">
         <v>3973</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="27" t="s">
         <v>3974</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="27" t="s">
         <v>3975</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="27" t="s">
         <v>3976</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="22">
         <v>9.5</v>
       </c>
-      <c r="G40" s="24">
+      <c r="G40" s="22">
         <v>1.0</v>
       </c>
-      <c r="H40" s="25">
+      <c r="H40" s="23">
         <v>0.10526315789473684</v>
       </c>
-      <c r="J40" s="26">
+      <c r="J40" s="24">
         <v>117.25</v>
       </c>
-      <c r="K40" s="26">
+      <c r="K40" s="24">
         <v>4.0</v>
       </c>
-      <c r="L40" s="27">
+      <c r="L40" s="25">
         <v>0.03411513859275053</v>
       </c>
-      <c r="M40" s="26">
+      <c r="M40" s="24">
         <v>88.75</v>
       </c>
-      <c r="N40" s="26">
+      <c r="N40" s="24">
         <v>5.0</v>
       </c>
-      <c r="O40" s="27">
+      <c r="O40" s="25">
         <v>0.056338028169014086</v>
       </c>
     </row>
     <row r="41" spans="8:8">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="20" t="s">
         <v>3977</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="20" t="s">
         <v>3978</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="27" t="s">
         <v>3979</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="27" t="s">
         <v>3980</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="27" t="s">
         <v>3981</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="22">
         <v>16.5</v>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="22">
         <v>3.0</v>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="23">
         <v>0.18181818181818182</v>
       </c>
-      <c r="J41" s="26">
+      <c r="J41" s="24">
         <v>204.25</v>
       </c>
-      <c r="K41" s="26">
+      <c r="K41" s="24">
         <v>14.0</v>
       </c>
-      <c r="L41" s="27">
+      <c r="L41" s="25">
         <v>0.06854345165238677</v>
       </c>
-      <c r="M41" s="26">
+      <c r="M41" s="24">
         <v>137.25</v>
       </c>
-      <c r="N41" s="26">
+      <c r="N41" s="24">
         <v>14.0</v>
       </c>
-      <c r="O41" s="27">
+      <c r="O41" s="25">
         <v>0.10200364298724955</v>
       </c>
     </row>
     <row r="42" spans="8:8">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="20" t="s">
         <v>3982</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="20" t="s">
         <v>3983</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="26" t="s">
         <v>3984</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="26" t="s">
         <v>3985</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="26" t="s">
         <v>3986</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="22">
         <v>122.0</v>
       </c>
-      <c r="G42" s="24">
+      <c r="G42" s="22">
         <v>8.0</v>
       </c>
-      <c r="H42" s="25">
+      <c r="H42" s="23">
         <v>0.06557377049180328</v>
       </c>
-      <c r="J42" s="26">
+      <c r="J42" s="24">
         <v>1468.0</v>
       </c>
-      <c r="K42" s="26">
+      <c r="K42" s="24">
         <v>124.0</v>
       </c>
-      <c r="L42" s="27">
+      <c r="L42" s="25">
         <v>0.08446866485013624</v>
       </c>
-      <c r="M42" s="26">
+      <c r="M42" s="24">
         <v>1163.0</v>
       </c>
-      <c r="N42" s="26">
+      <c r="N42" s="24">
         <v>92.0</v>
       </c>
-      <c r="O42" s="27">
+      <c r="O42" s="25">
         <v>0.07910576096302666</v>
       </c>
     </row>
     <row r="43" spans="8:8">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="20" t="s">
         <v>3987</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="20" t="s">
         <v>3988</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="27" t="s">
         <v>3989</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D43" s="27" t="s">
         <v>3990</v>
       </c>
-      <c r="E43" s="29" t="s">
+      <c r="E43" s="27" t="s">
         <v>3991</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="22">
         <v>73.0</v>
       </c>
-      <c r="G43" s="24">
+      <c r="G43" s="22">
         <v>6.0</v>
       </c>
-      <c r="H43" s="25">
+      <c r="H43" s="23">
         <v>0.0821917808219178</v>
       </c>
-      <c r="J43" s="26">
+      <c r="J43" s="24">
         <v>861.0</v>
       </c>
-      <c r="K43" s="26">
+      <c r="K43" s="24">
         <v>81.0</v>
       </c>
-      <c r="L43" s="27">
+      <c r="L43" s="25">
         <v>0.09407665505226481</v>
       </c>
-      <c r="M43" s="26">
+      <c r="M43" s="24">
         <v>666.0</v>
       </c>
-      <c r="N43" s="26">
+      <c r="N43" s="24">
         <v>58.0</v>
       </c>
-      <c r="O43" s="27">
+      <c r="O43" s="25">
         <v>0.08708708708708708</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="20" t="s">
         <v>3992</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="20" t="s">
         <v>3993</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="27" t="s">
         <v>3994</v>
       </c>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="27" t="s">
         <v>3995</v>
       </c>
-      <c r="E44" s="29" t="s">
+      <c r="E44" s="27" t="s">
         <v>3996</v>
       </c>
-      <c r="F44" s="24">
+      <c r="F44" s="22">
         <v>22.5</v>
       </c>
-      <c r="G44" s="24">
+      <c r="G44" s="22">
         <v>1.0</v>
       </c>
-      <c r="H44" s="25">
+      <c r="H44" s="23">
         <v>0.044444444444444446</v>
       </c>
-      <c r="J44" s="26">
+      <c r="J44" s="24">
         <v>210.0</v>
       </c>
-      <c r="K44" s="26">
+      <c r="K44" s="24">
         <v>18.0</v>
       </c>
-      <c r="L44" s="27">
+      <c r="L44" s="25">
         <v>0.08571428571428572</v>
       </c>
-      <c r="M44" s="26">
+      <c r="M44" s="24">
         <v>183.0</v>
       </c>
-      <c r="N44" s="26">
+      <c r="N44" s="24">
         <v>13.0</v>
       </c>
-      <c r="O44" s="27">
+      <c r="O44" s="25">
         <v>0.07103825136612021</v>
       </c>
     </row>
     <row r="45" spans="8:8">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="20" t="s">
         <v>3997</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="20" t="s">
         <v>3998</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="27" t="s">
         <v>3999</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D45" s="27" t="s">
         <v>4000</v>
       </c>
-      <c r="E45" s="29" t="s">
+      <c r="E45" s="27" t="s">
         <v>4001</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="22">
         <v>10.5</v>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="22">
         <v>4.0</v>
       </c>
-      <c r="H45" s="25">
+      <c r="H45" s="23">
         <v>0.38095238095238093</v>
       </c>
-      <c r="J45" s="26">
+      <c r="J45" s="24">
         <v>120.0</v>
       </c>
-      <c r="K45" s="26">
+      <c r="K45" s="24">
         <v>28.0</v>
       </c>
-      <c r="L45" s="27">
+      <c r="L45" s="25">
         <v>0.23333333333333334</v>
       </c>
-      <c r="M45" s="26">
+      <c r="M45" s="24">
         <v>85.5</v>
       </c>
-      <c r="N45" s="26">
+      <c r="N45" s="24">
         <v>15.0</v>
       </c>
-      <c r="O45" s="27">
+      <c r="O45" s="25">
         <v>0.17543859649122806</v>
       </c>
     </row>
     <row r="46" spans="8:8">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="20" t="s">
         <v>4002</v>
       </c>
-      <c r="B46" s="22" t="s">
+      <c r="B46" s="20" t="s">
         <v>4003</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" s="27" t="s">
         <v>4004</v>
       </c>
-      <c r="D46" s="29" t="s">
+      <c r="D46" s="27" t="s">
         <v>4005</v>
       </c>
-      <c r="E46" s="29" t="s">
+      <c r="E46" s="27" t="s">
         <v>4006</v>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="22">
         <v>11.5</v>
       </c>
-      <c r="G46" s="24">
+      <c r="G46" s="22">
         <v>0.0</v>
       </c>
-      <c r="H46" s="25">
+      <c r="H46" s="23">
         <v>0.0</v>
       </c>
-      <c r="J46" s="26">
+      <c r="J46" s="24">
         <v>185.0</v>
       </c>
-      <c r="K46" s="26">
+      <c r="K46" s="24">
         <v>4.0</v>
       </c>
-      <c r="L46" s="27">
+      <c r="L46" s="25">
         <v>0.021621621621621623</v>
       </c>
-      <c r="M46" s="26">
+      <c r="M46" s="24">
         <v>141.0</v>
       </c>
-      <c r="N46" s="26">
+      <c r="N46" s="24">
         <v>10.0</v>
       </c>
-      <c r="O46" s="27">
+      <c r="O46" s="25">
         <v>0.07092198581560284</v>
       </c>
     </row>
     <row r="47" spans="8:8">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="20" t="s">
         <v>4007</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="20" t="s">
         <v>4008</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="27" t="s">
         <v>4009</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D47" s="27" t="s">
         <v>4010</v>
       </c>
-      <c r="E47" s="29" t="s">
+      <c r="E47" s="27" t="s">
         <v>4011</v>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="22">
         <v>28.5</v>
       </c>
-      <c r="G47" s="24">
+      <c r="G47" s="22">
         <v>1.0</v>
       </c>
-      <c r="H47" s="25">
+      <c r="H47" s="23">
         <v>0.03508771929824561</v>
       </c>
-      <c r="J47" s="26">
+      <c r="J47" s="24">
         <v>346.0</v>
       </c>
-      <c r="K47" s="26">
+      <c r="K47" s="24">
         <v>31.0</v>
       </c>
-      <c r="L47" s="27">
+      <c r="L47" s="25">
         <v>0.08959537572254335</v>
       </c>
-      <c r="M47" s="26">
+      <c r="M47" s="24">
         <v>256.5</v>
       </c>
-      <c r="N47" s="26">
+      <c r="N47" s="24">
         <v>20.0</v>
       </c>
-      <c r="O47" s="27">
+      <c r="O47" s="25">
         <v>0.07797270955165692</v>
       </c>
     </row>
     <row r="48" spans="8:8">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="20" t="s">
         <v>4012</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="20" t="s">
         <v>4013</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="27" t="s">
         <v>4014</v>
       </c>
-      <c r="D48" s="29" t="s">
+      <c r="D48" s="27" t="s">
         <v>4015</v>
       </c>
-      <c r="E48" s="29" t="s">
+      <c r="E48" s="27" t="s">
         <v>4016</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="22">
         <v>49.0</v>
       </c>
-      <c r="G48" s="24">
+      <c r="G48" s="22">
         <v>2.0</v>
       </c>
-      <c r="H48" s="25">
+      <c r="H48" s="23">
         <v>0.04081632653061224</v>
       </c>
-      <c r="J48" s="26">
+      <c r="J48" s="24">
         <v>607.0</v>
       </c>
-      <c r="K48" s="26">
+      <c r="K48" s="24">
         <v>43.0</v>
       </c>
-      <c r="L48" s="27">
+      <c r="L48" s="25">
         <v>0.07084019769357495</v>
       </c>
-      <c r="M48" s="26">
+      <c r="M48" s="24">
         <v>497.0</v>
       </c>
-      <c r="N48" s="26">
+      <c r="N48" s="24">
         <v>34.0</v>
       </c>
-      <c r="O48" s="27">
+      <c r="O48" s="25">
         <v>0.06841046277665996</v>
       </c>
     </row>
     <row r="49" spans="8:8">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="20" t="s">
         <v>4017</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="20" t="s">
         <v>4018</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="27" t="s">
         <v>4019</v>
       </c>
-      <c r="D49" s="29" t="s">
+      <c r="D49" s="27" t="s">
         <v>4020</v>
       </c>
-      <c r="E49" s="29" t="s">
+      <c r="E49" s="27" t="s">
         <v>4021</v>
       </c>
-      <c r="F49" s="24">
+      <c r="F49" s="22">
         <v>14.333333333333332</v>
       </c>
-      <c r="G49" s="24">
+      <c r="G49" s="22">
         <v>0.0</v>
       </c>
-      <c r="H49" s="25">
+      <c r="H49" s="23">
         <v>0.0</v>
       </c>
-      <c r="J49" s="26">
+      <c r="J49" s="24">
         <v>172.83333333333334</v>
       </c>
-      <c r="K49" s="26">
+      <c r="K49" s="24">
         <v>11.0</v>
       </c>
-      <c r="L49" s="27">
+      <c r="L49" s="25">
         <v>0.06364513018322082</v>
       </c>
-      <c r="M49" s="26">
+      <c r="M49" s="24">
         <v>138.0</v>
       </c>
-      <c r="N49" s="26">
+      <c r="N49" s="24">
         <v>11.0</v>
       </c>
-      <c r="O49" s="27">
+      <c r="O49" s="25">
         <v>0.07971014492753623</v>
       </c>
     </row>
     <row r="50" spans="8:8">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="20" t="s">
         <v>4022</v>
       </c>
-      <c r="B50" s="22" t="s">
+      <c r="B50" s="20" t="s">
         <v>4023</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="27" t="s">
         <v>4024</v>
       </c>
-      <c r="D50" s="29" t="s">
+      <c r="D50" s="27" t="s">
         <v>4025</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="21" t="s">
         <v>4026</v>
       </c>
-      <c r="F50" s="24">
+      <c r="F50" s="22">
         <v>11.333333333333332</v>
       </c>
-      <c r="G50" s="24">
+      <c r="G50" s="22">
         <v>1.0</v>
       </c>
-      <c r="H50" s="25">
+      <c r="H50" s="23">
         <v>0.08823529411764706</v>
       </c>
-      <c r="J50" s="26">
+      <c r="J50" s="24">
         <v>186.83333333333334</v>
       </c>
-      <c r="K50" s="26">
+      <c r="K50" s="24">
         <v>17.0</v>
       </c>
-      <c r="L50" s="27">
+      <c r="L50" s="25">
         <v>0.09099018733273863</v>
       </c>
-      <c r="M50" s="26">
+      <c r="M50" s="24">
         <v>148.0</v>
       </c>
-      <c r="N50" s="26">
+      <c r="N50" s="24">
         <v>7.0</v>
       </c>
-      <c r="O50" s="27">
+      <c r="O50" s="25">
         <v>0.0472972972972973</v>
       </c>
     </row>
     <row r="51" spans="8:8">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="20" t="s">
         <v>4027</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="20" t="s">
         <v>4028</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="27" t="s">
         <v>4029</v>
       </c>
-      <c r="D51" s="29" t="s">
+      <c r="D51" s="27" t="s">
         <v>4030</v>
       </c>
-      <c r="E51" s="29" t="s">
+      <c r="E51" s="27" t="s">
         <v>4031</v>
       </c>
-      <c r="F51" s="24">
+      <c r="F51" s="22">
         <v>23.333333333333332</v>
       </c>
-      <c r="G51" s="24">
+      <c r="G51" s="22">
         <v>1.0</v>
       </c>
-      <c r="H51" s="25">
+      <c r="H51" s="23">
         <v>0.04285714285714286</v>
       </c>
-      <c r="J51" s="26">
+      <c r="J51" s="24">
         <v>247.33333333333334</v>
       </c>
-      <c r="K51" s="26">
+      <c r="K51" s="24">
         <v>15.0</v>
       </c>
-      <c r="L51" s="27">
+      <c r="L51" s="25">
         <v>0.060646900269541774</v>
       </c>
-      <c r="M51" s="26">
+      <c r="M51" s="24">
         <v>211.0</v>
       </c>
-      <c r="N51" s="26">
+      <c r="N51" s="24">
         <v>16.0</v>
       </c>
-      <c r="O51" s="27">
+      <c r="O51" s="25">
         <v>0.07582938388625593</v>
       </c>
     </row>
     <row r="52" spans="8:8">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="20" t="s">
         <v>4032</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B52" s="20" t="s">
         <v>4033</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="26" t="s">
         <v>4034</v>
       </c>
-      <c r="D52" s="28" t="s">
+      <c r="D52" s="26" t="s">
         <v>4035</v>
       </c>
-      <c r="E52" s="28" t="s">
+      <c r="E52" s="26" t="s">
         <v>4036</v>
       </c>
-      <c r="F52" s="24">
+      <c r="F52" s="22">
         <v>517.0</v>
       </c>
-      <c r="G52" s="24">
+      <c r="G52" s="22">
         <v>59.0</v>
       </c>
-      <c r="H52" s="25">
+      <c r="H52" s="23">
         <v>0.11411992263056092</v>
       </c>
-      <c r="J52" s="26">
+      <c r="J52" s="24">
         <v>782.0</v>
       </c>
-      <c r="K52" s="26">
+      <c r="K52" s="24">
         <v>75.0</v>
       </c>
-      <c r="L52" s="27">
+      <c r="L52" s="25">
         <v>0.0959079283887468</v>
       </c>
-      <c r="M52" s="26">
+      <c r="M52" s="24">
         <v>1374.0</v>
       </c>
-      <c r="N52" s="26">
+      <c r="N52" s="24">
         <v>125.0</v>
       </c>
-      <c r="O52" s="27">
+      <c r="O52" s="25">
         <v>0.09097525473071325</v>
       </c>
     </row>
     <row r="53" spans="8:8">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="20" t="s">
         <v>4037</v>
       </c>
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="20" t="s">
         <v>4038</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="27" t="s">
         <v>4039</v>
       </c>
-      <c r="D53" s="29" t="s">
+      <c r="D53" s="27" t="s">
         <v>4040</v>
       </c>
-      <c r="E53" s="29" t="s">
+      <c r="E53" s="27" t="s">
         <v>4041</v>
       </c>
-      <c r="F53" s="24">
+      <c r="F53" s="22">
         <v>517.0</v>
       </c>
-      <c r="G53" s="24">
+      <c r="G53" s="22">
         <v>59.0</v>
       </c>
-      <c r="H53" s="25">
+      <c r="H53" s="23">
         <v>0.11411992263056092</v>
       </c>
-      <c r="J53" s="26">
+      <c r="J53" s="24">
         <v>782.0</v>
       </c>
-      <c r="K53" s="26">
+      <c r="K53" s="24">
         <v>75.0</v>
       </c>
-      <c r="L53" s="27">
+      <c r="L53" s="25">
         <v>0.0959079283887468</v>
       </c>
-      <c r="M53" s="26">
+      <c r="M53" s="24">
         <v>1374.0</v>
       </c>
-      <c r="N53" s="26">
+      <c r="N53" s="24">
         <v>125.0</v>
       </c>
-      <c r="O53" s="27">
+      <c r="O53" s="25">
         <v>0.09097525473071325</v>
       </c>
     </row>
     <row r="54" spans="8:8">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="20" t="s">
         <v>4042</v>
       </c>
-      <c r="B54" s="22" t="s">
+      <c r="B54" s="20" t="s">
         <v>4043</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="27" t="s">
         <v>4044</v>
       </c>
-      <c r="D54" s="29" t="s">
+      <c r="D54" s="27" t="s">
         <v>4045</v>
       </c>
-      <c r="E54" s="29" t="s">
+      <c r="E54" s="27" t="s">
         <v>4046</v>
       </c>
-      <c r="F54" s="24">
+      <c r="F54" s="22">
         <v>170.25</v>
       </c>
-      <c r="G54" s="24">
+      <c r="G54" s="22">
         <v>20.0</v>
       </c>
-      <c r="H54" s="25">
+      <c r="H54" s="23">
         <v>0.11747430249632893</v>
       </c>
-      <c r="J54" s="26">
+      <c r="J54" s="24">
         <v>233.75</v>
       </c>
-      <c r="K54" s="26">
+      <c r="K54" s="24">
         <v>24.0</v>
       </c>
-      <c r="L54" s="27">
+      <c r="L54" s="25">
         <v>0.10267379679144385</v>
       </c>
-      <c r="M54" s="26">
+      <c r="M54" s="24">
         <v>415.0</v>
       </c>
-      <c r="N54" s="26">
+      <c r="N54" s="24">
         <v>28.0</v>
       </c>
-      <c r="O54" s="27">
+      <c r="O54" s="25">
         <v>0.06746987951807229</v>
       </c>
     </row>
     <row r="55" spans="8:8">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="20" t="s">
         <v>4047</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="20" t="s">
         <v>4048</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="27" t="s">
         <v>4049</v>
       </c>
-      <c r="D55" s="29" t="s">
+      <c r="D55" s="27" t="s">
         <v>4050</v>
       </c>
-      <c r="E55" s="29" t="s">
+      <c r="E55" s="27" t="s">
         <v>4051</v>
       </c>
-      <c r="F55" s="24">
+      <c r="F55" s="22">
         <v>67.25</v>
       </c>
-      <c r="G55" s="24">
+      <c r="G55" s="22">
         <v>12.0</v>
       </c>
-      <c r="H55" s="25">
+      <c r="H55" s="23">
         <v>0.17843866171003717</v>
       </c>
-      <c r="J55" s="26">
+      <c r="J55" s="24">
         <v>115.75</v>
       </c>
-      <c r="K55" s="26">
+      <c r="K55" s="24">
         <v>21.0</v>
       </c>
-      <c r="L55" s="27">
+      <c r="L55" s="25">
         <v>0.18142548596112312</v>
       </c>
-      <c r="M55" s="26">
+      <c r="M55" s="24">
         <v>167.5</v>
       </c>
-      <c r="N55" s="26">
+      <c r="N55" s="24">
         <v>27.0</v>
       </c>
-      <c r="O55" s="27">
+      <c r="O55" s="25">
         <v>0.16119402985074627</v>
       </c>
     </row>
     <row r="56" spans="8:8">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="20" t="s">
         <v>4052</v>
       </c>
-      <c r="B56" s="22" t="s">
+      <c r="B56" s="20" t="s">
         <v>4053</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="27" t="s">
         <v>4054</v>
       </c>
-      <c r="D56" s="29" t="s">
+      <c r="D56" s="27" t="s">
         <v>4055</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="27" t="s">
         <v>4056</v>
       </c>
-      <c r="F56" s="24">
+      <c r="F56" s="22">
         <v>92.25</v>
       </c>
-      <c r="G56" s="24">
+      <c r="G56" s="22">
         <v>5.0</v>
       </c>
-      <c r="H56" s="25">
+      <c r="H56" s="23">
         <v>0.05420054200542006</v>
       </c>
-      <c r="J56" s="26">
+      <c r="J56" s="24">
         <v>158.75</v>
       </c>
-      <c r="K56" s="26">
+      <c r="K56" s="24">
         <v>6.0</v>
       </c>
-      <c r="L56" s="27">
+      <c r="L56" s="25">
         <v>0.03779527559055118</v>
       </c>
-      <c r="M56" s="26">
+      <c r="M56" s="24">
         <v>256.0</v>
       </c>
-      <c r="N56" s="26">
+      <c r="N56" s="24">
         <v>12.0</v>
       </c>
-      <c r="O56" s="27">
+      <c r="O56" s="25">
         <v>0.046875</v>
       </c>
     </row>
     <row r="57" spans="8:8">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="20" t="s">
         <v>4057</v>
       </c>
-      <c r="B57" s="22" t="s">
+      <c r="B57" s="20" t="s">
         <v>4058</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="27" t="s">
         <v>4059</v>
       </c>
-      <c r="D57" s="29" t="s">
+      <c r="D57" s="27" t="s">
         <v>4060</v>
       </c>
-      <c r="E57" s="29" t="s">
+      <c r="E57" s="27" t="s">
         <v>4061</v>
       </c>
-      <c r="F57" s="24">
+      <c r="F57" s="22">
         <v>187.25</v>
       </c>
-      <c r="G57" s="24">
+      <c r="G57" s="22">
         <v>22.0</v>
       </c>
-      <c r="H57" s="25">
+      <c r="H57" s="23">
         <v>0.11748998664886515</v>
       </c>
-      <c r="J57" s="26">
+      <c r="J57" s="24">
         <v>273.75</v>
       </c>
-      <c r="K57" s="26">
+      <c r="K57" s="24">
         <v>24.0</v>
       </c>
-      <c r="L57" s="27">
+      <c r="L57" s="25">
         <v>0.08767123287671233</v>
       </c>
-      <c r="M57" s="26">
+      <c r="M57" s="24">
         <v>535.5</v>
       </c>
-      <c r="N57" s="26">
+      <c r="N57" s="24">
         <v>58.0</v>
       </c>
-      <c r="O57" s="27">
+      <c r="O57" s="25">
         <v>0.10830999066293184</v>
       </c>
     </row>
     <row r="58" spans="8:8">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="20" t="s">
         <v>4062</v>
       </c>
-      <c r="B58" s="22" t="s">
+      <c r="B58" s="20" t="s">
         <v>4063</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="C58" s="26" t="s">
         <v>4064</v>
       </c>
-      <c r="D58" s="28" t="s">
+      <c r="D58" s="26" t="s">
         <v>4065</v>
       </c>
-      <c r="E58" s="28" t="s">
+      <c r="E58" s="26" t="s">
         <v>4066</v>
       </c>
-      <c r="F58" s="24">
+      <c r="F58" s="22">
         <v>189.0</v>
       </c>
-      <c r="G58" s="24">
+      <c r="G58" s="22">
         <v>30.0</v>
       </c>
-      <c r="H58" s="25">
+      <c r="H58" s="23">
         <v>0.15873015873015872</v>
       </c>
-      <c r="J58" s="26">
+      <c r="J58" s="24">
         <v>514.0</v>
       </c>
-      <c r="K58" s="26">
+      <c r="K58" s="24">
         <v>51.0</v>
       </c>
-      <c r="L58" s="27">
+      <c r="L58" s="25">
         <v>0.09922178988326848</v>
       </c>
-      <c r="M58" s="26">
+      <c r="M58" s="24">
         <v>802.0</v>
       </c>
-      <c r="N58" s="26">
+      <c r="N58" s="24">
         <v>75.0</v>
       </c>
-      <c r="O58" s="27">
+      <c r="O58" s="25">
         <v>0.09351620947630923</v>
       </c>
     </row>
     <row r="59" spans="8:8">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="20" t="s">
         <v>4067</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="B59" s="20" t="s">
         <v>4068</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="27" t="s">
         <v>4069</v>
       </c>
-      <c r="D59" s="29" t="s">
+      <c r="D59" s="27" t="s">
         <v>4070</v>
       </c>
-      <c r="E59" s="29" t="s">
+      <c r="E59" s="27" t="s">
         <v>4071</v>
       </c>
-      <c r="F59" s="24">
+      <c r="F59" s="22">
         <v>162.0</v>
       </c>
-      <c r="G59" s="24">
+      <c r="G59" s="22">
         <v>25.0</v>
       </c>
-      <c r="H59" s="25">
+      <c r="H59" s="23">
         <v>0.15432098765432098</v>
       </c>
-      <c r="J59" s="26">
+      <c r="J59" s="24">
         <v>499.0</v>
       </c>
-      <c r="K59" s="26">
+      <c r="K59" s="24">
         <v>50.0</v>
       </c>
-      <c r="L59" s="27">
+      <c r="L59" s="25">
         <v>0.10020040080160321</v>
       </c>
-      <c r="M59" s="26">
+      <c r="M59" s="24">
         <v>763.0</v>
       </c>
-      <c r="N59" s="26">
+      <c r="N59" s="24">
         <v>68.0</v>
       </c>
-      <c r="O59" s="27">
+      <c r="O59" s="25">
         <v>0.0891218872870249</v>
       </c>
     </row>
     <row r="60" spans="8:8">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="20" t="s">
         <v>4072</v>
       </c>
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="20" t="s">
         <v>4073</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="27" t="s">
         <v>4074</v>
       </c>
-      <c r="D60" s="29" t="s">
+      <c r="D60" s="27" t="s">
         <v>4075</v>
       </c>
-      <c r="E60" s="29" t="s">
+      <c r="E60" s="27" t="s">
         <v>4076</v>
       </c>
-      <c r="F60" s="24">
+      <c r="F60" s="22">
         <v>43.75</v>
       </c>
-      <c r="G60" s="24">
+      <c r="G60" s="22">
         <v>11.0</v>
       </c>
-      <c r="H60" s="25">
+      <c r="H60" s="23">
         <v>0.25142857142857145</v>
       </c>
-      <c r="J60" s="26">
+      <c r="J60" s="24">
         <v>149.75</v>
       </c>
-      <c r="K60" s="26">
+      <c r="K60" s="24">
         <v>16.0</v>
       </c>
-      <c r="L60" s="27">
+      <c r="L60" s="25">
         <v>0.10684474123539232</v>
       </c>
-      <c r="M60" s="26">
+      <c r="M60" s="24">
         <v>234.75</v>
       </c>
-      <c r="N60" s="26">
+      <c r="N60" s="24">
         <v>25.0</v>
       </c>
-      <c r="O60" s="27">
+      <c r="O60" s="25">
         <v>0.10649627263045794</v>
       </c>
     </row>
     <row r="61" spans="8:8">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="20" t="s">
         <v>4077</v>
       </c>
-      <c r="B61" s="22" t="s">
+      <c r="B61" s="20" t="s">
         <v>4078</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="27" t="s">
         <v>4079</v>
       </c>
-      <c r="D61" s="29" t="s">
+      <c r="D61" s="27" t="s">
         <v>4080</v>
       </c>
-      <c r="E61" s="29" t="s">
+      <c r="E61" s="27" t="s">
         <v>4081</v>
       </c>
-      <c r="F61" s="24">
+      <c r="F61" s="22">
         <v>23.75</v>
       </c>
-      <c r="G61" s="24">
+      <c r="G61" s="22">
         <v>3.0</v>
       </c>
-      <c r="H61" s="25">
+      <c r="H61" s="23">
         <v>0.12631578947368421</v>
       </c>
-      <c r="J61" s="26">
+      <c r="J61" s="24">
         <v>54.75</v>
       </c>
-      <c r="K61" s="26">
+      <c r="K61" s="24">
         <v>10.0</v>
       </c>
-      <c r="L61" s="27">
+      <c r="L61" s="25">
         <v>0.182648401826484</v>
       </c>
-      <c r="M61" s="26">
+      <c r="M61" s="24">
         <v>116.25</v>
       </c>
-      <c r="N61" s="26">
+      <c r="N61" s="24">
         <v>19.0</v>
       </c>
-      <c r="O61" s="27">
+      <c r="O61" s="25">
         <v>0.16344086021505377</v>
       </c>
     </row>
     <row r="62" spans="8:8">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="20" t="s">
         <v>4082</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="20" t="s">
         <v>4083</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="27" t="s">
         <v>4084</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="D62" s="27" t="s">
         <v>4085</v>
       </c>
-      <c r="E62" s="29" t="s">
+      <c r="E62" s="27" t="s">
         <v>4086</v>
       </c>
-      <c r="F62" s="24">
+      <c r="F62" s="22">
         <v>35.75</v>
       </c>
-      <c r="G62" s="24">
+      <c r="G62" s="22">
         <v>4.0</v>
       </c>
-      <c r="H62" s="25">
+      <c r="H62" s="23">
         <v>0.11188811188811189</v>
       </c>
-      <c r="J62" s="26">
+      <c r="J62" s="24">
         <v>122.75</v>
       </c>
-      <c r="K62" s="26">
+      <c r="K62" s="24">
         <v>12.0</v>
       </c>
-      <c r="L62" s="27">
+      <c r="L62" s="25">
         <v>0.09775967413441955</v>
       </c>
-      <c r="M62" s="26">
+      <c r="M62" s="24">
         <v>160.75</v>
       </c>
-      <c r="N62" s="26">
+      <c r="N62" s="24">
         <v>11.0</v>
       </c>
-      <c r="O62" s="27">
+      <c r="O62" s="25">
         <v>0.06842923794712286</v>
       </c>
     </row>
     <row r="63" spans="8:8">
-      <c r="A63" s="22" t="s">
+      <c r="A63" s="20" t="s">
         <v>4087</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="20" t="s">
         <v>4088</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="27" t="s">
         <v>4089</v>
       </c>
-      <c r="D63" s="29" t="s">
+      <c r="D63" s="27" t="s">
         <v>4090</v>
       </c>
-      <c r="E63" s="29" t="s">
+      <c r="E63" s="27" t="s">
         <v>4091</v>
       </c>
-      <c r="F63" s="24">
+      <c r="F63" s="22">
         <v>58.75</v>
       </c>
-      <c r="G63" s="24">
+      <c r="G63" s="22">
         <v>7.0</v>
       </c>
-      <c r="H63" s="25">
+      <c r="H63" s="23">
         <v>0.11914893617021277</v>
       </c>
-      <c r="J63" s="26">
+      <c r="J63" s="24">
         <v>171.75</v>
       </c>
-      <c r="K63" s="26">
+      <c r="K63" s="24">
         <v>12.0</v>
       </c>
-      <c r="L63" s="27">
+      <c r="L63" s="25">
         <v>0.06986899563318777</v>
       </c>
-      <c r="M63" s="26">
+      <c r="M63" s="24">
         <v>251.25</v>
       </c>
-      <c r="N63" s="26">
+      <c r="N63" s="24">
         <v>13.0</v>
       </c>
-      <c r="O63" s="27">
+      <c r="O63" s="25">
         <v>0.051741293532338306</v>
       </c>
     </row>
     <row r="64" spans="8:8">
-      <c r="A64" s="22" t="s">
+      <c r="A64" s="20" t="s">
         <v>4092</v>
       </c>
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="20" t="s">
         <v>4093</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="27" t="s">
         <v>4094</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="D64" s="27" t="s">
         <v>4095</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="27" t="s">
         <v>4096</v>
       </c>
-      <c r="F64" s="24">
+      <c r="F64" s="22">
         <v>27.0</v>
       </c>
-      <c r="G64" s="24">
+      <c r="G64" s="22">
         <v>5.0</v>
       </c>
-      <c r="H64" s="25">
+      <c r="H64" s="23">
         <v>0.18518518518518517</v>
       </c>
-      <c r="J64" s="26">
+      <c r="J64" s="24">
         <v>15.0</v>
       </c>
-      <c r="K64" s="26">
+      <c r="K64" s="24">
         <v>1.0</v>
       </c>
-      <c r="L64" s="27">
+      <c r="L64" s="25">
         <v>0.06666666666666667</v>
       </c>
-      <c r="M64" s="26">
+      <c r="M64" s="24">
         <v>39.0</v>
       </c>
-      <c r="N64" s="26">
+      <c r="N64" s="24">
         <v>7.0</v>
       </c>
-      <c r="O64" s="27">
+      <c r="O64" s="25">
         <v>0.1794871794871795</v>
       </c>
     </row>
     <row r="65" spans="8:8">
-      <c r="A65" s="22" t="s">
+      <c r="A65" s="20" t="s">
         <v>4097</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="20" t="s">
         <v>4098</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="27" t="s">
         <v>4099</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D65" s="27" t="s">
         <v>4100</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="27" t="s">
         <v>4101</v>
       </c>
-      <c r="F65" s="24">
+      <c r="F65" s="22">
         <v>9.0</v>
       </c>
-      <c r="G65" s="24">
+      <c r="G65" s="22">
         <v>1.0</v>
       </c>
-      <c r="H65" s="25">
+      <c r="H65" s="23">
         <v>0.1111111111111111</v>
       </c>
-      <c r="J65" s="26">
+      <c r="J65" s="24">
         <v>3.0</v>
       </c>
-      <c r="K65" s="26">
+      <c r="K65" s="24">
         <v>0.0</v>
       </c>
-      <c r="L65" s="27">
+      <c r="L65" s="25">
         <v>0.0</v>
       </c>
-      <c r="M65" s="26">
+      <c r="M65" s="24">
         <v>11.166666666666666</v>
       </c>
-      <c r="N65" s="26">
+      <c r="N65" s="24">
         <v>1.0</v>
       </c>
-      <c r="O65" s="27">
+      <c r="O65" s="25">
         <v>0.08955223880597016</v>
       </c>
     </row>
     <row r="66" spans="8:8">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="20" t="s">
         <v>4102</v>
       </c>
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="20" t="s">
         <v>4103</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="27" t="s">
         <v>4104</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="27" t="s">
         <v>4105</v>
       </c>
-      <c r="E66" s="29" t="s">
+      <c r="E66" s="27" t="s">
         <v>4106</v>
       </c>
-      <c r="F66" s="24">
+      <c r="F66" s="22">
         <v>10.0</v>
       </c>
-      <c r="G66" s="24">
+      <c r="G66" s="22">
         <v>3.0</v>
       </c>
-      <c r="H66" s="25">
+      <c r="H66" s="23">
         <v>0.3</v>
       </c>
-      <c r="J66" s="26">
+      <c r="J66" s="24">
         <v>3.0</v>
       </c>
-      <c r="K66" s="26">
+      <c r="K66" s="24">
         <v>0.0</v>
       </c>
-      <c r="L66" s="27">
+      <c r="L66" s="25">
         <v>0.0</v>
       </c>
-      <c r="M66" s="26">
+      <c r="M66" s="24">
         <v>12.166666666666666</v>
       </c>
-      <c r="N66" s="26">
+      <c r="N66" s="24">
         <v>3.0</v>
       </c>
-      <c r="O66" s="27">
+      <c r="O66" s="25">
         <v>0.24657534246575344</v>
       </c>
     </row>
     <row r="67" spans="8:8">
-      <c r="A67" s="22" t="s">
+      <c r="A67" s="20" t="s">
         <v>4107</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="20" t="s">
         <v>4108</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="27" t="s">
         <v>4109</v>
       </c>
-      <c r="D67" s="29" t="s">
+      <c r="D67" s="27" t="s">
         <v>4110</v>
       </c>
-      <c r="E67" s="29" t="s">
+      <c r="E67" s="27" t="s">
         <v>4111</v>
       </c>
-      <c r="F67" s="24">
+      <c r="F67" s="22">
         <v>8.0</v>
       </c>
-      <c r="G67" s="24">
+      <c r="G67" s="22">
         <v>1.0</v>
       </c>
-      <c r="H67" s="25">
+      <c r="H67" s="23">
         <v>0.125</v>
       </c>
-      <c r="J67" s="26">
+      <c r="J67" s="24">
         <v>9.0</v>
       </c>
-      <c r="K67" s="26">
+      <c r="K67" s="24">
         <v>1.0</v>
       </c>
-      <c r="L67" s="27">
+      <c r="L67" s="25">
         <v>0.1111111111111111</v>
       </c>
-      <c r="M67" s="26">
+      <c r="M67" s="24">
         <v>15.666666666666666</v>
       </c>
-      <c r="N67" s="26">
+      <c r="N67" s="24">
         <v>3.0</v>
       </c>
-      <c r="O67" s="27">
+      <c r="O67" s="25">
         <v>0.19148936170212766</v>
       </c>
     </row>
     <row r="68" spans="8:8">
-      <c r="A68" s="22" t="s">
+      <c r="A68" s="20" t="s">
         <v>4112</v>
       </c>
-      <c r="B68" s="22" t="s">
+      <c r="B68" s="20" t="s">
         <v>4113</v>
       </c>
-      <c r="C68" s="28" t="s">
+      <c r="C68" s="26" t="s">
         <v>4114</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D68" s="26" t="s">
         <v>4115</v>
       </c>
-      <c r="E68" s="28" t="s">
+      <c r="E68" s="26" t="s">
         <v>4116</v>
       </c>
-      <c r="F68" s="24">
+      <c r="F68" s="22">
         <v>371.0</v>
       </c>
-      <c r="G68" s="24">
+      <c r="G68" s="22">
         <v>44.0</v>
       </c>
-      <c r="H68" s="25">
+      <c r="H68" s="23">
         <v>0.11859838274932614</v>
       </c>
-      <c r="J68" s="26">
+      <c r="J68" s="24">
         <v>1292.0</v>
       </c>
-      <c r="K68" s="26">
+      <c r="K68" s="24">
         <v>140.0</v>
       </c>
-      <c r="L68" s="27">
+      <c r="L68" s="25">
         <v>0.10835913312693499</v>
       </c>
-      <c r="M68" s="26">
+      <c r="M68" s="24">
         <v>1289.0</v>
       </c>
-      <c r="N68" s="26">
+      <c r="N68" s="24">
         <v>170.0</v>
       </c>
-      <c r="O68" s="27">
+      <c r="O68" s="25">
         <v>0.13188518231186966</v>
       </c>
     </row>
     <row r="69" spans="8:8">
-      <c r="A69" s="22" t="s">
+      <c r="A69" s="20" t="s">
         <v>4117</v>
       </c>
-      <c r="B69" s="22" t="s">
+      <c r="B69" s="20" t="s">
         <v>4118</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="27" t="s">
         <v>4119</v>
       </c>
-      <c r="D69" s="29" t="s">
+      <c r="D69" s="27" t="s">
         <v>4120</v>
       </c>
-      <c r="E69" s="29" t="s">
+      <c r="E69" s="27" t="s">
         <v>4121</v>
       </c>
-      <c r="F69" s="24">
+      <c r="F69" s="22">
         <v>360.0</v>
       </c>
-      <c r="G69" s="24">
+      <c r="G69" s="22">
         <v>42.0</v>
       </c>
-      <c r="H69" s="25">
+      <c r="H69" s="23">
         <v>0.11666666666666667</v>
       </c>
-      <c r="J69" s="26">
+      <c r="J69" s="24">
         <v>1249.0</v>
       </c>
-      <c r="K69" s="26">
+      <c r="K69" s="24">
         <v>132.0</v>
       </c>
-      <c r="L69" s="27">
+      <c r="L69" s="25">
         <v>0.10568454763811048</v>
       </c>
-      <c r="M69" s="26">
+      <c r="M69" s="24">
         <v>1264.0</v>
       </c>
-      <c r="N69" s="26">
+      <c r="N69" s="24">
         <v>165.0</v>
       </c>
-      <c r="O69" s="27">
+      <c r="O69" s="25">
         <v>0.1305379746835443</v>
       </c>
     </row>
     <row r="70" spans="8:8">
-      <c r="A70" s="22" t="s">
+      <c r="A70" s="20" t="s">
         <v>4122</v>
       </c>
-      <c r="B70" s="22" t="s">
+      <c r="B70" s="20" t="s">
         <v>4123</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="27" t="s">
         <v>4124</v>
       </c>
-      <c r="D70" s="29" t="s">
+      <c r="D70" s="27" t="s">
         <v>4125</v>
       </c>
-      <c r="E70" s="29" t="s">
+      <c r="E70" s="27" t="s">
         <v>4126</v>
       </c>
-      <c r="F70" s="24">
+      <c r="F70" s="22">
         <v>119.33333333333333</v>
       </c>
-      <c r="G70" s="24">
+      <c r="G70" s="22">
         <v>10.0</v>
       </c>
-      <c r="H70" s="25">
+      <c r="H70" s="23">
         <v>0.08379888268156425</v>
       </c>
-      <c r="J70" s="26">
+      <c r="J70" s="24">
         <v>438.5</v>
       </c>
-      <c r="K70" s="26">
+      <c r="K70" s="24">
         <v>67.0</v>
       </c>
-      <c r="L70" s="27">
+      <c r="L70" s="25">
         <v>0.15279361459521096</v>
       </c>
-      <c r="M70" s="26">
+      <c r="M70" s="24">
         <v>452.6666666666667</v>
       </c>
-      <c r="N70" s="26">
+      <c r="N70" s="24">
         <v>69.0</v>
       </c>
-      <c r="O70" s="27">
+      <c r="O70" s="25">
         <v>0.1524300441826215</v>
       </c>
     </row>
     <row r="71" spans="8:8">
-      <c r="A71" s="22" t="s">
+      <c r="A71" s="20" t="s">
         <v>4127</v>
       </c>
-      <c r="B71" s="22" t="s">
+      <c r="B71" s="20" t="s">
         <v>4128</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="27" t="s">
         <v>4129</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D71" s="27" t="s">
         <v>4130</v>
       </c>
-      <c r="E71" s="29" t="s">
+      <c r="E71" s="27" t="s">
         <v>4131</v>
       </c>
-      <c r="F71" s="24">
+      <c r="F71" s="22">
         <v>125.33333333333333</v>
       </c>
-      <c r="G71" s="24">
+      <c r="G71" s="22">
         <v>27.0</v>
       </c>
-      <c r="H71" s="25">
+      <c r="H71" s="23">
         <v>0.21542553191489364</v>
       </c>
-      <c r="J71" s="26">
+      <c r="J71" s="24">
         <v>350.5</v>
       </c>
-      <c r="K71" s="26">
+      <c r="K71" s="24">
         <v>30.0</v>
       </c>
-      <c r="L71" s="27">
+      <c r="L71" s="25">
         <v>0.08559201141226819</v>
       </c>
-      <c r="M71" s="26">
+      <c r="M71" s="24">
         <v>372.6666666666667</v>
       </c>
-      <c r="N71" s="26">
+      <c r="N71" s="24">
         <v>70.0</v>
       </c>
-      <c r="O71" s="27">
+      <c r="O71" s="25">
         <v>0.1878354203935599</v>
       </c>
     </row>
     <row r="72" spans="8:8">
-      <c r="A72" s="22" t="s">
+      <c r="A72" s="20" t="s">
         <v>4132</v>
       </c>
-      <c r="B72" s="22" t="s">
+      <c r="B72" s="20" t="s">
         <v>4133</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="27" t="s">
         <v>4134</v>
       </c>
-      <c r="D72" s="29" t="s">
+      <c r="D72" s="27" t="s">
         <v>4135</v>
       </c>
-      <c r="E72" s="29" t="s">
+      <c r="E72" s="27" t="s">
         <v>4136</v>
       </c>
-      <c r="F72" s="24">
+      <c r="F72" s="22">
         <v>115.33333333333333</v>
       </c>
-      <c r="G72" s="24">
+      <c r="G72" s="22">
         <v>5.0</v>
       </c>
-      <c r="H72" s="25">
+      <c r="H72" s="23">
         <v>0.04335260115606936</v>
       </c>
-      <c r="J72" s="26">
+      <c r="J72" s="24">
         <v>460.0</v>
       </c>
-      <c r="K72" s="26">
+      <c r="K72" s="24">
         <v>35.0</v>
       </c>
-      <c r="L72" s="27">
+      <c r="L72" s="25">
         <v>0.07608695652173914</v>
       </c>
-      <c r="M72" s="26">
+      <c r="M72" s="24">
         <v>438.6666666666667</v>
       </c>
-      <c r="N72" s="26">
+      <c r="N72" s="24">
         <v>26.0</v>
       </c>
-      <c r="O72" s="27">
+      <c r="O72" s="25">
         <v>0.05927051671732522</v>
       </c>
     </row>
     <row r="73" spans="8:8">
-      <c r="A73" s="22" t="s">
+      <c r="A73" s="20" t="s">
         <v>4137</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="20" t="s">
         <v>4138</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="27" t="s">
         <v>4139</v>
       </c>
-      <c r="D73" s="29" t="s">
+      <c r="D73" s="27" t="s">
         <v>4140</v>
       </c>
-      <c r="E73" s="29" t="s">
+      <c r="E73" s="27" t="s">
         <v>4141</v>
       </c>
-      <c r="F73" s="24">
+      <c r="F73" s="22">
         <v>11.0</v>
       </c>
-      <c r="G73" s="24">
+      <c r="G73" s="22">
         <v>2.0</v>
       </c>
-      <c r="H73" s="25">
+      <c r="H73" s="23">
         <v>0.18181818181818182</v>
       </c>
-      <c r="J73" s="26">
+      <c r="J73" s="24">
         <v>43.0</v>
       </c>
-      <c r="K73" s="26">
+      <c r="K73" s="24">
         <v>8.0</v>
       </c>
-      <c r="L73" s="27">
+      <c r="L73" s="25">
         <v>0.18604651162790697</v>
       </c>
-      <c r="M73" s="26">
+      <c r="M73" s="24">
         <v>25.0</v>
       </c>
-      <c r="N73" s="26">
+      <c r="N73" s="24">
         <v>5.0</v>
       </c>
-      <c r="O73" s="27">
+      <c r="O73" s="25">
         <v>0.2</v>
       </c>
     </row>
     <row r="74" spans="8:8">
-      <c r="A74" s="22" t="s">
+      <c r="A74" s="20" t="s">
         <v>4142</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="20" t="s">
         <v>4143</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="27" t="s">
         <v>4144</v>
       </c>
-      <c r="D74" s="29" t="s">
+      <c r="D74" s="27" t="s">
         <v>4145</v>
       </c>
-      <c r="E74" s="29" t="s">
+      <c r="E74" s="27" t="s">
         <v>4146</v>
       </c>
-      <c r="F74" s="24">
+      <c r="F74" s="22">
         <v>2.0</v>
       </c>
-      <c r="G74" s="24">
+      <c r="G74" s="22">
         <v>0.0</v>
       </c>
-      <c r="H74" s="25">
+      <c r="H74" s="23">
         <v>0.0</v>
       </c>
-      <c r="J74" s="26">
+      <c r="J74" s="24">
         <v>14.666666666666666</v>
       </c>
-      <c r="K74" s="26">
+      <c r="K74" s="24">
         <v>3.0</v>
       </c>
-      <c r="L74" s="27">
+      <c r="L74" s="25">
         <v>0.20454545454545456</v>
       </c>
-      <c r="M74" s="26">
+      <c r="M74" s="24">
         <v>8.0</v>
       </c>
-      <c r="N74" s="26">
+      <c r="N74" s="24">
         <v>1.0</v>
       </c>
-      <c r="O74" s="27">
+      <c r="O74" s="25">
         <v>0.125</v>
       </c>
     </row>
     <row r="75" spans="8:8">
-      <c r="A75" s="22" t="s">
+      <c r="A75" s="20" t="s">
         <v>4147</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" s="20" t="s">
         <v>4148</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="27" t="s">
         <v>4149</v>
       </c>
-      <c r="D75" s="29" t="s">
+      <c r="D75" s="27" t="s">
         <v>4150</v>
       </c>
-      <c r="E75" s="29" t="s">
+      <c r="E75" s="27" t="s">
         <v>4151</v>
       </c>
-      <c r="F75" s="24">
+      <c r="F75" s="22">
         <v>3.0</v>
       </c>
-      <c r="G75" s="24">
+      <c r="G75" s="22">
         <v>0.0</v>
       </c>
-      <c r="H75" s="25">
+      <c r="H75" s="23">
         <v>0.0</v>
       </c>
-      <c r="J75" s="26">
+      <c r="J75" s="24">
         <v>11.666666666666666</v>
       </c>
-      <c r="K75" s="26">
+      <c r="K75" s="24">
         <v>2.0</v>
       </c>
-      <c r="L75" s="27">
+      <c r="L75" s="25">
         <v>0.17142857142857143</v>
       </c>
-      <c r="M75" s="26">
+      <c r="M75" s="24">
         <v>6.0</v>
       </c>
-      <c r="N75" s="26">
+      <c r="N75" s="24">
         <v>0.0</v>
       </c>
-      <c r="O75" s="27">
+      <c r="O75" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="76" spans="8:8">
-      <c r="A76" s="22" t="s">
+      <c r="A76" s="20" t="s">
         <v>4152</v>
       </c>
-      <c r="B76" s="22" t="s">
+      <c r="B76" s="20" t="s">
         <v>4153</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="27" t="s">
         <v>4154</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="D76" s="27" t="s">
         <v>4155</v>
       </c>
-      <c r="E76" s="29" t="s">
+      <c r="E76" s="27" t="s">
         <v>4156</v>
       </c>
-      <c r="F76" s="24">
+      <c r="F76" s="22">
         <v>6.0</v>
       </c>
-      <c r="G76" s="24">
+      <c r="G76" s="22">
         <v>2.0</v>
       </c>
-      <c r="H76" s="25">
+      <c r="H76" s="23">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J76" s="26">
+      <c r="J76" s="24">
         <v>16.666666666666668</v>
       </c>
-      <c r="K76" s="26">
+      <c r="K76" s="24">
         <v>3.0</v>
       </c>
-      <c r="L76" s="27">
+      <c r="L76" s="25">
         <v>0.18</v>
       </c>
-      <c r="M76" s="26">
+      <c r="M76" s="24">
         <v>11.0</v>
       </c>
-      <c r="N76" s="26">
+      <c r="N76" s="24">
         <v>4.0</v>
       </c>
-      <c r="O76" s="27">
+      <c r="O76" s="25">
         <v>0.36363636363636365</v>
       </c>
     </row>
@@ -107283,1970 +107561,1970 @@
   <dimension ref="A1:AE79"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
-    <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="31"/>
-    <col min="4" max="4" customWidth="1" bestFit="1" width="10.0" style="31"/>
-    <col min="5" max="5" customWidth="1" bestFit="1" width="10.0" style="31"/>
-    <col min="6" max="6" customWidth="1" bestFit="1" width="11.503906" style="31"/>
+    <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="29"/>
+    <col min="4" max="4" customWidth="1" bestFit="1" width="10.0" style="29"/>
+    <col min="5" max="5" customWidth="1" bestFit="1" width="10.0" style="29"/>
+    <col min="6" max="6" customWidth="1" bestFit="1" width="11.503906" style="29"/>
     <col min="7" max="7" customWidth="1" width="4.5039062" style="0"/>
-    <col min="8" max="8" customWidth="1" bestFit="1" width="10.0" style="32"/>
-    <col min="9" max="9" customWidth="1" bestFit="1" width="10.0" style="32"/>
+    <col min="8" max="8" customWidth="1" bestFit="1" width="10.0" style="30"/>
+    <col min="9" max="9" customWidth="1" bestFit="1" width="10.0" style="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="8:8">
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>6056</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="14" t="s">
         <v>6057</v>
       </c>
     </row>
     <row r="2" spans="8:8" ht="25.4" customFormat="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>4801</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>4802</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>4803</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>4804</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>4805</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="16" t="s">
         <v>4806</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="18" t="s">
         <v>6058</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="18" t="s">
         <v>6059</v>
       </c>
     </row>
     <row r="3" spans="8:8">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="20" t="s">
         <v>4168</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>4169</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="27" t="s">
         <v>4170</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="27" t="s">
         <v>4171</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="27" t="s">
         <v>4172</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="23">
         <v>0.0714432076295579</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="25">
         <v>0.06098160086707704</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="25">
         <v>0.06246258875303785</v>
       </c>
     </row>
     <row r="4" spans="8:8">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="20" t="s">
         <v>4173</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>4174</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="27" t="s">
         <v>4175</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="27" t="s">
         <v>4176</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="27" t="s">
         <v>4177</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="23">
         <v>0.055007680833526564</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="25">
         <v>0.0551699464275635</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="25">
         <v>0.04675928649471554</v>
       </c>
     </row>
     <row r="5" spans="8:8">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>4178</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>4179</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="27" t="s">
         <v>4180</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="27" t="s">
         <v>4181</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="27" t="s">
         <v>4182</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="23">
         <v>0.07474073745054984</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="25">
         <v>0.06414128809467869</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="25">
         <v>0.07402333756046449</v>
       </c>
     </row>
     <row r="6" spans="8:8">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>4183</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>4184</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="27" t="s">
         <v>4185</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="27" t="s">
         <v>4186</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="27" t="s">
         <v>4187</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="23">
         <v>0.13654125990731147</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="25">
         <v>0.07817601341354315</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="25">
         <v>0.06474326844267664</v>
       </c>
     </row>
     <row r="7" spans="8:8">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="20" t="s">
         <v>4188</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>4189</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="27" t="s">
         <v>4190</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="27" t="s">
         <v>4191</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="27" t="s">
         <v>4192</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="23">
         <v>0.0869283199347427</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="25">
         <v>0.0454531374055001</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="25">
         <v>0.04008696459825768</v>
       </c>
     </row>
     <row r="8" spans="8:8">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="20" t="s">
         <v>4193</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>4194</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="27" t="s">
         <v>4195</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="27" t="s">
         <v>4196</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="27" t="s">
         <v>4197</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="23">
         <v>0.0</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="25">
         <v>0.05462346874149627</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="25">
         <v>0.0794785869965411</v>
       </c>
     </row>
     <row r="9" spans="8:8">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>4198</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>4199</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="27" t="s">
         <v>4200</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="27" t="s">
         <v>4201</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="27" t="s">
         <v>4202</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="23">
         <v>0.09703396470907238</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="25">
         <v>0.0703472500051208</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="25">
         <v>0.08782358651523879</v>
       </c>
     </row>
     <row r="10" spans="8:8">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>4203</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>4204</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="27" t="s">
         <v>4205</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="27" t="s">
         <v>4206</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="27" t="s">
         <v>4207</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="23">
         <v>0.05261335214437954</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="25">
         <v>0.05259384427639548</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="25">
         <v>0.04246826119336062</v>
       </c>
     </row>
     <row r="11" spans="8:8">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="20" t="s">
         <v>4208</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>4209</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="27" t="s">
         <v>4210</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="27" t="s">
         <v>4211</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="27" t="s">
         <v>4212</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="23">
         <v>0.04417564635318511</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="25">
         <v>0.037722930031919004</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="25">
         <v>0.02485526343572443</v>
       </c>
     </row>
     <row r="12" spans="8:8">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="20" t="s">
         <v>4213</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>4214</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="27" t="s">
         <v>4215</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="27" t="s">
         <v>4216</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="27" t="s">
         <v>4217</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="23">
         <v>0.09198119603477448</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="25">
         <v>0.06281704102885162</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="25">
         <v>0.04713649467462683</v>
       </c>
     </row>
     <row r="13" spans="8:8">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="20" t="s">
         <v>4218</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>4219</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="27" t="s">
         <v>4220</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="27" t="s">
         <v>4221</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="27" t="s">
         <v>4222</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="23">
         <v>0.01485922200500802</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="25">
         <v>0.03158221984527825</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="25">
         <v>0.038737081085029185</v>
       </c>
     </row>
     <row r="14" spans="8:8">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="20" t="s">
         <v>4223</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="20" t="s">
         <v>4224</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="27" t="s">
         <v>4225</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="27" t="s">
         <v>4226</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="27" t="s">
         <v>4227</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="23">
         <v>0.06594049607480489</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="25">
         <v>0.07417183953936354</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="25">
         <v>0.05722459419992368</v>
       </c>
     </row>
     <row r="15" spans="8:8">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>4228</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="20" t="s">
         <v>4229</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="27" t="s">
         <v>4230</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="27" t="s">
         <v>4231</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="27" t="s">
         <v>4232</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="23">
         <v>0.0391051294949675</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="25">
         <v>0.04259452558342196</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="25">
         <v>0.058783948573643725</v>
       </c>
     </row>
     <row r="16" spans="8:8">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>4233</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="20" t="s">
         <v>4234</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="27" t="s">
         <v>4235</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="27" t="s">
         <v>4236</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="27" t="s">
         <v>4237</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="23">
         <v>0.0391051294949675</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="25">
         <v>0.04259452558342196</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="25">
         <v>0.058783948573643725</v>
       </c>
     </row>
     <row r="17" spans="8:8">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>4238</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="20" t="s">
         <v>4239</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="27" t="s">
         <v>4240</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="27" t="s">
         <v>4241</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="27" t="s">
         <v>4242</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="23">
         <v>0.030216360899535482</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="25">
         <v>0.03723844758914133</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="25">
         <v>0.03756208611040777</v>
       </c>
     </row>
     <row r="18" spans="8:8">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>4243</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="20" t="s">
         <v>4244</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="27" t="s">
         <v>4245</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="27" t="s">
         <v>4246</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="27" t="s">
         <v>4247</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="23">
         <v>0.1029607329650065</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="25">
         <v>0.05457987347785562</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="25">
         <v>0.06830659841434439</v>
       </c>
     </row>
     <row r="19" spans="8:8">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>4248</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="20" t="s">
         <v>4249</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="27" t="s">
         <v>4250</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="27" t="s">
         <v>4251</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="27" t="s">
         <v>4252</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="23">
         <v>0.011241619109808853</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="25">
         <v>0.028415486056884025</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="25">
         <v>0.050046347980965265</v>
       </c>
     </row>
     <row r="20" spans="8:8">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>4253</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="20" t="s">
         <v>4254</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="27" t="s">
         <v>4255</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="27" t="s">
         <v>4256</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="27" t="s">
         <v>4257</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="23">
         <v>0.043858753060495005</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="25">
         <v>0.050309064302250586</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="25">
         <v>0.07196147723029654</v>
       </c>
     </row>
     <row r="21" spans="8:8">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>4258</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="20" t="s">
         <v>4259</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="27" t="s">
         <v>4260</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="27" t="s">
         <v>4261</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="27" t="s">
         <v>4262</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="23">
         <v>0.048940027015205834</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="25">
         <v>0.06275887670528484</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="25">
         <v>0.054176976817070684</v>
       </c>
     </row>
     <row r="22" spans="8:8">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>4263</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="20" t="s">
         <v>4264</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="27" t="s">
         <v>4265</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="27" t="s">
         <v>4266</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="27" t="s">
         <v>4267</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="23">
         <v>0.048940027015205834</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="25">
         <v>0.06275887670528484</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="25">
         <v>0.05608399679724047</v>
       </c>
     </row>
     <row r="23" spans="8:8">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="20" t="s">
         <v>4268</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="20" t="s">
         <v>4269</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="27" t="s">
         <v>4270</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="27" t="s">
         <v>4271</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="27" t="s">
         <v>4272</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="23">
         <v>0.1616977855127562</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="25">
         <v>0.0718865217868037</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="25">
         <v>0.05940452691638236</v>
       </c>
     </row>
     <row r="24" spans="8:8">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>4273</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="20" t="s">
         <v>4274</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="27" t="s">
         <v>4275</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="27" t="s">
         <v>4276</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="27" t="s">
         <v>4277</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="23">
         <v>0.0</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="25">
         <v>0.0838434280324384</v>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="25">
         <v>0.059165453683191045</v>
       </c>
     </row>
     <row r="25" spans="8:8">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>4278</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="20" t="s">
         <v>4279</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="27" t="s">
         <v>4280</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="27" t="s">
         <v>4281</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="27" t="s">
         <v>4282</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="23">
         <v>0.0</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="25">
         <v>0.04958406058859932</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="25">
         <v>0.09228080207276627</v>
       </c>
     </row>
     <row r="26" spans="8:8">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>4283</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="20" t="s">
         <v>4284</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="27" t="s">
         <v>4285</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="27" t="s">
         <v>4286</v>
       </c>
-      <c r="E26" s="29" t="s">
+      <c r="E26" s="27" t="s">
         <v>4287</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="23">
         <v>0.0</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="25">
         <v>0.05325235163529225</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="25">
         <v>0.024332784347365563</v>
       </c>
     </row>
     <row r="27" spans="8:8">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="20" t="s">
         <v>4288</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="20" t="s">
         <v>4289</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="27" t="s">
         <v>4290</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="27" t="s">
         <v>4291</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="27" t="s">
         <v>4292</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="23">
         <v>0.0</v>
       </c>
-      <c r="H27" s="27">
+      <c r="H27" s="25">
         <v>0.0</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="28" spans="8:8">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="20" t="s">
         <v>4293</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="20" t="s">
         <v>4294</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="27" t="s">
         <v>4295</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="27" t="s">
         <v>4296</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="27" t="s">
         <v>4297</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="23">
         <v>0.0</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="25">
         <v>0.0</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="29" spans="8:8">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="20" t="s">
         <v>4298</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="20" t="s">
         <v>4299</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="27" t="s">
         <v>4300</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="D29" s="27" t="s">
         <v>4301</v>
       </c>
-      <c r="E29" s="29" t="s">
+      <c r="E29" s="27" t="s">
         <v>4302</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="23">
         <v>0.0</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="25">
         <v>0.0</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="30" spans="8:8">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="20" t="s">
         <v>4303</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="20" t="s">
         <v>4304</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="27" t="s">
         <v>4305</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D30" s="27" t="s">
         <v>4306</v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="27" t="s">
         <v>4307</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="23">
         <v>0.0</v>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="25">
         <v>0.0</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="31" spans="8:8">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="20" t="s">
         <v>4308</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="20" t="s">
         <v>4309</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="27" t="s">
         <v>4310</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D31" s="27" t="s">
         <v>4311</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E31" s="27" t="s">
         <v>4312</v>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="23">
         <v>0.12572993630356574</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="25">
         <v>0.06686510248145955</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="25">
         <v>0.07112212963675735</v>
       </c>
     </row>
     <row r="32" spans="8:8">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="20" t="s">
         <v>4313</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="20" t="s">
         <v>4314</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="27" t="s">
         <v>4315</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D32" s="27" t="s">
         <v>4316</v>
       </c>
-      <c r="E32" s="29" t="s">
+      <c r="E32" s="27" t="s">
         <v>4317</v>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="23">
         <v>0.12637571126038125</v>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="25">
         <v>0.06964091791545708</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="25">
         <v>0.05785872607590887</v>
       </c>
     </row>
     <row r="33" spans="8:8">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="20" t="s">
         <v>4318</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="20" t="s">
         <v>4319</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="27" t="s">
         <v>4320</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="27" t="s">
         <v>4321</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="27" t="s">
         <v>4322</v>
       </c>
-      <c r="F33" s="25">
+      <c r="F33" s="23">
         <v>0.05315996628928036</v>
       </c>
-      <c r="H33" s="27">
+      <c r="H33" s="25">
         <v>0.06082120689025663</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="25">
         <v>0.03663356294202617</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>4323</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="20" t="s">
         <v>4324</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="27" t="s">
         <v>4325</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="27" t="s">
         <v>4326</v>
       </c>
-      <c r="E34" s="29" t="s">
+      <c r="E34" s="27" t="s">
         <v>4327</v>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="23">
         <v>0.1774868750300987</v>
       </c>
-      <c r="H34" s="27">
+      <c r="H34" s="25">
         <v>0.1201040948033431</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="25">
         <v>0.10842236131585735</v>
       </c>
     </row>
     <row r="35" spans="8:8">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="20" t="s">
         <v>4328</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="20" t="s">
         <v>4329</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="27" t="s">
         <v>4330</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="27" t="s">
         <v>4331</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="27" t="s">
         <v>4332</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="23">
         <v>0.010046861371849266</v>
       </c>
-      <c r="H35" s="27">
+      <c r="H35" s="25">
         <v>0.03790015110298493</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="25">
         <v>0.053604881478763675</v>
       </c>
     </row>
     <row r="36" spans="8:8">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="20" t="s">
         <v>4333</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="20" t="s">
         <v>4334</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="27" t="s">
         <v>4335</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="27" t="s">
         <v>4336</v>
       </c>
-      <c r="E36" s="29" t="s">
+      <c r="E36" s="27" t="s">
         <v>4337</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="23">
         <v>0.1827577708178128</v>
       </c>
-      <c r="H36" s="27">
+      <c r="H36" s="25">
         <v>0.07597722869424497</v>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="25">
         <v>0.052780880384555945</v>
       </c>
     </row>
     <row r="37" spans="8:8">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="20" t="s">
         <v>4338</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="20" t="s">
         <v>4339</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="27" t="s">
         <v>4340</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="27" t="s">
         <v>4341</v>
       </c>
-      <c r="E37" s="29" t="s">
+      <c r="E37" s="27" t="s">
         <v>4342</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="23">
         <v>0.12276548846203432</v>
       </c>
-      <c r="H37" s="27">
+      <c r="H37" s="25">
         <v>0.05768390535317222</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="25">
         <v>0.11788345290127854</v>
       </c>
     </row>
     <row r="38" spans="8:8">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="20" t="s">
         <v>4343</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="20" t="s">
         <v>4344</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="27" t="s">
         <v>4345</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="27" t="s">
         <v>4346</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="27" t="s">
         <v>4347</v>
       </c>
-      <c r="F38" s="25">
+      <c r="F38" s="23">
         <v>0.013635875796110801</v>
       </c>
-      <c r="H38" s="27">
+      <c r="H38" s="25">
         <v>0.060179134125691515</v>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="25">
         <v>0.06788764771337627</v>
       </c>
     </row>
     <row r="39" spans="8:8">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="20" t="s">
         <v>4348</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="20" t="s">
         <v>4349</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="27" t="s">
         <v>4350</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="27" t="s">
         <v>4351</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="27" t="s">
         <v>4352</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="23">
         <v>0.0</v>
       </c>
-      <c r="H39" s="27">
+      <c r="H39" s="25">
         <v>0.041275589812516306</v>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="25">
         <v>0.08188823956694011</v>
       </c>
     </row>
     <row r="40" spans="8:8">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="20" t="s">
         <v>4353</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="20" t="s">
         <v>4354</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="27" t="s">
         <v>4355</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="27" t="s">
         <v>4356</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="27" t="s">
         <v>4357</v>
       </c>
-      <c r="F40" s="25">
+      <c r="F40" s="23">
         <v>0.09664214099611108</v>
       </c>
-      <c r="H40" s="27">
+      <c r="H40" s="25">
         <v>0.071851834469613</v>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="25">
         <v>0.10873273434506832</v>
       </c>
     </row>
     <row r="41" spans="8:8">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="20" t="s">
         <v>4358</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="20" t="s">
         <v>4359</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="27" t="s">
         <v>4360</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="27" t="s">
         <v>4361</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="27" t="s">
         <v>4362</v>
       </c>
-      <c r="F41" s="25">
+      <c r="F41" s="23">
         <v>0.218312017878382</v>
       </c>
-      <c r="H41" s="27">
+      <c r="H41" s="25">
         <v>0.05386528971488993</v>
       </c>
-      <c r="I41" s="27">
+      <c r="I41" s="25">
         <v>0.1588581228501085</v>
       </c>
     </row>
     <row r="42" spans="8:8">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="20" t="s">
         <v>4363</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="20" t="s">
         <v>4364</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="27" t="s">
         <v>4365</v>
       </c>
-      <c r="D42" s="29" t="s">
+      <c r="D42" s="27" t="s">
         <v>4366</v>
       </c>
-      <c r="E42" s="29" t="s">
+      <c r="E42" s="27" t="s">
         <v>4367</v>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="23">
         <v>0.004963363369126116</v>
       </c>
-      <c r="H42" s="27">
+      <c r="H42" s="25">
         <v>0.05880860180475631</v>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="25">
         <v>0.06146650371058642</v>
       </c>
     </row>
     <row r="43" spans="8:8">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="20" t="s">
         <v>4368</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="20" t="s">
         <v>4369</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="27" t="s">
         <v>4370</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D43" s="27" t="s">
         <v>4371</v>
       </c>
-      <c r="E43" s="29" t="s">
+      <c r="E43" s="27" t="s">
         <v>4372</v>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="23">
         <v>0.00681952004335331</v>
       </c>
-      <c r="H43" s="27">
+      <c r="H43" s="25">
         <v>0.07033997723848215</v>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="25">
         <v>0.07225610267122516</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="20" t="s">
         <v>4373</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="20" t="s">
         <v>4374</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="27" t="s">
         <v>4375</v>
       </c>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="27" t="s">
         <v>4376</v>
       </c>
-      <c r="E44" s="29" t="s">
+      <c r="E44" s="27" t="s">
         <v>4377</v>
       </c>
-      <c r="F44" s="25">
+      <c r="F44" s="23">
         <v>0.010526373510113207</v>
       </c>
-      <c r="H44" s="27">
+      <c r="H44" s="25">
         <v>0.05309210228122905</v>
       </c>
-      <c r="I44" s="27">
+      <c r="I44" s="25">
         <v>0.03360894551733227</v>
       </c>
     </row>
     <row r="45" spans="8:8">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="20" t="s">
         <v>4378</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="20" t="s">
         <v>4379</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="27" t="s">
         <v>4380</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D45" s="27" t="s">
         <v>4381</v>
       </c>
-      <c r="E45" s="29" t="s">
+      <c r="E45" s="27" t="s">
         <v>4382</v>
       </c>
-      <c r="F45" s="25">
+      <c r="F45" s="23">
         <v>0.04215389736759091</v>
       </c>
-      <c r="H45" s="27">
+      <c r="H45" s="25">
         <v>0.08764286200574223</v>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="25">
         <v>0.11453382467468572</v>
       </c>
     </row>
     <row r="46" spans="8:8">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="20" t="s">
         <v>4383</v>
       </c>
-      <c r="B46" s="22" t="s">
+      <c r="B46" s="20" t="s">
         <v>4384</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" s="27" t="s">
         <v>4385</v>
       </c>
-      <c r="D46" s="29" t="s">
+      <c r="D46" s="27" t="s">
         <v>4386</v>
       </c>
-      <c r="E46" s="29" t="s">
+      <c r="E46" s="27" t="s">
         <v>4387</v>
       </c>
-      <c r="F46" s="25">
+      <c r="F46" s="23">
         <v>0.0</v>
       </c>
-      <c r="H46" s="27">
+      <c r="H46" s="25">
         <v>0.05437549225888266</v>
       </c>
-      <c r="I46" s="27">
+      <c r="I46" s="25">
         <v>0.06437634460103164</v>
       </c>
     </row>
     <row r="47" spans="8:8">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="20" t="s">
         <v>4388</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="20" t="s">
         <v>4389</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="27" t="s">
         <v>4390</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D47" s="27" t="s">
         <v>4391</v>
       </c>
-      <c r="E47" s="29" t="s">
+      <c r="E47" s="27" t="s">
         <v>4392</v>
       </c>
-      <c r="F47" s="25">
+      <c r="F47" s="23">
         <v>0.001641915547414574</v>
       </c>
-      <c r="H47" s="27">
+      <c r="H47" s="25">
         <v>0.08030535556111061</v>
       </c>
-      <c r="I47" s="27">
+      <c r="I47" s="25">
         <v>0.0846230492134316</v>
       </c>
     </row>
     <row r="48" spans="8:8">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="20" t="s">
         <v>4393</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="20" t="s">
         <v>4394</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="27" t="s">
         <v>4395</v>
       </c>
-      <c r="D48" s="29" t="s">
+      <c r="D48" s="27" t="s">
         <v>4396</v>
       </c>
-      <c r="E48" s="29" t="s">
+      <c r="E48" s="27" t="s">
         <v>4397</v>
       </c>
-      <c r="F48" s="25">
+      <c r="F48" s="23">
         <v>0.0027989234501122366</v>
       </c>
-      <c r="H48" s="27">
+      <c r="H48" s="25">
         <v>0.04027813545296318</v>
       </c>
-      <c r="I48" s="27">
+      <c r="I48" s="25">
         <v>0.046699467127821054</v>
       </c>
     </row>
     <row r="49" spans="8:8">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="20" t="s">
         <v>4398</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="20" t="s">
         <v>4399</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="27" t="s">
         <v>4400</v>
       </c>
-      <c r="D49" s="29" t="s">
+      <c r="D49" s="27" t="s">
         <v>4401</v>
       </c>
-      <c r="E49" s="29" t="s">
+      <c r="E49" s="27" t="s">
         <v>4402</v>
       </c>
-      <c r="F49" s="25">
+      <c r="F49" s="23">
         <v>0.0</v>
       </c>
-      <c r="H49" s="27">
+      <c r="H49" s="25">
         <v>0.04147625000783528</v>
       </c>
-      <c r="I49" s="27">
+      <c r="I49" s="25">
         <v>0.027512414832243946</v>
       </c>
     </row>
     <row r="50" spans="8:8">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="20" t="s">
         <v>4403</v>
       </c>
-      <c r="B50" s="22" t="s">
+      <c r="B50" s="20" t="s">
         <v>4404</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="27" t="s">
         <v>4405</v>
       </c>
-      <c r="D50" s="29" t="s">
+      <c r="D50" s="27" t="s">
         <v>4406</v>
       </c>
-      <c r="E50" s="29" t="s">
+      <c r="E50" s="27" t="s">
         <v>4407</v>
       </c>
-      <c r="F50" s="25">
+      <c r="F50" s="23">
         <v>0.0059452605550122505</v>
       </c>
-      <c r="H50" s="27">
+      <c r="H50" s="25">
         <v>0.05113228792699242</v>
       </c>
-      <c r="I50" s="27">
+      <c r="I50" s="25">
         <v>0.050680015976223416</v>
       </c>
     </row>
     <row r="51" spans="8:8">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="20" t="s">
         <v>4408</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="20" t="s">
         <v>4409</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="27" t="s">
         <v>4410</v>
       </c>
-      <c r="D51" s="29" t="s">
+      <c r="D51" s="27" t="s">
         <v>4411</v>
       </c>
-      <c r="E51" s="29" t="s">
+      <c r="E51" s="27" t="s">
         <v>4412</v>
       </c>
-      <c r="F51" s="25">
+      <c r="F51" s="23">
         <v>0.003242415358448011</v>
       </c>
-      <c r="H51" s="27">
+      <c r="H51" s="25">
         <v>0.032603277647457754</v>
       </c>
-      <c r="I51" s="27">
+      <c r="I51" s="25">
         <v>0.05486264596332969</v>
       </c>
     </row>
     <row r="52" spans="8:8">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="20" t="s">
         <v>4413</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B52" s="20" t="s">
         <v>4414</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="27" t="s">
         <v>4415</v>
       </c>
-      <c r="D52" s="29" t="s">
+      <c r="D52" s="27" t="s">
         <v>4416</v>
       </c>
-      <c r="E52" s="29" t="s">
+      <c r="E52" s="27" t="s">
         <v>4417</v>
       </c>
-      <c r="F52" s="25">
+      <c r="F52" s="23">
         <v>0.08627699530405306</v>
       </c>
-      <c r="H52" s="27">
+      <c r="H52" s="25">
         <v>0.051747299673365346</v>
       </c>
-      <c r="I52" s="27">
+      <c r="I52" s="25">
         <v>0.07990646637851548</v>
       </c>
     </row>
     <row r="53" spans="8:8">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="20" t="s">
         <v>4418</v>
       </c>
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="20" t="s">
         <v>4419</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="27" t="s">
         <v>4420</v>
       </c>
-      <c r="D53" s="29" t="s">
+      <c r="D53" s="27" t="s">
         <v>4421</v>
       </c>
-      <c r="E53" s="29" t="s">
+      <c r="E53" s="27" t="s">
         <v>4422</v>
       </c>
-      <c r="F53" s="25">
+      <c r="F53" s="23">
         <v>0.08627699530405306</v>
       </c>
-      <c r="H53" s="27">
+      <c r="H53" s="25">
         <v>0.051747299673365346</v>
       </c>
-      <c r="I53" s="27">
+      <c r="I53" s="25">
         <v>0.07990646637851548</v>
       </c>
     </row>
     <row r="54" spans="8:8">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="20" t="s">
         <v>4423</v>
       </c>
-      <c r="B54" s="22" t="s">
+      <c r="B54" s="20" t="s">
         <v>4424</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="27" t="s">
         <v>4425</v>
       </c>
-      <c r="D54" s="29" t="s">
+      <c r="D54" s="27" t="s">
         <v>4426</v>
       </c>
-      <c r="E54" s="29" t="s">
+      <c r="E54" s="27" t="s">
         <v>4427</v>
       </c>
-      <c r="F54" s="25">
+      <c r="F54" s="23">
         <v>0.05856550495192613</v>
       </c>
-      <c r="H54" s="27">
+      <c r="H54" s="25">
         <v>0.03864478289872982</v>
       </c>
-      <c r="I54" s="27">
+      <c r="I54" s="25">
         <v>0.032310045960774435</v>
       </c>
     </row>
     <row r="55" spans="8:8">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="20" t="s">
         <v>4428</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="20" t="s">
         <v>4429</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="27" t="s">
         <v>4430</v>
       </c>
-      <c r="D55" s="29" t="s">
+      <c r="D55" s="27" t="s">
         <v>4431</v>
       </c>
-      <c r="E55" s="29" t="s">
+      <c r="E55" s="27" t="s">
         <v>4432</v>
       </c>
-      <c r="F55" s="25">
+      <c r="F55" s="23">
         <v>0.06944001489267275</v>
       </c>
-      <c r="H55" s="27">
+      <c r="H55" s="25">
         <v>0.08776981781203018</v>
       </c>
-      <c r="I55" s="27">
+      <c r="I55" s="25">
         <v>0.17117918011917638</v>
       </c>
     </row>
     <row r="56" spans="8:8">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="20" t="s">
         <v>4433</v>
       </c>
-      <c r="B56" s="22" t="s">
+      <c r="B56" s="20" t="s">
         <v>4434</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="27" t="s">
         <v>4435</v>
       </c>
-      <c r="D56" s="29" t="s">
+      <c r="D56" s="27" t="s">
         <v>4436</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="27" t="s">
         <v>4437</v>
       </c>
-      <c r="F56" s="25">
+      <c r="F56" s="23">
         <v>0.10504546683598373</v>
       </c>
-      <c r="H56" s="27">
+      <c r="H56" s="25">
         <v>0.028959293489646237</v>
       </c>
-      <c r="I56" s="27">
+      <c r="I56" s="25">
         <v>0.03903079636113687</v>
       </c>
     </row>
     <row r="57" spans="8:8">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="20" t="s">
         <v>4438</v>
       </c>
-      <c r="B57" s="22" t="s">
+      <c r="B57" s="20" t="s">
         <v>4439</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="27" t="s">
         <v>4440</v>
       </c>
-      <c r="D57" s="29" t="s">
+      <c r="D57" s="27" t="s">
         <v>4441</v>
       </c>
-      <c r="E57" s="29" t="s">
+      <c r="E57" s="27" t="s">
         <v>4442</v>
       </c>
-      <c r="F57" s="25">
+      <c r="F57" s="23">
         <v>0.10505320405965639</v>
       </c>
-      <c r="H57" s="27">
+      <c r="H57" s="25">
         <v>0.061063635455106</v>
       </c>
-      <c r="I57" s="27">
+      <c r="I57" s="25">
         <v>0.10325711086494252</v>
       </c>
     </row>
     <row r="58" spans="8:8">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="20" t="s">
         <v>4443</v>
       </c>
-      <c r="B58" s="22" t="s">
+      <c r="B58" s="20" t="s">
         <v>4444</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="27" t="s">
         <v>4445</v>
       </c>
-      <c r="D58" s="29" t="s">
+      <c r="D58" s="27" t="s">
         <v>4446</v>
       </c>
-      <c r="E58" s="29" t="s">
+      <c r="E58" s="27" t="s">
         <v>4447</v>
       </c>
-      <c r="F58" s="25">
+      <c r="F58" s="23">
         <v>0.12000526950930522</v>
       </c>
-      <c r="H58" s="27">
+      <c r="H58" s="25">
         <v>0.07112602009100809</v>
       </c>
-      <c r="I58" s="27">
+      <c r="I58" s="25">
         <v>0.07470977550717703</v>
       </c>
     </row>
     <row r="59" spans="8:8">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="20" t="s">
         <v>4448</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="B59" s="20" t="s">
         <v>4449</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="27" t="s">
         <v>4450</v>
       </c>
-      <c r="D59" s="29" t="s">
+      <c r="D59" s="27" t="s">
         <v>4451</v>
       </c>
-      <c r="E59" s="29" t="s">
+      <c r="E59" s="27" t="s">
         <v>4452</v>
       </c>
-      <c r="F59" s="25">
+      <c r="F59" s="23">
         <v>0.11665534964588728</v>
       </c>
-      <c r="H59" s="27">
+      <c r="H59" s="25">
         <v>0.07383819857319583</v>
       </c>
-      <c r="I59" s="27">
+      <c r="I59" s="25">
         <v>0.06989554884783775</v>
       </c>
     </row>
     <row r="60" spans="8:8">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="20" t="s">
         <v>4453</v>
       </c>
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="20" t="s">
         <v>4454</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="27" t="s">
         <v>4455</v>
       </c>
-      <c r="D60" s="29" t="s">
+      <c r="D60" s="27" t="s">
         <v>4456</v>
       </c>
-      <c r="E60" s="29" t="s">
+      <c r="E60" s="27" t="s">
         <v>4457</v>
       </c>
-      <c r="F60" s="25">
+      <c r="F60" s="23">
         <v>0.1402641753710246</v>
       </c>
-      <c r="H60" s="27">
+      <c r="H60" s="25">
         <v>0.05791045472890207</v>
       </c>
-      <c r="I60" s="27">
+      <c r="I60" s="25">
         <v>0.04546405580036862</v>
       </c>
     </row>
     <row r="61" spans="8:8">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="20" t="s">
         <v>4458</v>
       </c>
-      <c r="B61" s="22" t="s">
+      <c r="B61" s="20" t="s">
         <v>4459</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="27" t="s">
         <v>4460</v>
       </c>
-      <c r="D61" s="29" t="s">
+      <c r="D61" s="27" t="s">
         <v>4461</v>
       </c>
-      <c r="E61" s="29" t="s">
+      <c r="E61" s="27" t="s">
         <v>4462</v>
       </c>
-      <c r="F61" s="25">
+      <c r="F61" s="23">
         <v>0.13821199061264777</v>
       </c>
-      <c r="H61" s="27">
+      <c r="H61" s="25">
         <v>0.09966135113269331</v>
       </c>
-      <c r="I61" s="27">
+      <c r="I61" s="25">
         <v>0.10930817695977806</v>
       </c>
     </row>
     <row r="62" spans="8:8">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="20" t="s">
         <v>4463</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="20" t="s">
         <v>4464</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="27" t="s">
         <v>4465</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="D62" s="27" t="s">
         <v>4466</v>
       </c>
-      <c r="E62" s="29" t="s">
+      <c r="E62" s="27" t="s">
         <v>4467</v>
       </c>
-      <c r="F62" s="25">
+      <c r="F62" s="23">
         <v>0.07267648865136646</v>
       </c>
-      <c r="H62" s="27">
+      <c r="H62" s="25">
         <v>0.08123188562332694</v>
       </c>
-      <c r="I62" s="27">
+      <c r="I62" s="25">
         <v>0.10115762124373626</v>
       </c>
     </row>
     <row r="63" spans="8:8">
-      <c r="A63" s="22" t="s">
+      <c r="A63" s="20" t="s">
         <v>4468</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="20" t="s">
         <v>4469</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="27" t="s">
         <v>4470</v>
       </c>
-      <c r="D63" s="29" t="s">
+      <c r="D63" s="27" t="s">
         <v>4471</v>
       </c>
-      <c r="E63" s="29" t="s">
+      <c r="E63" s="27" t="s">
         <v>4472</v>
       </c>
-      <c r="F63" s="25">
+      <c r="F63" s="23">
         <v>0.12382462987576354</v>
       </c>
-      <c r="H63" s="27">
+      <c r="H63" s="25">
         <v>0.07346979799641581</v>
       </c>
-      <c r="I63" s="27">
+      <c r="I63" s="25">
         <v>0.050394613702806346</v>
       </c>
     </row>
     <row r="64" spans="8:8">
-      <c r="A64" s="22" t="s">
+      <c r="A64" s="20" t="s">
         <v>4473</v>
       </c>
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="20" t="s">
         <v>4474</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="27" t="s">
         <v>4475</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="D64" s="27" t="s">
         <v>4476</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="27" t="s">
         <v>4477</v>
       </c>
-      <c r="F64" s="25">
+      <c r="F64" s="23">
         <v>0.13400589010515881</v>
       </c>
-      <c r="H64" s="27">
+      <c r="H64" s="25">
         <v>0.006138075483457187</v>
       </c>
-      <c r="I64" s="27">
+      <c r="I64" s="25">
         <v>0.15708337096028557</v>
       </c>
     </row>
     <row r="65" spans="8:8">
-      <c r="A65" s="22" t="s">
+      <c r="A65" s="20" t="s">
         <v>4478</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="20" t="s">
         <v>4479</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="27" t="s">
         <v>4480</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D65" s="27" t="s">
         <v>4481</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="27" t="s">
         <v>4482</v>
       </c>
-      <c r="F65" s="25">
+      <c r="F65" s="23">
         <v>0.026546295651946546</v>
       </c>
-      <c r="H65" s="27">
+      <c r="H65" s="25">
         <v>0.0</v>
       </c>
-      <c r="I65" s="27">
+      <c r="I65" s="25">
         <v>0.06305363229838544</v>
       </c>
     </row>
     <row r="66" spans="8:8">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="20" t="s">
         <v>4483</v>
       </c>
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="20" t="s">
         <v>4484</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="27" t="s">
         <v>4485</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="27" t="s">
         <v>4486</v>
       </c>
-      <c r="E66" s="29" t="s">
+      <c r="E66" s="27" t="s">
         <v>4487</v>
       </c>
-      <c r="F66" s="25">
+      <c r="F66" s="23">
         <v>0.34674246754013754</v>
       </c>
-      <c r="H66" s="27">
+      <c r="H66" s="25">
         <v>0.0</v>
       </c>
-      <c r="I66" s="27">
+      <c r="I66" s="25">
         <v>0.21887591244542312</v>
       </c>
     </row>
     <row r="67" spans="8:8">
-      <c r="A67" s="22" t="s">
+      <c r="A67" s="20" t="s">
         <v>4488</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="20" t="s">
         <v>4489</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="27" t="s">
         <v>4490</v>
       </c>
-      <c r="D67" s="29" t="s">
+      <c r="D67" s="27" t="s">
         <v>4491</v>
       </c>
-      <c r="E67" s="29" t="s">
+      <c r="E67" s="27" t="s">
         <v>4492</v>
       </c>
-      <c r="F67" s="25">
+      <c r="F67" s="23">
         <v>0.022402005488635468</v>
       </c>
-      <c r="H67" s="27">
+      <c r="H67" s="25">
         <v>0.00992930222684575</v>
       </c>
-      <c r="I67" s="27">
+      <c r="I67" s="25">
         <v>0.15444178277810133</v>
       </c>
     </row>
     <row r="68" spans="8:8">
-      <c r="A68" s="22" t="s">
+      <c r="A68" s="20" t="s">
         <v>4493</v>
       </c>
-      <c r="B68" s="22" t="s">
+      <c r="B68" s="20" t="s">
         <v>4494</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="27" t="s">
         <v>4495</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D68" s="27" t="s">
         <v>4496</v>
       </c>
-      <c r="E68" s="29" t="s">
+      <c r="E68" s="27" t="s">
         <v>4497</v>
       </c>
-      <c r="F68" s="25">
+      <c r="F68" s="23">
         <v>0.0764321942670123</v>
       </c>
-      <c r="H68" s="27">
+      <c r="H68" s="25">
         <v>0.0815567276804826</v>
       </c>
-      <c r="I68" s="27">
+      <c r="I68" s="25">
         <v>0.07307568961057789</v>
       </c>
     </row>
     <row r="69" spans="8:8">
-      <c r="A69" s="22" t="s">
+      <c r="A69" s="20" t="s">
         <v>4498</v>
       </c>
-      <c r="B69" s="22" t="s">
+      <c r="B69" s="20" t="s">
         <v>4499</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="27" t="s">
         <v>4500</v>
       </c>
-      <c r="D69" s="29" t="s">
+      <c r="D69" s="27" t="s">
         <v>4501</v>
       </c>
-      <c r="E69" s="29" t="s">
+      <c r="E69" s="27" t="s">
         <v>4502</v>
       </c>
-      <c r="F69" s="25">
+      <c r="F69" s="23">
         <v>0.07099396683483267</v>
       </c>
-      <c r="H69" s="27">
+      <c r="H69" s="25">
         <v>0.07821810662619413</v>
       </c>
-      <c r="I69" s="27">
+      <c r="I69" s="25">
         <v>0.06971091136783561</v>
       </c>
     </row>
     <row r="70" spans="8:8">
-      <c r="A70" s="22" t="s">
+      <c r="A70" s="20" t="s">
         <v>4503</v>
       </c>
-      <c r="B70" s="22" t="s">
+      <c r="B70" s="20" t="s">
         <v>4504</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="27" t="s">
         <v>4505</v>
       </c>
-      <c r="D70" s="29" t="s">
+      <c r="D70" s="27" t="s">
         <v>4506</v>
       </c>
-      <c r="E70" s="29" t="s">
+      <c r="E70" s="27" t="s">
         <v>4507</v>
       </c>
-      <c r="F70" s="25">
+      <c r="F70" s="23">
         <v>0.05075301294246951</v>
       </c>
-      <c r="H70" s="27">
+      <c r="H70" s="25">
         <v>0.07632021177610046</v>
       </c>
-      <c r="I70" s="27">
+      <c r="I70" s="25">
         <v>0.07690532478043993</v>
       </c>
     </row>
     <row r="71" spans="8:8">
-      <c r="A71" s="22" t="s">
+      <c r="A71" s="20" t="s">
         <v>4508</v>
       </c>
-      <c r="B71" s="22" t="s">
+      <c r="B71" s="20" t="s">
         <v>4509</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="27" t="s">
         <v>4510</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D71" s="27" t="s">
         <v>4511</v>
       </c>
-      <c r="E71" s="29" t="s">
+      <c r="E71" s="27" t="s">
         <v>4512</v>
       </c>
-      <c r="F71" s="25">
+      <c r="F71" s="23">
         <v>0.1232999704839467</v>
       </c>
-      <c r="H71" s="27">
+      <c r="H71" s="25">
         <v>0.04669245019606618</v>
       </c>
-      <c r="I71" s="27">
+      <c r="I71" s="25">
         <v>0.08796038555838961</v>
       </c>
     </row>
     <row r="72" spans="8:8">
-      <c r="A72" s="22" t="s">
+      <c r="A72" s="20" t="s">
         <v>4513</v>
       </c>
-      <c r="B72" s="22" t="s">
+      <c r="B72" s="20" t="s">
         <v>4514</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="27" t="s">
         <v>4515</v>
       </c>
-      <c r="D72" s="29" t="s">
+      <c r="D72" s="27" t="s">
         <v>4516</v>
       </c>
-      <c r="E72" s="29" t="s">
+      <c r="E72" s="27" t="s">
         <v>4517</v>
       </c>
-      <c r="F72" s="25">
+      <c r="F72" s="23">
         <v>0.03707050839549364</v>
       </c>
-      <c r="H72" s="27">
+      <c r="H72" s="25">
         <v>0.10076366875278608</v>
       </c>
-      <c r="I72" s="27">
+      <c r="I72" s="25">
         <v>0.048452251636374295</v>
       </c>
     </row>
     <row r="73" spans="8:8">
-      <c r="A73" s="22" t="s">
+      <c r="A73" s="20" t="s">
         <v>4518</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="20" t="s">
         <v>4519</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="27" t="s">
         <v>4520</v>
       </c>
-      <c r="D73" s="29" t="s">
+      <c r="D73" s="27" t="s">
         <v>4521</v>
       </c>
-      <c r="E73" s="29" t="s">
+      <c r="E73" s="27" t="s">
         <v>4522</v>
       </c>
-      <c r="F73" s="25">
+      <c r="F73" s="23">
         <v>0.3138605525440069</v>
       </c>
-      <c r="H73" s="27">
+      <c r="H73" s="25">
         <v>0.19678892697655986</v>
       </c>
-      <c r="I73" s="27">
+      <c r="I73" s="25">
         <v>0.2489440150482115</v>
       </c>
     </row>
     <row r="74" spans="8:8">
-      <c r="A74" s="22" t="s">
+      <c r="A74" s="20" t="s">
         <v>4523</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="20" t="s">
         <v>4524</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="27" t="s">
         <v>4525</v>
       </c>
-      <c r="D74" s="29" t="s">
+      <c r="D74" s="27" t="s">
         <v>4526</v>
       </c>
-      <c r="E74" s="29" t="s">
+      <c r="E74" s="27" t="s">
         <v>4527</v>
       </c>
-      <c r="F74" s="25">
+      <c r="F74" s="23">
         <v>0.0</v>
       </c>
-      <c r="H74" s="27">
+      <c r="H74" s="25">
         <v>0.10311697230790394</v>
       </c>
-      <c r="I74" s="27">
+      <c r="I74" s="25">
         <v>0.009813048169297308</v>
       </c>
     </row>
     <row r="75" spans="8:8">
-      <c r="A75" s="22" t="s">
+      <c r="A75" s="20" t="s">
         <v>4528</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" s="20" t="s">
         <v>4529</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="27" t="s">
         <v>4530</v>
       </c>
-      <c r="D75" s="29" t="s">
+      <c r="D75" s="27" t="s">
         <v>4531</v>
       </c>
-      <c r="E75" s="29" t="s">
+      <c r="E75" s="27" t="s">
         <v>4532</v>
       </c>
-      <c r="F75" s="25">
+      <c r="F75" s="23">
         <v>0.0</v>
       </c>
-      <c r="H75" s="27">
+      <c r="H75" s="25">
         <v>0.19123018093987426</v>
       </c>
-      <c r="I75" s="27">
+      <c r="I75" s="25">
         <v>0.0</v>
       </c>
     </row>
     <row r="76" spans="8:8">
-      <c r="A76" s="22" t="s">
+      <c r="A76" s="20" t="s">
         <v>4533</v>
       </c>
-      <c r="B76" s="22" t="s">
+      <c r="B76" s="20" t="s">
         <v>4534</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="27" t="s">
         <v>4535</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="D76" s="27" t="s">
         <v>4536</v>
       </c>
-      <c r="E76" s="29" t="s">
+      <c r="E76" s="27" t="s">
         <v>4537</v>
       </c>
-      <c r="F76" s="25">
+      <c r="F76" s="23">
         <v>0.4842167531733346</v>
       </c>
-      <c r="H76" s="27">
+      <c r="H76" s="25">
         <v>0.2890112246526713</v>
       </c>
-      <c r="I76" s="27">
+      <c r="I76" s="25">
         <v>0.4258120563350069</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10369" count="10369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10656" count="10656">
   <si>
     <t>Region</t>
   </si>
@@ -92703,6 +92703,2589 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
     </r>
   </si>
   <si>
@@ -94145,7 +96728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AZ397"/>
+  <dimension ref="A1:BA397"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.8828125" style="0"/>
@@ -94206,163 +96789,163 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>10082</v>
+        <v>10369</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10083</v>
+        <v>10370</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10084</v>
+        <v>10371</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10085</v>
+        <v>10372</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10086</v>
+        <v>10373</v>
       </c>
       <c r="F2" s="3">
         <v>787067.06</v>
       </c>
       <c r="G2" s="3">
-        <v>171799.43</v>
+        <v>185702.45</v>
       </c>
       <c r="H2" s="3">
-        <v>240939.45</v>
+        <v>240205.32</v>
       </c>
       <c r="I2" s="3">
-        <v>412738.88</v>
+        <v>425907.77</v>
       </c>
       <c r="J2" s="3">
-        <v>52.44</v>
+        <v>54.11</v>
       </c>
       <c r="K2" s="3">
-        <v>-374328.18</v>
+        <v>-361159.29</v>
       </c>
       <c r="L2" s="3">
-        <v>0.81</v>
+        <v>0.9</v>
       </c>
       <c r="M2" s="3">
-        <v>3343.16</v>
+        <v>3831.08</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>10087</v>
+        <v>10374</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10088</v>
+        <v>10375</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10089</v>
+        <v>10376</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10090</v>
+        <v>10377</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10091</v>
+        <v>10378</v>
       </c>
       <c r="F3" s="3">
         <v>792403.1</v>
       </c>
       <c r="G3" s="3">
-        <v>132398.31</v>
+        <v>137157.01</v>
       </c>
       <c r="H3" s="3">
-        <v>241495.22</v>
+        <v>246722.44</v>
       </c>
       <c r="I3" s="3">
-        <v>373893.53</v>
+        <v>383879.45</v>
       </c>
       <c r="J3" s="3">
-        <v>47.18</v>
+        <v>48.44</v>
       </c>
       <c r="K3" s="3">
-        <v>-418509.57</v>
+        <v>-408523.65</v>
       </c>
       <c r="L3" s="3">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="M3" s="3">
-        <v>5168.4</v>
+        <v>6000.4</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>10092</v>
+        <v>10379</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10093</v>
+        <v>10380</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10094</v>
+        <v>10381</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10095</v>
+        <v>10382</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10096</v>
+        <v>10383</v>
       </c>
       <c r="F4" s="3">
         <v>672792.28</v>
       </c>
       <c r="G4" s="3">
-        <v>305465.15</v>
+        <v>322401.6</v>
       </c>
       <c r="H4" s="3">
-        <v>184310.09</v>
+        <v>190891.55</v>
       </c>
       <c r="I4" s="3">
-        <v>489775.24</v>
+        <v>513293.15</v>
       </c>
       <c r="J4" s="3">
-        <v>72.8</v>
+        <v>76.29</v>
       </c>
       <c r="K4" s="3">
-        <v>-183017.04</v>
+        <v>-159499.13</v>
       </c>
       <c r="L4" s="3">
-        <v>0.65</v>
+        <v>0.95</v>
       </c>
       <c r="M4" s="3">
-        <v>3163.58</v>
+        <v>4857.02</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>10097</v>
+        <v>10384</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10098</v>
+        <v>10385</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10099</v>
+        <v>10386</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10100</v>
+        <v>10387</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10101</v>
+        <v>10388</v>
       </c>
       <c r="F5" s="3">
         <v>740010.55</v>
       </c>
       <c r="G5" s="3">
-        <v>140504.17</v>
+        <v>147842.76</v>
       </c>
       <c r="H5" s="3">
-        <v>162708.18</v>
+        <v>171558.61</v>
       </c>
       <c r="I5" s="3">
-        <v>303212.35</v>
+        <v>319401.37</v>
       </c>
       <c r="J5" s="3">
-        <v>40.97</v>
+        <v>43.16</v>
       </c>
       <c r="K5" s="3">
-        <v>-436798.2</v>
+        <v>-420609.18</v>
       </c>
       <c r="L5" s="3">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="M5" s="3">
         <v>4665.47</v>
@@ -94370,368 +96953,368 @@
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>10102</v>
+        <v>10389</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10103</v>
+        <v>10390</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10104</v>
+        <v>10391</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10105</v>
+        <v>10392</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10106</v>
+        <v>10393</v>
       </c>
       <c r="F6" s="3">
         <v>763526.5</v>
       </c>
       <c r="G6" s="3">
-        <v>223096.05</v>
+        <v>241110.58</v>
       </c>
       <c r="H6" s="3">
-        <v>187241.2</v>
+        <v>198343.42</v>
       </c>
       <c r="I6" s="3">
-        <v>410337.25</v>
+        <v>439454.0</v>
       </c>
       <c r="J6" s="3">
-        <v>53.74</v>
+        <v>57.56</v>
       </c>
       <c r="K6" s="3">
-        <v>-353189.25</v>
+        <v>-324072.5</v>
       </c>
       <c r="L6" s="3">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="M6" s="3">
-        <v>5110.53</v>
+        <v>7035.93</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>10107</v>
+        <v>10394</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10108</v>
+        <v>10395</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10109</v>
+        <v>10396</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10110</v>
+        <v>10397</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10111</v>
+        <v>10398</v>
       </c>
       <c r="F7" s="3">
         <v>803185.79</v>
       </c>
       <c r="G7" s="3">
-        <v>148616.18</v>
+        <v>173761.64</v>
       </c>
       <c r="H7" s="3">
-        <v>208902.03</v>
+        <v>202717.66</v>
       </c>
       <c r="I7" s="3">
-        <v>357518.21</v>
+        <v>376479.3</v>
       </c>
       <c r="J7" s="3">
-        <v>44.51</v>
+        <v>46.87</v>
       </c>
       <c r="K7" s="3">
-        <v>-445667.58</v>
+        <v>-426706.49</v>
       </c>
       <c r="L7" s="3">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M7" s="3">
-        <v>5810.91</v>
+        <v>6058.29</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>10112</v>
+        <v>10399</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10113</v>
+        <v>10400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10114</v>
+        <v>10401</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10115</v>
+        <v>10402</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>10116</v>
+        <v>10403</v>
       </c>
       <c r="F8" s="3">
-        <v>770724.92</v>
+        <v>774607.3</v>
       </c>
       <c r="G8" s="3">
-        <v>172917.41</v>
+        <v>172399.75</v>
       </c>
       <c r="H8" s="3">
-        <v>147895.83</v>
+        <v>156968.57</v>
       </c>
       <c r="I8" s="3">
-        <v>320813.24</v>
+        <v>329368.32</v>
       </c>
       <c r="J8" s="3">
-        <v>41.62</v>
+        <v>42.52</v>
       </c>
       <c r="K8" s="3">
-        <v>-449911.68</v>
+        <v>-445238.98</v>
       </c>
       <c r="L8" s="3">
-        <v>1.54</v>
+        <v>0.77</v>
       </c>
       <c r="M8" s="3">
-        <v>4949.2</v>
+        <v>2539.14</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>10117</v>
+        <v>10404</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10118</v>
+        <v>10405</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10119</v>
+        <v>10406</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10120</v>
+        <v>10407</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>10121</v>
+        <v>10408</v>
       </c>
       <c r="F9" s="3">
-        <v>774607.3</v>
+        <v>770724.92</v>
       </c>
       <c r="G9" s="3">
-        <v>163461.12</v>
+        <v>191821.56</v>
       </c>
       <c r="H9" s="3">
-        <v>151441.82</v>
+        <v>150743.64</v>
       </c>
       <c r="I9" s="3">
-        <v>314902.94</v>
+        <v>342565.2</v>
       </c>
       <c r="J9" s="3">
-        <v>40.65</v>
+        <v>44.45</v>
       </c>
       <c r="K9" s="3">
-        <v>-459704.36</v>
+        <v>-428159.72</v>
       </c>
       <c r="L9" s="3">
-        <v>0.81</v>
+        <v>1.78</v>
       </c>
       <c r="M9" s="3">
-        <v>2539.14</v>
+        <v>6081.86</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>10122</v>
+        <v>10409</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10123</v>
+        <v>10410</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10124</v>
+        <v>10411</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10125</v>
+        <v>10412</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>10126</v>
+        <v>10413</v>
       </c>
       <c r="F10" s="3">
         <v>900349.47</v>
       </c>
       <c r="G10" s="3">
-        <v>105670.29</v>
+        <v>117281.31</v>
       </c>
       <c r="H10" s="3">
-        <v>211817.6</v>
+        <v>211314.61</v>
       </c>
       <c r="I10" s="3">
-        <v>317487.89</v>
+        <v>328595.92</v>
       </c>
       <c r="J10" s="3">
-        <v>35.26</v>
+        <v>36.5</v>
       </c>
       <c r="K10" s="3">
-        <v>-582861.58</v>
+        <v>-571753.55</v>
       </c>
       <c r="L10" s="3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M10" s="3">
-        <v>3202.02</v>
+        <v>3651.82</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>10127</v>
+        <v>10414</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>10128</v>
+        <v>10415</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10129</v>
+        <v>10416</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10130</v>
+        <v>10417</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>10131</v>
+        <v>10418</v>
       </c>
       <c r="F11" s="3">
         <v>901291.26</v>
       </c>
       <c r="G11" s="3">
-        <v>112799.62</v>
+        <v>134758.74</v>
       </c>
       <c r="H11" s="3">
-        <v>181320.9</v>
+        <v>175549.25</v>
       </c>
       <c r="I11" s="3">
-        <v>294120.52</v>
+        <v>310307.99</v>
       </c>
       <c r="J11" s="3">
-        <v>32.63</v>
+        <v>34.43</v>
       </c>
       <c r="K11" s="3">
-        <v>-607170.74</v>
+        <v>-590983.27</v>
       </c>
       <c r="L11" s="3">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M11" s="3">
-        <v>4476.04</v>
+        <v>4908.64</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>10132</v>
+        <v>10419</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10133</v>
+        <v>10420</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10134</v>
+        <v>10421</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10135</v>
+        <v>10422</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>10136</v>
+        <v>10423</v>
       </c>
       <c r="F12" s="3">
         <v>790977.36</v>
       </c>
       <c r="G12" s="3">
-        <v>178272.09</v>
+        <v>195511.04</v>
       </c>
       <c r="H12" s="3">
-        <v>208974.81</v>
+        <v>217094.11</v>
       </c>
       <c r="I12" s="3">
-        <v>387246.9</v>
+        <v>412605.15</v>
       </c>
       <c r="J12" s="3">
-        <v>48.96</v>
+        <v>52.16</v>
       </c>
       <c r="K12" s="3">
-        <v>-403730.46</v>
+        <v>-378372.21</v>
       </c>
       <c r="L12" s="3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="M12" s="3">
-        <v>3976.4</v>
+        <v>4306.2</v>
       </c>
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>10137</v>
+        <v>10424</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10138</v>
+        <v>10425</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10139</v>
+        <v>10426</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10140</v>
+        <v>10427</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>10141</v>
+        <v>10428</v>
       </c>
       <c r="F13" s="3">
         <v>848180.28</v>
       </c>
       <c r="G13" s="3">
-        <v>163116.6</v>
+        <v>194251.64</v>
       </c>
       <c r="H13" s="3">
-        <v>261881.66</v>
+        <v>248376.62</v>
       </c>
       <c r="I13" s="3">
-        <v>424998.26</v>
+        <v>442628.26</v>
       </c>
       <c r="J13" s="3">
-        <v>50.11</v>
+        <v>52.19</v>
       </c>
       <c r="K13" s="3">
-        <v>-423182.02</v>
+        <v>-405552.02</v>
       </c>
       <c r="L13" s="3">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="M13" s="3">
-        <v>4959.08</v>
+        <v>5273.96</v>
       </c>
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>10142</v>
+        <v>10429</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10143</v>
+        <v>10430</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10144</v>
+        <v>10431</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10145</v>
+        <v>10432</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>10146</v>
+        <v>10433</v>
       </c>
       <c r="F14" s="3">
         <v>788558.37</v>
       </c>
       <c r="G14" s="3">
-        <v>138285.31</v>
+        <v>146122.61</v>
       </c>
       <c r="H14" s="3">
-        <v>212698.41</v>
+        <v>230417.04</v>
       </c>
       <c r="I14" s="3">
-        <v>350983.72</v>
+        <v>376539.65</v>
       </c>
       <c r="J14" s="3">
-        <v>44.51</v>
+        <v>47.75</v>
       </c>
       <c r="K14" s="3">
-        <v>-437574.65</v>
+        <v>-412018.72</v>
       </c>
       <c r="L14" s="3">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="M14" s="3">
         <v>5649.54</v>
@@ -94739,81 +97322,81 @@
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>10147</v>
+        <v>10434</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10148</v>
+        <v>10435</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10149</v>
+        <v>10436</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10150</v>
+        <v>10437</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>10151</v>
+        <v>10438</v>
       </c>
       <c r="F15" s="3">
         <v>816369.33</v>
       </c>
       <c r="G15" s="3">
-        <v>81939.14</v>
+        <v>87735.01</v>
       </c>
       <c r="H15" s="3">
-        <v>180574.68</v>
+        <v>190450.93</v>
       </c>
       <c r="I15" s="3">
-        <v>262513.82</v>
+        <v>278185.94</v>
       </c>
       <c r="J15" s="3">
-        <v>32.16</v>
+        <v>34.08</v>
       </c>
       <c r="K15" s="3">
-        <v>-553855.51</v>
+        <v>-538183.39</v>
       </c>
       <c r="L15" s="3">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="M15" s="3">
-        <v>4420.46</v>
+        <v>5858.82</v>
       </c>
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>10152</v>
+        <v>10439</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10153</v>
+        <v>10440</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10154</v>
+        <v>10441</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10155</v>
+        <v>10442</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>10156</v>
+        <v>10443</v>
       </c>
       <c r="F16" s="3">
         <v>792760.6</v>
       </c>
       <c r="G16" s="3">
-        <v>99730.56</v>
+        <v>104259.06</v>
       </c>
       <c r="H16" s="3">
-        <v>114075.71</v>
+        <v>127436.27</v>
       </c>
       <c r="I16" s="3">
-        <v>213806.27</v>
+        <v>231695.33</v>
       </c>
       <c r="J16" s="3">
-        <v>26.97</v>
+        <v>29.23</v>
       </c>
       <c r="K16" s="3">
-        <v>-578954.33</v>
+        <v>-561065.27</v>
       </c>
       <c r="L16" s="3">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M16" s="3">
         <v>1772.52</v>
@@ -94821,40 +97404,40 @@
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>10157</v>
+        <v>10444</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>10158</v>
+        <v>10445</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10159</v>
+        <v>10446</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>10160</v>
+        <v>10447</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>10161</v>
+        <v>10448</v>
       </c>
       <c r="F17" s="3">
         <v>786604.47</v>
       </c>
       <c r="G17" s="3">
-        <v>85538.43</v>
+        <v>88278.3</v>
       </c>
       <c r="H17" s="3">
-        <v>139361.44</v>
+        <v>154876.56</v>
       </c>
       <c r="I17" s="3">
-        <v>224899.87</v>
+        <v>243154.86</v>
       </c>
       <c r="J17" s="3">
-        <v>28.59</v>
+        <v>30.91</v>
       </c>
       <c r="K17" s="3">
-        <v>-561704.6</v>
+        <v>-543449.61</v>
       </c>
       <c r="L17" s="3">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="M17" s="3">
         <v>3058.08</v>
@@ -94862,19 +97445,19 @@
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>10162</v>
+        <v>10449</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>10163</v>
+        <v>10450</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10164</v>
+        <v>10451</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10165</v>
+        <v>10452</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>10166</v>
+        <v>10453</v>
       </c>
       <c r="F18" s="3">
         <v>1063383.58</v>
@@ -94883,19 +97466,19 @@
         <v>235426.35</v>
       </c>
       <c r="H18" s="3">
-        <v>73085.44</v>
+        <v>140398.75</v>
       </c>
       <c r="I18" s="3">
-        <v>308511.79</v>
+        <v>375825.1</v>
       </c>
       <c r="J18" s="3">
-        <v>29.01</v>
+        <v>35.34</v>
       </c>
       <c r="K18" s="3">
-        <v>-754871.79</v>
+        <v>-687558.48</v>
       </c>
       <c r="L18" s="3">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="M18" s="3">
         <v>5518.52</v>
@@ -94903,19 +97486,19 @@
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>10167</v>
+        <v>10454</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10168</v>
+        <v>10455</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10169</v>
+        <v>10456</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10170</v>
+        <v>10457</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>10171</v>
+        <v>10458</v>
       </c>
       <c r="F19" s="3">
         <v>886606.12</v>
@@ -94924,19 +97507,19 @@
         <v>238758.45</v>
       </c>
       <c r="H19" s="3">
-        <v>62470.28</v>
+        <v>146174.37</v>
       </c>
       <c r="I19" s="3">
-        <v>301228.73</v>
+        <v>384932.82</v>
       </c>
       <c r="J19" s="3">
-        <v>33.98</v>
+        <v>43.42</v>
       </c>
       <c r="K19" s="3">
-        <v>-585377.39</v>
+        <v>-501673.3</v>
       </c>
       <c r="L19" s="3">
-        <v>3.0</v>
+        <v>2.35</v>
       </c>
       <c r="M19" s="3">
         <v>9038.84</v>
@@ -94944,19 +97527,19 @@
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>10172</v>
+        <v>10459</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>10173</v>
+        <v>10460</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10174</v>
+        <v>10461</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10175</v>
+        <v>10462</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>10176</v>
+        <v>10463</v>
       </c>
       <c r="F20" s="3">
         <v>1264233.6</v>
@@ -94965,19 +97548,19 @@
         <v>256941.64</v>
       </c>
       <c r="H20" s="3">
-        <v>138961.04</v>
+        <v>239508.23</v>
       </c>
       <c r="I20" s="3">
-        <v>395902.68</v>
+        <v>496449.87</v>
       </c>
       <c r="J20" s="3">
-        <v>31.32</v>
+        <v>39.27</v>
       </c>
       <c r="K20" s="3">
-        <v>-868330.92</v>
+        <v>-767783.73</v>
       </c>
       <c r="L20" s="3">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="M20" s="3">
         <v>9495.49</v>
@@ -94985,204 +97568,204 @@
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>10177</v>
+        <v>10464</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>10178</v>
+        <v>10465</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10179</v>
+        <v>10466</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10180</v>
+        <v>10467</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>10181</v>
+        <v>10468</v>
       </c>
       <c r="F21" s="3">
-        <v>873034.8</v>
+        <v>821118.86</v>
       </c>
       <c r="G21" s="3">
-        <v>287421.73</v>
+        <v>396738.38</v>
       </c>
       <c r="H21" s="3">
-        <v>93697.9</v>
+        <v>114437.81</v>
       </c>
       <c r="I21" s="3">
-        <v>381119.63</v>
+        <v>511176.19</v>
       </c>
       <c r="J21" s="3">
-        <v>43.65</v>
+        <v>62.25</v>
       </c>
       <c r="K21" s="3">
-        <v>-491915.17</v>
+        <v>-309942.67</v>
       </c>
       <c r="L21" s="3">
-        <v>1.66</v>
+        <v>0.49</v>
       </c>
       <c r="M21" s="3">
-        <v>6311.42</v>
+        <v>2498.46</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>10182</v>
+        <v>10469</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>10183</v>
+        <v>10470</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10184</v>
+        <v>10471</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>10185</v>
+        <v>10472</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>10186</v>
+        <v>10473</v>
       </c>
       <c r="F22" s="3">
         <v>891542.61</v>
       </c>
       <c r="G22" s="3">
-        <v>231462.66</v>
+        <v>252864.78</v>
       </c>
       <c r="H22" s="3">
-        <v>104989.78</v>
+        <v>97422.02</v>
       </c>
       <c r="I22" s="3">
-        <v>336452.44</v>
+        <v>350286.8</v>
       </c>
       <c r="J22" s="3">
-        <v>37.74</v>
+        <v>39.29</v>
       </c>
       <c r="K22" s="3">
-        <v>-555090.17</v>
+        <v>-541255.81</v>
       </c>
       <c r="L22" s="3">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="M22" s="3">
-        <v>9440.34</v>
+        <v>9801.84</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>10187</v>
+        <v>10474</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10188</v>
+        <v>10475</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10189</v>
+        <v>10476</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>10190</v>
+        <v>10477</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>10191</v>
+        <v>10478</v>
       </c>
       <c r="F23" s="3">
         <v>876168.01</v>
       </c>
       <c r="G23" s="3">
-        <v>304916.07</v>
+        <v>324898.79</v>
       </c>
       <c r="H23" s="3">
-        <v>110713.58</v>
+        <v>126454.82</v>
       </c>
       <c r="I23" s="3">
-        <v>415629.65</v>
+        <v>451353.61</v>
       </c>
       <c r="J23" s="3">
-        <v>47.44</v>
+        <v>51.51</v>
       </c>
       <c r="K23" s="3">
-        <v>-460538.36</v>
+        <v>-424814.4</v>
       </c>
       <c r="L23" s="3">
-        <v>4.77</v>
+        <v>4.42</v>
       </c>
       <c r="M23" s="3">
-        <v>19804.78</v>
+        <v>19962.28</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>10192</v>
+        <v>10479</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>10193</v>
+        <v>10480</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10194</v>
+        <v>10481</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>10195</v>
+        <v>10482</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>10196</v>
+        <v>10483</v>
       </c>
       <c r="F24" s="3">
-        <v>821118.86</v>
+        <v>873034.8</v>
       </c>
       <c r="G24" s="3">
-        <v>383652.5</v>
+        <v>301624.26</v>
       </c>
       <c r="H24" s="3">
-        <v>92411.56</v>
+        <v>104686.67</v>
       </c>
       <c r="I24" s="3">
-        <v>476064.06</v>
+        <v>406310.93</v>
       </c>
       <c r="J24" s="3">
-        <v>57.98</v>
+        <v>46.54</v>
       </c>
       <c r="K24" s="3">
-        <v>-345054.8</v>
+        <v>-466723.87</v>
       </c>
       <c r="L24" s="3">
-        <v>0.52</v>
+        <v>1.55</v>
       </c>
       <c r="M24" s="3">
-        <v>2498.46</v>
+        <v>6311.42</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>10197</v>
+        <v>10484</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10198</v>
+        <v>10485</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10199</v>
+        <v>10486</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>10200</v>
+        <v>10487</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>10201</v>
+        <v>10488</v>
       </c>
       <c r="F25" s="3">
         <v>969063.25</v>
       </c>
       <c r="G25" s="3">
-        <v>143173.66</v>
+        <v>156163.65</v>
       </c>
       <c r="H25" s="3">
-        <v>143646.95</v>
+        <v>147535.74</v>
       </c>
       <c r="I25" s="3">
-        <v>286820.61</v>
+        <v>303699.39</v>
       </c>
       <c r="J25" s="3">
-        <v>29.6</v>
+        <v>31.34</v>
       </c>
       <c r="K25" s="3">
-        <v>-682242.64</v>
+        <v>-665363.86</v>
       </c>
       <c r="L25" s="3">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="M25" s="3">
         <v>2317.96</v>
@@ -95190,163 +97773,163 @@
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>10202</v>
+        <v>10489</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>10203</v>
+        <v>10490</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10204</v>
+        <v>10491</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>10205</v>
+        <v>10492</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>10206</v>
+        <v>10493</v>
       </c>
       <c r="F26" s="3">
         <v>1050193.29</v>
       </c>
       <c r="G26" s="3">
-        <v>145982.01</v>
+        <v>154054.77</v>
       </c>
       <c r="H26" s="3">
-        <v>98709.88</v>
+        <v>104646.24</v>
       </c>
       <c r="I26" s="3">
-        <v>244691.89</v>
+        <v>258701.01</v>
       </c>
       <c r="J26" s="3">
-        <v>23.3</v>
+        <v>24.63</v>
       </c>
       <c r="K26" s="3">
-        <v>-805501.4</v>
+        <v>-791492.28</v>
       </c>
       <c r="L26" s="3">
-        <v>0.96</v>
+        <v>1.0</v>
       </c>
       <c r="M26" s="3">
-        <v>2349.41</v>
+        <v>2574.41</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>10207</v>
+        <v>10494</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10208</v>
+        <v>10495</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10209</v>
+        <v>10496</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>10210</v>
+        <v>10497</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>10211</v>
+        <v>10498</v>
       </c>
       <c r="F27" s="3">
-        <v>919135.8</v>
+        <v>1002913.88</v>
       </c>
       <c r="G27" s="3">
-        <v>246835.82</v>
+        <v>201129.89</v>
       </c>
       <c r="H27" s="3">
-        <v>128654.69</v>
+        <v>111112.15</v>
       </c>
       <c r="I27" s="3">
-        <v>375490.51</v>
+        <v>312242.04</v>
       </c>
       <c r="J27" s="3">
-        <v>40.85</v>
+        <v>31.13</v>
       </c>
       <c r="K27" s="3">
-        <v>-543645.29</v>
+        <v>-690671.84</v>
       </c>
       <c r="L27" s="3">
-        <v>1.21</v>
+        <v>0.18</v>
       </c>
       <c r="M27" s="3">
-        <v>4552.44</v>
+        <v>568.13</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>10212</v>
+        <v>10499</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>10213</v>
+        <v>10500</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10214</v>
+        <v>10501</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10215</v>
+        <v>10502</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>10216</v>
+        <v>10503</v>
       </c>
       <c r="F28" s="3">
-        <v>1002913.88</v>
+        <v>919135.8</v>
       </c>
       <c r="G28" s="3">
-        <v>191614.32</v>
+        <v>274643.26</v>
       </c>
       <c r="H28" s="3">
-        <v>105136.2</v>
+        <v>138488.1</v>
       </c>
       <c r="I28" s="3">
-        <v>296750.52</v>
+        <v>413131.36</v>
       </c>
       <c r="J28" s="3">
-        <v>29.59</v>
+        <v>44.95</v>
       </c>
       <c r="K28" s="3">
-        <v>-706163.36</v>
+        <v>-506004.44</v>
       </c>
       <c r="L28" s="3">
-        <v>0.19</v>
+        <v>1.31</v>
       </c>
       <c r="M28" s="3">
-        <v>568.13</v>
+        <v>5429.32</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>10217</v>
+        <v>10504</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>10218</v>
+        <v>10505</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10219</v>
+        <v>10506</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10220</v>
+        <v>10507</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>10221</v>
+        <v>10508</v>
       </c>
       <c r="F29" s="3">
         <v>872858.67</v>
       </c>
       <c r="G29" s="3">
-        <v>349223.92</v>
+        <v>358384.18</v>
       </c>
       <c r="H29" s="3">
-        <v>91508.85</v>
+        <v>104906.58</v>
       </c>
       <c r="I29" s="3">
-        <v>440732.77</v>
+        <v>463290.76</v>
       </c>
       <c r="J29" s="3">
-        <v>50.49</v>
+        <v>53.08</v>
       </c>
       <c r="K29" s="3">
-        <v>-432125.9</v>
+        <v>-409567.91</v>
       </c>
       <c r="L29" s="3">
-        <v>2.71</v>
+        <v>2.58</v>
       </c>
       <c r="M29" s="3">
         <v>11932.62</v>
@@ -95354,265 +97937,265 @@
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>10222</v>
+        <v>10509</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>10223</v>
+        <v>10510</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10224</v>
+        <v>10511</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10225</v>
+        <v>10512</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>10226</v>
+        <v>10513</v>
       </c>
       <c r="F30" s="3">
         <v>890266.15</v>
       </c>
       <c r="G30" s="3">
-        <v>321033.29</v>
+        <v>334239.04</v>
       </c>
       <c r="H30" s="3">
-        <v>111236.62</v>
+        <v>134633.59</v>
       </c>
       <c r="I30" s="3">
-        <v>432269.91</v>
+        <v>468872.63</v>
       </c>
       <c r="J30" s="3">
-        <v>48.56</v>
+        <v>52.67</v>
       </c>
       <c r="K30" s="3">
-        <v>-457996.24</v>
+        <v>-421393.52</v>
       </c>
       <c r="L30" s="3">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="M30" s="3">
-        <v>11225.42</v>
+        <v>12449.3</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>10227</v>
+        <v>10514</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>10228</v>
+        <v>10515</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10229</v>
+        <v>10516</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>10230</v>
+        <v>10517</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>10231</v>
+        <v>10518</v>
       </c>
       <c r="F31" s="3">
         <v>984099.44</v>
       </c>
       <c r="G31" s="3">
-        <v>290163.25</v>
+        <v>305509.91</v>
       </c>
       <c r="H31" s="3">
-        <v>114760.91</v>
+        <v>131184.45</v>
       </c>
       <c r="I31" s="3">
-        <v>404924.16</v>
+        <v>436694.36</v>
       </c>
       <c r="J31" s="3">
-        <v>41.15</v>
+        <v>44.38</v>
       </c>
       <c r="K31" s="3">
-        <v>-579175.28</v>
+        <v>-547405.08</v>
       </c>
       <c r="L31" s="3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="M31" s="3">
-        <v>7169.01</v>
+        <v>7694.01</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>10232</v>
+        <v>10519</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10233</v>
+        <v>10520</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10234</v>
+        <v>10521</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>10235</v>
+        <v>10522</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>10236</v>
+        <v>10523</v>
       </c>
       <c r="F32" s="3">
         <v>926984.47</v>
       </c>
       <c r="G32" s="3">
-        <v>200256.05</v>
+        <v>210327.62</v>
       </c>
       <c r="H32" s="3">
-        <v>91713.97</v>
+        <v>105521.91</v>
       </c>
       <c r="I32" s="3">
-        <v>291970.02</v>
+        <v>315849.53</v>
       </c>
       <c r="J32" s="3">
-        <v>31.5</v>
+        <v>34.07</v>
       </c>
       <c r="K32" s="3">
-        <v>-635014.45</v>
+        <v>-611134.94</v>
       </c>
       <c r="L32" s="3">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="M32" s="3">
-        <v>7339.72</v>
+        <v>8058.4</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>10237</v>
+        <v>10524</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>10238</v>
+        <v>10525</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10239</v>
+        <v>10526</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>10240</v>
+        <v>10527</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>10241</v>
+        <v>10528</v>
       </c>
       <c r="F33" s="3">
         <v>1288411.21</v>
       </c>
       <c r="G33" s="3">
-        <v>277019.74</v>
+        <v>359726.18</v>
       </c>
       <c r="H33" s="3">
-        <v>362839.81</v>
+        <v>280020.35</v>
       </c>
       <c r="I33" s="3">
-        <v>639859.55</v>
+        <v>639746.53</v>
       </c>
       <c r="J33" s="3">
-        <v>49.66</v>
+        <v>49.65</v>
       </c>
       <c r="K33" s="3">
-        <v>-648551.66</v>
+        <v>-648664.68</v>
       </c>
       <c r="L33" s="3">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="M33" s="3">
-        <v>9733.66</v>
+        <v>11421.08</v>
       </c>
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>10242</v>
+        <v>10529</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>10243</v>
+        <v>10530</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10244</v>
+        <v>10531</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>10245</v>
+        <v>10532</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>10246</v>
+        <v>10533</v>
       </c>
       <c r="F34" s="3">
         <v>1074641.52</v>
       </c>
       <c r="G34" s="3">
-        <v>215549.87</v>
+        <v>297359.17</v>
       </c>
       <c r="H34" s="3">
-        <v>126317.45</v>
+        <v>45276.79</v>
       </c>
       <c r="I34" s="3">
-        <v>341867.32</v>
+        <v>342635.96</v>
       </c>
       <c r="J34" s="3">
-        <v>31.81</v>
+        <v>31.88</v>
       </c>
       <c r="K34" s="3">
-        <v>-732774.2</v>
+        <v>-732005.56</v>
       </c>
       <c r="L34" s="3">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="M34" s="3">
-        <v>4452.55</v>
+        <v>5087.55</v>
       </c>
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>10247</v>
+        <v>10534</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>10248</v>
+        <v>10535</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10249</v>
+        <v>10536</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>10250</v>
+        <v>10537</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>10251</v>
+        <v>10538</v>
       </c>
       <c r="F35" s="3">
         <v>1054434.17</v>
       </c>
       <c r="G35" s="3">
-        <v>242281.41</v>
+        <v>333597.27</v>
       </c>
       <c r="H35" s="3">
-        <v>178238.63</v>
+        <v>84130.83</v>
       </c>
       <c r="I35" s="3">
-        <v>420520.04</v>
+        <v>417728.1</v>
       </c>
       <c r="J35" s="3">
-        <v>39.88</v>
+        <v>39.62</v>
       </c>
       <c r="K35" s="3">
-        <v>-633914.13</v>
+        <v>-636706.07</v>
       </c>
       <c r="L35" s="3">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="M35" s="3">
-        <v>5997.88</v>
+        <v>9104.82</v>
       </c>
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>10252</v>
+        <v>10539</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>10253</v>
+        <v>10540</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10254</v>
+        <v>10541</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>10255</v>
+        <v>10542</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>10256</v>
+        <v>10543</v>
       </c>
       <c r="F36" s="3">
         <v>1145461.66</v>
@@ -95621,19 +98204,19 @@
         <v>325235.41</v>
       </c>
       <c r="H36" s="3">
-        <v>235703.92</v>
+        <v>305959.62</v>
       </c>
       <c r="I36" s="3">
-        <v>560939.33</v>
+        <v>631195.03</v>
       </c>
       <c r="J36" s="3">
-        <v>48.97</v>
+        <v>55.1</v>
       </c>
       <c r="K36" s="3">
-        <v>-584522.33</v>
+        <v>-514266.63</v>
       </c>
       <c r="L36" s="3">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="M36" s="3">
         <v>9251.82</v>
@@ -95641,101 +98224,101 @@
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>10257</v>
+        <v>10544</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>10258</v>
+        <v>10545</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10259</v>
+        <v>10546</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>10260</v>
+        <v>10547</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>10261</v>
+        <v>10548</v>
       </c>
       <c r="F37" s="3">
-        <v>1392111.83</v>
+        <v>958935.26</v>
       </c>
       <c r="G37" s="3">
-        <v>365952.23</v>
+        <v>276172.76</v>
       </c>
       <c r="H37" s="3">
-        <v>244557.22</v>
+        <v>220549.06</v>
       </c>
       <c r="I37" s="3">
-        <v>610509.45</v>
+        <v>496721.82</v>
       </c>
       <c r="J37" s="3">
-        <v>43.85</v>
+        <v>51.8</v>
       </c>
       <c r="K37" s="3">
-        <v>-781602.38</v>
+        <v>-462213.44</v>
       </c>
       <c r="L37" s="3">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="M37" s="3">
-        <v>14141.13</v>
+        <v>11288.49</v>
       </c>
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>10262</v>
+        <v>10549</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>10263</v>
+        <v>10550</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10264</v>
+        <v>10551</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>10265</v>
+        <v>10552</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>10266</v>
+        <v>10553</v>
       </c>
       <c r="F38" s="3">
-        <v>958935.26</v>
+        <v>1392111.83</v>
       </c>
       <c r="G38" s="3">
-        <v>276172.76</v>
+        <v>365952.23</v>
       </c>
       <c r="H38" s="3">
-        <v>170530.23</v>
+        <v>320326.61</v>
       </c>
       <c r="I38" s="3">
-        <v>446702.99</v>
+        <v>686278.84</v>
       </c>
       <c r="J38" s="3">
-        <v>46.58</v>
+        <v>49.3</v>
       </c>
       <c r="K38" s="3">
-        <v>-512232.27</v>
+        <v>-705832.99</v>
       </c>
       <c r="L38" s="3">
-        <v>2.53</v>
+        <v>2.06</v>
       </c>
       <c r="M38" s="3">
-        <v>11288.49</v>
+        <v>14141.13</v>
       </c>
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>10267</v>
+        <v>10554</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>10268</v>
+        <v>10555</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10269</v>
+        <v>10556</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>10270</v>
+        <v>10557</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>10271</v>
+        <v>10558</v>
       </c>
       <c r="F39" s="3">
         <v>1141876.38</v>
@@ -95744,19 +98327,19 @@
         <v>249492.18</v>
       </c>
       <c r="H39" s="3">
-        <v>171498.65</v>
+        <v>207545.14</v>
       </c>
       <c r="I39" s="3">
-        <v>420990.83</v>
+        <v>457037.32</v>
       </c>
       <c r="J39" s="3">
-        <v>36.87</v>
+        <v>40.03</v>
       </c>
       <c r="K39" s="3">
-        <v>-720885.55</v>
+        <v>-684839.06</v>
       </c>
       <c r="L39" s="3">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="M39" s="3">
         <v>5325.48</v>
@@ -95764,28 +98347,28 @@
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>10272</v>
+        <v>10559</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>10273</v>
+        <v>10560</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10274</v>
+        <v>10561</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>10275</v>
+        <v>10562</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>10276</v>
+        <v>10563</v>
       </c>
       <c r="F40" s="3">
         <v>936014.91</v>
       </c>
       <c r="G40" s="3">
-        <v>165218.75</v>
+        <v>241945.85</v>
       </c>
       <c r="H40" s="3">
-        <v>168970.82</v>
+        <v>92243.72</v>
       </c>
       <c r="I40" s="3">
         <v>334189.57</v>
@@ -95805,151 +98388,151 @@
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>10277</v>
+        <v>10564</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>10278</v>
+        <v>10565</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10279</v>
+        <v>10566</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>10280</v>
+        <v>10567</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>10281</v>
+        <v>10568</v>
       </c>
       <c r="F41" s="3">
         <v>1227064.36</v>
       </c>
       <c r="G41" s="3">
-        <v>194340.41</v>
+        <v>291710.72</v>
       </c>
       <c r="H41" s="3">
-        <v>247632.85</v>
+        <v>148463.11</v>
       </c>
       <c r="I41" s="3">
-        <v>441973.26</v>
+        <v>440173.83</v>
       </c>
       <c r="J41" s="3">
-        <v>36.02</v>
+        <v>35.87</v>
       </c>
       <c r="K41" s="3">
-        <v>-785091.1</v>
+        <v>-786890.53</v>
       </c>
       <c r="L41" s="3">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="M41" s="3">
-        <v>7231.82</v>
+        <v>9031.25</v>
       </c>
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>10282</v>
+        <v>10569</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>10283</v>
+        <v>10570</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10284</v>
+        <v>10571</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>10285</v>
+        <v>10572</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>10286</v>
+        <v>10573</v>
       </c>
       <c r="F42" s="3">
         <v>940955.58</v>
       </c>
       <c r="G42" s="3">
-        <v>210016.37</v>
+        <v>270662.69</v>
       </c>
       <c r="H42" s="3">
-        <v>216302.63</v>
+        <v>154554.11</v>
       </c>
       <c r="I42" s="3">
-        <v>426319.0</v>
+        <v>425216.8</v>
       </c>
       <c r="J42" s="3">
-        <v>45.31</v>
+        <v>45.19</v>
       </c>
       <c r="K42" s="3">
-        <v>-514636.58</v>
+        <v>-515738.78</v>
       </c>
       <c r="L42" s="3">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="M42" s="3">
-        <v>5898.98</v>
+        <v>7001.18</v>
       </c>
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>10287</v>
+        <v>10574</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>10288</v>
+        <v>10575</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10289</v>
+        <v>10576</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>10290</v>
+        <v>10577</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>10291</v>
+        <v>10578</v>
       </c>
       <c r="F43" s="3">
         <v>1062667.74</v>
       </c>
       <c r="G43" s="3">
-        <v>274944.01</v>
+        <v>391092.39</v>
       </c>
       <c r="H43" s="3">
-        <v>279264.72</v>
+        <v>162929.34</v>
       </c>
       <c r="I43" s="3">
-        <v>554208.73</v>
+        <v>554021.73</v>
       </c>
       <c r="J43" s="3">
-        <v>52.15</v>
+        <v>52.13</v>
       </c>
       <c r="K43" s="3">
-        <v>-508459.01</v>
+        <v>-508646.01</v>
       </c>
       <c r="L43" s="3">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="M43" s="3">
-        <v>4175.42</v>
+        <v>4362.42</v>
       </c>
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>10292</v>
+        <v>10579</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>10293</v>
+        <v>10580</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10294</v>
+        <v>10581</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>10295</v>
+        <v>10582</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>10296</v>
+        <v>10583</v>
       </c>
       <c r="F44" s="3">
         <v>1129524.64</v>
       </c>
       <c r="G44" s="3">
-        <v>274952.64</v>
+        <v>368321.46</v>
       </c>
       <c r="H44" s="3">
-        <v>130066.93</v>
+        <v>36698.11</v>
       </c>
       <c r="I44" s="3">
         <v>405019.57</v>
@@ -95969,330 +98552,330 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>10297</v>
+        <v>10584</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>10298</v>
+        <v>10585</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10299</v>
+        <v>10586</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>10300</v>
+        <v>10587</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>10301</v>
+        <v>10588</v>
       </c>
       <c r="F45" s="3">
         <v>931654.84</v>
       </c>
       <c r="G45" s="3">
-        <v>275150.97</v>
+        <v>376949.05</v>
       </c>
       <c r="H45" s="3">
-        <v>140499.81</v>
+        <v>38026.85</v>
       </c>
       <c r="I45" s="3">
-        <v>415650.78</v>
+        <v>414975.9</v>
       </c>
       <c r="J45" s="3">
-        <v>44.61</v>
+        <v>44.54</v>
       </c>
       <c r="K45" s="3">
-        <v>-516004.06</v>
+        <v>-516678.94</v>
       </c>
       <c r="L45" s="3">
-        <v>0.44</v>
+        <v>0.61</v>
       </c>
       <c r="M45" s="3">
-        <v>1838.41</v>
+        <v>2513.29</v>
       </c>
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>10302</v>
+        <v>10589</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>10303</v>
+        <v>10590</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10304</v>
+        <v>10591</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>10305</v>
+        <v>10592</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>10306</v>
+        <v>10593</v>
       </c>
       <c r="F46" s="3">
         <v>1096879.63</v>
       </c>
       <c r="G46" s="3">
-        <v>285292.7</v>
+        <v>381972.68</v>
       </c>
       <c r="H46" s="3">
-        <v>130378.98</v>
+        <v>33436.5</v>
       </c>
       <c r="I46" s="3">
-        <v>415671.68</v>
+        <v>415409.18</v>
       </c>
       <c r="J46" s="3">
-        <v>37.9</v>
+        <v>37.87</v>
       </c>
       <c r="K46" s="3">
-        <v>-681207.95</v>
+        <v>-681470.45</v>
       </c>
       <c r="L46" s="3">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="M46" s="3">
-        <v>4852.09</v>
+        <v>5114.59</v>
       </c>
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>10307</v>
+        <v>10594</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>10308</v>
+        <v>10595</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>10309</v>
+        <v>10596</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>10310</v>
+        <v>10597</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>10311</v>
+        <v>10598</v>
       </c>
       <c r="F47" s="3">
         <v>1362950.73</v>
       </c>
       <c r="G47" s="3">
-        <v>209489.73</v>
+        <v>268110.84</v>
       </c>
       <c r="H47" s="3">
-        <v>318630.03</v>
+        <v>258483.92</v>
       </c>
       <c r="I47" s="3">
-        <v>528119.76</v>
+        <v>526594.76</v>
       </c>
       <c r="J47" s="3">
-        <v>38.75</v>
+        <v>38.64</v>
       </c>
       <c r="K47" s="3">
-        <v>-834830.97</v>
+        <v>-836355.97</v>
       </c>
       <c r="L47" s="3">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="M47" s="3">
-        <v>5465.5</v>
+        <v>6990.5</v>
       </c>
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>10312</v>
+        <v>10599</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>10313</v>
+        <v>10600</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10314</v>
+        <v>10601</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>10315</v>
+        <v>10602</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>10316</v>
+        <v>10603</v>
       </c>
       <c r="F48" s="3">
         <v>1050721.66</v>
       </c>
       <c r="G48" s="3">
-        <v>146518.13</v>
+        <v>186435.86</v>
       </c>
       <c r="H48" s="3">
-        <v>160579.64</v>
+        <v>118553.41</v>
       </c>
       <c r="I48" s="3">
-        <v>307097.77</v>
+        <v>304989.27</v>
       </c>
       <c r="J48" s="3">
-        <v>29.23</v>
+        <v>29.03</v>
       </c>
       <c r="K48" s="3">
-        <v>-743623.89</v>
+        <v>-745732.39</v>
       </c>
       <c r="L48" s="3">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="M48" s="3">
-        <v>4296.88</v>
+        <v>6405.38</v>
       </c>
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>10317</v>
+        <v>10604</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>10318</v>
+        <v>10605</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>10319</v>
+        <v>10606</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>10320</v>
+        <v>10607</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>10321</v>
+        <v>10608</v>
       </c>
       <c r="F49" s="3">
         <v>989655.83</v>
       </c>
       <c r="G49" s="3">
-        <v>201429.4</v>
+        <v>287832.95</v>
       </c>
       <c r="H49" s="3">
-        <v>237824.12</v>
+        <v>150945.89</v>
       </c>
       <c r="I49" s="3">
-        <v>439253.52</v>
+        <v>438778.84</v>
       </c>
       <c r="J49" s="3">
-        <v>44.38</v>
+        <v>44.34</v>
       </c>
       <c r="K49" s="3">
-        <v>-550402.31</v>
+        <v>-550876.99</v>
       </c>
       <c r="L49" s="3">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="M49" s="3">
-        <v>4211.06</v>
+        <v>4685.74</v>
       </c>
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>10322</v>
+        <v>10609</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>10323</v>
+        <v>10610</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>10324</v>
+        <v>10611</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>10325</v>
+        <v>10612</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>10326</v>
+        <v>10613</v>
       </c>
       <c r="F50" s="3">
         <v>978747.3</v>
       </c>
       <c r="G50" s="3">
-        <v>220425.9</v>
+        <v>261696.17</v>
       </c>
       <c r="H50" s="3">
-        <v>210586.25</v>
+        <v>165581.98</v>
       </c>
       <c r="I50" s="3">
-        <v>431012.15</v>
+        <v>427278.15</v>
       </c>
       <c r="J50" s="3">
-        <v>44.04</v>
+        <v>43.66</v>
       </c>
       <c r="K50" s="3">
-        <v>-547735.15</v>
+        <v>-551469.15</v>
       </c>
       <c r="L50" s="3">
-        <v>4.65</v>
+        <v>5.57</v>
       </c>
       <c r="M50" s="3">
-        <v>20062.36</v>
+        <v>23796.36</v>
       </c>
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>10327</v>
+        <v>10614</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>10328</v>
+        <v>10615</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>10329</v>
+        <v>10616</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>10330</v>
+        <v>10617</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>10331</v>
+        <v>10618</v>
       </c>
       <c r="F51" s="3">
         <v>983156.92</v>
       </c>
       <c r="G51" s="3">
-        <v>124327.37</v>
+        <v>218500.36</v>
       </c>
       <c r="H51" s="3">
-        <v>191043.11</v>
+        <v>96097.12</v>
       </c>
       <c r="I51" s="3">
-        <v>315370.48</v>
+        <v>314597.48</v>
       </c>
       <c r="J51" s="3">
-        <v>32.08</v>
+        <v>32.0</v>
       </c>
       <c r="K51" s="3">
-        <v>-667786.44</v>
+        <v>-668559.44</v>
       </c>
       <c r="L51" s="3">
-        <v>2.93</v>
+        <v>3.19</v>
       </c>
       <c r="M51" s="3">
-        <v>9248.71</v>
+        <v>10021.71</v>
       </c>
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>10332</v>
+        <v>10619</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>10333</v>
+        <v>10620</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>10334</v>
+        <v>10621</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>10335</v>
+        <v>10622</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>10336</v>
+        <v>10623</v>
       </c>
       <c r="F52" s="3">
         <v>1178421.11</v>
       </c>
       <c r="G52" s="3">
-        <v>207146.43</v>
+        <v>264228.21</v>
       </c>
       <c r="H52" s="3">
-        <v>184030.48</v>
+        <v>125233.5</v>
       </c>
       <c r="I52" s="3">
-        <v>391176.91</v>
+        <v>389461.71</v>
       </c>
       <c r="J52" s="3">
-        <v>33.2</v>
+        <v>33.05</v>
       </c>
       <c r="K52" s="3">
-        <v>-787244.2</v>
+        <v>-788959.4</v>
       </c>
       <c r="L52" s="3">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="M52" s="3">
-        <v>8548.16</v>
+        <v>10263.36</v>
       </c>
     </row>
     <row r="56" spans="8:8">
@@ -102772,7 +105355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AV49"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -102822,206 +105405,206 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>10337</v>
+        <v>10624</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10338</v>
+        <v>10625</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10339</v>
+        <v>10626</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10340</v>
+        <v>10627</v>
       </c>
       <c r="E2" s="3">
         <v>6104317.5</v>
       </c>
       <c r="F2" s="3">
-        <v>1458257.81</v>
+        <v>1572197.33</v>
       </c>
       <c r="G2" s="3">
-        <v>1524933.81</v>
+        <v>1558151.2</v>
       </c>
       <c r="H2" s="3">
-        <v>2983191.62</v>
+        <v>3130348.53</v>
       </c>
       <c r="I2" s="3">
-        <v>48.87</v>
+        <v>51.28</v>
       </c>
       <c r="J2" s="3">
-        <v>-3121125.88</v>
+        <v>-2973968.97</v>
       </c>
       <c r="K2" s="3">
-        <v>34750.39</v>
+        <v>41069.19</v>
       </c>
       <c r="L2" s="3">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>10341</v>
+        <v>10628</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10342</v>
+        <v>10629</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10343</v>
+        <v>10630</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10344</v>
+        <v>10631</v>
       </c>
       <c r="E3" s="3">
         <v>3440798.37</v>
       </c>
       <c r="F3" s="3">
-        <v>559858.59</v>
+        <v>641802.73</v>
       </c>
       <c r="G3" s="3">
-        <v>863994.97</v>
+        <v>852334.58</v>
       </c>
       <c r="H3" s="3">
-        <v>1423853.56</v>
+        <v>1494137.31</v>
       </c>
       <c r="I3" s="3">
-        <v>41.38</v>
+        <v>43.42</v>
       </c>
       <c r="J3" s="3">
-        <v>-2016944.81</v>
+        <v>-1946661.06</v>
       </c>
       <c r="K3" s="3">
-        <v>16613.54</v>
+        <v>18140.62</v>
       </c>
       <c r="L3" s="3">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>10345</v>
+        <v>10632</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10346</v>
+        <v>10633</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10347</v>
+        <v>10634</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10348</v>
+        <v>10635</v>
       </c>
       <c r="E4" s="3">
         <v>6398516.07</v>
       </c>
       <c r="F4" s="3">
-        <v>1136619.88</v>
+        <v>1157521.41</v>
       </c>
       <c r="G4" s="3">
-        <v>921227.0</v>
+        <v>1229262.16</v>
       </c>
       <c r="H4" s="3">
-        <v>2057846.88</v>
+        <v>2386783.57</v>
       </c>
       <c r="I4" s="3">
-        <v>32.16</v>
+        <v>37.3</v>
       </c>
       <c r="J4" s="3">
-        <v>-4340669.19</v>
+        <v>-4011732.5</v>
       </c>
       <c r="K4" s="3">
-        <v>38953.45</v>
+        <v>40391.81</v>
       </c>
       <c r="L4" s="3">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>10349</v>
+        <v>10636</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10350</v>
+        <v>10637</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10351</v>
+        <v>10638</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10352</v>
+        <v>10639</v>
       </c>
       <c r="E5" s="3">
         <v>7403170.5</v>
       </c>
       <c r="F5" s="3">
-        <v>1935058.78</v>
+        <v>2062117.78</v>
       </c>
       <c r="G5" s="3">
-        <v>877960.54</v>
+        <v>944783.54</v>
       </c>
       <c r="H5" s="3">
-        <v>2813019.32</v>
+        <v>3006901.32</v>
       </c>
       <c r="I5" s="3">
-        <v>38.0</v>
+        <v>40.62</v>
       </c>
       <c r="J5" s="3">
-        <v>-4590151.18</v>
+        <v>-4396269.18</v>
       </c>
       <c r="K5" s="3">
-        <v>47842.94</v>
+        <v>49463.82</v>
       </c>
       <c r="L5" s="3">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>10353</v>
+        <v>10640</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10354</v>
+        <v>10641</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10355</v>
+        <v>10642</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10356</v>
+        <v>10643</v>
       </c>
       <c r="E6" s="3">
         <v>7091695.63</v>
       </c>
       <c r="F6" s="3">
-        <v>1895527.52</v>
+        <v>2199143.37</v>
       </c>
       <c r="G6" s="3">
-        <v>1076616.24</v>
+        <v>901622.48</v>
       </c>
       <c r="H6" s="3">
-        <v>2972143.76</v>
+        <v>3100765.85</v>
       </c>
       <c r="I6" s="3">
-        <v>41.91</v>
+        <v>43.72</v>
       </c>
       <c r="J6" s="3">
-        <v>-4119551.87</v>
+        <v>-3990929.78</v>
       </c>
       <c r="K6" s="3">
-        <v>57850.86</v>
+        <v>65747.78</v>
       </c>
       <c r="L6" s="3">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>10357</v>
+        <v>10644</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10358</v>
+        <v>10645</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10359</v>
+        <v>10646</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10360</v>
+        <v>10647</v>
       </c>
       <c r="E7" s="3">
         <v>4638385.13</v>
@@ -103030,98 +105613,98 @@
         <v>1216852.58</v>
       </c>
       <c r="G7" s="3">
-        <v>822290.02</v>
+        <v>1184871.19</v>
       </c>
       <c r="H7" s="3">
-        <v>2039142.6</v>
+        <v>2401723.77</v>
       </c>
       <c r="I7" s="3">
-        <v>43.96</v>
+        <v>51.78</v>
       </c>
       <c r="J7" s="3">
-        <v>-2599242.53</v>
+        <v>-2236661.36</v>
       </c>
       <c r="K7" s="3">
         <v>40006.92</v>
       </c>
       <c r="L7" s="3">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>10361</v>
+        <v>10648</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10362</v>
+        <v>10649</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10363</v>
+        <v>10650</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10364</v>
+        <v>10651</v>
       </c>
       <c r="E8" s="3">
         <v>7324761.7</v>
       </c>
       <c r="F8" s="3">
-        <v>1679915.85</v>
+        <v>2322654.84</v>
       </c>
       <c r="G8" s="3">
-        <v>1313116.74</v>
+        <v>666351.74</v>
       </c>
       <c r="H8" s="3">
-        <v>2993032.59</v>
+        <v>2989006.58</v>
       </c>
       <c r="I8" s="3">
-        <v>40.86</v>
+        <v>40.81</v>
       </c>
       <c r="J8" s="3">
-        <v>-4331729.11</v>
+        <v>-4335755.12</v>
       </c>
       <c r="K8" s="3">
-        <v>31444.02</v>
+        <v>35470.03</v>
       </c>
       <c r="L8" s="3">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>10365</v>
+        <v>10652</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10366</v>
+        <v>10653</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10367</v>
+        <v>10654</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10368</v>
+        <v>10655</v>
       </c>
       <c r="E9" s="3">
         <v>6543653.55</v>
       </c>
       <c r="F9" s="3">
-        <v>1109336.96</v>
+        <v>1486804.39</v>
       </c>
       <c r="G9" s="3">
-        <v>1302693.63</v>
+        <v>914895.82</v>
       </c>
       <c r="H9" s="3">
-        <v>2412030.59</v>
+        <v>2401700.21</v>
       </c>
       <c r="I9" s="3">
-        <v>36.86</v>
+        <v>36.7</v>
       </c>
       <c r="J9" s="3">
-        <v>-4131622.96</v>
+        <v>-4141953.34</v>
       </c>
       <c r="K9" s="3">
-        <v>51832.67</v>
+        <v>62163.05</v>
       </c>
       <c r="L9" s="3">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="13" spans="8:8">
@@ -104229,7 +106812,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AP78"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="9" max="9" customWidth="1" width="5.8984375" style="0"/>
@@ -107558,7 +110141,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AE79"/>
+  <dimension ref="A1:AF79"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="29"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10656" count="10656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10943" count="10943">
   <si>
     <t>Region</t>
   </si>
@@ -94611,6 +94611,2589 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Sakib Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Ashis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Raj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sarkar, Mr. Partho Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Solayman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Kazi Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ali, Mr. Md. Suruj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amin, Mr. Md. Ruhul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K51</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Md. Bulbul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Ashraful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shake, Mr. Md. Remon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Debnath, Mr. Pritom Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sharma, Mr. Sumon Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Aminul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hasan, Mr. Md. Mehedi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Gain, Mr. Amit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Rubel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Rashedul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mahmud, Mr. Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Kabir, Mr. Md. Khairul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rasheduzzaman, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Siddique, Mr. Mohammad Abu Bakar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zaman, Mr. Sheik Almuz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Islam, Mr. Md. Shafiqul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Khan Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Khandoker, Mr. Md. Anis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Biswas, Mr. Nirmalendu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Murad, Mr. Md. Wahid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fakir, Mr. Md. Emon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Bikash Chandra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossen, Mr. Md. Jakir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K80</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shahrawardi, Mr. Md.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ACD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Munna, Mr. A. K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Suman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Ekramul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hassan, Mr. Md. Hasibul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hushain, Mr. Md. Rakib</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shaikh, Mr. Alamin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Ataur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Maruf, Mr. Md. Alkuch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Sajanur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Haque, Mr. Jahurul</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Zakaria, Mr. Sheikh Abdullah Al</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Pal, Mr. Basudab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Raihan, Mr. Md. Abu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Alam, Mr. Jahangir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Anisur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Roy, Mr. Sourov</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ahmed, Mr. Sakin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Habibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sikder, Mr. Abu Taleb</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Parvez, Mr. Rasel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bhattacharya, Mr. Krittibus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K41</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hridoy, Mr. Md. Russel Khan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
     </r>
   </si>
   <si>
@@ -96728,7 +99311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BA397"/>
+  <dimension ref="A1:BB397"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.8828125" style="0"/>
@@ -96789,245 +99372,245 @@
     </row>
     <row r="2" spans="8:8" ht="20.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>10369</v>
+        <v>10656</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10370</v>
+        <v>10657</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10371</v>
+        <v>10658</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10372</v>
+        <v>10659</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10373</v>
+        <v>10660</v>
       </c>
       <c r="F2" s="3">
-        <v>787067.06</v>
+        <v>740010.55</v>
       </c>
       <c r="G2" s="3">
-        <v>185702.45</v>
+        <v>162878.65</v>
       </c>
       <c r="H2" s="3">
-        <v>240205.32</v>
+        <v>177146.46</v>
       </c>
       <c r="I2" s="3">
-        <v>425907.77</v>
+        <v>340025.11</v>
       </c>
       <c r="J2" s="3">
-        <v>54.11</v>
+        <v>45.95</v>
       </c>
       <c r="K2" s="3">
-        <v>-361159.29</v>
+        <v>-399985.44</v>
       </c>
       <c r="L2" s="3">
-        <v>0.9</v>
+        <v>1.71</v>
       </c>
       <c r="M2" s="3">
-        <v>3831.08</v>
+        <v>5818.6</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="20.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>10374</v>
+        <v>10661</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10375</v>
+        <v>10662</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10376</v>
+        <v>10663</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10377</v>
+        <v>10664</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10378</v>
+        <v>10665</v>
       </c>
       <c r="F3" s="3">
         <v>792403.1</v>
       </c>
       <c r="G3" s="3">
-        <v>137157.01</v>
+        <v>148217.78</v>
       </c>
       <c r="H3" s="3">
-        <v>246722.44</v>
+        <v>250387.52</v>
       </c>
       <c r="I3" s="3">
-        <v>383879.45</v>
+        <v>398605.3</v>
       </c>
       <c r="J3" s="3">
-        <v>48.44</v>
+        <v>50.3</v>
       </c>
       <c r="K3" s="3">
-        <v>-408523.65</v>
+        <v>-393797.8</v>
       </c>
       <c r="L3" s="3">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="M3" s="3">
-        <v>6000.4</v>
+        <v>6009.4</v>
       </c>
     </row>
     <row r="4" spans="8:8" ht="20.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>10379</v>
+        <v>10666</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10380</v>
+        <v>10667</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10381</v>
+        <v>10668</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10382</v>
+        <v>10669</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10383</v>
+        <v>10670</v>
       </c>
       <c r="F4" s="3">
         <v>672792.28</v>
       </c>
       <c r="G4" s="3">
-        <v>322401.6</v>
+        <v>346066.59</v>
       </c>
       <c r="H4" s="3">
-        <v>190891.55</v>
+        <v>194629.21</v>
       </c>
       <c r="I4" s="3">
-        <v>513293.15</v>
+        <v>540695.8</v>
       </c>
       <c r="J4" s="3">
-        <v>76.29</v>
+        <v>80.37</v>
       </c>
       <c r="K4" s="3">
-        <v>-159499.13</v>
+        <v>-132096.48</v>
       </c>
       <c r="L4" s="3">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="M4" s="3">
-        <v>4857.02</v>
+        <v>5299.4</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="20.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>10384</v>
+        <v>10671</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10385</v>
+        <v>10672</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10386</v>
+        <v>10673</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10387</v>
+        <v>10674</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10388</v>
+        <v>10675</v>
       </c>
       <c r="F5" s="3">
-        <v>740010.55</v>
+        <v>787067.06</v>
       </c>
       <c r="G5" s="3">
-        <v>147842.76</v>
+        <v>198763.21</v>
       </c>
       <c r="H5" s="3">
-        <v>171558.61</v>
+        <v>245149.06</v>
       </c>
       <c r="I5" s="3">
-        <v>319401.37</v>
+        <v>443912.27</v>
       </c>
       <c r="J5" s="3">
-        <v>43.16</v>
+        <v>56.4</v>
       </c>
       <c r="K5" s="3">
-        <v>-420609.18</v>
+        <v>-343154.79</v>
       </c>
       <c r="L5" s="3">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="M5" s="3">
-        <v>4665.47</v>
+        <v>4558.18</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="20.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>10389</v>
+        <v>10676</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10390</v>
+        <v>10677</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10391</v>
+        <v>10678</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10392</v>
+        <v>10679</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10393</v>
+        <v>10680</v>
       </c>
       <c r="F6" s="3">
         <v>763526.5</v>
       </c>
       <c r="G6" s="3">
-        <v>241110.58</v>
+        <v>265933.2</v>
       </c>
       <c r="H6" s="3">
-        <v>198343.42</v>
+        <v>196921.31</v>
       </c>
       <c r="I6" s="3">
-        <v>439454.0</v>
+        <v>462854.51</v>
       </c>
       <c r="J6" s="3">
-        <v>57.56</v>
+        <v>60.62</v>
       </c>
       <c r="K6" s="3">
-        <v>-324072.5</v>
+        <v>-300671.99</v>
       </c>
       <c r="L6" s="3">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="M6" s="3">
-        <v>7035.93</v>
+        <v>10073.18</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="20.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>10394</v>
+        <v>10681</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10395</v>
+        <v>10682</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10396</v>
+        <v>10683</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10397</v>
+        <v>10684</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10398</v>
+        <v>10685</v>
       </c>
       <c r="F7" s="3">
         <v>803185.79</v>
       </c>
       <c r="G7" s="3">
-        <v>173761.64</v>
+        <v>189368.76</v>
       </c>
       <c r="H7" s="3">
-        <v>202717.66</v>
+        <v>201602.78</v>
       </c>
       <c r="I7" s="3">
-        <v>376479.3</v>
+        <v>390971.54</v>
       </c>
       <c r="J7" s="3">
-        <v>46.87</v>
+        <v>48.68</v>
       </c>
       <c r="K7" s="3">
-        <v>-426706.49</v>
+        <v>-412214.25</v>
       </c>
       <c r="L7" s="3">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="M7" s="3">
         <v>6058.29</v>
@@ -97035,245 +99618,245 @@
     </row>
     <row r="8" spans="8:8" ht="20.0" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>10399</v>
+        <v>10686</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10400</v>
+        <v>10687</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10401</v>
+        <v>10688</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10402</v>
+        <v>10689</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>10403</v>
+        <v>10690</v>
       </c>
       <c r="F8" s="3">
-        <v>774607.3</v>
+        <v>770724.92</v>
       </c>
       <c r="G8" s="3">
-        <v>172399.75</v>
+        <v>211860.94</v>
       </c>
       <c r="H8" s="3">
-        <v>156968.57</v>
+        <v>150566.83</v>
       </c>
       <c r="I8" s="3">
-        <v>329368.32</v>
+        <v>362427.77</v>
       </c>
       <c r="J8" s="3">
-        <v>42.52</v>
+        <v>47.02</v>
       </c>
       <c r="K8" s="3">
-        <v>-445238.98</v>
+        <v>-408297.15</v>
       </c>
       <c r="L8" s="3">
-        <v>0.77</v>
+        <v>2.09</v>
       </c>
       <c r="M8" s="3">
-        <v>2539.14</v>
+        <v>7581.3</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="20.0" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>10404</v>
+        <v>10691</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10405</v>
+        <v>10692</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10406</v>
+        <v>10693</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10407</v>
+        <v>10694</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>10408</v>
+        <v>10695</v>
       </c>
       <c r="F9" s="3">
-        <v>770724.92</v>
+        <v>774607.3</v>
       </c>
       <c r="G9" s="3">
-        <v>191821.56</v>
+        <v>185751.6</v>
       </c>
       <c r="H9" s="3">
-        <v>150743.64</v>
+        <v>163159.13</v>
       </c>
       <c r="I9" s="3">
-        <v>342565.2</v>
+        <v>348910.73</v>
       </c>
       <c r="J9" s="3">
-        <v>44.45</v>
+        <v>45.04</v>
       </c>
       <c r="K9" s="3">
-        <v>-428159.72</v>
+        <v>-425696.57</v>
       </c>
       <c r="L9" s="3">
-        <v>1.78</v>
+        <v>0.77</v>
       </c>
       <c r="M9" s="3">
-        <v>6081.86</v>
+        <v>2675.27</v>
       </c>
     </row>
     <row r="10" spans="8:8" ht="20.0" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>10409</v>
+        <v>10696</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10410</v>
+        <v>10697</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10411</v>
+        <v>10698</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10412</v>
+        <v>10699</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>10413</v>
+        <v>10700</v>
       </c>
       <c r="F10" s="3">
         <v>900349.47</v>
       </c>
       <c r="G10" s="3">
-        <v>117281.31</v>
+        <v>129154.85</v>
       </c>
       <c r="H10" s="3">
-        <v>211314.61</v>
+        <v>233352.44</v>
       </c>
       <c r="I10" s="3">
-        <v>328595.92</v>
+        <v>362507.29</v>
       </c>
       <c r="J10" s="3">
-        <v>36.5</v>
+        <v>40.26</v>
       </c>
       <c r="K10" s="3">
-        <v>-571753.55</v>
+        <v>-537842.18</v>
       </c>
       <c r="L10" s="3">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="M10" s="3">
-        <v>3651.82</v>
+        <v>3663.51</v>
       </c>
     </row>
     <row r="11" spans="8:8" ht="20.0" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>10414</v>
+        <v>10701</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>10415</v>
+        <v>10702</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10416</v>
+        <v>10703</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10417</v>
+        <v>10704</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>10418</v>
+        <v>10705</v>
       </c>
       <c r="F11" s="3">
         <v>901291.26</v>
       </c>
       <c r="G11" s="3">
-        <v>134758.74</v>
+        <v>150202.75</v>
       </c>
       <c r="H11" s="3">
-        <v>175549.25</v>
+        <v>195343.26</v>
       </c>
       <c r="I11" s="3">
-        <v>310307.99</v>
+        <v>345546.01</v>
       </c>
       <c r="J11" s="3">
-        <v>34.43</v>
+        <v>38.34</v>
       </c>
       <c r="K11" s="3">
-        <v>-590983.27</v>
+        <v>-555745.25</v>
       </c>
       <c r="L11" s="3">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="M11" s="3">
-        <v>4908.64</v>
+        <v>6084.69</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="20.0" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>10419</v>
+        <v>10706</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10420</v>
+        <v>10707</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10421</v>
+        <v>10708</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10422</v>
+        <v>10709</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>10423</v>
+        <v>10710</v>
       </c>
       <c r="F12" s="3">
         <v>790977.36</v>
       </c>
       <c r="G12" s="3">
-        <v>195511.04</v>
+        <v>220861.68</v>
       </c>
       <c r="H12" s="3">
-        <v>217094.11</v>
+        <v>239935.52</v>
       </c>
       <c r="I12" s="3">
-        <v>412605.15</v>
+        <v>460797.2</v>
       </c>
       <c r="J12" s="3">
-        <v>52.16</v>
+        <v>58.26</v>
       </c>
       <c r="K12" s="3">
-        <v>-378372.21</v>
+        <v>-330180.16</v>
       </c>
       <c r="L12" s="3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="M12" s="3">
-        <v>4306.2</v>
+        <v>4845.81</v>
       </c>
     </row>
     <row r="13" spans="8:8" ht="20.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>10424</v>
+        <v>10711</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10425</v>
+        <v>10712</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10426</v>
+        <v>10713</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10427</v>
+        <v>10714</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>10428</v>
+        <v>10715</v>
       </c>
       <c r="F13" s="3">
         <v>848180.28</v>
       </c>
       <c r="G13" s="3">
-        <v>194251.64</v>
+        <v>212366.89</v>
       </c>
       <c r="H13" s="3">
-        <v>248376.62</v>
+        <v>264309.47</v>
       </c>
       <c r="I13" s="3">
-        <v>442628.26</v>
+        <v>476676.36</v>
       </c>
       <c r="J13" s="3">
-        <v>52.19</v>
+        <v>56.2</v>
       </c>
       <c r="K13" s="3">
-        <v>-405552.02</v>
+        <v>-371503.92</v>
       </c>
       <c r="L13" s="3">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="M13" s="3">
         <v>5273.96</v>
@@ -97281,798 +99864,798 @@
     </row>
     <row r="14" spans="8:8" ht="20.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>10429</v>
+        <v>10716</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10430</v>
+        <v>10717</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10431</v>
+        <v>10718</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10432</v>
+        <v>10719</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>10433</v>
+        <v>10720</v>
       </c>
       <c r="F14" s="3">
         <v>788558.37</v>
       </c>
       <c r="G14" s="3">
-        <v>146122.61</v>
+        <v>164609.21</v>
       </c>
       <c r="H14" s="3">
-        <v>230417.04</v>
+        <v>232604.93</v>
       </c>
       <c r="I14" s="3">
-        <v>376539.65</v>
+        <v>397214.14</v>
       </c>
       <c r="J14" s="3">
-        <v>47.75</v>
+        <v>50.37</v>
       </c>
       <c r="K14" s="3">
-        <v>-412018.72</v>
+        <v>-391344.23</v>
       </c>
       <c r="L14" s="3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M14" s="3">
-        <v>5649.54</v>
+        <v>5891.4</v>
       </c>
     </row>
     <row r="15" spans="8:8" ht="20.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>10434</v>
+        <v>10721</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10435</v>
+        <v>10722</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10436</v>
+        <v>10723</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10437</v>
+        <v>10724</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>10438</v>
+        <v>10725</v>
       </c>
       <c r="F15" s="3">
         <v>816369.33</v>
       </c>
       <c r="G15" s="3">
-        <v>87735.01</v>
+        <v>97474.11</v>
       </c>
       <c r="H15" s="3">
-        <v>190450.93</v>
+        <v>197918.48</v>
       </c>
       <c r="I15" s="3">
-        <v>278185.94</v>
+        <v>295392.59</v>
       </c>
       <c r="J15" s="3">
-        <v>34.08</v>
+        <v>36.18</v>
       </c>
       <c r="K15" s="3">
-        <v>-538183.39</v>
+        <v>-520976.74</v>
       </c>
       <c r="L15" s="3">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="M15" s="3">
-        <v>5858.82</v>
+        <v>5872.31</v>
       </c>
     </row>
     <row r="16" spans="8:8" ht="20.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>10439</v>
+        <v>10726</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10440</v>
+        <v>10727</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10441</v>
+        <v>10728</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10442</v>
+        <v>10729</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>10443</v>
+        <v>10730</v>
       </c>
       <c r="F16" s="3">
         <v>792760.6</v>
       </c>
       <c r="G16" s="3">
-        <v>104259.06</v>
+        <v>116125.81</v>
       </c>
       <c r="H16" s="3">
-        <v>127436.27</v>
+        <v>125703.1</v>
       </c>
       <c r="I16" s="3">
-        <v>231695.33</v>
+        <v>241828.91</v>
       </c>
       <c r="J16" s="3">
-        <v>29.23</v>
+        <v>30.5</v>
       </c>
       <c r="K16" s="3">
-        <v>-561065.27</v>
+        <v>-550931.69</v>
       </c>
       <c r="L16" s="3">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="M16" s="3">
-        <v>1772.52</v>
+        <v>1997.4</v>
       </c>
     </row>
     <row r="17" spans="8:8" ht="20.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>10444</v>
+        <v>10731</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>10445</v>
+        <v>10732</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10446</v>
+        <v>10733</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>10447</v>
+        <v>10734</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>10448</v>
+        <v>10735</v>
       </c>
       <c r="F17" s="3">
         <v>786604.47</v>
       </c>
       <c r="G17" s="3">
-        <v>88278.3</v>
+        <v>99896.11</v>
       </c>
       <c r="H17" s="3">
-        <v>154876.56</v>
+        <v>165359.65</v>
       </c>
       <c r="I17" s="3">
-        <v>243154.86</v>
+        <v>265255.76</v>
       </c>
       <c r="J17" s="3">
-        <v>30.91</v>
+        <v>33.72</v>
       </c>
       <c r="K17" s="3">
-        <v>-543449.61</v>
+        <v>-521348.71</v>
       </c>
       <c r="L17" s="3">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M17" s="3">
-        <v>3058.08</v>
+        <v>3433.08</v>
       </c>
     </row>
     <row r="18" spans="8:8" ht="20.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>10449</v>
+        <v>10736</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>10450</v>
+        <v>10737</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10451</v>
+        <v>10738</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10452</v>
+        <v>10739</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>10453</v>
+        <v>10740</v>
       </c>
       <c r="F18" s="3">
         <v>1063383.58</v>
       </c>
       <c r="G18" s="3">
-        <v>235426.35</v>
+        <v>301423.63</v>
       </c>
       <c r="H18" s="3">
-        <v>140398.75</v>
+        <v>73085.44</v>
       </c>
       <c r="I18" s="3">
-        <v>375825.1</v>
+        <v>374509.07</v>
       </c>
       <c r="J18" s="3">
-        <v>35.34</v>
+        <v>35.22</v>
       </c>
       <c r="K18" s="3">
-        <v>-687558.48</v>
+        <v>-688874.51</v>
       </c>
       <c r="L18" s="3">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="M18" s="3">
-        <v>5518.52</v>
+        <v>6834.55</v>
       </c>
     </row>
     <row r="19" spans="8:8" ht="20.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>10454</v>
+        <v>10741</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10455</v>
+        <v>10742</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10456</v>
+        <v>10743</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10457</v>
+        <v>10744</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>10458</v>
+        <v>10745</v>
       </c>
       <c r="F19" s="3">
         <v>886606.12</v>
       </c>
       <c r="G19" s="3">
-        <v>238758.45</v>
+        <v>321881.5</v>
       </c>
       <c r="H19" s="3">
-        <v>146174.37</v>
+        <v>62470.28</v>
       </c>
       <c r="I19" s="3">
-        <v>384932.82</v>
+        <v>384351.78</v>
       </c>
       <c r="J19" s="3">
-        <v>43.42</v>
+        <v>43.35</v>
       </c>
       <c r="K19" s="3">
-        <v>-501673.3</v>
+        <v>-502254.34</v>
       </c>
       <c r="L19" s="3">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="M19" s="3">
-        <v>9038.84</v>
+        <v>9619.88</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="20.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>10459</v>
+        <v>10746</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>10460</v>
+        <v>10747</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10461</v>
+        <v>10748</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10462</v>
+        <v>10749</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>10463</v>
+        <v>10750</v>
       </c>
       <c r="F20" s="3">
         <v>1264233.6</v>
       </c>
       <c r="G20" s="3">
-        <v>256941.64</v>
+        <v>356563.37</v>
       </c>
       <c r="H20" s="3">
-        <v>239508.23</v>
+        <v>138961.04</v>
       </c>
       <c r="I20" s="3">
-        <v>496449.87</v>
+        <v>495524.41</v>
       </c>
       <c r="J20" s="3">
-        <v>39.27</v>
+        <v>39.2</v>
       </c>
       <c r="K20" s="3">
-        <v>-767783.73</v>
+        <v>-768709.19</v>
       </c>
       <c r="L20" s="3">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="M20" s="3">
-        <v>9495.49</v>
+        <v>10420.95</v>
       </c>
     </row>
     <row r="21" spans="8:8" ht="20.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>10464</v>
+        <v>10751</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>10465</v>
+        <v>10752</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10466</v>
+        <v>10753</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10467</v>
+        <v>10754</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>10468</v>
+        <v>10755</v>
       </c>
       <c r="F21" s="3">
         <v>821118.86</v>
       </c>
       <c r="G21" s="3">
-        <v>396738.38</v>
+        <v>431996.5</v>
       </c>
       <c r="H21" s="3">
-        <v>114437.81</v>
+        <v>135579.2</v>
       </c>
       <c r="I21" s="3">
-        <v>511176.19</v>
+        <v>567575.7</v>
       </c>
       <c r="J21" s="3">
-        <v>62.25</v>
+        <v>69.12</v>
       </c>
       <c r="K21" s="3">
-        <v>-309942.67</v>
+        <v>-253543.16</v>
       </c>
       <c r="L21" s="3">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="M21" s="3">
-        <v>2498.46</v>
+        <v>2535.94</v>
       </c>
     </row>
     <row r="22" spans="8:8" ht="20.0" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>10469</v>
+        <v>10756</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>10470</v>
+        <v>10757</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10471</v>
+        <v>10758</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>10472</v>
+        <v>10759</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>10473</v>
+        <v>10760</v>
       </c>
       <c r="F22" s="3">
-        <v>891542.61</v>
+        <v>876168.01</v>
       </c>
       <c r="G22" s="3">
-        <v>252864.78</v>
+        <v>358273.14</v>
       </c>
       <c r="H22" s="3">
-        <v>97422.02</v>
+        <v>124512.65</v>
       </c>
       <c r="I22" s="3">
-        <v>350286.8</v>
+        <v>482785.79</v>
       </c>
       <c r="J22" s="3">
-        <v>39.29</v>
+        <v>55.1</v>
       </c>
       <c r="K22" s="3">
-        <v>-541255.81</v>
+        <v>-393382.22</v>
       </c>
       <c r="L22" s="3">
-        <v>2.8</v>
+        <v>4.54</v>
       </c>
       <c r="M22" s="3">
-        <v>9801.84</v>
+        <v>21913.27</v>
       </c>
     </row>
     <row r="23" spans="8:8" ht="20.0" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>10474</v>
+        <v>10761</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10475</v>
+        <v>10762</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10476</v>
+        <v>10763</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>10477</v>
+        <v>10764</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>10478</v>
+        <v>10765</v>
       </c>
       <c r="F23" s="3">
-        <v>876168.01</v>
+        <v>891542.61</v>
       </c>
       <c r="G23" s="3">
-        <v>324898.79</v>
+        <v>267063.44</v>
       </c>
       <c r="H23" s="3">
-        <v>126454.82</v>
+        <v>112054.5</v>
       </c>
       <c r="I23" s="3">
-        <v>451353.61</v>
+        <v>379117.94</v>
       </c>
       <c r="J23" s="3">
-        <v>51.51</v>
+        <v>42.52</v>
       </c>
       <c r="K23" s="3">
-        <v>-424814.4</v>
+        <v>-512424.67</v>
       </c>
       <c r="L23" s="3">
-        <v>4.42</v>
+        <v>2.68</v>
       </c>
       <c r="M23" s="3">
-        <v>19962.28</v>
+        <v>10151.63</v>
       </c>
     </row>
     <row r="24" spans="8:8" ht="20.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>10479</v>
+        <v>10766</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>10480</v>
+        <v>10767</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10481</v>
+        <v>10768</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>10482</v>
+        <v>10769</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>10483</v>
+        <v>10770</v>
       </c>
       <c r="F24" s="3">
         <v>873034.8</v>
       </c>
       <c r="G24" s="3">
-        <v>301624.26</v>
+        <v>326575.65</v>
       </c>
       <c r="H24" s="3">
-        <v>104686.67</v>
+        <v>111353.63</v>
       </c>
       <c r="I24" s="3">
-        <v>406310.93</v>
+        <v>437929.28</v>
       </c>
       <c r="J24" s="3">
-        <v>46.54</v>
+        <v>50.16</v>
       </c>
       <c r="K24" s="3">
-        <v>-466723.87</v>
+        <v>-435105.52</v>
       </c>
       <c r="L24" s="3">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="M24" s="3">
-        <v>6311.42</v>
+        <v>6401.39</v>
       </c>
     </row>
     <row r="25" spans="8:8" ht="20.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>10484</v>
+        <v>10771</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10485</v>
+        <v>10772</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10486</v>
+        <v>10773</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>10487</v>
+        <v>10774</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>10488</v>
+        <v>10775</v>
       </c>
       <c r="F25" s="3">
         <v>969063.25</v>
       </c>
       <c r="G25" s="3">
-        <v>156163.65</v>
+        <v>172754.43</v>
       </c>
       <c r="H25" s="3">
-        <v>147535.74</v>
+        <v>149866.06</v>
       </c>
       <c r="I25" s="3">
-        <v>303699.39</v>
+        <v>322620.49</v>
       </c>
       <c r="J25" s="3">
-        <v>31.34</v>
+        <v>33.29</v>
       </c>
       <c r="K25" s="3">
-        <v>-665363.86</v>
+        <v>-646442.76</v>
       </c>
       <c r="L25" s="3">
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="M25" s="3">
-        <v>2317.96</v>
+        <v>2605.96</v>
       </c>
     </row>
     <row r="26" spans="8:8" ht="20.0" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>10489</v>
+        <v>10776</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>10490</v>
+        <v>10777</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10491</v>
+        <v>10778</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>10492</v>
+        <v>10779</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>10493</v>
+        <v>10780</v>
       </c>
       <c r="F26" s="3">
         <v>1050193.29</v>
       </c>
       <c r="G26" s="3">
-        <v>154054.77</v>
+        <v>168652.86</v>
       </c>
       <c r="H26" s="3">
-        <v>104646.24</v>
+        <v>114972.83</v>
       </c>
       <c r="I26" s="3">
-        <v>258701.01</v>
+        <v>283625.69</v>
       </c>
       <c r="J26" s="3">
-        <v>24.63</v>
+        <v>27.01</v>
       </c>
       <c r="K26" s="3">
-        <v>-791492.28</v>
+        <v>-766567.6</v>
       </c>
       <c r="L26" s="3">
-        <v>1.0</v>
+        <v>0.95</v>
       </c>
       <c r="M26" s="3">
-        <v>2574.41</v>
+        <v>2688.96</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.0" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>10494</v>
+        <v>10781</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10495</v>
+        <v>10782</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10496</v>
+        <v>10783</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>10497</v>
+        <v>10784</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>10498</v>
+        <v>10785</v>
       </c>
       <c r="F27" s="3">
         <v>1002913.88</v>
       </c>
       <c r="G27" s="3">
-        <v>201129.89</v>
+        <v>216831.42</v>
       </c>
       <c r="H27" s="3">
-        <v>111112.15</v>
+        <v>112670.8</v>
       </c>
       <c r="I27" s="3">
-        <v>312242.04</v>
+        <v>329502.22</v>
       </c>
       <c r="J27" s="3">
-        <v>31.13</v>
+        <v>32.85</v>
       </c>
       <c r="K27" s="3">
-        <v>-690671.84</v>
+        <v>-673411.66</v>
       </c>
       <c r="L27" s="3">
         <v>0.18</v>
       </c>
       <c r="M27" s="3">
-        <v>568.13</v>
+        <v>607.11</v>
       </c>
     </row>
     <row r="28" spans="8:8" ht="20.0" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>10499</v>
+        <v>10786</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>10500</v>
+        <v>10787</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10501</v>
+        <v>10788</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10502</v>
+        <v>10789</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>10503</v>
+        <v>10790</v>
       </c>
       <c r="F28" s="3">
         <v>919135.8</v>
       </c>
       <c r="G28" s="3">
-        <v>274643.26</v>
+        <v>312835.27</v>
       </c>
       <c r="H28" s="3">
-        <v>138488.1</v>
+        <v>133925.89</v>
       </c>
       <c r="I28" s="3">
-        <v>413131.36</v>
+        <v>446761.16</v>
       </c>
       <c r="J28" s="3">
-        <v>44.95</v>
+        <v>48.61</v>
       </c>
       <c r="K28" s="3">
-        <v>-506004.44</v>
+        <v>-472374.64</v>
       </c>
       <c r="L28" s="3">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M28" s="3">
-        <v>5429.32</v>
+        <v>6050.56</v>
       </c>
     </row>
     <row r="29" spans="8:8" ht="20.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>10504</v>
+        <v>10791</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>10505</v>
+        <v>10792</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10506</v>
+        <v>10793</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10507</v>
+        <v>10794</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>10508</v>
+        <v>10795</v>
       </c>
       <c r="F29" s="3">
         <v>872858.67</v>
       </c>
       <c r="G29" s="3">
-        <v>358384.18</v>
+        <v>383704.49</v>
       </c>
       <c r="H29" s="3">
-        <v>104906.58</v>
+        <v>151788.96</v>
       </c>
       <c r="I29" s="3">
-        <v>463290.76</v>
+        <v>535493.45</v>
       </c>
       <c r="J29" s="3">
-        <v>53.08</v>
+        <v>61.35</v>
       </c>
       <c r="K29" s="3">
-        <v>-409567.91</v>
+        <v>-337365.22</v>
       </c>
       <c r="L29" s="3">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="M29" s="3">
-        <v>11932.62</v>
+        <v>12981.06</v>
       </c>
     </row>
     <row r="30" spans="8:8" ht="20.0" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>10509</v>
+        <v>10796</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>10510</v>
+        <v>10797</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10511</v>
+        <v>10798</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10512</v>
+        <v>10799</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>10513</v>
+        <v>10800</v>
       </c>
       <c r="F30" s="3">
         <v>890266.15</v>
       </c>
       <c r="G30" s="3">
-        <v>334239.04</v>
+        <v>371722.62</v>
       </c>
       <c r="H30" s="3">
-        <v>134633.59</v>
+        <v>148703.64</v>
       </c>
       <c r="I30" s="3">
-        <v>468872.63</v>
+        <v>520426.26</v>
       </c>
       <c r="J30" s="3">
-        <v>52.67</v>
+        <v>58.46</v>
       </c>
       <c r="K30" s="3">
-        <v>-421393.52</v>
+        <v>-369839.89</v>
       </c>
       <c r="L30" s="3">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
       <c r="M30" s="3">
-        <v>12449.3</v>
+        <v>15224.48</v>
       </c>
     </row>
     <row r="31" spans="8:8" ht="20.0" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>10514</v>
+        <v>10801</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>10515</v>
+        <v>10802</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10516</v>
+        <v>10803</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>10517</v>
+        <v>10804</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>10518</v>
+        <v>10805</v>
       </c>
       <c r="F31" s="3">
         <v>984099.44</v>
       </c>
       <c r="G31" s="3">
-        <v>305509.91</v>
+        <v>339149.48</v>
       </c>
       <c r="H31" s="3">
-        <v>131184.45</v>
+        <v>153936.66</v>
       </c>
       <c r="I31" s="3">
-        <v>436694.36</v>
+        <v>493086.14</v>
       </c>
       <c r="J31" s="3">
-        <v>44.38</v>
+        <v>50.11</v>
       </c>
       <c r="K31" s="3">
-        <v>-547405.08</v>
+        <v>-491013.3</v>
       </c>
       <c r="L31" s="3">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="M31" s="3">
-        <v>7694.01</v>
+        <v>8728.71</v>
       </c>
     </row>
     <row r="32" spans="8:8" ht="20.0" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>10519</v>
+        <v>10806</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10520</v>
+        <v>10807</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10521</v>
+        <v>10808</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>10522</v>
+        <v>10809</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>10523</v>
+        <v>10810</v>
       </c>
       <c r="F32" s="3">
         <v>926984.47</v>
       </c>
       <c r="G32" s="3">
-        <v>210327.62</v>
+        <v>233934.39</v>
       </c>
       <c r="H32" s="3">
-        <v>105521.91</v>
+        <v>123444.22</v>
       </c>
       <c r="I32" s="3">
-        <v>315849.53</v>
+        <v>357378.61</v>
       </c>
       <c r="J32" s="3">
-        <v>34.07</v>
+        <v>38.55</v>
       </c>
       <c r="K32" s="3">
-        <v>-611134.94</v>
+        <v>-569605.86</v>
       </c>
       <c r="L32" s="3">
-        <v>2.55</v>
+        <v>3.13</v>
       </c>
       <c r="M32" s="3">
-        <v>8058.4</v>
+        <v>11179.3</v>
       </c>
     </row>
     <row r="33" spans="8:8" ht="20.0" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>10524</v>
+        <v>10811</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>10525</v>
+        <v>10812</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10526</v>
+        <v>10813</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>10527</v>
+        <v>10814</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>10528</v>
+        <v>10815</v>
       </c>
       <c r="F33" s="3">
         <v>1288411.21</v>
@@ -98081,19 +100664,19 @@
         <v>359726.18</v>
       </c>
       <c r="H33" s="3">
-        <v>280020.35</v>
+        <v>360897.47</v>
       </c>
       <c r="I33" s="3">
-        <v>639746.53</v>
+        <v>720623.65</v>
       </c>
       <c r="J33" s="3">
-        <v>49.65</v>
+        <v>55.93</v>
       </c>
       <c r="K33" s="3">
-        <v>-648664.68</v>
+        <v>-567787.56</v>
       </c>
       <c r="L33" s="3">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="M33" s="3">
         <v>11421.08</v>
@@ -98101,19 +100684,19 @@
     </row>
     <row r="34" spans="8:8" ht="20.0" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>10529</v>
+        <v>10816</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>10530</v>
+        <v>10817</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10531</v>
+        <v>10818</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>10532</v>
+        <v>10819</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>10533</v>
+        <v>10820</v>
       </c>
       <c r="F34" s="3">
         <v>1074641.52</v>
@@ -98122,19 +100705,19 @@
         <v>297359.17</v>
       </c>
       <c r="H34" s="3">
-        <v>45276.79</v>
+        <v>102443.25</v>
       </c>
       <c r="I34" s="3">
-        <v>342635.96</v>
+        <v>399802.42</v>
       </c>
       <c r="J34" s="3">
-        <v>31.88</v>
+        <v>37.2</v>
       </c>
       <c r="K34" s="3">
-        <v>-732005.56</v>
+        <v>-674839.1</v>
       </c>
       <c r="L34" s="3">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="M34" s="3">
         <v>5087.55</v>
@@ -98142,19 +100725,19 @@
     </row>
     <row r="35" spans="8:8" ht="20.0" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>10534</v>
+        <v>10821</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>10535</v>
+        <v>10822</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10536</v>
+        <v>10823</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>10537</v>
+        <v>10824</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>10538</v>
+        <v>10825</v>
       </c>
       <c r="F35" s="3">
         <v>1054434.17</v>
@@ -98163,19 +100746,19 @@
         <v>333597.27</v>
       </c>
       <c r="H35" s="3">
-        <v>84130.83</v>
+        <v>144401.65</v>
       </c>
       <c r="I35" s="3">
-        <v>417728.1</v>
+        <v>477998.92</v>
       </c>
       <c r="J35" s="3">
-        <v>39.62</v>
+        <v>45.33</v>
       </c>
       <c r="K35" s="3">
-        <v>-636706.07</v>
+        <v>-576435.25</v>
       </c>
       <c r="L35" s="3">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="M35" s="3">
         <v>9104.82</v>
@@ -98183,40 +100766,40 @@
     </row>
     <row r="36" spans="8:8" ht="20.0" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>10539</v>
+        <v>10826</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>10540</v>
+        <v>10827</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10541</v>
+        <v>10828</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>10542</v>
+        <v>10829</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>10543</v>
+        <v>10830</v>
       </c>
       <c r="F36" s="3">
         <v>1145461.66</v>
       </c>
       <c r="G36" s="3">
-        <v>325235.41</v>
+        <v>364761.08</v>
       </c>
       <c r="H36" s="3">
-        <v>305959.62</v>
+        <v>299058.48</v>
       </c>
       <c r="I36" s="3">
-        <v>631195.03</v>
+        <v>663819.56</v>
       </c>
       <c r="J36" s="3">
-        <v>55.1</v>
+        <v>57.95</v>
       </c>
       <c r="K36" s="3">
-        <v>-514266.63</v>
+        <v>-481642.1</v>
       </c>
       <c r="L36" s="3">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="M36" s="3">
         <v>9251.82</v>
@@ -98224,40 +100807,40 @@
     </row>
     <row r="37" spans="8:8" ht="20.0" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>10544</v>
+        <v>10831</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>10545</v>
+        <v>10832</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10546</v>
+        <v>10833</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>10547</v>
+        <v>10834</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>10548</v>
+        <v>10835</v>
       </c>
       <c r="F37" s="3">
         <v>958935.26</v>
       </c>
       <c r="G37" s="3">
-        <v>276172.76</v>
+        <v>306660.53</v>
       </c>
       <c r="H37" s="3">
-        <v>220549.06</v>
+        <v>229543.42</v>
       </c>
       <c r="I37" s="3">
-        <v>496721.82</v>
+        <v>536203.95</v>
       </c>
       <c r="J37" s="3">
-        <v>51.8</v>
+        <v>55.92</v>
       </c>
       <c r="K37" s="3">
-        <v>-462213.44</v>
+        <v>-422731.31</v>
       </c>
       <c r="L37" s="3">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="M37" s="3">
         <v>11288.49</v>
@@ -98265,40 +100848,40 @@
     </row>
     <row r="38" spans="8:8" ht="20.0" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>10549</v>
+        <v>10836</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>10550</v>
+        <v>10837</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10551</v>
+        <v>10838</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>10552</v>
+        <v>10839</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>10553</v>
+        <v>10840</v>
       </c>
       <c r="F38" s="3">
         <v>1392111.83</v>
       </c>
       <c r="G38" s="3">
-        <v>365952.23</v>
+        <v>406759.92</v>
       </c>
       <c r="H38" s="3">
-        <v>320326.61</v>
+        <v>316565.68</v>
       </c>
       <c r="I38" s="3">
-        <v>686278.84</v>
+        <v>723325.6</v>
       </c>
       <c r="J38" s="3">
-        <v>49.3</v>
+        <v>51.96</v>
       </c>
       <c r="K38" s="3">
-        <v>-705832.99</v>
+        <v>-668786.23</v>
       </c>
       <c r="L38" s="3">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="M38" s="3">
         <v>14141.13</v>
@@ -98306,60 +100889,60 @@
     </row>
     <row r="39" spans="8:8" ht="20.0" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>10554</v>
+        <v>10841</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>10555</v>
+        <v>10842</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10556</v>
+        <v>10843</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>10557</v>
+        <v>10844</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>10558</v>
+        <v>10845</v>
       </c>
       <c r="F39" s="3">
         <v>1141876.38</v>
       </c>
       <c r="G39" s="3">
-        <v>249492.18</v>
+        <v>266870.54</v>
       </c>
       <c r="H39" s="3">
-        <v>207545.14</v>
+        <v>211010.44</v>
       </c>
       <c r="I39" s="3">
-        <v>457037.32</v>
+        <v>477880.98</v>
       </c>
       <c r="J39" s="3">
-        <v>40.03</v>
+        <v>41.85</v>
       </c>
       <c r="K39" s="3">
-        <v>-684839.06</v>
+        <v>-663995.4</v>
       </c>
       <c r="L39" s="3">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="M39" s="3">
-        <v>5325.48</v>
+        <v>5819.16</v>
       </c>
     </row>
     <row r="40" spans="8:8" ht="20.0" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>10559</v>
+        <v>10846</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>10560</v>
+        <v>10847</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10561</v>
+        <v>10848</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>10562</v>
+        <v>10849</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>10563</v>
+        <v>10850</v>
       </c>
       <c r="F40" s="3">
         <v>936014.91</v>
@@ -98368,19 +100951,19 @@
         <v>241945.85</v>
       </c>
       <c r="H40" s="3">
-        <v>92243.72</v>
+        <v>143714.96</v>
       </c>
       <c r="I40" s="3">
-        <v>334189.57</v>
+        <v>385660.81</v>
       </c>
       <c r="J40" s="3">
-        <v>35.7</v>
+        <v>41.2</v>
       </c>
       <c r="K40" s="3">
-        <v>-601825.34</v>
+        <v>-550354.1</v>
       </c>
       <c r="L40" s="3">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="M40" s="3">
         <v>2807.4</v>
@@ -98388,19 +100971,19 @@
     </row>
     <row r="41" spans="8:8" ht="20.0" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>10564</v>
+        <v>10851</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>10565</v>
+        <v>10852</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10566</v>
+        <v>10853</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>10567</v>
+        <v>10854</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>10568</v>
+        <v>10855</v>
       </c>
       <c r="F41" s="3">
         <v>1227064.36</v>
@@ -98409,19 +100992,19 @@
         <v>291710.72</v>
       </c>
       <c r="H41" s="3">
-        <v>148463.11</v>
+        <v>206219.53</v>
       </c>
       <c r="I41" s="3">
-        <v>440173.83</v>
+        <v>497930.25</v>
       </c>
       <c r="J41" s="3">
-        <v>35.87</v>
+        <v>40.58</v>
       </c>
       <c r="K41" s="3">
-        <v>-786890.53</v>
+        <v>-729134.11</v>
       </c>
       <c r="L41" s="3">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="M41" s="3">
         <v>9031.25</v>
@@ -98429,19 +101012,19 @@
     </row>
     <row r="42" spans="8:8" ht="20.0" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>10569</v>
+        <v>10856</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>10570</v>
+        <v>10857</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10571</v>
+        <v>10858</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>10572</v>
+        <v>10859</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>10573</v>
+        <v>10860</v>
       </c>
       <c r="F42" s="3">
         <v>940955.58</v>
@@ -98450,19 +101033,19 @@
         <v>270662.69</v>
       </c>
       <c r="H42" s="3">
-        <v>154554.11</v>
+        <v>216934.74</v>
       </c>
       <c r="I42" s="3">
-        <v>425216.8</v>
+        <v>487597.43</v>
       </c>
       <c r="J42" s="3">
-        <v>45.19</v>
+        <v>51.82</v>
       </c>
       <c r="K42" s="3">
-        <v>-515738.78</v>
+        <v>-453358.15</v>
       </c>
       <c r="L42" s="3">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="M42" s="3">
         <v>7001.18</v>
@@ -98470,19 +101053,19 @@
     </row>
     <row r="43" spans="8:8" ht="20.0" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>10574</v>
+        <v>10861</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>10575</v>
+        <v>10862</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10576</v>
+        <v>10863</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>10577</v>
+        <v>10864</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>10578</v>
+        <v>10865</v>
       </c>
       <c r="F43" s="3">
         <v>1062667.74</v>
@@ -98491,19 +101074,19 @@
         <v>391092.39</v>
       </c>
       <c r="H43" s="3">
-        <v>162929.34</v>
+        <v>241081.48</v>
       </c>
       <c r="I43" s="3">
-        <v>554021.73</v>
+        <v>632173.87</v>
       </c>
       <c r="J43" s="3">
-        <v>52.13</v>
+        <v>59.49</v>
       </c>
       <c r="K43" s="3">
-        <v>-508646.01</v>
+        <v>-430493.87</v>
       </c>
       <c r="L43" s="3">
-        <v>0.79</v>
+        <v>0.69</v>
       </c>
       <c r="M43" s="3">
         <v>4362.42</v>
@@ -98511,19 +101094,19 @@
     </row>
     <row r="44" spans="8:8" ht="20.0" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>10579</v>
+        <v>10866</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>10580</v>
+        <v>10867</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10581</v>
+        <v>10868</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>10582</v>
+        <v>10869</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>10583</v>
+        <v>10870</v>
       </c>
       <c r="F44" s="3">
         <v>1129524.64</v>
@@ -98552,19 +101135,19 @@
     </row>
     <row r="45" spans="8:8" ht="20.0" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>10584</v>
+        <v>10871</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>10585</v>
+        <v>10872</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10586</v>
+        <v>10873</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>10587</v>
+        <v>10874</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>10588</v>
+        <v>10875</v>
       </c>
       <c r="F45" s="3">
         <v>931654.84</v>
@@ -98593,19 +101176,19 @@
     </row>
     <row r="46" spans="8:8" ht="20.0" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>10589</v>
+        <v>10876</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>10590</v>
+        <v>10877</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10591</v>
+        <v>10878</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>10592</v>
+        <v>10879</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>10593</v>
+        <v>10880</v>
       </c>
       <c r="F46" s="3">
         <v>1096879.63</v>
@@ -98634,19 +101217,19 @@
     </row>
     <row r="47" spans="8:8" ht="20.0" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>10594</v>
+        <v>10881</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>10595</v>
+        <v>10882</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>10596</v>
+        <v>10883</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>10597</v>
+        <v>10884</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>10598</v>
+        <v>10885</v>
       </c>
       <c r="F47" s="3">
         <v>1362950.73</v>
@@ -98675,19 +101258,19 @@
     </row>
     <row r="48" spans="8:8" ht="20.0" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>10599</v>
+        <v>10886</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>10600</v>
+        <v>10887</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10601</v>
+        <v>10888</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>10602</v>
+        <v>10889</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>10603</v>
+        <v>10890</v>
       </c>
       <c r="F48" s="3">
         <v>1050721.66</v>
@@ -98716,19 +101299,19 @@
     </row>
     <row r="49" spans="8:8" ht="20.0" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>10604</v>
+        <v>10891</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>10605</v>
+        <v>10892</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>10606</v>
+        <v>10893</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>10607</v>
+        <v>10894</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>10608</v>
+        <v>10895</v>
       </c>
       <c r="F49" s="3">
         <v>989655.83</v>
@@ -98757,19 +101340,19 @@
     </row>
     <row r="50" spans="8:8" ht="20.0" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>10609</v>
+        <v>10896</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>10610</v>
+        <v>10897</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>10611</v>
+        <v>10898</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>10612</v>
+        <v>10899</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>10613</v>
+        <v>10900</v>
       </c>
       <c r="F50" s="3">
         <v>978747.3</v>
@@ -98798,19 +101381,19 @@
     </row>
     <row r="51" spans="8:8" ht="20.0" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>10614</v>
+        <v>10901</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>10615</v>
+        <v>10902</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>10616</v>
+        <v>10903</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>10617</v>
+        <v>10904</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>10618</v>
+        <v>10905</v>
       </c>
       <c r="F51" s="3">
         <v>983156.92</v>
@@ -98839,19 +101422,19 @@
     </row>
     <row r="52" spans="8:8" ht="20.0" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>10619</v>
+        <v>10906</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>10620</v>
+        <v>10907</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>10621</v>
+        <v>10908</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>10622</v>
+        <v>10909</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>10623</v>
+        <v>10910</v>
       </c>
       <c r="F52" s="3">
         <v>1178421.11</v>
@@ -105355,7 +107938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AV49"/>
+  <dimension ref="A1:AW49"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="13.363281" style="0"/>
@@ -105405,75 +107988,75 @@
     </row>
     <row r="2" spans="8:8" ht="36.7">
       <c r="A2" s="2" t="s">
-        <v>10624</v>
+        <v>10911</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10625</v>
+        <v>10912</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10626</v>
+        <v>10913</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10627</v>
+        <v>10914</v>
       </c>
       <c r="E2" s="3">
         <v>6104317.5</v>
       </c>
       <c r="F2" s="3">
-        <v>1572197.33</v>
+        <v>1716427.19</v>
       </c>
       <c r="G2" s="3">
-        <v>1558151.2</v>
+        <v>1568226.79</v>
       </c>
       <c r="H2" s="3">
-        <v>3130348.53</v>
+        <v>3284653.98</v>
       </c>
       <c r="I2" s="3">
-        <v>51.28</v>
+        <v>53.81</v>
       </c>
       <c r="J2" s="3">
-        <v>-2973968.97</v>
+        <v>-2819663.52</v>
       </c>
       <c r="K2" s="3">
-        <v>41069.19</v>
+        <v>48853.24</v>
       </c>
       <c r="L2" s="3">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="3" spans="8:8" ht="24.45">
       <c r="A3" s="2" t="s">
-        <v>10628</v>
+        <v>10915</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10629</v>
+        <v>10916</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10630</v>
+        <v>10917</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10631</v>
+        <v>10918</v>
       </c>
       <c r="E3" s="3">
         <v>3440798.37</v>
       </c>
       <c r="F3" s="3">
-        <v>641802.73</v>
+        <v>712586.17</v>
       </c>
       <c r="G3" s="3">
-        <v>852334.58</v>
+        <v>932940.69</v>
       </c>
       <c r="H3" s="3">
-        <v>1494137.31</v>
+        <v>1645526.86</v>
       </c>
       <c r="I3" s="3">
-        <v>43.42</v>
+        <v>47.82</v>
       </c>
       <c r="J3" s="3">
-        <v>-1946661.06</v>
+        <v>-1795271.51</v>
       </c>
       <c r="K3" s="3">
-        <v>18140.62</v>
+        <v>19867.98</v>
       </c>
       <c r="L3" s="3">
         <v>1.21</v>
@@ -105481,168 +108064,168 @@
     </row>
     <row r="4" spans="8:8" ht="24.45">
       <c r="A4" s="2" t="s">
-        <v>10632</v>
+        <v>10919</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10633</v>
+        <v>10920</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10634</v>
+        <v>10921</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10635</v>
+        <v>10922</v>
       </c>
       <c r="E4" s="3">
         <v>6398516.07</v>
       </c>
       <c r="F4" s="3">
-        <v>1157521.41</v>
+        <v>1468000.68</v>
       </c>
       <c r="G4" s="3">
-        <v>1229262.16</v>
+        <v>969050.31</v>
       </c>
       <c r="H4" s="3">
-        <v>2386783.57</v>
+        <v>2437050.99</v>
       </c>
       <c r="I4" s="3">
-        <v>37.3</v>
+        <v>38.09</v>
       </c>
       <c r="J4" s="3">
-        <v>-4011732.5</v>
+        <v>-3961465.08</v>
       </c>
       <c r="K4" s="3">
-        <v>40391.81</v>
+        <v>44069.57</v>
       </c>
       <c r="L4" s="3">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="24.45">
       <c r="A5" s="2" t="s">
-        <v>10636</v>
+        <v>10923</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10637</v>
+        <v>10924</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10638</v>
+        <v>10925</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10639</v>
+        <v>10926</v>
       </c>
       <c r="E5" s="3">
         <v>7403170.5</v>
       </c>
       <c r="F5" s="3">
-        <v>2062117.78</v>
+        <v>2254982.7</v>
       </c>
       <c r="G5" s="3">
-        <v>944783.54</v>
+        <v>999113.31</v>
       </c>
       <c r="H5" s="3">
-        <v>3006901.32</v>
+        <v>3254096.01</v>
       </c>
       <c r="I5" s="3">
-        <v>40.62</v>
+        <v>43.96</v>
       </c>
       <c r="J5" s="3">
-        <v>-4396269.18</v>
+        <v>-4149074.49</v>
       </c>
       <c r="K5" s="3">
-        <v>49463.82</v>
+        <v>53419.62</v>
       </c>
       <c r="L5" s="3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="6" spans="8:8" ht="24.45">
       <c r="A6" s="2" t="s">
-        <v>10640</v>
+        <v>10927</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10641</v>
+        <v>10928</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10642</v>
+        <v>10929</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10643</v>
+        <v>10930</v>
       </c>
       <c r="E6" s="3">
         <v>7091695.63</v>
       </c>
       <c r="F6" s="3">
-        <v>2199143.37</v>
+        <v>2319193.6</v>
       </c>
       <c r="G6" s="3">
-        <v>901622.48</v>
+        <v>1185615.86</v>
       </c>
       <c r="H6" s="3">
-        <v>3100765.85</v>
+        <v>3504809.46</v>
       </c>
       <c r="I6" s="3">
-        <v>43.72</v>
+        <v>49.42</v>
       </c>
       <c r="J6" s="3">
-        <v>-3990929.78</v>
+        <v>-3586886.17</v>
       </c>
       <c r="K6" s="3">
-        <v>65747.78</v>
+        <v>73726.99</v>
       </c>
       <c r="L6" s="3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7" spans="8:8" ht="36.7">
       <c r="A7" s="2" t="s">
-        <v>10644</v>
+        <v>10931</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10645</v>
+        <v>10932</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10646</v>
+        <v>10933</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10647</v>
+        <v>10934</v>
       </c>
       <c r="E7" s="3">
         <v>4638385.13</v>
       </c>
       <c r="F7" s="3">
-        <v>1216852.58</v>
+        <v>1345052.07</v>
       </c>
       <c r="G7" s="3">
-        <v>1184871.19</v>
+        <v>1056178.02</v>
       </c>
       <c r="H7" s="3">
-        <v>2401723.77</v>
+        <v>2401230.09</v>
       </c>
       <c r="I7" s="3">
-        <v>51.78</v>
+        <v>51.77</v>
       </c>
       <c r="J7" s="3">
-        <v>-2236661.36</v>
+        <v>-2237155.04</v>
       </c>
       <c r="K7" s="3">
-        <v>40006.92</v>
+        <v>40500.6</v>
       </c>
       <c r="L7" s="3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="24.45">
       <c r="A8" s="2" t="s">
-        <v>10648</v>
+        <v>10935</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10649</v>
+        <v>10936</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10650</v>
+        <v>10937</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10651</v>
+        <v>10938</v>
       </c>
       <c r="E8" s="3">
         <v>7324761.7</v>
@@ -105651,36 +108234,36 @@
         <v>2322654.84</v>
       </c>
       <c r="G8" s="3">
-        <v>666351.74</v>
+        <v>916112.17</v>
       </c>
       <c r="H8" s="3">
-        <v>2989006.58</v>
+        <v>3238767.01</v>
       </c>
       <c r="I8" s="3">
-        <v>40.81</v>
+        <v>44.22</v>
       </c>
       <c r="J8" s="3">
-        <v>-4335755.12</v>
+        <v>-4085994.69</v>
       </c>
       <c r="K8" s="3">
         <v>35470.03</v>
       </c>
       <c r="L8" s="3">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="24.45">
       <c r="A9" s="2" t="s">
-        <v>10652</v>
+        <v>10939</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10653</v>
+        <v>10940</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10654</v>
+        <v>10941</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10655</v>
+        <v>10942</v>
       </c>
       <c r="E9" s="3">
         <v>6543653.55</v>
@@ -106812,7 +109395,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP78"/>
+  <dimension ref="A1:AQ78"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="9" max="9" customWidth="1" width="5.8984375" style="0"/>
@@ -110141,7 +112724,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AF79"/>
+  <dimension ref="A1:AG79"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <cols>
     <col min="3" max="3" customWidth="1" bestFit="1" width="10.0" style="29"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10943" count="10943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11230" count="11230">
   <si>
     <t>Region</t>
   </si>
@@ -97869,6 +97869,2589 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>Centina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Shil, Mr. Arjun Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Hasibur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fortuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Monzur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Origina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hossain, Mr. Md. Sakawat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Optima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>K71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rahman, Mr. Md. Moshiur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
